--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -508,25 +508,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>옵티시스</t>
+          <t>캡스톤파트너스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16120</v>
+        <v>4645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+30.00%</t>
+          <t>+29.93%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.31</v>
+        <v>-3.53</v>
       </c>
       <c r="E2" t="n">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="F2" t="n">
-        <v>1.13</v>
+        <v>2.95</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>12400</v>
+        <v>3575</v>
       </c>
       <c r="I2" t="n">
-        <v>1.44</v>
+        <v>6.48</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -557,48 +557,48 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>109080</t>
+          <t>452300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>109080</t>
+          <t>452300</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>캡스톤파트너스</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4645</v>
+        <v>7520</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+29.93%</t>
+          <t>+29.88%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-3.53</v>
+        <v>-0.28</v>
       </c>
       <c r="E3" t="n">
-        <v>172</v>
+        <v>309</v>
       </c>
       <c r="F3" t="n">
-        <v>2.95</v>
+        <v>18.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3575</v>
+        <v>5790</v>
       </c>
       <c r="I3" t="n">
-        <v>6.48</v>
+        <v>18.48</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -618,48 +618,48 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>452300</t>
+          <t>017900</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>452300</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>아크릴</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7520</v>
+        <v>37650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+29.88%</t>
+          <t>+19.33%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.28</v>
+        <v>-1.12</v>
       </c>
       <c r="E4" t="n">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="F4" t="n">
-        <v>18.2</v>
+        <v>3.71</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5790</v>
+        <v>31550</v>
       </c>
       <c r="I4" t="n">
-        <v>18.48</v>
+        <v>4.83</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,37 +679,37 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>0007C0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>0007C0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>아크릴</t>
+          <t>프로이천</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37650</v>
+        <v>2900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+19.33%</t>
+          <t>+18.37%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.12</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="F5" t="n">
-        <v>3.71</v>
+        <v>1.92</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>31550</v>
+        <v>2450</v>
       </c>
       <c r="I5" t="n">
-        <v>4.83</v>
+        <v>0.92</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -740,37 +740,37 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0007C0</t>
+          <t>321260</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0007C0</t>
+          <t>321260</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로이천</t>
+          <t>서울반도체</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2900</v>
+        <v>10300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+18.37%</t>
+          <t>+17.58%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>-0.83</v>
       </c>
       <c r="E6" t="n">
-        <v>261</v>
+        <v>152</v>
       </c>
       <c r="F6" t="n">
-        <v>1.92</v>
+        <v>7.85</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2450</v>
+        <v>8760</v>
       </c>
       <c r="I6" t="n">
-        <v>0.92</v>
+        <v>8.68</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -801,48 +801,48 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>321260</t>
+          <t>046890</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>321260</t>
+          <t>046890</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>서울반도체</t>
+          <t>풍산홀딩스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10300</v>
+        <v>54800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+17.58%</t>
+          <t>+15.98%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.83</v>
+        <v>-1.21</v>
       </c>
       <c r="E7" t="n">
-        <v>152</v>
+        <v>786</v>
       </c>
       <c r="F7" t="n">
-        <v>7.85</v>
+        <v>11.62</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8760</v>
+        <v>47250</v>
       </c>
       <c r="I7" t="n">
-        <v>8.68</v>
+        <v>12.83</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -862,48 +862,48 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>046890</t>
+          <t>005810</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>046890</t>
+          <t>005810</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>풍산홀딩스</t>
+          <t>창해에탄올</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54800</v>
+        <v>12010</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+15.98%</t>
+          <t>+15.93%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.21</v>
+        <v>-0.54</v>
       </c>
       <c r="E8" t="n">
-        <v>782</v>
+        <v>572</v>
       </c>
       <c r="F8" t="n">
-        <v>11.62</v>
+        <v>1.37</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>47250</v>
+        <v>10360</v>
       </c>
       <c r="I8" t="n">
-        <v>12.83</v>
+        <v>1.91</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -923,37 +923,37 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>005810</t>
+          <t>004650</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>005810</t>
+          <t>004650</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>창해에탄올</t>
+          <t>리센스메디컬</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12010</v>
+        <v>23600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+15.93%</t>
+          <t>+12.38%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.54</v>
+        <v>0.74</v>
       </c>
       <c r="E9" t="n">
-        <v>569</v>
+        <v>246</v>
       </c>
       <c r="F9" t="n">
-        <v>1.37</v>
+        <v>1.91</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10360</v>
+        <v>21000</v>
       </c>
       <c r="I9" t="n">
-        <v>1.91</v>
+        <v>1.17</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,37 +984,37 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>004650</t>
+          <t>394420</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>004650</t>
+          <t>394420</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>리센스메디컬</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23600</v>
+        <v>22850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+12.38%</t>
+          <t>+9.86%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.74</v>
+        <v>1.11</v>
       </c>
       <c r="E10" t="n">
-        <v>246</v>
+        <v>1017</v>
       </c>
       <c r="F10" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>21000</v>
+        <v>20800</v>
       </c>
       <c r="I10" t="n">
-        <v>1.17</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1045,48 +1045,48 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>394420</t>
+          <t>024060</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>394420</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22850</v>
+        <v>185000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+9.86%</t>
+          <t>+8.44%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.11</v>
+        <v>0.45</v>
       </c>
       <c r="E11" t="n">
-        <v>993</v>
+        <v>286</v>
       </c>
       <c r="F11" t="n">
-        <v>1.22</v>
+        <v>19.75</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>20800</v>
+        <v>170600</v>
       </c>
       <c r="I11" t="n">
-        <v>0.11</v>
+        <v>19.3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1106,48 +1106,48 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>066970</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>파워넷</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>185000</v>
+        <v>5680</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+8.44%</t>
+          <t>+8.19%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.45</v>
+        <v>-1.94</v>
       </c>
       <c r="E12" t="n">
-        <v>283</v>
+        <v>191</v>
       </c>
       <c r="F12" t="n">
-        <v>19.75</v>
+        <v>2.48</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>170600</v>
+        <v>5250</v>
       </c>
       <c r="I12" t="n">
-        <v>19.3</v>
+        <v>4.42</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1167,48 +1167,48 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>037030</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>037030</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>파워넷</t>
+          <t>에코프로머티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5680</v>
+        <v>73100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+8.19%</t>
+          <t>+6.10%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.94</v>
+        <v>0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>191</v>
+        <v>283</v>
       </c>
       <c r="F13" t="n">
-        <v>2.48</v>
+        <v>16.74</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5250</v>
+        <v>68900</v>
       </c>
       <c r="I13" t="n">
-        <v>4.42</v>
+        <v>16.63</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1228,37 +1228,37 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>037030</t>
+          <t>450080</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>037030</t>
+          <t>450080</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>에코프로머티</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>73100</v>
+        <v>1537000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+6.10%</t>
+          <t>+6.00%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
       <c r="E14" t="n">
-        <v>282</v>
+        <v>133</v>
       </c>
       <c r="F14" t="n">
-        <v>16.74</v>
+        <v>45.38</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>68900</v>
+        <v>1450000</v>
       </c>
       <c r="I14" t="n">
-        <v>16.63</v>
+        <v>45.19</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1289,48 +1289,48 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>450080</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>450080</t>
+          <t>012450</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>풍국주정</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1537000</v>
+        <v>11140</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+6.00%</t>
+          <t>+5.00%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="E15" t="n">
         <v>130</v>
       </c>
       <c r="F15" t="n">
-        <v>45.38</v>
+        <v>0.9</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1450000</v>
+        <v>10610</v>
       </c>
       <c r="I15" t="n">
-        <v>45.19</v>
+        <v>0.93</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1350,48 +1350,48 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>023900</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>023900</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>풍국주정</t>
+          <t>한국ANKOR유전</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11140</v>
+        <v>280</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+5.00%</t>
+          <t>+4.87%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.03</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>10610</v>
+        <v>267</v>
       </c>
       <c r="I16" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1411,37 +1411,37 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>023900</t>
+          <t>152550</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>023900</t>
+          <t>152550</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한국ANKOR유전</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>280</v>
+        <v>47800</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+4.87%</t>
+          <t>+4.71%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.14</v>
       </c>
       <c r="E17" t="n">
-        <v>146</v>
+        <v>768</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8</v>
+        <v>45.1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>267</v>
+        <v>45650</v>
       </c>
       <c r="I17" t="n">
-        <v>0.86</v>
+        <v>45.24</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1472,48 +1472,48 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>152550</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>152550</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>세림B&amp;G</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47800</v>
+        <v>2385</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+4.71%</t>
+          <t>+4.61%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.14</v>
+        <v>0.41</v>
       </c>
       <c r="E18" t="n">
-        <v>764</v>
+        <v>158</v>
       </c>
       <c r="F18" t="n">
-        <v>45.1</v>
+        <v>2.92</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>45650</v>
+        <v>2280</v>
       </c>
       <c r="I18" t="n">
-        <v>45.24</v>
+        <v>2.51</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,48 +1533,48 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>340440</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>340440</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>세림B&amp;G</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2385</v>
+        <v>46400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+4.61%</t>
+          <t>+3.46%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.41</v>
+        <v>0.14</v>
       </c>
       <c r="E19" t="n">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F19" t="n">
-        <v>2.92</v>
+        <v>29.58</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2280</v>
+        <v>44850</v>
       </c>
       <c r="I19" t="n">
-        <v>2.51</v>
+        <v>29.44</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1594,37 +1594,37 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>340440</t>
+          <t>035720</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>340440</t>
+          <t>035720</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>46400</v>
+        <v>916000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>+3.46%</t>
+          <t>+3.39%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>170</v>
+        <v>1029</v>
       </c>
       <c r="F20" t="n">
-        <v>29.58</v>
+        <v>52.69</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>44850</v>
+        <v>886000</v>
       </c>
       <c r="I20" t="n">
-        <v>29.44</v>
+        <v>52.61</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1655,37 +1655,37 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>916000</v>
+        <v>131700</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>+3.39%</t>
+          <t>+3.21%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="E21" t="n">
-        <v>994</v>
+        <v>451</v>
       </c>
       <c r="F21" t="n">
-        <v>52.69</v>
+        <v>9.01</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>886000</v>
+        <v>127600</v>
       </c>
       <c r="I21" t="n">
-        <v>52.61</v>
+        <v>8.84</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1716,37 +1716,37 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>272210</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>남선알미늄</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>131700</v>
+        <v>2180</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>+3.21%</t>
+          <t>+2.35%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.17</v>
+        <v>-0.7</v>
       </c>
       <c r="E22" t="n">
-        <v>446</v>
+        <v>482</v>
       </c>
       <c r="F22" t="n">
-        <v>9.01</v>
+        <v>1.9</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>127600</v>
+        <v>2130</v>
       </c>
       <c r="I22" t="n">
-        <v>8.84</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1777,37 +1777,37 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>008350</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>008350</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>남선알미늄</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2180</v>
+        <v>196500</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>+2.35%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.7</v>
+        <v>-0.05</v>
       </c>
       <c r="E23" t="n">
-        <v>476</v>
+        <v>1189</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9</v>
+        <v>48.39</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2130</v>
+        <v>193100</v>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>48.44</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1838,48 +1838,48 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>008350</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>008350</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>196500</v>
+        <v>7070</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.05</v>
+        <v>0.54</v>
       </c>
       <c r="E24" t="n">
-        <v>1008</v>
+        <v>313</v>
       </c>
       <c r="F24" t="n">
-        <v>48.39</v>
+        <v>2.82</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>193100</v>
+        <v>6950</v>
       </c>
       <c r="I24" t="n">
-        <v>48.44</v>
+        <v>2.28</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1899,45 +1899,45 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>046970</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>대영포장</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7070</v>
+        <v>1288</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>+1.73%</t>
+          <t>+1.42%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.54</v>
+        <v>-0.93</v>
       </c>
       <c r="E25" t="n">
-        <v>312</v>
+        <v>156</v>
       </c>
       <c r="F25" t="n">
-        <v>2.82</v>
+        <v>1.35</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6950</v>
+        <v>1270</v>
       </c>
       <c r="I25" t="n">
         <v>2.28</v>
@@ -1960,37 +1960,37 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>014160</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>014160</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>대영포장</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1288</v>
+        <v>130900</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>+1.39%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.93</v>
+        <v>-0.06</v>
       </c>
       <c r="E26" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F26" t="n">
-        <v>1.35</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1270</v>
+        <v>129100</v>
       </c>
       <c r="I26" t="n">
-        <v>2.28</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2021,48 +2021,48 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>014160</t>
+          <t>005935</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>014160</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>기가레인</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>130900</v>
+        <v>2400</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.06</v>
+        <v>-0.34</v>
       </c>
       <c r="E27" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="F27" t="n">
-        <v>76.15000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>129100</v>
+        <v>2390</v>
       </c>
       <c r="I27" t="n">
-        <v>76.20999999999999</v>
+        <v>1.87</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2082,48 +2082,48 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>049080</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>049080</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>기가레인</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2400</v>
+        <v>17350</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.34</v>
+        <v>-0.08</v>
       </c>
       <c r="E28" t="n">
-        <v>199</v>
+        <v>339</v>
       </c>
       <c r="F28" t="n">
-        <v>1.53</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2390</v>
+        <v>17310</v>
       </c>
       <c r="I28" t="n">
-        <v>1.87</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2143,37 +2143,37 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>049080</t>
+          <t>047040</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>049080</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17350</v>
+        <v>3795</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-0.08</v>
+        <v>0.18</v>
       </c>
       <c r="E29" t="n">
-        <v>336</v>
+        <v>804</v>
       </c>
       <c r="F29" t="n">
-        <v>9.550000000000001</v>
+        <v>1.54</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>17310</v>
+        <v>3790</v>
       </c>
       <c r="I29" t="n">
-        <v>9.630000000000001</v>
+        <v>1.36</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2204,37 +2204,37 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>003280</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3795</v>
+        <v>9870</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.18</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>783</v>
+        <v>201</v>
       </c>
       <c r="F30" t="n">
-        <v>1.54</v>
+        <v>7.18</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3790</v>
+        <v>9900</v>
       </c>
       <c r="I30" t="n">
-        <v>1.36</v>
+        <v>6.62</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2265,48 +2265,48 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>에코플라스틱</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9870</v>
+        <v>4000</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.76</v>
       </c>
       <c r="E31" t="n">
-        <v>199</v>
+        <v>130</v>
       </c>
       <c r="F31" t="n">
-        <v>7.18</v>
+        <v>0.72</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>9900</v>
+        <v>4020</v>
       </c>
       <c r="I31" t="n">
-        <v>6.62</v>
+        <v>1.48</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>038110</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>038110</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
         <v>-0.28</v>
       </c>
       <c r="E32" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F32" t="n">
         <v>0.74</v>
@@ -2414,7 +2414,7 @@
         <v>0.04</v>
       </c>
       <c r="E33" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F33" t="n">
         <v>35.07</v>
@@ -2475,7 +2475,7 @@
         <v>0.72</v>
       </c>
       <c r="E34" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F34" t="n">
         <v>8.98</v>
@@ -2536,7 +2536,7 @@
         <v>-0.37</v>
       </c>
       <c r="E35" t="n">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F35" t="n">
         <v>12.66</v>
@@ -2658,7 +2658,7 @@
         <v>0.42</v>
       </c>
       <c r="E37" t="n">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F37" t="n">
         <v>6.41</v>
@@ -2719,7 +2719,7 @@
         <v>0.16</v>
       </c>
       <c r="E38" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F38" t="n">
         <v>44.93</v>
@@ -2780,7 +2780,7 @@
         <v>0.74</v>
       </c>
       <c r="E39" t="n">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F39" t="n">
         <v>0.79</v>
@@ -2841,7 +2841,7 @@
         <v>-2.41</v>
       </c>
       <c r="E40" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F40" t="n">
         <v>3.74</v>
@@ -2902,7 +2902,7 @@
         <v>0.06</v>
       </c>
       <c r="E41" t="n">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="F41" t="n">
         <v>4.74</v>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -523,7 +523,7 @@
         <v>-3.53</v>
       </c>
       <c r="E2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F2" t="n">
         <v>2.95</v>
@@ -584,7 +584,7 @@
         <v>-0.28</v>
       </c>
       <c r="E3" t="n">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="F3" t="n">
         <v>18.2</v>
@@ -645,7 +645,7 @@
         <v>-1.12</v>
       </c>
       <c r="E4" t="n">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F4" t="n">
         <v>3.71</v>
@@ -706,7 +706,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F5" t="n">
         <v>1.92</v>
@@ -767,7 +767,7 @@
         <v>-0.83</v>
       </c>
       <c r="E6" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F6" t="n">
         <v>7.85</v>
@@ -828,7 +828,7 @@
         <v>-1.21</v>
       </c>
       <c r="E7" t="n">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="F7" t="n">
         <v>11.62</v>
@@ -889,7 +889,7 @@
         <v>-0.54</v>
       </c>
       <c r="E8" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F8" t="n">
         <v>1.37</v>
@@ -950,7 +950,7 @@
         <v>0.74</v>
       </c>
       <c r="E9" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F9" t="n">
         <v>1.91</v>
@@ -1011,7 +1011,7 @@
         <v>1.11</v>
       </c>
       <c r="E10" t="n">
-        <v>1017</v>
+        <v>1072</v>
       </c>
       <c r="F10" t="n">
         <v>1.22</v>
@@ -1072,7 +1072,7 @@
         <v>0.45</v>
       </c>
       <c r="E11" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F11" t="n">
         <v>19.75</v>
@@ -1194,7 +1194,7 @@
         <v>0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F13" t="n">
         <v>16.74</v>
@@ -1255,7 +1255,7 @@
         <v>0.19</v>
       </c>
       <c r="E14" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F14" t="n">
         <v>45.38</v>
@@ -1377,7 +1377,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F16" t="n">
         <v>1.8</v>
@@ -1438,7 +1438,7 @@
         <v>-0.14</v>
       </c>
       <c r="E17" t="n">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="F17" t="n">
         <v>45.1</v>
@@ -1499,7 +1499,7 @@
         <v>0.41</v>
       </c>
       <c r="E18" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F18" t="n">
         <v>2.92</v>
@@ -1621,7 +1621,7 @@
         <v>0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>1029</v>
+        <v>1096</v>
       </c>
       <c r="F20" t="n">
         <v>52.69</v>
@@ -1682,7 +1682,7 @@
         <v>0.17</v>
       </c>
       <c r="E21" t="n">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F21" t="n">
         <v>9.01</v>
@@ -1743,7 +1743,7 @@
         <v>-0.7</v>
       </c>
       <c r="E22" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F22" t="n">
         <v>1.9</v>
@@ -1804,7 +1804,7 @@
         <v>-0.05</v>
       </c>
       <c r="E23" t="n">
-        <v>1189</v>
+        <v>1521</v>
       </c>
       <c r="F23" t="n">
         <v>48.39</v>
@@ -1926,7 +1926,7 @@
         <v>-0.93</v>
       </c>
       <c r="E25" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F25" t="n">
         <v>1.35</v>
@@ -2048,7 +2048,7 @@
         <v>-0.34</v>
       </c>
       <c r="E27" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F27" t="n">
         <v>1.53</v>
@@ -2109,7 +2109,7 @@
         <v>-0.08</v>
       </c>
       <c r="E28" t="n">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F28" t="n">
         <v>9.550000000000001</v>
@@ -2170,7 +2170,7 @@
         <v>0.18</v>
       </c>
       <c r="E29" t="n">
-        <v>804</v>
+        <v>832</v>
       </c>
       <c r="F29" t="n">
         <v>1.54</v>
@@ -2231,7 +2231,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F30" t="n">
         <v>7.18</v>
@@ -2353,7 +2353,7 @@
         <v>-0.28</v>
       </c>
       <c r="E32" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F32" t="n">
         <v>0.74</v>
@@ -2414,7 +2414,7 @@
         <v>0.04</v>
       </c>
       <c r="E33" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F33" t="n">
         <v>35.07</v>
@@ -2475,7 +2475,7 @@
         <v>0.72</v>
       </c>
       <c r="E34" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F34" t="n">
         <v>8.98</v>
@@ -2536,7 +2536,7 @@
         <v>-0.37</v>
       </c>
       <c r="E35" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F35" t="n">
         <v>12.66</v>
@@ -2597,7 +2597,7 @@
         <v>0.61</v>
       </c>
       <c r="E36" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F36" t="n">
         <v>9.09</v>
@@ -2658,7 +2658,7 @@
         <v>0.42</v>
       </c>
       <c r="E37" t="n">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="F37" t="n">
         <v>6.41</v>
@@ -2719,7 +2719,7 @@
         <v>0.16</v>
       </c>
       <c r="E38" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F38" t="n">
         <v>44.93</v>
@@ -2780,7 +2780,7 @@
         <v>0.74</v>
       </c>
       <c r="E39" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F39" t="n">
         <v>0.79</v>
@@ -2841,7 +2841,7 @@
         <v>-2.41</v>
       </c>
       <c r="E40" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="F40" t="n">
         <v>3.74</v>
@@ -2902,7 +2902,7 @@
         <v>0.06</v>
       </c>
       <c r="E41" t="n">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="F41" t="n">
         <v>4.74</v>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,45 +503,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>지투파워</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6320</v>
+        <v>14990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+28.46%</t>
+          <t>+15.93%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.02</v>
+        <v>-1</v>
       </c>
       <c r="E2" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F2" t="n">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4920</v>
+        <v>12930</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>3.68</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 152건 토론 포착</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
+          <t>[데이터 분석] '시장 주도주' 중심 159건 토론 포착</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -552,229 +550,59 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>388050</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71900</v>
+        <v>3560</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+10.11%</t>
+          <t>-8.37%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="E3" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F3" t="n">
-        <v>9.58</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66500</v>
+        <v>3885</v>
       </c>
       <c r="I3" t="n">
-        <v>9.59</v>
+        <v>2.46</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 160건 토론 포착</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+          <t>[데이터 분석] '시장 주도주' 중심 158건 토론 포착</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
       <c r="N3" t="inlineStr">
-        <is>
-          <t>006800</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>삼성전자</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>209500</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>+4.23%</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="E4" t="n">
-        <v>98</v>
-      </c>
-      <c r="F4" t="n">
-        <v>48.62</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>206000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>48.65</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>[데이터 분석] '시장 주도주' 중심 98건 토론 포착</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>대한광통신</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>19530</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>-1.71%</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="E5" t="n">
-        <v>159</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>17770</v>
-      </c>
-      <c r="I5" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>[데이터 분석] '시장 주도주' 중심 159건 토론 포착</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>010170</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>한국첨단소재</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3825</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>-6.71%</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>104</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>4055</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>[데이터 분석] '시장 주도주' 중심 104건 토론 포착</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr">
         <is>
           <t>062970</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,60 +563,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25500</v>
+        <v>220500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+8.51%</t>
+          <t>+9.43%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>113</v>
+        <v>481</v>
       </c>
       <c r="H2" t="n">
-        <v>0.16</v>
+        <v>29.46</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>23500</v>
+        <v>201500</v>
       </c>
       <c r="K2" t="n">
-        <v>23200</v>
+        <v>212500</v>
       </c>
       <c r="L2" t="n">
-        <v>25500</v>
+        <v>222500</v>
       </c>
       <c r="M2" t="n">
-        <v>23000</v>
+        <v>212500</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>29.51</v>
       </c>
       <c r="O2" t="n">
-        <v>27429090425</v>
+        <v>78807675250</v>
       </c>
       <c r="P2" t="n">
-        <v>28750</v>
+        <v>438000</v>
       </c>
       <c r="Q2" t="n">
-        <v>8200</v>
+        <v>74700</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>스카이랩스, CART 혈압계 관련 뉴스 및 임상 연구 결과 발표. 신사업 진출 기대감 있으나, 적자 규모 대비 시가총액 논란 및 주가 변동성 우려 존재.</t>
+          <t>로봇 사업 진출 기대감에 따른 주가 상승 전망. 3분기 영업이익 호조 예상.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['CART', '임상연구', '신사업']</t>
+          <t>['로봇', '액츄에이터', '영업이익']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1738000</v>
+        <v>1748000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+5.53%</t>
+          <t>+6.13%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>636</v>
+        <v>723</v>
       </c>
       <c r="F3" t="n">
-        <v>403</v>
+        <v>448</v>
       </c>
       <c r="G3" t="n">
-        <v>2606</v>
+        <v>2796</v>
       </c>
       <c r="H3" t="n">
         <v>50.5</v>
@@ -693,16 +693,16 @@
         <v>1737000</v>
       </c>
       <c r="L3" t="n">
-        <v>1745000</v>
+        <v>1751000</v>
       </c>
       <c r="M3" t="n">
-        <v>1735000</v>
+        <v>1734000</v>
       </c>
       <c r="N3" t="n">
         <v>50.45</v>
       </c>
       <c r="O3" t="n">
-        <v>300358177500</v>
+        <v>751901631500</v>
       </c>
       <c r="P3" t="n">
         <v>2987000</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>266500</v>
+        <v>267250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+4.31%</t>
+          <t>+4.60%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="F4" t="n">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="G4" t="n">
-        <v>2354</v>
+        <v>2426</v>
       </c>
       <c r="H4" t="n">
         <v>46.73</v>
@@ -788,13 +788,13 @@
         <v>267500</v>
       </c>
       <c r="M4" t="n">
-        <v>266500</v>
+        <v>265500</v>
       </c>
       <c r="N4" t="n">
         <v>46.71</v>
       </c>
       <c r="O4" t="n">
-        <v>140359478000</v>
+        <v>408600028750</v>
       </c>
       <c r="P4" t="n">
         <v>374500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성전자, 3개월 보유 시 5% 배당 기대감 및 목표 주가 50~60만+a 전망. 단기적 주가 상승 기대감 존재하나, 검증 가능한 구체적 근거는 미흡.</t>
+          <t>단기적 상승 및 목표주가 상향 전망. 5% 배당 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['배당', '목표주가', '실적']</t>
+          <t>['배당', '목표주가', '상승']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5170</v>
+        <v>23900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-9.93%</t>
+          <t>+1.70%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5740</v>
+        <v>23500</v>
       </c>
       <c r="K5" t="n">
-        <v>5250</v>
+        <v>23200</v>
       </c>
       <c r="L5" t="n">
-        <v>5260</v>
+        <v>25600</v>
       </c>
       <c r="M5" t="n">
-        <v>5000</v>
+        <v>22800</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>503851040</v>
+        <v>97173794975</v>
       </c>
       <c r="P5" t="n">
-        <v>9680</v>
+        <v>28750</v>
       </c>
       <c r="Q5" t="n">
-        <v>371</v>
+        <v>8200</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -902,27 +902,119 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>본느, 반기보고서 제출 지연 악재 발생. 하한가 예상 및 주가 하락 우려 증폭. 긍정적인 매수세 유입 가능성은 낮음.</t>
+          <t>혈압계 뉴스 및 신사업 진출 관련 기대감. 시총 대비 적자 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['혈압계', '신사업', '적자']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5290</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-7.84%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>54</v>
+      </c>
+      <c r="F6" t="n">
+        <v>29</v>
+      </c>
+      <c r="G6" t="n">
+        <v>109</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1252158300</v>
+      </c>
+      <c r="P6" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>371</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 악재 발생. 주가 하락세.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
         <v>0.1</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>['반기보고서', '악재', '하한가']</t>
-        </is>
-      </c>
-      <c r="X5" t="n">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['반기보고서', '악재', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
         <v>1</v>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>226340</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>220500</v>
+        <v>50400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+9.43%</t>
+          <t>+14.94%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.05</v>
+        <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>481</v>
+        <v>172</v>
       </c>
       <c r="H2" t="n">
-        <v>29.46</v>
+        <v>14.18</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>201500</v>
+        <v>43850</v>
       </c>
       <c r="K2" t="n">
-        <v>212500</v>
+        <v>45650</v>
       </c>
       <c r="L2" t="n">
-        <v>222500</v>
+        <v>52300</v>
       </c>
       <c r="M2" t="n">
-        <v>212500</v>
+        <v>45650</v>
       </c>
       <c r="N2" t="n">
-        <v>29.51</v>
+        <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>78807675250</v>
+        <v>38270895575</v>
       </c>
       <c r="P2" t="n">
-        <v>438000</v>
+        <v>108900</v>
       </c>
       <c r="Q2" t="n">
-        <v>74700</v>
+        <v>18230</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇 사업 진출 기대감에 따른 주가 상승 전망. 3분기 영업이익 호조 예상.</t>
+          <t>데이터센터 수주 기대감과 공매도 감소 추세. 5만원 돌파 및 연말 최고가 갱신 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇', '액츄에이터', '영업이익']</t>
+          <t>['데이터센터', '수주', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1748000</v>
+        <v>221000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+6.13%</t>
+          <t>+9.68%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>723</v>
+        <v>161</v>
       </c>
       <c r="F3" t="n">
-        <v>448</v>
+        <v>98</v>
       </c>
       <c r="G3" t="n">
-        <v>2796</v>
+        <v>515</v>
       </c>
       <c r="H3" t="n">
-        <v>50.5</v>
+        <v>29.46</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1647000</v>
+        <v>201500</v>
       </c>
       <c r="K3" t="n">
-        <v>1737000</v>
+        <v>212500</v>
       </c>
       <c r="L3" t="n">
-        <v>1751000</v>
+        <v>222500</v>
       </c>
       <c r="M3" t="n">
-        <v>1734000</v>
+        <v>212500</v>
       </c>
       <c r="N3" t="n">
-        <v>50.45</v>
+        <v>29.51</v>
       </c>
       <c r="O3" t="n">
-        <v>751901631500</v>
+        <v>110172002250</v>
       </c>
       <c r="P3" t="n">
-        <v>2987000</v>
+        <v>438000</v>
       </c>
       <c r="Q3" t="n">
-        <v>274000</v>
+        <v>74700</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>SK하이닉스, 외국인 매수세 유입 및 나스닥 선물 상승 출발 등 긍정적 신호 포착. 금주 200 돌파 전망 강하나, 구체적인 실적 기반 분석은 부족.</t>
+          <t>로봇 액츄에이터 사업 관련 긍정적 뉴스. 3분기 영업이익 컨센서스 상회 기대 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['외국인매수', '나스닥', '주가예측']</t>
+          <t>['로봇', '액츄에이터', '영업이익']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>267250</v>
+        <v>1744000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+4.60%</t>
+          <t>+5.89%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>552</v>
+        <v>798</v>
       </c>
       <c r="F4" t="n">
-        <v>345</v>
+        <v>484</v>
       </c>
       <c r="G4" t="n">
-        <v>2426</v>
+        <v>3024</v>
       </c>
       <c r="H4" t="n">
-        <v>46.73</v>
+        <v>50.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>255500</v>
+        <v>1647000</v>
       </c>
       <c r="K4" t="n">
-        <v>267000</v>
+        <v>1737000</v>
       </c>
       <c r="L4" t="n">
-        <v>267500</v>
+        <v>1751000</v>
       </c>
       <c r="M4" t="n">
-        <v>265500</v>
+        <v>1734000</v>
       </c>
       <c r="N4" t="n">
-        <v>46.71</v>
+        <v>50.45</v>
       </c>
       <c r="O4" t="n">
-        <v>408600028750</v>
+        <v>970356252000</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q4" t="n">
-        <v>69600</v>
+        <v>274000</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>147000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>단기적 상승 및 목표주가 상향 전망. 5% 배당 기대.</t>
+          <t>외국인 매수세 유입 및 나스닥 선물 상승 출발. 연말 20만원 돌파 및 사상 최고가 갱신 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['배당', '목표주가', '상승']</t>
+          <t>['외국인', '나스닥', '자사주매입']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23900</v>
+        <v>266000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+1.70%</t>
+          <t>+4.11%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>121</v>
+        <v>599</v>
       </c>
       <c r="F5" t="n">
-        <v>79</v>
+        <v>369</v>
       </c>
       <c r="G5" t="n">
-        <v>135</v>
+        <v>2535</v>
       </c>
       <c r="H5" t="n">
-        <v>0.16</v>
+        <v>46.73</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>23500</v>
+        <v>255500</v>
       </c>
       <c r="K5" t="n">
-        <v>23200</v>
+        <v>267000</v>
       </c>
       <c r="L5" t="n">
-        <v>25600</v>
+        <v>268000</v>
       </c>
       <c r="M5" t="n">
-        <v>22800</v>
+        <v>265500</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>46.71</v>
       </c>
       <c r="O5" t="n">
-        <v>97173794975</v>
+        <v>611300990250</v>
       </c>
       <c r="P5" t="n">
-        <v>28750</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>8200</v>
+        <v>69600</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>710000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>혈압계 뉴스 및 신사업 진출 관련 기대감. 시총 대비 적자 우려.</t>
+          <t>단기적 상승 및 목표주가 상향 전망. 5% 배당 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['혈압계', '신사업', '적자']</t>
+          <t>['배당', '목표주가', '상승']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5290</v>
+        <v>24100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-7.84%</t>
+          <t>+2.55%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="G6" t="n">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,58 +963,150 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5740</v>
+        <v>23500</v>
       </c>
       <c r="K6" t="n">
-        <v>5250</v>
+        <v>23200</v>
       </c>
       <c r="L6" t="n">
-        <v>5420</v>
+        <v>25600</v>
       </c>
       <c r="M6" t="n">
-        <v>5000</v>
+        <v>22800</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1252158300</v>
+        <v>129936625950</v>
       </c>
       <c r="P6" t="n">
-        <v>9680</v>
+        <v>28750</v>
       </c>
       <c r="Q6" t="n">
-        <v>371</v>
+        <v>8200</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-13000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 악재 발생. 주가 하락세.</t>
+          <t>CART 혈압계 관련 뉴스 호재. 그러나 단기 하락 가능성 및 횡보장 우려도 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '주가 하락']</t>
+          <t>['CART', '혈압계', '뉴스']</t>
         </is>
       </c>
       <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5220</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-9.06%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>56</v>
+      </c>
+      <c r="F7" t="n">
+        <v>29</v>
+      </c>
+      <c r="G7" t="n">
+        <v>129</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1512181950</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>371</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 악재 발생. 조선일보 기사 통해 하한가 및 상장폐지 가능성 제기.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['반기보고서', '악재', '조선일보']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>226340</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50400</v>
+        <v>52000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+14.94%</t>
+          <t>+18.59%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>172</v>
+        <v>224</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>38270895575</v>
+        <v>47109199625</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>데이터센터 수주 기대감과 공매도 감소 추세. 5만원 돌파 및 연말 최고가 갱신 전망.</t>
+          <t>매수세 유입 및 5% 돌파 후 수익 전환 기대. 전고점 돌파 및 연말 사상 최고가 갱신 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['데이터센터', '수주', '공매도']</t>
+          <t>['공매도', '추세', '최고가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>221000</v>
+        <v>3770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+9.68%</t>
+          <t>+15.47%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.05</v>
+        <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>161</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>515</v>
+        <v>45</v>
       </c>
       <c r="H3" t="n">
-        <v>29.46</v>
+        <v>1.25</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>201500</v>
+        <v>3265</v>
       </c>
       <c r="K3" t="n">
-        <v>212500</v>
+        <v>3200</v>
       </c>
       <c r="L3" t="n">
-        <v>222500</v>
+        <v>3900</v>
       </c>
       <c r="M3" t="n">
-        <v>212500</v>
+        <v>3185</v>
       </c>
       <c r="N3" t="n">
-        <v>29.51</v>
+        <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>110172002250</v>
+        <v>94555482044</v>
       </c>
       <c r="P3" t="n">
-        <v>438000</v>
+        <v>3900</v>
       </c>
       <c r="Q3" t="n">
-        <v>74700</v>
+        <v>1246</v>
       </c>
       <c r="R3" t="n">
-        <v>190000</v>
+        <v>419000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇 액츄에이터 사업 관련 긍정적 뉴스. 3분기 영업이익 컨센서스 상회 기대 및 주가 상승 전망.</t>
+          <t>탈모약 관련 기대감 및 3연상 가능성 언급. 5천원 목표가 설정 및 10% 이상 상승.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇', '액츄에이터', '영업이익']</t>
+          <t>['탈모약', '3연상', '목표가']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1744000</v>
+        <v>224500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+5.89%</t>
+          <t>+11.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>798</v>
+        <v>204</v>
       </c>
       <c r="F4" t="n">
-        <v>484</v>
+        <v>126</v>
       </c>
       <c r="G4" t="n">
-        <v>3024</v>
+        <v>576</v>
       </c>
       <c r="H4" t="n">
-        <v>50.5</v>
+        <v>29.46</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1647000</v>
+        <v>201500</v>
       </c>
       <c r="K4" t="n">
-        <v>1737000</v>
+        <v>212500</v>
       </c>
       <c r="L4" t="n">
-        <v>1751000</v>
+        <v>225500</v>
       </c>
       <c r="M4" t="n">
-        <v>1734000</v>
+        <v>212500</v>
       </c>
       <c r="N4" t="n">
-        <v>50.45</v>
+        <v>29.51</v>
       </c>
       <c r="O4" t="n">
-        <v>970356252000</v>
+        <v>162543542750</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>438000</v>
       </c>
       <c r="Q4" t="n">
-        <v>274000</v>
+        <v>74700</v>
       </c>
       <c r="R4" t="n">
-        <v>147000</v>
+        <v>190000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입 및 나스닥 선물 상승 출발. 연말 20만원 돌파 및 사상 최고가 갱신 기대.</t>
+          <t>로봇 액츄에이터 부품 사업 관련 뉴스 기반 23만 탈환 기대. 3분기 영업이익 컨센서스 1조 1천억 예상.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['외국인', '나스닥', '자사주매입']</t>
+          <t>['로봇', '액츄에이터', '컨센서스']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>266000</v>
+        <v>1743000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+4.11%</t>
+          <t>+5.83%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>599</v>
+        <v>796</v>
       </c>
       <c r="F5" t="n">
-        <v>369</v>
+        <v>469</v>
       </c>
       <c r="G5" t="n">
-        <v>2535</v>
+        <v>2634</v>
       </c>
       <c r="H5" t="n">
-        <v>46.73</v>
+        <v>50.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>255500</v>
+        <v>1647000</v>
       </c>
       <c r="K5" t="n">
-        <v>267000</v>
+        <v>1737000</v>
       </c>
       <c r="L5" t="n">
-        <v>268000</v>
+        <v>1751000</v>
       </c>
       <c r="M5" t="n">
-        <v>265500</v>
+        <v>1734000</v>
       </c>
       <c r="N5" t="n">
-        <v>46.71</v>
+        <v>50.45</v>
       </c>
       <c r="O5" t="n">
-        <v>611300990250</v>
+        <v>1152379595000</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>69600</v>
+        <v>274000</v>
       </c>
       <c r="R5" t="n">
-        <v>710000</v>
+        <v>147000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>단기적 상승 및 목표주가 상향 전망. 5% 배당 기대.</t>
+          <t>외국인 매수세 유입 및 ADR 상승에 따른 주가 상승 기대. 200 돌파 및 180만원 목표 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['배당', '목표주가', '상승']</t>
+          <t>['외국인', 'ADR', '주가예측']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24100</v>
+        <v>266000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+2.55%</t>
+          <t>+4.11%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>156</v>
+        <v>643</v>
       </c>
       <c r="F6" t="n">
-        <v>89</v>
+        <v>394</v>
       </c>
       <c r="G6" t="n">
-        <v>172</v>
+        <v>2687</v>
       </c>
       <c r="H6" t="n">
-        <v>0.16</v>
+        <v>46.73</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>23500</v>
+        <v>255500</v>
       </c>
       <c r="K6" t="n">
-        <v>23200</v>
+        <v>267000</v>
       </c>
       <c r="L6" t="n">
-        <v>25600</v>
+        <v>268000</v>
       </c>
       <c r="M6" t="n">
-        <v>22800</v>
+        <v>265500</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>46.71</v>
       </c>
       <c r="O6" t="n">
-        <v>129936625950</v>
+        <v>774384559500</v>
       </c>
       <c r="P6" t="n">
-        <v>28750</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>8200</v>
+        <v>69600</v>
       </c>
       <c r="R6" t="n">
-        <v>-13000</v>
+        <v>710000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>CART 혈압계 관련 뉴스 호재. 그러나 단기 하락 가능성 및 횡보장 우려도 존재.</t>
+          <t>단기적 상승 및 목표주가 상향 전망. 5% 배당 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['CART', '혈압계', '뉴스']</t>
+          <t>['배당', '목표주가', '상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5220</v>
+        <v>23700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-9.06%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>173</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="G7" t="n">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,28 +1055,28 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5740</v>
+        <v>23500</v>
       </c>
       <c r="K7" t="n">
-        <v>5250</v>
+        <v>23200</v>
       </c>
       <c r="L7" t="n">
-        <v>5420</v>
+        <v>25600</v>
       </c>
       <c r="M7" t="n">
-        <v>5000</v>
+        <v>22800</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1512181950</v>
+        <v>148262170750</v>
       </c>
       <c r="P7" t="n">
-        <v>9680</v>
+        <v>28750</v>
       </c>
       <c r="Q7" t="n">
-        <v>371</v>
+        <v>8200</v>
       </c>
       <c r="R7" t="n">
         <v>-13000</v>
@@ -1086,27 +1086,119 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 악재 발생. 조선일보 기사 통해 하한가 및 상장폐지 가능성 제기.</t>
+          <t>CART 혈압계 관련 뉴스 언급. 일부 투자자는 하락 및 고평가 주장.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '조선일보']</t>
+          <t>['CART', '혈압계', '의료기기']</t>
         </is>
       </c>
       <c r="X7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5280</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-8.01%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>58</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" t="n">
+        <v>141</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1772900000</v>
+      </c>
+      <c r="P8" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>371</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 및 악재 뉴스 출현으로 인한 하한가 가능성 제기. 일부 투자자는 탈출.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['반기보고서', '악재', '하한가']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
         <v>1</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>226340</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52000</v>
+        <v>54300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+18.59%</t>
+          <t>+23.83%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G2" t="n">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -601,7 +601,7 @@
         <v>45650</v>
       </c>
       <c r="L2" t="n">
-        <v>52300</v>
+        <v>54400</v>
       </c>
       <c r="M2" t="n">
         <v>45650</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>47109199625</v>
+        <v>62590887375</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>매수세 유입 및 5% 돌파 후 수익 전환 기대. 전고점 돌파 및 연말 사상 최고가 갱신 전망.</t>
+          <t>두산퓨얼셀, 전고점 10만원 돌파 및 사상최고가 갱신 전망. 공매도 언급과 함께 5% 수익 실현 및 46000원 매수 완료 기록.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공매도', '추세', '최고가']</t>
+          <t>['전고점', '사상최고가', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3770</v>
+        <v>3715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+15.47%</t>
+          <t>+13.78%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>94555482044</v>
+        <v>111050001406</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>탈모약 관련 기대감 및 3연상 가능성 언급. 5천원 목표가 설정 및 10% 이상 상승.</t>
+          <t>JW신약, 탈모약 대장으로서 3연상 및 5천원 목표 전망. 월가 상승 및 삼익과의 비교 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['탈모약', '3연상', '목표가']</t>
+          <t>['탈모약', '3연상', '5천원']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>224500</v>
+        <v>223000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+11.41%</t>
+          <t>+10.67%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="F4" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="G4" t="n">
-        <v>576</v>
+        <v>636</v>
       </c>
       <c r="H4" t="n">
         <v>29.46</v>
@@ -794,7 +794,7 @@
         <v>29.51</v>
       </c>
       <c r="O4" t="n">
-        <v>162543542750</v>
+        <v>193173066500</v>
       </c>
       <c r="P4" t="n">
         <v>438000</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 액츄에이터 부품 사업 관련 뉴스 기반 23만 탈환 기대. 3분기 영업이익 컨센서스 1조 1천억 예상.</t>
+          <t>LG전자, 로봇 액츄에이터 부품 기술력 기반 23만원 탈환 및 40만원 목표 전망. CES 2023 관련 뉴스 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', '액츄에이터', '컨센서스']</t>
+          <t>['로봇 액츄에이터', 'CES 2023', '23만원']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,70 +839,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1743000</v>
+        <v>6350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+5.83%</t>
+          <t>+8.55%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>-0.7</v>
       </c>
       <c r="E5" t="n">
-        <v>796</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>469</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>2634</v>
+        <v>149</v>
       </c>
       <c r="H5" t="n">
-        <v>50.5</v>
+        <v>1.61</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1647000</v>
+        <v>5850</v>
       </c>
       <c r="K5" t="n">
-        <v>1737000</v>
+        <v>6000</v>
       </c>
       <c r="L5" t="n">
-        <v>1751000</v>
+        <v>6480</v>
       </c>
       <c r="M5" t="n">
-        <v>1734000</v>
+        <v>5940</v>
       </c>
       <c r="N5" t="n">
-        <v>50.45</v>
+        <v>2.31</v>
       </c>
       <c r="O5" t="n">
-        <v>1152379595000</v>
+        <v>7841899440</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>21500</v>
       </c>
       <c r="Q5" t="n">
-        <v>274000</v>
+        <v>2300</v>
       </c>
       <c r="R5" t="n">
-        <v>147000</v>
+        <v>-24000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입 및 ADR 상승에 따른 주가 상승 기대. 200 돌파 및 180만원 목표 전망.</t>
+          <t>신약 개발 관련 기대감과 함께 '주당 1억' 등 높은 목표 가격 제시. 공매도 언급 및 저점 매수 권유.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외국인', 'ADR', '주가예측']</t>
+          <t>['신약 개발', '임상2상', '공매견']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>266000</v>
+        <v>1738000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+4.11%</t>
+          <t>+5.53%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>643</v>
+        <v>796</v>
       </c>
       <c r="F6" t="n">
-        <v>394</v>
+        <v>459</v>
       </c>
       <c r="G6" t="n">
-        <v>2687</v>
+        <v>2172</v>
       </c>
       <c r="H6" t="n">
-        <v>46.73</v>
+        <v>50.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>255500</v>
+        <v>1647000</v>
       </c>
       <c r="K6" t="n">
-        <v>267000</v>
+        <v>1737000</v>
       </c>
       <c r="L6" t="n">
-        <v>268000</v>
+        <v>1751000</v>
       </c>
       <c r="M6" t="n">
-        <v>265500</v>
+        <v>1734000</v>
       </c>
       <c r="N6" t="n">
-        <v>46.71</v>
+        <v>50.45</v>
       </c>
       <c r="O6" t="n">
-        <v>774384559500</v>
+        <v>1295662124500</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>69600</v>
+        <v>274000</v>
       </c>
       <c r="R6" t="n">
-        <v>710000</v>
+        <v>147000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>단기적 상승 및 목표주가 상향 전망. 5% 배당 기대.</t>
+          <t>SK하이닉스, 자사주 매입 및 200만원 돌파 예상. 외인 매집과 함께 170만원대 매수 및 매도 관련 논의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['배당', '목표주가', '상승']</t>
+          <t>['자사주 매입', '200만원', '외인 매집']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23700</v>
+        <v>83200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>+5.05%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="H7" t="n">
-        <v>0.16</v>
+        <v>23.53</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>23500</v>
+        <v>79200</v>
       </c>
       <c r="K7" t="n">
-        <v>23200</v>
+        <v>80200</v>
       </c>
       <c r="L7" t="n">
-        <v>25600</v>
+        <v>84300</v>
       </c>
       <c r="M7" t="n">
-        <v>22800</v>
+        <v>79000</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>23.61</v>
       </c>
       <c r="O7" t="n">
-        <v>148262170750</v>
+        <v>79127864800</v>
       </c>
       <c r="P7" t="n">
-        <v>28750</v>
+        <v>139200</v>
       </c>
       <c r="Q7" t="n">
-        <v>8200</v>
+        <v>57000</v>
       </c>
       <c r="R7" t="n">
-        <v>-13000</v>
+        <v>21000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>CART 혈압계 관련 뉴스 언급. 일부 투자자는 하락 및 고평가 주장.</t>
+          <t>두산에너빌리티, 하반기 본 수주 및 10만원 돌파 전망. 두산퓨얼셀과의 비교 및 원전 건설 관련 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['CART', '혈압계', '의료기기']</t>
+          <t>['하반기 수주', '원전 건설', '10만원']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5280</v>
+        <v>23400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-8.01%</t>
+          <t>+4.00%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>141</v>
+        <v>85</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5740</v>
+        <v>22500</v>
       </c>
       <c r="K8" t="n">
-        <v>5250</v>
+        <v>23100</v>
       </c>
       <c r="L8" t="n">
-        <v>5420</v>
+        <v>24000</v>
       </c>
       <c r="M8" t="n">
-        <v>5000</v>
+        <v>21500</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O8" t="n">
-        <v>1772900000</v>
+        <v>87574922750</v>
       </c>
       <c r="P8" t="n">
-        <v>9680</v>
+        <v>50600</v>
       </c>
       <c r="Q8" t="n">
-        <v>371</v>
+        <v>9070</v>
       </c>
       <c r="R8" t="n">
-        <v>-13000</v>
+        <v>-22000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 악재 뉴스 출현으로 인한 하한가 가능성 제기. 일부 투자자는 탈출.</t>
+          <t>원익홀딩스, 로봇주 폭발 및 신사업 진출 재료 기반 상승 전망. 국민성장펀드 3500억 유일무이 상장사 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,18 +1187,570 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '하한가']</t>
+          <t>['로봇주', '신사업', '국민성장펀드']</t>
         </is>
       </c>
       <c r="X8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>030530</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>265250</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>+3.82%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E9" t="n">
+        <v>678</v>
+      </c>
+      <c r="F9" t="n">
+        <v>410</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2783</v>
+      </c>
+      <c r="H9" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>255500</v>
+      </c>
+      <c r="K9" t="n">
+        <v>267000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>268000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>264500</v>
+      </c>
+      <c r="N9" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="O9" t="n">
+        <v>891462676250</v>
+      </c>
+      <c r="P9" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>69600</v>
+      </c>
+      <c r="R9" t="n">
+        <v>710000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>삼성전자, 30만원 터치 및 50~60만+a 목표주가 언급. 배당 기대와 함께 단기 매도 의견도 혼재.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['목표주가', '배당', '매도']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>스카이랩스</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>23850</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>+1.49%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>184</v>
+      </c>
+      <c r="F10" t="n">
+        <v>98</v>
+      </c>
+      <c r="G10" t="n">
+        <v>228</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>23500</v>
+      </c>
+      <c r="K10" t="n">
+        <v>23200</v>
+      </c>
+      <c r="L10" t="n">
+        <v>25600</v>
+      </c>
+      <c r="M10" t="n">
+        <v>22800</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>162298431025</v>
+      </c>
+      <c r="P10" t="n">
+        <v>28750</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8200</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>스카이랩스, CART 혈압계 뉴스 언급에도 불구하고 적자 기업 고평가 및 하락 전망. 주포 변태 언급.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['CART 혈압계', '적자 기업', '하락']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>16190</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>+0.62%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" t="n">
+        <v>31</v>
+      </c>
+      <c r="G11" t="n">
+        <v>200</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>16090</v>
+      </c>
+      <c r="K11" t="n">
+        <v>16150</v>
+      </c>
+      <c r="L11" t="n">
+        <v>16480</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15830</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>18330240905</v>
+      </c>
+      <c r="P11" t="n">
+        <v>19380</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3200</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>금호건설, 9월 메가특구법 발의 및 호남 반도체 산단 인프라 언급. 일부에서는 재탕글과 하방 예상.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['메가특구법', '반도체 산단', '하방']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>002990</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>바이오니아</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10380</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F12" t="n">
+        <v>31</v>
+      </c>
+      <c r="G12" t="n">
+        <v>88</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>10390</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10050</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9770</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>14608303835</v>
+      </c>
+      <c r="P12" t="n">
+        <v>15640</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5470</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-16000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>주가 상승 및 거래량 증가에 대한 기대감 표출. 다만, 공매도 관련 부정적 언급도 존재.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['주포', '공매도', '순환매']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>1</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>064550</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>아난티</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5410</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-5.25%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E13" t="n">
+        <v>42</v>
+      </c>
+      <c r="F13" t="n">
+        <v>34</v>
+      </c>
+      <c r="G13" t="n">
+        <v>126</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>5710</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5640</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5650</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5270</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="O13" t="n">
+        <v>10064838020</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10480</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3150</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-265000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>아난티, 북한 여행자 보험 및 금강산 관광 관련 언급. 외인, 연기금 매수세에도 불구하고 하락 및 주가 조작 의혹 제기.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['북한', '금강산', '주가 조작']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>025980</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5290</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-7.84%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F14" t="n">
+        <v>34</v>
+      </c>
+      <c r="G14" t="n">
+        <v>144</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1968597240</v>
+      </c>
+      <c r="P14" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>371</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 악재로 인한 하한가 및 급락. 조선일보 기사 인용 및 투자자들의 탈출 언급.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['반기보고서', '악재', '조선일보']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>226340</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54300</v>
+        <v>54600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+23.83%</t>
+          <t>+24.52%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="F2" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>258</v>
+        <v>349</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -601,7 +601,7 @@
         <v>45650</v>
       </c>
       <c r="L2" t="n">
-        <v>54400</v>
+        <v>55000</v>
       </c>
       <c r="M2" t="n">
         <v>45650</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>62590887375</v>
+        <v>77772460625</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -619,14 +619,14 @@
         <v>18230</v>
       </c>
       <c r="R2" t="n">
-        <v>67000</v>
+        <v>160000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>두산퓨얼셀, 전고점 10만원 돌파 및 사상최고가 갱신 전망. 공매도 언급과 함께 5% 수익 실현 및 46000원 매수 완료 기록.</t>
+          <t>강한 상승 추세 속 공매도 세력과의 경쟁, 전고점 돌파 기대감 형성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['전고점', '사상최고가', '공매도']</t>
+          <t>['추세', '공매도', '전고점']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3715</v>
+        <v>3690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+13.78%</t>
+          <t>+13.02%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>111050001406</v>
+        <v>121250479961</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -711,23 +711,23 @@
         <v>1246</v>
       </c>
       <c r="R3" t="n">
-        <v>419000</v>
+        <v>179000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>JW신약, 탈모약 대장으로서 3연상 및 5천원 목표 전망. 월가 상승 및 삼익과의 비교 언급.</t>
+          <t>탈모약 관련 기대감 속에 주가 상승 모멘텀 형성, 거래량 부진 우려.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['탈모약', '3연상', '5천원']</t>
+          <t>['탈모약', '상승 모멘텀', '거래량']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>223000</v>
+        <v>221500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.67%</t>
+          <t>+9.93%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="F4" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G4" t="n">
-        <v>636</v>
+        <v>686</v>
       </c>
       <c r="H4" t="n">
         <v>29.46</v>
@@ -794,7 +794,7 @@
         <v>29.51</v>
       </c>
       <c r="O4" t="n">
-        <v>193173066500</v>
+        <v>207350807500</v>
       </c>
       <c r="P4" t="n">
         <v>438000</v>
@@ -803,14 +803,14 @@
         <v>74700</v>
       </c>
       <c r="R4" t="n">
-        <v>190000</v>
+        <v>317000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>102000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>LG전자, 로봇 액츄에이터 부품 기술력 기반 23만원 탈환 및 40만원 목표 전망. CES 2023 관련 뉴스 언급.</t>
+          <t>로봇 액츄에이터 사업 관련 호재와 CES 2026 참가 소식으로 인한 급등세.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇 액츄에이터', 'CES 2023', '23만원']</t>
+          <t>['로봇', '액츄에이터', 'CES 2026']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,11 +839,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6350</v>
+        <v>8630</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -851,71 +851,71 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.7</v>
+        <v>-0.72</v>
       </c>
       <c r="E5" t="n">
         <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>149</v>
+        <v>43</v>
       </c>
       <c r="H5" t="n">
-        <v>1.61</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5850</v>
+        <v>7950</v>
       </c>
       <c r="K5" t="n">
-        <v>6000</v>
+        <v>8200</v>
       </c>
       <c r="L5" t="n">
-        <v>6480</v>
+        <v>9210</v>
       </c>
       <c r="M5" t="n">
-        <v>5940</v>
+        <v>7980</v>
       </c>
       <c r="N5" t="n">
-        <v>2.31</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
-        <v>7841899440</v>
+        <v>66907313720</v>
       </c>
       <c r="P5" t="n">
-        <v>21500</v>
+        <v>15960</v>
       </c>
       <c r="Q5" t="n">
-        <v>2300</v>
+        <v>3500</v>
       </c>
       <c r="R5" t="n">
-        <v>-24000</v>
+        <v>208000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>신약 개발 관련 기대감과 함께 '주당 1억' 등 높은 목표 가격 제시. 공매도 언급 및 저점 매수 권유.</t>
+          <t>미프진 관련 소식 공식화 가능성에 대한 기대감 있으나, 주가 변동은 제한적.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['신약 개발', '임상2상', '공매견']</t>
+          <t>['미프진', '공식화']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1738000</v>
+        <v>6210</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+5.53%</t>
+          <t>+6.15%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>-0.7</v>
       </c>
       <c r="E6" t="n">
-        <v>796</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>459</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>2172</v>
+        <v>178</v>
       </c>
       <c r="H6" t="n">
-        <v>50.5</v>
+        <v>1.61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1647000</v>
+        <v>5850</v>
       </c>
       <c r="K6" t="n">
-        <v>1737000</v>
+        <v>6000</v>
       </c>
       <c r="L6" t="n">
-        <v>1751000</v>
+        <v>6490</v>
       </c>
       <c r="M6" t="n">
-        <v>1734000</v>
+        <v>5940</v>
       </c>
       <c r="N6" t="n">
-        <v>50.45</v>
+        <v>2.31</v>
       </c>
       <c r="O6" t="n">
-        <v>1295662124500</v>
+        <v>9150073130</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>21500</v>
       </c>
       <c r="Q6" t="n">
-        <v>274000</v>
+        <v>2300</v>
       </c>
       <c r="R6" t="n">
-        <v>147000</v>
+        <v>-35000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>SK하이닉스, 자사주 매입 및 200만원 돌파 예상. 외인 매집과 함께 170만원대 매수 및 매도 관련 논의.</t>
+          <t>신약 개발 기대감이 있으나, 주가 상승에 대한 확신은 낮으며 보수적인 전망이 주를 이룹니다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['자사주 매입', '200만원', '외인 매집']</t>
+          <t>['신약 개발', '공매', '홀딩']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83200</v>
+        <v>1736000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+5.05%</t>
+          <t>+5.40%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>798</v>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>454</v>
       </c>
       <c r="G7" t="n">
-        <v>179</v>
+        <v>2107</v>
       </c>
       <c r="H7" t="n">
-        <v>23.53</v>
+        <v>50.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>79200</v>
+        <v>1647000</v>
       </c>
       <c r="K7" t="n">
-        <v>80200</v>
+        <v>1737000</v>
       </c>
       <c r="L7" t="n">
-        <v>84300</v>
+        <v>1751000</v>
       </c>
       <c r="M7" t="n">
-        <v>79000</v>
+        <v>1734000</v>
       </c>
       <c r="N7" t="n">
-        <v>23.61</v>
+        <v>50.45</v>
       </c>
       <c r="O7" t="n">
-        <v>79127864800</v>
+        <v>1430800050500</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>274000</v>
       </c>
       <c r="R7" t="n">
-        <v>21000</v>
+        <v>281000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>146000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 하반기 본 수주 및 10만원 돌파 전망. 두산퓨얼셀과의 비교 및 원전 건설 관련 언급.</t>
+          <t>자사주 매입 및 외인 수급에 대한 기대감이 높으며, 200만원 돌파 가능성에 대한 긍정적인 전망이 우세합니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['하반기 수주', '원전 건설', '10만원']</t>
+          <t>['자사주매입', '외인수급', '숏커버링']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23400</v>
+        <v>83300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+4.00%</t>
+          <t>+5.18%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.62</v>
+        <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="H8" t="n">
-        <v>5.6</v>
+        <v>23.53</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>22500</v>
+        <v>79200</v>
       </c>
       <c r="K8" t="n">
-        <v>23100</v>
+        <v>80200</v>
       </c>
       <c r="L8" t="n">
-        <v>24000</v>
+        <v>84300</v>
       </c>
       <c r="M8" t="n">
-        <v>21500</v>
+        <v>79000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.98</v>
+        <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>87574922750</v>
+        <v>91318481500</v>
       </c>
       <c r="P8" t="n">
-        <v>50600</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>9070</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>-22000</v>
+        <v>5000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원익홀딩스, 로봇주 폭발 및 신사업 진출 재료 기반 상승 전망. 국민성장펀드 3500억 유일무이 상장사 언급.</t>
+          <t>하반기 수주 기대감 및 원전 건설 관련 모멘텀, 단기적 불안감도 상존.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '국민성장펀드']</t>
+          <t>['수주', '원전', '모멘텀']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>265250</v>
+        <v>13600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+3.82%</t>
+          <t>+4.53%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>678</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>410</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>2783</v>
+        <v>177</v>
       </c>
       <c r="H9" t="n">
-        <v>46.73</v>
+        <v>1.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>255500</v>
+        <v>13010</v>
       </c>
       <c r="K9" t="n">
-        <v>267000</v>
+        <v>13420</v>
       </c>
       <c r="L9" t="n">
-        <v>268000</v>
+        <v>14100</v>
       </c>
       <c r="M9" t="n">
-        <v>264500</v>
+        <v>13410</v>
       </c>
       <c r="N9" t="n">
-        <v>46.71</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>891462676250</v>
+        <v>49637950980</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>69600</v>
+        <v>1252</v>
       </c>
       <c r="R9" t="n">
-        <v>710000</v>
+        <v>204000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성전자, 30만원 터치 및 50~60만+a 목표주가 언급. 배당 기대와 함께 단기 매도 의견도 혼재.</t>
+          <t>미국 광통신주 상승에도 불구하고 국내 거래량 및 대금 부진으로 인한 약세.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['목표주가', '배당', '매도']</t>
+          <t>['광통신', '거래량', '거래대금']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23850</v>
+        <v>264750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>+3.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>184</v>
+        <v>736</v>
       </c>
       <c r="F10" t="n">
-        <v>98</v>
+        <v>435</v>
       </c>
       <c r="G10" t="n">
-        <v>228</v>
+        <v>2801</v>
       </c>
       <c r="H10" t="n">
-        <v>0.16</v>
+        <v>46.73</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>23500</v>
+        <v>255500</v>
       </c>
       <c r="K10" t="n">
-        <v>23200</v>
+        <v>267000</v>
       </c>
       <c r="L10" t="n">
-        <v>25600</v>
+        <v>268000</v>
       </c>
       <c r="M10" t="n">
-        <v>22800</v>
+        <v>264500</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>46.71</v>
       </c>
       <c r="O10" t="n">
-        <v>162298431025</v>
+        <v>988809072750</v>
       </c>
       <c r="P10" t="n">
-        <v>28750</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>8200</v>
+        <v>69600</v>
       </c>
       <c r="R10" t="n">
-        <v>-13000</v>
+        <v>1074000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>809000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>스카이랩스, CART 혈압계 뉴스 언급에도 불구하고 적자 기업 고평가 및 하락 전망. 주포 변태 언급.</t>
+          <t>삼성전자, 30만원 터치 및 50~60만+a 목표주가 언급. 배당 기대와 함께 단기 매도 의견도 혼재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['CART 혈압계', '적자 기업', '하락']</t>
+          <t>['목표주가', '배당', '매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16190</v>
+        <v>23100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>+2.67%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16090</v>
+        <v>22500</v>
       </c>
       <c r="K11" t="n">
-        <v>16150</v>
+        <v>23100</v>
       </c>
       <c r="L11" t="n">
-        <v>16480</v>
+        <v>24000</v>
       </c>
       <c r="M11" t="n">
-        <v>15830</v>
+        <v>21500</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O11" t="n">
-        <v>18330240905</v>
+        <v>93317591000</v>
       </c>
       <c r="P11" t="n">
-        <v>19380</v>
+        <v>50600</v>
       </c>
       <c r="Q11" t="n">
-        <v>3200</v>
+        <v>9070</v>
       </c>
       <c r="R11" t="n">
-        <v>2000</v>
+        <v>-51000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>금호건설, 9월 메가특구법 발의 및 호남 반도체 산단 인프라 언급. 일부에서는 재탕글과 하방 예상.</t>
+          <t>로봇 관련주로 인한 상승 기대감, 단기 급등 후 변동성 출현.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['메가특구법', '반도체 산단', '하방']</t>
+          <t>['로봇', '신사업', '변동성']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10380</v>
+        <v>23650</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="F12" t="n">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="G12" t="n">
-        <v>88</v>
+        <v>271</v>
       </c>
       <c r="H12" t="n">
-        <v>5.75</v>
+        <v>0.16</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10390</v>
+        <v>23500</v>
       </c>
       <c r="K12" t="n">
-        <v>10050</v>
+        <v>23200</v>
       </c>
       <c r="L12" t="n">
-        <v>11000</v>
+        <v>25600</v>
       </c>
       <c r="M12" t="n">
-        <v>9770</v>
+        <v>22800</v>
       </c>
       <c r="N12" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>14608303835</v>
+        <v>170143091300</v>
       </c>
       <c r="P12" t="n">
-        <v>15640</v>
+        <v>28750</v>
       </c>
       <c r="Q12" t="n">
-        <v>5470</v>
+        <v>8200</v>
       </c>
       <c r="R12" t="n">
-        <v>-16000</v>
+        <v>-2000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주가 상승 및 거래량 증가에 대한 기대감 표출. 다만, 공매도 관련 부정적 언급도 존재.</t>
+          <t>CART 혈압계 관련 뉴스에도 불구하고 적자 및 고평가 논란으로 인한 하락 압력.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주포', '공매도', '순환매']</t>
+          <t>['혈압계', '적자', '고평가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>아난티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5410</v>
+        <v>16190</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-5.25%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>126</v>
+        <v>221</v>
       </c>
       <c r="H13" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>5710</v>
+        <v>16090</v>
       </c>
       <c r="K13" t="n">
-        <v>5640</v>
+        <v>16150</v>
       </c>
       <c r="L13" t="n">
-        <v>5650</v>
+        <v>16480</v>
       </c>
       <c r="M13" t="n">
-        <v>5270</v>
+        <v>15830</v>
       </c>
       <c r="N13" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>10064838020</v>
+        <v>20711752555</v>
       </c>
       <c r="P13" t="n">
-        <v>10480</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>3150</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-265000</v>
+        <v>-3000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>아난티, 북한 여행자 보험 및 금강산 관광 관련 언급. 외인, 연기금 매수세에도 불구하고 하락 및 주가 조작 의혹 제기.</t>
+          <t>메가특구법 발의 및 호남 반도체 산단 관련 호재 속 우상향 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['북한', '금강산', '주가 조작']</t>
+          <t>['메가특구법', '반도체 산단', '우상향']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>025980</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5290</v>
+        <v>10360</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-7.84%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G14" t="n">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>5740</v>
+        <v>10390</v>
       </c>
       <c r="K14" t="n">
-        <v>5250</v>
+        <v>10050</v>
       </c>
       <c r="L14" t="n">
-        <v>5420</v>
+        <v>11000</v>
       </c>
       <c r="M14" t="n">
-        <v>5000</v>
+        <v>9770</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1968597240</v>
+        <v>15463626470</v>
       </c>
       <c r="P14" t="n">
-        <v>9680</v>
+        <v>15640</v>
       </c>
       <c r="Q14" t="n">
-        <v>371</v>
+        <v>5470</v>
       </c>
       <c r="R14" t="n">
-        <v>-13000</v>
+        <v>-84000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 악재로 인한 하한가 및 급락. 조선일보 기사 인용 및 투자자들의 탈출 언급.</t>
+          <t>개인 투자자들의 긍정적인 기대감과 함께 일부 호재 가능성이 언급되고 있으나, 구체적인 근거는 부족한 상황입니다.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '조선일보']</t>
+          <t>['주포', '순환매', '공매']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1751,6 +1751,190 @@
         </is>
       </c>
       <c r="Z14" t="inlineStr">
+        <is>
+          <t>064550</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>아난티</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5380</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-5.78%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E15" t="n">
+        <v>45</v>
+      </c>
+      <c r="F15" t="n">
+        <v>35</v>
+      </c>
+      <c r="G15" t="n">
+        <v>149</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>5710</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5640</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5650</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5270</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="O15" t="n">
+        <v>10480719635</v>
+      </c>
+      <c r="P15" t="n">
+        <v>10480</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3150</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-307000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>북한 관련 기대감 약화 및 연이은 하락세, 외인 매수세 유입에도 반등 모색.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['북한', '금강산', '외인 매수']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>025980</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5310</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-7.49%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>70</v>
+      </c>
+      <c r="F16" t="n">
+        <v>37</v>
+      </c>
+      <c r="G16" t="n">
+        <v>148</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2073256090</v>
+      </c>
+      <c r="P16" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>371</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 및 악재 뉴스 발생으로 주가 하락에 대한 우려가 크며, 상폐 가능성까지 제기되고 있습니다.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['반기보고서', '악재뉴스', '상폐']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>226340</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54600</v>
+        <v>53600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+24.52%</t>
+          <t>+22.23%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="F2" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G2" t="n">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>77772460625</v>
+        <v>85083940325</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>강한 상승 추세 속 공매도 세력과의 경쟁, 전고점 돌파 기대감 형성.</t>
+          <t>수익 전환 및 공매도 감소세 확인. 전고점 돌파 가능성 및 7만원 이상 목표 주가 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['추세', '공매도', '전고점']</t>
+          <t>['수익 전환', '공매도', '전고점']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3690</v>
+        <v>3765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+13.02%</t>
+          <t>+15.31%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>121250479961</v>
+        <v>131866463949</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>탈모약 관련 기대감 속에 주가 상승 모멘텀 형성, 거래량 부진 우려.</t>
+          <t>탈모약 관련 기대감 및 거래량 증가. 5천원 목표 주가 제시 및 3연상 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['탈모약', '상승 모멘텀', '거래량']</t>
+          <t>['탈모약', '거래량', '3연상']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>221500</v>
+        <v>8790</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>+10.57%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.05</v>
+        <v>-0.72</v>
       </c>
       <c r="E4" t="n">
-        <v>242</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>139</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>686</v>
+        <v>54</v>
       </c>
       <c r="H4" t="n">
-        <v>29.46</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>201500</v>
+        <v>7950</v>
       </c>
       <c r="K4" t="n">
-        <v>212500</v>
+        <v>8200</v>
       </c>
       <c r="L4" t="n">
-        <v>225500</v>
+        <v>9210</v>
       </c>
       <c r="M4" t="n">
-        <v>212500</v>
+        <v>7980</v>
       </c>
       <c r="N4" t="n">
-        <v>29.51</v>
+        <v>1.32</v>
       </c>
       <c r="O4" t="n">
-        <v>207350807500</v>
+        <v>71826623070</v>
       </c>
       <c r="P4" t="n">
-        <v>438000</v>
+        <v>15960</v>
       </c>
       <c r="Q4" t="n">
-        <v>74700</v>
+        <v>3500</v>
       </c>
       <c r="R4" t="n">
-        <v>317000</v>
+        <v>208000</v>
       </c>
       <c r="S4" t="n">
-        <v>102000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 액츄에이터 사업 관련 호재와 CES 2026 참가 소식으로 인한 급등세.</t>
+          <t>미프진 관련 이슈 공식화 및 외국인/기관 매수세 유입 기대. 다만, 상승 추세는 제한적.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', '액츄에이터', 'CES 2026']</t>
+          <t>['미프진', '매수세', '상승']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8630</v>
+        <v>219000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+8.55%</t>
+          <t>+8.68%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.72</v>
+        <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>148</v>
       </c>
       <c r="G5" t="n">
-        <v>43</v>
+        <v>745</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6</v>
+        <v>29.46</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7950</v>
+        <v>201500</v>
       </c>
       <c r="K5" t="n">
-        <v>8200</v>
+        <v>212500</v>
       </c>
       <c r="L5" t="n">
-        <v>9210</v>
+        <v>225500</v>
       </c>
       <c r="M5" t="n">
-        <v>7980</v>
+        <v>212500</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>29.51</v>
       </c>
       <c r="O5" t="n">
-        <v>66907313720</v>
+        <v>218009800000</v>
       </c>
       <c r="P5" t="n">
-        <v>15960</v>
+        <v>438000</v>
       </c>
       <c r="Q5" t="n">
-        <v>3500</v>
+        <v>74700</v>
       </c>
       <c r="R5" t="n">
-        <v>208000</v>
+        <v>317000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>102000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미프진 관련 소식 공식화 가능성에 대한 기대감 있으나, 주가 변동은 제한적.</t>
+          <t>로봇 액츄에이터 부품 기술력 기반 급등. 피지컬 AI 관련 투자 및 빅테크 협력 기대감 고조.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['미프진', '공식화']</t>
+          <t>['로봇 액츄에이터', '피지컬 AI', '빅테크']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6210</v>
+        <v>24900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+6.15%</t>
+          <t>+5.96%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="G6" t="n">
-        <v>178</v>
+        <v>304</v>
       </c>
       <c r="H6" t="n">
-        <v>1.61</v>
+        <v>0.16</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5850</v>
+        <v>23500</v>
       </c>
       <c r="K6" t="n">
-        <v>6000</v>
+        <v>23200</v>
       </c>
       <c r="L6" t="n">
-        <v>6490</v>
+        <v>25600</v>
       </c>
       <c r="M6" t="n">
-        <v>5940</v>
+        <v>22800</v>
       </c>
       <c r="N6" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>9150073130</v>
+        <v>192688563325</v>
       </c>
       <c r="P6" t="n">
-        <v>21500</v>
+        <v>28750</v>
       </c>
       <c r="Q6" t="n">
-        <v>2300</v>
+        <v>8200</v>
       </c>
       <c r="R6" t="n">
-        <v>-35000</v>
+        <v>-2000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>신약 개발 기대감이 있으나, 주가 상승에 대한 확신은 낮으며 보수적인 전망이 주를 이룹니다.</t>
+          <t>CART 혈압계 관련 뉴스 및 세계 최초/1위 기술력 보유. 다만, 적자 기업 및 고평가 논란 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['신약 개발', '공매', '홀딩']</t>
+          <t>['CART 혈압계', '의료기기', '적자']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1736000</v>
+        <v>6180</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+5.40%</t>
+          <t>+5.64%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>-0.7</v>
       </c>
       <c r="E7" t="n">
-        <v>798</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
-        <v>454</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>2107</v>
+        <v>198</v>
       </c>
       <c r="H7" t="n">
-        <v>50.5</v>
+        <v>1.61</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1647000</v>
+        <v>5850</v>
       </c>
       <c r="K7" t="n">
-        <v>1737000</v>
+        <v>6000</v>
       </c>
       <c r="L7" t="n">
-        <v>1751000</v>
+        <v>6490</v>
       </c>
       <c r="M7" t="n">
-        <v>1734000</v>
+        <v>5940</v>
       </c>
       <c r="N7" t="n">
-        <v>50.45</v>
+        <v>2.31</v>
       </c>
       <c r="O7" t="n">
-        <v>1430800050500</v>
+        <v>9846018855</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>21500</v>
       </c>
       <c r="Q7" t="n">
-        <v>274000</v>
+        <v>2300</v>
       </c>
       <c r="R7" t="n">
-        <v>281000</v>
+        <v>-35000</v>
       </c>
       <c r="S7" t="n">
-        <v>146000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>자사주 매입 및 외인 수급에 대한 기대감이 높으며, 200만원 돌파 가능성에 대한 긍정적인 전망이 우세합니다.</t>
+          <t>신약 개발 가능성 및 현대바이오와의 연관성 언급. 다만, 허황된 꿈이라는 부정적 시각 및 고점 매도 주의 필요.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['자사주매입', '외인수급', '숏커버링']</t>
+          <t>['신약 개발', '현대바이오', '고점 매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83300</v>
+        <v>1733000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.18%</t>
+          <t>+5.22%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>87</v>
+        <v>796</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>453</v>
       </c>
       <c r="G8" t="n">
-        <v>202</v>
+        <v>1947</v>
       </c>
       <c r="H8" t="n">
-        <v>23.53</v>
+        <v>50.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>79200</v>
+        <v>1647000</v>
       </c>
       <c r="K8" t="n">
-        <v>80200</v>
+        <v>1737000</v>
       </c>
       <c r="L8" t="n">
-        <v>84300</v>
+        <v>1751000</v>
       </c>
       <c r="M8" t="n">
-        <v>79000</v>
+        <v>1733000</v>
       </c>
       <c r="N8" t="n">
-        <v>23.61</v>
+        <v>50.45</v>
       </c>
       <c r="O8" t="n">
-        <v>91318481500</v>
+        <v>1562468445500</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>274000</v>
       </c>
       <c r="R8" t="n">
-        <v>5000</v>
+        <v>281000</v>
       </c>
       <c r="S8" t="n">
-        <v>1000</v>
+        <v>146000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>하반기 수주 기대감 및 원전 건설 관련 모멘텀, 단기적 불안감도 상존.</t>
+          <t>자사주 매입 예정 및 외인 매수세 유입에 따른 200만원 돌파 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주', '원전', '모멘텀']</t>
+          <t>['자사주매입', '외인매집', '주가전망']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13600</v>
+        <v>83300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>+5.18%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="G9" t="n">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82</v>
+        <v>23.53</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13010</v>
+        <v>79200</v>
       </c>
       <c r="K9" t="n">
-        <v>13420</v>
+        <v>80200</v>
       </c>
       <c r="L9" t="n">
-        <v>14100</v>
+        <v>84400</v>
       </c>
       <c r="M9" t="n">
-        <v>13410</v>
+        <v>79000</v>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>23.61</v>
       </c>
       <c r="O9" t="n">
-        <v>49637950980</v>
+        <v>107081084850</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>1252</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>204000</v>
+        <v>5000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 광통신주 상승에도 불구하고 국내 거래량 및 대금 부진으로 인한 약세.</t>
+          <t>하반기 수주 기대감 및 원자력주 전반의 상승세. 10만원 돌파 가능성 및 83000원대 매물 소화 중.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '거래량', '거래대금']</t>
+          <t>['수주', '원자력주', '매물 소화']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>264750</v>
+        <v>13590</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+3.62%</t>
+          <t>+4.46%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E10" t="n">
-        <v>736</v>
+        <v>45</v>
       </c>
       <c r="F10" t="n">
-        <v>435</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>2801</v>
+        <v>193</v>
       </c>
       <c r="H10" t="n">
-        <v>46.73</v>
+        <v>1.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>255500</v>
+        <v>13010</v>
       </c>
       <c r="K10" t="n">
-        <v>267000</v>
+        <v>13420</v>
       </c>
       <c r="L10" t="n">
-        <v>268000</v>
+        <v>14100</v>
       </c>
       <c r="M10" t="n">
-        <v>264500</v>
+        <v>13410</v>
       </c>
       <c r="N10" t="n">
-        <v>46.71</v>
+        <v>1.91</v>
       </c>
       <c r="O10" t="n">
-        <v>988809072750</v>
+        <v>51258681645</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>69600</v>
+        <v>1252</v>
       </c>
       <c r="R10" t="n">
-        <v>1074000</v>
+        <v>204000</v>
       </c>
       <c r="S10" t="n">
-        <v>809000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>삼성전자, 30만원 터치 및 50~60만+a 목표주가 언급. 배당 기대와 함께 단기 매도 의견도 혼재.</t>
+          <t>광통신주 상승 추세 및 미국 시장 동반 상승 기대. 다만, 주가 변동성이 크고 14000원대 매물 부담 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['목표주가', '배당', '매도']</t>
+          <t>['광통신주', '상승 추세', '변동성']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23100</v>
+        <v>264250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.67%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.62</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>781</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>456</v>
       </c>
       <c r="G11" t="n">
-        <v>95</v>
+        <v>2901</v>
       </c>
       <c r="H11" t="n">
-        <v>5.6</v>
+        <v>46.73</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>22500</v>
+        <v>255500</v>
       </c>
       <c r="K11" t="n">
-        <v>23100</v>
+        <v>267000</v>
       </c>
       <c r="L11" t="n">
-        <v>24000</v>
+        <v>268000</v>
       </c>
       <c r="M11" t="n">
-        <v>21500</v>
+        <v>264000</v>
       </c>
       <c r="N11" t="n">
-        <v>4.98</v>
+        <v>46.71</v>
       </c>
       <c r="O11" t="n">
-        <v>93317591000</v>
+        <v>1088118218250</v>
       </c>
       <c r="P11" t="n">
-        <v>50600</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>9070</v>
+        <v>69600</v>
       </c>
       <c r="R11" t="n">
-        <v>-51000</v>
+        <v>1074000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>809000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>로봇 관련주로 인한 상승 기대감, 단기 급등 후 변동성 출현.</t>
+          <t>삼성전자, 30만원 터치 및 50~60만+a 목표주가 언급. 배당 기대와 함께 단기 매도 의견도 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['로봇', '신사업', '변동성']</t>
+          <t>['목표주가', '배당', '매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23650</v>
+        <v>23150</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+2.89%</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" t="n">
+        <v>36</v>
+      </c>
+      <c r="G12" t="n">
+        <v>99</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>22500</v>
+      </c>
+      <c r="K12" t="n">
+        <v>23100</v>
+      </c>
+      <c r="L12" t="n">
+        <v>24000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>21500</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="O12" t="n">
+        <v>102752774350</v>
+      </c>
+      <c r="P12" t="n">
+        <v>50600</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>9070</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-51000</v>
+      </c>
+      <c r="S12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>205</v>
-      </c>
-      <c r="F12" t="n">
-        <v>110</v>
-      </c>
-      <c r="G12" t="n">
-        <v>271</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>23500</v>
-      </c>
-      <c r="K12" t="n">
-        <v>23200</v>
-      </c>
-      <c r="L12" t="n">
-        <v>25600</v>
-      </c>
-      <c r="M12" t="n">
-        <v>22800</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>170143091300</v>
-      </c>
-      <c r="P12" t="n">
-        <v>28750</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>8200</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-1000</v>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>CART 혈압계 관련 뉴스에도 불구하고 적자 및 고평가 논란으로 인한 하락 압력.</t>
+          <t>로봇 관련주로 인한 상승 기대감, 단기 급등 후 변동성 출현.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['혈압계', '적자', '고평가']</t>
+          <t>['로봇', '신사업', '변동성']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16190</v>
+        <v>10440</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G13" t="n">
-        <v>221</v>
+        <v>115</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16090</v>
+        <v>10390</v>
       </c>
       <c r="K13" t="n">
-        <v>16150</v>
+        <v>10050</v>
       </c>
       <c r="L13" t="n">
-        <v>16480</v>
+        <v>11000</v>
       </c>
       <c r="M13" t="n">
-        <v>15830</v>
+        <v>9770</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
-        <v>20711752555</v>
+        <v>16099632815</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>15640</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>5470</v>
       </c>
       <c r="R13" t="n">
-        <v>-3000</v>
+        <v>-84000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>메가특구법 발의 및 호남 반도체 산단 관련 호재 속 우상향 기대감.</t>
+          <t>호재 발생 및 공매도 세력과의 공방 속 200만원 목표 주가 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['메가특구법', '반도체 산단', '우상향']</t>
+          <t>['호재', '공매도', '주가목표']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10360</v>
+        <v>16100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
-        <v>109</v>
+        <v>243</v>
       </c>
       <c r="H14" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10390</v>
+        <v>16090</v>
       </c>
       <c r="K14" t="n">
-        <v>10050</v>
+        <v>16150</v>
       </c>
       <c r="L14" t="n">
-        <v>11000</v>
+        <v>16480</v>
       </c>
       <c r="M14" t="n">
-        <v>9770</v>
+        <v>15830</v>
       </c>
       <c r="N14" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>15463626470</v>
+        <v>22033196395</v>
       </c>
       <c r="P14" t="n">
-        <v>15640</v>
+        <v>19380</v>
       </c>
       <c r="Q14" t="n">
-        <v>5470</v>
+        <v>3200</v>
       </c>
       <c r="R14" t="n">
-        <v>-84000</v>
+        <v>-3000</v>
       </c>
       <c r="S14" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>개인 투자자들의 긍정적인 기대감과 함께 일부 호재 가능성이 언급되고 있으나, 구체적인 근거는 부족한 상황입니다.</t>
+          <t>메가특구법 발의 및 호남 반도체 산단 관련 긍정적 뉴스. 다만, 투자 주체별 매매 동향은 혼조세.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주포', '순환매', '공매']</t>
+          <t>['메가특구법', '반도체 산단', '투자 심리']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5380</v>
+        <v>5440</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-5.78%</t>
+          <t>-4.73%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.42</v>
       </c>
       <c r="E15" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="H15" t="n">
         <v>4.81</v>
@@ -1806,7 +1806,7 @@
         <v>4.39</v>
       </c>
       <c r="O15" t="n">
-        <v>10480719635</v>
+        <v>10881645515</v>
       </c>
       <c r="P15" t="n">
         <v>10480</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>북한 관련 기대감 약화 및 연이은 하락세, 외인 매수세 유입에도 반등 모색.</t>
+          <t>대북주 테마 부각 및 금강산 관광 기대. 다만, 외인/연기금 매수세에도 불구하고 주가 하락 및 도박주 리스크 존재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['북한', '금강산', '외인 매수']</t>
+          <t>['대북주', '금강산 관광', '도박주']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1869,10 +1869,10 @@
         <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2073256090</v>
+        <v>2152749210</v>
       </c>
       <c r="P16" t="n">
         <v>9680</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 악재 뉴스 발생으로 주가 하락에 대한 우려가 크며, 상폐 가능성까지 제기되고 있습니다.</t>
+          <t>반기보고서 제출 지연 및 구주 매각 이슈로 인한 악재 발생, 하한가 기록.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재뉴스', '상폐']</t>
+          <t>['반기보고서', '악재', '하한가']</t>
         </is>
       </c>
       <c r="X16" t="n">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53600</v>
+        <v>52800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+22.23%</t>
+          <t>+20.41%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F2" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G2" t="n">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>85083940325</v>
+        <v>91378657225</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>수익 전환 및 공매도 감소세 확인. 전고점 돌파 가능성 및 7만원 이상 목표 주가 전망.</t>
+          <t>상승 추세와 공매도 감소에 따른 강한 상승 기대감 및 수익 실현 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['수익 전환', '공매도', '전고점']</t>
+          <t>['상승추세', '공매도', '수익실현']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3765</v>
+        <v>3695</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+15.31%</t>
+          <t>+13.17%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>131866463949</v>
+        <v>138654130162</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>탈모약 관련 기대감 및 거래량 증가. 5천원 목표 주가 제시 및 3연상 가능성 언급.</t>
+          <t>탈모약 관련 이슈와 함께 단기 급등 및 3연상 기대감 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['탈모약', '거래량', '3연상']</t>
+          <t>['탈모약', '급등', '3연상']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8790</v>
+        <v>220000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.57%</t>
+          <t>+9.18%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.72</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>268</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>153</v>
       </c>
       <c r="G4" t="n">
-        <v>54</v>
+        <v>782</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6</v>
+        <v>29.46</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7950</v>
+        <v>201500</v>
       </c>
       <c r="K4" t="n">
-        <v>8200</v>
+        <v>212500</v>
       </c>
       <c r="L4" t="n">
-        <v>9210</v>
+        <v>225500</v>
       </c>
       <c r="M4" t="n">
-        <v>7980</v>
+        <v>212500</v>
       </c>
       <c r="N4" t="n">
-        <v>1.32</v>
+        <v>29.51</v>
       </c>
       <c r="O4" t="n">
-        <v>71826623070</v>
+        <v>226568504000</v>
       </c>
       <c r="P4" t="n">
-        <v>15960</v>
+        <v>438000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3500</v>
+        <v>74700</v>
       </c>
       <c r="R4" t="n">
-        <v>208000</v>
+        <v>317000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>102000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미프진 관련 이슈 공식화 및 외국인/기관 매수세 유입 기대. 다만, 상승 추세는 제한적.</t>
+          <t>로봇 사업 및 액추에이터 기술 관련 호재와 프로그램 매수세 유입에 따른 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['미프진', '매수세', '상승']</t>
+          <t>['로봇사업', '액추에이터', '프로그램매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>219000</v>
+        <v>8680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+8.68%</t>
+          <t>+9.18%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>-0.72</v>
       </c>
       <c r="E5" t="n">
-        <v>257</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>148</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>745</v>
+        <v>60</v>
       </c>
       <c r="H5" t="n">
-        <v>29.46</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>201500</v>
+        <v>7950</v>
       </c>
       <c r="K5" t="n">
-        <v>212500</v>
+        <v>8200</v>
       </c>
       <c r="L5" t="n">
-        <v>225500</v>
+        <v>9210</v>
       </c>
       <c r="M5" t="n">
-        <v>212500</v>
+        <v>7980</v>
       </c>
       <c r="N5" t="n">
-        <v>29.51</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
-        <v>218009800000</v>
+        <v>76245412660</v>
       </c>
       <c r="P5" t="n">
-        <v>438000</v>
+        <v>15960</v>
       </c>
       <c r="Q5" t="n">
-        <v>74700</v>
+        <v>3500</v>
       </c>
       <c r="R5" t="n">
-        <v>317000</v>
+        <v>208000</v>
       </c>
       <c r="S5" t="n">
-        <v>102000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇 액츄에이터 부품 기술력 기반 급등. 피지컬 AI 관련 투자 및 빅테크 협력 기대감 고조.</t>
+          <t>미프진 관련 이슈와 함께 주가 상승 기대감 및 단기 매매 관점의 글 다수.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇 액츄에이터', '피지컬 AI', '빅테크']</t>
+          <t>['미프진', '단기매매', '주가']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24900</v>
+        <v>25350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+5.96%</t>
+          <t>+7.87%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="F6" t="n">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="G6" t="n">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="H6" t="n">
         <v>0.16</v>
@@ -969,7 +969,7 @@
         <v>23200</v>
       </c>
       <c r="L6" t="n">
-        <v>25600</v>
+        <v>26450</v>
       </c>
       <c r="M6" t="n">
         <v>22800</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>192688563325</v>
+        <v>280986319875</v>
       </c>
       <c r="P6" t="n">
         <v>28750</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>CART 혈압계 관련 뉴스 및 세계 최초/1위 기술력 보유. 다만, 적자 기업 및 고평가 논란 존재.</t>
+          <t>의료기기 및 혈압계 관련 뉴스 기반 상승 기대와 함께 매집 및 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['CART 혈압계', '의료기기', '적자']</t>
+          <t>['의료기기', '혈압계', '매집']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6180</v>
+        <v>6230</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+5.64%</t>
+          <t>+6.50%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.7</v>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H7" t="n">
         <v>1.61</v>
@@ -1070,7 +1070,7 @@
         <v>2.31</v>
       </c>
       <c r="O7" t="n">
-        <v>9846018855</v>
+        <v>10298601465</v>
       </c>
       <c r="P7" t="n">
         <v>21500</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1733000</v>
+        <v>1741000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.22%</t>
+          <t>+5.71%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F8" t="n">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G8" t="n">
-        <v>1947</v>
+        <v>1889</v>
       </c>
       <c r="H8" t="n">
         <v>50.5</v>
@@ -1162,7 +1162,7 @@
         <v>50.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1562468445500</v>
+        <v>1653003990000</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입 예정 및 외인 매수세 유입에 따른 200만원 돌파 기대감.</t>
+          <t>자사주 매입과 200만원 돌파에 대한 기대감 표출. 상승 추세 진입 및 외인 매집 정황.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주매입', '외인매집', '주가전망']</t>
+          <t>['자사주매입', '상승추세', '외인매집']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83300</v>
+        <v>83400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.18%</t>
+          <t>+5.30%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" t="n">
-        <v>250</v>
+        <v>302</v>
       </c>
       <c r="H9" t="n">
         <v>23.53</v>
@@ -1254,7 +1254,7 @@
         <v>23.61</v>
       </c>
       <c r="O9" t="n">
-        <v>107081084850</v>
+        <v>113283186850</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>하반기 수주 기대감 및 원자력주 전반의 상승세. 10만원 돌파 가능성 및 83000원대 매물 소화 중.</t>
+          <t>하반기 수주 및 대미 투자 관련 긍정적 전망과 함께 원자력주 전반의 상승세 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주', '원자력주', '매물 소화']</t>
+          <t>['하반기수주', '대미투자', '원자력']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,70 +1299,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13590</v>
+        <v>17590</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.46%</t>
+          <t>+4.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>193</v>
+        <v>122</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82</v>
+        <v>10.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13010</v>
+        <v>16850</v>
       </c>
       <c r="K10" t="n">
-        <v>13420</v>
+        <v>16870</v>
       </c>
       <c r="L10" t="n">
-        <v>14100</v>
+        <v>17770</v>
       </c>
       <c r="M10" t="n">
-        <v>13410</v>
+        <v>16590</v>
       </c>
       <c r="N10" t="n">
-        <v>1.91</v>
+        <v>10.36</v>
       </c>
       <c r="O10" t="n">
-        <v>51258681645</v>
+        <v>50735908700</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>1252</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>204000</v>
+        <v>82000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>광통신주 상승 추세 및 미국 시장 동반 상승 기대. 다만, 주가 변동성이 크고 14000원대 매물 부담 존재.</t>
+          <t>러우 전쟁 종전 분위기와 원전 관련 이슈로 인한 상승 기대 및 단기 수익 실현 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신주', '상승 추세', '변동성']</t>
+          <t>['러우전쟁', '원전', '수익실현']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>264250</v>
+        <v>13580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+4.38%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>781</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>456</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>2901</v>
+        <v>211</v>
       </c>
       <c r="H11" t="n">
-        <v>46.73</v>
+        <v>1.82</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>255500</v>
+        <v>13010</v>
       </c>
       <c r="K11" t="n">
-        <v>267000</v>
+        <v>13420</v>
       </c>
       <c r="L11" t="n">
-        <v>268000</v>
+        <v>14100</v>
       </c>
       <c r="M11" t="n">
-        <v>264000</v>
+        <v>13410</v>
       </c>
       <c r="N11" t="n">
-        <v>46.71</v>
+        <v>1.91</v>
       </c>
       <c r="O11" t="n">
-        <v>1088118218250</v>
+        <v>52941862185</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>69600</v>
+        <v>1252</v>
       </c>
       <c r="R11" t="n">
-        <v>1074000</v>
+        <v>204000</v>
       </c>
       <c r="S11" t="n">
-        <v>809000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>삼성전자, 30만원 터치 및 50~60만+a 목표주가 언급. 배당 기대와 함께 단기 매도 의견도 혼재.</t>
+          <t>광통신주 대장주로서의 기대감 및 공매도 현황 언급. 주가 변동성에 대한 의견 교환.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['목표주가', '배당', '매도']</t>
+          <t>['공매도', '대장주', '변동성']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23150</v>
+        <v>265000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2.89%</t>
+          <t>+3.72%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.62</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>792</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>463</v>
       </c>
       <c r="G12" t="n">
-        <v>99</v>
+        <v>2674</v>
       </c>
       <c r="H12" t="n">
-        <v>5.6</v>
+        <v>46.73</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>22500</v>
+        <v>255500</v>
       </c>
       <c r="K12" t="n">
-        <v>23100</v>
+        <v>267000</v>
       </c>
       <c r="L12" t="n">
-        <v>24000</v>
+        <v>268000</v>
       </c>
       <c r="M12" t="n">
-        <v>21500</v>
+        <v>264000</v>
       </c>
       <c r="N12" t="n">
-        <v>4.98</v>
+        <v>46.71</v>
       </c>
       <c r="O12" t="n">
-        <v>102752774350</v>
+        <v>1139126873500</v>
       </c>
       <c r="P12" t="n">
-        <v>50600</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>9070</v>
+        <v>69600</v>
       </c>
       <c r="R12" t="n">
-        <v>-51000</v>
+        <v>1074000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>809000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>로봇 관련주로 인한 상승 기대감, 단기 급등 후 변동성 출현.</t>
+          <t>배당 및 반도체 이슈를 기반으로 한 상승 기대감과 목표 주가 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['로봇', '신사업', '변동성']</t>
+          <t>['배당', '반도체', '목표주가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10440</v>
+        <v>23050</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.05</v>
+        <v>0.62</v>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="H13" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10390</v>
+        <v>22500</v>
       </c>
       <c r="K13" t="n">
-        <v>10050</v>
+        <v>23100</v>
       </c>
       <c r="L13" t="n">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="M13" t="n">
-        <v>9770</v>
+        <v>21500</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>4.98</v>
       </c>
       <c r="O13" t="n">
-        <v>16099632815</v>
+        <v>108890589525</v>
       </c>
       <c r="P13" t="n">
-        <v>15640</v>
+        <v>50600</v>
       </c>
       <c r="Q13" t="n">
-        <v>5470</v>
+        <v>9070</v>
       </c>
       <c r="R13" t="n">
-        <v>-84000</v>
+        <v>-51000</v>
       </c>
       <c r="S13" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>호재 발생 및 공매도 세력과의 공방 속 200만원 목표 주가 기대.</t>
+          <t>로봇주 테마와 신사업 진출 기대감 속에서 단기 급등 및 거래량 주목.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['호재', '공매도', '주가목표']</t>
+          <t>['로봇주', '신사업', '거래량']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16100</v>
+        <v>16130</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>22033196395</v>
+        <v>23991815880</v>
       </c>
       <c r="P14" t="n">
         <v>19380</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>메가특구법 발의 및 호남 반도체 산단 관련 긍정적 뉴스. 다만, 투자 주체별 매매 동향은 혼조세.</t>
+          <t>신규 사업 및 인프라 투자 관련 언급과 함께 개별 주포에 대한 기대감 혼재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['메가특구법', '반도체 산단', '투자 심리']</t>
+          <t>['신규사업', '인프라', '주포']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>아난티</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5440</v>
+        <v>10360</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.73%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.42</v>
+        <v>0.05</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="H15" t="n">
-        <v>4.81</v>
+        <v>5.75</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>5710</v>
+        <v>10390</v>
       </c>
       <c r="K15" t="n">
-        <v>5640</v>
+        <v>10050</v>
       </c>
       <c r="L15" t="n">
-        <v>5650</v>
+        <v>11000</v>
       </c>
       <c r="M15" t="n">
-        <v>5270</v>
+        <v>9770</v>
       </c>
       <c r="N15" t="n">
-        <v>4.39</v>
+        <v>5.7</v>
       </c>
       <c r="O15" t="n">
-        <v>10881645515</v>
+        <v>16599223805</v>
       </c>
       <c r="P15" t="n">
-        <v>10480</v>
+        <v>15640</v>
       </c>
       <c r="Q15" t="n">
-        <v>3150</v>
+        <v>5470</v>
       </c>
       <c r="R15" t="n">
-        <v>-307000</v>
+        <v>-84000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대북주 테마 부각 및 금강산 관광 기대. 다만, 외인/연기금 매수세에도 불구하고 주가 하락 및 도박주 리스크 존재.</t>
+          <t>주가 상승에 대한 기대감과 함께 공매도에 대한 부정적 의견. 호재 발생 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대북주', '금강산 관광', '도박주']</t>
+          <t>['공매도', '호재', '주가상승']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>025980</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>아난티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5310</v>
+        <v>5450</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-7.49%</t>
+          <t>-4.55%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>5740</v>
+        <v>5710</v>
       </c>
       <c r="K16" t="n">
-        <v>5250</v>
+        <v>5640</v>
       </c>
       <c r="L16" t="n">
-        <v>5420</v>
+        <v>5650</v>
       </c>
       <c r="M16" t="n">
-        <v>5000</v>
+        <v>5270</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="O16" t="n">
-        <v>2152749210</v>
+        <v>11409265005</v>
       </c>
       <c r="P16" t="n">
-        <v>9680</v>
+        <v>10480</v>
       </c>
       <c r="Q16" t="n">
-        <v>371</v>
+        <v>3150</v>
       </c>
       <c r="R16" t="n">
-        <v>-10000</v>
+        <v>-307000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 구주 매각 이슈로 인한 악재 발생, 하한가 기록.</t>
+          <t>하락세에 대한 우려와 함께 외인·연기금의 매수세, 북한 관련 이슈 언급. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,18 +1923,110 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>['외인매수', '대북주', '주가조작']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>025980</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5250</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-8.54%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>75</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G17" t="n">
+        <v>161</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2290123640</v>
+      </c>
+      <c r="P17" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>371</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 및 구주 매각 이슈로 인한 악재 발생, 하한가 기록.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>['반기보고서', '악재', '하한가']</t>
         </is>
       </c>
-      <c r="X16" t="n">
+      <c r="X17" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>226340</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52800</v>
+        <v>52300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+20.41%</t>
+          <t>+19.27%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" t="n">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>91378657225</v>
+        <v>96427909375</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>상승 추세와 공매도 감소에 따른 강한 상승 기대감 및 수익 실현 언급.</t>
+          <t>공매도 감소 및 우상향 추세 언급, 전고점 돌파 및 6-7만원 구간 매물대 약화 전망. 큰 폭 상승 마감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['상승추세', '공매도', '수익실현']</t>
+          <t>['공매도', '우상향', '매물대']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3695</v>
+        <v>3655</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+13.17%</t>
+          <t>+11.94%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>138654130162</v>
+        <v>143932071492</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>탈모약 관련 이슈와 함께 단기 급등 및 3연상 기대감 언급.</t>
+          <t>바이오니아, 삼익 등 타 종목 언급과 함께 긍정적 흐름 기대. '60% 상승' 등 구체적 전망 제시. 큰 폭 상승 마감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['탈모약', '급등', '3연상']</t>
+          <t>['바이오니아', '상승 전망']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="F4" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G4" t="n">
-        <v>782</v>
+        <v>799</v>
       </c>
       <c r="H4" t="n">
         <v>29.46</v>
@@ -794,7 +794,7 @@
         <v>29.51</v>
       </c>
       <c r="O4" t="n">
-        <v>226568504000</v>
+        <v>235319289500</v>
       </c>
       <c r="P4" t="n">
         <v>438000</v>
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8680</v>
+        <v>6370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+9.18%</t>
+          <t>+8.89%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>227</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6</v>
+        <v>1.61</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7950</v>
+        <v>5850</v>
       </c>
       <c r="K5" t="n">
-        <v>8200</v>
+        <v>6000</v>
       </c>
       <c r="L5" t="n">
-        <v>9210</v>
+        <v>6490</v>
       </c>
       <c r="M5" t="n">
-        <v>7980</v>
+        <v>5940</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>2.31</v>
       </c>
       <c r="O5" t="n">
-        <v>76245412660</v>
+        <v>10650637125</v>
       </c>
       <c r="P5" t="n">
-        <v>15960</v>
+        <v>21500</v>
       </c>
       <c r="Q5" t="n">
-        <v>3500</v>
+        <v>2300</v>
       </c>
       <c r="R5" t="n">
-        <v>208000</v>
+        <v>-35000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미프진 관련 이슈와 함께 주가 상승 기대감 및 단기 매매 관점의 글 다수.</t>
+          <t>세계폐암학회 관련 뉴스와 신약 개발 가능성에 대한 기대감이 높음. 보유 및 저점 추매 권유가 있으며, 공매도에 대한 언급도 존재. 주가 상승에 대한 강한 의지 표현.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['미프진', '단기매매', '주가']</t>
+          <t>['신약 개발', '세계폐암학회', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25350</v>
+        <v>8600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+7.87%</t>
+          <t>+8.18%</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="E6" t="n">
+        <v>52</v>
+      </c>
+      <c r="F6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G6" t="n">
+        <v>85</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>7950</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8200</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9210</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7980</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O6" t="n">
+        <v>78960682395</v>
+      </c>
+      <c r="P6" t="n">
+        <v>15960</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>208000</v>
+      </c>
+      <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
-        <v>281</v>
-      </c>
-      <c r="F6" t="n">
-        <v>138</v>
-      </c>
-      <c r="G6" t="n">
-        <v>341</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>23500</v>
-      </c>
-      <c r="K6" t="n">
-        <v>23200</v>
-      </c>
-      <c r="L6" t="n">
-        <v>26450</v>
-      </c>
-      <c r="M6" t="n">
-        <v>22800</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>280986319875</v>
-      </c>
-      <c r="P6" t="n">
-        <v>28750</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>8200</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-1000</v>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>의료기기 및 혈압계 관련 뉴스 기반 상승 기대와 함께 매집 및 단기 급등 가능성 언급.</t>
+          <t>미프진 관련 언급 다수, 시장 기대감은 있으나 뚜렷한 근거 제시 부족. 등락률 소폭 상승.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['의료기기', '혈압계', '매집']</t>
+          <t>['미프진', '기대감']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6230</v>
+        <v>25000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.50%</t>
+          <t>+6.38%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>307</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="G7" t="n">
-        <v>205</v>
+        <v>359</v>
       </c>
       <c r="H7" t="n">
-        <v>1.61</v>
+        <v>0.16</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5850</v>
+        <v>23500</v>
       </c>
       <c r="K7" t="n">
-        <v>6000</v>
+        <v>23200</v>
       </c>
       <c r="L7" t="n">
-        <v>6490</v>
+        <v>26450</v>
       </c>
       <c r="M7" t="n">
-        <v>5940</v>
+        <v>22800</v>
       </c>
       <c r="N7" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>10298601465</v>
+        <v>321941425550</v>
       </c>
       <c r="P7" t="n">
-        <v>21500</v>
+        <v>28750</v>
       </c>
       <c r="Q7" t="n">
-        <v>2300</v>
+        <v>8200</v>
       </c>
       <c r="R7" t="n">
-        <v>-35000</v>
+        <v>-2000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신약 개발 가능성 및 현대바이오와의 연관성 언급. 다만, 허황된 꿈이라는 부정적 시각 및 고점 매도 주의 필요.</t>
+          <t>CART 혈압계 관련 뉴스 언급, 서울대 등 유수 기관 협력 기반. 단기 급등 후 조정 및 향후 급등 가능성 언급. 소폭 상승 마감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['신약 개발', '현대바이오', '고점 매도']</t>
+          <t>['CART', '혈압계', '협력']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1741000</v>
+        <v>1744000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.71%</t>
+          <t>+5.89%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>797</v>
       </c>
       <c r="F8" t="n">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="G8" t="n">
-        <v>1889</v>
+        <v>1914</v>
       </c>
       <c r="H8" t="n">
         <v>50.5</v>
@@ -1162,7 +1162,7 @@
         <v>50.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1653003990000</v>
+        <v>1784139813000</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입과 200만원 돌파에 대한 기대감 표출. 상승 추세 진입 및 외인 매집 정황.</t>
+          <t>자사주 매입 및 외국인/기관 순매수세 유입에 따른 주가 상승 기대감 높음. 200만원 돌파 및 고공 행진 전망. 숏커버링 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주매입', '상승추세', '외인매집']</t>
+          <t>['자사주매입', '외국인순매수', '숏커버링']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83400</v>
+        <v>82900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.30%</t>
+          <t>+4.67%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F9" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G9" t="n">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="H9" t="n">
         <v>23.53</v>
@@ -1254,7 +1254,7 @@
         <v>23.61</v>
       </c>
       <c r="O9" t="n">
-        <v>113283186850</v>
+        <v>119518966050</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>하반기 수주 및 대미 투자 관련 긍정적 전망과 함께 원자력주 전반의 상승세 언급.</t>
+          <t>하반기 본격 수주 및 대형 원전, 가스복합화력발전 언급. 기술력 입증 기반 상승 추세 전망. 큰 폭 상승 마감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['하반기수주', '대미투자', '원자력']</t>
+          <t>['하반기 수주', '대형 원전', '기술력']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,70 +1299,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17590</v>
+        <v>13530</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.39%</t>
+          <t>+4.00%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>122</v>
+        <v>214</v>
       </c>
       <c r="H10" t="n">
-        <v>10.4</v>
+        <v>1.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16850</v>
+        <v>13010</v>
       </c>
       <c r="K10" t="n">
-        <v>16870</v>
+        <v>13420</v>
       </c>
       <c r="L10" t="n">
-        <v>17770</v>
+        <v>14100</v>
       </c>
       <c r="M10" t="n">
-        <v>16590</v>
+        <v>13410</v>
       </c>
       <c r="N10" t="n">
-        <v>10.36</v>
+        <v>1.91</v>
       </c>
       <c r="O10" t="n">
-        <v>50735908700</v>
+        <v>54829891005</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>1252</v>
       </c>
       <c r="R10" t="n">
-        <v>82000</v>
+        <v>204000</v>
       </c>
       <c r="S10" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>러우 전쟁 종전 분위기와 원전 관련 이슈로 인한 상승 기대 및 단기 수익 실현 언급.</t>
+          <t>회사의 가치를 긍정적으로 평가하며, 당일 광통신주 대장으로서의 역할 기대. 공매도 물량 언급과 함께 주가 변동성에 대한 언급 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['러우전쟁', '원전', '수익실현']</t>
+          <t>['광통신주', '공매도', '주가 변동성']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13580</v>
+        <v>264750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.38%</t>
+          <t>+3.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
+        <v>795</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>460</v>
       </c>
       <c r="G11" t="n">
-        <v>211</v>
+        <v>2492</v>
       </c>
       <c r="H11" t="n">
-        <v>1.82</v>
+        <v>46.73</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13010</v>
+        <v>255500</v>
       </c>
       <c r="K11" t="n">
-        <v>13420</v>
+        <v>267000</v>
       </c>
       <c r="L11" t="n">
-        <v>14100</v>
+        <v>268000</v>
       </c>
       <c r="M11" t="n">
-        <v>13410</v>
+        <v>264000</v>
       </c>
       <c r="N11" t="n">
-        <v>1.91</v>
+        <v>46.71</v>
       </c>
       <c r="O11" t="n">
-        <v>52941862185</v>
+        <v>1203393250000</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>1252</v>
+        <v>69600</v>
       </c>
       <c r="R11" t="n">
-        <v>204000</v>
+        <v>1074000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>809000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>광통신주 대장주로서의 기대감 및 공매도 현황 언급. 주가 변동성에 대한 의견 교환.</t>
+          <t>배당 및 목표 주가 언급, 반도체 관련 뉴스 인용. 긍정적 전망과 더불어 소폭 상승 마감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '대장주', '변동성']</t>
+          <t>['배당', '목표 주가', '반도체']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>265000</v>
+        <v>17400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.72%</t>
+          <t>+3.26%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>792</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
-        <v>463</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>2674</v>
+        <v>128</v>
       </c>
       <c r="H12" t="n">
-        <v>46.73</v>
+        <v>10.4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>255500</v>
+        <v>16850</v>
       </c>
       <c r="K12" t="n">
-        <v>267000</v>
+        <v>16870</v>
       </c>
       <c r="L12" t="n">
-        <v>268000</v>
+        <v>17770</v>
       </c>
       <c r="M12" t="n">
-        <v>264000</v>
+        <v>16590</v>
       </c>
       <c r="N12" t="n">
-        <v>46.71</v>
+        <v>10.36</v>
       </c>
       <c r="O12" t="n">
-        <v>1139126873500</v>
+        <v>54569644560</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>69600</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>1074000</v>
+        <v>82000</v>
       </c>
       <c r="S12" t="n">
-        <v>809000</v>
+        <v>-8000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>배당 및 반도체 이슈를 기반으로 한 상승 기대감과 목표 주가 언급.</t>
+          <t>러우 전쟁 종전 분위기 및 중동 관련 언급, 주가 상승 기대감 표출. 소폭 상승 마감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['배당', '반도체', '목표주가']</t>
+          <t>['러우 전쟁', '중동']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23050</v>
+        <v>6850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+2.44%</t>
+          <t>+2.09%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="H13" t="n">
-        <v>5.6</v>
+        <v>16.4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22500</v>
+        <v>6710</v>
       </c>
       <c r="K13" t="n">
-        <v>23100</v>
+        <v>6680</v>
       </c>
       <c r="L13" t="n">
-        <v>24000</v>
+        <v>7040</v>
       </c>
       <c r="M13" t="n">
-        <v>21500</v>
+        <v>6600</v>
       </c>
       <c r="N13" t="n">
-        <v>4.98</v>
+        <v>15.55</v>
       </c>
       <c r="O13" t="n">
-        <v>108890589525</v>
+        <v>7271284755</v>
       </c>
       <c r="P13" t="n">
-        <v>50600</v>
+        <v>13000</v>
       </c>
       <c r="Q13" t="n">
-        <v>9070</v>
+        <v>6030</v>
       </c>
       <c r="R13" t="n">
-        <v>-51000</v>
+        <v>2000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>로봇주 테마와 신사업 진출 기대감 속에서 단기 급등 및 거래량 주목.</t>
+          <t>반도체 및 로봇 관련 언급, IPO 예정 기업 존재. 주가 부양 기대와 함께 '폭락주', '개미 털기' 등 부정적 언급 혼재. 소폭 상승 마감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '거래량']</t>
+          <t>['반도체', '로봇', 'IPO']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16130</v>
+        <v>22750</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>274</v>
+        <v>104</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16090</v>
+        <v>22500</v>
       </c>
       <c r="K14" t="n">
-        <v>16150</v>
+        <v>23100</v>
       </c>
       <c r="L14" t="n">
-        <v>16480</v>
+        <v>24000</v>
       </c>
       <c r="M14" t="n">
-        <v>15830</v>
+        <v>21500</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O14" t="n">
-        <v>23991815880</v>
+        <v>112588277225</v>
       </c>
       <c r="P14" t="n">
-        <v>19380</v>
+        <v>50600</v>
       </c>
       <c r="Q14" t="n">
-        <v>3200</v>
+        <v>9070</v>
       </c>
       <c r="R14" t="n">
-        <v>-3000</v>
+        <v>-51000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>신규 사업 및 인프라 투자 관련 언급과 함께 개별 주포에 대한 기대감 혼재.</t>
+          <t>국민성장펀드 관련 언급과 함께 거래량에 주목. 신사업 진출 및 로봇주 테마 상승 기대감 존재. 그러나 단기 급등락 및 투자주의 종목 지정 언급으로 변동성 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['신규사업', '인프라', '주포']</t>
+          <t>['국민성장펀드', '로봇주', '거래량']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10360</v>
+        <v>30250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="H15" t="n">
-        <v>5.75</v>
+        <v>48.88</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>10390</v>
+        <v>30200</v>
       </c>
       <c r="K15" t="n">
-        <v>10050</v>
+        <v>30350</v>
       </c>
       <c r="L15" t="n">
-        <v>11000</v>
+        <v>30900</v>
       </c>
       <c r="M15" t="n">
-        <v>9770</v>
+        <v>29900</v>
       </c>
       <c r="N15" t="n">
-        <v>5.7</v>
+        <v>24.02</v>
       </c>
       <c r="O15" t="n">
-        <v>16599223805</v>
+        <v>46245487700</v>
       </c>
       <c r="P15" t="n">
-        <v>15640</v>
+        <v>31200</v>
       </c>
       <c r="Q15" t="n">
-        <v>5470</v>
+        <v>21000</v>
       </c>
       <c r="R15" t="n">
-        <v>-84000</v>
+        <v>139000</v>
       </c>
       <c r="S15" t="n">
-        <v>-2000</v>
+        <v>28000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 기대감과 함께 공매도에 대한 부정적 의견. 호재 발생 가능성 언급.</t>
+          <t>정배열 우상향 추세 및 공매도 물량 언급, 3만원 구간 지지선 기대. 소폭 상승 마감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '호재', '주가상승']</t>
+          <t>['정배열', '공매도', '지지선']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>아난티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5450</v>
+        <v>16080</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>148</v>
+        <v>287</v>
       </c>
       <c r="H16" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>5710</v>
+        <v>16090</v>
       </c>
       <c r="K16" t="n">
-        <v>5640</v>
+        <v>16150</v>
       </c>
       <c r="L16" t="n">
-        <v>5650</v>
+        <v>16480</v>
       </c>
       <c r="M16" t="n">
-        <v>5270</v>
+        <v>15830</v>
       </c>
       <c r="N16" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>11409265005</v>
+        <v>24994319225</v>
       </c>
       <c r="P16" t="n">
-        <v>10480</v>
+        <v>19380</v>
       </c>
       <c r="Q16" t="n">
-        <v>3150</v>
+        <v>3200</v>
       </c>
       <c r="R16" t="n">
-        <v>-307000</v>
+        <v>-3000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>하락세에 대한 우려와 함께 외인·연기금의 매수세, 북한 관련 이슈 언급. 주가 조작 의혹 제기.</t>
+          <t>메가 특구법 발의 및 호남 반도체 산단 관련 언급, 주가 상승 기대감 있으나 '개잡주' 등 부정적 표현 혼재. 소폭 하락 마감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['외인매수', '대북주', '주가조작']</t>
+          <t>['메가 특구법', '반도체 산단', '개잡주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>025980</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5250</v>
+        <v>10340</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-8.54%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G17" t="n">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,47 +1975,47 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>5740</v>
+        <v>10390</v>
       </c>
       <c r="K17" t="n">
-        <v>5250</v>
+        <v>10050</v>
       </c>
       <c r="L17" t="n">
-        <v>5420</v>
+        <v>11000</v>
       </c>
       <c r="M17" t="n">
-        <v>5000</v>
+        <v>9770</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>2290123640</v>
+        <v>16925165495</v>
       </c>
       <c r="P17" t="n">
-        <v>9680</v>
+        <v>15640</v>
       </c>
       <c r="Q17" t="n">
-        <v>371</v>
+        <v>5470</v>
       </c>
       <c r="R17" t="n">
-        <v>-10000</v>
+        <v>-84000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 구주 매각 이슈로 인한 악재 발생, 하한가 기록.</t>
+          <t>주가 상승에 대한 강한 기대감과 함께 2백만원 목표가 언급. 순환매 및 호재 가능성 제기. 공매도 세력에 대한 경계심 존재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '하한가']</t>
+          <t>['순환매', '공매도', '호재']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2027,6 +2027,190 @@
         </is>
       </c>
       <c r="Z17" t="inlineStr">
+        <is>
+          <t>064550</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>아난티</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5435</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-4.82%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E18" t="n">
+        <v>51</v>
+      </c>
+      <c r="F18" t="n">
+        <v>40</v>
+      </c>
+      <c r="G18" t="n">
+        <v>150</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>5710</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5640</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5650</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5270</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="O18" t="n">
+        <v>11756896085</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10480</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3150</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-307000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>하락세에 대한 우려와 함께 외인·연기금의 매수세, 북한 관련 이슈 언급. 주가 조작 의혹 제기.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['외인매수', '대북주', '주가조작']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>025980</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5240</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-8.71%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>79</v>
+      </c>
+      <c r="F19" t="n">
+        <v>44</v>
+      </c>
+      <c r="G19" t="n">
+        <v>168</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2368134080</v>
+      </c>
+      <c r="P19" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>371</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 및 악재성 기사 출현으로 하한가 예상. 주가 하락에 대한 우려와 함께 일부 투자자들의 탈출 언급. 구주 매각 관련 불확실성 존재.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['반기보고서', '악재 뉴스', '구주 매각']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>226340</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52300</v>
+        <v>51800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+19.27%</t>
+          <t>+18.13%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F2" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>96427909375</v>
+        <v>101946804075</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>공매도 감소 및 우상향 추세 언급, 전고점 돌파 및 6-7만원 구간 매물대 약화 전망. 큰 폭 상승 마감.</t>
+          <t>공매도 감소 및 전고점 돌파 기대감. 6~7만원 구간 매물벽 약세 전망. 긍정적 우상향 추세.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공매도', '우상향', '매물대']</t>
+          <t>['공매도', '전고점', '우상향']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>143932071492</v>
+        <v>146977492358</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>바이오니아, 삼익 등 타 종목 언급과 함께 긍정적 흐름 기대. '60% 상승' 등 구체적 전망 제시. 큰 폭 상승 마감.</t>
+          <t>금주 60% 이상 상승 전망. 월가 급등 및 거래량 증가 기대. 삼익, 제이신약과의 비교 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['바이오니아', '상승 전망']</t>
+          <t>['상승전망', '월가', '거래량']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>220000</v>
+        <v>6380</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+9.18%</t>
+          <t>+9.06%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.05</v>
+        <v>-0.7</v>
       </c>
       <c r="E4" t="n">
-        <v>282</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>163</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>799</v>
+        <v>250</v>
       </c>
       <c r="H4" t="n">
-        <v>29.46</v>
+        <v>1.61</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>201500</v>
+        <v>5850</v>
       </c>
       <c r="K4" t="n">
-        <v>212500</v>
+        <v>6000</v>
       </c>
       <c r="L4" t="n">
-        <v>225500</v>
+        <v>6525</v>
       </c>
       <c r="M4" t="n">
-        <v>212500</v>
+        <v>5940</v>
       </c>
       <c r="N4" t="n">
-        <v>29.51</v>
+        <v>2.31</v>
       </c>
       <c r="O4" t="n">
-        <v>235319289500</v>
+        <v>11773989395</v>
       </c>
       <c r="P4" t="n">
-        <v>438000</v>
+        <v>21500</v>
       </c>
       <c r="Q4" t="n">
-        <v>74700</v>
+        <v>2300</v>
       </c>
       <c r="R4" t="n">
-        <v>317000</v>
+        <v>-35000</v>
       </c>
       <c r="S4" t="n">
-        <v>102000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 사업 및 액추에이터 기술 관련 호재와 프로그램 매수세 유입에 따른 기대감.</t>
+          <t>폐암학회 관련 기대감 및 신약 개발 가능성 언급. 저점 매수 기회 및 보유 권고. 다만, 6,500원 돌파 필요성 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇사업', '액추에이터', '프로그램매수']</t>
+          <t>['폐암학회', '신약 개발', '저점 매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6370</v>
+        <v>218500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+8.89%</t>
+          <t>+8.44%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.7</v>
+        <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>290</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>166</v>
       </c>
       <c r="G5" t="n">
-        <v>227</v>
+        <v>841</v>
       </c>
       <c r="H5" t="n">
-        <v>1.61</v>
+        <v>29.46</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5850</v>
+        <v>201500</v>
       </c>
       <c r="K5" t="n">
-        <v>6000</v>
+        <v>212500</v>
       </c>
       <c r="L5" t="n">
-        <v>6490</v>
+        <v>225500</v>
       </c>
       <c r="M5" t="n">
-        <v>5940</v>
+        <v>212500</v>
       </c>
       <c r="N5" t="n">
-        <v>2.31</v>
+        <v>29.51</v>
       </c>
       <c r="O5" t="n">
-        <v>10650637125</v>
+        <v>240706070000</v>
       </c>
       <c r="P5" t="n">
-        <v>21500</v>
+        <v>438000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2300</v>
+        <v>74700</v>
       </c>
       <c r="R5" t="n">
-        <v>-35000</v>
+        <v>317000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>102000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>세계폐암학회 관련 뉴스와 신약 개발 가능성에 대한 기대감이 높음. 보유 및 저점 추매 권유가 있으며, 공매도에 대한 언급도 존재. 주가 상승에 대한 강한 의지 표현.</t>
+          <t>로봇 사업 진출 및 기술력 부각. CES 2024 관련 긍정적 뉴스 및 프로그램 매수세 유입. 23만 탈환 및 100조 시총 저평가 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['신약 개발', '세계폐암학회', '공매도']</t>
+          <t>['로봇', 'CES 2024', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
@@ -946,13 +946,13 @@
         <v>-0.72</v>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H6" t="n">
         <v>0.6</v>
@@ -978,7 +978,7 @@
         <v>1.32</v>
       </c>
       <c r="O6" t="n">
-        <v>78960682395</v>
+        <v>80371183605</v>
       </c>
       <c r="P6" t="n">
         <v>15960</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미프진 관련 언급 다수, 시장 기대감은 있으나 뚜렷한 근거 제시 부족. 등락률 소폭 상승.</t>
+          <t>미프진 공식화 및 단계적 도입 지시 관련 기대감. 외국인, 기관 순매수 진입.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['미프진', '기대감']</t>
+          <t>['미프진', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25000</v>
+        <v>25400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.38%</t>
+          <t>+8.09%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="F7" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G7" t="n">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="H7" t="n">
         <v>0.16</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>321941425550</v>
+        <v>339471343850</v>
       </c>
       <c r="P7" t="n">
         <v>28750</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>CART 혈압계 관련 뉴스 언급, 서울대 등 유수 기관 협력 기반. 단기 급등 후 조정 및 향후 급등 가능성 언급. 소폭 상승 마감.</t>
+          <t>CART 혈압계 뉴스 및 서울대, 아산병원 등 임상 협력 기반 급등 기대. 세계 1위, 최초 타이틀.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['CART', '혈압계', '협력']</t>
+          <t>['CART', '혈압계', '임상']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1744000</v>
+        <v>1742000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.89%</t>
+          <t>+5.77%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F8" t="n">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="G8" t="n">
-        <v>1914</v>
+        <v>1965</v>
       </c>
       <c r="H8" t="n">
         <v>50.5</v>
@@ -1162,7 +1162,7 @@
         <v>50.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1784139813000</v>
+        <v>1962577041500</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입 및 외국인/기관 순매수세 유입에 따른 주가 상승 기대감 높음. 200만원 돌파 및 고공 행진 전망. 숏커버링 가능성 언급.</t>
+          <t>자사주 매입 및 외국인, 기관 순매수 지속. 200만원 돌파 및 숏커버링 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주매입', '외국인순매수', '숏커버링']</t>
+          <t>['자사주매입', '외국인', '숏커버링']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82900</v>
+        <v>83100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.67%</t>
+          <t>+4.92%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F9" t="n">
         <v>76</v>
       </c>
       <c r="G9" t="n">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="H9" t="n">
         <v>23.53</v>
@@ -1254,7 +1254,7 @@
         <v>23.61</v>
       </c>
       <c r="O9" t="n">
-        <v>119518966050</v>
+        <v>124297243000</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>하반기 본격 수주 및 대형 원전, 가스복합화력발전 언급. 기술력 입증 기반 상승 추세 전망. 큰 폭 상승 마감.</t>
+          <t>대미 투자 1호(가스복합) 계약 및 하반기 본격 수주 기대. 원자력주 전반적 상승세.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['하반기 수주', '대형 원전', '기술력']</t>
+          <t>['대미투자', '가스복합', '원자력']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13530</v>
+        <v>265000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.00%</t>
+          <t>+3.72%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>51</v>
+        <v>795</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>467</v>
       </c>
       <c r="G10" t="n">
-        <v>214</v>
+        <v>2265</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82</v>
+        <v>46.73</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13010</v>
+        <v>255500</v>
       </c>
       <c r="K10" t="n">
-        <v>13420</v>
+        <v>267000</v>
       </c>
       <c r="L10" t="n">
-        <v>14100</v>
+        <v>268000</v>
       </c>
       <c r="M10" t="n">
-        <v>13410</v>
+        <v>264000</v>
       </c>
       <c r="N10" t="n">
-        <v>1.91</v>
+        <v>46.71</v>
       </c>
       <c r="O10" t="n">
-        <v>54829891005</v>
+        <v>1304293699500</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>1252</v>
+        <v>69600</v>
       </c>
       <c r="R10" t="n">
-        <v>204000</v>
+        <v>1074000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>809000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>회사의 가치를 긍정적으로 평가하며, 당일 광통신주 대장으로서의 역할 기대. 공매도 물량 언급과 함께 주가 변동성에 대한 언급 존재.</t>
+          <t>애플 배당 및 샌디스크 폭등 뉴스 기반 반도체 섹터 상승 기대. 30만원 목표 매수세 유입.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신주', '공매도', '주가 변동성']</t>
+          <t>['반도체', '배당', '매수세']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>264750</v>
+        <v>13460</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.62%</t>
+          <t>+3.46%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>795</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>460</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>2492</v>
+        <v>220</v>
       </c>
       <c r="H11" t="n">
-        <v>46.73</v>
+        <v>1.82</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>255500</v>
+        <v>13010</v>
       </c>
       <c r="K11" t="n">
-        <v>267000</v>
+        <v>13420</v>
       </c>
       <c r="L11" t="n">
-        <v>268000</v>
+        <v>14100</v>
       </c>
       <c r="M11" t="n">
-        <v>264000</v>
+        <v>13410</v>
       </c>
       <c r="N11" t="n">
-        <v>46.71</v>
+        <v>1.91</v>
       </c>
       <c r="O11" t="n">
-        <v>1203393250000</v>
+        <v>57156289370</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>69600</v>
+        <v>1252</v>
       </c>
       <c r="R11" t="n">
-        <v>1074000</v>
+        <v>204000</v>
       </c>
       <c r="S11" t="n">
-        <v>809000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>배당 및 목표 주가 언급, 반도체 관련 뉴스 인용. 긍정적 전망과 더불어 소폭 상승 마감.</t>
+          <t>회사의 가치를 긍정적으로 평가하며, 당일 광통신주 대장으로서의 역할 기대. 공매도 물량 언급과 함께 주가 변동성에 대한 언급 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['배당', '목표 주가', '반도체']</t>
+          <t>['광통신주', '공매도', '주가 변동성']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17400</v>
+        <v>17310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.26%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="H12" t="n">
         <v>10.4</v>
@@ -1530,7 +1530,7 @@
         <v>10.36</v>
       </c>
       <c r="O12" t="n">
-        <v>54569644560</v>
+        <v>57627212320</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>러우 전쟁 종전 분위기 및 중동 관련 언급, 주가 상승 기대감 표출. 소폭 상승 마감.</t>
+          <t>러우 전쟁 종전 분위기 및 중동 투자 관련 기대감. 외국인, 기관, 프매도 순매수.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['러우 전쟁', '중동']</t>
+          <t>['러우전쟁', '중동', '외국인']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6850</v>
+        <v>22925</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+2.09%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="E13" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="H13" t="n">
-        <v>16.4</v>
+        <v>5.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6710</v>
+        <v>22500</v>
       </c>
       <c r="K13" t="n">
-        <v>6680</v>
+        <v>23100</v>
       </c>
       <c r="L13" t="n">
-        <v>7040</v>
+        <v>24000</v>
       </c>
       <c r="M13" t="n">
-        <v>6600</v>
+        <v>21500</v>
       </c>
       <c r="N13" t="n">
-        <v>15.55</v>
+        <v>4.98</v>
       </c>
       <c r="O13" t="n">
-        <v>7271284755</v>
+        <v>114111433750</v>
       </c>
       <c r="P13" t="n">
-        <v>13000</v>
+        <v>50600</v>
       </c>
       <c r="Q13" t="n">
-        <v>6030</v>
+        <v>9070</v>
       </c>
       <c r="R13" t="n">
-        <v>2000</v>
+        <v>-51000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 및 로봇 관련 언급, IPO 예정 기업 존재. 주가 부양 기대와 함께 '폭락주', '개미 털기' 등 부정적 언급 혼재. 소폭 상승 마감.</t>
+          <t>국민성장펀드 3500억 상장사. 거래량 주목, 신사업 진출 재료 부각. 다만, 투자 주의 종목 지정 및 급등락 반복.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', '로봇', 'IPO']</t>
+          <t>['국민성장펀드', '신사업', '거래량']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22750</v>
+        <v>6830</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+1.79%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6</v>
+        <v>16.4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>22500</v>
+        <v>6710</v>
       </c>
       <c r="K14" t="n">
-        <v>23100</v>
+        <v>6680</v>
       </c>
       <c r="L14" t="n">
-        <v>24000</v>
+        <v>7040</v>
       </c>
       <c r="M14" t="n">
-        <v>21500</v>
+        <v>6600</v>
       </c>
       <c r="N14" t="n">
-        <v>4.98</v>
+        <v>15.55</v>
       </c>
       <c r="O14" t="n">
-        <v>112588277225</v>
+        <v>7554808955</v>
       </c>
       <c r="P14" t="n">
-        <v>50600</v>
+        <v>13000</v>
       </c>
       <c r="Q14" t="n">
-        <v>9070</v>
+        <v>6030</v>
       </c>
       <c r="R14" t="n">
-        <v>-51000</v>
+        <v>2000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>국민성장펀드 관련 언급과 함께 거래량에 주목. 신사업 진출 및 로봇주 테마 상승 기대감 존재. 그러나 단기 급등락 및 투자주의 종목 지정 언급으로 변동성 우려.</t>
+          <t>한화로보틱스, 한화세미텍 IPO 예정. 반도체 및 로봇 사업 연계 분석. 흑자 회사 및 10000원 이상 목표가 제시. 외국인 순매수 확인.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['국민성장펀드', '로봇주', '거래량']</t>
+          <t>['IPO', '반도체', '로봇']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
@@ -1774,16 +1774,16 @@
         <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
         <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H15" t="n">
-        <v>48.88</v>
+        <v>48.89</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>24.02</v>
       </c>
       <c r="O15" t="n">
-        <v>46245487700</v>
+        <v>47387889150</v>
       </c>
       <c r="P15" t="n">
         <v>31200</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정배열 우상향 추세 및 공매도 물량 언급, 3만원 구간 지지선 기대. 소폭 상승 마감.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['정배열', '공매도', '지지선']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16080</v>
+        <v>15990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F16" t="n">
         <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>24994319225</v>
+        <v>26292124990</v>
       </c>
       <c r="P16" t="n">
         <v>19380</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>메가 특구법 발의 및 호남 반도체 산단 관련 언급, 주가 상승 기대감 있으나 '개잡주' 등 부정적 표현 혼재. 소폭 하락 마감.</t>
+          <t>9월 메가특구법 발의 및 호남 반도체 산단 관련 기대감. '개잡주' 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['메가 특구법', '반도체 산단', '개잡주']</t>
+          <t>['메가특구법', '반도체', '호남']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10340</v>
+        <v>10260</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="H17" t="n">
         <v>5.75</v>
@@ -1990,7 +1990,7 @@
         <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>16925165495</v>
+        <v>17219936235</v>
       </c>
       <c r="P17" t="n">
         <v>15640</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 강한 기대감과 함께 2백만원 목표가 언급. 순환매 및 호재 가능성 제기. 공매도 세력에 대한 경계심 존재.</t>
+          <t>급등 기대감 및 2백만원 목표가 제시. 공매도 소굴이라는 부정적 의견과 함께 매집 및 순환매 기대. 금일 12층 목표.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['순환매', '공매도', '호재']</t>
+          <t>['급등', '공매도', '순환매']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5435</v>
+        <v>5430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.82%</t>
+          <t>-4.90%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.42</v>
       </c>
       <c r="E18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" t="n">
         <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H18" t="n">
         <v>4.81</v>
@@ -2082,7 +2082,7 @@
         <v>4.39</v>
       </c>
       <c r="O18" t="n">
-        <v>11756896085</v>
+        <v>12018243530</v>
       </c>
       <c r="P18" t="n">
         <v>10480</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>하락세에 대한 우려와 함께 외인·연기금의 매수세, 북한 관련 이슈 언급. 주가 조작 의혹 제기.</t>
+          <t>시진핑 방미 관련 뉴스 부재 및 하락 시작 우려. 대북주 변동성 및 주가 조작 의혹 제기. 외국인, 연기금 매수세 일부 확인.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['외인매수', '대북주', '주가조작']</t>
+          <t>['시진핑', '대북주', '주가 조작']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5240</v>
+        <v>5250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-8.71%</t>
+          <t>-8.54%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2368134080</v>
+        <v>2400412680</v>
       </c>
       <c r="P19" t="n">
         <v>9680</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 악재성 기사 출현으로 하한가 예상. 주가 하락에 대한 우려와 함께 일부 투자자들의 탈출 언급. 구주 매각 관련 불확실성 존재.</t>
+          <t>반기 보고서 제출 지연 악재 및 조선비즈 기사로 인한 하한가 가능성 언급. 구미현 관련 논란 및 탈출 의견 다수.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재 뉴스', '구주 매각']</t>
+          <t>['반기 보고서', '악재', '구미현']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51800</v>
+        <v>51900</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+18.13%</t>
+          <t>+18.36%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G2" t="n">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>101946804075</v>
+        <v>106285735675</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3655</v>
+        <v>3675</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+11.94%</t>
+          <t>+12.56%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>146977492358</v>
+        <v>149696187048</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>금주 60% 이상 상승 전망. 월가 급등 및 거래량 증가 기대. 삼익, 제이신약과의 비교 언급.</t>
+          <t>월가 소식 및 특정 종목과의 동반 상승 기대감 있으나, 뚜렷한 근거는 부족.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['상승전망', '월가', '거래량']</t>
+          <t>['월가', '기대감']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6380</v>
+        <v>218000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+9.06%</t>
+          <t>+8.19%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.7</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>302</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="G4" t="n">
-        <v>250</v>
+        <v>863</v>
       </c>
       <c r="H4" t="n">
-        <v>1.61</v>
+        <v>29.46</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5850</v>
+        <v>201500</v>
       </c>
       <c r="K4" t="n">
-        <v>6000</v>
+        <v>212500</v>
       </c>
       <c r="L4" t="n">
-        <v>6525</v>
+        <v>225500</v>
       </c>
       <c r="M4" t="n">
-        <v>5940</v>
+        <v>212500</v>
       </c>
       <c r="N4" t="n">
-        <v>2.31</v>
+        <v>29.51</v>
       </c>
       <c r="O4" t="n">
-        <v>11773989395</v>
+        <v>246430637500</v>
       </c>
       <c r="P4" t="n">
-        <v>21500</v>
+        <v>438000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2300</v>
+        <v>74700</v>
       </c>
       <c r="R4" t="n">
-        <v>-35000</v>
+        <v>317000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>102000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>폐암학회 관련 기대감 및 신약 개발 가능성 언급. 저점 매수 기회 및 보유 권고. 다만, 6,500원 돌파 필요성 제기.</t>
+          <t>로봇 사업 진출 및 기술력 부각. CES 2024 관련 긍정적 뉴스 및 프로그램 매수세 유입. 23만 탈환 및 100조 시총 저평가 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['폐암학회', '신약 개발', '저점 매수']</t>
+          <t>['로봇', 'CES 2024', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>218500</v>
+        <v>8600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+8.44%</t>
+          <t>+8.18%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>-0.72</v>
       </c>
       <c r="E5" t="n">
-        <v>290</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>841</v>
+        <v>92</v>
       </c>
       <c r="H5" t="n">
-        <v>29.46</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>201500</v>
+        <v>7950</v>
       </c>
       <c r="K5" t="n">
-        <v>212500</v>
+        <v>8200</v>
       </c>
       <c r="L5" t="n">
-        <v>225500</v>
+        <v>9210</v>
       </c>
       <c r="M5" t="n">
-        <v>212500</v>
+        <v>7980</v>
       </c>
       <c r="N5" t="n">
-        <v>29.51</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
-        <v>240706070000</v>
+        <v>81295869340</v>
       </c>
       <c r="P5" t="n">
-        <v>438000</v>
+        <v>15960</v>
       </c>
       <c r="Q5" t="n">
-        <v>74700</v>
+        <v>3500</v>
       </c>
       <c r="R5" t="n">
-        <v>317000</v>
+        <v>208000</v>
       </c>
       <c r="S5" t="n">
-        <v>102000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇 사업 진출 및 기술력 부각. CES 2024 관련 긍정적 뉴스 및 프로그램 매수세 유입. 23만 탈환 및 100조 시총 저평가 전망.</t>
+          <t>미프진 관련 소식과 함께 주가 상승 기대감이 있으나, 윗꼬리 달며 변동성이 큰 모습.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇', 'CES 2024', '프로그램 매수']</t>
+          <t>['미프진', '변동성']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,77 +924,77 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8600</v>
+        <v>25350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+8.18%</t>
+          <t>+7.87%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>341</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>163</v>
       </c>
       <c r="G6" t="n">
-        <v>82</v>
+        <v>461</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6</v>
+        <v>0.16</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7950</v>
+        <v>23500</v>
       </c>
       <c r="K6" t="n">
+        <v>23200</v>
+      </c>
+      <c r="L6" t="n">
+        <v>26450</v>
+      </c>
+      <c r="M6" t="n">
+        <v>22800</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>359190114375</v>
+      </c>
+      <c r="P6" t="n">
+        <v>28750</v>
+      </c>
+      <c r="Q6" t="n">
         <v>8200</v>
       </c>
-      <c r="L6" t="n">
-        <v>9210</v>
-      </c>
-      <c r="M6" t="n">
-        <v>7980</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="O6" t="n">
-        <v>80371183605</v>
-      </c>
-      <c r="P6" t="n">
-        <v>15960</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3500</v>
-      </c>
       <c r="R6" t="n">
-        <v>208000</v>
+        <v>-2000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미프진 공식화 및 단계적 도입 지시 관련 기대감. 외국인, 기관 순매수 진입.</t>
+          <t>CART 혈압계 관련 뉴스 및 서울대/아산병원 등 주요 기관 임상 진입 사실.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['미프진', '외국인', '기관']</t>
+          <t>['CART', '임상', '뉴스']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25400</v>
+        <v>6310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.09%</t>
+          <t>+7.86%</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>66</v>
+      </c>
+      <c r="F7" t="n">
+        <v>41</v>
+      </c>
+      <c r="G7" t="n">
+        <v>266</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>5850</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6525</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5940</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O7" t="n">
+        <v>11952651545</v>
+      </c>
+      <c r="P7" t="n">
+        <v>21500</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2300</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-35000</v>
+      </c>
+      <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>318</v>
-      </c>
-      <c r="F7" t="n">
-        <v>152</v>
-      </c>
-      <c r="G7" t="n">
-        <v>378</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>23500</v>
-      </c>
-      <c r="K7" t="n">
-        <v>23200</v>
-      </c>
-      <c r="L7" t="n">
-        <v>26450</v>
-      </c>
-      <c r="M7" t="n">
-        <v>22800</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>339471343850</v>
-      </c>
-      <c r="P7" t="n">
-        <v>28750</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>8200</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-1000</v>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>CART 혈압계 뉴스 및 서울대, 아산병원 등 임상 협력 기반 급등 기대. 세계 1위, 최초 타이틀.</t>
+          <t>현대바이오 홈페이지 공지 및 세계폐암학회 관련 내용 언급, 신약 개발 가능성 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['CART', '혈압계', '임상']</t>
+          <t>['현대바이오', '폐암학회', '신약']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1742000</v>
+        <v>84300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.77%</t>
+          <t>+6.44%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>795</v>
+        <v>113</v>
       </c>
       <c r="F8" t="n">
-        <v>446</v>
+        <v>76</v>
       </c>
       <c r="G8" t="n">
-        <v>1965</v>
+        <v>373</v>
       </c>
       <c r="H8" t="n">
-        <v>50.5</v>
+        <v>23.53</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1647000</v>
+        <v>79200</v>
       </c>
       <c r="K8" t="n">
-        <v>1737000</v>
+        <v>80200</v>
       </c>
       <c r="L8" t="n">
-        <v>1751000</v>
+        <v>84700</v>
       </c>
       <c r="M8" t="n">
-        <v>1733000</v>
+        <v>79000</v>
       </c>
       <c r="N8" t="n">
-        <v>50.45</v>
+        <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>1962577041500</v>
+        <v>143610861400</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>274000</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>281000</v>
+        <v>5000</v>
       </c>
       <c r="S8" t="n">
-        <v>146000</v>
+        <v>1000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입 및 외국인, 기관 순매수 지속. 200만원 돌파 및 숏커버링 기대감.</t>
+          <t>대미 투자 1호 가스복합 발전소 수주 기반 하반기 본격 수주 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주매입', '외국인', '숏커버링']</t>
+          <t>['대미투자', '가스복합', '원전']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83100</v>
+        <v>1737000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.92%</t>
+          <t>+5.46%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>113</v>
+        <v>796</v>
       </c>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>447</v>
       </c>
       <c r="G9" t="n">
-        <v>355</v>
+        <v>2014</v>
       </c>
       <c r="H9" t="n">
-        <v>23.53</v>
+        <v>50.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>79200</v>
+        <v>1647000</v>
       </c>
       <c r="K9" t="n">
-        <v>80200</v>
+        <v>1737000</v>
       </c>
       <c r="L9" t="n">
-        <v>84400</v>
+        <v>1751000</v>
       </c>
       <c r="M9" t="n">
-        <v>79000</v>
+        <v>1733000</v>
       </c>
       <c r="N9" t="n">
-        <v>23.61</v>
+        <v>50.45</v>
       </c>
       <c r="O9" t="n">
-        <v>124297243000</v>
+        <v>2080964424500</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>274000</v>
       </c>
       <c r="R9" t="n">
-        <v>5000</v>
+        <v>281000</v>
       </c>
       <c r="S9" t="n">
-        <v>1000</v>
+        <v>146000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대미 투자 1호(가스복합) 계약 및 하반기 본격 수주 기대. 원자력주 전반적 상승세.</t>
+          <t>자사주 매입 및 외국인/기관 순매수세 유입, 200만원 돌파 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['대미투자', '가스복합', '원자력']</t>
+          <t>['자사주매입', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>265000</v>
+        <v>17640</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+3.72%</t>
+          <t>+4.69%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>795</v>
+        <v>47</v>
       </c>
       <c r="F10" t="n">
-        <v>467</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>2265</v>
+        <v>152</v>
       </c>
       <c r="H10" t="n">
-        <v>46.73</v>
+        <v>10.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>255500</v>
+        <v>16850</v>
       </c>
       <c r="K10" t="n">
-        <v>267000</v>
+        <v>16870</v>
       </c>
       <c r="L10" t="n">
-        <v>268000</v>
+        <v>17770</v>
       </c>
       <c r="M10" t="n">
-        <v>264000</v>
+        <v>16590</v>
       </c>
       <c r="N10" t="n">
-        <v>46.71</v>
+        <v>10.36</v>
       </c>
       <c r="O10" t="n">
-        <v>1304293699500</v>
+        <v>60435920295</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>69600</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>1074000</v>
+        <v>82000</v>
       </c>
       <c r="S10" t="n">
-        <v>809000</v>
+        <v>-8000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>애플 배당 및 샌디스크 폭등 뉴스 기반 반도체 섹터 상승 기대. 30만원 목표 매수세 유입.</t>
+          <t>러우 전쟁 종전 분위기 및 중동 투자 기대감 속 원전 관련주 동반 상승.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '배당', '매수세']</t>
+          <t>['원전', '러우전쟁', '중동']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13460</v>
+        <v>265500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.46%</t>
+          <t>+3.91%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>795</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>474</v>
       </c>
       <c r="G11" t="n">
-        <v>220</v>
+        <v>2103</v>
       </c>
       <c r="H11" t="n">
-        <v>1.82</v>
+        <v>46.73</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13010</v>
+        <v>255500</v>
       </c>
       <c r="K11" t="n">
-        <v>13420</v>
+        <v>267000</v>
       </c>
       <c r="L11" t="n">
-        <v>14100</v>
+        <v>268000</v>
       </c>
       <c r="M11" t="n">
-        <v>13410</v>
+        <v>264000</v>
       </c>
       <c r="N11" t="n">
-        <v>1.91</v>
+        <v>46.71</v>
       </c>
       <c r="O11" t="n">
-        <v>57156289370</v>
+        <v>1349112367000</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>1252</v>
+        <v>69600</v>
       </c>
       <c r="R11" t="n">
-        <v>204000</v>
+        <v>1074000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>809000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>회사의 가치를 긍정적으로 평가하며, 당일 광통신주 대장으로서의 역할 기대. 공매도 물량 언급과 함께 주가 변동성에 대한 언급 존재.</t>
+          <t>반도체 섹터 호재 및 외국인/기관 순매수세 유입 속 30만원 목표 매수 의견.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신주', '공매도', '주가 변동성']</t>
+          <t>['반도체', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17310</v>
+        <v>13480</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2.73%</t>
+          <t>+3.61%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>142</v>
+        <v>237</v>
       </c>
       <c r="H12" t="n">
-        <v>10.4</v>
+        <v>1.82</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16850</v>
+        <v>13010</v>
       </c>
       <c r="K12" t="n">
-        <v>16870</v>
+        <v>13420</v>
       </c>
       <c r="L12" t="n">
-        <v>17770</v>
+        <v>14100</v>
       </c>
       <c r="M12" t="n">
-        <v>16590</v>
+        <v>13410</v>
       </c>
       <c r="N12" t="n">
-        <v>10.36</v>
+        <v>1.91</v>
       </c>
       <c r="O12" t="n">
-        <v>57627212320</v>
+        <v>58784963700</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>1252</v>
       </c>
       <c r="R12" t="n">
-        <v>82000</v>
+        <v>204000</v>
       </c>
       <c r="S12" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>러우 전쟁 종전 분위기 및 중동 투자 관련 기대감. 외국인, 기관, 프매도 순매수.</t>
+          <t>광통신주 대장 언급 및 기대감 있으나, 잦은 매도 공방과 요동치는 주가 흐름.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['러우전쟁', '중동', '외국인']</t>
+          <t>['광통신', '공매도', '변동성']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22925</v>
+        <v>6825</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.89%</t>
+          <t>+1.71%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="E13" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G13" t="n">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="H13" t="n">
-        <v>5.6</v>
+        <v>16.4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22500</v>
+        <v>6710</v>
       </c>
       <c r="K13" t="n">
-        <v>23100</v>
+        <v>6680</v>
       </c>
       <c r="L13" t="n">
-        <v>24000</v>
+        <v>7040</v>
       </c>
       <c r="M13" t="n">
-        <v>21500</v>
+        <v>6600</v>
       </c>
       <c r="N13" t="n">
-        <v>4.98</v>
+        <v>15.55</v>
       </c>
       <c r="O13" t="n">
-        <v>114111433750</v>
+        <v>7901597015</v>
       </c>
       <c r="P13" t="n">
-        <v>50600</v>
+        <v>13000</v>
       </c>
       <c r="Q13" t="n">
-        <v>9070</v>
+        <v>6030</v>
       </c>
       <c r="R13" t="n">
-        <v>-51000</v>
+        <v>2000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국민성장펀드 3500억 상장사. 거래량 주목, 신사업 진출 재료 부각. 다만, 투자 주의 종목 지정 및 급등락 반복.</t>
+          <t>한화세미텍, 한화로보틱스 IPO 예정. 반도체 및 로봇 사업 관련 기대감 존재. 현재 시점에서의 매수/매도 관련 혼조세.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['국민성장펀드', '신사업', '거래량']</t>
+          <t>['IPO', '로봇', '반도체']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6830</v>
+        <v>22700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>+0.89%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="H14" t="n">
-        <v>16.4</v>
+        <v>5.6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6710</v>
+        <v>22500</v>
       </c>
       <c r="K14" t="n">
-        <v>6680</v>
+        <v>23100</v>
       </c>
       <c r="L14" t="n">
-        <v>7040</v>
+        <v>24000</v>
       </c>
       <c r="M14" t="n">
-        <v>6600</v>
+        <v>21500</v>
       </c>
       <c r="N14" t="n">
-        <v>15.55</v>
+        <v>4.98</v>
       </c>
       <c r="O14" t="n">
-        <v>7554808955</v>
+        <v>115922548050</v>
       </c>
       <c r="P14" t="n">
-        <v>13000</v>
+        <v>50600</v>
       </c>
       <c r="Q14" t="n">
-        <v>6030</v>
+        <v>9070</v>
       </c>
       <c r="R14" t="n">
-        <v>2000</v>
+        <v>-51000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>한화로보틱스, 한화세미텍 IPO 예정. 반도체 및 로봇 사업 연계 분석. 흑자 회사 및 10000원 이상 목표가 제시. 외국인 순매수 확인.</t>
+          <t>로봇주 상승세 속 신사업 진출 재료 언급되나, 투자주의 환기 종목 지정 및 하락 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['IPO', '반도체', '로봇']</t>
+          <t>['로봇주', '신사업', '투자주의']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
@@ -1763,27 +1763,27 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30250</v>
+        <v>30150</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H15" t="n">
-        <v>48.89</v>
+        <v>48.91</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>24.02</v>
       </c>
       <c r="O15" t="n">
-        <v>47387889150</v>
+        <v>50417824400</v>
       </c>
       <c r="P15" t="n">
         <v>31200</v>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -1866,13 +1866,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>26292124990</v>
+        <v>27183157400</v>
       </c>
       <c r="P16" t="n">
         <v>19380</v>
@@ -1958,13 +1958,13 @@
         <v>0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H17" t="n">
         <v>5.75</v>
@@ -1990,7 +1990,7 @@
         <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>17219936235</v>
+        <v>17472216145</v>
       </c>
       <c r="P17" t="n">
         <v>15640</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5430</v>
+        <v>5450</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.90%</t>
+          <t>-4.55%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H18" t="n">
         <v>4.81</v>
@@ -2082,7 +2082,7 @@
         <v>4.39</v>
       </c>
       <c r="O18" t="n">
-        <v>12018243530</v>
+        <v>12200277065</v>
       </c>
       <c r="P18" t="n">
         <v>10480</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5250</v>
+        <v>5270</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-8.54%</t>
+          <t>-8.19%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2400412680</v>
+        <v>2495393030</v>
       </c>
       <c r="P19" t="n">
         <v>9680</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>반기 보고서 제출 지연 악재 및 조선비즈 기사로 인한 하한가 가능성 언급. 구미현 관련 논란 및 탈출 의견 다수.</t>
+          <t>반기보고서 제출 지연 및 구주 매각 관련 악재 발생. 조선비즈 기사 언급 및 투심 훼손 우려. 일부 투자자들은 이미 탈출.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반기 보고서', '악재', '구미현']</t>
+          <t>['반기보고서', '악재', '투심 훼손']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51900</v>
+        <v>50900</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+18.36%</t>
+          <t>+16.08%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G2" t="n">
-        <v>471</v>
+        <v>499</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>106285735675</v>
+        <v>111097326825</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>공매도 감소 및 전고점 돌파 기대감. 6~7만원 구간 매물벽 약세 전망. 긍정적 우상향 추세.</t>
+          <t>수소 관련 성장 기대감 및 공매도 감소 추세. 전고점 돌파 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공매도', '전고점', '우상향']</t>
+          <t>['수소', '공매도', '전고점']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3675</v>
+        <v>3640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+12.56%</t>
+          <t>+11.49%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>149696187048</v>
+        <v>151890669427</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>월가 소식 및 특정 종목과의 동반 상승 기대감 있으나, 뚜렷한 근거는 부족.</t>
+          <t>뚜렷한 근거 없는 단기 급등 기대감. 거래량 대비 상승폭 제한.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['월가', '기대감']</t>
+          <t>['단기 급등', '거래량', '바이오']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>218000</v>
+        <v>26000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+8.19%</t>
+          <t>+10.64%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>302</v>
+        <v>371</v>
       </c>
       <c r="F4" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G4" t="n">
-        <v>863</v>
+        <v>514</v>
       </c>
       <c r="H4" t="n">
-        <v>29.46</v>
+        <v>0.16</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>201500</v>
+        <v>23500</v>
       </c>
       <c r="K4" t="n">
-        <v>212500</v>
+        <v>23200</v>
       </c>
       <c r="L4" t="n">
-        <v>225500</v>
+        <v>26700</v>
       </c>
       <c r="M4" t="n">
-        <v>212500</v>
+        <v>22800</v>
       </c>
       <c r="N4" t="n">
-        <v>29.51</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>246430637500</v>
+        <v>410518505575</v>
       </c>
       <c r="P4" t="n">
-        <v>438000</v>
+        <v>28750</v>
       </c>
       <c r="Q4" t="n">
-        <v>74700</v>
+        <v>8200</v>
       </c>
       <c r="R4" t="n">
-        <v>317000</v>
+        <v>-2000</v>
       </c>
       <c r="S4" t="n">
-        <v>102000</v>
+        <v>-1000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 사업 진출 및 기술력 부각. CES 2024 관련 긍정적 뉴스 및 프로그램 매수세 유입. 23만 탈환 및 100조 시총 저평가 전망.</t>
+          <t>CART 혈압계 뉴스 및 기술력 부각. 세계 1위/최초 타이틀 강조. 3만원 돌파 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', 'CES 2024', '프로그램 매수']</t>
+          <t>['CART 혈압계', '세계 1위', '최초']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8600</v>
+        <v>6380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+8.18%</t>
+          <t>+9.06%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>92</v>
+        <v>278</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6</v>
+        <v>1.61</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7950</v>
+        <v>5850</v>
       </c>
       <c r="K5" t="n">
-        <v>8200</v>
+        <v>6000</v>
       </c>
       <c r="L5" t="n">
-        <v>9210</v>
+        <v>6525</v>
       </c>
       <c r="M5" t="n">
-        <v>7980</v>
+        <v>5940</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>2.31</v>
       </c>
       <c r="O5" t="n">
-        <v>81295869340</v>
+        <v>12078412335</v>
       </c>
       <c r="P5" t="n">
-        <v>15960</v>
+        <v>21500</v>
       </c>
       <c r="Q5" t="n">
-        <v>3500</v>
+        <v>2300</v>
       </c>
       <c r="R5" t="n">
-        <v>208000</v>
+        <v>-35000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미프진 관련 소식과 함께 주가 상승 기대감이 있으나, 윗꼬리 달며 변동성이 큰 모습.</t>
+          <t>현대바이오 홈페이지 공지 및 폐암 관련 재료 언급. 19년 만에 서울 찾은 세계폐암학회 소식과 신약 개발 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['미프진', '변동성']</t>
+          <t>['폐암', '신약 개발', '홈페이지 공지']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25350</v>
+        <v>218500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+7.87%</t>
+          <t>+8.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="F6" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="G6" t="n">
-        <v>461</v>
+        <v>898</v>
       </c>
       <c r="H6" t="n">
-        <v>0.16</v>
+        <v>29.46</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>23500</v>
+        <v>201500</v>
       </c>
       <c r="K6" t="n">
-        <v>23200</v>
+        <v>212500</v>
       </c>
       <c r="L6" t="n">
-        <v>26450</v>
+        <v>225500</v>
       </c>
       <c r="M6" t="n">
-        <v>22800</v>
+        <v>212500</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>29.51</v>
       </c>
       <c r="O6" t="n">
-        <v>359190114375</v>
+        <v>253789224000</v>
       </c>
       <c r="P6" t="n">
-        <v>28750</v>
+        <v>438000</v>
       </c>
       <c r="Q6" t="n">
-        <v>8200</v>
+        <v>74700</v>
       </c>
       <c r="R6" t="n">
-        <v>-2000</v>
+        <v>317000</v>
       </c>
       <c r="S6" t="n">
-        <v>-1000</v>
+        <v>102000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>CART 혈압계 관련 뉴스 및 서울대/아산병원 등 주요 기관 임상 진입 사실.</t>
+          <t>로봇 사업 진출 및 기술력 부각. CES 2024 관련 긍정적 뉴스 및 프로그램 매수세 유입. 23만 탈환 및 100조 시총 저평가 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['CART', '임상', '뉴스']</t>
+          <t>['로봇', 'CES 2024', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6310</v>
+        <v>8520</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+7.86%</t>
+          <t>+7.17%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.7</v>
+        <v>-0.72</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>266</v>
+        <v>96</v>
       </c>
       <c r="H7" t="n">
-        <v>1.61</v>
+        <v>0.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5850</v>
+        <v>7950</v>
       </c>
       <c r="K7" t="n">
-        <v>6000</v>
+        <v>8200</v>
       </c>
       <c r="L7" t="n">
-        <v>6525</v>
+        <v>9210</v>
       </c>
       <c r="M7" t="n">
-        <v>5940</v>
+        <v>7980</v>
       </c>
       <c r="N7" t="n">
-        <v>2.31</v>
+        <v>1.32</v>
       </c>
       <c r="O7" t="n">
-        <v>11952651545</v>
+        <v>82497687765</v>
       </c>
       <c r="P7" t="n">
-        <v>21500</v>
+        <v>15960</v>
       </c>
       <c r="Q7" t="n">
-        <v>2300</v>
+        <v>3500</v>
       </c>
       <c r="R7" t="n">
-        <v>-35000</v>
+        <v>208000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>현대바이오 홈페이지 공지 및 세계폐암학회 관련 내용 언급, 신약 개발 가능성 기대.</t>
+          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['현대바이오', '폐암학회', '신약']</t>
+          <t>['미프진', '거래량', '수급']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84300</v>
+        <v>83750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+6.44%</t>
+          <t>+5.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F8" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G8" t="n">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="H8" t="n">
         <v>23.53</v>
@@ -1162,7 +1162,7 @@
         <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>143610861400</v>
+        <v>147923841300</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1737000</v>
+        <v>1737500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.46%</t>
+          <t>+5.49%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F9" t="n">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="G9" t="n">
-        <v>2014</v>
+        <v>1890</v>
       </c>
       <c r="H9" t="n">
         <v>50.5</v>
@@ -1254,7 +1254,7 @@
         <v>50.45</v>
       </c>
       <c r="O9" t="n">
-        <v>2080964424500</v>
+        <v>2169070398500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>자사주 매입 및 외국인/기관 순매수세 유입, 200만원 돌파 기대감.</t>
+          <t>자사주 매입 기대감 및 외국인/기관 순매수세 유입. 200만원 터치 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['자사주매입', '외국인', '기관']</t>
+          <t>['자사주 매입', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17640</v>
+        <v>17530</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.69%</t>
+          <t>+4.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="H10" t="n">
         <v>10.4</v>
@@ -1346,7 +1346,7 @@
         <v>10.36</v>
       </c>
       <c r="O10" t="n">
-        <v>60435920295</v>
+        <v>62227920420</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>러우 전쟁 종전 분위기 및 중동 투자 기대감 속 원전 관련주 동반 상승.</t>
+          <t>러우전쟁 종전 기대감 속 건설주 동반 상승. 5% 수익 실현.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '러우전쟁', '중동']</t>
+          <t>['러우전쟁', '건설주', '종전']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>265500</v>
+        <v>13530</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.91%</t>
+          <t>+4.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>795</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>474</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>2103</v>
+        <v>231</v>
       </c>
       <c r="H11" t="n">
-        <v>46.73</v>
+        <v>1.82</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>255500</v>
+        <v>13010</v>
       </c>
       <c r="K11" t="n">
-        <v>267000</v>
+        <v>13420</v>
       </c>
       <c r="L11" t="n">
-        <v>268000</v>
+        <v>14100</v>
       </c>
       <c r="M11" t="n">
-        <v>264000</v>
+        <v>13410</v>
       </c>
       <c r="N11" t="n">
-        <v>46.71</v>
+        <v>1.91</v>
       </c>
       <c r="O11" t="n">
-        <v>1349112367000</v>
+        <v>59512415170</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>69600</v>
+        <v>1252</v>
       </c>
       <c r="R11" t="n">
-        <v>1074000</v>
+        <v>204000</v>
       </c>
       <c r="S11" t="n">
-        <v>809000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 섹터 호재 및 외국인/기관 순매수세 유입 속 30만원 목표 매수 의견.</t>
+          <t>광통신 섹터 강세 및 공매도 물량 소화 기대. 14000원 물린 개미.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '외국인', '기관']</t>
+          <t>['광통신', '공매도', '섹터']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13480</v>
+        <v>265500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.61%</t>
+          <t>+3.91%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>795</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>475</v>
       </c>
       <c r="G12" t="n">
-        <v>237</v>
+        <v>2019</v>
       </c>
       <c r="H12" t="n">
-        <v>1.82</v>
+        <v>46.73</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13010</v>
+        <v>255500</v>
       </c>
       <c r="K12" t="n">
-        <v>13420</v>
+        <v>267000</v>
       </c>
       <c r="L12" t="n">
-        <v>14100</v>
+        <v>268000</v>
       </c>
       <c r="M12" t="n">
-        <v>13410</v>
+        <v>264000</v>
       </c>
       <c r="N12" t="n">
-        <v>1.91</v>
+        <v>46.71</v>
       </c>
       <c r="O12" t="n">
-        <v>58784963700</v>
+        <v>1377602355500</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>1252</v>
+        <v>69600</v>
       </c>
       <c r="R12" t="n">
-        <v>204000</v>
+        <v>1074000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>809000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>광통신주 대장 언급 및 기대감 있으나, 잦은 매도 공방과 요동치는 주가 흐름.</t>
+          <t>반도체 업황 개선 기대감 및 외국인/기관 순매수세 유입. 3만원 복귀 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '공매도', '변동성']</t>
+          <t>['반도체', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6825</v>
+        <v>6890</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.71%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.85</v>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H13" t="n">
         <v>16.4</v>
@@ -1622,7 +1622,7 @@
         <v>15.55</v>
       </c>
       <c r="O13" t="n">
-        <v>7901597015</v>
+        <v>8198118050</v>
       </c>
       <c r="P13" t="n">
         <v>13000</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>한화세미텍, 한화로보틱스 IPO 예정. 반도체 및 로봇 사업 관련 기대감 존재. 현재 시점에서의 매수/매도 관련 혼조세.</t>
+          <t>한화 세미텍, 한화 로보틱스 IPO 언급 및 반도체, 로봇 사업 관련 기대감. 하지만 일부 매도 움직임 관찰.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['IPO', '로봇', '반도체']</t>
+          <t>['IPO', '반도체', '로봇']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22700</v>
+        <v>22900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>+1.78%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H14" t="n">
         <v>5.6</v>
@@ -1714,7 +1714,7 @@
         <v>4.98</v>
       </c>
       <c r="O14" t="n">
-        <v>115922548050</v>
+        <v>116834542225</v>
       </c>
       <c r="P14" t="n">
         <v>50600</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>로봇주 상승세 속 신사업 진출 재료 언급되나, 투자주의 환기 종목 지정 및 하락 우려.</t>
+          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '투자주의']</t>
+          <t>['로봇주', '신사업', '2연상']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30150</v>
+        <v>16050</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>327</v>
       </c>
       <c r="H15" t="n">
-        <v>48.91</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>30200</v>
+        <v>16090</v>
       </c>
       <c r="K15" t="n">
-        <v>30350</v>
+        <v>16150</v>
       </c>
       <c r="L15" t="n">
-        <v>30900</v>
+        <v>16480</v>
       </c>
       <c r="M15" t="n">
-        <v>29900</v>
+        <v>15830</v>
       </c>
       <c r="N15" t="n">
-        <v>24.02</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>50417824400</v>
+        <v>27834129940</v>
       </c>
       <c r="P15" t="n">
-        <v>31200</v>
+        <v>19380</v>
       </c>
       <c r="Q15" t="n">
-        <v>21000</v>
+        <v>3200</v>
       </c>
       <c r="R15" t="n">
-        <v>139000</v>
+        <v>-3000</v>
       </c>
       <c r="S15" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
+          <t>메가특구법 발의 및 반도체 산단 조성 기대감. 15만원 목표.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['환율', '반도체', '공매도']</t>
+          <t>['메가특구법', '반도체', '산단']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15990</v>
+        <v>30100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E16" t="n">
+        <v>36</v>
+      </c>
+      <c r="F16" t="n">
+        <v>23</v>
+      </c>
+      <c r="G16" t="n">
         <v>66</v>
       </c>
-      <c r="F16" t="n">
-        <v>45</v>
-      </c>
-      <c r="G16" t="n">
-        <v>303</v>
-      </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>48.92</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,60 +1883,60 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>16090</v>
+        <v>30200</v>
       </c>
       <c r="K16" t="n">
-        <v>16150</v>
+        <v>30350</v>
       </c>
       <c r="L16" t="n">
-        <v>16480</v>
+        <v>30900</v>
       </c>
       <c r="M16" t="n">
-        <v>15830</v>
+        <v>29900</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>24.02</v>
       </c>
       <c r="O16" t="n">
-        <v>27183157400</v>
+        <v>52251958925</v>
       </c>
       <c r="P16" t="n">
-        <v>19380</v>
+        <v>31200</v>
       </c>
       <c r="Q16" t="n">
-        <v>3200</v>
+        <v>21000</v>
       </c>
       <c r="R16" t="n">
-        <v>-3000</v>
+        <v>139000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>9월 메가특구법 발의 및 호남 반도체 산단 관련 기대감. '개잡주' 언급.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['메가특구법', '반도체', '호남']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10260</v>
+        <v>10160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-2.21%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H17" t="n">
         <v>5.75</v>
@@ -1990,7 +1990,7 @@
         <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>17472216145</v>
+        <v>17666234955</v>
       </c>
       <c r="P17" t="n">
         <v>15640</v>
@@ -2050,7 +2050,7 @@
         <v>0.42</v>
       </c>
       <c r="E18" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" t="n">
         <v>40</v>
@@ -2082,7 +2082,7 @@
         <v>4.39</v>
       </c>
       <c r="O18" t="n">
-        <v>12200277065</v>
+        <v>12271334140</v>
       </c>
       <c r="P18" t="n">
         <v>10480</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5270</v>
+        <v>5300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-8.19%</t>
+          <t>-7.67%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2495393030</v>
+        <v>2584933620</v>
       </c>
       <c r="P19" t="n">
         <v>9680</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 구주 매각 관련 악재 발생. 조선비즈 기사 언급 및 투심 훼손 우려. 일부 투자자들은 이미 탈출.</t>
+          <t>반기보고서 제출 지연 및 악재 뉴스로 인한 투심 훼손 우려. 구주 매각 불확실성과 기사 출현으로 인한 하한가 가능성 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '투심 훼손']</t>
+          <t>['반기보고서', '악재 뉴스', '투심 훼손']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50900</v>
+        <v>51800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+16.08%</t>
+          <t>+18.13%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F2" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G2" t="n">
-        <v>499</v>
+        <v>568</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>111097326825</v>
+        <v>129586984575</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -619,23 +619,23 @@
         <v>18230</v>
       </c>
       <c r="R2" t="n">
-        <v>160000</v>
+        <v>176000</v>
       </c>
       <c r="S2" t="n">
-        <v>31000</v>
+        <v>44000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>수소 관련 성장 기대감 및 공매도 감소 추세. 전고점 돌파 전망.</t>
+          <t>공매도 세력에 대한 기대감 및 6~7만원 구간 매물벽 약세 전망. 단기 급등 후 소강 상태 진입 및 4만원 재진입 가능성 언급. 공급 계약 발표 후 급등 사례 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['수소', '공매도', '전고점']</t>
+          <t>['공매도', '매물벽', '공급계약']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3640</v>
+        <v>27600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+11.49%</t>
+          <t>+17.45%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>649</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>271</v>
       </c>
       <c r="G3" t="n">
-        <v>130</v>
+        <v>951</v>
       </c>
       <c r="H3" t="n">
-        <v>1.25</v>
+        <v>0.16</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3265</v>
+        <v>23500</v>
       </c>
       <c r="K3" t="n">
-        <v>3200</v>
+        <v>23200</v>
       </c>
       <c r="L3" t="n">
-        <v>3900</v>
+        <v>29600</v>
       </c>
       <c r="M3" t="n">
-        <v>3185</v>
+        <v>22800</v>
       </c>
       <c r="N3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>151890669427</v>
+        <v>665867321400</v>
       </c>
       <c r="P3" t="n">
-        <v>3900</v>
+        <v>29600</v>
       </c>
       <c r="Q3" t="n">
-        <v>1246</v>
+        <v>8200</v>
       </c>
       <c r="R3" t="n">
-        <v>179000</v>
+        <v>-9000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>뚜렷한 근거 없는 단기 급등 기대감. 거래량 대비 상승폭 제한.</t>
+          <t>CART 혈압계 관련 뉴스 확인 및 거래량 증가에 따른 상승 기대감. 주포의 움직임 및 종가 상한가 가능성 언급. '세계 1위, 최초' 등의 수식어 활용.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['단기 급등', '거래량', '바이오']</t>
+          <t>['CART 혈압계', '거래량', '주포']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26000</v>
+        <v>6430</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.64%</t>
+          <t>+9.91%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="E4" t="n">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="F4" t="n">
-        <v>169</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>514</v>
+        <v>380</v>
       </c>
       <c r="H4" t="n">
-        <v>0.16</v>
+        <v>1.61</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>23500</v>
+        <v>5850</v>
       </c>
       <c r="K4" t="n">
-        <v>23200</v>
+        <v>6000</v>
       </c>
       <c r="L4" t="n">
-        <v>26700</v>
+        <v>6525</v>
       </c>
       <c r="M4" t="n">
-        <v>22800</v>
+        <v>5940</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O4" t="n">
-        <v>410518505575</v>
+        <v>13532531285</v>
       </c>
       <c r="P4" t="n">
-        <v>28750</v>
+        <v>21500</v>
       </c>
       <c r="Q4" t="n">
-        <v>8200</v>
+        <v>2300</v>
       </c>
       <c r="R4" t="n">
-        <v>-2000</v>
+        <v>-14000</v>
       </c>
       <c r="S4" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>CART 혈압계 뉴스 및 기술력 부각. 세계 1위/최초 타이틀 강조. 3만원 돌파 기대.</t>
+          <t>임상 2a의 의미 및 신약 개발 가능성 언급. 현대바이오와의 연관성 및 유증 자금 활용 가능성. '게임 체인저' 가능성 제시 및 저가 매수 권유.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['CART 혈압계', '세계 1위', '최초']</t>
+          <t>['임상 2a', '신약 개발', '게임 체인저']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6380</v>
+        <v>3575</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+9.06%</t>
+          <t>+9.49%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.7</v>
+        <v>-0.52</v>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>278</v>
+        <v>206</v>
       </c>
       <c r="H5" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5850</v>
+        <v>3265</v>
       </c>
       <c r="K5" t="n">
-        <v>6000</v>
+        <v>3200</v>
       </c>
       <c r="L5" t="n">
-        <v>6525</v>
+        <v>3900</v>
       </c>
       <c r="M5" t="n">
-        <v>5940</v>
+        <v>3185</v>
       </c>
       <c r="N5" t="n">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="O5" t="n">
-        <v>12078412335</v>
+        <v>166454174974</v>
       </c>
       <c r="P5" t="n">
-        <v>21500</v>
+        <v>3900</v>
       </c>
       <c r="Q5" t="n">
-        <v>2300</v>
+        <v>1246</v>
       </c>
       <c r="R5" t="n">
-        <v>-35000</v>
+        <v>-25000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>현대바이오 홈페이지 공지 및 폐암 관련 재료 언급. 19년 만에 서울 찾은 세계폐암학회 소식과 신약 개발 기대감.</t>
+          <t>단기적인 상승 및 하락 반복, 투자 주의 필요성 언급. 탈모 관련 사업 우려 및 회사의 재무 상태에 대한 부정적 시각. 프로그램 매매 활용 후 이탈 가능성 시사.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['폐암', '신약 개발', '홈페이지 공지']</t>
+          <t>['투자주의', '탈모', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>218500</v>
+        <v>215500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+8.44%</t>
+          <t>+6.95%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>315</v>
+        <v>404</v>
       </c>
       <c r="F6" t="n">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="G6" t="n">
-        <v>898</v>
+        <v>1127</v>
       </c>
       <c r="H6" t="n">
         <v>29.46</v>
@@ -978,7 +978,7 @@
         <v>29.51</v>
       </c>
       <c r="O6" t="n">
-        <v>253789224000</v>
+        <v>284539442750</v>
       </c>
       <c r="P6" t="n">
         <v>438000</v>
@@ -987,23 +987,23 @@
         <v>74700</v>
       </c>
       <c r="R6" t="n">
-        <v>317000</v>
+        <v>353000</v>
       </c>
       <c r="S6" t="n">
-        <v>102000</v>
+        <v>124000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>로봇 사업 진출 및 기술력 부각. CES 2024 관련 긍정적 뉴스 및 프로그램 매수세 유입. 23만 탈환 및 100조 시총 저평가 전망.</t>
+          <t>로봇 사업 관련 기술력 부각 및 60년 기술 노하우 강조. 외인·기관 매수세 유입에 따른 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['로봇', 'CES 2024', '프로그램 매수']</t>
+          <t>['로봇', '기술력', '액츄에이터']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8520</v>
+        <v>1747000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+7.17%</t>
+          <t>+6.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.72</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>794</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>419</v>
       </c>
       <c r="G7" t="n">
-        <v>96</v>
+        <v>2127</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>50.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7950</v>
+        <v>1647000</v>
       </c>
       <c r="K7" t="n">
-        <v>8200</v>
+        <v>1737000</v>
       </c>
       <c r="L7" t="n">
-        <v>9210</v>
+        <v>1751000</v>
       </c>
       <c r="M7" t="n">
-        <v>7980</v>
+        <v>1733000</v>
       </c>
       <c r="N7" t="n">
-        <v>1.32</v>
+        <v>50.45</v>
       </c>
       <c r="O7" t="n">
-        <v>82497687765</v>
+        <v>2682641606500</v>
       </c>
       <c r="P7" t="n">
-        <v>15960</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>3500</v>
+        <v>274000</v>
       </c>
       <c r="R7" t="n">
-        <v>208000</v>
+        <v>330000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>138000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
+          <t>외국인 및 기관 쌍끌이 매수세 유입에 따른 상승 추세 가속화 전망. 자사주 매입 기대감 및 메모리 재고 부족 뉴스 언급. 200만원 터치 및 급등 가능성 제시.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['미프진', '거래량', '수급']</t>
+          <t>['자사주매입', '메모리 재고', '쌍끌이 매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83750</v>
+        <v>83650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.74%</t>
+          <t>+5.62%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="F8" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="G8" t="n">
-        <v>393</v>
+        <v>508</v>
       </c>
       <c r="H8" t="n">
         <v>23.53</v>
@@ -1162,7 +1162,7 @@
         <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>147923841300</v>
+        <v>170941399250</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1171,23 +1171,23 @@
         <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>5000</v>
+        <v>146000</v>
       </c>
       <c r="S8" t="n">
-        <v>1000</v>
+        <v>38000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대미 투자 1호 가스복합 발전소 수주 기반 하반기 본격 수주 전망.</t>
+          <t>대규모 가스복합화력발전 투자 확정 및 하반기 본격 수주 기대감. 기술력 입증 및 10만원 돌파 전망. 원전주 전반적인 상승세 속에서 상대적 우위 확인.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['대미투자', '가스복합', '원전']</t>
+          <t>['대미투자', '가스터빈', '본격수주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1737500</v>
+        <v>8350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.49%</t>
+          <t>+5.03%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>-0.72</v>
       </c>
       <c r="E9" t="n">
-        <v>795</v>
+        <v>68</v>
       </c>
       <c r="F9" t="n">
-        <v>437</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>1890</v>
+        <v>142</v>
       </c>
       <c r="H9" t="n">
-        <v>50.5</v>
+        <v>0.6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,60 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1647000</v>
+        <v>7950</v>
       </c>
       <c r="K9" t="n">
-        <v>1737000</v>
+        <v>8200</v>
       </c>
       <c r="L9" t="n">
-        <v>1751000</v>
+        <v>9210</v>
       </c>
       <c r="M9" t="n">
-        <v>1733000</v>
+        <v>7980</v>
       </c>
       <c r="N9" t="n">
-        <v>50.45</v>
+        <v>1.32</v>
       </c>
       <c r="O9" t="n">
-        <v>2169070398500</v>
+        <v>88855097300</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>15960</v>
       </c>
       <c r="Q9" t="n">
-        <v>274000</v>
+        <v>3500</v>
       </c>
       <c r="R9" t="n">
-        <v>281000</v>
+        <v>149000</v>
       </c>
       <c r="S9" t="n">
-        <v>146000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>자사주 매입 기대감 및 외국인/기관 순매수세 유입. 200만원 터치 전망.</t>
+          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['자사주 매입', '외국인', '기관']</t>
+          <t>['미프진', '거래량', '수급']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17530</v>
+        <v>17640</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.04%</t>
+          <t>+4.69%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="H10" t="n">
         <v>10.4</v>
@@ -1337,7 +1337,7 @@
         <v>16870</v>
       </c>
       <c r="L10" t="n">
-        <v>17770</v>
+        <v>17800</v>
       </c>
       <c r="M10" t="n">
         <v>16590</v>
@@ -1346,7 +1346,7 @@
         <v>10.36</v>
       </c>
       <c r="O10" t="n">
-        <v>62227920420</v>
+        <v>77896447200</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1355,10 +1355,10 @@
         <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>82000</v>
+        <v>266000</v>
       </c>
       <c r="S10" t="n">
-        <v>-8000</v>
+        <v>58000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13530</v>
+        <v>265750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.00%</t>
+          <t>+4.01%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
+        <v>793</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>449</v>
       </c>
       <c r="G11" t="n">
-        <v>231</v>
+        <v>1870</v>
       </c>
       <c r="H11" t="n">
-        <v>1.82</v>
+        <v>46.73</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13010</v>
+        <v>255500</v>
       </c>
       <c r="K11" t="n">
-        <v>13420</v>
+        <v>267000</v>
       </c>
       <c r="L11" t="n">
-        <v>14100</v>
+        <v>268000</v>
       </c>
       <c r="M11" t="n">
-        <v>13410</v>
+        <v>264000</v>
       </c>
       <c r="N11" t="n">
-        <v>1.91</v>
+        <v>46.71</v>
       </c>
       <c r="O11" t="n">
-        <v>59512415170</v>
+        <v>1845746056250</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>1252</v>
+        <v>69600</v>
       </c>
       <c r="R11" t="n">
-        <v>204000</v>
+        <v>1189000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>911000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>광통신 섹터 강세 및 공매도 물량 소화 기대. 14000원 물린 개미.</t>
+          <t>외국인 및 기관 매수세 유입에도 불구하고, 정치적 이슈 및 보수적인 시장 전망. 반도체 관련 긍정적 뉴스에도 불구하고 개인 물량 털어내기 및 음전 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '공매도', '섹터']</t>
+          <t>['반도체', '외국인 매수', '기관 매수']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,99 +1476,99 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>265500</v>
+        <v>13460</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.91%</t>
+          <t>+3.46%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>795</v>
+        <v>65</v>
       </c>
       <c r="F12" t="n">
-        <v>475</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>2019</v>
+        <v>285</v>
       </c>
       <c r="H12" t="n">
-        <v>46.73</v>
+        <v>1.82</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>255500</v>
+        <v>13010</v>
       </c>
       <c r="K12" t="n">
-        <v>267000</v>
+        <v>13420</v>
       </c>
       <c r="L12" t="n">
-        <v>268000</v>
+        <v>14100</v>
       </c>
       <c r="M12" t="n">
-        <v>264000</v>
+        <v>13410</v>
       </c>
       <c r="N12" t="n">
-        <v>46.71</v>
+        <v>1.91</v>
       </c>
       <c r="O12" t="n">
-        <v>1377602355500</v>
+        <v>63876292275</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>69600</v>
+        <v>1252</v>
       </c>
       <c r="R12" t="n">
-        <v>1074000</v>
+        <v>317000</v>
       </c>
       <c r="S12" t="n">
-        <v>809000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>반도체 업황 개선 기대감 및 외국인/기관 순매수세 유입. 3만원 복귀 전망.</t>
+          <t>광통신 섹터 강세 및 공매도 물량 소화 기대. 14000원 물린 개미.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', '외국인', '기관']</t>
+          <t>['광통신', '공매도', '섹터']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6890</v>
+        <v>6880</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+2.53%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.85</v>
       </c>
       <c r="E13" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H13" t="n">
         <v>16.4</v>
@@ -1622,7 +1622,7 @@
         <v>15.55</v>
       </c>
       <c r="O13" t="n">
-        <v>8198118050</v>
+        <v>9747060585</v>
       </c>
       <c r="P13" t="n">
         <v>13000</v>
@@ -1631,7 +1631,7 @@
         <v>6030</v>
       </c>
       <c r="R13" t="n">
-        <v>2000</v>
+        <v>33000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22900</v>
+        <v>22600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+1.78%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F14" t="n">
         <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="H14" t="n">
         <v>5.6</v>
@@ -1714,7 +1714,7 @@
         <v>4.98</v>
       </c>
       <c r="O14" t="n">
-        <v>116834542225</v>
+        <v>121946555900</v>
       </c>
       <c r="P14" t="n">
         <v>50600</v>
@@ -1723,10 +1723,10 @@
         <v>9070</v>
       </c>
       <c r="R14" t="n">
-        <v>-51000</v>
+        <v>28000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16050</v>
+        <v>30200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G15" t="n">
-        <v>327</v>
+        <v>76</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>48.96</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>16090</v>
+        <v>30200</v>
       </c>
       <c r="K15" t="n">
-        <v>16150</v>
+        <v>30350</v>
       </c>
       <c r="L15" t="n">
-        <v>16480</v>
+        <v>30900</v>
       </c>
       <c r="M15" t="n">
-        <v>15830</v>
+        <v>29900</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>24.02</v>
       </c>
       <c r="O15" t="n">
-        <v>27834129940</v>
+        <v>61997678325</v>
       </c>
       <c r="P15" t="n">
-        <v>19380</v>
+        <v>31200</v>
       </c>
       <c r="Q15" t="n">
-        <v>3200</v>
+        <v>21000</v>
       </c>
       <c r="R15" t="n">
-        <v>-3000</v>
+        <v>222000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>메가특구법 발의 및 반도체 산단 조성 기대감. 15만원 목표.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['메가특구법', '반도체', '산단']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30100</v>
+        <v>15970</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-0.75%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="F16" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="G16" t="n">
-        <v>66</v>
+        <v>392</v>
       </c>
       <c r="H16" t="n">
-        <v>48.92</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,60 +1883,60 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>30200</v>
+        <v>16090</v>
       </c>
       <c r="K16" t="n">
-        <v>30350</v>
+        <v>16150</v>
       </c>
       <c r="L16" t="n">
-        <v>30900</v>
+        <v>16480</v>
       </c>
       <c r="M16" t="n">
-        <v>29900</v>
+        <v>15830</v>
       </c>
       <c r="N16" t="n">
-        <v>24.02</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>52251958925</v>
+        <v>33394293660</v>
       </c>
       <c r="P16" t="n">
-        <v>31200</v>
+        <v>19380</v>
       </c>
       <c r="Q16" t="n">
-        <v>21000</v>
+        <v>3200</v>
       </c>
       <c r="R16" t="n">
-        <v>139000</v>
+        <v>-21000</v>
       </c>
       <c r="S16" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
+          <t>17000선 지지 여부 불확실성 및 개인 간의 치열한 눈치 싸움. 반도체 관련 긍정적 뉴스에도 불구하고 '개잡주' 언급 및 실적 분석 필요성 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['환율', '반도체', '공매도']</t>
+          <t>['반도체', '주포', '2분기보고서']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10160</v>
+        <v>10140</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F17" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G17" t="n">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="H17" t="n">
         <v>5.75</v>
@@ -1990,7 +1990,7 @@
         <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>17666234955</v>
+        <v>18367413380</v>
       </c>
       <c r="P17" t="n">
         <v>15640</v>
@@ -1999,7 +1999,7 @@
         <v>5470</v>
       </c>
       <c r="R17" t="n">
-        <v>-84000</v>
+        <v>-85000</v>
       </c>
       <c r="S17" t="n">
         <v>-2000</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>아난티</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5450</v>
+        <v>5500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>-4.18%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F18" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G18" t="n">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="H18" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>5710</v>
+        <v>5740</v>
       </c>
       <c r="K18" t="n">
-        <v>5640</v>
+        <v>5250</v>
       </c>
       <c r="L18" t="n">
-        <v>5650</v>
+        <v>5530</v>
       </c>
       <c r="M18" t="n">
-        <v>5270</v>
+        <v>5000</v>
       </c>
       <c r="N18" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>12271334140</v>
+        <v>3099343510</v>
       </c>
       <c r="P18" t="n">
-        <v>10480</v>
+        <v>9680</v>
       </c>
       <c r="Q18" t="n">
-        <v>3150</v>
+        <v>371</v>
       </c>
       <c r="R18" t="n">
-        <v>-307000</v>
+        <v>-9000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>시진핑 방미 관련 뉴스 부재 및 하락 시작 우려. 대북주 변동성 및 주가 조작 의혹 제기. 외국인, 연기금 매수세 일부 확인.</t>
+          <t>반기보고서 제출 지연 및 악재 뉴스 발생으로 인한 하한가 우려. 투심 훼손 및 구주 매각 관련 불확실성. 'ㅈ되었다', '탈출' 등 부정적 심리 표현.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['시진핑', '대북주', '주가 조작']</t>
+          <t>['반기보고서', '악재 뉴스', '투심 훼손']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>025980</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>아난티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5300</v>
+        <v>5470</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-7.67%</t>
+          <t>-4.20%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="E19" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,60 +2159,60 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>5740</v>
+        <v>5710</v>
       </c>
       <c r="K19" t="n">
-        <v>5250</v>
+        <v>5640</v>
       </c>
       <c r="L19" t="n">
-        <v>5420</v>
+        <v>5650</v>
       </c>
       <c r="M19" t="n">
-        <v>5000</v>
+        <v>5270</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="O19" t="n">
-        <v>2584933620</v>
+        <v>15592118200</v>
       </c>
       <c r="P19" t="n">
-        <v>9680</v>
+        <v>10480</v>
       </c>
       <c r="Q19" t="n">
-        <v>371</v>
+        <v>3150</v>
       </c>
       <c r="R19" t="n">
-        <v>-10000</v>
+        <v>-336000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 악재 뉴스로 인한 투심 훼손 우려. 구주 매각 불확실성과 기사 출현으로 인한 하한가 가능성 제기.</t>
+          <t>시진핑 방미 관련 뉴스 부재 및 하락 시작 우려. 대북주 변동성 및 주가 조작 의혹 제기. 외국인, 연기금 매수세 일부 확인.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재 뉴스', '투심 훼손']</t>
+          <t>['시진핑', '대북주', '주가 조작']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>025980</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,70 +563,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51800</v>
+        <v>30550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+18.13%</t>
+          <t>+30.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>160</v>
+        <v>798</v>
       </c>
       <c r="F2" t="n">
-        <v>106</v>
+        <v>313</v>
       </c>
       <c r="G2" t="n">
-        <v>568</v>
+        <v>1160</v>
       </c>
       <c r="H2" t="n">
-        <v>14.18</v>
+        <v>0.16</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>43850</v>
+        <v>23500</v>
       </c>
       <c r="K2" t="n">
-        <v>45650</v>
+        <v>23200</v>
       </c>
       <c r="L2" t="n">
-        <v>55000</v>
+        <v>30550</v>
       </c>
       <c r="M2" t="n">
-        <v>45650</v>
+        <v>22800</v>
       </c>
       <c r="N2" t="n">
-        <v>13.71</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>129586984575</v>
+        <v>775414311525</v>
       </c>
       <c r="P2" t="n">
-        <v>108900</v>
+        <v>30550</v>
       </c>
       <c r="Q2" t="n">
-        <v>18230</v>
+        <v>8200</v>
       </c>
       <c r="R2" t="n">
-        <v>176000</v>
+        <v>-9000</v>
       </c>
       <c r="S2" t="n">
-        <v>44000</v>
+        <v>-1000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 기대감 및 6~7만원 구간 매물벽 약세 전망. 단기 급등 후 소강 상태 진입 및 4만원 재진입 가능성 언급. 공급 계약 발표 후 급등 사례 언급.</t>
+          <t>주포 등장 및 거래량 증가 언급. 3만원 돌파 및 상한가 기대감 높으나, 주가 조작 의혹 및 단기 급등 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공매도', '매물벽', '공급계약']</t>
+          <t>['주포', '거래량', '상한가']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27600</v>
+        <v>10320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+17.45%</t>
+          <t>+23.59%</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E3" t="n">
+        <v>103</v>
+      </c>
+      <c r="F3" t="n">
+        <v>73</v>
+      </c>
+      <c r="G3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>8350</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8660</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10850</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8420</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>112187227720</v>
+      </c>
+      <c r="P3" t="n">
+        <v>20850</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4020</v>
+      </c>
+      <c r="R3" t="n">
+        <v>70000</v>
+      </c>
+      <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>649</v>
-      </c>
-      <c r="F3" t="n">
-        <v>271</v>
-      </c>
-      <c r="G3" t="n">
-        <v>951</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>23500</v>
-      </c>
-      <c r="K3" t="n">
-        <v>23200</v>
-      </c>
-      <c r="L3" t="n">
-        <v>29600</v>
-      </c>
-      <c r="M3" t="n">
-        <v>22800</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>665867321400</v>
-      </c>
-      <c r="P3" t="n">
-        <v>29600</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>8200</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-9000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-1000</v>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CART 혈압계 관련 뉴스 확인 및 거래량 증가에 따른 상승 기대감. 주포의 움직임 및 종가 상한가 가능성 언급. '세계 1위, 최초' 등의 수식어 활용.</t>
+          <t>두산에너빌리티 연관된 가스터빈 테마 및 일론 머스크 xAI 관련 뉴스 언급. 스카이랩스 다음 테마로 지목되나, 주가 조작 및 재료 소멸 우려도 공존.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['CART 혈압계', '거래량', '주포']</t>
+          <t>['가스터빈', '테마', '주가조작']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>매드업</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6430</v>
+        <v>10000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+9.91%</t>
+          <t>+22.25%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.7</v>
+        <v>0.44</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>380</v>
+        <v>64</v>
       </c>
       <c r="H4" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5850</v>
+        <v>8180</v>
       </c>
       <c r="K4" t="n">
-        <v>6000</v>
+        <v>8200</v>
       </c>
       <c r="L4" t="n">
-        <v>6525</v>
+        <v>10390</v>
       </c>
       <c r="M4" t="n">
-        <v>5940</v>
+        <v>8120</v>
       </c>
       <c r="N4" t="n">
-        <v>2.31</v>
+        <v>1.14</v>
       </c>
       <c r="O4" t="n">
-        <v>13532531285</v>
+        <v>68519688910</v>
       </c>
       <c r="P4" t="n">
-        <v>21500</v>
+        <v>22500</v>
       </c>
       <c r="Q4" t="n">
-        <v>2300</v>
+        <v>4560</v>
       </c>
       <c r="R4" t="n">
-        <v>-14000</v>
+        <v>110000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>임상 2a의 의미 및 신약 개발 가능성 언급. 현대바이오와의 연관성 및 유증 자금 활용 가능성. '게임 체인저' 가능성 제시 및 저가 매수 권유.</t>
+          <t>AI 관련주로 스카이랩스와 비교하며 상승 기대감. 프로그램 매수 등장 및 9300원 돌파 시 VI 언급. 무빙에 대한 불안감도 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['임상 2a', '신약 개발', '게임 체인저']</t>
+          <t>['AI', '프로그램매수', 'VI']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>0039P0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3575</v>
+        <v>51200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+9.49%</t>
+          <t>+16.76%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.52</v>
+        <v>0.47</v>
       </c>
       <c r="E5" t="n">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="G5" t="n">
-        <v>206</v>
+        <v>590</v>
       </c>
       <c r="H5" t="n">
-        <v>1.25</v>
+        <v>14.18</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3265</v>
+        <v>43850</v>
       </c>
       <c r="K5" t="n">
-        <v>3200</v>
+        <v>45650</v>
       </c>
       <c r="L5" t="n">
-        <v>3900</v>
+        <v>55000</v>
       </c>
       <c r="M5" t="n">
-        <v>3185</v>
+        <v>45650</v>
       </c>
       <c r="N5" t="n">
-        <v>1.77</v>
+        <v>13.71</v>
       </c>
       <c r="O5" t="n">
-        <v>166454174974</v>
+        <v>137885511075</v>
       </c>
       <c r="P5" t="n">
-        <v>3900</v>
+        <v>108900</v>
       </c>
       <c r="Q5" t="n">
-        <v>1246</v>
+        <v>18230</v>
       </c>
       <c r="R5" t="n">
-        <v>-25000</v>
+        <v>176000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>단기적인 상승 및 하락 반복, 투자 주의 필요성 언급. 탈모 관련 사업 우려 및 회사의 재무 상태에 대한 부정적 시각. 프로그램 매매 활용 후 이탈 가능성 시사.</t>
+          <t>공매도 감소 및 기술적 반등 기대감. 9월 2일 수주 공시 확인되었으나, 단기 급등 후 조정 가능성도 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['투자주의', '탈모', '프로그램 매매']</t>
+          <t>['공매도', '수주', '저항']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>215500</v>
+        <v>18340</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+6.95%</t>
+          <t>+16.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.05</v>
+        <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>404</v>
+        <v>116</v>
       </c>
       <c r="F6" t="n">
-        <v>220</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>1127</v>
+        <v>105</v>
       </c>
       <c r="H6" t="n">
-        <v>29.46</v>
+        <v>1.08</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>201500</v>
+        <v>15750</v>
       </c>
       <c r="K6" t="n">
-        <v>212500</v>
+        <v>16080</v>
       </c>
       <c r="L6" t="n">
-        <v>225500</v>
+        <v>18900</v>
       </c>
       <c r="M6" t="n">
-        <v>212500</v>
+        <v>15920</v>
       </c>
       <c r="N6" t="n">
-        <v>29.51</v>
+        <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>284539442750</v>
+        <v>66770388500</v>
       </c>
       <c r="P6" t="n">
-        <v>438000</v>
+        <v>34650</v>
       </c>
       <c r="Q6" t="n">
-        <v>74700</v>
+        <v>6980</v>
       </c>
       <c r="R6" t="n">
-        <v>353000</v>
+        <v>-21000</v>
       </c>
       <c r="S6" t="n">
-        <v>124000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>로봇 사업 관련 기술력 부각 및 60년 기술 노하우 강조. 외인·기관 매수세 유입에 따른 상승 기대감 표출.</t>
+          <t>18500원 돌파 및 저평가 기업 주장. 반도체 주 흐름 연관 기대감 있으나, 투매 및 음봉 전환 가능성도 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['로봇', '기술력', '액츄에이터']</t>
+          <t>['저평가', '저항대', '투매']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>387690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1747000</v>
+        <v>3640</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.07%</t>
+          <t>+11.49%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>-0.52</v>
       </c>
       <c r="E7" t="n">
-        <v>794</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
-        <v>419</v>
+        <v>77</v>
       </c>
       <c r="G7" t="n">
-        <v>2127</v>
+        <v>219</v>
       </c>
       <c r="H7" t="n">
-        <v>50.5</v>
+        <v>1.25</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1647000</v>
+        <v>3265</v>
       </c>
       <c r="K7" t="n">
-        <v>1737000</v>
+        <v>3200</v>
       </c>
       <c r="L7" t="n">
-        <v>1751000</v>
+        <v>3900</v>
       </c>
       <c r="M7" t="n">
-        <v>1733000</v>
+        <v>3185</v>
       </c>
       <c r="N7" t="n">
-        <v>50.45</v>
+        <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>2682641606500</v>
+        <v>181284511786</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>3900</v>
       </c>
       <c r="Q7" t="n">
-        <v>274000</v>
+        <v>1246</v>
       </c>
       <c r="R7" t="n">
-        <v>330000</v>
+        <v>-25000</v>
       </c>
       <c r="S7" t="n">
-        <v>138000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외국인 및 기관 쌍끌이 매수세 유입에 따른 상승 추세 가속화 전망. 자사주 매입 기대감 및 메모리 재고 부족 뉴스 언급. 200만원 터치 및 급등 가능성 제시.</t>
+          <t>단기적인 상승 및 하락 반복, 투자 주의 필요성 언급. 탈모 관련 사업 우려 및 회사의 재무 상태에 대한 부정적 시각. 프로그램 매매 활용 후 이탈 가능성 시사.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['자사주매입', '메모리 재고', '쌍끌이 매수']</t>
+          <t>['투자주의', '탈모', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83650</v>
+        <v>87000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.62%</t>
+          <t>+9.85%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>149</v>
+        <v>207</v>
       </c>
       <c r="F8" t="n">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="G8" t="n">
-        <v>508</v>
+        <v>851</v>
       </c>
       <c r="H8" t="n">
         <v>23.53</v>
@@ -1153,7 +1153,7 @@
         <v>80200</v>
       </c>
       <c r="L8" t="n">
-        <v>84700</v>
+        <v>87300</v>
       </c>
       <c r="M8" t="n">
         <v>79000</v>
@@ -1162,7 +1162,7 @@
         <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>170941399250</v>
+        <v>265912925200</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대규모 가스복합화력발전 투자 확정 및 하반기 본격 수주 기대감. 기술력 입증 및 10만원 돌파 전망. 원전주 전반적인 상승세 속에서 상대적 우위 확인.</t>
+          <t>일론 머스크 xAI와의 협력 소식에 따른 기대감 상승. 대규모 투자 및 가스터빈 기술력 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['대미투자', '가스터빈', '본격수주']</t>
+          <t>['복합화력발전', '가스터빈', '투자']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,123 +1207,123 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8350</v>
+        <v>6340</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.03%</t>
+          <t>+8.38%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G9" t="n">
-        <v>142</v>
+        <v>465</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>1.61</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7950</v>
+        <v>5850</v>
       </c>
       <c r="K9" t="n">
-        <v>8200</v>
+        <v>6000</v>
       </c>
       <c r="L9" t="n">
-        <v>9210</v>
+        <v>6550</v>
       </c>
       <c r="M9" t="n">
-        <v>7980</v>
+        <v>5940</v>
       </c>
       <c r="N9" t="n">
-        <v>1.32</v>
+        <v>2.31</v>
       </c>
       <c r="O9" t="n">
-        <v>88855097300</v>
+        <v>14730918325</v>
       </c>
       <c r="P9" t="n">
-        <v>15960</v>
+        <v>21500</v>
       </c>
       <c r="Q9" t="n">
-        <v>3500</v>
+        <v>2300</v>
       </c>
       <c r="R9" t="n">
-        <v>149000</v>
+        <v>-14000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
+          <t>임상 2a 및 WCLC 2026 관련 호재 언급. 6500원 돌파 시 기대감 고조. 현대바이오와 비교하며 게임 체인저 가능성 주장. 인내심 필요 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['미프진', '거래량', '수급']</t>
+          <t>['임상', '신약', '게임체인저']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17640</v>
+        <v>215500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.69%</t>
+          <t>+6.95%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>442</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>242</v>
       </c>
       <c r="G10" t="n">
-        <v>146</v>
+        <v>1247</v>
       </c>
       <c r="H10" t="n">
-        <v>10.4</v>
+        <v>29.46</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16850</v>
+        <v>201500</v>
       </c>
       <c r="K10" t="n">
-        <v>16870</v>
+        <v>212500</v>
       </c>
       <c r="L10" t="n">
-        <v>17800</v>
+        <v>225500</v>
       </c>
       <c r="M10" t="n">
-        <v>16590</v>
+        <v>212500</v>
       </c>
       <c r="N10" t="n">
-        <v>10.36</v>
+        <v>29.51</v>
       </c>
       <c r="O10" t="n">
-        <v>77896447200</v>
+        <v>295660731750</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>438000</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>74700</v>
       </c>
       <c r="R10" t="n">
-        <v>266000</v>
+        <v>353000</v>
       </c>
       <c r="S10" t="n">
-        <v>58000</v>
+        <v>124000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>러우전쟁 종전 기대감 속 건설주 동반 상승. 5% 수익 실현.</t>
+          <t>LG전자, 프로그램 매수세 유입 및 60년 모터 기술 기반 로봇 사업 기대감으로 급등. 젠슨 황 부재 속 목표 주가 100만원 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['러우전쟁', '건설주', '종전']</t>
+          <t>['로봇', 'CES 2026', '모터 기술']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>265750</v>
+        <v>1750000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.01%</t>
+          <t>+6.25%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="F11" t="n">
-        <v>449</v>
+        <v>413</v>
       </c>
       <c r="G11" t="n">
-        <v>1870</v>
+        <v>2333</v>
       </c>
       <c r="H11" t="n">
-        <v>46.73</v>
+        <v>50.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>255500</v>
+        <v>1647000</v>
       </c>
       <c r="K11" t="n">
-        <v>267000</v>
+        <v>1737000</v>
       </c>
       <c r="L11" t="n">
-        <v>268000</v>
+        <v>1751000</v>
       </c>
       <c r="M11" t="n">
-        <v>264000</v>
+        <v>1733000</v>
       </c>
       <c r="N11" t="n">
-        <v>46.71</v>
+        <v>50.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1845746056250</v>
+        <v>3195968376500</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>69600</v>
+        <v>274000</v>
       </c>
       <c r="R11" t="n">
-        <v>1189000</v>
+        <v>330000</v>
       </c>
       <c r="S11" t="n">
-        <v>911000</v>
+        <v>138000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수세 유입에도 불구하고, 정치적 이슈 및 보수적인 시장 전망. 반도체 관련 긍정적 뉴스에도 불구하고 개인 물량 털어내기 및 음전 가능성 언급.</t>
+          <t>개인 매도세 속 외인·기관 쌍끌이 매수 확인. 메모리 재고 소진 및 상승 추세 가속 기대. 200만원 목표 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '외국인 매수', '기관 매수']</t>
+          <t>['메모리', '수급', '추세']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13460</v>
+        <v>17780</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.46%</t>
+          <t>+5.52%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>285</v>
+        <v>167</v>
       </c>
       <c r="H12" t="n">
-        <v>1.82</v>
+        <v>10.4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13010</v>
+        <v>16850</v>
       </c>
       <c r="K12" t="n">
-        <v>13420</v>
+        <v>16870</v>
       </c>
       <c r="L12" t="n">
-        <v>14100</v>
+        <v>17800</v>
       </c>
       <c r="M12" t="n">
-        <v>13410</v>
+        <v>16590</v>
       </c>
       <c r="N12" t="n">
-        <v>1.91</v>
+        <v>10.36</v>
       </c>
       <c r="O12" t="n">
-        <v>63876292275</v>
+        <v>85328950395</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>1252</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>317000</v>
+        <v>266000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>광통신 섹터 강세 및 공매도 물량 소화 기대. 14000원 물린 개미.</t>
+          <t>러우전쟁 종전 기대감 속 건설주 동반 상승. 5% 수익 실현.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '공매도', '섹터']</t>
+          <t>['러우전쟁', '건설주', '종전']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6880</v>
+        <v>8370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+2.53%</t>
+          <t>+5.28%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.85</v>
+        <v>-0.72</v>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="H13" t="n">
-        <v>16.4</v>
+        <v>0.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6710</v>
+        <v>7950</v>
       </c>
       <c r="K13" t="n">
-        <v>6680</v>
+        <v>8200</v>
       </c>
       <c r="L13" t="n">
-        <v>7040</v>
+        <v>9210</v>
       </c>
       <c r="M13" t="n">
-        <v>6600</v>
+        <v>7980</v>
       </c>
       <c r="N13" t="n">
-        <v>15.55</v>
+        <v>1.32</v>
       </c>
       <c r="O13" t="n">
-        <v>9747060585</v>
+        <v>92892003420</v>
       </c>
       <c r="P13" t="n">
-        <v>13000</v>
+        <v>15960</v>
       </c>
       <c r="Q13" t="n">
-        <v>6030</v>
+        <v>3500</v>
       </c>
       <c r="R13" t="n">
-        <v>33000</v>
+        <v>149000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>한화 세미텍, 한화 로보틱스 IPO 언급 및 반도체, 로봇 사업 관련 기대감. 하지만 일부 매도 움직임 관찰.</t>
+          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['IPO', '반도체', '로봇']</t>
+          <t>['미프진', '거래량', '수급']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,169 +1660,169 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22600</v>
+        <v>267000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+4.50%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.62</v>
+        <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>784</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>428</v>
       </c>
       <c r="G14" t="n">
-        <v>130</v>
+        <v>1802</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6</v>
+        <v>46.73</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>22500</v>
+        <v>255500</v>
       </c>
       <c r="K14" t="n">
-        <v>23100</v>
+        <v>267000</v>
       </c>
       <c r="L14" t="n">
-        <v>24000</v>
+        <v>268000</v>
       </c>
       <c r="M14" t="n">
-        <v>21500</v>
+        <v>264000</v>
       </c>
       <c r="N14" t="n">
-        <v>4.98</v>
+        <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>121946555900</v>
+        <v>2143200430750</v>
       </c>
       <c r="P14" t="n">
-        <v>50600</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>9070</v>
+        <v>69600</v>
       </c>
       <c r="R14" t="n">
-        <v>28000</v>
+        <v>1189000</v>
       </c>
       <c r="S14" t="n">
-        <v>1000</v>
+        <v>911000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
+          <t>외국인 및 기관 매수세 유입, 재고 바닥 및 3분기 영업이익 120조 예상 언급. 단, 정치적 발언 및 감정적 기대 포함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '2연상']</t>
+          <t>['영업이익', '수급', '전망']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30200</v>
+        <v>13490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+3.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.4</v>
+        <v>-0.09</v>
       </c>
       <c r="E15" t="n">
+        <v>69</v>
+      </c>
+      <c r="F15" t="n">
         <v>46</v>
       </c>
-      <c r="F15" t="n">
-        <v>29</v>
-      </c>
       <c r="G15" t="n">
-        <v>76</v>
+        <v>347</v>
       </c>
       <c r="H15" t="n">
-        <v>48.96</v>
+        <v>1.82</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>30200</v>
+        <v>13010</v>
       </c>
       <c r="K15" t="n">
-        <v>30350</v>
+        <v>13420</v>
       </c>
       <c r="L15" t="n">
-        <v>30900</v>
+        <v>14100</v>
       </c>
       <c r="M15" t="n">
-        <v>29900</v>
+        <v>13400</v>
       </c>
       <c r="N15" t="n">
-        <v>24.02</v>
+        <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>61997678325</v>
+        <v>67858985950</v>
       </c>
       <c r="P15" t="n">
-        <v>31200</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>21000</v>
+        <v>1252</v>
       </c>
       <c r="R15" t="n">
-        <v>222000</v>
+        <v>317000</v>
       </c>
       <c r="S15" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
+          <t>광통신 섹터 강세 및 공매도 물량 소화 기대. 14000원 물린 개미.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['환율', '반도체', '공매도']</t>
+          <t>['광통신', '공매도', '섹터']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15970</v>
+        <v>6750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>+0.60%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="E16" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>392</v>
+        <v>94</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>16.4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>16090</v>
+        <v>6710</v>
       </c>
       <c r="K16" t="n">
-        <v>16150</v>
+        <v>6680</v>
       </c>
       <c r="L16" t="n">
-        <v>16480</v>
+        <v>7040</v>
       </c>
       <c r="M16" t="n">
-        <v>15830</v>
+        <v>6600</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>15.55</v>
       </c>
       <c r="O16" t="n">
-        <v>33394293660</v>
+        <v>10812466265</v>
       </c>
       <c r="P16" t="n">
-        <v>19380</v>
+        <v>13000</v>
       </c>
       <c r="Q16" t="n">
-        <v>3200</v>
+        <v>6030</v>
       </c>
       <c r="R16" t="n">
-        <v>-21000</v>
+        <v>33000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>17000선 지지 여부 불확실성 및 개인 간의 치열한 눈치 싸움. 반도체 관련 긍정적 뉴스에도 불구하고 '개잡주' 언급 및 실적 분석 필요성 제기.</t>
+          <t>한화머시너리앤서비스홀딩스, 공매도 압박 및 IPO 관련 불확실성 언급. 로봇 및 반도체 사업에 대한 기대감과 우려 혼재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['반도체', '주포', '2분기보고서']</t>
+          <t>['공매도', 'IPO', '로봇']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,130 +1936,130 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10140</v>
+        <v>16100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G17" t="n">
-        <v>162</v>
+        <v>450</v>
       </c>
       <c r="H17" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10390</v>
+        <v>16090</v>
       </c>
       <c r="K17" t="n">
-        <v>10050</v>
+        <v>16150</v>
       </c>
       <c r="L17" t="n">
-        <v>11000</v>
+        <v>16480</v>
       </c>
       <c r="M17" t="n">
-        <v>9770</v>
+        <v>15830</v>
       </c>
       <c r="N17" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>18367413380</v>
+        <v>36134113480</v>
       </c>
       <c r="P17" t="n">
-        <v>15640</v>
+        <v>19380</v>
       </c>
       <c r="Q17" t="n">
-        <v>5470</v>
+        <v>3200</v>
       </c>
       <c r="R17" t="n">
-        <v>-85000</v>
+        <v>-21000</v>
       </c>
       <c r="S17" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>급등 기대감 및 2백만원 목표가 제시. 공매도 소굴이라는 부정적 의견과 함께 매집 및 순환매 기대. 금일 12층 목표.</t>
+          <t>메가특구법 발의 및 호남 반도체 산단 관련 기대감. 반도체 첫 삽 시 15만원 목표 언급 있으나, 구체적 근거는 부족.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['급등', '공매도', '순환매']</t>
+          <t>['반도체', '산단', '인프라']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5500</v>
+        <v>22500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.18%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E18" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="F18" t="n">
         <v>49</v>
       </c>
       <c r="G18" t="n">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,130 +2067,130 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>5740</v>
+        <v>22500</v>
       </c>
       <c r="K18" t="n">
-        <v>5250</v>
+        <v>23100</v>
       </c>
       <c r="L18" t="n">
-        <v>5530</v>
+        <v>24000</v>
       </c>
       <c r="M18" t="n">
-        <v>5000</v>
+        <v>21500</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O18" t="n">
-        <v>3099343510</v>
+        <v>126039557675</v>
       </c>
       <c r="P18" t="n">
-        <v>9680</v>
+        <v>50600</v>
       </c>
       <c r="Q18" t="n">
-        <v>371</v>
+        <v>9070</v>
       </c>
       <c r="R18" t="n">
-        <v>-9000</v>
+        <v>28000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 악재 뉴스 발생으로 인한 하한가 우려. 투심 훼손 및 구주 매각 관련 불확실성. 'ㅈ되었다', '탈출' 등 부정적 심리 표현.</t>
+          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재 뉴스', '투심 훼손']</t>
+          <t>['로봇주', '신사업', '2연상']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>아난티</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5470</v>
+        <v>30200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.20%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F19" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="H19" t="n">
-        <v>4.81</v>
+        <v>48.95</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>5710</v>
+        <v>30200</v>
       </c>
       <c r="K19" t="n">
-        <v>5640</v>
+        <v>30350</v>
       </c>
       <c r="L19" t="n">
-        <v>5650</v>
+        <v>30900</v>
       </c>
       <c r="M19" t="n">
-        <v>5270</v>
+        <v>29900</v>
       </c>
       <c r="N19" t="n">
-        <v>4.39</v>
+        <v>24.02</v>
       </c>
       <c r="O19" t="n">
-        <v>15592118200</v>
+        <v>66912181025</v>
       </c>
       <c r="P19" t="n">
-        <v>10480</v>
+        <v>31200</v>
       </c>
       <c r="Q19" t="n">
-        <v>3150</v>
+        <v>21000</v>
       </c>
       <c r="R19" t="n">
-        <v>-336000</v>
+        <v>222000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>시진핑 방미 관련 뉴스 부재 및 하락 시작 우려. 대북주 변동성 및 주가 조작 의혹 제기. 외국인, 연기금 매수세 일부 확인.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['시진핑', '대북주', '주가 조작']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,7 +2212,283 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
+          <t>003490</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>바이오니아</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>10120</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-2.60%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E20" t="n">
+        <v>65</v>
+      </c>
+      <c r="F20" t="n">
+        <v>44</v>
+      </c>
+      <c r="G20" t="n">
+        <v>180</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>10390</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10050</v>
+      </c>
+      <c r="L20" t="n">
+        <v>11000</v>
+      </c>
+      <c r="M20" t="n">
+        <v>9770</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>18805893680</v>
+      </c>
+      <c r="P20" t="n">
+        <v>15640</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5470</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-85000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>급등 기대감 및 2백만원 목표가 제시. 공매도 소굴이라는 부정적 의견과 함께 매집 및 순환매 기대. 금일 12층 목표.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['급등', '공매도', '순환매']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>064550</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>아난티</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5450</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-4.55%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E21" t="n">
+        <v>69</v>
+      </c>
+      <c r="F21" t="n">
+        <v>48</v>
+      </c>
+      <c r="G21" t="n">
+        <v>203</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>5710</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5640</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5650</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5270</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="O21" t="n">
+        <v>16425603565</v>
+      </c>
+      <c r="P21" t="n">
+        <v>10480</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3150</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-336000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>시진핑 방미 관련 뉴스 부재 및 하락 시작 우려. 대북주 변동성 및 주가 조작 의혹 제기. 외국인, 연기금 매수세 일부 확인.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['시진핑', '대북주', '주가 조작']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>025980</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5370</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-6.45%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>93</v>
+      </c>
+      <c r="F22" t="n">
+        <v>51</v>
+      </c>
+      <c r="G22" t="n">
+        <v>229</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5530</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3565711900</v>
+      </c>
+      <c r="P22" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>371</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 및 구주 매각 관련 악재 뉴스가 연이어 발생하며 하한가 우려가 제기되었으나, 일부에서는 보합 가능성 및 악재 노출 완료 언급.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['반기보고서', '악재', '매각']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>226340</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F2" t="n">
         <v>313</v>
       </c>
       <c r="G2" t="n">
-        <v>1160</v>
+        <v>1178</v>
       </c>
       <c r="H2" t="n">
         <v>0.16</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>775414311525</v>
+        <v>775997663775</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>주포 등장 및 거래량 증가 언급. 3만원 돌파 및 상한가 기대감 높으나, 주가 조작 의혹 및 단기 급등 관련 언급.</t>
+          <t>주포의 개입 및 물량 장악 언급. 거래량 동반 상승 및 3만원 돌파 기대감. 추가 상승 여력에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '상한가']</t>
+          <t>['주포', '거래량', '상승 기대']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10320</v>
+        <v>10290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+23.59%</t>
+          <t>+23.23%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F3" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H3" t="n">
         <v>0.21</v>
@@ -702,7 +702,7 @@
         <v>0.25</v>
       </c>
       <c r="O3" t="n">
-        <v>112187227720</v>
+        <v>115959808690</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>두산에너빌리티 연관된 가스터빈 테마 및 일론 머스크 xAI 관련 뉴스 언급. 스카이랩스 다음 테마로 지목되나, 주가 조작 및 재료 소멸 우려도 공존.</t>
+          <t>일론 머스크 및 두산에너빌리티 관련 뉴스와 연계된 가스터빈 테마 부각. 새로운 테마 형성 및 상한가 기대감. IBK 관련 매수세 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['가스터빈', '테마', '주가조작']</t>
+          <t>['가스터빈', '일론 머스크', '테마']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10000</v>
+        <v>10040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+22.25%</t>
+          <t>+22.74%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.44</v>
       </c>
       <c r="E4" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="H4" t="n">
         <v>1.58</v>
@@ -794,7 +794,7 @@
         <v>1.14</v>
       </c>
       <c r="O4" t="n">
-        <v>68519688910</v>
+        <v>72233528755</v>
       </c>
       <c r="P4" t="n">
         <v>22500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>AI 관련주로 스카이랩스와 비교하며 상승 기대감. 프로그램 매수 등장 및 9300원 돌파 시 VI 언급. 무빙에 대한 불안감도 존재.</t>
+          <t>주포 및 외인 프로그램 매수 등장 언급과 함께 AI 관련 뉴스 부각. 가격 변동성에 대한 불안감과 함께 매도/관망 의견 혼재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI', '프로그램매수', 'VI']</t>
+          <t>['AI', '주포', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51200</v>
+        <v>51600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.76%</t>
+          <t>+17.67%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.47</v>
       </c>
       <c r="E5" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F5" t="n">
         <v>112</v>
       </c>
       <c r="G5" t="n">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="H5" t="n">
         <v>14.18</v>
@@ -886,7 +886,7 @@
         <v>13.71</v>
       </c>
       <c r="O5" t="n">
-        <v>137885511075</v>
+        <v>139258734525</v>
       </c>
       <c r="P5" t="n">
         <v>108900</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>공매도 감소 및 기술적 반등 기대감. 9월 2일 수주 공시 확인되었으나, 단기 급등 후 조정 가능성도 언급.</t>
+          <t>공매도 감소 및 6~7만원 구간 매물대 약화 언급. 7월 중순부터 매수 독려 및 단기 급등에 대한 기대감 표출. 수주 공시 관련 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['공매도', '수주', '저항']</t>
+          <t>['공매도', '매물벽', '수주 공시']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18340</v>
+        <v>18210</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+16.44%</t>
+          <t>+15.62%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H6" t="n">
         <v>1.08</v>
@@ -978,7 +978,7 @@
         <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>66770388500</v>
+        <v>70797468275</v>
       </c>
       <c r="P6" t="n">
         <v>34650</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>18500원 돌파 및 저평가 기업 주장. 반도체 주 흐름 연관 기대감 있으나, 투매 및 음봉 전환 가능성도 언급.</t>
+          <t>저평가 인식 및 18,500원 돌파에 대한 기대감. 반도체 주 강세 속 레메디 주가 흐름에 대한 의문 제기. 단타 거래에 유리하다는 의견.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저평가', '저항대', '투매']</t>
+          <t>['저평가', '반도체', '단타']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3640</v>
+        <v>3620</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+11.49%</t>
+          <t>+10.87%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.52</v>
       </c>
       <c r="E7" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F7" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G7" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="H7" t="n">
         <v>1.25</v>
@@ -1070,7 +1070,7 @@
         <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>181284511786</v>
+        <v>182707647785</v>
       </c>
       <c r="P7" t="n">
         <v>3900</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기적인 상승 및 하락 반복, 투자 주의 필요성 언급. 탈모 관련 사업 우려 및 회사의 재무 상태에 대한 부정적 시각. 프로그램 매매 활용 후 이탈 가능성 시사.</t>
+          <t>단기적 가격 변동에 대한 언급과 함께 투자 주의 및 매도 권유. 특정 가격대에서의 매수/매도 공방이 관찰됨.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['투자주의', '탈모', '프로그램 매매']</t>
+          <t>['가격 변동', '투자 주의', '매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>87000</v>
+        <v>6460</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>+10.43%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.08</v>
+        <v>-0.7</v>
       </c>
       <c r="E8" t="n">
-        <v>207</v>
+        <v>91</v>
       </c>
       <c r="F8" t="n">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
-        <v>851</v>
+        <v>473</v>
       </c>
       <c r="H8" t="n">
-        <v>23.53</v>
+        <v>1.61</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>79200</v>
+        <v>5850</v>
       </c>
       <c r="K8" t="n">
-        <v>80200</v>
+        <v>6000</v>
       </c>
       <c r="L8" t="n">
-        <v>87300</v>
+        <v>6550</v>
       </c>
       <c r="M8" t="n">
-        <v>79000</v>
+        <v>5940</v>
       </c>
       <c r="N8" t="n">
-        <v>23.61</v>
+        <v>2.31</v>
       </c>
       <c r="O8" t="n">
-        <v>265912925200</v>
+        <v>14933843415</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>21500</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>2300</v>
       </c>
       <c r="R8" t="n">
-        <v>146000</v>
+        <v>-14000</v>
       </c>
       <c r="S8" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>일론 머스크 xAI와의 협력 소식에 따른 기대감 상승. 대규모 투자 및 가스터빈 기술력 언급.</t>
+          <t>임상 2a 및 WCLC 2026 관련 호재 언급. 6500원 돌파 시 기대감 고조. 현대바이오와 비교하며 게임 체인저 가능성 주장. 인내심 필요 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['복합화력발전', '가스터빈', '투자']</t>
+          <t>['임상', '신약', '게임체인저']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6340</v>
+        <v>86600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.38%</t>
+          <t>+9.34%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.7</v>
+        <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>89</v>
+        <v>233</v>
       </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>147</v>
       </c>
       <c r="G9" t="n">
-        <v>465</v>
+        <v>987</v>
       </c>
       <c r="H9" t="n">
-        <v>1.61</v>
+        <v>23.53</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>5850</v>
+        <v>79200</v>
       </c>
       <c r="K9" t="n">
-        <v>6000</v>
+        <v>80200</v>
       </c>
       <c r="L9" t="n">
-        <v>6550</v>
+        <v>87800</v>
       </c>
       <c r="M9" t="n">
-        <v>5940</v>
+        <v>79000</v>
       </c>
       <c r="N9" t="n">
-        <v>2.31</v>
+        <v>23.61</v>
       </c>
       <c r="O9" t="n">
-        <v>14730918325</v>
+        <v>294644958200</v>
       </c>
       <c r="P9" t="n">
-        <v>21500</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>2300</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>-14000</v>
+        <v>146000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>임상 2a 및 WCLC 2026 관련 호재 언급. 6500원 돌파 시 기대감 고조. 현대바이오와 비교하며 게임 체인저 가능성 주장. 인내심 필요 언급.</t>
+          <t>일론 머스크 및 xAI 관련 뉴스와 연계된 긍정적 전망. 대규모 투자 및 6.3GW 가스복합 사업 관련 언급. 수급 개선 확인.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['임상', '신약', '게임체인저']</t>
+          <t>['일론 머스크', '가스복합', '수주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>215500</v>
+        <v>215000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.95%</t>
+          <t>+6.70%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="F10" t="n">
         <v>242</v>
       </c>
       <c r="G10" t="n">
-        <v>1247</v>
+        <v>1271</v>
       </c>
       <c r="H10" t="n">
         <v>29.46</v>
@@ -1346,7 +1346,7 @@
         <v>29.51</v>
       </c>
       <c r="O10" t="n">
-        <v>295660731750</v>
+        <v>302563989250</v>
       </c>
       <c r="P10" t="n">
         <v>438000</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1750000</v>
+        <v>1753000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+6.25%</t>
+          <t>+6.44%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="F11" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="G11" t="n">
-        <v>2333</v>
+        <v>2456</v>
       </c>
       <c r="H11" t="n">
         <v>50.5</v>
@@ -1429,7 +1429,7 @@
         <v>1737000</v>
       </c>
       <c r="L11" t="n">
-        <v>1751000</v>
+        <v>1754000</v>
       </c>
       <c r="M11" t="n">
         <v>1733000</v>
@@ -1438,7 +1438,7 @@
         <v>50.45</v>
       </c>
       <c r="O11" t="n">
-        <v>3195968376500</v>
+        <v>3308479719000</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>개인 매도세 속 외인·기관 쌍끌이 매수 확인. 메모리 재고 소진 및 상승 추세 가속 기대. 200만원 목표 언급.</t>
+          <t>메모리 재고 감소 및 반등 기대감. 외국인, 기관의 쌍끌이 매수세 유입 확인. 180~200 내외 종가 및 상승 추세 가속 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['메모리', '수급', '추세']</t>
+          <t>['메모리 재고', '쌍끌이 매수', '상승 추세']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17780</v>
+        <v>8410</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+5.52%</t>
+          <t>+5.79%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.04</v>
+        <v>-0.72</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G12" t="n">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="H12" t="n">
-        <v>10.4</v>
+        <v>0.6</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16850</v>
+        <v>7950</v>
       </c>
       <c r="K12" t="n">
-        <v>16870</v>
+        <v>8200</v>
       </c>
       <c r="L12" t="n">
-        <v>17800</v>
+        <v>9210</v>
       </c>
       <c r="M12" t="n">
-        <v>16590</v>
+        <v>7980</v>
       </c>
       <c r="N12" t="n">
-        <v>10.36</v>
+        <v>1.32</v>
       </c>
       <c r="O12" t="n">
-        <v>85328950395</v>
+        <v>93320537920</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>15960</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>3500</v>
       </c>
       <c r="R12" t="n">
-        <v>266000</v>
+        <v>149000</v>
       </c>
       <c r="S12" t="n">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>러우전쟁 종전 기대감 속 건설주 동반 상승. 5% 수익 실현.</t>
+          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['러우전쟁', '건설주', '종전']</t>
+          <t>['미프진', '거래량', '수급']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8370</v>
+        <v>17820</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+5.28%</t>
+          <t>+5.76%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.72</v>
+        <v>0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="G13" t="n">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6</v>
+        <v>10.4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7950</v>
+        <v>16850</v>
       </c>
       <c r="K13" t="n">
-        <v>8200</v>
+        <v>16870</v>
       </c>
       <c r="L13" t="n">
-        <v>9210</v>
+        <v>17860</v>
       </c>
       <c r="M13" t="n">
-        <v>7980</v>
+        <v>16590</v>
       </c>
       <c r="N13" t="n">
-        <v>1.32</v>
+        <v>10.36</v>
       </c>
       <c r="O13" t="n">
-        <v>92892003420</v>
+        <v>89682335950</v>
       </c>
       <c r="P13" t="n">
-        <v>15960</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>3500</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>149000</v>
+        <v>266000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
+          <t>러우전쟁 종전 기대감 속 건설주 동반 상승. 5% 수익 실현.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['미프진', '거래량', '수급']</t>
+          <t>['러우전쟁', '건설주', '종전']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="F14" t="n">
         <v>428</v>
       </c>
       <c r="G14" t="n">
-        <v>1802</v>
+        <v>1747</v>
       </c>
       <c r="H14" t="n">
         <v>46.73</v>
@@ -1714,7 +1714,7 @@
         <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>2143200430750</v>
+        <v>2251102102750</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수세 유입, 재고 바닥 및 3분기 영업이익 120조 예상 언급. 단, 정치적 발언 및 감정적 기대 포함.</t>
+          <t>외국인 및 기관 매수세 유입 감지. 재고 소진 및 3분기 영업이익 예상치에 대한 언급이 있으나, 정치적 언급과 함께 감정적 표현이 다수.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '수급', '전망']</t>
+          <t>['재고', '영업이익', '매수세']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13490</v>
+        <v>13460</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.69%</t>
+          <t>+3.46%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.09</v>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="H15" t="n">
         <v>1.82</v>
@@ -1806,7 +1806,7 @@
         <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>67858985950</v>
+        <v>68312931285</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1851,92 +1851,92 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6750</v>
+        <v>22650</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.60%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="E16" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>94</v>
+        <v>174</v>
       </c>
       <c r="H16" t="n">
-        <v>16.4</v>
+        <v>5.6</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6710</v>
+        <v>22500</v>
       </c>
       <c r="K16" t="n">
-        <v>6680</v>
+        <v>23100</v>
       </c>
       <c r="L16" t="n">
-        <v>7040</v>
+        <v>24000</v>
       </c>
       <c r="M16" t="n">
-        <v>6600</v>
+        <v>21500</v>
       </c>
       <c r="N16" t="n">
-        <v>15.55</v>
+        <v>4.98</v>
       </c>
       <c r="O16" t="n">
-        <v>10812466265</v>
+        <v>126743785400</v>
       </c>
       <c r="P16" t="n">
-        <v>13000</v>
+        <v>50600</v>
       </c>
       <c r="Q16" t="n">
-        <v>6030</v>
+        <v>9070</v>
       </c>
       <c r="R16" t="n">
-        <v>33000</v>
+        <v>28000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스, 공매도 압박 및 IPO 관련 불확실성 언급. 로봇 및 반도체 사업에 대한 기대감과 우려 혼재.</t>
+          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도', 'IPO', '로봇']</t>
+          <t>['로봇주', '신사업', '2연상']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16100</v>
+        <v>16160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>36134113480</v>
+        <v>37677899785</v>
       </c>
       <c r="P17" t="n">
         <v>19380</v>
@@ -2035,70 +2035,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22500</v>
+        <v>30250</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.62</v>
+        <v>0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="G18" t="n">
-        <v>154</v>
+        <v>89</v>
       </c>
       <c r="H18" t="n">
-        <v>5.6</v>
+        <v>48.95</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>22500</v>
+        <v>30200</v>
       </c>
       <c r="K18" t="n">
-        <v>23100</v>
+        <v>30350</v>
       </c>
       <c r="L18" t="n">
-        <v>24000</v>
+        <v>30900</v>
       </c>
       <c r="M18" t="n">
-        <v>21500</v>
+        <v>29900</v>
       </c>
       <c r="N18" t="n">
-        <v>4.98</v>
+        <v>24.02</v>
       </c>
       <c r="O18" t="n">
-        <v>126039557675</v>
+        <v>68200986675</v>
       </c>
       <c r="P18" t="n">
-        <v>50600</v>
+        <v>31200</v>
       </c>
       <c r="Q18" t="n">
-        <v>9070</v>
+        <v>21000</v>
       </c>
       <c r="R18" t="n">
-        <v>28000</v>
+        <v>222000</v>
       </c>
       <c r="S18" t="n">
-        <v>1000</v>
+        <v>35000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '2연상']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,18 +2120,18 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30200</v>
+        <v>6710</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="H19" t="n">
-        <v>48.95</v>
+        <v>16.4</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,60 +2159,60 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>30200</v>
+        <v>6710</v>
       </c>
       <c r="K19" t="n">
-        <v>30350</v>
+        <v>6680</v>
       </c>
       <c r="L19" t="n">
-        <v>30900</v>
+        <v>7040</v>
       </c>
       <c r="M19" t="n">
-        <v>29900</v>
+        <v>6600</v>
       </c>
       <c r="N19" t="n">
-        <v>24.02</v>
+        <v>15.55</v>
       </c>
       <c r="O19" t="n">
-        <v>66912181025</v>
+        <v>11039043240</v>
       </c>
       <c r="P19" t="n">
-        <v>31200</v>
+        <v>13000</v>
       </c>
       <c r="Q19" t="n">
-        <v>21000</v>
+        <v>6030</v>
       </c>
       <c r="R19" t="n">
-        <v>222000</v>
+        <v>33000</v>
       </c>
       <c r="S19" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
+          <t>한화머시너리앤서비스홀딩스, 공매도 압박 및 IPO 관련 불확실성 언급. 로봇 및 반도체 사업에 대한 기대감과 우려 혼재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['환율', '반도체', '공매도']</t>
+          <t>['공매도', 'IPO', '로봇']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10120</v>
+        <v>10290</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.60%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.05</v>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="H20" t="n">
         <v>5.75</v>
@@ -2266,7 +2266,7 @@
         <v>5.7</v>
       </c>
       <c r="O20" t="n">
-        <v>18805893680</v>
+        <v>18975353870</v>
       </c>
       <c r="P20" t="n">
         <v>15640</v>
@@ -2326,7 +2326,7 @@
         <v>0.42</v>
       </c>
       <c r="E21" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F21" t="n">
         <v>48</v>
@@ -2358,7 +2358,7 @@
         <v>4.39</v>
       </c>
       <c r="O21" t="n">
-        <v>16425603565</v>
+        <v>16720291895</v>
       </c>
       <c r="P21" t="n">
         <v>10480</v>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5370</v>
+        <v>5410</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-6.45%</t>
+          <t>-5.75%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F22" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G22" t="n">
         <v>229</v>
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3565711900</v>
+        <v>3601832550</v>
       </c>
       <c r="P22" t="n">
         <v>9680</v>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -581,10 +581,10 @@
         <v>799</v>
       </c>
       <c r="F2" t="n">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G2" t="n">
-        <v>1178</v>
+        <v>1223</v>
       </c>
       <c r="H2" t="n">
         <v>0.16</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>775997663775</v>
+        <v>776552268475</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -619,23 +619,23 @@
         <v>8200</v>
       </c>
       <c r="R2" t="n">
-        <v>-9000</v>
+        <v>1000</v>
       </c>
       <c r="S2" t="n">
         <v>-1000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>주포의 개입 및 물량 장악 언급. 거래량 동반 상승 및 3만원 돌파 기대감. 추가 상승 여력에 대한 긍정적 전망.</t>
+          <t>스카이랩스, 거래량 증가와 함께 급등 가능성 언급. '주포' 언급 등 시세 조종 관련 논란 존재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '상승 기대']</t>
+          <t>['거래량', '시세 조종', '주포']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10290</v>
+        <v>10220</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+23.23%</t>
+          <t>+22.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H3" t="n">
         <v>0.21</v>
@@ -702,7 +702,7 @@
         <v>0.25</v>
       </c>
       <c r="O3" t="n">
-        <v>115959808690</v>
+        <v>118262341050</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -711,14 +711,14 @@
         <v>4020</v>
       </c>
       <c r="R3" t="n">
-        <v>70000</v>
+        <v>100000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-232000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>일론 머스크 및 두산에너빌리티 관련 뉴스와 연계된 가스터빈 테마 부각. 새로운 테마 형성 및 상한가 기대감. IBK 관련 매수세 언급.</t>
+          <t>삼미금속, 두산에너빌리티 및 일론 머스크 관련 가스터빈 테마 편입 가능성으로 급등. 신규 재료 부각.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['가스터빈', '일론 머스크', '테마']</t>
+          <t>['가스터빈', '테마', '두산에너빌리티']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10040</v>
+        <v>9970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+22.74%</t>
+          <t>+21.88%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.44</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H4" t="n">
         <v>1.58</v>
@@ -794,7 +794,7 @@
         <v>1.14</v>
       </c>
       <c r="O4" t="n">
-        <v>72233528755</v>
+        <v>75434428540</v>
       </c>
       <c r="P4" t="n">
         <v>22500</v>
@@ -803,23 +803,23 @@
         <v>4560</v>
       </c>
       <c r="R4" t="n">
-        <v>110000</v>
+        <v>152000</v>
       </c>
       <c r="S4" t="n">
         <v>-9000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>주포 및 외인 프로그램 매수 등장 언급과 함께 AI 관련 뉴스 부각. 가격 변동성에 대한 불안감과 함께 매도/관망 의견 혼재.</t>
+          <t>매드업, AI 관련주로 부각되며 외국인·프로그램 매수세 유입. 매물대 소화 후 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI', '주포', '프로그램 매수']</t>
+          <t>['AI', '외국인 매수', '매물대']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51600</v>
+        <v>51800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.67%</t>
+          <t>+18.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.47</v>
       </c>
       <c r="E5" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F5" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G5" t="n">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="H5" t="n">
         <v>14.18</v>
@@ -886,7 +886,7 @@
         <v>13.71</v>
       </c>
       <c r="O5" t="n">
-        <v>139258734525</v>
+        <v>140581808925</v>
       </c>
       <c r="P5" t="n">
         <v>108900</v>
@@ -895,10 +895,10 @@
         <v>18230</v>
       </c>
       <c r="R5" t="n">
-        <v>176000</v>
+        <v>156000</v>
       </c>
       <c r="S5" t="n">
-        <v>44000</v>
+        <v>-11000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18210</v>
+        <v>18360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+15.62%</t>
+          <t>+16.57%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F6" t="n">
         <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="H6" t="n">
         <v>1.08</v>
@@ -978,7 +978,7 @@
         <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>70797468275</v>
+        <v>74204682845</v>
       </c>
       <c r="P6" t="n">
         <v>34650</v>
@@ -987,23 +987,23 @@
         <v>6980</v>
       </c>
       <c r="R6" t="n">
-        <v>-21000</v>
+        <v>-36000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>저평가 인식 및 18,500원 돌파에 대한 기대감. 반도체 주 강세 속 레메디 주가 흐름에 대한 의문 제기. 단타 거래에 유리하다는 의견.</t>
+          <t>레메디, 저평가된 기업으로 텐배거 기대감 존재. 저항대 소화 및 반도체 섹터 흐름에 따른 추가 상승 가능성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저평가', '반도체', '단타']</t>
+          <t>['저평가', '텐배거', '반도체']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3620</v>
+        <v>3605</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+10.87%</t>
+          <t>+10.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.52</v>
       </c>
       <c r="E7" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F7" t="n">
         <v>79</v>
       </c>
       <c r="G7" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H7" t="n">
         <v>1.25</v>
@@ -1070,7 +1070,7 @@
         <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>182707647785</v>
+        <v>184414286932</v>
       </c>
       <c r="P7" t="n">
         <v>3900</v>
@@ -1079,14 +1079,14 @@
         <v>1246</v>
       </c>
       <c r="R7" t="n">
-        <v>-25000</v>
+        <v>-840000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기적 가격 변동에 대한 언급과 함께 투자 주의 및 매도 권유. 특정 가격대에서의 매수/매도 공방이 관찰됨.</t>
+          <t>단기적인 상승 및 하락 반복, 투자 주의 필요성 언급. 탈모 관련 사업 우려 및 회사의 재무 상태에 대한 부정적 시각. 프로그램 매매 활용 후 이탈 가능성 시사.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['가격 변동', '투자 주의', '매도']</t>
+          <t>['투자주의', '탈모', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6460</v>
+        <v>86700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+10.43%</t>
+          <t>+9.47%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.7</v>
+        <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>91</v>
+        <v>256</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>163</v>
       </c>
       <c r="G8" t="n">
-        <v>473</v>
+        <v>1054</v>
       </c>
       <c r="H8" t="n">
-        <v>1.61</v>
+        <v>23.53</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5850</v>
+        <v>79200</v>
       </c>
       <c r="K8" t="n">
-        <v>6000</v>
+        <v>80200</v>
       </c>
       <c r="L8" t="n">
-        <v>6550</v>
+        <v>87800</v>
       </c>
       <c r="M8" t="n">
-        <v>5940</v>
+        <v>79000</v>
       </c>
       <c r="N8" t="n">
-        <v>2.31</v>
+        <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>14933843415</v>
+        <v>309901135300</v>
       </c>
       <c r="P8" t="n">
-        <v>21500</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>2300</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>-14000</v>
+        <v>519000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>107000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>임상 2a 및 WCLC 2026 관련 호재 언급. 6500원 돌파 시 기대감 고조. 현대바이오와 비교하며 게임 체인저 가능성 주장. 인내심 필요 언급.</t>
+          <t>두산에너빌리티, 일론 머스크 관련 뉴스 및 대규모 투자 발표로 인한 기대감 급증. 하반기 수주 전망 긍정적.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['임상', '신약', '게임체인저']</t>
+          <t>['일론 머스크', '가스터빈', '수주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86600</v>
+        <v>6370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+9.34%</t>
+          <t>+8.89%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.08</v>
+        <v>-0.7</v>
       </c>
       <c r="E9" t="n">
-        <v>233</v>
+        <v>92</v>
       </c>
       <c r="F9" t="n">
-        <v>147</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>987</v>
+        <v>474</v>
       </c>
       <c r="H9" t="n">
-        <v>23.53</v>
+        <v>1.61</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>79200</v>
+        <v>5850</v>
       </c>
       <c r="K9" t="n">
-        <v>80200</v>
+        <v>6000</v>
       </c>
       <c r="L9" t="n">
-        <v>87800</v>
+        <v>6550</v>
       </c>
       <c r="M9" t="n">
-        <v>79000</v>
+        <v>5940</v>
       </c>
       <c r="N9" t="n">
-        <v>23.61</v>
+        <v>2.31</v>
       </c>
       <c r="O9" t="n">
-        <v>294644958200</v>
+        <v>15032602260</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>21500</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>2300</v>
       </c>
       <c r="R9" t="n">
-        <v>146000</v>
+        <v>-8000</v>
       </c>
       <c r="S9" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>일론 머스크 및 xAI 관련 뉴스와 연계된 긍정적 전망. 대규모 투자 및 6.3GW 가스복합 사업 관련 언급. 수급 개선 확인.</t>
+          <t>페니트리움바이오, 임상 2a 결과 발표 및 세계폐암학회 참가 예정으로 인한 기대감 형성. 6500원 돌파 시 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['일론 머스크', '가스복합', '수주']</t>
+          <t>['임상 2a', '폐암학회', '6500원']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>215000</v>
+        <v>1757000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.70%</t>
+          <t>+6.68%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>454</v>
+        <v>797</v>
       </c>
       <c r="F10" t="n">
-        <v>242</v>
+        <v>417</v>
       </c>
       <c r="G10" t="n">
-        <v>1271</v>
+        <v>2633</v>
       </c>
       <c r="H10" t="n">
-        <v>29.46</v>
+        <v>50.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>201500</v>
+        <v>1647000</v>
       </c>
       <c r="K10" t="n">
-        <v>212500</v>
+        <v>1737000</v>
       </c>
       <c r="L10" t="n">
-        <v>225500</v>
+        <v>1758000</v>
       </c>
       <c r="M10" t="n">
-        <v>212500</v>
+        <v>1733000</v>
       </c>
       <c r="N10" t="n">
-        <v>29.51</v>
+        <v>50.45</v>
       </c>
       <c r="O10" t="n">
-        <v>302563989250</v>
+        <v>3441858171500</v>
       </c>
       <c r="P10" t="n">
-        <v>438000</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>74700</v>
+        <v>274000</v>
       </c>
       <c r="R10" t="n">
-        <v>353000</v>
+        <v>479000</v>
       </c>
       <c r="S10" t="n">
-        <v>124000</v>
+        <v>203000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>LG전자, 프로그램 매수세 유입 및 60년 모터 기술 기반 로봇 사업 기대감으로 급등. 젠슨 황 부재 속 목표 주가 100만원 언급.</t>
+          <t>SK하이닉스, 메모리 재고 감소 및 외국인·기관 매수세 증가로 인한 상승 추세 가속. 200달성 기대감 고조.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['로봇', 'CES 2026', '모터 기술']</t>
+          <t>['메모리', '재고', '외국인 매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1753000</v>
+        <v>214500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+6.44%</t>
+          <t>+6.45%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>792</v>
+        <v>462</v>
       </c>
       <c r="F11" t="n">
-        <v>409</v>
+        <v>243</v>
       </c>
       <c r="G11" t="n">
-        <v>2456</v>
+        <v>1293</v>
       </c>
       <c r="H11" t="n">
-        <v>50.5</v>
+        <v>29.46</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1647000</v>
+        <v>201500</v>
       </c>
       <c r="K11" t="n">
-        <v>1737000</v>
+        <v>212500</v>
       </c>
       <c r="L11" t="n">
-        <v>1754000</v>
+        <v>225500</v>
       </c>
       <c r="M11" t="n">
-        <v>1733000</v>
+        <v>212500</v>
       </c>
       <c r="N11" t="n">
-        <v>50.45</v>
+        <v>29.51</v>
       </c>
       <c r="O11" t="n">
-        <v>3308479719000</v>
+        <v>304727357250</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>438000</v>
       </c>
       <c r="Q11" t="n">
-        <v>274000</v>
+        <v>74700</v>
       </c>
       <c r="R11" t="n">
-        <v>330000</v>
+        <v>306000</v>
       </c>
       <c r="S11" t="n">
-        <v>138000</v>
+        <v>133000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>메모리 재고 감소 및 반등 기대감. 외국인, 기관의 쌍끌이 매수세 유입 확인. 180~200 내외 종가 및 상승 추세 가속 전망.</t>
+          <t>LG전자, 프로그램 매수세 유입 및 60년 모터 기술 기반 로봇 사업 기대감으로 급등. 젠슨 황 부재 속 목표 주가 100만원 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['메모리 재고', '쌍끌이 매수', '상승 추세']</t>
+          <t>['로봇', 'CES 2026', '모터 기술']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8410</v>
+        <v>17850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+5.79%</t>
+          <t>+5.93%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.72</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6</v>
+        <v>10.4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7950</v>
+        <v>16850</v>
       </c>
       <c r="K12" t="n">
-        <v>8200</v>
+        <v>16870</v>
       </c>
       <c r="L12" t="n">
-        <v>9210</v>
+        <v>17910</v>
       </c>
       <c r="M12" t="n">
-        <v>7980</v>
+        <v>16590</v>
       </c>
       <c r="N12" t="n">
-        <v>1.32</v>
+        <v>10.36</v>
       </c>
       <c r="O12" t="n">
-        <v>93320537920</v>
+        <v>93629367575</v>
       </c>
       <c r="P12" t="n">
-        <v>15960</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>3500</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>149000</v>
+        <v>340000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
+          <t>러우전쟁 종전 기대감 속 건설주 동반 상승. 5% 수익 실현.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미프진', '거래량', '수급']</t>
+          <t>['러우전쟁', '건설주', '종전']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17820</v>
+        <v>8360</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+5.76%</t>
+          <t>+5.16%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.04</v>
+        <v>-0.72</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="H13" t="n">
-        <v>10.4</v>
+        <v>0.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16850</v>
+        <v>7950</v>
       </c>
       <c r="K13" t="n">
-        <v>16870</v>
+        <v>8200</v>
       </c>
       <c r="L13" t="n">
-        <v>17860</v>
+        <v>9210</v>
       </c>
       <c r="M13" t="n">
-        <v>16590</v>
+        <v>7980</v>
       </c>
       <c r="N13" t="n">
-        <v>10.36</v>
+        <v>1.32</v>
       </c>
       <c r="O13" t="n">
-        <v>89682335950</v>
+        <v>93728011260</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>15960</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>3500</v>
       </c>
       <c r="R13" t="n">
-        <v>266000</v>
+        <v>26000</v>
       </c>
       <c r="S13" t="n">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>러우전쟁 종전 기대감 속 건설주 동반 상승. 5% 수익 실현.</t>
+          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['러우전쟁', '건설주', '종전']</t>
+          <t>['미프진', '거래량', '수급']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>267000</v>
+        <v>267750</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+4.50%</t>
+          <t>+4.79%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F14" t="n">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G14" t="n">
-        <v>1747</v>
+        <v>1877</v>
       </c>
       <c r="H14" t="n">
         <v>46.73</v>
@@ -1714,7 +1714,7 @@
         <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>2251102102750</v>
+        <v>2349215087750</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1723,14 +1723,14 @@
         <v>69600</v>
       </c>
       <c r="R14" t="n">
-        <v>1189000</v>
+        <v>1309000</v>
       </c>
       <c r="S14" t="n">
-        <v>911000</v>
+        <v>1097000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수세 유입 감지. 재고 소진 및 3분기 영업이익 예상치에 대한 언급이 있으나, 정치적 언급과 함께 감정적 표현이 다수.</t>
+          <t>삼성전자, 반도체 재고 감소 및 HBM 가격 상승 기대감 형성. 그러나 정치적 언급과 불확실한 전망이 혼재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['재고', '영업이익', '매수세']</t>
+          <t>['HBM', '재고', '반도체']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>-0.09</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="H15" t="n">
         <v>1.82</v>
@@ -1806,7 +1806,7 @@
         <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>68312931285</v>
+        <v>68873394290</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1815,7 +1815,7 @@
         <v>1252</v>
       </c>
       <c r="R15" t="n">
-        <v>317000</v>
+        <v>336000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1851,215 +1851,215 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22650</v>
+        <v>6750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+0.60%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="E16" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G16" t="n">
-        <v>174</v>
+        <v>97</v>
       </c>
       <c r="H16" t="n">
-        <v>5.6</v>
+        <v>16.4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>22500</v>
+        <v>6710</v>
       </c>
       <c r="K16" t="n">
-        <v>23100</v>
+        <v>6680</v>
       </c>
       <c r="L16" t="n">
-        <v>24000</v>
+        <v>7040</v>
       </c>
       <c r="M16" t="n">
-        <v>21500</v>
+        <v>6600</v>
       </c>
       <c r="N16" t="n">
-        <v>4.98</v>
+        <v>15.55</v>
       </c>
       <c r="O16" t="n">
-        <v>126743785400</v>
+        <v>11088297960</v>
       </c>
       <c r="P16" t="n">
-        <v>50600</v>
+        <v>13000</v>
       </c>
       <c r="Q16" t="n">
-        <v>9070</v>
+        <v>6030</v>
       </c>
       <c r="R16" t="n">
-        <v>28000</v>
+        <v>-57000</v>
       </c>
       <c r="S16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
+          <t>공매도 및 모건스탠리 매도 의혹 제기. 2차 폭락 및 개미 투자자 유입 시 하락 전망. IPO 예정 종목(한화세미텍, 한화로보틱스) 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '2연상']</t>
+          <t>['공매도', 'IPO', '모건스탠리']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16160</v>
+        <v>22550</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>461</v>
+        <v>174</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>16090</v>
+        <v>22500</v>
       </c>
       <c r="K17" t="n">
-        <v>16150</v>
+        <v>23100</v>
       </c>
       <c r="L17" t="n">
-        <v>16480</v>
+        <v>24000</v>
       </c>
       <c r="M17" t="n">
-        <v>15830</v>
+        <v>21500</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O17" t="n">
-        <v>37677899785</v>
+        <v>127257326225</v>
       </c>
       <c r="P17" t="n">
-        <v>19380</v>
+        <v>50600</v>
       </c>
       <c r="Q17" t="n">
-        <v>3200</v>
+        <v>9070</v>
       </c>
       <c r="R17" t="n">
-        <v>-21000</v>
+        <v>9000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>메가특구법 발의 및 호남 반도체 산단 관련 기대감. 반도체 첫 삽 시 15만원 목표 언급 있으나, 구체적 근거는 부족.</t>
+          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['반도체', '산단', '인프라']</t>
+          <t>['로봇주', '신사업', '2연상']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30250</v>
+        <v>16120</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G18" t="n">
-        <v>89</v>
+        <v>476</v>
       </c>
       <c r="H18" t="n">
-        <v>48.95</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,91 +2067,91 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>30200</v>
+        <v>16090</v>
       </c>
       <c r="K18" t="n">
-        <v>30350</v>
+        <v>16150</v>
       </c>
       <c r="L18" t="n">
-        <v>30900</v>
+        <v>16480</v>
       </c>
       <c r="M18" t="n">
-        <v>29900</v>
+        <v>15830</v>
       </c>
       <c r="N18" t="n">
-        <v>24.02</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>68200986675</v>
+        <v>38839397945</v>
       </c>
       <c r="P18" t="n">
-        <v>31200</v>
+        <v>19380</v>
       </c>
       <c r="Q18" t="n">
-        <v>21000</v>
+        <v>3200</v>
       </c>
       <c r="R18" t="n">
-        <v>222000</v>
+        <v>31000</v>
       </c>
       <c r="S18" t="n">
-        <v>35000</v>
+        <v>-1000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
+          <t>금호건설, 반도체 산업 연관 가능성 언급에도 불구하고 주가 부진 및 차트 하향 추세 관찰. 투자 심리 불확실.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['환율', '반도체', '공매도']</t>
+          <t>['반도체', '산단', '주가']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6710</v>
+        <v>30250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="E19" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H19" t="n">
-        <v>16.4</v>
+        <v>48.95</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,60 +2159,60 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6710</v>
+        <v>30200</v>
       </c>
       <c r="K19" t="n">
-        <v>6680</v>
+        <v>30350</v>
       </c>
       <c r="L19" t="n">
-        <v>7040</v>
+        <v>30900</v>
       </c>
       <c r="M19" t="n">
-        <v>6600</v>
+        <v>29900</v>
       </c>
       <c r="N19" t="n">
-        <v>15.55</v>
+        <v>24.02</v>
       </c>
       <c r="O19" t="n">
-        <v>11039043240</v>
+        <v>69264692475</v>
       </c>
       <c r="P19" t="n">
-        <v>13000</v>
+        <v>31200</v>
       </c>
       <c r="Q19" t="n">
-        <v>6030</v>
+        <v>21000</v>
       </c>
       <c r="R19" t="n">
-        <v>33000</v>
+        <v>481000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>113000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스, 공매도 압박 및 IPO 관련 불확실성 언급. 로봇 및 반도체 사업에 대한 기대감과 우려 혼재.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['공매도', 'IPO', '로봇']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10290</v>
+        <v>10230</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.05</v>
       </c>
       <c r="E20" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="H20" t="n">
         <v>5.75</v>
@@ -2266,7 +2266,7 @@
         <v>5.7</v>
       </c>
       <c r="O20" t="n">
-        <v>18975353870</v>
+        <v>19164156865</v>
       </c>
       <c r="P20" t="n">
         <v>15640</v>
@@ -2275,7 +2275,7 @@
         <v>5470</v>
       </c>
       <c r="R20" t="n">
-        <v>-85000</v>
+        <v>-120000</v>
       </c>
       <c r="S20" t="n">
         <v>-2000</v>
@@ -2326,13 +2326,13 @@
         <v>0.42</v>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H21" t="n">
         <v>4.81</v>
@@ -2358,7 +2358,7 @@
         <v>4.39</v>
       </c>
       <c r="O21" t="n">
-        <v>16720291895</v>
+        <v>16794965110</v>
       </c>
       <c r="P21" t="n">
         <v>10480</v>
@@ -2367,7 +2367,7 @@
         <v>3150</v>
       </c>
       <c r="R21" t="n">
-        <v>-336000</v>
+        <v>-432000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5410</v>
+        <v>5420</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.75%</t>
+          <t>-5.57%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F22" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G22" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3601832550</v>
+        <v>3627191580</v>
       </c>
       <c r="P22" t="n">
         <v>9680</v>
@@ -2459,23 +2459,23 @@
         <v>371</v>
       </c>
       <c r="R22" t="n">
-        <v>-9000</v>
+        <v>-5000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 구주 매각 관련 악재 뉴스가 연이어 발생하며 하한가 우려가 제기되었으나, 일부에서는 보합 가능성 및 악재 노출 완료 언급.</t>
+          <t>본느, 반기보고서 제출 지연 및 악재 뉴스 발생으로 인한 투심 훼손. 주가 하락 가능성 및 불확실성 증대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '매각']</t>
+          <t>['반기보고서', '악재', '투심']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>799</v>
+        <v>559</v>
       </c>
       <c r="F2" t="n">
-        <v>317</v>
+        <v>243</v>
       </c>
       <c r="G2" t="n">
-        <v>1223</v>
+        <v>783</v>
       </c>
       <c r="H2" t="n">
         <v>0.16</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>776552268475</v>
+        <v>776910283925</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>스카이랩스, 거래량 증가와 함께 급등 가능성 언급. '주포' 언급 등 시세 조종 관련 논란 존재.</t>
+          <t>주포 언급 및 거래량 증가에 따른 급등 기대. F1 재무 투자자 상장일 미매도 소식.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['거래량', '시세 조종', '주포']</t>
+          <t>['주포', '거래량', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10220</v>
+        <v>10270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+22.40%</t>
+          <t>+22.99%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0.21</v>
@@ -702,7 +702,7 @@
         <v>0.25</v>
       </c>
       <c r="O3" t="n">
-        <v>118262341050</v>
+        <v>121551260410</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>매드업</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9970</v>
+        <v>18940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.88%</t>
+          <t>+20.25%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="E4" t="n">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="H4" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8180</v>
+        <v>15750</v>
       </c>
       <c r="K4" t="n">
-        <v>8200</v>
+        <v>16080</v>
       </c>
       <c r="L4" t="n">
-        <v>10390</v>
+        <v>19110</v>
       </c>
       <c r="M4" t="n">
-        <v>8120</v>
+        <v>15920</v>
       </c>
       <c r="N4" t="n">
-        <v>1.14</v>
+        <v>0.71</v>
       </c>
       <c r="O4" t="n">
-        <v>75434428540</v>
+        <v>83129209455</v>
       </c>
       <c r="P4" t="n">
-        <v>22500</v>
+        <v>34650</v>
       </c>
       <c r="Q4" t="n">
-        <v>4560</v>
+        <v>6980</v>
       </c>
       <c r="R4" t="n">
-        <v>152000</v>
+        <v>-36000</v>
       </c>
       <c r="S4" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>매드업, AI 관련주로 부각되며 외국인·프로그램 매수세 유입. 매물대 소화 후 상승 기대감 형성.</t>
+          <t>저평가 기업 분석 및 텐배거 기대. 공모가 대비 현재 가격 비교 및 저항대 소화.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI', '외국인 매수', '매물대']</t>
+          <t>['공모가', '저평가', '텐배거']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0039P0</t>
+          <t>387690</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>매드업</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51800</v>
+        <v>9820</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+18.13%</t>
+          <t>+20.05%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="E5" t="n">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="F5" t="n">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>606</v>
+        <v>93</v>
       </c>
       <c r="H5" t="n">
-        <v>14.18</v>
+        <v>1.58</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>43850</v>
+        <v>8180</v>
       </c>
       <c r="K5" t="n">
-        <v>45650</v>
+        <v>8200</v>
       </c>
       <c r="L5" t="n">
-        <v>55000</v>
+        <v>10390</v>
       </c>
       <c r="M5" t="n">
-        <v>45650</v>
+        <v>8120</v>
       </c>
       <c r="N5" t="n">
-        <v>13.71</v>
+        <v>1.14</v>
       </c>
       <c r="O5" t="n">
-        <v>140581808925</v>
+        <v>78758810440</v>
       </c>
       <c r="P5" t="n">
-        <v>108900</v>
+        <v>22500</v>
       </c>
       <c r="Q5" t="n">
-        <v>18230</v>
+        <v>4560</v>
       </c>
       <c r="R5" t="n">
-        <v>156000</v>
+        <v>152000</v>
       </c>
       <c r="S5" t="n">
-        <v>-11000</v>
+        <v>-9000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>공매도 감소 및 6~7만원 구간 매물대 약화 언급. 7월 중순부터 매수 독려 및 단기 급등에 대한 기대감 표출. 수주 공시 관련 언급.</t>
+          <t>외인/프로그램 매수세 유입 감지. AI 셀럽 영상 매출 관련 뉴스 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['공매도', '매물벽', '수주 공시']</t>
+          <t>['AI', '프로그램매수', '매물대']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>0039P0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18360</v>
+        <v>50800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+16.57%</t>
+          <t>+15.85%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="G6" t="n">
-        <v>122</v>
+        <v>610</v>
       </c>
       <c r="H6" t="n">
-        <v>1.08</v>
+        <v>14.18</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>15750</v>
+        <v>43850</v>
       </c>
       <c r="K6" t="n">
-        <v>16080</v>
+        <v>45650</v>
       </c>
       <c r="L6" t="n">
-        <v>18900</v>
+        <v>55000</v>
       </c>
       <c r="M6" t="n">
-        <v>15920</v>
+        <v>45650</v>
       </c>
       <c r="N6" t="n">
-        <v>0.71</v>
+        <v>13.71</v>
       </c>
       <c r="O6" t="n">
-        <v>74204682845</v>
+        <v>143386644525</v>
       </c>
       <c r="P6" t="n">
-        <v>34650</v>
+        <v>108900</v>
       </c>
       <c r="Q6" t="n">
-        <v>6980</v>
+        <v>18230</v>
       </c>
       <c r="R6" t="n">
-        <v>-36000</v>
+        <v>156000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-11000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>레메디, 저평가된 기업으로 텐배거 기대감 존재. 저항대 소화 및 반도체 섹터 흐름에 따른 추가 상승 가능성.</t>
+          <t>공매도 감소 및 6~7만원 구간 매물대 약화 언급. 7월 중순부터 매수 독려 및 단기 급등에 대한 기대감 표출. 수주 공시 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저평가', '텐배거', '반도체']</t>
+          <t>['공매도', '매물벽', '수주 공시']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>387690</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3605</v>
+        <v>3600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+10.41%</t>
+          <t>+10.26%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.52</v>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="F7" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G7" t="n">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="H7" t="n">
         <v>1.25</v>
@@ -1070,7 +1070,7 @@
         <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>184414286932</v>
+        <v>186427769594</v>
       </c>
       <c r="P7" t="n">
         <v>3900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기적인 상승 및 하락 반복, 투자 주의 필요성 언급. 탈모 관련 사업 우려 및 회사의 재무 상태에 대한 부정적 시각. 프로그램 매매 활용 후 이탈 가능성 시사.</t>
+          <t>단기 수익 달성 후 투자주의 필요성 제기. 탈모 관련 사업 반복 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['투자주의', '탈모', '프로그램 매매']</t>
+          <t>['탈모', '수익', '투자주의']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86700</v>
+        <v>86600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.47%</t>
+          <t>+9.34%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="F8" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G8" t="n">
-        <v>1054</v>
+        <v>1102</v>
       </c>
       <c r="H8" t="n">
         <v>23.53</v>
@@ -1162,7 +1162,7 @@
         <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>309901135300</v>
+        <v>323876864300</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 일론 머스크 관련 뉴스 및 대규모 투자 발표로 인한 기대감 급증. 하반기 수주 전망 긍정적.</t>
+          <t>일론 머스크의 두산에너빌리티 선택 속보. 하반기 본격 수주 기대 및 기술력 입증.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['일론 머스크', '가스터빈', '수주']</t>
+          <t>['가스터빈', '대미투자', '수주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1228,7 +1228,7 @@
         <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="H9" t="n">
         <v>1.61</v>
@@ -1254,7 +1254,7 @@
         <v>2.31</v>
       </c>
       <c r="O9" t="n">
-        <v>15032602260</v>
+        <v>15296274690</v>
       </c>
       <c r="P9" t="n">
         <v>21500</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1757000</v>
+        <v>1766000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.68%</t>
+          <t>+7.23%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>797</v>
+        <v>637</v>
       </c>
       <c r="F10" t="n">
-        <v>417</v>
+        <v>372</v>
       </c>
       <c r="G10" t="n">
-        <v>2633</v>
+        <v>2161</v>
       </c>
       <c r="H10" t="n">
         <v>50.5</v>
@@ -1337,7 +1337,7 @@
         <v>1737000</v>
       </c>
       <c r="L10" t="n">
-        <v>1758000</v>
+        <v>1768000</v>
       </c>
       <c r="M10" t="n">
         <v>1733000</v>
@@ -1346,7 +1346,7 @@
         <v>50.45</v>
       </c>
       <c r="O10" t="n">
-        <v>3441858171500</v>
+        <v>3633699737000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SK하이닉스, 메모리 재고 감소 및 외국인·기관 매수세 증가로 인한 상승 추세 가속. 200달성 기대감 고조.</t>
+          <t>메모리 재고 감소 전망 속 2차 상승 시작 기대. 외인/기관 매수 확대 및 개인 매도세.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['메모리', '재고', '외국인 매수']</t>
+          <t>['메모리', '재고', '상승 추세']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F11" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G11" t="n">
-        <v>1293</v>
+        <v>1316</v>
       </c>
       <c r="H11" t="n">
         <v>29.46</v>
@@ -1438,7 +1438,7 @@
         <v>29.51</v>
       </c>
       <c r="O11" t="n">
-        <v>304727357250</v>
+        <v>309267583500</v>
       </c>
       <c r="P11" t="n">
         <v>438000</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>LG전자, 프로그램 매수세 유입 및 60년 모터 기술 기반 로봇 사업 기대감으로 급등. 젠슨 황 부재 속 목표 주가 100만원 언급.</t>
+          <t>LG전자 로봇 관련 기술력 부각 및 목표주가 100만원 제시. 프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.7</v>
+        <v>0.15</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['로봇', 'CES 2026', '모터 기술']</t>
+          <t>['로봇', '모터 기술', '목표주가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17850</v>
+        <v>17730</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+5.93%</t>
+          <t>+5.22%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>66</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="H12" t="n">
         <v>10.4</v>
@@ -1530,7 +1530,7 @@
         <v>10.36</v>
       </c>
       <c r="O12" t="n">
-        <v>93629367575</v>
+        <v>96836919485</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1596,7 +1596,7 @@
         <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H13" t="n">
         <v>0.6</v>
@@ -1622,7 +1622,7 @@
         <v>1.32</v>
       </c>
       <c r="O13" t="n">
-        <v>93728011260</v>
+        <v>94122052565</v>
       </c>
       <c r="P13" t="n">
         <v>15960</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>267750</v>
+        <v>268000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+4.79%</t>
+          <t>+4.89%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="F14" t="n">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="G14" t="n">
-        <v>1877</v>
+        <v>1926</v>
       </c>
       <c r="H14" t="n">
         <v>46.73</v>
@@ -1705,7 +1705,7 @@
         <v>267000</v>
       </c>
       <c r="L14" t="n">
-        <v>268000</v>
+        <v>268500</v>
       </c>
       <c r="M14" t="n">
         <v>264000</v>
@@ -1714,7 +1714,7 @@
         <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>2349215087750</v>
+        <v>2589704910000</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼성전자, 반도체 재고 감소 및 HBM 가격 상승 기대감 형성. 그러나 정치적 언급과 불확실한 전망이 혼재.</t>
+          <t>미국장 휴장 속 재고 바닥 전망 및 기술적 반등 기대. 외국인/기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['HBM', '재고', '반도체']</t>
+          <t>['HBM', '반도체', '영업이익']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13460</v>
+        <v>13400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.46%</t>
+          <t>+3.00%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.09</v>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="H15" t="n">
         <v>1.82</v>
@@ -1800,13 +1800,13 @@
         <v>14100</v>
       </c>
       <c r="M15" t="n">
-        <v>13400</v>
+        <v>13360</v>
       </c>
       <c r="N15" t="n">
         <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>68873394290</v>
+        <v>70636470665</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6750</v>
+        <v>6770</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.60%</t>
+          <t>+0.89%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.85</v>
       </c>
       <c r="E16" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
         <v>37</v>
       </c>
       <c r="G16" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H16" t="n">
         <v>16.4</v>
@@ -1898,7 +1898,7 @@
         <v>15.55</v>
       </c>
       <c r="O16" t="n">
-        <v>11088297960</v>
+        <v>11180149305</v>
       </c>
       <c r="P16" t="n">
         <v>13000</v>
@@ -1943,70 +1943,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22550</v>
+        <v>30300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.62</v>
+        <v>0.4</v>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G17" t="n">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>5.6</v>
+        <v>48.95</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>22500</v>
+        <v>30200</v>
       </c>
       <c r="K17" t="n">
-        <v>23100</v>
+        <v>30350</v>
       </c>
       <c r="L17" t="n">
-        <v>24000</v>
+        <v>30900</v>
       </c>
       <c r="M17" t="n">
-        <v>21500</v>
+        <v>29900</v>
       </c>
       <c r="N17" t="n">
-        <v>4.98</v>
+        <v>24.02</v>
       </c>
       <c r="O17" t="n">
-        <v>127257326225</v>
+        <v>70538324725</v>
       </c>
       <c r="P17" t="n">
-        <v>50600</v>
+        <v>31200</v>
       </c>
       <c r="Q17" t="n">
-        <v>9070</v>
+        <v>21000</v>
       </c>
       <c r="R17" t="n">
-        <v>9000</v>
+        <v>481000</v>
       </c>
       <c r="S17" t="n">
-        <v>1000</v>
+        <v>113000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '2연상']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16120</v>
+        <v>16140</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F18" t="n">
         <v>57</v>
       </c>
       <c r="G18" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>38839397945</v>
+        <v>39379321330</v>
       </c>
       <c r="P18" t="n">
         <v>19380</v>
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30250</v>
+        <v>22400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.4</v>
+        <v>0.62</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F19" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>90</v>
+        <v>174</v>
       </c>
       <c r="H19" t="n">
-        <v>48.95</v>
+        <v>5.6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>30200</v>
+        <v>22500</v>
       </c>
       <c r="K19" t="n">
-        <v>30350</v>
+        <v>23100</v>
       </c>
       <c r="L19" t="n">
-        <v>30900</v>
+        <v>24000</v>
       </c>
       <c r="M19" t="n">
-        <v>29900</v>
+        <v>21500</v>
       </c>
       <c r="N19" t="n">
-        <v>24.02</v>
+        <v>4.98</v>
       </c>
       <c r="O19" t="n">
-        <v>69264692475</v>
+        <v>128704847300</v>
       </c>
       <c r="P19" t="n">
-        <v>31200</v>
+        <v>50600</v>
       </c>
       <c r="Q19" t="n">
-        <v>21000</v>
+        <v>9070</v>
       </c>
       <c r="R19" t="n">
-        <v>481000</v>
+        <v>9000</v>
       </c>
       <c r="S19" t="n">
-        <v>113000</v>
+        <v>1000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
+          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['환율', '반도체', '공매도']</t>
+          <t>['로봇주', '신사업', '2연상']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10230</v>
+        <v>10220</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H20" t="n">
         <v>5.75</v>
@@ -2266,7 +2266,7 @@
         <v>5.7</v>
       </c>
       <c r="O20" t="n">
-        <v>19164156865</v>
+        <v>19311642465</v>
       </c>
       <c r="P20" t="n">
         <v>15640</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5450</v>
+        <v>5470</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>-4.20%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.42</v>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F21" t="n">
         <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="H21" t="n">
         <v>4.81</v>
@@ -2358,7 +2358,7 @@
         <v>4.39</v>
       </c>
       <c r="O21" t="n">
-        <v>16794965110</v>
+        <v>17047380650</v>
       </c>
       <c r="P21" t="n">
         <v>10480</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5420</v>
+        <v>5390</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.57%</t>
+          <t>-6.10%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F22" t="n">
         <v>54</v>
       </c>
       <c r="G22" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3627191580</v>
+        <v>3683674400</v>
       </c>
       <c r="P22" t="n">
         <v>9680</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>본느, 반기보고서 제출 지연 및 악재 뉴스 발생으로 인한 투심 훼손. 주가 하락 가능성 및 불확실성 증대.</t>
+          <t>악재 뉴스 발생(조선비즈 기사) 및 투심 훼손 우려. 반기보고서 제출 지연.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '투심']</t>
+          <t>['악재', '반기보고서', '투심']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>559</v>
+        <v>799</v>
       </c>
       <c r="F2" t="n">
-        <v>243</v>
+        <v>331</v>
       </c>
       <c r="G2" t="n">
-        <v>783</v>
+        <v>1313</v>
       </c>
       <c r="H2" t="n">
         <v>0.16</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>776910283925</v>
+        <v>779537095125</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>주포 언급 및 거래량 증가에 따른 급등 기대. F1 재무 투자자 상장일 미매도 소식.</t>
+          <t>세계 최초 반지 혈압계 기술력과 건강보험 급여 등재 관련 뉴스를 기반으로 한 강한 상승 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '급등']</t>
+          <t>['반지 혈압계', '건강보험 급여', '세계 최초']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10270</v>
+        <v>10080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+22.99%</t>
+          <t>+20.72%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="H3" t="n">
         <v>0.21</v>
@@ -702,7 +702,7 @@
         <v>0.25</v>
       </c>
       <c r="O3" t="n">
-        <v>121551260410</v>
+        <v>136695787280</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼미금속, 두산에너빌리티 및 일론 머스크 관련 가스터빈 테마 편입 가능성으로 급등. 신규 재료 부각.</t>
+          <t>일론 머스크 관련 뉴스 및 두산에너빌리티 연관성을 바탕으로 한 강한 상승 기대감, 기술적 재료 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['가스터빈', '테마', '두산에너빌리티']</t>
+          <t>['일론 머스크', '두산에너빌리티', '가스터빈']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18940</v>
+        <v>18590</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+20.25%</t>
+          <t>+18.03%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.37</v>
       </c>
       <c r="E4" t="n">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="H4" t="n">
         <v>1.08</v>
@@ -785,7 +785,7 @@
         <v>16080</v>
       </c>
       <c r="L4" t="n">
-        <v>19110</v>
+        <v>19440</v>
       </c>
       <c r="M4" t="n">
         <v>15920</v>
@@ -794,7 +794,7 @@
         <v>0.71</v>
       </c>
       <c r="O4" t="n">
-        <v>83129209455</v>
+        <v>107134387535</v>
       </c>
       <c r="P4" t="n">
         <v>34650</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>저평가 기업 분석 및 텐배거 기대. 공모가 대비 현재 가격 비교 및 저항대 소화.</t>
+          <t>스카이랩스와의 비교 및 저평가 논리를 바탕으로 한 급등 기대감, 공모가 대비 높은 상승 잠재력 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공모가', '저평가', '텐배거']</t>
+          <t>['저평가', '공모가', '텐배거']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9820</v>
+        <v>9510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+20.05%</t>
+          <t>+16.26%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.44</v>
       </c>
       <c r="E5" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="H5" t="n">
         <v>1.58</v>
@@ -886,7 +886,7 @@
         <v>1.14</v>
       </c>
       <c r="O5" t="n">
-        <v>78758810440</v>
+        <v>88725666105</v>
       </c>
       <c r="P5" t="n">
         <v>22500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>외인/프로그램 매수세 유입 감지. AI 셀럽 영상 매출 관련 뉴스 언급.</t>
+          <t>외인 프로그램 매수 등장과 함께 10000원 안착 및 신고가 돌파에 대한 기대감, 추세 분석.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI', '프로그램매수', '매물대']</t>
+          <t>['외인 매수', '신고가', '추세 분석']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50800</v>
+        <v>50400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+15.85%</t>
+          <t>+14.94%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.47</v>
       </c>
       <c r="E6" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F6" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G6" t="n">
-        <v>610</v>
+        <v>701</v>
       </c>
       <c r="H6" t="n">
         <v>14.18</v>
@@ -978,7 +978,7 @@
         <v>13.71</v>
       </c>
       <c r="O6" t="n">
-        <v>143386644525</v>
+        <v>153406524325</v>
       </c>
       <c r="P6" t="n">
         <v>108900</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>공매도 감소 및 6~7만원 구간 매물대 약화 언급. 7월 중순부터 매수 독려 및 단기 급등에 대한 기대감 표출. 수주 공시 관련 언급.</t>
+          <t>공매도 감소와 단기 급등에 대한 언급, 7월부터의 매수 독려 및 기술적 저항대 분석.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공매도', '매물벽', '수주 공시']</t>
+          <t>['공매도', '기술적 분석', '수주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3600</v>
+        <v>3580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+10.26%</t>
+          <t>+9.65%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.52</v>
       </c>
       <c r="E7" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F7" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G7" t="n">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="H7" t="n">
         <v>1.25</v>
@@ -1070,7 +1070,7 @@
         <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>186427769594</v>
+        <v>193321474153</v>
       </c>
       <c r="P7" t="n">
         <v>3900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기 수익 달성 후 투자주의 필요성 제기. 탈모 관련 사업 반복 언급.</t>
+          <t>긍정적인 단기 수익 언급과 함께 장기 투자 가능성을 질문하는 내용, 투자 경고에 대한 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['탈모', '수익', '투자주의']</t>
+          <t>['단기 수익', '장기 투자', '투자 경고']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86600</v>
+        <v>86300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.34%</t>
+          <t>+8.96%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>265</v>
+        <v>320</v>
       </c>
       <c r="F8" t="n">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="G8" t="n">
-        <v>1102</v>
+        <v>1299</v>
       </c>
       <c r="H8" t="n">
         <v>23.53</v>
@@ -1162,7 +1162,7 @@
         <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>323876864300</v>
+        <v>366978024550</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>일론 머스크의 두산에너빌리티 선택 속보. 하반기 본격 수주 기대 및 기술력 입증.</t>
+          <t>일론 머스크 관련 뉴스와 대규모 투자 소식을 기반으로 한 긍정적인 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['가스터빈', '대미투자', '수주']</t>
+          <t>['일론 머스크', '대미 투자', '가스복합']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6370</v>
+        <v>6320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.89%</t>
+          <t>+8.03%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.7</v>
       </c>
       <c r="E9" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G9" t="n">
-        <v>480</v>
+        <v>548</v>
       </c>
       <c r="H9" t="n">
         <v>1.61</v>
@@ -1254,7 +1254,7 @@
         <v>2.31</v>
       </c>
       <c r="O9" t="n">
-        <v>15296274690</v>
+        <v>15977173930</v>
       </c>
       <c r="P9" t="n">
         <v>21500</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1766000</v>
+        <v>1764000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+7.23%</t>
+          <t>+7.10%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>637</v>
+        <v>798</v>
       </c>
       <c r="F10" t="n">
-        <v>372</v>
+        <v>462</v>
       </c>
       <c r="G10" t="n">
-        <v>2161</v>
+        <v>2597</v>
       </c>
       <c r="H10" t="n">
         <v>50.5</v>
@@ -1337,7 +1337,7 @@
         <v>1737000</v>
       </c>
       <c r="L10" t="n">
-        <v>1768000</v>
+        <v>1778000</v>
       </c>
       <c r="M10" t="n">
         <v>1733000</v>
@@ -1346,7 +1346,7 @@
         <v>50.45</v>
       </c>
       <c r="O10" t="n">
-        <v>3633699737000</v>
+        <v>4385237957000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>메모리 재고 감소 전망 속 2차 상승 시작 기대. 외인/기관 매수 확대 및 개인 매도세.</t>
+          <t>메모리 재고 감소 및 2차 상승 시작 기대감, 외인/기관 매수 확대에 따른 긍정적 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['메모리', '재고', '상승 추세']</t>
+          <t>['메모리 재고', '외인 매수', '기술적 분석']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>466</v>
+        <v>506</v>
       </c>
       <c r="F11" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="G11" t="n">
-        <v>1316</v>
+        <v>1430</v>
       </c>
       <c r="H11" t="n">
         <v>29.46</v>
@@ -1438,7 +1438,7 @@
         <v>29.51</v>
       </c>
       <c r="O11" t="n">
-        <v>309267583500</v>
+        <v>328638040750</v>
       </c>
       <c r="P11" t="n">
         <v>438000</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>LG전자 로봇 관련 기술력 부각 및 목표주가 100만원 제시. 프로그램 매수세 유입.</t>
+          <t>CES 2024 관련 호재와 함께 100만원 목표주가 제시. 빅테크와의 액추에이터 수주 협의 중 소식.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['로봇', '모터 기술', '목표주가']</t>
+          <t>['CES', '액추에이터', '수주']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17730</v>
+        <v>17880</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+5.22%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G12" t="n">
-        <v>204</v>
+        <v>262</v>
       </c>
       <c r="H12" t="n">
         <v>10.4</v>
@@ -1521,7 +1521,7 @@
         <v>16870</v>
       </c>
       <c r="L12" t="n">
-        <v>17910</v>
+        <v>17990</v>
       </c>
       <c r="M12" t="n">
         <v>16590</v>
@@ -1530,7 +1530,7 @@
         <v>10.36</v>
       </c>
       <c r="O12" t="n">
-        <v>96836919485</v>
+        <v>110729083955</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8360</v>
+        <v>267750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+5.16%</t>
+          <t>+4.79%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.72</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>795</v>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>423</v>
       </c>
       <c r="G13" t="n">
-        <v>162</v>
+        <v>2152</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6</v>
+        <v>46.73</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7950</v>
+        <v>255500</v>
       </c>
       <c r="K13" t="n">
-        <v>8200</v>
+        <v>267000</v>
       </c>
       <c r="L13" t="n">
-        <v>9210</v>
+        <v>269000</v>
       </c>
       <c r="M13" t="n">
-        <v>7980</v>
+        <v>264000</v>
       </c>
       <c r="N13" t="n">
-        <v>1.32</v>
+        <v>46.71</v>
       </c>
       <c r="O13" t="n">
-        <v>94122052565</v>
+        <v>3261256177250</v>
       </c>
       <c r="P13" t="n">
-        <v>15960</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3500</v>
+        <v>69600</v>
       </c>
       <c r="R13" t="n">
-        <v>26000</v>
+        <v>1309000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1097000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
+          <t>정치적 언급과 개인적인 희망사항이 혼재된 게시글들로, 객관적인 분석 근거 부족.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,51 +1647,51 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['미프진', '거래량', '수급']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>268000</v>
+        <v>8300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+4.89%</t>
+          <t>+4.40%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.02</v>
+        <v>-0.72</v>
       </c>
       <c r="E14" t="n">
-        <v>794</v>
+        <v>84</v>
       </c>
       <c r="F14" t="n">
-        <v>427</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>1926</v>
+        <v>179</v>
       </c>
       <c r="H14" t="n">
-        <v>46.73</v>
+        <v>0.6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>255500</v>
+        <v>7950</v>
       </c>
       <c r="K14" t="n">
-        <v>267000</v>
+        <v>8200</v>
       </c>
       <c r="L14" t="n">
-        <v>268500</v>
+        <v>9210</v>
       </c>
       <c r="M14" t="n">
-        <v>264000</v>
+        <v>7980</v>
       </c>
       <c r="N14" t="n">
-        <v>46.71</v>
+        <v>1.32</v>
       </c>
       <c r="O14" t="n">
-        <v>2589704910000</v>
+        <v>96018536220</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>15960</v>
       </c>
       <c r="Q14" t="n">
-        <v>69600</v>
+        <v>3500</v>
       </c>
       <c r="R14" t="n">
-        <v>1309000</v>
+        <v>26000</v>
       </c>
       <c r="S14" t="n">
-        <v>1097000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국장 휴장 속 재고 바닥 전망 및 기술적 반등 기대. 외국인/기관 매수세 유입.</t>
+          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['HBM', '반도체', '영업이익']</t>
+          <t>['미프진', '거래량', '수급']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13400</v>
+        <v>13410</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.00%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.09</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F15" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="H15" t="n">
         <v>1.82</v>
@@ -1806,7 +1806,7 @@
         <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>70636470665</v>
+        <v>73940319390</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6770</v>
+        <v>5870</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G16" t="n">
-        <v>99</v>
+        <v>352</v>
       </c>
       <c r="H16" t="n">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6710</v>
+        <v>5740</v>
       </c>
       <c r="K16" t="n">
-        <v>6680</v>
+        <v>5250</v>
       </c>
       <c r="L16" t="n">
-        <v>7040</v>
+        <v>6790</v>
       </c>
       <c r="M16" t="n">
-        <v>6600</v>
+        <v>5000</v>
       </c>
       <c r="N16" t="n">
-        <v>15.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>11180149305</v>
+        <v>17210590800</v>
       </c>
       <c r="P16" t="n">
-        <v>13000</v>
+        <v>9680</v>
       </c>
       <c r="Q16" t="n">
-        <v>6030</v>
+        <v>371</v>
       </c>
       <c r="R16" t="n">
-        <v>-57000</v>
+        <v>-5000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>공매도 및 모건스탠리 매도 의혹 제기. 2차 폭락 및 개미 투자자 유입 시 하락 전망. IPO 예정 종목(한화세미텍, 한화로보틱스) 언급.</t>
+          <t>유증 및 전환사채 납입 완료 호재에도 불구하고, 반기 보고서 제출 지연 및 악재성 기사로 인한 하락 우려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도', 'IPO', '모건스탠리']</t>
+          <t>['유증', '반기 보고서', '악재']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30300</v>
+        <v>6740</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="H17" t="n">
-        <v>48.95</v>
+        <v>16.4</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>30200</v>
+        <v>6710</v>
       </c>
       <c r="K17" t="n">
-        <v>30350</v>
+        <v>6680</v>
       </c>
       <c r="L17" t="n">
-        <v>30900</v>
+        <v>7040</v>
       </c>
       <c r="M17" t="n">
-        <v>29900</v>
+        <v>6600</v>
       </c>
       <c r="N17" t="n">
-        <v>24.02</v>
+        <v>15.55</v>
       </c>
       <c r="O17" t="n">
-        <v>70538324725</v>
+        <v>12217773245</v>
       </c>
       <c r="P17" t="n">
-        <v>31200</v>
+        <v>13000</v>
       </c>
       <c r="Q17" t="n">
-        <v>21000</v>
+        <v>6030</v>
       </c>
       <c r="R17" t="n">
-        <v>481000</v>
+        <v>-57000</v>
       </c>
       <c r="S17" t="n">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
+          <t>공매도 및 모건스탠리 매도 의혹 제기. 2차 폭락 및 개미 투자자 유입 시 하락 전망. IPO 예정 종목(한화세미텍, 한화로보틱스) 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['환율', '반도체', '공매도']</t>
+          <t>['공매도', 'IPO', '모건스탠리']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16140</v>
+        <v>30300</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F18" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="G18" t="n">
-        <v>477</v>
+        <v>123</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>48.99</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,130 +2067,130 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>16090</v>
+        <v>30200</v>
       </c>
       <c r="K18" t="n">
-        <v>16150</v>
+        <v>30350</v>
       </c>
       <c r="L18" t="n">
-        <v>16480</v>
+        <v>30900</v>
       </c>
       <c r="M18" t="n">
-        <v>15830</v>
+        <v>29900</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>24.02</v>
       </c>
       <c r="O18" t="n">
-        <v>39379321330</v>
+        <v>79874130900</v>
       </c>
       <c r="P18" t="n">
-        <v>19380</v>
+        <v>31200</v>
       </c>
       <c r="Q18" t="n">
-        <v>3200</v>
+        <v>21000</v>
       </c>
       <c r="R18" t="n">
-        <v>31000</v>
+        <v>481000</v>
       </c>
       <c r="S18" t="n">
-        <v>-1000</v>
+        <v>113000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>금호건설, 반도체 산업 연관 가능성 언급에도 불구하고 주가 부진 및 차트 하향 추세 관찰. 투자 심리 불확실.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['반도체', '산단', '주가']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22400</v>
+        <v>16090</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="F19" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G19" t="n">
-        <v>174</v>
+        <v>520</v>
       </c>
       <c r="H19" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>22500</v>
+        <v>16090</v>
       </c>
       <c r="K19" t="n">
-        <v>23100</v>
+        <v>16150</v>
       </c>
       <c r="L19" t="n">
-        <v>24000</v>
+        <v>16480</v>
       </c>
       <c r="M19" t="n">
-        <v>21500</v>
+        <v>15830</v>
       </c>
       <c r="N19" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>128704847300</v>
+        <v>42148599715</v>
       </c>
       <c r="P19" t="n">
-        <v>50600</v>
+        <v>19380</v>
       </c>
       <c r="Q19" t="n">
-        <v>9070</v>
+        <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>9000</v>
+        <v>31000</v>
       </c>
       <c r="S19" t="n">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
+          <t>금호건설, 반도체 산업 연관 가능성 언급에도 불구하고 주가 부진 및 차트 하향 추세 관찰. 투자 심리 불확실.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '2연상']</t>
+          <t>['반도체', '산단', '주가']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10220</v>
+        <v>22350</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.05</v>
+        <v>0.62</v>
       </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H20" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,38 +2251,38 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>10390</v>
+        <v>22500</v>
       </c>
       <c r="K20" t="n">
-        <v>10050</v>
+        <v>23100</v>
       </c>
       <c r="L20" t="n">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="M20" t="n">
-        <v>9770</v>
+        <v>21500</v>
       </c>
       <c r="N20" t="n">
-        <v>5.7</v>
+        <v>4.98</v>
       </c>
       <c r="O20" t="n">
-        <v>19311642465</v>
+        <v>131733327025</v>
       </c>
       <c r="P20" t="n">
-        <v>15640</v>
+        <v>50600</v>
       </c>
       <c r="Q20" t="n">
-        <v>5470</v>
+        <v>9070</v>
       </c>
       <c r="R20" t="n">
-        <v>-120000</v>
+        <v>9000</v>
       </c>
       <c r="S20" t="n">
-        <v>-2000</v>
+        <v>1000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>급등 기대감 및 2백만원 목표가 제시. 공매도 소굴이라는 부정적 의견과 함께 매집 및 순환매 기대. 금일 12층 목표.</t>
+          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['급등', '공매도', '순환매']</t>
+          <t>['로봇주', '신사업', '2연상']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,77 +2304,77 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>아난티</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>10120</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-2.60%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E21" t="n">
+        <v>71</v>
+      </c>
+      <c r="F21" t="n">
+        <v>45</v>
+      </c>
+      <c r="G21" t="n">
+        <v>215</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>10390</v>
+      </c>
+      <c r="K21" t="n">
+        <v>10050</v>
+      </c>
+      <c r="L21" t="n">
+        <v>11000</v>
+      </c>
+      <c r="M21" t="n">
+        <v>9770</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>19846267585</v>
+      </c>
+      <c r="P21" t="n">
+        <v>15640</v>
+      </c>
+      <c r="Q21" t="n">
         <v>5470</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>-4.20%</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E21" t="n">
-        <v>75</v>
-      </c>
-      <c r="F21" t="n">
-        <v>49</v>
-      </c>
-      <c r="G21" t="n">
-        <v>214</v>
-      </c>
-      <c r="H21" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>5710</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5640</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5650</v>
-      </c>
-      <c r="M21" t="n">
-        <v>5270</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="O21" t="n">
-        <v>17047380650</v>
-      </c>
-      <c r="P21" t="n">
-        <v>10480</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3150</v>
-      </c>
       <c r="R21" t="n">
-        <v>-432000</v>
+        <v>-120000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>시진핑 방미 관련 뉴스 부재 및 하락 시작 우려. 대북주 변동성 및 주가 조작 의혹 제기. 외국인, 연기금 매수세 일부 확인.</t>
+          <t>급등 기대감 및 2백만원 목표가 제시. 공매도 소굴이라는 부정적 의견과 함께 매집 및 순환매 기대. 금일 12층 목표.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['시진핑', '대북주', '주가 조작']</t>
+          <t>['급등', '공매도', '순환매']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>025980</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>아난티</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5390</v>
+        <v>5500</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-6.10%</t>
+          <t>-3.68%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="E22" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="F22" t="n">
         <v>54</v>
       </c>
       <c r="G22" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,60 +2435,60 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>5740</v>
+        <v>5710</v>
       </c>
       <c r="K22" t="n">
-        <v>5250</v>
+        <v>5640</v>
       </c>
       <c r="L22" t="n">
-        <v>5530</v>
+        <v>5650</v>
       </c>
       <c r="M22" t="n">
-        <v>5000</v>
+        <v>5270</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="O22" t="n">
-        <v>3683674400</v>
+        <v>20732557755</v>
       </c>
       <c r="P22" t="n">
-        <v>9680</v>
+        <v>10480</v>
       </c>
       <c r="Q22" t="n">
-        <v>371</v>
+        <v>3150</v>
       </c>
       <c r="R22" t="n">
-        <v>-5000</v>
+        <v>-432000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>악재 뉴스 발생(조선비즈 기사) 및 투심 훼손 우려. 반기보고서 제출 지연.</t>
+          <t>시진핑 방미 관련 뉴스 부재 및 하락 시작 우려. 대북주 변동성 및 주가 조작 의혹 제기. 외국인, 연기금 매수세 일부 확인.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['악재', '반기보고서', '투심']</t>
+          <t>['시진핑', '대북주', '주가 조작']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>025980</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -581,10 +581,10 @@
         <v>799</v>
       </c>
       <c r="F2" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G2" t="n">
-        <v>1313</v>
+        <v>1344</v>
       </c>
       <c r="H2" t="n">
         <v>0.16</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>779537095125</v>
+        <v>779882249025</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -619,23 +619,23 @@
         <v>8200</v>
       </c>
       <c r="R2" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="S2" t="n">
         <v>-1000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>세계 최초 반지 혈압계 기술력과 건강보험 급여 등재 관련 뉴스를 기반으로 한 강한 상승 기대감.</t>
+          <t>‘CART 혈압계’의 건강보험 급여 등재 및 세계 최초 반지 혈압계 기술력에 기반한 급등 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['반지 혈압계', '건강보험 급여', '세계 최초']</t>
+          <t>['CART 혈압계', '건강보험 급여', '세계 최초']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10080</v>
+        <v>10070</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+20.72%</t>
+          <t>+20.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="F3" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="H3" t="n">
         <v>0.21</v>
@@ -702,7 +702,7 @@
         <v>0.25</v>
       </c>
       <c r="O3" t="n">
-        <v>136695787280</v>
+        <v>147600024660</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -711,23 +711,23 @@
         <v>4020</v>
       </c>
       <c r="R3" t="n">
-        <v>100000</v>
+        <v>54000</v>
       </c>
       <c r="S3" t="n">
-        <v>-232000</v>
+        <v>-937000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>일론 머스크 관련 뉴스 및 두산에너빌리티 연관성을 바탕으로 한 강한 상승 기대감, 기술적 재료 언급.</t>
+          <t>삼미금속, 미국 초대형 가스발전 열병합 사업 수주 뉴스로 급등. 테마 기대감 형성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['일론 머스크', '두산에너빌리티', '가스터빈']</t>
+          <t>['가스터빈', '가스발전', '테마']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.37</v>
       </c>
       <c r="E4" t="n">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="H4" t="n">
         <v>1.08</v>
@@ -794,7 +794,7 @@
         <v>0.71</v>
       </c>
       <c r="O4" t="n">
-        <v>107134387535</v>
+        <v>119482542980</v>
       </c>
       <c r="P4" t="n">
         <v>34650</v>
@@ -803,23 +803,23 @@
         <v>6980</v>
       </c>
       <c r="R4" t="n">
-        <v>-36000</v>
+        <v>-29000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>스카이랩스와의 비교 및 저평가 논리를 바탕으로 한 급등 기대감, 공모가 대비 높은 상승 잠재력 언급.</t>
+          <t>레메디, 기술력 부각 및 공모가 대비 저평가 논란 속 18500원 돌파 시도. 텐배거 기대감 형성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['저평가', '공모가', '텐배거']</t>
+          <t>['기술력', '저평가', '공모가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9510</v>
+        <v>9460</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.26%</t>
+          <t>+15.65%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.44</v>
       </c>
       <c r="E5" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="H5" t="n">
         <v>1.58</v>
@@ -886,7 +886,7 @@
         <v>1.14</v>
       </c>
       <c r="O5" t="n">
-        <v>88725666105</v>
+        <v>92171434740</v>
       </c>
       <c r="P5" t="n">
         <v>22500</v>
@@ -895,23 +895,23 @@
         <v>4560</v>
       </c>
       <c r="R5" t="n">
-        <v>152000</v>
+        <v>146000</v>
       </c>
       <c r="S5" t="n">
         <v>-9000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>외인 프로그램 매수 등장과 함께 10000원 안착 및 신고가 돌파에 대한 기대감, 추세 분석.</t>
+          <t>매드업, AI 관련 뉴스 및 외인 프로그램 매수 유입으로 10000원 안착 시도. 신고가 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외인 매수', '신고가', '추세 분석']</t>
+          <t>['AI', '외인 프로그램 매수', '신고가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50400</v>
+        <v>50600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.94%</t>
+          <t>+15.39%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.47</v>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>701</v>
+        <v>156</v>
       </c>
       <c r="H6" t="n">
         <v>14.18</v>
@@ -978,7 +978,7 @@
         <v>13.71</v>
       </c>
       <c r="O6" t="n">
-        <v>153406524325</v>
+        <v>158352557825</v>
       </c>
       <c r="P6" t="n">
         <v>108900</v>
@@ -987,10 +987,10 @@
         <v>18230</v>
       </c>
       <c r="R6" t="n">
-        <v>156000</v>
+        <v>170000</v>
       </c>
       <c r="S6" t="n">
-        <v>-11000</v>
+        <v>-46000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3580</v>
+        <v>6490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.65%</t>
+          <t>+10.94%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.52</v>
+        <v>-0.7</v>
       </c>
       <c r="E7" t="n">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="F7" t="n">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>268</v>
+        <v>570</v>
       </c>
       <c r="H7" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,60 +1055,60 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3265</v>
+        <v>5850</v>
       </c>
       <c r="K7" t="n">
-        <v>3200</v>
+        <v>6000</v>
       </c>
       <c r="L7" t="n">
-        <v>3900</v>
+        <v>6550</v>
       </c>
       <c r="M7" t="n">
-        <v>3185</v>
+        <v>5940</v>
       </c>
       <c r="N7" t="n">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="O7" t="n">
-        <v>193321474153</v>
+        <v>16600447335</v>
       </c>
       <c r="P7" t="n">
-        <v>3900</v>
+        <v>21500</v>
       </c>
       <c r="Q7" t="n">
-        <v>1246</v>
+        <v>2300</v>
       </c>
       <c r="R7" t="n">
-        <v>-840000</v>
+        <v>13000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>긍정적인 단기 수익 언급과 함께 장기 투자 가능성을 질문하는 내용, 투자 경고에 대한 언급.</t>
+          <t>페니트리움바이오, 임상 2a 결과 발표 및 세계폐암학회 참가 예정으로 인한 기대감 형성. 6500원 돌파 시 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['단기 수익', '장기 투자', '투자 경고']</t>
+          <t>['임상 2a', '폐암학회', '6500원']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86300</v>
+        <v>87100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.96%</t>
+          <t>+9.97%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>320</v>
+        <v>184</v>
       </c>
       <c r="F8" t="n">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="G8" t="n">
-        <v>1299</v>
+        <v>666</v>
       </c>
       <c r="H8" t="n">
         <v>23.53</v>
@@ -1162,7 +1162,7 @@
         <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>366978024550</v>
+        <v>408197486350</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1171,23 +1171,23 @@
         <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>519000</v>
+        <v>540000</v>
       </c>
       <c r="S8" t="n">
-        <v>107000</v>
+        <v>169000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>일론 머스크 관련 뉴스와 대규모 투자 소식을 기반으로 한 긍정적인 전망.</t>
+          <t>두산에너빌리티, 일론 머스크 관련 복합화력발전소 뉴스 주목. 외인 매수세 유입되며 상승 기대감 고조.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['일론 머스크', '대미 투자', '가스복합']</t>
+          <t>['복합화력발전소', '일론 머스크', '외인 매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6320</v>
+        <v>3580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.03%</t>
+          <t>+9.65%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.7</v>
+        <v>-0.52</v>
       </c>
       <c r="E9" t="n">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>548</v>
+        <v>288</v>
       </c>
       <c r="H9" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,60 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>5850</v>
+        <v>3265</v>
       </c>
       <c r="K9" t="n">
-        <v>6000</v>
+        <v>3200</v>
       </c>
       <c r="L9" t="n">
-        <v>6550</v>
+        <v>3900</v>
       </c>
       <c r="M9" t="n">
-        <v>5940</v>
+        <v>3185</v>
       </c>
       <c r="N9" t="n">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="O9" t="n">
-        <v>15977173930</v>
+        <v>195981206566</v>
       </c>
       <c r="P9" t="n">
-        <v>21500</v>
+        <v>3900</v>
       </c>
       <c r="Q9" t="n">
-        <v>2300</v>
+        <v>1246</v>
       </c>
       <c r="R9" t="n">
-        <v>-8000</v>
+        <v>-1196000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>페니트리움바이오, 임상 2a 결과 발표 및 세계폐암학회 참가 예정으로 인한 기대감 형성. 6500원 돌파 시 추가 상승 전망.</t>
+          <t>JW신약, 탈모 치료제 관련 언급 있으나 투자 주의 필요. 단기 수익 관찰.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['임상 2a', '폐암학회', '6500원']</t>
+          <t>['탈모', '투자 주의', '단기 수익']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1764000</v>
+        <v>1768000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+7.10%</t>
+          <t>+7.35%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="F10" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G10" t="n">
-        <v>2597</v>
+        <v>2637</v>
       </c>
       <c r="H10" t="n">
         <v>50.5</v>
@@ -1346,7 +1346,7 @@
         <v>50.45</v>
       </c>
       <c r="O10" t="n">
-        <v>4385237957000</v>
+        <v>4743944213000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1355,23 +1355,23 @@
         <v>274000</v>
       </c>
       <c r="R10" t="n">
-        <v>479000</v>
+        <v>537000</v>
       </c>
       <c r="S10" t="n">
-        <v>203000</v>
+        <v>243000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>메모리 재고 감소 및 2차 상승 시작 기대감, 외인/기관 매수 확대에 따른 긍정적 전망.</t>
+          <t>SK하이닉스, 메모리 시장 2차 상승 기대감 속 180만원 돌파 시도. 외인 및 기관 매수 확대 관찰.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['메모리 재고', '외인 매수', '기술적 분석']</t>
+          <t>['메모리', '외인 매수', '기관 매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>214500</v>
+        <v>215500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+6.45%</t>
+          <t>+6.95%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="F11" t="n">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="G11" t="n">
-        <v>1430</v>
+        <v>1456</v>
       </c>
       <c r="H11" t="n">
         <v>29.46</v>
@@ -1438,7 +1438,7 @@
         <v>29.51</v>
       </c>
       <c r="O11" t="n">
-        <v>328638040750</v>
+        <v>337800402250</v>
       </c>
       <c r="P11" t="n">
         <v>438000</v>
@@ -1447,23 +1447,23 @@
         <v>74700</v>
       </c>
       <c r="R11" t="n">
-        <v>306000</v>
+        <v>311000</v>
       </c>
       <c r="S11" t="n">
-        <v>133000</v>
+        <v>140000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>CES 2024 관련 호재와 함께 100만원 목표주가 제시. 빅테크와의 액추에이터 수주 협의 중 소식.</t>
+          <t>모간의 공매도 및 숏커버, LG전자 모터 기술의 로봇 관절 적용 등 호재에 따른 급등세.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['CES', '액추에이터', '수주']</t>
+          <t>['공매도', '숏커버', '로봇 관절']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17880</v>
+        <v>17970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+6.11%</t>
+          <t>+6.65%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G12" t="n">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="H12" t="n">
         <v>10.4</v>
@@ -1530,7 +1530,7 @@
         <v>10.36</v>
       </c>
       <c r="O12" t="n">
-        <v>110729083955</v>
+        <v>117385246150</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1539,10 +1539,10 @@
         <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>340000</v>
+        <v>330000</v>
       </c>
       <c r="S12" t="n">
-        <v>24000</v>
+        <v>39000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>267750</v>
+        <v>8460</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+4.79%</t>
+          <t>+6.42%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>-0.72</v>
       </c>
       <c r="E13" t="n">
-        <v>795</v>
+        <v>77</v>
       </c>
       <c r="F13" t="n">
-        <v>423</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>2152</v>
+        <v>174</v>
       </c>
       <c r="H13" t="n">
-        <v>46.73</v>
+        <v>0.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>255500</v>
+        <v>7950</v>
       </c>
       <c r="K13" t="n">
-        <v>267000</v>
+        <v>8200</v>
       </c>
       <c r="L13" t="n">
-        <v>269000</v>
+        <v>9210</v>
       </c>
       <c r="M13" t="n">
-        <v>264000</v>
+        <v>7980</v>
       </c>
       <c r="N13" t="n">
-        <v>46.71</v>
+        <v>1.32</v>
       </c>
       <c r="O13" t="n">
-        <v>3261256177250</v>
+        <v>98044573210</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>15960</v>
       </c>
       <c r="Q13" t="n">
-        <v>69600</v>
+        <v>3500</v>
       </c>
       <c r="R13" t="n">
-        <v>1309000</v>
+        <v>-10000</v>
       </c>
       <c r="S13" t="n">
-        <v>1097000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 언급과 개인적인 희망사항이 혼재된 게시글들로, 객관적인 분석 근거 부족.</t>
+          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,51 +1647,51 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['미프진', '거래량', '수급']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8300</v>
+        <v>268750</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+4.40%</t>
+          <t>+5.19%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.72</v>
+        <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>84</v>
+        <v>636</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>360</v>
       </c>
       <c r="G14" t="n">
-        <v>179</v>
+        <v>1669</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6</v>
+        <v>46.73</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7950</v>
+        <v>255500</v>
       </c>
       <c r="K14" t="n">
-        <v>8200</v>
+        <v>267000</v>
       </c>
       <c r="L14" t="n">
-        <v>9210</v>
+        <v>269500</v>
       </c>
       <c r="M14" t="n">
-        <v>7980</v>
+        <v>264000</v>
       </c>
       <c r="N14" t="n">
-        <v>1.32</v>
+        <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>96018536220</v>
+        <v>3705990040750</v>
       </c>
       <c r="P14" t="n">
-        <v>15960</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>3500</v>
+        <v>69600</v>
       </c>
       <c r="R14" t="n">
-        <v>26000</v>
+        <v>1534000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1290000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
+          <t>삼성전자, 기술적 반등 및 자사주 매입 기대감 속 27만원 돌파 시도. 개미 매도세 관찰.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['미프진', '거래량', '수급']</t>
+          <t>['자사주 매입', '기술적 반등', '반도체']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13410</v>
+        <v>13430</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.07%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.09</v>
       </c>
       <c r="E15" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F15" t="n">
         <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="H15" t="n">
         <v>1.82</v>
@@ -1806,7 +1806,7 @@
         <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>73940319390</v>
+        <v>76100674165</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1815,7 +1815,7 @@
         <v>1252</v>
       </c>
       <c r="R15" t="n">
-        <v>336000</v>
+        <v>312000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5870</v>
+        <v>5780</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="F16" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G16" t="n">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>17210590800</v>
+        <v>17988951265</v>
       </c>
       <c r="P16" t="n">
         <v>9680</v>
@@ -1907,23 +1907,23 @@
         <v>371</v>
       </c>
       <c r="R16" t="n">
-        <v>-5000</v>
+        <v>-1000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유증 및 전환사채 납입 완료 호재에도 불구하고, 반기 보고서 제출 지연 및 악재성 기사로 인한 하락 우려.</t>
+          <t>계약금, 유증, 전환사채 납입 완료에도 불구하고 반기보고서 지연 및 악재 뉴스 발생.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유증', '반기 보고서', '악재']</t>
+          <t>['반기보고서', '유증', '악재']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6740</v>
+        <v>30300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="E17" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="F17" t="n">
         <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="H17" t="n">
-        <v>16.4</v>
+        <v>49.01</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6710</v>
+        <v>30200</v>
       </c>
       <c r="K17" t="n">
-        <v>6680</v>
+        <v>30350</v>
       </c>
       <c r="L17" t="n">
-        <v>7040</v>
+        <v>30900</v>
       </c>
       <c r="M17" t="n">
-        <v>6600</v>
+        <v>29900</v>
       </c>
       <c r="N17" t="n">
-        <v>15.55</v>
+        <v>24.02</v>
       </c>
       <c r="O17" t="n">
-        <v>12217773245</v>
+        <v>83722516150</v>
       </c>
       <c r="P17" t="n">
-        <v>13000</v>
+        <v>31200</v>
       </c>
       <c r="Q17" t="n">
-        <v>6030</v>
+        <v>21000</v>
       </c>
       <c r="R17" t="n">
-        <v>-57000</v>
+        <v>541000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>161000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>공매도 및 모건스탠리 매도 의혹 제기. 2차 폭락 및 개미 투자자 유입 시 하락 전망. IPO 예정 종목(한화세미텍, 한화로보틱스) 언급.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도', 'IPO', '모건스탠리']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30300</v>
+        <v>6730</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="E18" t="n">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H18" t="n">
-        <v>48.99</v>
+        <v>16.4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>30200</v>
+        <v>6710</v>
       </c>
       <c r="K18" t="n">
-        <v>30350</v>
+        <v>6680</v>
       </c>
       <c r="L18" t="n">
-        <v>30900</v>
+        <v>7040</v>
       </c>
       <c r="M18" t="n">
-        <v>29900</v>
+        <v>6600</v>
       </c>
       <c r="N18" t="n">
-        <v>24.02</v>
+        <v>15.55</v>
       </c>
       <c r="O18" t="n">
-        <v>79874130900</v>
+        <v>12625851420</v>
       </c>
       <c r="P18" t="n">
-        <v>31200</v>
+        <v>13000</v>
       </c>
       <c r="Q18" t="n">
-        <v>21000</v>
+        <v>6030</v>
       </c>
       <c r="R18" t="n">
-        <v>481000</v>
+        <v>-65000</v>
       </c>
       <c r="S18" t="n">
-        <v>113000</v>
+        <v>-1000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
+          <t>공매도 및 모건스탠리 매도 의혹 제기. 2차 폭락 및 개미 투자자 유입 시 하락 전망. IPO 예정 종목(한화세미텍, 한화로보틱스) 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['환율', '반도체', '공매도']</t>
+          <t>['공매도', 'IPO', '모건스탠리']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16090</v>
+        <v>22550</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E19" t="n">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="F19" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G19" t="n">
-        <v>520</v>
+        <v>214</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>16090</v>
+        <v>22500</v>
       </c>
       <c r="K19" t="n">
-        <v>16150</v>
+        <v>23100</v>
       </c>
       <c r="L19" t="n">
-        <v>16480</v>
+        <v>24000</v>
       </c>
       <c r="M19" t="n">
-        <v>15830</v>
+        <v>21500</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O19" t="n">
-        <v>42148599715</v>
+        <v>133127809550</v>
       </c>
       <c r="P19" t="n">
-        <v>19380</v>
+        <v>50600</v>
       </c>
       <c r="Q19" t="n">
-        <v>3200</v>
+        <v>9070</v>
       </c>
       <c r="R19" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>금호건설, 반도체 산업 연관 가능성 언급에도 불구하고 주가 부진 및 차트 하향 추세 관찰. 투자 심리 불확실.</t>
+          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반도체', '산단', '주가']</t>
+          <t>['로봇주', '신사업', '2연상']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22350</v>
+        <v>16110</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="G20" t="n">
-        <v>200</v>
+        <v>560</v>
       </c>
       <c r="H20" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>22500</v>
+        <v>16090</v>
       </c>
       <c r="K20" t="n">
-        <v>23100</v>
+        <v>16150</v>
       </c>
       <c r="L20" t="n">
-        <v>24000</v>
+        <v>16480</v>
       </c>
       <c r="M20" t="n">
-        <v>21500</v>
+        <v>15830</v>
       </c>
       <c r="N20" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>131733327025</v>
+        <v>43998164990</v>
       </c>
       <c r="P20" t="n">
-        <v>50600</v>
+        <v>19380</v>
       </c>
       <c r="Q20" t="n">
-        <v>9070</v>
+        <v>3200</v>
       </c>
       <c r="R20" t="n">
-        <v>9000</v>
+        <v>72000</v>
       </c>
       <c r="S20" t="n">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
+          <t>금호건설, 반도체 산업 연관 가능성 언급에도 불구하고 주가 부진 및 차트 하향 추세 관찰. 투자 심리 불확실.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '2연상']</t>
+          <t>['반도체', '산단', '주가']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10120</v>
+        <v>10280</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.60%</t>
+          <t>-1.06%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.05</v>
       </c>
       <c r="E21" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G21" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H21" t="n">
         <v>5.75</v>
@@ -2358,7 +2358,7 @@
         <v>5.7</v>
       </c>
       <c r="O21" t="n">
-        <v>19846267585</v>
+        <v>20283509785</v>
       </c>
       <c r="P21" t="n">
         <v>15640</v>
@@ -2367,7 +2367,7 @@
         <v>5470</v>
       </c>
       <c r="R21" t="n">
-        <v>-120000</v>
+        <v>-122000</v>
       </c>
       <c r="S21" t="n">
         <v>-2000</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5500</v>
+        <v>5510</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.68%</t>
+          <t>-3.50%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>84</v>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G22" t="n">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="H22" t="n">
         <v>4.81</v>
@@ -2450,7 +2450,7 @@
         <v>4.39</v>
       </c>
       <c r="O22" t="n">
-        <v>20732557755</v>
+        <v>21326612740</v>
       </c>
       <c r="P22" t="n">
         <v>10480</v>
@@ -2459,7 +2459,7 @@
         <v>3150</v>
       </c>
       <c r="R22" t="n">
-        <v>-432000</v>
+        <v>-473000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G2" t="n">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2" t="n">
         <v>0.16</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>779882249025</v>
+        <v>780327270875</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>‘CART 혈압계’의 건강보험 급여 등재 및 세계 최초 반지 혈압계 기술력에 기반한 급등 전망.</t>
+          <t>세계 최초 반지 혈압계 건강보험 급여 등재 및 주가 평가액 대비 저평가 부각. 주포의 물량 확보 의지 확인.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['CART 혈압계', '건강보험 급여', '세계 최초']</t>
+          <t>['반지 혈압계', '급여 등재', '주포']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10070</v>
+        <v>10160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+20.60%</t>
+          <t>+21.68%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="F3" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G3" t="n">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="H3" t="n">
         <v>0.21</v>
@@ -702,7 +702,7 @@
         <v>0.25</v>
       </c>
       <c r="O3" t="n">
-        <v>147600024660</v>
+        <v>169348735940</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼미금속, 미국 초대형 가스발전 열병합 사업 수주 뉴스로 급등. 테마 기대감 형성.</t>
+          <t>대미 투자 1호 (가스터빈) 관련 뉴스 부각. 수급 불안 및 매물 폭탄 경계.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['가스터빈', '가스발전', '테마']</t>
+          <t>['가스터빈', '대미 투자', '수급 불안']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18590</v>
+        <v>18170</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+18.03%</t>
+          <t>+15.37%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.37</v>
       </c>
       <c r="E4" t="n">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G4" t="n">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="H4" t="n">
         <v>1.08</v>
@@ -794,7 +794,7 @@
         <v>0.71</v>
       </c>
       <c r="O4" t="n">
-        <v>119482542980</v>
+        <v>129481081795</v>
       </c>
       <c r="P4" t="n">
         <v>34650</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>레메디, 기술력 부각 및 공모가 대비 저평가 논란 속 18500원 돌파 시도. 텐배거 기대감 형성.</t>
+          <t>기술력 부각 및 18500원 돌파 시도. 공모가 대비 저평가 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['기술력', '저평가', '공모가']</t>
+          <t>['기술력', '공모가', '개미 털기']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,79 +839,79 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>매드업</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9460</v>
+        <v>50200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+15.65%</t>
+          <t>+14.48%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="E5" t="n">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="H5" t="n">
-        <v>1.58</v>
+        <v>14.18</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8180</v>
+        <v>43850</v>
       </c>
       <c r="K5" t="n">
-        <v>8200</v>
+        <v>45650</v>
       </c>
       <c r="L5" t="n">
-        <v>10390</v>
+        <v>55000</v>
       </c>
       <c r="M5" t="n">
-        <v>8120</v>
+        <v>45650</v>
       </c>
       <c r="N5" t="n">
-        <v>1.14</v>
+        <v>13.71</v>
       </c>
       <c r="O5" t="n">
-        <v>92171434740</v>
+        <v>168151044825</v>
       </c>
       <c r="P5" t="n">
-        <v>22500</v>
+        <v>108900</v>
       </c>
       <c r="Q5" t="n">
-        <v>4560</v>
+        <v>18230</v>
       </c>
       <c r="R5" t="n">
-        <v>146000</v>
+        <v>170000</v>
       </c>
       <c r="S5" t="n">
-        <v>-9000</v>
+        <v>-46000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>매드업, AI 관련 뉴스 및 외인 프로그램 매수 유입으로 10000원 안착 시도. 신고가 기대감.</t>
+          <t>공매도 감소와 단기 급등에 대한 언급, 7월부터의 매수 독려 및 기술적 저항대 분석.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI', '외인 프로그램 매수', '신고가']</t>
+          <t>['공매도', '기술적 분석', '수주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,91 +919,91 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0039P0</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>매드업</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50600</v>
+        <v>9300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+15.39%</t>
+          <t>+13.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H6" t="n">
-        <v>14.18</v>
+        <v>1.58</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>43850</v>
+        <v>8180</v>
       </c>
       <c r="K6" t="n">
-        <v>45650</v>
+        <v>8200</v>
       </c>
       <c r="L6" t="n">
-        <v>55000</v>
+        <v>10390</v>
       </c>
       <c r="M6" t="n">
-        <v>45650</v>
+        <v>8120</v>
       </c>
       <c r="N6" t="n">
-        <v>13.71</v>
+        <v>1.14</v>
       </c>
       <c r="O6" t="n">
-        <v>158352557825</v>
+        <v>96634575130</v>
       </c>
       <c r="P6" t="n">
-        <v>108900</v>
+        <v>22500</v>
       </c>
       <c r="Q6" t="n">
-        <v>18230</v>
+        <v>4560</v>
       </c>
       <c r="R6" t="n">
-        <v>170000</v>
+        <v>146000</v>
       </c>
       <c r="S6" t="n">
-        <v>-46000</v>
+        <v>-9000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>공매도 감소와 단기 급등에 대한 언급, 7월부터의 매수 독려 및 기술적 저항대 분석.</t>
+          <t>AI 관련 뉴스 부각 및 10000원 안착 기대. 계단식 하락 패턴 관찰.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공매도', '기술적 분석', '수주']</t>
+          <t>['AI 셀럽', '계단식 하락', '매물벽']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,196 +1011,196 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>0039P0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6490</v>
+        <v>87900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+10.94%</t>
+          <t>+10.98%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.7</v>
+        <v>-0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>103</v>
+        <v>257</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="G7" t="n">
-        <v>570</v>
+        <v>973</v>
       </c>
       <c r="H7" t="n">
-        <v>1.61</v>
+        <v>23.53</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5850</v>
+        <v>79200</v>
       </c>
       <c r="K7" t="n">
-        <v>6000</v>
+        <v>80200</v>
       </c>
       <c r="L7" t="n">
-        <v>6550</v>
+        <v>89400</v>
       </c>
       <c r="M7" t="n">
-        <v>5940</v>
+        <v>79000</v>
       </c>
       <c r="N7" t="n">
-        <v>2.31</v>
+        <v>23.61</v>
       </c>
       <c r="O7" t="n">
-        <v>16600447335</v>
+        <v>513692190050</v>
       </c>
       <c r="P7" t="n">
-        <v>21500</v>
+        <v>139200</v>
       </c>
       <c r="Q7" t="n">
-        <v>2300</v>
+        <v>57000</v>
       </c>
       <c r="R7" t="n">
-        <v>13000</v>
+        <v>540000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>169000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>페니트리움바이오, 임상 2a 결과 발표 및 세계폐암학회 참가 예정으로 인한 기대감 형성. 6500원 돌파 시 추가 상승 전망.</t>
+          <t>대미 투자 1호 (6.3GW 가스복합) 확정 및 일론 머스크 관련 뉴스 부각. 하반기 본격 수주 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['임상 2a', '폐암학회', '6500원']</t>
+          <t>['대미 투자', '일론 머스크', '복합화력발전']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>87100</v>
+        <v>6460</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.97%</t>
+          <t>+10.43%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.08</v>
+        <v>-0.7</v>
       </c>
       <c r="E8" t="n">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="F8" t="n">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="G8" t="n">
-        <v>666</v>
+        <v>618</v>
       </c>
       <c r="H8" t="n">
-        <v>23.53</v>
+        <v>1.61</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>79200</v>
+        <v>5850</v>
       </c>
       <c r="K8" t="n">
-        <v>80200</v>
+        <v>6000</v>
       </c>
       <c r="L8" t="n">
-        <v>87800</v>
+        <v>6550</v>
       </c>
       <c r="M8" t="n">
-        <v>79000</v>
+        <v>5940</v>
       </c>
       <c r="N8" t="n">
-        <v>23.61</v>
+        <v>2.31</v>
       </c>
       <c r="O8" t="n">
-        <v>408197486350</v>
+        <v>17551109715</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>21500</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>2300</v>
       </c>
       <c r="R8" t="n">
-        <v>540000</v>
+        <v>13000</v>
       </c>
       <c r="S8" t="n">
-        <v>169000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 일론 머스크 관련 복합화력발전소 뉴스 주목. 외인 매수세 유입되며 상승 기대감 고조.</t>
+          <t>페니트리움바이오, 임상 2a 결과 발표 및 세계폐암학회 참가 예정으로 인한 기대감 형성. 6500원 돌파 시 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['복합화력발전소', '일론 머스크', '외인 매수']</t>
+          <t>['임상 2a', '폐암학회', '6500원']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3580</v>
+        <v>3570</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+9.65%</t>
+          <t>+9.34%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.52</v>
       </c>
       <c r="E9" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G9" t="n">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="H9" t="n">
         <v>1.25</v>
@@ -1254,7 +1254,7 @@
         <v>1.77</v>
       </c>
       <c r="O9" t="n">
-        <v>195981206566</v>
+        <v>204245889608</v>
       </c>
       <c r="P9" t="n">
         <v>3900</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>JW신약, 탈모 치료제 관련 언급 있으나 투자 주의 필요. 단기 수익 관찰.</t>
+          <t>투자경고/위험에도 불구하고 상승 가능성 언급. 외국인 매도세 지속 관찰.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['탈모', '투자 주의', '단기 수익']</t>
+          <t>['투자경고', '외국인 매도', '장투']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1768000</v>
+        <v>18410</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+7.35%</t>
+          <t>+9.26%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>795</v>
+        <v>134</v>
       </c>
       <c r="F10" t="n">
-        <v>463</v>
+        <v>76</v>
       </c>
       <c r="G10" t="n">
-        <v>2637</v>
+        <v>433</v>
       </c>
       <c r="H10" t="n">
-        <v>50.5</v>
+        <v>10.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1647000</v>
+        <v>16850</v>
       </c>
       <c r="K10" t="n">
-        <v>1737000</v>
+        <v>16870</v>
       </c>
       <c r="L10" t="n">
-        <v>1778000</v>
+        <v>18550</v>
       </c>
       <c r="M10" t="n">
-        <v>1733000</v>
+        <v>16590</v>
       </c>
       <c r="N10" t="n">
-        <v>50.45</v>
+        <v>10.36</v>
       </c>
       <c r="O10" t="n">
-        <v>4743944213000</v>
+        <v>161507035845</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>274000</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>537000</v>
+        <v>330000</v>
       </c>
       <c r="S10" t="n">
-        <v>243000</v>
+        <v>39000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SK하이닉스, 메모리 시장 2차 상승 기대감 속 180만원 돌파 시도. 외인 및 기관 매수 확대 관찰.</t>
+          <t>러우전쟁 종전 분위기 및 가덕도 신공항 공사 본격화 기대감. 대미 원전 수출 모멘텀 부각.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['메모리', '외인 매수', '기관 매수']</t>
+          <t>['가덕도 신공항', '원전 수출', '러우전쟁']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>215500</v>
+        <v>1775000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+6.95%</t>
+          <t>+7.77%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>514</v>
+        <v>791</v>
       </c>
       <c r="F11" t="n">
-        <v>265</v>
+        <v>457</v>
       </c>
       <c r="G11" t="n">
-        <v>1456</v>
+        <v>2486</v>
       </c>
       <c r="H11" t="n">
-        <v>29.46</v>
+        <v>50.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>201500</v>
+        <v>1647000</v>
       </c>
       <c r="K11" t="n">
-        <v>212500</v>
+        <v>1737000</v>
       </c>
       <c r="L11" t="n">
-        <v>225500</v>
+        <v>1783000</v>
       </c>
       <c r="M11" t="n">
-        <v>212500</v>
+        <v>1733000</v>
       </c>
       <c r="N11" t="n">
-        <v>29.51</v>
+        <v>50.45</v>
       </c>
       <c r="O11" t="n">
-        <v>337800402250</v>
+        <v>5468052143500</v>
       </c>
       <c r="P11" t="n">
-        <v>438000</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>74700</v>
+        <v>274000</v>
       </c>
       <c r="R11" t="n">
-        <v>311000</v>
+        <v>537000</v>
       </c>
       <c r="S11" t="n">
-        <v>140000</v>
+        <v>243000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>모간의 공매도 및 숏커버, LG전자 모터 기술의 로봇 관절 적용 등 호재에 따른 급등세.</t>
+          <t>200만원 돌파 기대감 속 단기 매물 저항선 도달. 사모펀드 코스피 유입 및 숏커버링/숏스퀴즈 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '숏커버', '로봇 관절']</t>
+          <t>['숏커버링', '매물 저항선', '사모펀드']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17970</v>
+        <v>213500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+6.65%</t>
+          <t>+5.96%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>562</v>
       </c>
       <c r="F12" t="n">
-        <v>51</v>
+        <v>283</v>
       </c>
       <c r="G12" t="n">
-        <v>291</v>
+        <v>1517</v>
       </c>
       <c r="H12" t="n">
-        <v>10.4</v>
+        <v>29.46</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,60 +1515,60 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16850</v>
+        <v>201500</v>
       </c>
       <c r="K12" t="n">
-        <v>16870</v>
+        <v>212500</v>
       </c>
       <c r="L12" t="n">
-        <v>17990</v>
+        <v>225500</v>
       </c>
       <c r="M12" t="n">
-        <v>16590</v>
+        <v>212500</v>
       </c>
       <c r="N12" t="n">
-        <v>10.36</v>
+        <v>29.51</v>
       </c>
       <c r="O12" t="n">
-        <v>117385246150</v>
+        <v>354925281750</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>438000</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>74700</v>
       </c>
       <c r="R12" t="n">
-        <v>330000</v>
+        <v>311000</v>
       </c>
       <c r="S12" t="n">
-        <v>39000</v>
+        <v>140000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>러우전쟁 종전 기대감 속 건설주 동반 상승. 5% 수익 실현.</t>
+          <t>LG전자, CES 2024 관련 빅테크와 액추에이터 수주 협의 소식 및 60년 모터 기술 기반 로봇 관절 사업 부각. 주가 급등 및 상한가 기록.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['러우전쟁', '건설주', '종전']</t>
+          <t>['액추에이터', '수주', '로봇']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8460</v>
+        <v>8420</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+6.42%</t>
+          <t>+5.91%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.72</v>
       </c>
       <c r="E13" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="H13" t="n">
         <v>0.6</v>
@@ -1622,7 +1622,7 @@
         <v>1.32</v>
       </c>
       <c r="O13" t="n">
-        <v>98044573210</v>
+        <v>101482085065</v>
       </c>
       <c r="P13" t="n">
         <v>15960</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>268750</v>
+        <v>269000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+5.19%</t>
+          <t>+5.28%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F14" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G14" t="n">
-        <v>1669</v>
+        <v>1968</v>
       </c>
       <c r="H14" t="n">
         <v>46.73</v>
@@ -1705,7 +1705,7 @@
         <v>267000</v>
       </c>
       <c r="L14" t="n">
-        <v>269500</v>
+        <v>270000</v>
       </c>
       <c r="M14" t="n">
         <v>264000</v>
@@ -1714,7 +1714,7 @@
         <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>3705990040750</v>
+        <v>4267250674250</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼성전자, 기술적 반등 및 자사주 매입 기대감 속 27만원 돌파 시도. 개미 매도세 관찰.</t>
+          <t>미국장 휴장 속 매물 소화 및 단기 전고점 도달 가능성 언급. 개미 폭풍 매도세 관찰.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주 매입', '기술적 반등', '반도체']</t>
+          <t>['단기 전고점', '매물 소화', '수급 동향']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13430</v>
+        <v>13400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.23%</t>
+          <t>+3.00%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.09</v>
       </c>
       <c r="E15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F15" t="n">
         <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>434</v>
+        <v>475</v>
       </c>
       <c r="H15" t="n">
         <v>1.82</v>
@@ -1806,7 +1806,7 @@
         <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>76100674165</v>
+        <v>80240821860</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5780</v>
+        <v>10570</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E16" t="n">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>369</v>
+        <v>242</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,47 +1883,47 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>5740</v>
+        <v>10390</v>
       </c>
       <c r="K16" t="n">
-        <v>5250</v>
+        <v>10050</v>
       </c>
       <c r="L16" t="n">
-        <v>6790</v>
+        <v>11000</v>
       </c>
       <c r="M16" t="n">
-        <v>5000</v>
+        <v>9770</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O16" t="n">
-        <v>17988951265</v>
+        <v>23226433000</v>
       </c>
       <c r="P16" t="n">
-        <v>9680</v>
+        <v>15640</v>
       </c>
       <c r="Q16" t="n">
-        <v>371</v>
+        <v>5470</v>
       </c>
       <c r="R16" t="n">
-        <v>-1000</v>
+        <v>-122000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>계약금, 유증, 전환사채 납입 완료에도 불구하고 반기보고서 지연 및 악재 뉴스 발생.</t>
+          <t>급등 기대감 및 2백만원 목표가 제시. 공매도 소굴이라는 부정적 의견과 함께 매집 및 순환매 기대. 금일 12층 목표.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['반기보고서', '유증', '악재']</t>
+          <t>['급등', '공매도', '순환매']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
@@ -1947,27 +1947,27 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30300</v>
+        <v>30250</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.4</v>
       </c>
       <c r="E17" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="H17" t="n">
-        <v>49.01</v>
+        <v>49.09</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>24.02</v>
       </c>
       <c r="O17" t="n">
-        <v>83722516150</v>
+        <v>93259852575</v>
       </c>
       <c r="P17" t="n">
         <v>31200</v>
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6730</v>
+        <v>16110</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="G18" t="n">
-        <v>132</v>
+        <v>641</v>
       </c>
       <c r="H18" t="n">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,130 +2067,130 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6710</v>
+        <v>16090</v>
       </c>
       <c r="K18" t="n">
-        <v>6680</v>
+        <v>16150</v>
       </c>
       <c r="L18" t="n">
-        <v>7040</v>
+        <v>16480</v>
       </c>
       <c r="M18" t="n">
-        <v>6600</v>
+        <v>15830</v>
       </c>
       <c r="N18" t="n">
-        <v>15.55</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>12625851420</v>
+        <v>47480454430</v>
       </c>
       <c r="P18" t="n">
-        <v>13000</v>
+        <v>19380</v>
       </c>
       <c r="Q18" t="n">
-        <v>6030</v>
+        <v>3200</v>
       </c>
       <c r="R18" t="n">
-        <v>-65000</v>
+        <v>72000</v>
       </c>
       <c r="S18" t="n">
         <v>-1000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>공매도 및 모건스탠리 매도 의혹 제기. 2차 폭락 및 개미 투자자 유입 시 하락 전망. IPO 예정 종목(한화세미텍, 한화로보틱스) 언급.</t>
+          <t>9월 메가특구법 발의 및 호남 반도체 산단 관련 기대감. 주포의 매집 정황 관찰.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['공매도', 'IPO', '모건스탠리']</t>
+          <t>['메가특구법', '반도체 산단', '주포']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22550</v>
+        <v>6670</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="E19" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="F19" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>214</v>
+        <v>148</v>
       </c>
       <c r="H19" t="n">
-        <v>5.6</v>
+        <v>16.4</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>22500</v>
+        <v>6710</v>
       </c>
       <c r="K19" t="n">
-        <v>23100</v>
+        <v>6680</v>
       </c>
       <c r="L19" t="n">
-        <v>24000</v>
+        <v>7040</v>
       </c>
       <c r="M19" t="n">
-        <v>21500</v>
+        <v>6600</v>
       </c>
       <c r="N19" t="n">
-        <v>4.98</v>
+        <v>15.55</v>
       </c>
       <c r="O19" t="n">
-        <v>133127809550</v>
+        <v>13641459855</v>
       </c>
       <c r="P19" t="n">
-        <v>50600</v>
+        <v>13000</v>
       </c>
       <c r="Q19" t="n">
-        <v>9070</v>
+        <v>6030</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>-65000</v>
       </c>
       <c r="S19" t="n">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
+          <t>공매도 및 모건스탠리 매도 의혹 제기. 2차 폭락 및 개미 투자자 유입 시 하락 전망. IPO 예정 종목(한화세미텍, 한화로보틱스) 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '2연상']</t>
+          <t>['공매도', 'IPO', '모건스탠리']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16110</v>
+        <v>22350</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E20" t="n">
+        <v>86</v>
+      </c>
+      <c r="F20" t="n">
+        <v>62</v>
+      </c>
+      <c r="G20" t="n">
+        <v>239</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>22500</v>
+      </c>
+      <c r="K20" t="n">
+        <v>23100</v>
+      </c>
+      <c r="L20" t="n">
+        <v>24000</v>
+      </c>
+      <c r="M20" t="n">
+        <v>21500</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="O20" t="n">
+        <v>137568789525</v>
+      </c>
+      <c r="P20" t="n">
+        <v>50600</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>9070</v>
+      </c>
+      <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="n">
-        <v>109</v>
-      </c>
-      <c r="F20" t="n">
-        <v>68</v>
-      </c>
-      <c r="G20" t="n">
-        <v>560</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>16090</v>
-      </c>
-      <c r="K20" t="n">
-        <v>16150</v>
-      </c>
-      <c r="L20" t="n">
-        <v>16480</v>
-      </c>
-      <c r="M20" t="n">
-        <v>15830</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>43998164990</v>
-      </c>
-      <c r="P20" t="n">
-        <v>19380</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3200</v>
-      </c>
-      <c r="R20" t="n">
-        <v>72000</v>
-      </c>
       <c r="S20" t="n">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>금호건설, 반도체 산업 연관 가능성 언급에도 불구하고 주가 부진 및 차트 하향 추세 관찰. 투자 심리 불확실.</t>
+          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['반도체', '산단', '주가']</t>
+          <t>['로봇주', '신사업', '2연상']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10280</v>
+        <v>5660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="F21" t="n">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="G21" t="n">
-        <v>220</v>
+        <v>389</v>
       </c>
       <c r="H21" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,47 +2343,47 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>10390</v>
+        <v>5740</v>
       </c>
       <c r="K21" t="n">
-        <v>10050</v>
+        <v>5250</v>
       </c>
       <c r="L21" t="n">
-        <v>11000</v>
+        <v>6790</v>
       </c>
       <c r="M21" t="n">
-        <v>9770</v>
+        <v>5000</v>
       </c>
       <c r="N21" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>20283509785</v>
+        <v>18832761640</v>
       </c>
       <c r="P21" t="n">
-        <v>15640</v>
+        <v>9680</v>
       </c>
       <c r="Q21" t="n">
-        <v>5470</v>
+        <v>371</v>
       </c>
       <c r="R21" t="n">
-        <v>-122000</v>
+        <v>-1000</v>
       </c>
       <c r="S21" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>급등 기대감 및 2백만원 목표가 제시. 공매도 소굴이라는 부정적 의견과 함께 매집 및 순환매 기대. 금일 12층 목표.</t>
+          <t>계약금, 유증, 전환사채 납입 완료. 조선비즈 악재 기사 발생 및 하한가 가능성 언급. 반기보고서 제출 지연 우려. 인수 관련 긍정적/부정적 의견 혼재.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['급등', '공매도', '순환매']</t>
+          <t>['전환사채', '반기보고서', '인수']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5510</v>
+        <v>5480</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.50%</t>
+          <t>-4.03%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.42</v>
       </c>
       <c r="E22" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F22" t="n">
         <v>55</v>
       </c>
       <c r="G22" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H22" t="n">
         <v>4.81</v>
@@ -2450,7 +2450,7 @@
         <v>4.39</v>
       </c>
       <c r="O22" t="n">
-        <v>21326612740</v>
+        <v>22518986310</v>
       </c>
       <c r="P22" t="n">
         <v>10480</v>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,60 +563,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33050</v>
+        <v>142300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+8.18%</t>
+          <t>+16.35%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="E2" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>155</v>
+        <v>96</v>
       </c>
       <c r="H2" t="n">
-        <v>0.23</v>
+        <v>13.33</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>30550</v>
+        <v>122300</v>
       </c>
       <c r="K2" t="n">
-        <v>31650</v>
+        <v>129400</v>
       </c>
       <c r="L2" t="n">
-        <v>33600</v>
+        <v>142300</v>
       </c>
       <c r="M2" t="n">
-        <v>31350</v>
+        <v>128100</v>
       </c>
       <c r="N2" t="n">
-        <v>0.16</v>
+        <v>13.22</v>
       </c>
       <c r="O2" t="n">
-        <v>71111568425</v>
+        <v>52060871700</v>
       </c>
       <c r="P2" t="n">
-        <v>33600</v>
+        <v>198000</v>
       </c>
       <c r="Q2" t="n">
-        <v>8200</v>
+        <v>77100</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>정부 지분 공시 및 세계 최초 반지형 웨어러블 기기 개발 언급. 단기 변동성 및 주의 요구.</t>
+          <t>미국 원전 8기 건설 관련 대형 수주 기대감. 웨스팅하우스 설계 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['웨어러블', '공시', '신규주']</t>
+          <t>['원전', '수주', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,67 +648,67 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>052690</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>90800</v>
+        <v>33000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+3.30%</t>
+          <t>+8.02%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="F3" t="n">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>1304</v>
+        <v>187</v>
       </c>
       <c r="H3" t="n">
-        <v>23.63</v>
+        <v>0.23</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>87900</v>
+        <v>30550</v>
       </c>
       <c r="K3" t="n">
-        <v>91200</v>
+        <v>31650</v>
       </c>
       <c r="L3" t="n">
-        <v>91700</v>
+        <v>34600</v>
       </c>
       <c r="M3" t="n">
-        <v>90200</v>
+        <v>31350</v>
       </c>
       <c r="N3" t="n">
-        <v>23.53</v>
+        <v>0.16</v>
       </c>
       <c r="O3" t="n">
-        <v>32339180700</v>
+        <v>209947806850</v>
       </c>
       <c r="P3" t="n">
-        <v>139200</v>
+        <v>34600</v>
       </c>
       <c r="Q3" t="n">
-        <v>57000</v>
+        <v>8200</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,20 +718,20 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>텍사스 발전 사업 관련 원전 8기 수주 기대감 고조. SMR 기술력 부각 및 대규모 투자 유치 가능성.</t>
+          <t>정부 지분 공시 및 신규주로서의 기대감. 주가 조작 의혹 및 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '투자']</t>
+          <t>['신규주', '지분', '주포']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>271500</v>
+        <v>93500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>+6.37%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>655</v>
+        <v>198</v>
       </c>
       <c r="F4" t="n">
-        <v>382</v>
+        <v>141</v>
       </c>
       <c r="G4" t="n">
-        <v>3183</v>
+        <v>1401</v>
       </c>
       <c r="H4" t="n">
-        <v>46.79</v>
+        <v>23.63</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>270000</v>
+        <v>87900</v>
       </c>
       <c r="K4" t="n">
-        <v>272000</v>
+        <v>91200</v>
       </c>
       <c r="L4" t="n">
-        <v>272500</v>
+        <v>93500</v>
       </c>
       <c r="M4" t="n">
-        <v>270500</v>
+        <v>90200</v>
       </c>
       <c r="N4" t="n">
-        <v>46.73</v>
+        <v>23.53</v>
       </c>
       <c r="O4" t="n">
-        <v>90199037500</v>
+        <v>118519584400</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q4" t="n">
-        <v>69600</v>
+        <v>57000</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,20 +810,20 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>야간 선물 상승 및 반도체 선물 급등 속 자사주 매수 신청 확인. 메모리 재고 부족 심화 전망.</t>
+          <t>텍사스 발전 사업 관련 원전 8기 수주 기대감 고조. SMR 기술력 부각 및 대규모 투자 유치 가능성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '자사주']</t>
+          <t>['원전', 'SMR', '투자']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1791000</v>
+        <v>1794000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>755</v>
+        <v>798</v>
       </c>
       <c r="F5" t="n">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="G5" t="n">
-        <v>3368</v>
+        <v>2972</v>
       </c>
       <c r="H5" t="n">
         <v>50.63</v>
@@ -877,16 +877,16 @@
         <v>1799000</v>
       </c>
       <c r="L5" t="n">
-        <v>1799000</v>
+        <v>1800000</v>
       </c>
       <c r="M5" t="n">
-        <v>1784000</v>
+        <v>1777000</v>
       </c>
       <c r="N5" t="n">
         <v>50.5</v>
       </c>
       <c r="O5" t="n">
-        <v>172326340000</v>
+        <v>469178508000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>야간 선물 상승에 따른 주가 상승 기대감 형성. BNK증권 연구원 관련 부정적 언급.</t>
+          <t>야간 선물 상승에 따른 SK하이닉스 주가 상승 기대. 190만원 돌파 및 200만원 터치 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '전망']</t>
+          <t>['야간선물', '전망', '추세']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -925,6 +925,98 @@
       <c r="Z5" t="inlineStr">
         <is>
           <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>270000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E6" t="n">
+        <v>701</v>
+      </c>
+      <c r="F6" t="n">
+        <v>409</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3253</v>
+      </c>
+      <c r="H6" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>270000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>272000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>272500</v>
+      </c>
+      <c r="M6" t="n">
+        <v>269000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="O6" t="n">
+        <v>268236231000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>69600</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>야간 선물 상승 및 반도체 선물 급등 속 자사주 매수 신청 확인. 메모리 재고 부족 심화 전망.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['반도체', '선물', '자사주']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>101</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>005930</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>142300</v>
+        <v>34800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+16.35%</t>
+          <t>+13.91%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="G2" t="n">
-        <v>96</v>
+        <v>236</v>
       </c>
       <c r="H2" t="n">
-        <v>13.33</v>
+        <v>0.23</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>122300</v>
+        <v>30550</v>
       </c>
       <c r="K2" t="n">
-        <v>129400</v>
+        <v>31650</v>
       </c>
       <c r="L2" t="n">
-        <v>142300</v>
+        <v>34800</v>
       </c>
       <c r="M2" t="n">
-        <v>128100</v>
+        <v>31350</v>
       </c>
       <c r="N2" t="n">
-        <v>13.22</v>
+        <v>0.16</v>
       </c>
       <c r="O2" t="n">
-        <v>52060871700</v>
+        <v>287011422325</v>
       </c>
       <c r="P2" t="n">
-        <v>198000</v>
+        <v>34800</v>
       </c>
       <c r="Q2" t="n">
-        <v>77100</v>
+        <v>8200</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-33000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 원전 8기 건설 관련 대형 수주 기대감. 웨스팅하우스 설계 관련 언급.</t>
+          <t>정부 지분 공시 및 비교군 없는 세계 최초 기술 언급. 주가 부양 의지 및 신규주 특성 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['원전', '수주', '웨스팅하우스']</t>
+          <t>['신규주', '정부지분', '기술']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33000</v>
+        <v>136900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+8.02%</t>
+          <t>+11.94%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="E3" t="n">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>187</v>
+        <v>95</v>
       </c>
       <c r="H3" t="n">
-        <v>0.23</v>
+        <v>13.33</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>30550</v>
+        <v>122300</v>
       </c>
       <c r="K3" t="n">
-        <v>31650</v>
+        <v>129400</v>
       </c>
       <c r="L3" t="n">
-        <v>34600</v>
+        <v>143100</v>
       </c>
       <c r="M3" t="n">
-        <v>31350</v>
+        <v>128100</v>
       </c>
       <c r="N3" t="n">
-        <v>0.16</v>
+        <v>13.22</v>
       </c>
       <c r="O3" t="n">
-        <v>209947806850</v>
+        <v>80610303100</v>
       </c>
       <c r="P3" t="n">
-        <v>34600</v>
+        <v>198000</v>
       </c>
       <c r="Q3" t="n">
-        <v>8200</v>
+        <v>77100</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-62000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부 지분 공시 및 신규주로서의 기대감. 주가 조작 의혹 및 단기 급등 가능성 언급.</t>
+          <t>미국 원전 8기 건설(260조 규모) 수주 기대감. 웨스팅하우스 설계와의 연관성 및 신사업 진출 재료 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['신규주', '지분', '주포']</t>
+          <t>['원전', '수주', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>052690</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93500</v>
+        <v>11880</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+6.37%</t>
+          <t>+8.79%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="E4" t="n">
-        <v>198</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>141</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>1401</v>
+        <v>137</v>
       </c>
       <c r="H4" t="n">
-        <v>23.63</v>
+        <v>5.42</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>87900</v>
+        <v>10920</v>
       </c>
       <c r="K4" t="n">
-        <v>91200</v>
+        <v>11300</v>
       </c>
       <c r="L4" t="n">
-        <v>93500</v>
+        <v>12700</v>
       </c>
       <c r="M4" t="n">
-        <v>90200</v>
+        <v>11050</v>
       </c>
       <c r="N4" t="n">
-        <v>23.53</v>
+        <v>5.53</v>
       </c>
       <c r="O4" t="n">
-        <v>118519584400</v>
+        <v>59729969995</v>
       </c>
       <c r="P4" t="n">
-        <v>139200</v>
+        <v>30200</v>
       </c>
       <c r="Q4" t="n">
-        <v>57000</v>
+        <v>3540</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-249000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>텍사스 발전 사업 관련 원전 8기 수주 기대감 고조. SMR 기술력 부각 및 대규모 투자 유치 가능성.</t>
+          <t>원전 섹터 전반의 상승세에 따른 기대감. 프랑스와의 원자력 협정 및 공매도 상환 압박 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '투자']</t>
+          <t>['원전', '협정', '공매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1794000</v>
+        <v>19530</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>+6.08%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>798</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>426</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>2972</v>
+        <v>155</v>
       </c>
       <c r="H5" t="n">
-        <v>50.63</v>
+        <v>10.47</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1783000</v>
+        <v>18410</v>
       </c>
       <c r="K5" t="n">
-        <v>1799000</v>
+        <v>18800</v>
       </c>
       <c r="L5" t="n">
-        <v>1800000</v>
+        <v>20200</v>
       </c>
       <c r="M5" t="n">
-        <v>1777000</v>
+        <v>18480</v>
       </c>
       <c r="N5" t="n">
-        <v>50.5</v>
+        <v>10.4</v>
       </c>
       <c r="O5" t="n">
-        <v>469178508000</v>
+        <v>116752892720</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q5" t="n">
-        <v>274000</v>
+        <v>3320</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-133000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>야간 선물 상승에 따른 SK하이닉스 주가 상승 기대. 190만원 돌파 및 200만원 터치 가능성 언급.</t>
+          <t>신사업 재료 발표 기대감 속 원전 관련 긍정적 언급. 하지만 아직 확정된 내용은 없는 상황.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['야간선물', '전망', '추세']</t>
+          <t>['신사업', '원전', '재료']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>270000</v>
+        <v>91900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+4.55%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="n">
-        <v>701</v>
+        <v>225</v>
       </c>
       <c r="F6" t="n">
-        <v>409</v>
+        <v>160</v>
       </c>
       <c r="G6" t="n">
-        <v>3253</v>
+        <v>1445</v>
       </c>
       <c r="H6" t="n">
-        <v>46.79</v>
+        <v>23.63</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,58 +963,334 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>270000</v>
+        <v>87900</v>
       </c>
       <c r="K6" t="n">
-        <v>272000</v>
+        <v>91200</v>
       </c>
       <c r="L6" t="n">
-        <v>272500</v>
+        <v>93500</v>
       </c>
       <c r="M6" t="n">
-        <v>269000</v>
+        <v>90200</v>
       </c>
       <c r="N6" t="n">
-        <v>46.73</v>
+        <v>23.53</v>
       </c>
       <c r="O6" t="n">
-        <v>268236231000</v>
+        <v>168885957800</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q6" t="n">
-        <v>69600</v>
+        <v>57000</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-253000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>야간 선물 상승 및 반도체 선물 급등 속 자사주 매수 신청 확인. 메모리 재고 부족 심화 전망.</t>
+          <t>30조 텍사스 발전 사업 포함 원전 8기 건설 등 대규모 수주 기대감. SMR 강자 부각 및 웨스팅하우스 지분 인수 관련 뉴스 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['원전', 'SMR', '대미투자']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1843000</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>+3.37%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E7" t="n">
+        <v>797</v>
+      </c>
+      <c r="F7" t="n">
+        <v>446</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1946</v>
+      </c>
+      <c r="H7" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1783000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1799000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1846000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1777000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>986576404000</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>274000</v>
+      </c>
+      <c r="R7" t="n">
+        <v>25000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>180만원 돌파 및 200만원 터치 가능성 언급. 연말 전고점 돌파 기대감 및 유럽 시장과의 비교 언급.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
         <v>0.2</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['180만원', '200만원', '전고점']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>한국전력</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>33800</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>+3.21%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E8" t="n">
+        <v>42</v>
+      </c>
+      <c r="F8" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" t="n">
+        <v>128</v>
+      </c>
+      <c r="H8" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>32750</v>
+      </c>
+      <c r="K8" t="n">
+        <v>33700</v>
+      </c>
+      <c r="L8" t="n">
+        <v>34350</v>
+      </c>
+      <c r="M8" t="n">
+        <v>33600</v>
+      </c>
+      <c r="N8" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="O8" t="n">
+        <v>26139433400</v>
+      </c>
+      <c r="P8" t="n">
+        <v>69500</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>30400</v>
+      </c>
+      <c r="R8" t="n">
+        <v>187000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>웨스팅하우스 지분 인수 및 미국 원전 8기 추진 관련 긍정적 전망. PBR 저평가 해소 기대감 및 공매도 물량 언급.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['원전', '웨스팅하우스', 'PBR']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>015760</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>273250</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>+1.20%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E9" t="n">
+        <v>779</v>
+      </c>
+      <c r="F9" t="n">
+        <v>448</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3361</v>
+      </c>
+      <c r="H9" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>270000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>272000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>274000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>269000</v>
+      </c>
+      <c r="N9" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="O9" t="n">
+        <v>510004004500</v>
+      </c>
+      <c r="P9" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>69600</v>
+      </c>
+      <c r="R9" t="n">
+        <v>91000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>야간 선물 상승 및 반도체 선물 급등 속 자사주 매수 신청 확인. 메모리 재고 부족 심화 전망.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>['반도체', '선물', '자사주']</t>
         </is>
       </c>
-      <c r="X6" t="n">
+      <c r="X9" t="n">
         <v>101</v>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>005930</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34800</v>
+        <v>3640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+13.91%</t>
+          <t>+30.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>175</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>236</v>
+        <v>59</v>
       </c>
       <c r="H2" t="n">
-        <v>0.23</v>
+        <v>0.45</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>30550</v>
+        <v>2800</v>
       </c>
       <c r="K2" t="n">
-        <v>31650</v>
+        <v>2900</v>
       </c>
       <c r="L2" t="n">
-        <v>34800</v>
+        <v>3640</v>
       </c>
       <c r="M2" t="n">
-        <v>31350</v>
+        <v>2900</v>
       </c>
       <c r="N2" t="n">
-        <v>0.16</v>
+        <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>287011422325</v>
+        <v>115796227613</v>
       </c>
       <c r="P2" t="n">
-        <v>34800</v>
+        <v>8100</v>
       </c>
       <c r="Q2" t="n">
-        <v>8200</v>
+        <v>592</v>
       </c>
       <c r="R2" t="n">
-        <v>-33000</v>
+        <v>662000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>정부 지분 공시 및 비교군 없는 세계 최초 기술 언급. 주가 부양 의지 및 신규주 특성 관련 언급.</t>
+          <t>AI 및 6G 광통신 부품 국책 사업 선정 기반 주가 상승 기대. 외국인 매수세 관찰.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규주', '정부지분', '기술']</t>
+          <t>['AI', '광통신', '국책사업']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>136900</v>
+        <v>36250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+11.94%</t>
+          <t>+18.66%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>367</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>211</v>
       </c>
       <c r="G3" t="n">
-        <v>95</v>
+        <v>423</v>
       </c>
       <c r="H3" t="n">
-        <v>13.33</v>
+        <v>0.23</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>122300</v>
+        <v>30550</v>
       </c>
       <c r="K3" t="n">
-        <v>129400</v>
+        <v>31650</v>
       </c>
       <c r="L3" t="n">
-        <v>143100</v>
+        <v>39350</v>
       </c>
       <c r="M3" t="n">
-        <v>128100</v>
+        <v>31350</v>
       </c>
       <c r="N3" t="n">
-        <v>13.22</v>
+        <v>0.16</v>
       </c>
       <c r="O3" t="n">
-        <v>80610303100</v>
+        <v>564837237975</v>
       </c>
       <c r="P3" t="n">
-        <v>198000</v>
+        <v>39350</v>
       </c>
       <c r="Q3" t="n">
-        <v>77100</v>
+        <v>8200</v>
       </c>
       <c r="R3" t="n">
-        <v>-62000</v>
+        <v>-33000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 원전 8기 건설(260조 규모) 수주 기대감. 웨스팅하우스 설계와의 연관성 및 신사업 진출 재료 언급.</t>
+          <t>신규 상장주로서 주포 활동 및 5만원, 7~8만원 목표 제시. 매출 대비 큰 손실 구조.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['원전', '수주', '웨스팅하우스']</t>
+          <t>['신규주', '주포', '시총']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,77 +740,77 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11880</v>
+        <v>138300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+8.79%</t>
+          <t>+13.08%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.11</v>
+        <v>0.11</v>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="H4" t="n">
-        <v>5.42</v>
+        <v>13.33</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>10920</v>
+        <v>122300</v>
       </c>
       <c r="K4" t="n">
-        <v>11300</v>
+        <v>129400</v>
       </c>
       <c r="L4" t="n">
-        <v>12700</v>
+        <v>143100</v>
       </c>
       <c r="M4" t="n">
-        <v>11050</v>
+        <v>128100</v>
       </c>
       <c r="N4" t="n">
-        <v>5.53</v>
+        <v>13.22</v>
       </c>
       <c r="O4" t="n">
-        <v>59729969995</v>
+        <v>119964268000</v>
       </c>
       <c r="P4" t="n">
-        <v>30200</v>
+        <v>198000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3540</v>
+        <v>77100</v>
       </c>
       <c r="R4" t="n">
-        <v>-249000</v>
+        <v>-62000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>원전 섹터 전반의 상승세에 따른 기대감. 프랑스와의 원자력 협정 및 공매도 상환 압박 언급.</t>
+          <t>미국 원전 8기 수주 가능성 및 AP1000 관련 사업 내용 언급, 단기 고점 및 시세 끝 가능성도 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['원전', '협정', '공매도']</t>
+          <t>['원전', 'AP1000', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>052690</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19530</v>
+        <v>19730</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+6.08%</t>
+          <t>+7.17%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>155</v>
+        <v>263</v>
       </c>
       <c r="H5" t="n">
         <v>10.47</v>
@@ -886,7 +886,7 @@
         <v>10.4</v>
       </c>
       <c r="O5" t="n">
-        <v>116752892720</v>
+        <v>179220947935</v>
       </c>
       <c r="P5" t="n">
         <v>40350</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>신사업 재료 발표 기대감 속 원전 관련 긍정적 언급. 하지만 아직 확정된 내용은 없는 상황.</t>
+          <t>원전 사업 확대 및 상반기 순이익 2745% 성장 기반 3만원 목표 전망. 신규 사업 재료 발표 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['신사업', '원전', '재료']</t>
+          <t>['원전', '신사업', '순이익']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>91900</v>
+        <v>319</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+4.55%</t>
+          <t>+6.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>225</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>1445</v>
+        <v>26</v>
       </c>
       <c r="H6" t="n">
-        <v>23.63</v>
+        <v>5.34</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>87900</v>
+        <v>299</v>
       </c>
       <c r="K6" t="n">
-        <v>91200</v>
+        <v>220</v>
       </c>
       <c r="L6" t="n">
-        <v>93500</v>
+        <v>344</v>
       </c>
       <c r="M6" t="n">
-        <v>90200</v>
+        <v>220</v>
       </c>
       <c r="N6" t="n">
-        <v>23.53</v>
+        <v>5.29</v>
       </c>
       <c r="O6" t="n">
-        <v>168885957800</v>
+        <v>4393579975</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>901</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>217</v>
       </c>
       <c r="R6" t="n">
-        <v>-253000</v>
+        <v>687000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>30조 텍사스 발전 사업 포함 원전 8기 건설 등 대규모 수주 기대감. SMR 강자 부각 및 웨스팅하우스 지분 인수 관련 뉴스 언급.</t>
+          <t>상장 폐지 우려 속 정매 마지막 불꽃 및 1500원 이상 가치 주장. 회사 자산 대비 시총 괴리 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '대미투자']</t>
+          <t>['상폐', '정매', '자산']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1843000</v>
+        <v>14370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+3.37%</t>
+          <t>+6.68%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>797</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
-        <v>446</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>1946</v>
+        <v>238</v>
       </c>
       <c r="H7" t="n">
-        <v>50.63</v>
+        <v>1.94</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1783000</v>
+        <v>13470</v>
       </c>
       <c r="K7" t="n">
-        <v>1799000</v>
+        <v>13580</v>
       </c>
       <c r="L7" t="n">
-        <v>1846000</v>
+        <v>14380</v>
       </c>
       <c r="M7" t="n">
-        <v>1777000</v>
+        <v>13420</v>
       </c>
       <c r="N7" t="n">
-        <v>50.5</v>
+        <v>1.82</v>
       </c>
       <c r="O7" t="n">
-        <v>986576404000</v>
+        <v>104501558690</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>274000</v>
+        <v>1252</v>
       </c>
       <c r="R7" t="n">
-        <v>25000</v>
+        <v>267000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>180만원 돌파 및 200만원 터치 가능성 언급. 연말 전고점 돌파 기대감 및 유럽 시장과의 비교 언급.</t>
+          <t>Texas 소식 기반 상승 기대감, 빛과전자와의 비교 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['180만원', '200만원', '전고점']</t>
+          <t>['Texas', '광통신주', '품절주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,86 +1108,86 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33800</v>
+        <v>11570</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+3.21%</t>
+          <t>+5.95%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>-0.11</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="H8" t="n">
-        <v>52.7</v>
+        <v>5.42</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>32750</v>
+        <v>10920</v>
       </c>
       <c r="K8" t="n">
-        <v>33700</v>
+        <v>11300</v>
       </c>
       <c r="L8" t="n">
-        <v>34350</v>
+        <v>12700</v>
       </c>
       <c r="M8" t="n">
-        <v>33600</v>
+        <v>11050</v>
       </c>
       <c r="N8" t="n">
-        <v>21.02</v>
+        <v>5.53</v>
       </c>
       <c r="O8" t="n">
-        <v>26139433400</v>
+        <v>81237175970</v>
       </c>
       <c r="P8" t="n">
-        <v>69500</v>
+        <v>30200</v>
       </c>
       <c r="Q8" t="n">
-        <v>30400</v>
+        <v>3540</v>
       </c>
       <c r="R8" t="n">
-        <v>187000</v>
+        <v>-249000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 및 미국 원전 8기 추진 관련 긍정적 전망. PBR 저평가 해소 기대감 및 공매도 물량 언급.</t>
+          <t>프랑스와의 원자력 협정 및 공매도 상환 기대, 원전 섹터 전반의 상승 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '웨스팅하우스', 'PBR']</t>
+          <t>['원전', '프랑스', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>273250</v>
+        <v>50200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+4.58%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>779</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>448</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>3361</v>
+        <v>110</v>
       </c>
       <c r="H9" t="n">
-        <v>46.79</v>
+        <v>38.34</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,704 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>270000</v>
+        <v>48000</v>
       </c>
       <c r="K9" t="n">
-        <v>272000</v>
+        <v>48550</v>
       </c>
       <c r="L9" t="n">
-        <v>274000</v>
+        <v>51600</v>
       </c>
       <c r="M9" t="n">
-        <v>269000</v>
+        <v>48350</v>
       </c>
       <c r="N9" t="n">
-        <v>46.73</v>
+        <v>38.24</v>
       </c>
       <c r="O9" t="n">
-        <v>510004004500</v>
+        <v>75138864650</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q9" t="n">
-        <v>69600</v>
+        <v>23150</v>
       </c>
       <c r="R9" t="n">
-        <v>91000</v>
+        <v>286000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>야간 선물 상승 및 반도체 선물 급등 속 자사주 매수 신청 확인. 메모리 재고 부족 심화 전망.</t>
+          <t>5만원 돌파 및 캡상승 기대감 존재. 조만간 공시 예정 및 공매도 관련 언급. 개인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['공시', '공매도', '개인매도']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>91600</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>+4.21%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>274</v>
+      </c>
+      <c r="F10" t="n">
+        <v>190</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1523</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>87900</v>
+      </c>
+      <c r="K10" t="n">
+        <v>91200</v>
+      </c>
+      <c r="L10" t="n">
+        <v>93500</v>
+      </c>
+      <c r="M10" t="n">
+        <v>90200</v>
+      </c>
+      <c r="N10" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="O10" t="n">
+        <v>222076519650</v>
+      </c>
+      <c r="P10" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-253000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['원전', 'SMR', '텍사스']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1842000</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>+3.31%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E11" t="n">
+        <v>795</v>
+      </c>
+      <c r="F11" t="n">
+        <v>466</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1817</v>
+      </c>
+      <c r="H11" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1783000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1799000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1848000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1777000</v>
+      </c>
+      <c r="N11" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1672870603500</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>274000</v>
+      </c>
+      <c r="R11" t="n">
+        <v>25000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>180 돌파 및 박스권 돌파에 대한 기대감, 외인 매수세 유입 관찰 및 전고점 돌파 전망.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['박스권 돌파', '외인 매수', '전고점']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>한국전력</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>33800</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>+3.21%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" t="n">
+        <v>41</v>
+      </c>
+      <c r="G12" t="n">
+        <v>164</v>
+      </c>
+      <c r="H12" t="n">
+        <v>52.69</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>32750</v>
+      </c>
+      <c r="K12" t="n">
+        <v>33700</v>
+      </c>
+      <c r="L12" t="n">
+        <v>34350</v>
+      </c>
+      <c r="M12" t="n">
+        <v>33600</v>
+      </c>
+      <c r="N12" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="O12" t="n">
+        <v>35535850625</v>
+      </c>
+      <c r="P12" t="n">
+        <v>69500</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>30400</v>
+      </c>
+      <c r="R12" t="n">
+        <v>199000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>미국 원전 8기 추진 및 웨스팅하우스 지분 인수 관련 기대감. PBR 0.48 대비 상승 여력 존재.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['원전', '웨스팅하우스', 'PBR']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>015760</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>274000</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>+1.48%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E13" t="n">
+        <v>797</v>
+      </c>
+      <c r="F13" t="n">
+        <v>460</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2324</v>
+      </c>
+      <c r="H13" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>270000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>272000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>275000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>269000</v>
+      </c>
+      <c r="N13" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1053166192000</v>
+      </c>
+      <c r="P13" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>69600</v>
+      </c>
+      <c r="R13" t="n">
+        <v>122000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>자사주 매수 200만주 신청 및 15조 규모 자사주 매입 계획에 따른 주가 상승 기대. 휴머노이드 기대감 존재.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['자사주매입', '휴머노이드', '주주환원']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>101</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>JW신약</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3605</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>+0.70%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E14" t="n">
+        <v>53</v>
+      </c>
+      <c r="F14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G14" t="n">
+        <v>59</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>3580</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3600</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3820</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3450</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>48935572352</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3900</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1246</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-123000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>탈모 치료제 건보 적용 시 급등 기대감. 월가 탈모주 금광 언급 및 바이오니아 상승세 주목.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
         <v>0.2</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>['반도체', '선물', '자사주']</t>
-        </is>
-      </c>
-      <c r="X9" t="n">
-        <v>101</v>
-      </c>
-      <c r="Y9" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['탈모', '건보', '바이오니아']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>005930</t>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>067290</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>삼미금속</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10060</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-1.37%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43</v>
+      </c>
+      <c r="G15" t="n">
+        <v>41</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>10200</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10600</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10970</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10010</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="O15" t="n">
+        <v>47629326690</v>
+      </c>
+      <c r="P15" t="n">
+        <v>20850</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4020</v>
+      </c>
+      <c r="R15" t="n">
+        <v>24000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>가스터빈 수주 기대와 미국 독점 공급 가능성 언급, 매수세 관찰 및 보수적 전망.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['가스터빈', '수주', '미국']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>012210</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15480</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-3.91%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>57</v>
+      </c>
+      <c r="F16" t="n">
+        <v>39</v>
+      </c>
+      <c r="G16" t="n">
+        <v>198</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>16110</v>
+      </c>
+      <c r="K16" t="n">
+        <v>16130</v>
+      </c>
+      <c r="L16" t="n">
+        <v>16140</v>
+      </c>
+      <c r="M16" t="n">
+        <v>15310</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>21697855700</v>
+      </c>
+      <c r="P16" t="n">
+        <v>19380</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3200</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-41000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>대미 투자 1호 가스 복합 발전소 수주 기대감 있으나, 주가 하락 및 15천원 이탈 우려. 광주 공항 재개장 언급.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['대미투자', '가스발전', '광주공항']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>002990</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>115796227613</v>
+        <v>139756897823</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -619,23 +619,23 @@
         <v>592</v>
       </c>
       <c r="R2" t="n">
-        <v>662000</v>
+        <v>832000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 및 6G 광통신 부품 국책 사업 선정 기반 주가 상승 기대. 외국인 매수세 관찰.</t>
+          <t>AI 데이터센터 국책사업 선정 및 6G 광통신 부품 사업 본격화. 정부 주도 국산화 이슈 부각.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '국책사업']</t>
+          <t>['AI데이터센터', '국책사업', '광통신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,70 +655,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36250</v>
+        <v>10760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+18.66%</t>
+          <t>+27.79%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>367</v>
+        <v>99</v>
       </c>
       <c r="F3" t="n">
-        <v>211</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>423</v>
+        <v>84</v>
       </c>
       <c r="H3" t="n">
-        <v>0.23</v>
+        <v>0.62</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>30550</v>
+        <v>8420</v>
       </c>
       <c r="K3" t="n">
-        <v>31650</v>
+        <v>8640</v>
       </c>
       <c r="L3" t="n">
-        <v>39350</v>
+        <v>10900</v>
       </c>
       <c r="M3" t="n">
-        <v>31350</v>
+        <v>8230</v>
       </c>
       <c r="N3" t="n">
-        <v>0.16</v>
+        <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>564837237975</v>
+        <v>172137579505</v>
       </c>
       <c r="P3" t="n">
-        <v>39350</v>
+        <v>15960</v>
       </c>
       <c r="Q3" t="n">
-        <v>8200</v>
+        <v>3500</v>
       </c>
       <c r="R3" t="n">
-        <v>-33000</v>
+        <v>-3000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>신규 상장주로서 주포 활동 및 5만원, 7~8만원 목표 제시. 매출 대비 큰 손실 구조.</t>
+          <t>정부 정책 기대감 속 미프진 독점 판매 이슈 부각. 기대감에 따른 급등 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['신규주', '주포', '시총']</t>
+          <t>['미프진', '정부정책', '독점판매']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>138300</v>
+        <v>36850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+13.08%</t>
+          <t>+20.62%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>443</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>244</v>
       </c>
       <c r="G4" t="n">
-        <v>106</v>
+        <v>606</v>
       </c>
       <c r="H4" t="n">
-        <v>13.33</v>
+        <v>0.23</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>122300</v>
+        <v>30550</v>
       </c>
       <c r="K4" t="n">
-        <v>129400</v>
+        <v>31650</v>
       </c>
       <c r="L4" t="n">
-        <v>143100</v>
+        <v>39350</v>
       </c>
       <c r="M4" t="n">
-        <v>128100</v>
+        <v>31350</v>
       </c>
       <c r="N4" t="n">
-        <v>13.22</v>
+        <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>119964268000</v>
+        <v>650516473450</v>
       </c>
       <c r="P4" t="n">
-        <v>198000</v>
+        <v>39350</v>
       </c>
       <c r="Q4" t="n">
-        <v>77100</v>
+        <v>8200</v>
       </c>
       <c r="R4" t="n">
-        <v>-62000</v>
+        <v>-36000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 원전 8기 수주 가능성 및 AP1000 관련 사업 내용 언급, 단기 고점 및 시세 끝 가능성도 제기.</t>
+          <t>정부 지분 공시 및 주포 활동 언급. 비교군 없는 신규 상장주로 분석.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['원전', 'AP1000', '웨스팅하우스']</t>
+          <t>['지분공시', '주포', '신규주']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19730</v>
+        <v>4100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+7.17%</t>
+          <t>+14.53%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>263</v>
+        <v>92</v>
       </c>
       <c r="H5" t="n">
-        <v>10.47</v>
+        <v>1.56</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>18410</v>
+        <v>3580</v>
       </c>
       <c r="K5" t="n">
-        <v>18800</v>
+        <v>3600</v>
       </c>
       <c r="L5" t="n">
-        <v>20200</v>
+        <v>4200</v>
       </c>
       <c r="M5" t="n">
-        <v>18480</v>
+        <v>3450</v>
       </c>
       <c r="N5" t="n">
-        <v>10.4</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>179220947935</v>
+        <v>117566955541</v>
       </c>
       <c r="P5" t="n">
-        <v>40350</v>
+        <v>4200</v>
       </c>
       <c r="Q5" t="n">
-        <v>3320</v>
+        <v>1246</v>
       </c>
       <c r="R5" t="n">
-        <v>-133000</v>
+        <v>169000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>원전 사업 확대 및 상반기 순이익 2745% 성장 기반 3만원 목표 전망. 신규 사업 재료 발표 기대.</t>
+          <t>탈모 관련 건보 적용 기대감 및 현대약품과의 동반 상승 가능성. 매력적인 가격 구간 진입.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '신사업', '순이익']</t>
+          <t>['탈모', '건보적용', '현대약품']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+6.69%</t>
+          <t>+12.71%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H6" t="n">
         <v>5.34</v>
@@ -969,7 +969,7 @@
         <v>220</v>
       </c>
       <c r="L6" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="M6" t="n">
         <v>220</v>
@@ -978,7 +978,7 @@
         <v>5.29</v>
       </c>
       <c r="O6" t="n">
-        <v>4393579975</v>
+        <v>6256043195</v>
       </c>
       <c r="P6" t="n">
         <v>901</v>
@@ -987,23 +987,23 @@
         <v>217</v>
       </c>
       <c r="R6" t="n">
-        <v>687000</v>
+        <v>645000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>상장 폐지 우려 속 정매 마지막 불꽃 및 1500원 이상 가치 주장. 회사 자산 대비 시총 괴리 언급.</t>
+          <t>상장폐지 관련 공시 확인 및 정리매매 가능성. 회사 자산 대비 시총이 크다는 분석.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['상폐', '정매', '자산']</t>
+          <t>['상장폐지', '정리매매', '자산']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14370</v>
+        <v>136300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.68%</t>
+          <t>+11.45%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>238</v>
+        <v>130</v>
       </c>
       <c r="H7" t="n">
-        <v>1.94</v>
+        <v>13.33</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13470</v>
+        <v>122300</v>
       </c>
       <c r="K7" t="n">
-        <v>13580</v>
+        <v>129400</v>
       </c>
       <c r="L7" t="n">
-        <v>14380</v>
+        <v>143100</v>
       </c>
       <c r="M7" t="n">
-        <v>13420</v>
+        <v>128100</v>
       </c>
       <c r="N7" t="n">
-        <v>1.82</v>
+        <v>13.22</v>
       </c>
       <c r="O7" t="n">
-        <v>104501558690</v>
+        <v>132312047350</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>198000</v>
       </c>
       <c r="Q7" t="n">
-        <v>1252</v>
+        <v>77100</v>
       </c>
       <c r="R7" t="n">
-        <v>267000</v>
+        <v>-37000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>51000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Texas 소식 기반 상승 기대감, 빛과전자와의 비교 언급.</t>
+          <t>원전 대형 사업 관련 뉴스 및 웨스팅하우스 지분 급물살. 260조 사업 규모와 수익 계산 포함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['Texas', '광통신주', '품절주']</t>
+          <t>['원전', '웨스팅하우스', '사업규모']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>052690</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11570</v>
+        <v>20150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.95%</t>
+          <t>+9.45%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G8" t="n">
-        <v>189</v>
+        <v>337</v>
       </c>
       <c r="H8" t="n">
-        <v>5.42</v>
+        <v>10.47</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10920</v>
+        <v>18410</v>
       </c>
       <c r="K8" t="n">
-        <v>11300</v>
+        <v>18800</v>
       </c>
       <c r="L8" t="n">
-        <v>12700</v>
+        <v>20300</v>
       </c>
       <c r="M8" t="n">
-        <v>11050</v>
+        <v>18480</v>
       </c>
       <c r="N8" t="n">
-        <v>5.53</v>
+        <v>10.4</v>
       </c>
       <c r="O8" t="n">
-        <v>81237175970</v>
+        <v>223235878415</v>
       </c>
       <c r="P8" t="n">
-        <v>30200</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>3540</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>-249000</v>
+        <v>-8000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>프랑스와의 원자력 협정 및 공매도 상환 기대, 원전 섹터 전반의 상승 전망.</t>
+          <t>원전 사업 부각 및 신사업 재료 발표 기대감. 상반기 순이익 급증으로 인한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '프랑스', '공매도']</t>
+          <t>['원전', '신사업', '순이익']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50200</v>
+        <v>11750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>+7.60%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="G9" t="n">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="H9" t="n">
-        <v>38.34</v>
+        <v>5.42</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>48000</v>
+        <v>10920</v>
       </c>
       <c r="K9" t="n">
-        <v>48550</v>
+        <v>11300</v>
       </c>
       <c r="L9" t="n">
-        <v>51600</v>
+        <v>12700</v>
       </c>
       <c r="M9" t="n">
-        <v>48350</v>
+        <v>11050</v>
       </c>
       <c r="N9" t="n">
-        <v>38.24</v>
+        <v>5.53</v>
       </c>
       <c r="O9" t="n">
-        <v>75138864650</v>
+        <v>91446062600</v>
       </c>
       <c r="P9" t="n">
-        <v>67300</v>
+        <v>30200</v>
       </c>
       <c r="Q9" t="n">
-        <v>23150</v>
+        <v>3540</v>
       </c>
       <c r="R9" t="n">
-        <v>286000</v>
+        <v>-212000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>5만원 돌파 및 캡상승 기대감 존재. 조만간 공시 예정 및 공매도 관련 언급. 개인 매도세 관찰.</t>
+          <t>원전 섹터 관련 협정 및 공매도 이슈 언급. 거래량 대비 높은 가격 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공시', '공매도', '개인매도']</t>
+          <t>['원전', '공매도', '협정']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,86 +1292,86 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91600</v>
+        <v>14120</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.21%</t>
+          <t>+4.83%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E10" t="n">
-        <v>274</v>
+        <v>79</v>
       </c>
       <c r="F10" t="n">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
-        <v>1523</v>
+        <v>327</v>
       </c>
       <c r="H10" t="n">
-        <v>23.63</v>
+        <v>1.94</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>87900</v>
+        <v>13470</v>
       </c>
       <c r="K10" t="n">
-        <v>91200</v>
+        <v>13580</v>
       </c>
       <c r="L10" t="n">
-        <v>93500</v>
+        <v>14450</v>
       </c>
       <c r="M10" t="n">
-        <v>90200</v>
+        <v>13420</v>
       </c>
       <c r="N10" t="n">
-        <v>23.53</v>
+        <v>1.82</v>
       </c>
       <c r="O10" t="n">
-        <v>222076519650</v>
+        <v>163124443610</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>1252</v>
       </c>
       <c r="R10" t="n">
-        <v>-253000</v>
+        <v>20000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
+          <t>Texas 관련 소식 및 공매도 언급. 투경재 지정 판단일 관련 내용 포함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '텍사스']</t>
+          <t>['Texas', '공매도', '투경재']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1842000</v>
+        <v>50200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.31%</t>
+          <t>+4.58%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>795</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>466</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>1817</v>
+        <v>144</v>
       </c>
       <c r="H11" t="n">
-        <v>50.63</v>
+        <v>38.34</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1783000</v>
+        <v>48000</v>
       </c>
       <c r="K11" t="n">
-        <v>1799000</v>
+        <v>48550</v>
       </c>
       <c r="L11" t="n">
-        <v>1848000</v>
+        <v>51600</v>
       </c>
       <c r="M11" t="n">
-        <v>1777000</v>
+        <v>48350</v>
       </c>
       <c r="N11" t="n">
-        <v>50.5</v>
+        <v>38.24</v>
       </c>
       <c r="O11" t="n">
-        <v>1672870603500</v>
+        <v>85981058225</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>67300</v>
       </c>
       <c r="Q11" t="n">
-        <v>274000</v>
+        <v>23150</v>
       </c>
       <c r="R11" t="n">
-        <v>25000</v>
+        <v>266000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>180 돌파 및 박스권 돌파에 대한 기대감, 외인 매수세 유입 관찰 및 전고점 돌파 전망.</t>
+          <t>건설, 원전, 재건 등 복합 테마 기대감. 5만원대 안착 시 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['박스권 돌파', '외인 매수', '전고점']</t>
+          <t>['건설', '원전', '재건']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33800</v>
+        <v>91200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.21%</t>
+          <t>+3.75%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.01</v>
+        <v>0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>326</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>213</v>
       </c>
       <c r="G12" t="n">
-        <v>164</v>
+        <v>1612</v>
       </c>
       <c r="H12" t="n">
-        <v>52.69</v>
+        <v>23.63</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>32750</v>
+        <v>87900</v>
       </c>
       <c r="K12" t="n">
-        <v>33700</v>
+        <v>91200</v>
       </c>
       <c r="L12" t="n">
-        <v>34350</v>
+        <v>93500</v>
       </c>
       <c r="M12" t="n">
-        <v>33600</v>
+        <v>90200</v>
       </c>
       <c r="N12" t="n">
-        <v>21.02</v>
+        <v>23.53</v>
       </c>
       <c r="O12" t="n">
-        <v>35535850625</v>
+        <v>264688603100</v>
       </c>
       <c r="P12" t="n">
-        <v>69500</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>30400</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>199000</v>
+        <v>-211000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>236000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 원전 8기 추진 및 웨스팅하우스 지분 인수 관련 기대감. PBR 0.48 대비 상승 여력 존재.</t>
+          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '웨스팅하우스', 'PBR']</t>
+          <t>['원전', 'SMR', '텍사스']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>274000</v>
+        <v>33800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+3.21%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>797</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>460</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>2324</v>
+        <v>189</v>
       </c>
       <c r="H13" t="n">
-        <v>46.79</v>
+        <v>52.67</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>270000</v>
+        <v>32750</v>
       </c>
       <c r="K13" t="n">
-        <v>272000</v>
+        <v>33700</v>
       </c>
       <c r="L13" t="n">
-        <v>275000</v>
+        <v>34350</v>
       </c>
       <c r="M13" t="n">
-        <v>269000</v>
+        <v>33450</v>
       </c>
       <c r="N13" t="n">
-        <v>46.73</v>
+        <v>21.02</v>
       </c>
       <c r="O13" t="n">
-        <v>1053166192000</v>
+        <v>44485162425</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>69500</v>
       </c>
       <c r="Q13" t="n">
-        <v>69600</v>
+        <v>30400</v>
       </c>
       <c r="R13" t="n">
-        <v>122000</v>
+        <v>290000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>157000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>자사주 매수 200만주 신청 및 15조 규모 자사주 매입 계획에 따른 주가 상승 기대. 휴머노이드 기대감 존재.</t>
+          <t>웨스팅하우스 지분 인수 및 미국 원전 사업 추진 본격화. 공매도 물량 소화 후 상승 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주매입', '휴머노이드', '주주환원']</t>
+          <t>['웨스팅하우스', '원전', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3605</v>
+        <v>1837000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.31</v>
+        <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>795</v>
       </c>
       <c r="F14" t="n">
-        <v>33</v>
+        <v>476</v>
       </c>
       <c r="G14" t="n">
-        <v>59</v>
+        <v>1837</v>
       </c>
       <c r="H14" t="n">
-        <v>1.56</v>
+        <v>50.63</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3580</v>
+        <v>1783000</v>
       </c>
       <c r="K14" t="n">
-        <v>3600</v>
+        <v>1799000</v>
       </c>
       <c r="L14" t="n">
-        <v>3820</v>
+        <v>1860000</v>
       </c>
       <c r="M14" t="n">
-        <v>3450</v>
+        <v>1777000</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>50.5</v>
       </c>
       <c r="O14" t="n">
-        <v>48935572352</v>
+        <v>2336835759500</v>
       </c>
       <c r="P14" t="n">
-        <v>3900</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>1246</v>
+        <v>274000</v>
       </c>
       <c r="R14" t="n">
-        <v>-123000</v>
+        <v>55000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>탈모 치료제 건보 적용 시 급등 기대감. 월가 탈모주 금광 언급 및 바이오니아 상승세 주목.</t>
+          <t>기관 및 외인 매수세 유입에 따른 반도체 업황 개선 기대. 치명적인 저평가 구간 진입.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['탈모', '건보', '바이오니아']</t>
+          <t>['반도체', '기관외인', '저평가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10060</v>
+        <v>273500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.23</v>
+        <v>0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>55</v>
+        <v>798</v>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
+        <v>474</v>
       </c>
       <c r="G15" t="n">
-        <v>41</v>
+        <v>1751</v>
       </c>
       <c r="H15" t="n">
-        <v>0.44</v>
+        <v>46.79</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>10200</v>
+        <v>270000</v>
       </c>
       <c r="K15" t="n">
-        <v>10600</v>
+        <v>272000</v>
       </c>
       <c r="L15" t="n">
-        <v>10970</v>
+        <v>275000</v>
       </c>
       <c r="M15" t="n">
-        <v>10010</v>
+        <v>269000</v>
       </c>
       <c r="N15" t="n">
-        <v>0.21</v>
+        <v>46.73</v>
       </c>
       <c r="O15" t="n">
-        <v>47629326690</v>
+        <v>1388196998500</v>
       </c>
       <c r="P15" t="n">
-        <v>20850</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>4020</v>
+        <v>69600</v>
       </c>
       <c r="R15" t="n">
-        <v>24000</v>
+        <v>498000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>가스터빈 수주 기대와 미국 독점 공급 가능성 언급, 매수세 관찰 및 보수적 전망.</t>
+          <t>자사주 매수 및 주주환원 정책 기대감. 단기적 공매도 및 개인 매물 출회.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['가스터빈', '수주', '미국']</t>
+          <t>['자사주매수', '주주환원', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,99 +1844,375 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15480</v>
+        <v>10060</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.91%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="E16" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>198</v>
+        <v>53</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>16110</v>
+        <v>10200</v>
       </c>
       <c r="K16" t="n">
-        <v>16130</v>
+        <v>10600</v>
       </c>
       <c r="L16" t="n">
-        <v>16140</v>
+        <v>10970</v>
       </c>
       <c r="M16" t="n">
-        <v>15310</v>
+        <v>9980</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="O16" t="n">
-        <v>21697855700</v>
+        <v>51064233465</v>
       </c>
       <c r="P16" t="n">
-        <v>19380</v>
+        <v>20850</v>
       </c>
       <c r="Q16" t="n">
-        <v>3200</v>
+        <v>4020</v>
       </c>
       <c r="R16" t="n">
-        <v>-41000</v>
+        <v>-7000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대미 투자 1호 가스 복합 발전소 수주 기대감 있으나, 주가 하락 및 15천원 이탈 우려. 광주 공항 재개장 언급.</t>
+          <t>터빈 블레이드 수주 기대감 및 뉴스 언급. 미국 가스터빈 독점 공급 관련 분석.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['가스터빈', '수주', '독점공급']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>012210</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>15560</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-3.41%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F17" t="n">
+        <v>43</v>
+      </c>
+      <c r="G17" t="n">
+        <v>243</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>16110</v>
+      </c>
+      <c r="K17" t="n">
+        <v>16130</v>
+      </c>
+      <c r="L17" t="n">
+        <v>16140</v>
+      </c>
+      <c r="M17" t="n">
+        <v>15310</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>26097154465</v>
+      </c>
+      <c r="P17" t="n">
+        <v>19380</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3200</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-57000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>호남 메가 프로젝트 및 대규모 투자 유치 기대감. 광주 개발 등 연계 호재 부각.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['메가프로젝트', '대규모투자', '광주개발']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>002990</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>8410</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-11.10%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" t="n">
+        <v>97</v>
+      </c>
+      <c r="H18" t="n">
+        <v>38.84</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>9460</v>
+      </c>
+      <c r="K18" t="n">
+        <v>9700</v>
+      </c>
+      <c r="L18" t="n">
+        <v>9760</v>
+      </c>
+      <c r="M18" t="n">
+        <v>8110</v>
+      </c>
+      <c r="N18" t="n">
+        <v>38.69</v>
+      </c>
+      <c r="O18" t="n">
+        <v>20333802075</v>
+      </c>
+      <c r="P18" t="n">
+        <v>19150</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3445</v>
+      </c>
+      <c r="R18" t="n">
+        <v>53000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-14000</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>삼성, 포스코 관계사 상승 언급 및 차익 실현 가능성. 대차잔고 및 프로그램 매수 관련 논의.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
         <v>0.1</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>['대미투자', '가스발전', '광주공항']</t>
-        </is>
-      </c>
-      <c r="X16" t="n">
-        <v>49</v>
-      </c>
-      <c r="Y16" t="inlineStr">
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['관계사', '차익실현', '대차잔고']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>002990</t>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>033790</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>카프로</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>340</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-90.71%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>44</v>
+      </c>
+      <c r="F19" t="n">
+        <v>33</v>
+      </c>
+      <c r="G19" t="n">
+        <v>95</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>3660</v>
+      </c>
+      <c r="K19" t="n">
+        <v>300</v>
+      </c>
+      <c r="L19" t="n">
+        <v>340</v>
+      </c>
+      <c r="M19" t="n">
+        <v>300</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O19" t="n">
+        <v>614195520</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3660</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>300</v>
+      </c>
+      <c r="R19" t="n">
+        <v>38000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>감사의견 적정 확보에도 불구하고 유증 물량 및 재무 악화 우려. 급락 후 회복 기대.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['감사의견', '유증', '재무악화']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>006380</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>139756897823</v>
+        <v>140455533943</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 국책사업 선정 및 6G 광통신 부품 사업 본격화. 정부 주도 국산화 이슈 부각.</t>
+          <t>AI 데이터센터, 6G 광통신 관련 정부 주관 사업 선정 뉴스가 부각되며 급등. AI 바람 재차 불면 추가 상승 기대감 높음.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI데이터센터', '국책사업', '광통신']</t>
+          <t>['AI', '광통신', '정부 사업']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10760</v>
+        <v>10640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+27.79%</t>
+          <t>+26.37%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="G3" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -693,7 +693,7 @@
         <v>8640</v>
       </c>
       <c r="L3" t="n">
-        <v>10900</v>
+        <v>10940</v>
       </c>
       <c r="M3" t="n">
         <v>8230</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>172137579505</v>
+        <v>239541510935</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부 정책 기대감 속 미프진 독점 판매 이슈 부각. 기대감에 따른 급등 전망.</t>
+          <t>정부의 저출산 대책으로 미프진 관련주로 부각되며 상승 기대감 형성. 그러나 구체적인 공시나 뉴스는 부족.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미프진', '정부정책', '독점판매']</t>
+          <t>['미프진', '정부 정책']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36850</v>
+        <v>36900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+20.62%</t>
+          <t>+20.79%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="F4" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="G4" t="n">
-        <v>606</v>
+        <v>738</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>650516473450</v>
+        <v>683388640725</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 지분 공시 및 주포 활동 언급. 비교군 없는 신규 상장주로 분석.</t>
+          <t>정부 지분 공시, 비교군 없는 신규 상장주로서의 기대감 및 급등 조짐.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['지분공시', '주포', '신규주']</t>
+          <t>['신규주', '정부 지분', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4100</v>
+        <v>4160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+14.53%</t>
+          <t>+16.20%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="H5" t="n">
         <v>1.56</v>
@@ -877,7 +877,7 @@
         <v>3600</v>
       </c>
       <c r="L5" t="n">
-        <v>4200</v>
+        <v>4335</v>
       </c>
       <c r="M5" t="n">
         <v>3450</v>
@@ -886,10 +886,10 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>117566955541</v>
+        <v>192711605976</v>
       </c>
       <c r="P5" t="n">
-        <v>4200</v>
+        <v>4335</v>
       </c>
       <c r="Q5" t="n">
         <v>1246</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>탈모 관련 건보 적용 기대감 및 현대약품과의 동반 상승 가능성. 매력적인 가격 구간 진입.</t>
+          <t>탈모 건보료 적용 시 난리 날 것이라는 기대감과 함께 10년 매집 구간 돌파 및 30만 목표가 제시. 약효에 대한 긍정적 평가.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['탈모', '건보적용', '현대약품']</t>
+          <t>['탈모', '건보료', '신약']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,79 +931,79 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>337</v>
+        <v>137700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+12.71%</t>
+          <t>+12.59%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="E6" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="H6" t="n">
-        <v>5.34</v>
+        <v>13.33</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>299</v>
+        <v>122300</v>
       </c>
       <c r="K6" t="n">
-        <v>220</v>
+        <v>129400</v>
       </c>
       <c r="L6" t="n">
-        <v>349</v>
+        <v>143100</v>
       </c>
       <c r="M6" t="n">
-        <v>220</v>
+        <v>128100</v>
       </c>
       <c r="N6" t="n">
-        <v>5.29</v>
+        <v>13.22</v>
       </c>
       <c r="O6" t="n">
-        <v>6256043195</v>
+        <v>136963977850</v>
       </c>
       <c r="P6" t="n">
-        <v>901</v>
+        <v>198000</v>
       </c>
       <c r="Q6" t="n">
-        <v>217</v>
+        <v>77100</v>
       </c>
       <c r="R6" t="n">
-        <v>645000</v>
+        <v>-37000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>51000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>상장폐지 관련 공시 확인 및 정리매매 가능성. 회사 자산 대비 시총이 크다는 분석.</t>
+          <t>미국 원전 8기 수주 관련 대형 사업 언급, AP1000 사업 및 웨스팅 지분 급물살.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['상장폐지', '정리매매', '자산']</t>
+          <t>['원전', 'AP1000', '미국 수주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>052690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>136300</v>
+        <v>20450</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+11.45%</t>
+          <t>+11.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="G7" t="n">
-        <v>130</v>
+        <v>498</v>
       </c>
       <c r="H7" t="n">
-        <v>13.33</v>
+        <v>10.47</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>122300</v>
+        <v>18410</v>
       </c>
       <c r="K7" t="n">
-        <v>129400</v>
+        <v>18800</v>
       </c>
       <c r="L7" t="n">
-        <v>143100</v>
+        <v>20725</v>
       </c>
       <c r="M7" t="n">
-        <v>128100</v>
+        <v>18480</v>
       </c>
       <c r="N7" t="n">
-        <v>13.22</v>
+        <v>10.4</v>
       </c>
       <c r="O7" t="n">
-        <v>132312047350</v>
+        <v>274267825940</v>
       </c>
       <c r="P7" t="n">
-        <v>198000</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>77100</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-37000</v>
+        <v>-8000</v>
       </c>
       <c r="S7" t="n">
-        <v>51000</v>
+        <v>85000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원전 대형 사업 관련 뉴스 및 웨스팅하우스 지분 급물살. 260조 사업 규모와 수익 계산 포함.</t>
+          <t>원전 사업 복 터졌다는 기대감과 함께 2만 원 돌파 및 신사업 재료 발표 기대감 상승. 다만, 확정된 내용은 아직 없음.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '웨스팅하우스', '사업규모']</t>
+          <t>['원전', '신사업', '건설']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20150</v>
+        <v>331</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.45%</t>
+          <t>+10.70%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="F8" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>337</v>
+        <v>38</v>
       </c>
       <c r="H8" t="n">
-        <v>10.47</v>
+        <v>5.34</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18410</v>
+        <v>299</v>
       </c>
       <c r="K8" t="n">
-        <v>18800</v>
+        <v>220</v>
       </c>
       <c r="L8" t="n">
-        <v>20300</v>
+        <v>349</v>
       </c>
       <c r="M8" t="n">
-        <v>18480</v>
+        <v>220</v>
       </c>
       <c r="N8" t="n">
-        <v>10.4</v>
+        <v>5.29</v>
       </c>
       <c r="O8" t="n">
-        <v>223235878415</v>
+        <v>6781829232</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>901</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>217</v>
       </c>
       <c r="R8" t="n">
-        <v>-8000</v>
+        <v>645000</v>
       </c>
       <c r="S8" t="n">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원전 사업 부각 및 신사업 재료 발표 기대감. 상반기 순이익 급증으로 인한 긍정적 전망.</t>
+          <t>상장폐지 가능성 속 정리매매 진행, 상속 지분 및 자산 가치 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '신사업', '순이익']</t>
+          <t>['상장폐지', '정리매매', '자산 가치']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11750</v>
+        <v>11700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.60%</t>
+          <t>+7.14%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.11</v>
       </c>
       <c r="E9" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G9" t="n">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="H9" t="n">
         <v>5.42</v>
@@ -1254,7 +1254,7 @@
         <v>5.53</v>
       </c>
       <c r="O9" t="n">
-        <v>91446062600</v>
+        <v>95919571905</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원전 섹터 관련 협정 및 공매도 이슈 언급. 거래량 대비 높은 가격 상승 기대.</t>
+          <t>원전 섹터 관련 협정 및 투자 소식, 공매도 상환 압박 및 2조 시총 논란.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '협정']</t>
+          <t>['원전', '공매도', '프랑스 협정']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14120</v>
+        <v>50400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.83%</t>
+          <t>+5.00%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>327</v>
+        <v>168</v>
       </c>
       <c r="H10" t="n">
-        <v>1.94</v>
+        <v>38.34</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13470</v>
+        <v>48000</v>
       </c>
       <c r="K10" t="n">
-        <v>13580</v>
+        <v>48550</v>
       </c>
       <c r="L10" t="n">
-        <v>14450</v>
+        <v>51600</v>
       </c>
       <c r="M10" t="n">
-        <v>13420</v>
+        <v>48350</v>
       </c>
       <c r="N10" t="n">
-        <v>1.82</v>
+        <v>38.24</v>
       </c>
       <c r="O10" t="n">
-        <v>163124443610</v>
+        <v>92505033275</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>67300</v>
       </c>
       <c r="Q10" t="n">
-        <v>1252</v>
+        <v>23150</v>
       </c>
       <c r="R10" t="n">
-        <v>20000</v>
+        <v>266000</v>
       </c>
       <c r="S10" t="n">
-        <v>5000</v>
+        <v>40000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Texas 관련 소식 및 공매도 언급. 투경재 지정 판단일 관련 내용 포함.</t>
+          <t>건설주 전반의 상승세와 함께 원전, 재건 등 다양한 테마 기대감 존재. 그러나 단기 급등 후 조정 가능성 및 개인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['Texas', '공매도', '투경재']</t>
+          <t>['건설', '원전', '재건']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50200</v>
+        <v>14100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>+4.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>144</v>
+        <v>369</v>
       </c>
       <c r="H11" t="n">
-        <v>38.34</v>
+        <v>1.94</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>48000</v>
+        <v>13470</v>
       </c>
       <c r="K11" t="n">
-        <v>48550</v>
+        <v>13580</v>
       </c>
       <c r="L11" t="n">
-        <v>51600</v>
+        <v>14450</v>
       </c>
       <c r="M11" t="n">
-        <v>48350</v>
+        <v>13420</v>
       </c>
       <c r="N11" t="n">
-        <v>38.24</v>
+        <v>1.82</v>
       </c>
       <c r="O11" t="n">
-        <v>85981058225</v>
+        <v>171748424080</v>
       </c>
       <c r="P11" t="n">
-        <v>67300</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>23150</v>
+        <v>1252</v>
       </c>
       <c r="R11" t="n">
-        <v>266000</v>
+        <v>20000</v>
       </c>
       <c r="S11" t="n">
-        <v>40000</v>
+        <v>5000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>건설, 원전, 재건 등 복합 테마 기대감. 5만원대 안착 시 추가 상승 전망.</t>
+          <t>Texas 소식과 함께 큰 폭 상승 기대, 공매도 물량 언급 및 매물대 소화 과정.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['건설', '원전', '재건']</t>
+          <t>['광통신', '공매도', '매물대']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>91200</v>
+        <v>9180</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.75%</t>
+          <t>+4.56%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>326</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
-        <v>213</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>1612</v>
+        <v>33</v>
       </c>
       <c r="H12" t="n">
-        <v>23.63</v>
+        <v>1.68</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>87900</v>
+        <v>8780</v>
       </c>
       <c r="K12" t="n">
-        <v>91200</v>
+        <v>9060</v>
       </c>
       <c r="L12" t="n">
-        <v>93500</v>
+        <v>9960</v>
       </c>
       <c r="M12" t="n">
-        <v>90200</v>
+        <v>8270</v>
       </c>
       <c r="N12" t="n">
-        <v>23.53</v>
+        <v>1.72</v>
       </c>
       <c r="O12" t="n">
-        <v>264688603100</v>
+        <v>90007819410</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>25050</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>3705</v>
       </c>
       <c r="R12" t="n">
-        <v>-211000</v>
+        <v>51000</v>
       </c>
       <c r="S12" t="n">
-        <v>236000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
+          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '텍사스']</t>
+          <t>['투경', '탈모 테마', 'JAK 억제']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33800</v>
+        <v>91600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.21%</t>
+          <t>+4.21%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>57</v>
+        <v>345</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>221</v>
       </c>
       <c r="G13" t="n">
-        <v>189</v>
+        <v>1669</v>
       </c>
       <c r="H13" t="n">
-        <v>52.67</v>
+        <v>23.63</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>32750</v>
+        <v>87900</v>
       </c>
       <c r="K13" t="n">
-        <v>33700</v>
+        <v>91200</v>
       </c>
       <c r="L13" t="n">
-        <v>34350</v>
+        <v>93500</v>
       </c>
       <c r="M13" t="n">
-        <v>33450</v>
+        <v>90200</v>
       </c>
       <c r="N13" t="n">
-        <v>21.02</v>
+        <v>23.53</v>
       </c>
       <c r="O13" t="n">
-        <v>44485162425</v>
+        <v>280149092250</v>
       </c>
       <c r="P13" t="n">
-        <v>69500</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>30400</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>290000</v>
+        <v>-211000</v>
       </c>
       <c r="S13" t="n">
-        <v>157000</v>
+        <v>236000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 및 미국 원전 사업 추진 본격화. 공매도 물량 소화 후 상승 기대.</t>
+          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '원전', '공매도']</t>
+          <t>['원전', 'SMR', '텍사스']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1837000</v>
+        <v>1850000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+3.76%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F14" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G14" t="n">
-        <v>1837</v>
+        <v>2039</v>
       </c>
       <c r="H14" t="n">
         <v>50.63</v>
@@ -1714,7 +1714,7 @@
         <v>50.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2336835759500</v>
+        <v>2606620111500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>기관 및 외인 매수세 유입에 따른 반도체 업황 개선 기대. 치명적인 저평가 구간 진입.</t>
+          <t>낸드 메모리 품귀 현상 및 반도체 시즌2 도래 전망. 기관·외인 재매수세 유입되며 300만 돌파 기대감 고조. 자사주 매수 및 숏 악귀 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', '기관외인', '저평가']</t>
+          <t>['낸드 메모리', '반도체', '자사주 매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>273500</v>
+        <v>33850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+1.30%</t>
+          <t>+3.36%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>798</v>
+        <v>60</v>
       </c>
       <c r="F15" t="n">
-        <v>474</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>1751</v>
+        <v>220</v>
       </c>
       <c r="H15" t="n">
-        <v>46.79</v>
+        <v>52.67</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>270000</v>
+        <v>32750</v>
       </c>
       <c r="K15" t="n">
-        <v>272000</v>
+        <v>33700</v>
       </c>
       <c r="L15" t="n">
-        <v>275000</v>
+        <v>34350</v>
       </c>
       <c r="M15" t="n">
-        <v>269000</v>
+        <v>33450</v>
       </c>
       <c r="N15" t="n">
-        <v>46.73</v>
+        <v>21.02</v>
       </c>
       <c r="O15" t="n">
-        <v>1388196998500</v>
+        <v>48111481200</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>69500</v>
       </c>
       <c r="Q15" t="n">
-        <v>69600</v>
+        <v>30400</v>
       </c>
       <c r="R15" t="n">
-        <v>498000</v>
+        <v>290000</v>
       </c>
       <c r="S15" t="n">
-        <v>160000</v>
+        <v>157000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>자사주 매수 및 주주환원 정책 기대감. 단기적 공매도 및 개인 매물 출회.</t>
+          <t>미국 웨스팅하우스 지분 인수 및 원전 사업 관련 호재. PBR 저평가 및 공매도 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주매수', '주주환원', '공매도']</t>
+          <t>['웨스팅하우스', '원전', 'PBR']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10060</v>
+        <v>15050</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="G16" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H16" t="n">
-        <v>0.44</v>
+        <v>1.72</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,47 +1883,47 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>10200</v>
+        <v>14650</v>
       </c>
       <c r="K16" t="n">
-        <v>10600</v>
+        <v>15100</v>
       </c>
       <c r="L16" t="n">
-        <v>10970</v>
+        <v>16680</v>
       </c>
       <c r="M16" t="n">
-        <v>9980</v>
+        <v>14800</v>
       </c>
       <c r="N16" t="n">
-        <v>0.21</v>
+        <v>1.58</v>
       </c>
       <c r="O16" t="n">
-        <v>51064233465</v>
+        <v>42075117990</v>
       </c>
       <c r="P16" t="n">
-        <v>20850</v>
+        <v>21400</v>
       </c>
       <c r="Q16" t="n">
-        <v>4020</v>
+        <v>12090</v>
       </c>
       <c r="R16" t="n">
-        <v>-7000</v>
+        <v>35000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>터빈 블레이드 수주 기대감 및 뉴스 언급. 미국 가스터빈 독점 공급 관련 분석.</t>
+          <t>스카이랩스 대비 저평가 언급, 단타 및 자전거래 의혹, 보호예수 물량 주의.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['가스터빈', '수주', '독점공급']</t>
+          <t>['단타', '자전거래', '보호예수']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>0155E0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15560</v>
+        <v>276000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.41%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>62</v>
+        <v>799</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>464</v>
       </c>
       <c r="G17" t="n">
-        <v>243</v>
+        <v>1723</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>46.79</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>16110</v>
+        <v>270000</v>
       </c>
       <c r="K17" t="n">
-        <v>16130</v>
+        <v>272000</v>
       </c>
       <c r="L17" t="n">
-        <v>16140</v>
+        <v>276000</v>
       </c>
       <c r="M17" t="n">
-        <v>15310</v>
+        <v>269000</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>46.73</v>
       </c>
       <c r="O17" t="n">
-        <v>26097154465</v>
+        <v>1719792942750</v>
       </c>
       <c r="P17" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q17" t="n">
-        <v>3200</v>
+        <v>69600</v>
       </c>
       <c r="R17" t="n">
-        <v>-57000</v>
+        <v>498000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>호남 메가 프로젝트 및 대규모 투자 유치 기대감. 광주 개발 등 연계 호재 부각.</t>
+          <t>자사주 15조 매수 뉴스가 부각되며 주가 상승 기대감 형성. 그러나 일부 투자자들의 매도 움직임과 정치적 언급도 혼재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['메가프로젝트', '대규모투자', '광주개발']</t>
+          <t>['자사주 매수', '반도체']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8410</v>
+        <v>10200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-11.10%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="H18" t="n">
-        <v>38.84</v>
+        <v>0.44</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>9460</v>
+        <v>10200</v>
       </c>
       <c r="K18" t="n">
-        <v>9700</v>
+        <v>10600</v>
       </c>
       <c r="L18" t="n">
-        <v>9760</v>
+        <v>10970</v>
       </c>
       <c r="M18" t="n">
-        <v>8110</v>
+        <v>9980</v>
       </c>
       <c r="N18" t="n">
-        <v>38.69</v>
+        <v>0.21</v>
       </c>
       <c r="O18" t="n">
-        <v>20333802075</v>
+        <v>54619762390</v>
       </c>
       <c r="P18" t="n">
-        <v>19150</v>
+        <v>20850</v>
       </c>
       <c r="Q18" t="n">
-        <v>3445</v>
+        <v>4020</v>
       </c>
       <c r="R18" t="n">
-        <v>53000</v>
+        <v>-7000</v>
       </c>
       <c r="S18" t="n">
-        <v>-14000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>삼성, 포스코 관계사 상승 언급 및 차익 실현 가능성. 대차잔고 및 프로그램 매수 관련 논의.</t>
+          <t>터빈블레이드 수주 기대감, 원전 및 헷지주 분류 논란, 변동성 속 기대감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['관계사', '차익실현', '대차잔고']</t>
+          <t>['터빈블레이드', '수주', '가스터빈']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>340</v>
+        <v>15480</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-90.71%</t>
+          <t>-3.91%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="H19" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3660</v>
+        <v>16110</v>
       </c>
       <c r="K19" t="n">
-        <v>300</v>
+        <v>16130</v>
       </c>
       <c r="L19" t="n">
-        <v>340</v>
+        <v>16140</v>
       </c>
       <c r="M19" t="n">
-        <v>300</v>
+        <v>15310</v>
       </c>
       <c r="N19" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>614195520</v>
+        <v>28039386470</v>
       </c>
       <c r="P19" t="n">
-        <v>3660</v>
+        <v>19380</v>
       </c>
       <c r="Q19" t="n">
-        <v>300</v>
+        <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>38000</v>
+        <v>-57000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>감사의견 적정 확보에도 불구하고 유증 물량 및 재무 악화 우려. 급락 후 회복 기대.</t>
+          <t>반도체 섹터 조정과 건설주 상승 흐름 속에서 금호건설은 뚜렷한 호재 없이 부진. 광주공항 재개 등 일부 테마 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,18 +2199,294 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['감사의견', '유증', '재무악화']</t>
+          <t>['건설', '광주공항']</t>
         </is>
       </c>
       <c r="X19" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>002990</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>금호전기</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>12160</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-4.10%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E20" t="n">
+        <v>41</v>
+      </c>
+      <c r="F20" t="n">
+        <v>29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>105</v>
+      </c>
+      <c r="H20" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>12680</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12680</v>
+      </c>
+      <c r="L20" t="n">
+        <v>12680</v>
+      </c>
+      <c r="M20" t="n">
+        <v>11550</v>
+      </c>
+      <c r="N20" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="O20" t="n">
+        <v>21988104080</v>
+      </c>
+      <c r="P20" t="n">
+        <v>14350</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>465</v>
+      </c>
+      <c r="R20" t="n">
+        <v>9000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>계단식 하락 추세 지속되며 하한가 우려 제기. 반도체 섹터 조정과 외인 프로그램 매도세 속 투자 심리 위축.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['하락 추세', '반도체']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>001210</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>8430</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-10.89%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E21" t="n">
+        <v>52</v>
+      </c>
+      <c r="F21" t="n">
+        <v>32</v>
+      </c>
+      <c r="G21" t="n">
+        <v>116</v>
+      </c>
+      <c r="H21" t="n">
+        <v>38.84</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>9460</v>
+      </c>
+      <c r="K21" t="n">
+        <v>9700</v>
+      </c>
+      <c r="L21" t="n">
+        <v>9760</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8110</v>
+      </c>
+      <c r="N21" t="n">
+        <v>38.69</v>
+      </c>
+      <c r="O21" t="n">
+        <v>22510046425</v>
+      </c>
+      <c r="P21" t="n">
+        <v>19150</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3445</v>
+      </c>
+      <c r="R21" t="n">
+        <v>53000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-14000</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>삼성, 포스코 관계사 대비 부진, 매도 조장 및 대차잔고 관련 우려.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['포스코', '대차잔고', '매도 조장']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
         <v>1</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>033790</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>카프로</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>251</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-93.14%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>56</v>
+      </c>
+      <c r="F22" t="n">
+        <v>40</v>
+      </c>
+      <c r="G22" t="n">
+        <v>122</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>3660</v>
+      </c>
+      <c r="K22" t="n">
+        <v>300</v>
+      </c>
+      <c r="L22" t="n">
+        <v>340</v>
+      </c>
+      <c r="M22" t="n">
+        <v>251</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O22" t="n">
+        <v>668255900</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3660</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>251</v>
+      </c>
+      <c r="R22" t="n">
+        <v>38000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>감사의견 적정으로 거래 재개 기대감 있었으나, 유증 물량과 재무 상태에 대한 우려로 주가 급락. 향후 전망 불투명.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['감사의견', '유증']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>006380</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F2" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>140455533943</v>
+        <v>140745973183</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터, 6G 광통신 관련 정부 주관 사업 선정 뉴스가 부각되며 급등. AI 바람 재차 불면 추가 상승 기대감 높음.</t>
+          <t>AI 데이터센터 국산화 수행기관 선정 및 6G 광통신 부품 사업 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '정부 사업']</t>
+          <t>['AI', '데이터센터', '광통신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10640</v>
+        <v>10520</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+26.37%</t>
+          <t>+24.94%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>239541510935</v>
+        <v>245312281155</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 저출산 대책으로 미프진 관련주로 부각되며 상승 기대감 형성. 그러나 구체적인 공시나 뉴스는 부족.</t>
+          <t>정부의 미프진 도입 추진 관련 기대감. 투자 유치 및 상한가 기록.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미프진', '정부 정책']</t>
+          <t>['미프진', '정부 정책', '상한가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36900</v>
+        <v>36750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+20.79%</t>
+          <t>+20.29%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="F4" t="n">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="G4" t="n">
-        <v>738</v>
+        <v>756</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>683388640725</v>
+        <v>689420350825</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 지분 공시, 비교군 없는 신규 상장주로서의 기대감 및 급등 조짐.</t>
+          <t>정부 지분 공시와 세계 최초 비침습 혈당 측정 기술에 대한 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['신규주', '정부 지분', '주포']</t>
+          <t>['혈당 측정', '정부 지분', '기술']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4160</v>
+        <v>4110</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.20%</t>
+          <t>+14.80%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="H5" t="n">
         <v>1.56</v>
@@ -886,7 +886,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>192711605976</v>
+        <v>206199635125</v>
       </c>
       <c r="P5" t="n">
         <v>4335</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>탈모 건보료 적용 시 난리 날 것이라는 기대감과 함께 10년 매집 구간 돌파 및 30만 목표가 제시. 약효에 대한 긍정적 평가.</t>
+          <t>탈모 치료제 관련 기대감. 건보 적용 시 큰 상승 예상. 10년 매집 구간.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['탈모', '건보료', '신약']</t>
+          <t>['탈모 치료제', '건보 적용', '신약']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>137700</v>
+        <v>138800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+12.59%</t>
+          <t>+13.49%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.11</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H6" t="n">
         <v>13.33</v>
@@ -978,7 +978,7 @@
         <v>13.22</v>
       </c>
       <c r="O6" t="n">
-        <v>136963977850</v>
+        <v>140466722250</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 원전 8기 수주 관련 대형 사업 언급, AP1000 사업 및 웨스팅 지분 급물살.</t>
+          <t>미국 원전 8기 수주 가능성과 신사업 진출 재료로 인한 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', 'AP1000', '미국 수주']</t>
+          <t>['원전', '신사업', 'AP1000']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20450</v>
+        <v>20750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+11.08%</t>
+          <t>+12.71%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="F7" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G7" t="n">
-        <v>498</v>
+        <v>559</v>
       </c>
       <c r="H7" t="n">
         <v>10.47</v>
@@ -1061,7 +1061,7 @@
         <v>18800</v>
       </c>
       <c r="L7" t="n">
-        <v>20725</v>
+        <v>20850</v>
       </c>
       <c r="M7" t="n">
         <v>18480</v>
@@ -1070,7 +1070,7 @@
         <v>10.4</v>
       </c>
       <c r="O7" t="n">
-        <v>274267825940</v>
+        <v>291884232215</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원전 사업 복 터졌다는 기대감과 함께 2만 원 돌파 및 신사업 재료 발표 기대감 상승. 다만, 확정된 내용은 아직 없음.</t>
+          <t>원전 사업 수주 기대감에 따른 주가 상승. 미국 원전 건설 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '신사업', '건설']</t>
+          <t>['원전', '건설', '신사업']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+10.70%</t>
+          <t>+9.36%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H8" t="n">
         <v>5.34</v>
@@ -1162,7 +1162,7 @@
         <v>5.29</v>
       </c>
       <c r="O8" t="n">
-        <v>6781829232</v>
+        <v>6955160437</v>
       </c>
       <c r="P8" t="n">
         <v>901</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>상장폐지 가능성 속 정리매매 진행, 상속 지분 및 자산 가치 언급.</t>
+          <t>상장폐지 가능성 속 정리매매 시점과 회사 자산 가치에 대한 의견 대립.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['상장폐지', '정리매매', '자산 가치']</t>
+          <t>['상장폐지', '정리매매', '자산가치']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11700</v>
+        <v>11750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.14%</t>
+          <t>+7.60%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.11</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G9" t="n">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="H9" t="n">
         <v>5.42</v>
@@ -1254,7 +1254,7 @@
         <v>5.53</v>
       </c>
       <c r="O9" t="n">
-        <v>95919571905</v>
+        <v>97093519980</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원전 섹터 관련 협정 및 투자 소식, 공매도 상환 압박 및 2조 시총 논란.</t>
+          <t>프랑스와의 원자력 협정 및 대미 투자 관련 소식으로 인한 원전 섹터 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '프랑스 협정']</t>
+          <t>['원전', '원자력 협정', '대미 투자']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50400</v>
+        <v>50500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.00%</t>
+          <t>+5.21%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H10" t="n">
         <v>38.34</v>
@@ -1346,7 +1346,7 @@
         <v>38.24</v>
       </c>
       <c r="O10" t="n">
-        <v>92505033275</v>
+        <v>94481112375</v>
       </c>
       <c r="P10" t="n">
         <v>67300</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>건설주 전반의 상승세와 함께 원전, 재건 등 다양한 테마 기대감 존재. 그러나 단기 급등 후 조정 가능성 및 개인 매도세 관찰.</t>
+          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14100</v>
+        <v>14140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.68%</t>
+          <t>+4.97%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.12</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="H11" t="n">
         <v>1.94</v>
@@ -1438,7 +1438,7 @@
         <v>1.82</v>
       </c>
       <c r="O11" t="n">
-        <v>171748424080</v>
+        <v>173900879895</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Texas 소식과 함께 큰 폭 상승 기대, 공매도 물량 언급 및 매물대 소화 과정.</t>
+          <t>Texas 관련 소식과 투기과열지구 지정 판단일에 따른 변동성 예상.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '공매도', '매물대']</t>
+          <t>['광통신', '투기과열', 'Texas']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9180</v>
+        <v>9210</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.56%</t>
+          <t>+4.90%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F12" t="n">
         <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H12" t="n">
         <v>1.68</v>
@@ -1530,7 +1530,7 @@
         <v>1.72</v>
       </c>
       <c r="O12" t="n">
-        <v>90007819410</v>
+        <v>93687652650</v>
       </c>
       <c r="P12" t="n">
         <v>25050</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>91600</v>
+        <v>15310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+4.21%</t>
+          <t>+4.51%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="E13" t="n">
-        <v>345</v>
+        <v>42</v>
       </c>
       <c r="F13" t="n">
-        <v>221</v>
+        <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>1669</v>
+        <v>45</v>
       </c>
       <c r="H13" t="n">
-        <v>23.63</v>
+        <v>1.72</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>87900</v>
+        <v>14650</v>
       </c>
       <c r="K13" t="n">
-        <v>91200</v>
+        <v>15100</v>
       </c>
       <c r="L13" t="n">
-        <v>93500</v>
+        <v>16680</v>
       </c>
       <c r="M13" t="n">
-        <v>90200</v>
+        <v>14800</v>
       </c>
       <c r="N13" t="n">
-        <v>23.53</v>
+        <v>1.58</v>
       </c>
       <c r="O13" t="n">
-        <v>280149092250</v>
+        <v>42598164105</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>21400</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>12090</v>
       </c>
       <c r="R13" t="n">
-        <v>-211000</v>
+        <v>35000</v>
       </c>
       <c r="S13" t="n">
-        <v>236000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
+          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '텍사스']</t>
+          <t>['단주 거래', '자전거래', '스카이랩스']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>0155E0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1850000</v>
+        <v>91600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.76%</t>
+          <t>+4.21%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>798</v>
+        <v>351</v>
       </c>
       <c r="F14" t="n">
-        <v>477</v>
+        <v>222</v>
       </c>
       <c r="G14" t="n">
-        <v>2039</v>
+        <v>1694</v>
       </c>
       <c r="H14" t="n">
-        <v>50.63</v>
+        <v>23.63</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1783000</v>
+        <v>87900</v>
       </c>
       <c r="K14" t="n">
-        <v>1799000</v>
+        <v>91200</v>
       </c>
       <c r="L14" t="n">
-        <v>1860000</v>
+        <v>93500</v>
       </c>
       <c r="M14" t="n">
-        <v>1777000</v>
+        <v>90200</v>
       </c>
       <c r="N14" t="n">
-        <v>50.5</v>
+        <v>23.53</v>
       </c>
       <c r="O14" t="n">
-        <v>2606620111500</v>
+        <v>285380489700</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>274000</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>55000</v>
+        <v>-211000</v>
       </c>
       <c r="S14" t="n">
-        <v>71000</v>
+        <v>236000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>낸드 메모리 품귀 현상 및 반도체 시즌2 도래 전망. 기관·외인 재매수세 유입되며 300만 돌파 기대감 고조. 자사주 매수 및 숏 악귀 언급.</t>
+          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['낸드 메모리', '반도체', '자사주 매수']</t>
+          <t>['원전', 'SMR', '텍사스']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1763,27 +1763,27 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33850</v>
+        <v>34100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+4.12%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F15" t="n">
         <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H15" t="n">
-        <v>52.67</v>
+        <v>52.69</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>21.02</v>
       </c>
       <c r="O15" t="n">
-        <v>48111481200</v>
+        <v>50851841650</v>
       </c>
       <c r="P15" t="n">
         <v>69500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 웨스팅하우스 지분 인수 및 원전 사업 관련 호재. PBR 저평가 및 공매도 언급.</t>
+          <t>미국 원전 사업 투자 기대감으로 인한 주가 상승. 공매도 세력과의 공방.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '원전', 'PBR']</t>
+          <t>['원전', '투자', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15050</v>
+        <v>1855000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.73%</t>
+          <t>+4.04%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>797</v>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>478</v>
       </c>
       <c r="G16" t="n">
-        <v>42</v>
+        <v>2101</v>
       </c>
       <c r="H16" t="n">
-        <v>1.72</v>
+        <v>50.63</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14650</v>
+        <v>1783000</v>
       </c>
       <c r="K16" t="n">
-        <v>15100</v>
+        <v>1799000</v>
       </c>
       <c r="L16" t="n">
-        <v>16680</v>
+        <v>1860000</v>
       </c>
       <c r="M16" t="n">
-        <v>14800</v>
+        <v>1777000</v>
       </c>
       <c r="N16" t="n">
-        <v>1.58</v>
+        <v>50.5</v>
       </c>
       <c r="O16" t="n">
-        <v>42075117990</v>
+        <v>2737120166500</v>
       </c>
       <c r="P16" t="n">
-        <v>21400</v>
+        <v>2987000</v>
       </c>
       <c r="Q16" t="n">
-        <v>12090</v>
+        <v>274000</v>
       </c>
       <c r="R16" t="n">
-        <v>35000</v>
+        <v>55000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>스카이랩스 대비 저평가 언급, 단타 및 자전거래 의혹, 보호예수 물량 주의.</t>
+          <t>낸드 메모리 품귀 현상 및 AI 반도체 시장 성장 기대. 30만 전자 목표.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['단타', '자전거래', '보호예수']</t>
+          <t>['낸드', 'AI 반도체', '품귀']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0155E0</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>276000</v>
+        <v>276750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+2.50%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="F17" t="n">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="G17" t="n">
-        <v>1723</v>
+        <v>1641</v>
       </c>
       <c r="H17" t="n">
         <v>46.79</v>
@@ -1981,7 +1981,7 @@
         <v>272000</v>
       </c>
       <c r="L17" t="n">
-        <v>276000</v>
+        <v>277000</v>
       </c>
       <c r="M17" t="n">
         <v>269000</v>
@@ -1990,7 +1990,7 @@
         <v>46.73</v>
       </c>
       <c r="O17" t="n">
-        <v>1719792942750</v>
+        <v>1865055266750</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>자사주 15조 매수 뉴스가 부각되며 주가 상승 기대감 형성. 그러나 일부 투자자들의 매도 움직임과 정치적 언급도 혼재.</t>
+          <t>자사주 매수 및 배당 확대 발표에 따른 주가 상승 기대. 30만 전자 목표.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['자사주 매수', '반도체']</t>
+          <t>['주주환원', '자사주 매수', '배당']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10200</v>
+        <v>10330</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+1.27%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.23</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H18" t="n">
         <v>0.44</v>
@@ -2082,7 +2082,7 @@
         <v>0.21</v>
       </c>
       <c r="O18" t="n">
-        <v>54619762390</v>
+        <v>55680042645</v>
       </c>
       <c r="P18" t="n">
         <v>20850</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>터빈블레이드 수주 기대감, 원전 및 헷지주 분류 논란, 변동성 속 기대감.</t>
+          <t>터빈블레이드 수주 기대감에도 불구하고 주가 움직임에 대한 답답함.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['터빈블레이드', '수주', '가스터빈']</t>
+          <t>['터빈블레이드', '수주', '강재료']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15480</v>
+        <v>15510</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.91%</t>
+          <t>-3.72%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>28039386470</v>
+        <v>28751256630</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>반도체 섹터 조정과 건설주 상승 흐름 속에서 금호건설은 뚜렷한 호재 없이 부진. 광주공항 재개 등 일부 테마 언급.</t>
+          <t>건설주 강세 속 주가 부진. 대규모 투자 프로젝트 관련 언급 및 반등 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['건설', '광주공항']</t>
+          <t>['건설', '투자', '반등']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12160</v>
+        <v>12110</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.10%</t>
+          <t>-4.50%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H20" t="n">
         <v>17.11</v>
@@ -2266,7 +2266,7 @@
         <v>18.05</v>
       </c>
       <c r="O20" t="n">
-        <v>21988104080</v>
+        <v>22719290910</v>
       </c>
       <c r="P20" t="n">
         <v>14350</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>계단식 하락 추세 지속되며 하한가 우려 제기. 반도체 섹터 조정과 외인 프로그램 매도세 속 투자 심리 위축.</t>
+          <t>계단식 하락 및 하한가 가능성 언급. 투자자들의 공포 심리 확산.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['하락 추세', '반도체']</t>
+          <t>['하락', '하한가', '공포']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8430</v>
+        <v>8440</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-10.89%</t>
+          <t>-10.78%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H21" t="n">
         <v>38.84</v>
@@ -2358,7 +2358,7 @@
         <v>38.69</v>
       </c>
       <c r="O21" t="n">
-        <v>22510046425</v>
+        <v>23113652335</v>
       </c>
       <c r="P21" t="n">
         <v>19150</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>삼성, 포스코 관계사 대비 부진, 매도 조장 및 대차잔고 관련 우려.</t>
+          <t>삼성, 포스코 관련주 상승 대비 부진한 주가 흐름과 조정에 대한 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['포스코', '대차잔고', '매도 조장']</t>
+          <t>['포스코', '삼성', '조정']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2418,13 +2418,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G22" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="H22" t="n">
         <v>0.08</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>감사의견 적정으로 거래 재개 기대감 있었으나, 유증 물량과 재무 상태에 대한 우려로 주가 급락. 향후 전망 불투명.</t>
+          <t>감사의견 적정 판정 후 주가 급락. 재무 건전성 우려 및 상폐 가능성 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['감사의견', '유증']</t>
+          <t>['감사의견', '재무', '상장폐지']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>140745973183</v>
+        <v>140894492463</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -619,23 +619,23 @@
         <v>592</v>
       </c>
       <c r="R2" t="n">
-        <v>832000</v>
+        <v>1255000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 국산화 수행기관 선정 및 6G 광통신 부품 사업 기대감.</t>
+          <t>AI 데이터센터 및 6G 광통신 부품 국산화 사업 선정. 정부 주관 사업 참여 관련 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', '데이터센터', '광통신']</t>
+          <t>['AI 데이터센터', '6G', '광통신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10520</v>
+        <v>10500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+24.94%</t>
+          <t>+24.70%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
+        <v>151</v>
+      </c>
+      <c r="F3" t="n">
+        <v>86</v>
+      </c>
+      <c r="G3" t="n">
         <v>140</v>
-      </c>
-      <c r="F3" t="n">
-        <v>81</v>
-      </c>
-      <c r="G3" t="n">
-        <v>125</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>245312281155</v>
+        <v>249629237955</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -711,23 +711,23 @@
         <v>3500</v>
       </c>
       <c r="R3" t="n">
-        <v>-3000</v>
+        <v>57000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 미프진 도입 추진 관련 기대감. 투자 유치 및 상한가 기록.</t>
+          <t>정부의 미프진 도입 구체화 및 전략적 투자 관련 논의. 긍정적 기대감과 함께 일부 부정적 전망도 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미프진', '정부 정책', '상한가']</t>
+          <t>['미프진', '정부 정책', '낙태약']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36750</v>
+        <v>36700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+20.29%</t>
+          <t>+20.13%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="F4" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="G4" t="n">
-        <v>756</v>
+        <v>801</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>689420350825</v>
+        <v>699629355875</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -803,14 +803,14 @@
         <v>8200</v>
       </c>
       <c r="R4" t="n">
-        <v>-36000</v>
+        <v>-49000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 지분 공시와 세계 최초 비침습 혈당 측정 기술에 대한 기대감.</t>
+          <t>정부 지분 공시 및 세계 최초 비대면 진료 플랫폼 개발 관련 논의. 11시 급등 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['혈당 측정', '정부 지분', '기술']</t>
+          <t>['비대면 진료', '정부 지분', '플랫폼']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4110</v>
+        <v>4070</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+14.80%</t>
+          <t>+13.69%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H5" t="n">
         <v>1.56</v>
@@ -886,7 +886,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>206199635125</v>
+        <v>213803012109</v>
       </c>
       <c r="P5" t="n">
         <v>4335</v>
@@ -895,23 +895,23 @@
         <v>1246</v>
       </c>
       <c r="R5" t="n">
-        <v>169000</v>
+        <v>-338000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>탈모 치료제 관련 기대감. 건보 적용 시 큰 상승 예상. 10년 매집 구간.</t>
+          <t>탈모 치료제 관련 기대감과 함께 건보료 적용 가능성 논의. 목표가 30만 원 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '건보 적용', '신약']</t>
+          <t>['탈모 치료제', '건보료', '신약']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>138800</v>
+        <v>138300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+13.49%</t>
+          <t>+13.08%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.11</v>
       </c>
       <c r="E6" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H6" t="n">
         <v>13.33</v>
@@ -978,7 +978,7 @@
         <v>13.22</v>
       </c>
       <c r="O6" t="n">
-        <v>140466722250</v>
+        <v>143420195500</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -987,23 +987,23 @@
         <v>77100</v>
       </c>
       <c r="R6" t="n">
-        <v>-37000</v>
+        <v>-11000</v>
       </c>
       <c r="S6" t="n">
-        <v>51000</v>
+        <v>64000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 원전 8기 수주 가능성과 신사업 진출 재료로 인한 기대감.</t>
+          <t>미국 원전 8기 수주 및 260조 사업 관련 논의. 웨스팅 지분 급물살 및 신사업 진출 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '신사업', 'AP1000']</t>
+          <t>['원전', '미국 수주', '260조 사업']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20750</v>
+        <v>20650</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+12.71%</t>
+          <t>+12.17%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="F7" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G7" t="n">
-        <v>559</v>
+        <v>607</v>
       </c>
       <c r="H7" t="n">
         <v>10.47</v>
@@ -1070,7 +1070,7 @@
         <v>10.4</v>
       </c>
       <c r="O7" t="n">
-        <v>291884232215</v>
+        <v>303977118915</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1079,23 +1079,23 @@
         <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-8000</v>
+        <v>256000</v>
       </c>
       <c r="S7" t="n">
-        <v>85000</v>
+        <v>207000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원전 사업 수주 기대감에 따른 주가 상승. 미국 원전 건설 관련 긍정적 전망.</t>
+          <t>미국 원전 건설 수주 및 에너지 인프라 사업 확대 기대감. 2만 원 돌파 및 시총 저평가 논의.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '건설', '신사업']</t>
+          <t>['원전', '에너지 인프라', '수주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>327</v>
+        <v>11830</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.36%</t>
+          <t>+8.33%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="E8" t="n">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="G8" t="n">
-        <v>39</v>
+        <v>250</v>
       </c>
       <c r="H8" t="n">
-        <v>5.34</v>
+        <v>5.42</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>299</v>
+        <v>10920</v>
       </c>
       <c r="K8" t="n">
-        <v>220</v>
+        <v>11300</v>
       </c>
       <c r="L8" t="n">
-        <v>349</v>
+        <v>12700</v>
       </c>
       <c r="M8" t="n">
-        <v>220</v>
+        <v>11050</v>
       </c>
       <c r="N8" t="n">
-        <v>5.29</v>
+        <v>5.53</v>
       </c>
       <c r="O8" t="n">
-        <v>6955160437</v>
+        <v>99115349020</v>
       </c>
       <c r="P8" t="n">
-        <v>901</v>
+        <v>30200</v>
       </c>
       <c r="Q8" t="n">
-        <v>217</v>
+        <v>3540</v>
       </c>
       <c r="R8" t="n">
-        <v>645000</v>
+        <v>-712000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>상장폐지 가능성 속 정리매매 시점과 회사 자산 가치에 대한 의견 대립.</t>
+          <t>원전 섹터 전반의 상승세 및 프랑스와의 원자력 협정 소식. 15000원 목표가 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['상장폐지', '정리매매', '자산가치']</t>
+          <t>['원전', '원자력 협정', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11750</v>
+        <v>323</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.60%</t>
+          <t>+8.03%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.11</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="F9" t="n">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>246</v>
+        <v>44</v>
       </c>
       <c r="H9" t="n">
-        <v>5.42</v>
+        <v>5.34</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10920</v>
+        <v>299</v>
       </c>
       <c r="K9" t="n">
-        <v>11300</v>
+        <v>220</v>
       </c>
       <c r="L9" t="n">
-        <v>12700</v>
+        <v>349</v>
       </c>
       <c r="M9" t="n">
-        <v>11050</v>
+        <v>220</v>
       </c>
       <c r="N9" t="n">
-        <v>5.53</v>
+        <v>5.29</v>
       </c>
       <c r="O9" t="n">
-        <v>97093519980</v>
+        <v>7094841844</v>
       </c>
       <c r="P9" t="n">
-        <v>30200</v>
+        <v>901</v>
       </c>
       <c r="Q9" t="n">
-        <v>3540</v>
+        <v>217</v>
       </c>
       <c r="R9" t="n">
-        <v>-212000</v>
+        <v>727000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>프랑스와의 원자력 협정 및 대미 투자 관련 소식으로 인한 원전 섹터 기대감.</t>
+          <t>상장폐지 가능성 속 정리매매 시점과 회사 자산 가치에 대한 의견 대립.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '원자력 협정', '대미 투자']</t>
+          <t>['상장폐지', '정리매매', '자산가치']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50500</v>
+        <v>50700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.21%</t>
+          <t>+5.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="H10" t="n">
         <v>38.34</v>
@@ -1346,7 +1346,7 @@
         <v>38.24</v>
       </c>
       <c r="O10" t="n">
-        <v>94481112375</v>
+        <v>98039533975</v>
       </c>
       <c r="P10" t="n">
         <v>67300</v>
@@ -1355,10 +1355,10 @@
         <v>23150</v>
       </c>
       <c r="R10" t="n">
-        <v>266000</v>
+        <v>275000</v>
       </c>
       <c r="S10" t="n">
-        <v>40000</v>
+        <v>66000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14140</v>
+        <v>14210</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.97%</t>
+          <t>+5.49%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.12</v>
       </c>
       <c r="E11" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G11" t="n">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="H11" t="n">
         <v>1.94</v>
@@ -1438,7 +1438,7 @@
         <v>1.82</v>
       </c>
       <c r="O11" t="n">
-        <v>173900879895</v>
+        <v>176522062170</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1447,14 +1447,14 @@
         <v>1252</v>
       </c>
       <c r="R11" t="n">
-        <v>20000</v>
+        <v>-161000</v>
       </c>
       <c r="S11" t="n">
-        <v>5000</v>
+        <v>11000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Texas 관련 소식과 투기과열지구 지정 판단일에 따른 변동성 예상.</t>
+          <t>Texas 관련 소식 및 광통신 사업 관련 논의. 투기과열종목 지정 여부 판단 시점.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '투기과열', 'Texas']</t>
+          <t>['광통신', 'Texas', '투기과열']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9210</v>
+        <v>15250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.90%</t>
+          <t>+4.10%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>0.14</v>
       </c>
       <c r="E12" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H12" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8780</v>
+        <v>14650</v>
       </c>
       <c r="K12" t="n">
-        <v>9060</v>
+        <v>15100</v>
       </c>
       <c r="L12" t="n">
-        <v>9960</v>
+        <v>16680</v>
       </c>
       <c r="M12" t="n">
-        <v>8270</v>
+        <v>14800</v>
       </c>
       <c r="N12" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="O12" t="n">
-        <v>93687652650</v>
+        <v>43604548790</v>
       </c>
       <c r="P12" t="n">
-        <v>25050</v>
+        <v>21400</v>
       </c>
       <c r="Q12" t="n">
-        <v>3705</v>
+        <v>12090</v>
       </c>
       <c r="R12" t="n">
-        <v>51000</v>
+        <v>-3000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
+          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['투경', '탈모 테마', 'JAK 억제']</t>
+          <t>['단주 거래', '자전거래', '스카이랩스']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,99 +1568,99 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>0155E0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15310</v>
+        <v>34050</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+4.51%</t>
+          <t>+3.97%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.14</v>
+        <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="F13" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>45</v>
+        <v>228</v>
       </c>
       <c r="H13" t="n">
-        <v>1.72</v>
+        <v>52.68</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14650</v>
+        <v>32750</v>
       </c>
       <c r="K13" t="n">
-        <v>15100</v>
+        <v>33700</v>
       </c>
       <c r="L13" t="n">
-        <v>16680</v>
+        <v>34350</v>
       </c>
       <c r="M13" t="n">
-        <v>14800</v>
+        <v>33450</v>
       </c>
       <c r="N13" t="n">
-        <v>1.58</v>
+        <v>21.02</v>
       </c>
       <c r="O13" t="n">
-        <v>42598164105</v>
+        <v>52633435675</v>
       </c>
       <c r="P13" t="n">
-        <v>21400</v>
+        <v>69500</v>
       </c>
       <c r="Q13" t="n">
-        <v>12090</v>
+        <v>30400</v>
       </c>
       <c r="R13" t="n">
-        <v>35000</v>
+        <v>324000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>194000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
+          <t>미국 원전 사업 투자 기대감으로 인한 주가 상승. 공매도 세력과의 공방.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['단주 거래', '자전거래', '스카이랩스']</t>
+          <t>['원전', '투자', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0155E0</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>91600</v>
+        <v>91300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+4.21%</t>
+          <t>+3.87%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F14" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="G14" t="n">
-        <v>1694</v>
+        <v>1722</v>
       </c>
       <c r="H14" t="n">
         <v>23.63</v>
@@ -1714,7 +1714,7 @@
         <v>23.53</v>
       </c>
       <c r="O14" t="n">
-        <v>285380489700</v>
+        <v>291287379200</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1723,10 +1723,10 @@
         <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-211000</v>
+        <v>-222000</v>
       </c>
       <c r="S14" t="n">
-        <v>236000</v>
+        <v>267000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1759,92 +1759,92 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34100</v>
+        <v>9120</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+4.12%</t>
+          <t>+3.87%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>224</v>
+        <v>31</v>
       </c>
       <c r="H15" t="n">
-        <v>52.69</v>
+        <v>1.68</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>32750</v>
+        <v>8780</v>
       </c>
       <c r="K15" t="n">
-        <v>33700</v>
+        <v>9060</v>
       </c>
       <c r="L15" t="n">
-        <v>34350</v>
+        <v>9960</v>
       </c>
       <c r="M15" t="n">
-        <v>33450</v>
+        <v>8270</v>
       </c>
       <c r="N15" t="n">
-        <v>21.02</v>
+        <v>1.72</v>
       </c>
       <c r="O15" t="n">
-        <v>50851841650</v>
+        <v>96313536550</v>
       </c>
       <c r="P15" t="n">
-        <v>69500</v>
+        <v>25050</v>
       </c>
       <c r="Q15" t="n">
-        <v>30400</v>
+        <v>3705</v>
       </c>
       <c r="R15" t="n">
-        <v>290000</v>
+        <v>-59000</v>
       </c>
       <c r="S15" t="n">
-        <v>157000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 원전 사업 투자 기대감으로 인한 주가 상승. 공매도 세력과의 공방.</t>
+          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', '투자', '공매도']</t>
+          <t>['투경', '탈모 테마', 'JAK 억제']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1855000</v>
+        <v>1851500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+4.04%</t>
+          <t>+3.84%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.13</v>
       </c>
       <c r="E16" t="n">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F16" t="n">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="G16" t="n">
-        <v>2101</v>
+        <v>2187</v>
       </c>
       <c r="H16" t="n">
         <v>50.63</v>
@@ -1898,7 +1898,7 @@
         <v>50.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2737120166500</v>
+        <v>2928879682000</v>
       </c>
       <c r="P16" t="n">
         <v>2987000</v>
@@ -1907,14 +1907,14 @@
         <v>274000</v>
       </c>
       <c r="R16" t="n">
-        <v>55000</v>
+        <v>-8000</v>
       </c>
       <c r="S16" t="n">
-        <v>71000</v>
+        <v>108000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>낸드 메모리 품귀 현상 및 AI 반도체 시장 성장 기대. 30만 전자 목표.</t>
+          <t>메모리 반도체 품귀 현상 및 재고 감소 추세. 300만 원 돌파 목표 및 기관/외인 매수세 유입 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['낸드', 'AI 반도체', '품귀']</t>
+          <t>['반도체', '메모리', '재고']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>276750</v>
+        <v>276500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+2.50%</t>
+          <t>+2.41%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>796</v>
       </c>
       <c r="F17" t="n">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="G17" t="n">
-        <v>1641</v>
+        <v>1659</v>
       </c>
       <c r="H17" t="n">
         <v>46.79</v>
@@ -1981,7 +1981,7 @@
         <v>272000</v>
       </c>
       <c r="L17" t="n">
-        <v>277000</v>
+        <v>277500</v>
       </c>
       <c r="M17" t="n">
         <v>269000</v>
@@ -1990,7 +1990,7 @@
         <v>46.73</v>
       </c>
       <c r="O17" t="n">
-        <v>1865055266750</v>
+        <v>2082423099250</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -1999,23 +1999,23 @@
         <v>69600</v>
       </c>
       <c r="R17" t="n">
-        <v>498000</v>
+        <v>1295000</v>
       </c>
       <c r="S17" t="n">
-        <v>160000</v>
+        <v>223000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>자사주 매수 및 배당 확대 발표에 따른 주가 상승 기대. 30만 전자 목표.</t>
+          <t>자사주 15조 매수 발표 및 주주환원 정책 기대감. 반도체 사업 및 로봇 출시 관련 논의.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주주환원', '자사주 매수', '배당']</t>
+          <t>['자사주 매수', '주주환원', '반도체']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10330</v>
+        <v>10260</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+1.27%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H18" t="n">
         <v>0.44</v>
@@ -2082,7 +2082,7 @@
         <v>0.21</v>
       </c>
       <c r="O18" t="n">
-        <v>55680042645</v>
+        <v>56403892280</v>
       </c>
       <c r="P18" t="n">
         <v>20850</v>
@@ -2091,7 +2091,7 @@
         <v>4020</v>
       </c>
       <c r="R18" t="n">
-        <v>-7000</v>
+        <v>-59000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15510</v>
+        <v>15490</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.72%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
         <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>28751256630</v>
+        <v>29224130810</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>
@@ -2183,7 +2183,7 @@
         <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>-57000</v>
+        <v>-5000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12110</v>
+        <v>12120</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.50%</t>
+          <t>-4.42%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F20" t="n">
         <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H20" t="n">
         <v>17.11</v>
@@ -2266,7 +2266,7 @@
         <v>18.05</v>
       </c>
       <c r="O20" t="n">
-        <v>22719290910</v>
+        <v>23389261050</v>
       </c>
       <c r="P20" t="n">
         <v>14350</v>
@@ -2275,7 +2275,7 @@
         <v>465</v>
       </c>
       <c r="R20" t="n">
-        <v>9000</v>
+        <v>48000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8440</v>
+        <v>8400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-10.78%</t>
+          <t>-11.21%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G21" t="n">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="H21" t="n">
         <v>38.84</v>
@@ -2358,7 +2358,7 @@
         <v>38.69</v>
       </c>
       <c r="O21" t="n">
-        <v>23113652335</v>
+        <v>23893961760</v>
       </c>
       <c r="P21" t="n">
         <v>19150</v>
@@ -2367,10 +2367,10 @@
         <v>3445</v>
       </c>
       <c r="R21" t="n">
-        <v>53000</v>
+        <v>-32000</v>
       </c>
       <c r="S21" t="n">
-        <v>-14000</v>
+        <v>-106000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2418,13 +2418,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G22" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H22" t="n">
         <v>0.08</v>
@@ -2450,7 +2450,7 @@
         <v>0.08</v>
       </c>
       <c r="O22" t="n">
-        <v>668255900</v>
+        <v>769787659</v>
       </c>
       <c r="P22" t="n">
         <v>3660</v>
@@ -2459,7 +2459,7 @@
         <v>251</v>
       </c>
       <c r="R22" t="n">
-        <v>38000</v>
+        <v>-2000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
         <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>140894492463</v>
+        <v>141041748663</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 및 6G 광통신 부품 국산화 사업 선정. 정부 주관 사업 참여 관련 기대감.</t>
+          <t>AI 데이터센터 관련 정부 주관 사업 선정 및 국산화 수행 기관 지정 사실이 부각됨. 광통신 사업과의 연관성을 언급하며 주가 상승 가능성을 제기함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '6G', '광통신']</t>
+          <t>['AI 데이터센터', '광통신', '정부 사업']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10500</v>
+        <v>10410</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+24.70%</t>
+          <t>+23.63%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F3" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G3" t="n">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>249629237955</v>
+        <v>253071240960</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 미프진 도입 구체화 및 전략적 투자 관련 논의. 긍정적 기대감과 함께 일부 부정적 전망도 존재.</t>
+          <t>정부의 미프진 도입 구체화 및 연내 허가 관련 뉴스가 언급되며 주가 상승 기대감이 형성됨. 다만, 관련 뉴스 인용 외 구체적인 실적 근거는 부족함.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미프진', '정부 정책', '낙태약']</t>
+          <t>['미프진', '정부 도입', '연내 허가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36700</v>
+        <v>37100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+20.13%</t>
+          <t>+21.44%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="F4" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G4" t="n">
-        <v>801</v>
+        <v>825</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>699629355875</v>
+        <v>707071245950</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 지분 공시 및 세계 최초 비대면 진료 플랫폼 개발 관련 논의. 11시 급등 기대감.</t>
+          <t>세계 최초 반지형 웨어러블 디바이스 관련 기술력과 정부 지분 공시 등 긍정적 요인이 부각되며 급등 기대감이 형성됨. 주포 개입 가능성을 언급하며 강한 상승세를 예상함.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['비대면 진료', '정부 지분', '플랫폼']</t>
+          <t>['웨어러블 디바이스', '정부 지분', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4070</v>
+        <v>139200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+13.69%</t>
+          <t>+13.82%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.31</v>
+        <v>0.11</v>
       </c>
       <c r="E5" t="n">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="H5" t="n">
-        <v>1.56</v>
+        <v>13.33</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3580</v>
+        <v>122300</v>
       </c>
       <c r="K5" t="n">
-        <v>3600</v>
+        <v>129400</v>
       </c>
       <c r="L5" t="n">
-        <v>4335</v>
+        <v>143100</v>
       </c>
       <c r="M5" t="n">
-        <v>3450</v>
+        <v>128100</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>13.22</v>
       </c>
       <c r="O5" t="n">
-        <v>213803012109</v>
+        <v>146761411400</v>
       </c>
       <c r="P5" t="n">
-        <v>4335</v>
+        <v>198000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1246</v>
+        <v>77100</v>
       </c>
       <c r="R5" t="n">
-        <v>-338000</v>
+        <v>-11000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>64000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>탈모 치료제 관련 기대감과 함께 건보료 적용 가능성 논의. 목표가 30만 원 제시.</t>
+          <t>미국 원전 8기 수주 관련 260조 사업 규모의 구체적인 내용과 수익 계산법이 제시되며 긍정적인 전망이 우세함. 기관 및 연기금의 순매수세 유입도 긍정적 신호로 작용함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '건보료', '신약']</t>
+          <t>['원전 사업', '260조', '기관 연기금']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>052690</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>138300</v>
+        <v>4070</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+13.08%</t>
+          <t>+13.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.11</v>
+        <v>0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>151</v>
+        <v>205</v>
       </c>
       <c r="H6" t="n">
-        <v>13.33</v>
+        <v>1.56</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>122300</v>
+        <v>3580</v>
       </c>
       <c r="K6" t="n">
-        <v>129400</v>
+        <v>3600</v>
       </c>
       <c r="L6" t="n">
-        <v>143100</v>
+        <v>4335</v>
       </c>
       <c r="M6" t="n">
-        <v>128100</v>
+        <v>3450</v>
       </c>
       <c r="N6" t="n">
-        <v>13.22</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>143420195500</v>
+        <v>220133090515</v>
       </c>
       <c r="P6" t="n">
-        <v>198000</v>
+        <v>4335</v>
       </c>
       <c r="Q6" t="n">
-        <v>77100</v>
+        <v>1246</v>
       </c>
       <c r="R6" t="n">
-        <v>-11000</v>
+        <v>-338000</v>
       </c>
       <c r="S6" t="n">
-        <v>64000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 원전 8기 수주 및 260조 사업 관련 논의. 웨스팅 지분 급물살 및 신사업 진출 기대.</t>
+          <t>탈모 치료제 관련 건보료 적용 기대감으로 긍정적인 논조가 형성됨. 다만, 구체적인 실적 발표나 공시보다는 기대감에 기반한 언급이 주를 이룸.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '미국 수주', '260조 사업']</t>
+          <t>['탈모 치료제', '건보료 적용', '기대감']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20650</v>
+        <v>20600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+12.17%</t>
+          <t>+11.90%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="F7" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G7" t="n">
-        <v>607</v>
+        <v>654</v>
       </c>
       <c r="H7" t="n">
         <v>10.47</v>
@@ -1070,7 +1070,7 @@
         <v>10.4</v>
       </c>
       <c r="O7" t="n">
-        <v>303977118915</v>
+        <v>311660409665</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 원전 건설 수주 및 에너지 인프라 사업 확대 기대감. 2만 원 돌파 및 시총 저평가 논의.</t>
+          <t>원전 사업 수주 및 미국 원전 건설 관련 뉴스가 부각되며 주가 상승 기대감이 높음. 2만 돌파 및 시가총액 저평가 의견이 제시되며 긍정적인 전망을 보임.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '에너지 인프라', '수주']</t>
+          <t>['원전', '신사업', '미국 건설']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11830</v>
+        <v>11990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.33%</t>
+          <t>+9.80%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.11</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F8" t="n">
         <v>73</v>
       </c>
       <c r="G8" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="H8" t="n">
         <v>5.42</v>
@@ -1162,7 +1162,7 @@
         <v>5.53</v>
       </c>
       <c r="O8" t="n">
-        <v>99115349020</v>
+        <v>101739671470</v>
       </c>
       <c r="P8" t="n">
         <v>30200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원전 섹터 전반의 상승세 및 프랑스와의 원자력 협정 소식. 15000원 목표가 제시.</t>
+          <t>프랑스와의 원자력 협정 체결 및 미국 원전 8기 수주 관련 뉴스가 주가 상승 모멘텀으로 작용하고 있음. 원전 섹터 전반의 강세와 함께 긍정적 전망을 보임.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '원자력 협정', '공매도']</t>
+          <t>['원자력 협정', '미국 원전', '원전 섹터']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.03%</t>
+          <t>+7.02%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H9" t="n">
         <v>5.34</v>
@@ -1254,7 +1254,7 @@
         <v>5.29</v>
       </c>
       <c r="O9" t="n">
-        <v>7094841844</v>
+        <v>7191481676</v>
       </c>
       <c r="P9" t="n">
         <v>901</v>
@@ -1299,276 +1299,276 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50700</v>
+        <v>14150</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.62%</t>
+          <t>+5.05%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="G10" t="n">
-        <v>188</v>
+        <v>425</v>
       </c>
       <c r="H10" t="n">
-        <v>38.34</v>
+        <v>1.94</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>48000</v>
+        <v>13470</v>
       </c>
       <c r="K10" t="n">
-        <v>48550</v>
+        <v>13580</v>
       </c>
       <c r="L10" t="n">
-        <v>51600</v>
+        <v>14450</v>
       </c>
       <c r="M10" t="n">
-        <v>48350</v>
+        <v>13420</v>
       </c>
       <c r="N10" t="n">
-        <v>38.24</v>
+        <v>1.82</v>
       </c>
       <c r="O10" t="n">
-        <v>98039533975</v>
+        <v>178608753115</v>
       </c>
       <c r="P10" t="n">
-        <v>67300</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>23150</v>
+        <v>1252</v>
       </c>
       <c r="R10" t="n">
-        <v>275000</v>
+        <v>-161000</v>
       </c>
       <c r="S10" t="n">
-        <v>66000</v>
+        <v>11000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
+          <t>Texas 관련 소식 및 광통신 섹터 전반의 긍정적 분위기 속에서 주가 상승 기대감이 형성됨. 공매도 물량 언급과 함께 투경 재지정 여부가 주목받고 있음.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['건설', '원전', '재건']</t>
+          <t>['광통신', 'Texas', '투경']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14210</v>
+        <v>50400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.49%</t>
+          <t>+5.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>404</v>
+        <v>188</v>
       </c>
       <c r="H11" t="n">
-        <v>1.94</v>
+        <v>38.34</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13470</v>
+        <v>48000</v>
       </c>
       <c r="K11" t="n">
-        <v>13580</v>
+        <v>48550</v>
       </c>
       <c r="L11" t="n">
-        <v>14450</v>
+        <v>51600</v>
       </c>
       <c r="M11" t="n">
-        <v>13420</v>
+        <v>48350</v>
       </c>
       <c r="N11" t="n">
-        <v>1.82</v>
+        <v>38.24</v>
       </c>
       <c r="O11" t="n">
-        <v>176522062170</v>
+        <v>100309016575</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>67300</v>
       </c>
       <c r="Q11" t="n">
-        <v>1252</v>
+        <v>23150</v>
       </c>
       <c r="R11" t="n">
-        <v>-161000</v>
+        <v>275000</v>
       </c>
       <c r="S11" t="n">
-        <v>11000</v>
+        <v>66000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Texas 관련 소식 및 광통신 사업 관련 논의. 투기과열종목 지정 여부 판단 시점.</t>
+          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', 'Texas', '투기과열']</t>
+          <t>['건설', '원전', '재건']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15250</v>
+        <v>92000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.10%</t>
+          <t>+4.66%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>364</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>232</v>
       </c>
       <c r="G12" t="n">
-        <v>46</v>
+        <v>1701</v>
       </c>
       <c r="H12" t="n">
-        <v>1.72</v>
+        <v>23.63</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14650</v>
+        <v>87900</v>
       </c>
       <c r="K12" t="n">
-        <v>15100</v>
+        <v>91200</v>
       </c>
       <c r="L12" t="n">
-        <v>16680</v>
+        <v>93500</v>
       </c>
       <c r="M12" t="n">
-        <v>14800</v>
+        <v>90200</v>
       </c>
       <c r="N12" t="n">
-        <v>1.58</v>
+        <v>23.53</v>
       </c>
       <c r="O12" t="n">
-        <v>43604548790</v>
+        <v>301042717300</v>
       </c>
       <c r="P12" t="n">
-        <v>21400</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>12090</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-3000</v>
+        <v>-222000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>267000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
+          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['단주 거래', '자전거래', '스카이랩스']</t>
+          <t>['원전', 'SMR', '텍사스']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0155E0</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1579,27 +1579,27 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34050</v>
+        <v>34250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.97%</t>
+          <t>+4.58%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="H13" t="n">
-        <v>52.68</v>
+        <v>52.69</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>21.02</v>
       </c>
       <c r="O13" t="n">
-        <v>52633435675</v>
+        <v>55203062750</v>
       </c>
       <c r="P13" t="n">
         <v>69500</v>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>91300</v>
+        <v>1850000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.87%</t>
+          <t>+3.76%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>361</v>
+        <v>797</v>
       </c>
       <c r="F14" t="n">
-        <v>227</v>
+        <v>469</v>
       </c>
       <c r="G14" t="n">
-        <v>1722</v>
+        <v>2128</v>
       </c>
       <c r="H14" t="n">
-        <v>23.63</v>
+        <v>50.63</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>87900</v>
+        <v>1783000</v>
       </c>
       <c r="K14" t="n">
-        <v>91200</v>
+        <v>1799000</v>
       </c>
       <c r="L14" t="n">
-        <v>93500</v>
+        <v>1860000</v>
       </c>
       <c r="M14" t="n">
-        <v>90200</v>
+        <v>1777000</v>
       </c>
       <c r="N14" t="n">
-        <v>23.53</v>
+        <v>50.5</v>
       </c>
       <c r="O14" t="n">
-        <v>291287379200</v>
+        <v>3041898609500</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>274000</v>
       </c>
       <c r="R14" t="n">
-        <v>-222000</v>
+        <v>-8000</v>
       </c>
       <c r="S14" t="n">
-        <v>267000</v>
+        <v>108000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
+          <t>낸드메모리 품귀 현상 및 반도체 시즌 2 도래 전망으로 주가 상승 기대감이 높음. 기관 및 외인 매수세 유입과 함께 300만 돌파 목표를 제시하는 등 긍정적 전망이 우세함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '텍사스']</t>
+          <t>['낸드메모리', '반도체', '기관 외인']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9120</v>
+        <v>15140</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.87%</t>
+          <t>+3.34%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>0.14</v>
       </c>
       <c r="E15" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="H15" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8780</v>
+        <v>14650</v>
       </c>
       <c r="K15" t="n">
-        <v>9060</v>
+        <v>15100</v>
       </c>
       <c r="L15" t="n">
-        <v>9960</v>
+        <v>16680</v>
       </c>
       <c r="M15" t="n">
-        <v>8270</v>
+        <v>14800</v>
       </c>
       <c r="N15" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="O15" t="n">
-        <v>96313536550</v>
+        <v>43952456650</v>
       </c>
       <c r="P15" t="n">
-        <v>25050</v>
+        <v>21400</v>
       </c>
       <c r="Q15" t="n">
-        <v>3705</v>
+        <v>12090</v>
       </c>
       <c r="R15" t="n">
-        <v>-59000</v>
+        <v>-3000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
+          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['투경', '탈모 테마', 'JAK 억제']</t>
+          <t>['단주 거래', '자전거래', '스카이랩스']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>0155E0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1851500</v>
+        <v>276750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+3.84%</t>
+          <t>+2.50%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F16" t="n">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="G16" t="n">
-        <v>2187</v>
+        <v>1740</v>
       </c>
       <c r="H16" t="n">
-        <v>50.63</v>
+        <v>46.79</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1783000</v>
+        <v>270000</v>
       </c>
       <c r="K16" t="n">
-        <v>1799000</v>
+        <v>272000</v>
       </c>
       <c r="L16" t="n">
-        <v>1860000</v>
+        <v>277500</v>
       </c>
       <c r="M16" t="n">
-        <v>1777000</v>
+        <v>269000</v>
       </c>
       <c r="N16" t="n">
-        <v>50.5</v>
+        <v>46.73</v>
       </c>
       <c r="O16" t="n">
-        <v>2928879682000</v>
+        <v>2240704915000</v>
       </c>
       <c r="P16" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>274000</v>
+        <v>69600</v>
       </c>
       <c r="R16" t="n">
-        <v>-8000</v>
+        <v>1295000</v>
       </c>
       <c r="S16" t="n">
-        <v>108000</v>
+        <v>223000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>메모리 반도체 품귀 현상 및 재고 감소 추세. 300만 원 돌파 목표 및 기관/외인 매수세 유입 기대.</t>
+          <t>15조 규모 자사주 매수 및 주주환원 정책 발표로 긍정적 투자 심리가 형성됨. 30만 전자 목표 언급과 함께 개인 투자자들의 홀딩 의견이 지배적이나, 정치적 언급이 다소 혼재됨.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['반도체', '메모리', '재고']</t>
+          <t>['자사주 매수', '주주환원', '반도체']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,99 +1936,99 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>276500</v>
+        <v>8960</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+2.41%</t>
+          <t>+2.05%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>796</v>
+        <v>37</v>
       </c>
       <c r="F17" t="n">
-        <v>466</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>1659</v>
+        <v>29</v>
       </c>
       <c r="H17" t="n">
-        <v>46.79</v>
+        <v>1.68</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>270000</v>
+        <v>8780</v>
       </c>
       <c r="K17" t="n">
-        <v>272000</v>
+        <v>9060</v>
       </c>
       <c r="L17" t="n">
-        <v>277500</v>
+        <v>9960</v>
       </c>
       <c r="M17" t="n">
-        <v>269000</v>
+        <v>8270</v>
       </c>
       <c r="N17" t="n">
-        <v>46.73</v>
+        <v>1.72</v>
       </c>
       <c r="O17" t="n">
-        <v>2082423099250</v>
+        <v>98256381975</v>
       </c>
       <c r="P17" t="n">
-        <v>374500</v>
+        <v>25050</v>
       </c>
       <c r="Q17" t="n">
-        <v>69600</v>
+        <v>3705</v>
       </c>
       <c r="R17" t="n">
-        <v>1295000</v>
+        <v>-59000</v>
       </c>
       <c r="S17" t="n">
-        <v>223000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>자사주 15조 매수 발표 및 주주환원 정책 기대감. 반도체 사업 및 로봇 출시 관련 논의.</t>
+          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['자사주 매수', '주주환원', '반도체']</t>
+          <t>['투경', '탈모 테마', 'JAK 억제']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10260</v>
+        <v>10240</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.23</v>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H18" t="n">
         <v>0.44</v>
@@ -2082,7 +2082,7 @@
         <v>0.21</v>
       </c>
       <c r="O18" t="n">
-        <v>56403892280</v>
+        <v>56786381370</v>
       </c>
       <c r="P18" t="n">
         <v>20850</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15490</v>
+        <v>15520</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-3.66%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G19" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>29224130810</v>
+        <v>29661605860</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12120</v>
+        <v>11970</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.42%</t>
+          <t>-5.60%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H20" t="n">
         <v>17.11</v>
@@ -2266,7 +2266,7 @@
         <v>18.05</v>
       </c>
       <c r="O20" t="n">
-        <v>23389261050</v>
+        <v>24190282355</v>
       </c>
       <c r="P20" t="n">
         <v>14350</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8400</v>
+        <v>8340</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-11.21%</t>
+          <t>-11.84%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" t="n">
         <v>33</v>
       </c>
       <c r="G21" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="H21" t="n">
         <v>38.84</v>
@@ -2358,7 +2358,7 @@
         <v>38.69</v>
       </c>
       <c r="O21" t="n">
-        <v>23893961760</v>
+        <v>24813441985</v>
       </c>
       <c r="P21" t="n">
         <v>19150</v>
@@ -2418,13 +2418,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H22" t="n">
         <v>0.08</v>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,10 +578,10 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
         <v>151</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>141041748663</v>
+        <v>141314522983</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 관련 정부 주관 사업 선정 및 국산화 수행 기관 지정 사실이 부각됨. 광통신 사업과의 연관성을 언급하며 주가 상승 가능성을 제기함.</t>
+          <t>AI 데이터센터 정부 주최 국산화 수행기관 선정 및 광통신 상용화 관련 재료 부각. 최소 3방 이상 상승 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '정부 사업']</t>
+          <t>['AI 데이터센터', '국산화', '광통신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10410</v>
+        <v>10360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+23.63%</t>
+          <t>+23.04%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F3" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G3" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>253071240960</v>
+        <v>259954044870</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 미프진 도입 구체화 및 연내 허가 관련 뉴스가 언급되며 주가 상승 기대감이 형성됨. 다만, 관련 뉴스 인용 외 구체적인 실적 근거는 부족함.</t>
+          <t>정부의 미프진 도입 구체화 및 연내 허가 뉴스 기반 주가 상승 기대감. 그러나 원내/약국 처방 관련 불확실성 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미프진', '정부 도입', '연내 허가']</t>
+          <t>['미프진', '정부 도입', '낙태약']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37100</v>
+        <v>37200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.44%</t>
+          <t>+21.77%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="F4" t="n">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="G4" t="n">
-        <v>825</v>
+        <v>899</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>707071245950</v>
+        <v>745023788500</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>세계 최초 반지형 웨어러블 디바이스 관련 기술력과 정부 지분 공시 등 긍정적 요인이 부각되며 급등 기대감이 형성됨. 주포 개입 가능성을 언급하며 강한 상승세를 예상함.</t>
+          <t>세계 최초 반지형 웨어러블 기기 관련 기술력 및 정부 지분 공시 기반 상승 기대. 주포의 적극적인 매수세 유입 및 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['웨어러블 디바이스', '정부 지분', '급등']</t>
+          <t>['웨어러블 기기', '정부 지분', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>139200</v>
+        <v>140100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+13.82%</t>
+          <t>+14.55%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.11</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H5" t="n">
         <v>13.33</v>
@@ -886,7 +886,7 @@
         <v>13.22</v>
       </c>
       <c r="O5" t="n">
-        <v>146761411400</v>
+        <v>155096632150</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 원전 8기 수주 관련 260조 사업 규모의 구체적인 내용과 수익 계산법이 제시되며 긍정적인 전망이 우세함. 기관 및 연기금의 순매수세 유입도 긍정적 신호로 작용함.</t>
+          <t>미국 원전 8기 수주 및 260조 사업 구체화에 따른 상승 기대. AP1000 관련 사업성 분석 및 기관/연기금 매수세 유입.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전 사업', '260조', '기관 연기금']</t>
+          <t>['원전 수주', '260조 사업', 'AP1000']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4070</v>
+        <v>20900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+13.69%</t>
+          <t>+13.53%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.31</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="G6" t="n">
-        <v>205</v>
+        <v>786</v>
       </c>
       <c r="H6" t="n">
-        <v>1.56</v>
+        <v>10.47</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3580</v>
+        <v>18410</v>
       </c>
       <c r="K6" t="n">
-        <v>3600</v>
+        <v>18800</v>
       </c>
       <c r="L6" t="n">
-        <v>4335</v>
+        <v>20950</v>
       </c>
       <c r="M6" t="n">
-        <v>3450</v>
+        <v>18480</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>10.4</v>
       </c>
       <c r="O6" t="n">
-        <v>220133090515</v>
+        <v>338835453165</v>
       </c>
       <c r="P6" t="n">
-        <v>4335</v>
+        <v>40350</v>
       </c>
       <c r="Q6" t="n">
-        <v>1246</v>
+        <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>-338000</v>
+        <v>256000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>207000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>탈모 치료제 관련 건보료 적용 기대감으로 긍정적인 논조가 형성됨. 다만, 구체적인 실적 발표나 공시보다는 기대감에 기반한 언급이 주를 이룸.</t>
+          <t>원전 사업 및 미국 원전 건설 관련 신규 사업 재료 부각으로 인한 주가 상승 기대. 골든크로스 형성 및 시가총액 대비 저평가 분석.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '건보료 적용', '기대감']</t>
+          <t>['원전', '신사업', '건설']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20600</v>
+        <v>4000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+11.90%</t>
+          <t>+11.73%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="F7" t="n">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="G7" t="n">
-        <v>654</v>
+        <v>219</v>
       </c>
       <c r="H7" t="n">
-        <v>10.47</v>
+        <v>1.56</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18410</v>
+        <v>3580</v>
       </c>
       <c r="K7" t="n">
-        <v>18800</v>
+        <v>3600</v>
       </c>
       <c r="L7" t="n">
-        <v>20850</v>
+        <v>4335</v>
       </c>
       <c r="M7" t="n">
-        <v>18480</v>
+        <v>3450</v>
       </c>
       <c r="N7" t="n">
-        <v>10.4</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>311660409665</v>
+        <v>232807115237</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>4335</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>1246</v>
       </c>
       <c r="R7" t="n">
-        <v>256000</v>
+        <v>-338000</v>
       </c>
       <c r="S7" t="n">
-        <v>207000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원전 사업 수주 및 미국 원전 건설 관련 뉴스가 부각되며 주가 상승 기대감이 높음. 2만 돌파 및 시가총액 저평가 의견이 제시되며 긍정적인 전망을 보임.</t>
+          <t>탈모 치료제 관련 건보료 적용 시 큰 폭 상승 기대감. 10년 매집 및 차트상 긍정적 분석 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '신사업', '미국 건설']</t>
+          <t>['탈모 치료제', '건보료 적용', '10년 매집']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11990</v>
+        <v>12020</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.80%</t>
+          <t>+10.07%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.11</v>
       </c>
       <c r="E8" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F8" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
-        <v>264</v>
+        <v>320</v>
       </c>
       <c r="H8" t="n">
         <v>5.42</v>
@@ -1162,7 +1162,7 @@
         <v>5.53</v>
       </c>
       <c r="O8" t="n">
-        <v>101739671470</v>
+        <v>109461653960</v>
       </c>
       <c r="P8" t="n">
         <v>30200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>프랑스와의 원자력 협정 체결 및 미국 원전 8기 수주 관련 뉴스가 주가 상승 모멘텀으로 작용하고 있음. 원전 섹터 전반의 강세와 함께 긍정적 전망을 보임.</t>
+          <t>원전 섹터 전반의 상승세 및 프랑스와의 원자력 협정 관련 호재. 대미 투자 원전 8기 관련 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원자력 협정', '미국 원전', '원전 섹터']</t>
+          <t>['원전', '프랑스 협력', '대미 투자']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.02%</t>
+          <t>+6.35%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
         <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H9" t="n">
         <v>5.34</v>
@@ -1254,7 +1254,7 @@
         <v>5.29</v>
       </c>
       <c r="O9" t="n">
-        <v>7191481676</v>
+        <v>7309908210</v>
       </c>
       <c r="P9" t="n">
         <v>901</v>
@@ -1299,123 +1299,123 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14150</v>
+        <v>50700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.05%</t>
+          <t>+5.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>425</v>
+        <v>184</v>
       </c>
       <c r="H10" t="n">
-        <v>1.94</v>
+        <v>38.34</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13470</v>
+        <v>48000</v>
       </c>
       <c r="K10" t="n">
-        <v>13580</v>
+        <v>48550</v>
       </c>
       <c r="L10" t="n">
-        <v>14450</v>
+        <v>51600</v>
       </c>
       <c r="M10" t="n">
-        <v>13420</v>
+        <v>48350</v>
       </c>
       <c r="N10" t="n">
-        <v>1.82</v>
+        <v>38.24</v>
       </c>
       <c r="O10" t="n">
-        <v>178608753115</v>
+        <v>103623558975</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>67300</v>
       </c>
       <c r="Q10" t="n">
-        <v>1252</v>
+        <v>23150</v>
       </c>
       <c r="R10" t="n">
-        <v>-161000</v>
+        <v>275000</v>
       </c>
       <c r="S10" t="n">
-        <v>11000</v>
+        <v>66000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Texas 관련 소식 및 광통신 섹터 전반의 긍정적 분위기 속에서 주가 상승 기대감이 형성됨. 공매도 물량 언급과 함께 투경 재지정 여부가 주목받고 있음.</t>
+          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', 'Texas', '투경']</t>
+          <t>['건설', '원전', '재건']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50400</v>
+        <v>92500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.00%</t>
+          <t>+5.23%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>381</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>240</v>
       </c>
       <c r="G11" t="n">
-        <v>188</v>
+        <v>1728</v>
       </c>
       <c r="H11" t="n">
-        <v>38.34</v>
+        <v>23.63</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>48000</v>
+        <v>87900</v>
       </c>
       <c r="K11" t="n">
-        <v>48550</v>
+        <v>91200</v>
       </c>
       <c r="L11" t="n">
-        <v>51600</v>
+        <v>93500</v>
       </c>
       <c r="M11" t="n">
-        <v>48350</v>
+        <v>90200</v>
       </c>
       <c r="N11" t="n">
-        <v>38.24</v>
+        <v>23.53</v>
       </c>
       <c r="O11" t="n">
-        <v>100309016575</v>
+        <v>319683913650</v>
       </c>
       <c r="P11" t="n">
-        <v>67300</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>23150</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>275000</v>
+        <v>-222000</v>
       </c>
       <c r="S11" t="n">
-        <v>66000</v>
+        <v>267000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
+          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['건설', '원전', '재건']</t>
+          <t>['원전', 'SMR', '텍사스']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>92000</v>
+        <v>34225</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.66%</t>
+          <t>+4.50%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>364</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
-        <v>232</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
-        <v>1701</v>
+        <v>255</v>
       </c>
       <c r="H12" t="n">
-        <v>23.63</v>
+        <v>52.69</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,152 +1515,152 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>87900</v>
+        <v>32750</v>
       </c>
       <c r="K12" t="n">
-        <v>91200</v>
+        <v>33700</v>
       </c>
       <c r="L12" t="n">
-        <v>93500</v>
+        <v>34350</v>
       </c>
       <c r="M12" t="n">
-        <v>90200</v>
+        <v>33450</v>
       </c>
       <c r="N12" t="n">
-        <v>23.53</v>
+        <v>21.02</v>
       </c>
       <c r="O12" t="n">
-        <v>301042717300</v>
+        <v>58057707600</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>69500</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>30400</v>
       </c>
       <c r="R12" t="n">
-        <v>-222000</v>
+        <v>324000</v>
       </c>
       <c r="S12" t="n">
-        <v>267000</v>
+        <v>194000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
+          <t>미국 원전 사업 투자 기대감으로 인한 주가 상승. 공매도 세력과의 공방.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '텍사스']</t>
+          <t>['원전', '투자', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34250</v>
+        <v>14070</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>+4.45%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="E13" t="n">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
-        <v>245</v>
+        <v>448</v>
       </c>
       <c r="H13" t="n">
-        <v>52.69</v>
+        <v>1.94</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>32750</v>
+        <v>13470</v>
       </c>
       <c r="K13" t="n">
-        <v>33700</v>
+        <v>13580</v>
       </c>
       <c r="L13" t="n">
-        <v>34350</v>
+        <v>14450</v>
       </c>
       <c r="M13" t="n">
-        <v>33450</v>
+        <v>13420</v>
       </c>
       <c r="N13" t="n">
-        <v>21.02</v>
+        <v>1.82</v>
       </c>
       <c r="O13" t="n">
-        <v>55203062750</v>
+        <v>184654490570</v>
       </c>
       <c r="P13" t="n">
-        <v>69500</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>30400</v>
+        <v>1252</v>
       </c>
       <c r="R13" t="n">
-        <v>324000</v>
+        <v>-161000</v>
       </c>
       <c r="S13" t="n">
-        <v>194000</v>
+        <v>11000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 원전 사업 투자 기대감으로 인한 주가 상승. 공매도 세력과의 공방.</t>
+          <t>Texas 관련 소식 및 광통신 섹터 전반의 긍정적 분위기 속에서 주가 상승 기대감이 형성됨. 공매도 물량 언급과 함께 투경 재지정 여부가 주목받고 있음.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '투자', '공매도']</t>
+          <t>['광통신', 'Texas', '투경']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1850000</v>
+        <v>1859000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.76%</t>
+          <t>+4.26%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="F14" t="n">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="G14" t="n">
-        <v>2128</v>
+        <v>2114</v>
       </c>
       <c r="H14" t="n">
         <v>50.63</v>
@@ -1714,7 +1714,7 @@
         <v>50.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3041898609500</v>
+        <v>3280333620000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>낸드메모리 품귀 현상 및 반도체 시즌 2 도래 전망으로 주가 상승 기대감이 높음. 기관 및 외인 매수세 유입과 함께 300만 돌파 목표를 제시하는 등 긍정적 전망이 우세함.</t>
+          <t>반도체 품귀 현상 및 재고 감소 전망에 따른 200만 돌파 기대감. 자사주 매수 여력 및 한국 주식 시장 견인 역할 분석.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['낸드메모리', '반도체', '기관 외인']</t>
+          <t>['반도체', '품귀 현상', '자사주 매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15140</v>
+        <v>15100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.34%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.14</v>
       </c>
       <c r="E15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H15" t="n">
         <v>1.72</v>
@@ -1806,7 +1806,7 @@
         <v>1.58</v>
       </c>
       <c r="O15" t="n">
-        <v>43952456650</v>
+        <v>44509141155</v>
       </c>
       <c r="P15" t="n">
         <v>21400</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>276750</v>
+        <v>277500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.50%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="F16" t="n">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="G16" t="n">
-        <v>1740</v>
+        <v>1774</v>
       </c>
       <c r="H16" t="n">
         <v>46.79</v>
@@ -1898,7 +1898,7 @@
         <v>46.73</v>
       </c>
       <c r="O16" t="n">
-        <v>2240704915000</v>
+        <v>2456439327250</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>15조 규모 자사주 매수 및 주주환원 정책 발표로 긍정적 투자 심리가 형성됨. 30만 전자 목표 언급과 함께 개인 투자자들의 홀딩 의견이 지배적이나, 정치적 언급이 다소 혼재됨.</t>
+          <t>공매도 발악 및 숏커버링 기대감 속 28만 및 30만 돌파 전망. 자사주 매수 및 배당 확대 뉴스 기반 주주 환원 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['자사주 매수', '주주환원', '반도체']</t>
+          <t>['공매도', '자사주 매수', '주주 환원']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8960</v>
+        <v>8930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+2.05%</t>
+          <t>+1.71%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H17" t="n">
         <v>1.68</v>
@@ -1990,7 +1990,7 @@
         <v>1.72</v>
       </c>
       <c r="O17" t="n">
-        <v>98256381975</v>
+        <v>101376099485</v>
       </c>
       <c r="P17" t="n">
         <v>25050</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10240</v>
+        <v>10230</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.23</v>
       </c>
       <c r="E18" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F18" t="n">
         <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H18" t="n">
         <v>0.44</v>
@@ -2082,7 +2082,7 @@
         <v>0.21</v>
       </c>
       <c r="O18" t="n">
-        <v>56786381370</v>
+        <v>58100332545</v>
       </c>
       <c r="P18" t="n">
         <v>20850</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15520</v>
+        <v>15460</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.66%</t>
+          <t>-4.03%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F19" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G19" t="n">
-        <v>281</v>
+        <v>319</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>29661605860</v>
+        <v>31258972165</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>건설주 강세 속 주가 부진. 대규모 투자 프로젝트 관련 언급 및 반등 기대.</t>
+          <t>호남 메가프로젝트 및 광주공항 재개장 관련 호재 가능성 언급. 반도체 조정 시 건설주 상승 추세에 따른 기대감.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['건설', '투자', '반등']</t>
+          <t>['호남 메가프로젝트', '광주공항', '건설주']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11970</v>
+        <v>12040</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-5.60%</t>
+          <t>-5.05%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F20" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G20" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H20" t="n">
         <v>17.11</v>
@@ -2266,7 +2266,7 @@
         <v>18.05</v>
       </c>
       <c r="O20" t="n">
-        <v>24190282355</v>
+        <v>25405636355</v>
       </c>
       <c r="P20" t="n">
         <v>14350</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8340</v>
+        <v>8420</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-11.84%</t>
+          <t>-10.99%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="H21" t="n">
         <v>38.84</v>
@@ -2358,7 +2358,7 @@
         <v>38.69</v>
       </c>
       <c r="O21" t="n">
-        <v>24813441985</v>
+        <v>25620551935</v>
       </c>
       <c r="P21" t="n">
         <v>19150</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-93.14%</t>
+          <t>-92.98%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G22" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="H22" t="n">
         <v>0.08</v>
@@ -2450,7 +2450,7 @@
         <v>0.08</v>
       </c>
       <c r="O22" t="n">
-        <v>769787659</v>
+        <v>826334598</v>
       </c>
       <c r="P22" t="n">
         <v>3660</v>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G2" t="n">
-        <v>151</v>
+        <v>206</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>141314522983</v>
+        <v>141690531343</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 정부 주최 국산화 수행기관 선정 및 광통신 상용화 관련 재료 부각. 최소 3방 이상 상승 전망.</t>
+          <t>AI 데이터센터 국산화 사업 수행 기관 선정 및 광통신 상용화 기대감. 정부 주도 사업 선정으로 인한 급등세 및 추가 상승 가능성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '국산화', '광통신']</t>
+          <t>['AI 데이터센터', '광통신', '국산화']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10360</v>
+        <v>10260</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+23.04%</t>
+          <t>+21.85%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="F3" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G3" t="n">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>259954044870</v>
+        <v>268222900480</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 미프진 도입 구체화 및 연내 허가 뉴스 기반 주가 상승 기대감. 그러나 원내/약국 처방 관련 불확실성 존재.</t>
+          <t>미프진 국내 독점 판권 보유 기업으로서, 연내 허가 기대감 및 정부 지원 가능성에 따른 급등세. 전략적 투자 유치 및 탈모 이슈와 함께 제2의 삼천당제약으로 거론.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미프진', '정부 도입', '낙태약']</t>
+          <t>['미프진', '독점 판권', '탈모']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37200</v>
+        <v>36400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.77%</t>
+          <t>+19.15%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>544</v>
+        <v>579</v>
       </c>
       <c r="F4" t="n">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="G4" t="n">
-        <v>899</v>
+        <v>996</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>745023788500</v>
+        <v>774664933225</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>세계 최초 반지형 웨어러블 기기 관련 기술력 및 정부 지분 공시 기반 상승 기대. 주포의 적극적인 매수세 유입 및 급등 가능성 언급.</t>
+          <t>정부 지분 공시(6.54%) 및 차세대 기술 보유 부각, 주포 세력의 강한 매집 의지 확인. 10만원 돌파 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['웨어러블 기기', '정부 지분', '주포']</t>
+          <t>['정부 지분', '차세대 기술', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>140100</v>
+        <v>143200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+14.55%</t>
+          <t>+17.09%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.11</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="F5" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G5" t="n">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="H5" t="n">
         <v>13.33</v>
@@ -877,7 +877,7 @@
         <v>129400</v>
       </c>
       <c r="L5" t="n">
-        <v>143100</v>
+        <v>144600</v>
       </c>
       <c r="M5" t="n">
         <v>128100</v>
@@ -886,7 +886,7 @@
         <v>13.22</v>
       </c>
       <c r="O5" t="n">
-        <v>155096632150</v>
+        <v>186998260600</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 원전 8기 수주 및 260조 사업 구체화에 따른 상승 기대. AP1000 관련 사업성 분석 및 기관/연기금 매수세 유입.</t>
+          <t>260조 원전 사업 관련 뉴스 기반 단기적 고점 논란. 미국 원전 수주 구체적 내용 및 외인 매도세 주목.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전 수주', '260조 사업', 'AP1000']</t>
+          <t>['원전 사업', '260조', '외인']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20900</v>
+        <v>20800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+13.53%</t>
+          <t>+12.98%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>188</v>
+        <v>262</v>
       </c>
       <c r="F6" t="n">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="G6" t="n">
-        <v>786</v>
+        <v>1079</v>
       </c>
       <c r="H6" t="n">
         <v>10.47</v>
@@ -969,7 +969,7 @@
         <v>18800</v>
       </c>
       <c r="L6" t="n">
-        <v>20950</v>
+        <v>21300</v>
       </c>
       <c r="M6" t="n">
         <v>18480</v>
@@ -978,7 +978,7 @@
         <v>10.4</v>
       </c>
       <c r="O6" t="n">
-        <v>338835453165</v>
+        <v>407327081865</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>원전 사업 및 미국 원전 건설 관련 신규 사업 재료 부각으로 인한 주가 상승 기대. 골든크로스 형성 및 시가총액 대비 저평가 분석.</t>
+          <t>원전 사업 수주 및 신사업 재료 발표 기대감으로 인한 급등세. 미국 원전 건설 및 에너지 인프라 건설 관련 호재가 부각되며 2만 돌파.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '신사업', '건설']</t>
+          <t>['원전', '신사업', '에너지 인프라']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4000</v>
+        <v>12110</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+11.73%</t>
+          <t>+10.90%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.31</v>
+        <v>-0.11</v>
       </c>
       <c r="E7" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="F7" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G7" t="n">
-        <v>219</v>
+        <v>398</v>
       </c>
       <c r="H7" t="n">
-        <v>1.56</v>
+        <v>5.42</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3580</v>
+        <v>10920</v>
       </c>
       <c r="K7" t="n">
-        <v>3600</v>
+        <v>11300</v>
       </c>
       <c r="L7" t="n">
-        <v>4335</v>
+        <v>12700</v>
       </c>
       <c r="M7" t="n">
-        <v>3450</v>
+        <v>11050</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>5.53</v>
       </c>
       <c r="O7" t="n">
-        <v>232807115237</v>
+        <v>121111478900</v>
       </c>
       <c r="P7" t="n">
-        <v>4335</v>
+        <v>30200</v>
       </c>
       <c r="Q7" t="n">
-        <v>1246</v>
+        <v>3540</v>
       </c>
       <c r="R7" t="n">
-        <v>-338000</v>
+        <v>-712000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>탈모 치료제 관련 건보료 적용 시 큰 폭 상승 기대감. 10년 매집 및 차트상 긍정적 분석 기반 상승 전망.</t>
+          <t>프랑스와의 원자력 협정 및 대규모 원전 투자 기대감. 주가 상승 및 공매도 상환 압박 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '건보료 적용', '10년 매집']</t>
+          <t>['원전', '협정', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12020</v>
+        <v>3910</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+10.07%</t>
+          <t>+9.22%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.11</v>
+        <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G8" t="n">
-        <v>320</v>
+        <v>238</v>
       </c>
       <c r="H8" t="n">
-        <v>5.42</v>
+        <v>1.56</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10920</v>
+        <v>3580</v>
       </c>
       <c r="K8" t="n">
-        <v>11300</v>
+        <v>3600</v>
       </c>
       <c r="L8" t="n">
-        <v>12700</v>
+        <v>4335</v>
       </c>
       <c r="M8" t="n">
-        <v>11050</v>
+        <v>3450</v>
       </c>
       <c r="N8" t="n">
-        <v>5.53</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>109461653960</v>
+        <v>249011910123</v>
       </c>
       <c r="P8" t="n">
-        <v>30200</v>
+        <v>4335</v>
       </c>
       <c r="Q8" t="n">
-        <v>3540</v>
+        <v>1246</v>
       </c>
       <c r="R8" t="n">
-        <v>-712000</v>
+        <v>-338000</v>
       </c>
       <c r="S8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원전 섹터 전반의 상승세 및 프랑스와의 원자력 협정 관련 호재. 대미 투자 원전 8기 관련 기대감.</t>
+          <t>탈모 치료제 관련 건보료 적용 기대감 및 신약 개발 가능성 부각. 10년 매집 후 시세 분출 가능성에 대한 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '프랑스 협력', '대미 투자']</t>
+          <t>['탈모 치료제', '건보료 적용', '신약 개발']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>318</v>
+        <v>50900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.35%</t>
+          <t>+6.04%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>51</v>
+        <v>205</v>
       </c>
       <c r="H9" t="n">
-        <v>5.34</v>
+        <v>38.34</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>299</v>
+        <v>48000</v>
       </c>
       <c r="K9" t="n">
-        <v>220</v>
+        <v>48550</v>
       </c>
       <c r="L9" t="n">
-        <v>349</v>
+        <v>51600</v>
       </c>
       <c r="M9" t="n">
-        <v>220</v>
+        <v>48350</v>
       </c>
       <c r="N9" t="n">
-        <v>5.29</v>
+        <v>38.24</v>
       </c>
       <c r="O9" t="n">
-        <v>7309908210</v>
+        <v>115559988725</v>
       </c>
       <c r="P9" t="n">
-        <v>901</v>
+        <v>67300</v>
       </c>
       <c r="Q9" t="n">
-        <v>217</v>
+        <v>23150</v>
       </c>
       <c r="R9" t="n">
-        <v>727000</v>
+        <v>275000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>상장폐지 가능성 속 정리매매 시점과 회사 자산 가치에 대한 의견 대립.</t>
+          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['상장폐지', '정리매매', '자산가치']</t>
+          <t>['건설', '원전', '재건']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50700</v>
+        <v>92800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.62%</t>
+          <t>+5.57%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>424</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>256</v>
       </c>
       <c r="G10" t="n">
-        <v>184</v>
+        <v>1947</v>
       </c>
       <c r="H10" t="n">
-        <v>38.34</v>
+        <v>23.63</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>48000</v>
+        <v>87900</v>
       </c>
       <c r="K10" t="n">
-        <v>48550</v>
+        <v>91200</v>
       </c>
       <c r="L10" t="n">
-        <v>51600</v>
+        <v>93500</v>
       </c>
       <c r="M10" t="n">
-        <v>48350</v>
+        <v>90200</v>
       </c>
       <c r="N10" t="n">
-        <v>38.24</v>
+        <v>23.53</v>
       </c>
       <c r="O10" t="n">
-        <v>103623558975</v>
+        <v>357298618100</v>
       </c>
       <c r="P10" t="n">
-        <v>67300</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>23150</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>275000</v>
+        <v>-222000</v>
       </c>
       <c r="S10" t="n">
-        <v>66000</v>
+        <v>267000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
+          <t>미국 텍사스 발전 사업 참여 확정 및 원전 8기 건설 수주 기대감. SMR 분야 강자로서 웨스팅하우스 지분 인수 및 체코 원전 시공 참여 가능성 부각.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['건설', '원전', '재건']</t>
+          <t>['SMR', '미국 발전 사업', '원전']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>92500</v>
+        <v>1869000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.23%</t>
+          <t>+4.82%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E11" t="n">
-        <v>381</v>
+        <v>795</v>
       </c>
       <c r="F11" t="n">
-        <v>240</v>
+        <v>471</v>
       </c>
       <c r="G11" t="n">
-        <v>1728</v>
+        <v>2318</v>
       </c>
       <c r="H11" t="n">
-        <v>23.63</v>
+        <v>50.63</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>87900</v>
+        <v>1783000</v>
       </c>
       <c r="K11" t="n">
-        <v>91200</v>
+        <v>1799000</v>
       </c>
       <c r="L11" t="n">
-        <v>93500</v>
+        <v>1870000</v>
       </c>
       <c r="M11" t="n">
-        <v>90200</v>
+        <v>1777000</v>
       </c>
       <c r="N11" t="n">
-        <v>23.53</v>
+        <v>50.5</v>
       </c>
       <c r="O11" t="n">
-        <v>319683913650</v>
+        <v>3885814059000</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>274000</v>
       </c>
       <c r="R11" t="n">
-        <v>-222000</v>
+        <v>-8000</v>
       </c>
       <c r="S11" t="n">
-        <v>267000</v>
+        <v>108000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
+          <t>반도체 업황 개선 및 낸드메모리 품귀 현상으로 인한 4거래일 만 19% 상승. 용인 반도체 클러스터 구축 및 40조 자사주 매입 계획은 향후 추가 상승 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '텍사스']</t>
+          <t>['낸드메모리', '자사주 매입', '반도체 클러스터']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,222 +1476,222 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34225</v>
+        <v>13990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.50%</t>
+          <t>+3.86%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>255</v>
+        <v>513</v>
       </c>
       <c r="H12" t="n">
-        <v>52.69</v>
+        <v>1.94</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>32750</v>
+        <v>13470</v>
       </c>
       <c r="K12" t="n">
-        <v>33700</v>
+        <v>13580</v>
       </c>
       <c r="L12" t="n">
-        <v>34350</v>
+        <v>14450</v>
       </c>
       <c r="M12" t="n">
-        <v>33450</v>
+        <v>13420</v>
       </c>
       <c r="N12" t="n">
-        <v>21.02</v>
+        <v>1.82</v>
       </c>
       <c r="O12" t="n">
-        <v>58057707600</v>
+        <v>195448208715</v>
       </c>
       <c r="P12" t="n">
-        <v>69500</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>30400</v>
+        <v>1252</v>
       </c>
       <c r="R12" t="n">
-        <v>324000</v>
+        <v>-161000</v>
       </c>
       <c r="S12" t="n">
-        <v>194000</v>
+        <v>11000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 원전 사업 투자 기대감으로 인한 주가 상승. 공매도 세력과의 공방.</t>
+          <t>Texas 관련 소식 및 차트 분석 기반 단기 저항선 돌파 기대감. 투경 판단일 변동성 주시.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '투자', '공매도']</t>
+          <t>['Texas', '매물대', '차트']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14070</v>
+        <v>34000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+4.45%</t>
+          <t>+3.82%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
-        <v>448</v>
+        <v>302</v>
       </c>
       <c r="H13" t="n">
-        <v>1.94</v>
+        <v>52.7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13470</v>
+        <v>32750</v>
       </c>
       <c r="K13" t="n">
-        <v>13580</v>
+        <v>33700</v>
       </c>
       <c r="L13" t="n">
-        <v>14450</v>
+        <v>34350</v>
       </c>
       <c r="M13" t="n">
-        <v>13420</v>
+        <v>33450</v>
       </c>
       <c r="N13" t="n">
-        <v>1.82</v>
+        <v>21.02</v>
       </c>
       <c r="O13" t="n">
-        <v>184654490570</v>
+        <v>64856933425</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>69500</v>
       </c>
       <c r="Q13" t="n">
-        <v>1252</v>
+        <v>30400</v>
       </c>
       <c r="R13" t="n">
-        <v>-161000</v>
+        <v>324000</v>
       </c>
       <c r="S13" t="n">
-        <v>11000</v>
+        <v>194000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Texas 관련 소식 및 광통신 섹터 전반의 긍정적 분위기 속에서 주가 상승 기대감이 형성됨. 공매도 물량 언급과 함께 투경 재지정 여부가 주목받고 있음.</t>
+          <t>미국 원전 사업 투자 기대감으로 인한 주가 상승. 공매도 세력과의 공방.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', 'Texas', '투경']</t>
+          <t>['원전', '투자', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1859000</v>
+        <v>277500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+4.26%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="F14" t="n">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="G14" t="n">
-        <v>2114</v>
+        <v>1872</v>
       </c>
       <c r="H14" t="n">
-        <v>50.63</v>
+        <v>46.79</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1783000</v>
+        <v>270000</v>
       </c>
       <c r="K14" t="n">
-        <v>1799000</v>
+        <v>272000</v>
       </c>
       <c r="L14" t="n">
-        <v>1860000</v>
+        <v>278000</v>
       </c>
       <c r="M14" t="n">
-        <v>1777000</v>
+        <v>269000</v>
       </c>
       <c r="N14" t="n">
-        <v>50.5</v>
+        <v>46.73</v>
       </c>
       <c r="O14" t="n">
-        <v>3280333620000</v>
+        <v>3067860465750</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>274000</v>
+        <v>69600</v>
       </c>
       <c r="R14" t="n">
-        <v>-8000</v>
+        <v>1295000</v>
       </c>
       <c r="S14" t="n">
-        <v>108000</v>
+        <v>223000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 품귀 현상 및 재고 감소 전망에 따른 200만 돌파 기대감. 자사주 매수 여력 및 한국 주식 시장 견인 역할 분석.</t>
+          <t>공매도 압박 속 28만 돌파 시도 및 30만 전자 입성 기대감. 자사주 매수 및 배당 정책 강화, 로봇 출시 등은 긍정적 요인.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', '품귀 현상', '자사주 매수']</t>
+          <t>['공매도', '자사주 매수', '로봇']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15100</v>
+        <v>10450</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.07%</t>
+          <t>+2.45%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="G15" t="n">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="H15" t="n">
-        <v>1.72</v>
+        <v>0.44</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,47 +1791,47 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14650</v>
+        <v>10200</v>
       </c>
       <c r="K15" t="n">
-        <v>15100</v>
+        <v>10600</v>
       </c>
       <c r="L15" t="n">
-        <v>16680</v>
+        <v>10970</v>
       </c>
       <c r="M15" t="n">
-        <v>14800</v>
+        <v>9980</v>
       </c>
       <c r="N15" t="n">
-        <v>1.58</v>
+        <v>0.21</v>
       </c>
       <c r="O15" t="n">
-        <v>44509141155</v>
+        <v>67888891495</v>
       </c>
       <c r="P15" t="n">
-        <v>21400</v>
+        <v>20850</v>
       </c>
       <c r="Q15" t="n">
-        <v>12090</v>
+        <v>4020</v>
       </c>
       <c r="R15" t="n">
-        <v>-3000</v>
+        <v>-59000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
+          <t>터빈블레이드 수주 기대감 속 기관/외인 매수세 유입 전망. 대주주 물량 매도 후 변동성 예상.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['단주 거래', '자전거래', '스카이랩스']</t>
+          <t>['터빈블레이드', '수주', '기관']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,95 +1839,95 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0155E0</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>277500</v>
+        <v>306</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.78%</t>
+          <t>+2.34%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E16" t="n">
-        <v>793</v>
+        <v>87</v>
       </c>
       <c r="F16" t="n">
-        <v>452</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>1774</v>
+        <v>54</v>
       </c>
       <c r="H16" t="n">
-        <v>46.79</v>
+        <v>5.34</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>270000</v>
+        <v>299</v>
       </c>
       <c r="K16" t="n">
-        <v>272000</v>
+        <v>220</v>
       </c>
       <c r="L16" t="n">
-        <v>277500</v>
+        <v>349</v>
       </c>
       <c r="M16" t="n">
-        <v>269000</v>
+        <v>220</v>
       </c>
       <c r="N16" t="n">
-        <v>46.73</v>
+        <v>5.29</v>
       </c>
       <c r="O16" t="n">
-        <v>2456439327250</v>
+        <v>8008445856</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>901</v>
       </c>
       <c r="Q16" t="n">
-        <v>69600</v>
+        <v>217</v>
       </c>
       <c r="R16" t="n">
-        <v>1295000</v>
+        <v>727000</v>
       </c>
       <c r="S16" t="n">
-        <v>223000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>공매도 발악 및 숏커버링 기대감 속 28만 및 30만 돌파 전망. 자사주 매수 및 배당 확대 뉴스 기반 주주 환원 기대.</t>
+          <t>상장폐지 가능성 및 정리매매 돌입에 대한 우려. 대규모 거래량 발생 및 변동성 확대 속에 투자 주의 요구.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도', '자사주 매수', '주주 환원']</t>
+          <t>['상장폐지', '정리매매', '거래량']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8930</v>
+        <v>14970</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.71%</t>
+          <t>+2.18%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.04</v>
+        <v>0.14</v>
       </c>
       <c r="E17" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F17" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H17" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8780</v>
+        <v>14650</v>
       </c>
       <c r="K17" t="n">
-        <v>9060</v>
+        <v>15100</v>
       </c>
       <c r="L17" t="n">
-        <v>9960</v>
+        <v>16680</v>
       </c>
       <c r="M17" t="n">
-        <v>8270</v>
+        <v>14800</v>
       </c>
       <c r="N17" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="O17" t="n">
-        <v>101376099485</v>
+        <v>45582431950</v>
       </c>
       <c r="P17" t="n">
-        <v>25050</v>
+        <v>21400</v>
       </c>
       <c r="Q17" t="n">
-        <v>3705</v>
+        <v>12090</v>
       </c>
       <c r="R17" t="n">
-        <v>-59000</v>
+        <v>-3000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
+          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['투경', '탈모 테마', 'JAK 억제']</t>
+          <t>['단주 거래', '자전거래', '스카이랩스']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,191 +2028,191 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>0155E0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10230</v>
+        <v>15730</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-2.36%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G18" t="n">
-        <v>76</v>
+        <v>389</v>
       </c>
       <c r="H18" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>10200</v>
+        <v>16110</v>
       </c>
       <c r="K18" t="n">
-        <v>10600</v>
+        <v>16130</v>
       </c>
       <c r="L18" t="n">
-        <v>10970</v>
+        <v>16140</v>
       </c>
       <c r="M18" t="n">
-        <v>9980</v>
+        <v>15310</v>
       </c>
       <c r="N18" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>58100332545</v>
+        <v>36651884795</v>
       </c>
       <c r="P18" t="n">
-        <v>20850</v>
+        <v>19380</v>
       </c>
       <c r="Q18" t="n">
-        <v>4020</v>
+        <v>3200</v>
       </c>
       <c r="R18" t="n">
-        <v>-59000</v>
+        <v>-5000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>터빈블레이드 수주 기대감에도 불구하고 주가 움직임에 대한 답답함.</t>
+          <t>건설주 상승세 속 호남 메가프로젝트 및 대미 투자 1호 가스복합발전소 수주 기대감. 광주공항 재개장 이슈도 긍정적 요인.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['터빈블레이드', '수주', '강재료']</t>
+          <t>['건설주', '대미 투자', '광주공항']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15460</v>
+        <v>8530</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.03%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="F19" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>319</v>
+        <v>44</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>16110</v>
+        <v>8780</v>
       </c>
       <c r="K19" t="n">
-        <v>16130</v>
+        <v>9060</v>
       </c>
       <c r="L19" t="n">
-        <v>16140</v>
+        <v>9960</v>
       </c>
       <c r="M19" t="n">
-        <v>15310</v>
+        <v>8270</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O19" t="n">
-        <v>31258972165</v>
+        <v>106143746645</v>
       </c>
       <c r="P19" t="n">
-        <v>19380</v>
+        <v>25050</v>
       </c>
       <c r="Q19" t="n">
-        <v>3200</v>
+        <v>3705</v>
       </c>
       <c r="R19" t="n">
-        <v>-5000</v>
+        <v>-59000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>호남 메가프로젝트 및 광주공항 재개장 관련 호재 가능성 언급. 반도체 조정 시 건설주 상승 추세에 따른 기대감.</t>
+          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['호남 메가프로젝트', '광주공항', '건설주']</t>
+          <t>['투경', '탈모 테마', 'JAK 억제']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12040</v>
+        <v>12140</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-5.05%</t>
+          <t>-4.26%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G20" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="H20" t="n">
         <v>17.11</v>
@@ -2266,7 +2266,7 @@
         <v>18.05</v>
       </c>
       <c r="O20" t="n">
-        <v>25405636355</v>
+        <v>27233477290</v>
       </c>
       <c r="P20" t="n">
         <v>14350</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8420</v>
+        <v>8240</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-10.99%</t>
+          <t>-12.90%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F21" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G21" t="n">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="H21" t="n">
         <v>38.84</v>
@@ -2358,7 +2358,7 @@
         <v>38.69</v>
       </c>
       <c r="O21" t="n">
-        <v>25620551935</v>
+        <v>28545078540</v>
       </c>
       <c r="P21" t="n">
         <v>19150</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-92.98%</t>
+          <t>-93.01%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F22" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="H22" t="n">
         <v>0.08</v>
@@ -2450,7 +2450,7 @@
         <v>0.08</v>
       </c>
       <c r="O22" t="n">
-        <v>826334598</v>
+        <v>863046022</v>
       </c>
       <c r="P22" t="n">
         <v>3660</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>감사의견 적정 판정 후 주가 급락. 재무 건전성 우려 및 상폐 가능성 제기.</t>
+          <t>감사의견 적정 및 상반기 보고서 적정으로 인한 거래 재개 기대감. 그러나 과거 재무 악화 및 정리매매 시작으로 인한 불확실성 상존.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['감사의견', '재무', '상장폐지']</t>
+          <t>['감사의견 적정', '정리매매', '재무']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>141690531343</v>
+        <v>141766964063</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 국산화 사업 수행 기관 선정 및 광통신 상용화 기대감. 정부 주도 사업 선정으로 인한 급등세 및 추가 상승 가능성.</t>
+          <t>AI 데이터센터 정부 주최 국산화 수행기관 선정 및 광통신 사업 성장 기대감. 30% 급등 기록.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '국산화']</t>
+          <t>['AI 데이터센터', '국산화', '광통신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10260</v>
+        <v>10240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+21.85%</t>
+          <t>+21.62%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G3" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>268222900480</v>
+        <v>269491521400</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미프진 국내 독점 판권 보유 기업으로서, 연내 허가 기대감 및 정부 지원 가능성에 따른 급등세. 전략적 투자 유치 및 탈모 이슈와 함께 제2의 삼천당제약으로 거론.</t>
+          <t>미프진 국내 독점 판권 보유 및 연내 허가 기대감. 탈모 이슈와 함께 복합적 재료 보유.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36400</v>
+        <v>36450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+19.15%</t>
+          <t>+19.31%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="F4" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G4" t="n">
-        <v>996</v>
+        <v>1044</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>774664933225</v>
+        <v>783789631625</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 지분 공시(6.54%) 및 차세대 기술 보유 부각, 주포 세력의 강한 매집 의지 확인. 10만원 돌파 기대.</t>
+          <t>정부 지분 공시 및 비교군 없는 세계 최초 기술 보유. 주포의 강한 상승 의지 표출.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정부 지분', '차세대 기술', '주포']</t>
+          <t>['정부 지분', '세계 최초 기술', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>143200</v>
+        <v>143300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.09%</t>
+          <t>+17.17%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.11</v>
       </c>
       <c r="E5" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F5" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G5" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H5" t="n">
         <v>13.33</v>
@@ -886,7 +886,7 @@
         <v>13.22</v>
       </c>
       <c r="O5" t="n">
-        <v>186998260600</v>
+        <v>191185813200</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>260조 원전 사업 관련 뉴스 기반 단기적 고점 논란. 미국 원전 수주 구체적 내용 및 외인 매도세 주목.</t>
+          <t>260조 규모의 미국 원전 사업 관련 뉴스와 구체적인 내용 언급이 있으나, 단기적 고점 및 재료 소멸 우려와 외인 매도세가 관찰됩니다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전 사업', '260조', '외인']</t>
+          <t>['원전 사업', '260조', '외인 매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20800</v>
+        <v>20650</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+12.98%</t>
+          <t>+12.17%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F6" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G6" t="n">
-        <v>1079</v>
+        <v>1086</v>
       </c>
       <c r="H6" t="n">
         <v>10.47</v>
@@ -978,7 +978,7 @@
         <v>10.4</v>
       </c>
       <c r="O6" t="n">
-        <v>407327081865</v>
+        <v>419577119365</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>원전 사업 수주 및 신사업 재료 발표 기대감으로 인한 급등세. 미국 원전 건설 및 에너지 인프라 건설 관련 호재가 부각되며 2만 돌파.</t>
+          <t>원전 사업 신사업 재료 발표 임박 및 에너지 인프라 건설 수요 증가 전망. 2만 원 돌파 기록.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12110</v>
+        <v>12020</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+10.90%</t>
+          <t>+10.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.11</v>
       </c>
       <c r="E7" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F7" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G7" t="n">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="H7" t="n">
         <v>5.42</v>
@@ -1070,7 +1070,7 @@
         <v>5.53</v>
       </c>
       <c r="O7" t="n">
-        <v>121111478900</v>
+        <v>122724730790</v>
       </c>
       <c r="P7" t="n">
         <v>30200</v>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>프랑스와의 원자력 협정 및 대규모 원전 투자 기대감. 주가 상승 및 공매도 상환 압박 전망.</t>
+          <t>원전 섹터 전반의 상승 기대감과 프랑스와의 원자력 협정 소식이 있으나, 공매도 상환 및 관망 심리가 혼재합니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3910</v>
+        <v>3885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.22%</t>
+          <t>+8.52%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F8" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G8" t="n">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="H8" t="n">
         <v>1.56</v>
@@ -1162,7 +1162,7 @@
         <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>249011910123</v>
+        <v>251443374892</v>
       </c>
       <c r="P8" t="n">
         <v>4335</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>탈모 치료제 관련 건보료 적용 기대감 및 신약 개발 가능성 부각. 10년 매집 후 시세 분출 가능성에 대한 기대감.</t>
+          <t>탈모 치료제 관련 이슈와 함께 10년 매집 후 주가 상승 기대감. 거래량 증가 추세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '건보료 적용', '신약 개발']</t>
+          <t>['탈모 치료제', '10년 매집', '거래량']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50900</v>
+        <v>50700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.04%</t>
+          <t>+5.62%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H9" t="n">
         <v>38.34</v>
@@ -1254,7 +1254,7 @@
         <v>38.24</v>
       </c>
       <c r="O9" t="n">
-        <v>115559988725</v>
+        <v>117433076875</v>
       </c>
       <c r="P9" t="n">
         <v>67300</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92800</v>
+        <v>92700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.57%</t>
+          <t>+5.46%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="F10" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G10" t="n">
-        <v>1947</v>
+        <v>1959</v>
       </c>
       <c r="H10" t="n">
         <v>23.63</v>
@@ -1346,7 +1346,7 @@
         <v>23.53</v>
       </c>
       <c r="O10" t="n">
-        <v>357298618100</v>
+        <v>364898887000</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1869000</v>
+        <v>1877000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.82%</t>
+          <t>+5.27%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.13</v>
       </c>
       <c r="E11" t="n">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F11" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G11" t="n">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="H11" t="n">
         <v>50.63</v>
@@ -1429,7 +1429,7 @@
         <v>1799000</v>
       </c>
       <c r="L11" t="n">
-        <v>1870000</v>
+        <v>1878000</v>
       </c>
       <c r="M11" t="n">
         <v>1777000</v>
@@ -1438,7 +1438,7 @@
         <v>50.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3885814059000</v>
+        <v>4047769922500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 업황 개선 및 낸드메모리 품귀 현상으로 인한 4거래일 만 19% 상승. 용인 반도체 클러스터 구축 및 40조 자사주 매입 계획은 향후 추가 상승 기대감.</t>
+          <t>반도체 업황 개선 및 낸드메모리 품귀 현상 전망. 40조 자사주 매수 및 400만 원 목표 주가 제시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['낸드메모리', '자사주 매입', '반도체 클러스터']</t>
+          <t>['낸드메모리', '자사주 매수', '반도체']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13990</v>
+        <v>13980</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.86%</t>
+          <t>+3.79%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.12</v>
       </c>
       <c r="E12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F12" t="n">
         <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="H12" t="n">
         <v>1.94</v>
@@ -1530,7 +1530,7 @@
         <v>1.82</v>
       </c>
       <c r="O12" t="n">
-        <v>195448208715</v>
+        <v>196527939310</v>
       </c>
       <c r="P12" t="n">
         <v>31500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Texas 관련 소식 및 차트 분석 기반 단기 저항선 돌파 기대감. 투경 판단일 변동성 주시.</t>
+          <t>Texas 소식과 함께 광통신 사업 성장 기대감. 투경 재지정 판단 및 공매도 물량 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['Texas', '매물대', '차트']</t>
+          <t>['Texas', '광통신', '투경']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34000</v>
+        <v>33950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.82%</t>
+          <t>+3.66%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G13" t="n">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="H13" t="n">
         <v>52.7</v>
@@ -1622,7 +1622,7 @@
         <v>21.02</v>
       </c>
       <c r="O13" t="n">
-        <v>64856933425</v>
+        <v>65558705250</v>
       </c>
       <c r="P13" t="n">
         <v>69500</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 원전 사업 투자 기대감으로 인한 주가 상승. 공매도 세력과의 공방.</t>
+          <t>미국 웨스팅하우스 지분 인수 추진 및 원전 사업 확대 기대감. 공매도 물량 집중에도 반등 시도.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '투자', '공매도']</t>
+          <t>['웨스팅하우스', '원전', '지분 인수']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>277500</v>
+        <v>278500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+2.78%</t>
+          <t>+3.15%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="F14" t="n">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="G14" t="n">
-        <v>1872</v>
+        <v>1838</v>
       </c>
       <c r="H14" t="n">
         <v>46.79</v>
@@ -1705,7 +1705,7 @@
         <v>272000</v>
       </c>
       <c r="L14" t="n">
-        <v>278000</v>
+        <v>278500</v>
       </c>
       <c r="M14" t="n">
         <v>269000</v>
@@ -1714,7 +1714,7 @@
         <v>46.73</v>
       </c>
       <c r="O14" t="n">
-        <v>3067860465750</v>
+        <v>3308810046000</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 압박 속 28만 돌파 시도 및 30만 전자 입성 기대감. 자사주 매수 및 배당 정책 강화, 로봇 출시 등은 긍정적 요인.</t>
+          <t>정치적 이슈와 함께 공매도 세력과의 공방 지속. 30만 전자 입성 및 자사주 매수 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '자사주 매수', '로봇']</t>
+          <t>['공매도', '자사주 매수', '30만 전자']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10450</v>
+        <v>10520</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>+3.14%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.23</v>
       </c>
       <c r="E15" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H15" t="n">
         <v>0.44</v>
@@ -1806,7 +1806,7 @@
         <v>0.21</v>
       </c>
       <c r="O15" t="n">
-        <v>67888891495</v>
+        <v>72942831290</v>
       </c>
       <c r="P15" t="n">
         <v>20850</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>터빈블레이드 수주 기대감 속 기관/외인 매수세 유입 전망. 대주주 물량 매도 후 변동성 예상.</t>
+          <t>터빈블레이드 수주 기대감과 강한 재료 발생 가능성이 제기되나, 대주주 물량 매도 및 개미 털기 의혹이 존재합니다.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['터빈블레이드', '수주', '기관']</t>
+          <t>['수주', '대주주', '재료']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>306</v>
+        <v>15040</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.34%</t>
+          <t>+2.66%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="E16" t="n">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H16" t="n">
-        <v>5.34</v>
+        <v>1.72</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>299</v>
+        <v>14650</v>
       </c>
       <c r="K16" t="n">
-        <v>220</v>
+        <v>15100</v>
       </c>
       <c r="L16" t="n">
-        <v>349</v>
+        <v>16680</v>
       </c>
       <c r="M16" t="n">
-        <v>220</v>
+        <v>14800</v>
       </c>
       <c r="N16" t="n">
-        <v>5.29</v>
+        <v>1.58</v>
       </c>
       <c r="O16" t="n">
-        <v>8008445856</v>
+        <v>45861196040</v>
       </c>
       <c r="P16" t="n">
-        <v>901</v>
+        <v>21400</v>
       </c>
       <c r="Q16" t="n">
-        <v>217</v>
+        <v>12090</v>
       </c>
       <c r="R16" t="n">
-        <v>727000</v>
+        <v>-3000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>상장폐지 가능성 및 정리매매 돌입에 대한 우려. 대규모 거래량 발생 및 변동성 확대 속에 투자 주의 요구.</t>
+          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['상장폐지', '정리매매', '거래량']</t>
+          <t>['단주 거래', '자전거래', '스카이랩스']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>0155E0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14970</v>
+        <v>300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="F17" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H17" t="n">
-        <v>1.72</v>
+        <v>5.34</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,60 +1975,60 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>14650</v>
+        <v>299</v>
       </c>
       <c r="K17" t="n">
-        <v>15100</v>
+        <v>220</v>
       </c>
       <c r="L17" t="n">
-        <v>16680</v>
+        <v>349</v>
       </c>
       <c r="M17" t="n">
-        <v>14800</v>
+        <v>220</v>
       </c>
       <c r="N17" t="n">
-        <v>1.58</v>
+        <v>5.29</v>
       </c>
       <c r="O17" t="n">
-        <v>45582431950</v>
+        <v>8192145524</v>
       </c>
       <c r="P17" t="n">
-        <v>21400</v>
+        <v>901</v>
       </c>
       <c r="Q17" t="n">
-        <v>12090</v>
+        <v>217</v>
       </c>
       <c r="R17" t="n">
-        <v>-3000</v>
+        <v>727000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
+          <t>상장폐지 가능성 언급 속 변동성 확대. 정리매매 및 종가 하락 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['단주 거래', '자전거래', '스카이랩스']</t>
+          <t>['상장폐지', '정리매매', '변동성']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0155E0</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15730</v>
+        <v>16070</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.36%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G18" t="n">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>36651884795</v>
+        <v>41184091345</v>
       </c>
       <c r="P18" t="n">
         <v>19380</v>
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8530</v>
+        <v>12370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-2.44%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.04</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="H19" t="n">
-        <v>1.68</v>
+        <v>17.11</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8780</v>
+        <v>12680</v>
       </c>
       <c r="K19" t="n">
-        <v>9060</v>
+        <v>12680</v>
       </c>
       <c r="L19" t="n">
-        <v>9960</v>
+        <v>12680</v>
       </c>
       <c r="M19" t="n">
-        <v>8270</v>
+        <v>11550</v>
       </c>
       <c r="N19" t="n">
-        <v>1.72</v>
+        <v>18.05</v>
       </c>
       <c r="O19" t="n">
-        <v>106143746645</v>
+        <v>29297294100</v>
       </c>
       <c r="P19" t="n">
-        <v>25050</v>
+        <v>14350</v>
       </c>
       <c r="Q19" t="n">
-        <v>3705</v>
+        <v>465</v>
       </c>
       <c r="R19" t="n">
-        <v>-59000</v>
+        <v>48000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
+          <t>계단식 하락 및 하한가 가능성 언급. 투자자들의 공포 심리 확산.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['투경', '탈모 테마', 'JAK 억제']</t>
+          <t>['하락', '하한가', '공포']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12140</v>
+        <v>8430</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.26%</t>
+          <t>-3.99%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F20" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="H20" t="n">
-        <v>17.11</v>
+        <v>1.68</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>12680</v>
+        <v>8780</v>
       </c>
       <c r="K20" t="n">
-        <v>12680</v>
+        <v>9060</v>
       </c>
       <c r="L20" t="n">
-        <v>12680</v>
+        <v>9960</v>
       </c>
       <c r="M20" t="n">
-        <v>11550</v>
+        <v>8270</v>
       </c>
       <c r="N20" t="n">
-        <v>18.05</v>
+        <v>1.72</v>
       </c>
       <c r="O20" t="n">
-        <v>27233477290</v>
+        <v>106990736255</v>
       </c>
       <c r="P20" t="n">
-        <v>14350</v>
+        <v>25050</v>
       </c>
       <c r="Q20" t="n">
-        <v>465</v>
+        <v>3705</v>
       </c>
       <c r="R20" t="n">
-        <v>48000</v>
+        <v>-59000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>계단식 하락 및 하한가 가능성 언급. 투자자들의 공포 심리 확산.</t>
+          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['하락', '하한가', '공포']</t>
+          <t>['투경', '탈모 테마', 'JAK 억제']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
@@ -2326,13 +2326,13 @@
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="H21" t="n">
         <v>38.84</v>
@@ -2358,7 +2358,7 @@
         <v>38.69</v>
       </c>
       <c r="O21" t="n">
-        <v>28545078540</v>
+        <v>28978939025</v>
       </c>
       <c r="P21" t="n">
         <v>19150</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-93.01%</t>
+          <t>-92.98%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2424,7 +2424,7 @@
         <v>52</v>
       </c>
       <c r="G22" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H22" t="n">
         <v>0.08</v>
@@ -2450,7 +2450,7 @@
         <v>0.08</v>
       </c>
       <c r="O22" t="n">
-        <v>863046022</v>
+        <v>897092097</v>
       </c>
       <c r="P22" t="n">
         <v>3660</v>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F2" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G2" t="n">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>141766964063</v>
+        <v>141941767783</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 정부 주최 국산화 수행기관 선정 및 광통신 사업 성장 기대감. 30% 급등 기록.</t>
+          <t>빛과전자, AI 데이터센터 국산화 수행기관 선정 및 광통신 상용화 기대. 10방 뉴스 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '국산화', '광통신']</t>
+          <t>['빛과전자', 'AI 데이터센터', '광통신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10240</v>
+        <v>10320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+21.62%</t>
+          <t>+22.57%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F3" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G3" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>269491521400</v>
+        <v>274126572370</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미프진 국내 독점 판권 보유 및 연내 허가 기대감. 탈모 이슈와 함께 복합적 재료 보유.</t>
+          <t>미프진 국내 독점 판권 보유 현대약품, 연내 허가 기대감. 정부 지원 및 전략적 투자 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미프진', '독점 판권', '탈모']</t>
+          <t>['미프진', '현대약품', '독점 판권']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36450</v>
+        <v>36900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+19.31%</t>
+          <t>+20.79%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>590</v>
+        <v>622</v>
       </c>
       <c r="F4" t="n">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="G4" t="n">
-        <v>1044</v>
+        <v>1147</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>783789631625</v>
+        <v>804827269225</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 지분 공시 및 비교군 없는 세계 최초 기술 보유. 주포의 강한 상승 의지 표출.</t>
+          <t>정부 지분 공시 및 비교군 없는 세계 첫 기술 보유, 주포 언급 및 급등 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정부 지분', '세계 최초 기술', '주포']</t>
+          <t>['정부 지분', '세계 최초', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>143300</v>
+        <v>141300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.17%</t>
+          <t>+15.54%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.11</v>
       </c>
       <c r="E5" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="F5" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G5" t="n">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="H5" t="n">
         <v>13.33</v>
@@ -886,7 +886,7 @@
         <v>13.22</v>
       </c>
       <c r="O5" t="n">
-        <v>191185813200</v>
+        <v>199526246100</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>260조 규모의 미국 원전 사업 관련 뉴스와 구체적인 내용 언급이 있으나, 단기적 고점 및 재료 소멸 우려와 외인 매도세가 관찰됩니다.</t>
+          <t>미국 260조 원전 사업 수주 구체화 및 AP1000 계약 관련 기대감. 대형 원전 사업 관련 내용 포함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전 사업', '260조', '외인 매도']</t>
+          <t>['원전', '사업', '계약']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20650</v>
+        <v>20800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+12.17%</t>
+          <t>+12.98%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="F6" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G6" t="n">
-        <v>1086</v>
+        <v>1117</v>
       </c>
       <c r="H6" t="n">
         <v>10.47</v>
@@ -978,7 +978,7 @@
         <v>10.4</v>
       </c>
       <c r="O6" t="n">
-        <v>419577119365</v>
+        <v>431887965915</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12020</v>
+        <v>11980</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+10.07%</t>
+          <t>+9.71%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.11</v>
       </c>
       <c r="E7" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F7" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G7" t="n">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="H7" t="n">
         <v>5.42</v>
@@ -1070,7 +1070,7 @@
         <v>5.53</v>
       </c>
       <c r="O7" t="n">
-        <v>122724730790</v>
+        <v>126157464270</v>
       </c>
       <c r="P7" t="n">
         <v>30200</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원전 섹터 전반의 상승 기대감과 프랑스와의 원자력 협정 소식이 있으나, 공매도 상환 및 관망 심리가 혼재합니다.</t>
+          <t>프랑스 원자력 협정 및 미국 원전 8기 수주 기대감에 따른 주가 상승 전망. 다만, 과도한 테마 열기 가능성 경계.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '협정', '공매도']</t>
+          <t>['원전', '협정', '기대감']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3885</v>
+        <v>3875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.52%</t>
+          <t>+8.24%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F8" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G8" t="n">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="H8" t="n">
         <v>1.56</v>
@@ -1162,7 +1162,7 @@
         <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>251443374892</v>
+        <v>257292170977</v>
       </c>
       <c r="P8" t="n">
         <v>4335</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>탈모 치료제 관련 이슈와 함께 10년 매집 후 주가 상승 기대감. 거래량 증가 추세.</t>
+          <t>JW신약, 탈모 관련 사업 기대감. 10년 매집 언급 및 목표가 30만 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '10년 매집', '거래량']</t>
+          <t>['JW신약', '탈모', '10년 매집']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50700</v>
+        <v>1884000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.62%</t>
+          <t>+5.66%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>72</v>
+        <v>798</v>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>486</v>
       </c>
       <c r="G9" t="n">
-        <v>208</v>
+        <v>2366</v>
       </c>
       <c r="H9" t="n">
-        <v>38.34</v>
+        <v>50.63</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>48000</v>
+        <v>1783000</v>
       </c>
       <c r="K9" t="n">
-        <v>48550</v>
+        <v>1799000</v>
       </c>
       <c r="L9" t="n">
-        <v>51600</v>
+        <v>1887000</v>
       </c>
       <c r="M9" t="n">
-        <v>48350</v>
+        <v>1777000</v>
       </c>
       <c r="N9" t="n">
-        <v>38.24</v>
+        <v>50.5</v>
       </c>
       <c r="O9" t="n">
-        <v>117433076875</v>
+        <v>4327610092000</v>
       </c>
       <c r="P9" t="n">
-        <v>67300</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>23150</v>
+        <v>274000</v>
       </c>
       <c r="R9" t="n">
-        <v>275000</v>
+        <v>-8000</v>
       </c>
       <c r="S9" t="n">
-        <v>66000</v>
+        <v>108000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
+          <t>SK하이닉스, 185~195만대 물량 소화 후 상승 기대. 용인 반도체 클러스터 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['건설', '원전', '재건']</t>
+          <t>['SK하이닉스', '반도체 클러스터', '물량 소화']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92700</v>
+        <v>50600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.46%</t>
+          <t>+5.42%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>430</v>
+        <v>72</v>
       </c>
       <c r="F10" t="n">
-        <v>257</v>
+        <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>1959</v>
+        <v>209</v>
       </c>
       <c r="H10" t="n">
-        <v>23.63</v>
+        <v>38.34</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>87900</v>
+        <v>48000</v>
       </c>
       <c r="K10" t="n">
-        <v>91200</v>
+        <v>48550</v>
       </c>
       <c r="L10" t="n">
-        <v>93500</v>
+        <v>51600</v>
       </c>
       <c r="M10" t="n">
-        <v>90200</v>
+        <v>48350</v>
       </c>
       <c r="N10" t="n">
-        <v>23.53</v>
+        <v>38.24</v>
       </c>
       <c r="O10" t="n">
-        <v>364898887000</v>
+        <v>121092116825</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>67300</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>23150</v>
       </c>
       <c r="R10" t="n">
-        <v>-222000</v>
+        <v>275000</v>
       </c>
       <c r="S10" t="n">
-        <v>267000</v>
+        <v>66000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 텍사스 발전 사업 참여 확정 및 원전 8기 건설 수주 기대감. SMR 분야 강자로서 웨스팅하우스 지분 인수 및 체코 원전 시공 참여 가능성 부각.</t>
+          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['SMR', '미국 발전 사업', '원전']</t>
+          <t>['건설', '원전', '재건']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1877000</v>
+        <v>92300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.27%</t>
+          <t>+5.01%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>798</v>
+        <v>444</v>
       </c>
       <c r="F11" t="n">
-        <v>476</v>
+        <v>262</v>
       </c>
       <c r="G11" t="n">
-        <v>2320</v>
+        <v>2033</v>
       </c>
       <c r="H11" t="n">
-        <v>50.63</v>
+        <v>23.63</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1783000</v>
+        <v>87900</v>
       </c>
       <c r="K11" t="n">
-        <v>1799000</v>
+        <v>91200</v>
       </c>
       <c r="L11" t="n">
-        <v>1878000</v>
+        <v>93500</v>
       </c>
       <c r="M11" t="n">
-        <v>1777000</v>
+        <v>90200</v>
       </c>
       <c r="N11" t="n">
-        <v>50.5</v>
+        <v>23.53</v>
       </c>
       <c r="O11" t="n">
-        <v>4047769922500</v>
+        <v>377347841300</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>274000</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>-8000</v>
+        <v>-222000</v>
       </c>
       <c r="S11" t="n">
-        <v>108000</v>
+        <v>267000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 업황 개선 및 낸드메모리 품귀 현상 전망. 40조 자사주 매수 및 400만 원 목표 주가 제시.</t>
+          <t>미국 텍사스 발전 사업 참여 확정 및 원전 8기 건설 수주 기대감. SMR 분야 강자로서 웨스팅하우스 지분 인수 및 체코 원전 시공 참여 가능성 부각.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['낸드메모리', '자사주 매수', '반도체']</t>
+          <t>['SMR', '미국 발전 사업', '원전']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13980</v>
+        <v>14070</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.79%</t>
+          <t>+4.45%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.12</v>
       </c>
       <c r="E12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G12" t="n">
-        <v>525</v>
+        <v>553</v>
       </c>
       <c r="H12" t="n">
         <v>1.94</v>
@@ -1530,7 +1530,7 @@
         <v>1.82</v>
       </c>
       <c r="O12" t="n">
-        <v>196527939310</v>
+        <v>199515799545</v>
       </c>
       <c r="P12" t="n">
         <v>31500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Texas 소식과 함께 광통신 사업 성장 기대감. 투경 재지정 판단 및 공매도 물량 언급.</t>
+          <t>대한광통신, Texas 소식 및 단기 저항선 돌파 기대. 빛과전자와의 연관성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['Texas', '광통신', '투경']</t>
+          <t>['대한광통신', 'Texas', '단기 저항선']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33950</v>
+        <v>33900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.66%</t>
+          <t>+3.51%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F13" t="n">
         <v>58</v>
       </c>
       <c r="G13" t="n">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="H13" t="n">
         <v>52.7</v>
@@ -1622,7 +1622,7 @@
         <v>21.02</v>
       </c>
       <c r="O13" t="n">
-        <v>65558705250</v>
+        <v>67561681150</v>
       </c>
       <c r="P13" t="n">
         <v>69500</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 웨스팅하우스 지분 인수 추진 및 원전 사업 확대 기대감. 공매도 물량 집중에도 반등 시도.</t>
+          <t>한국전력, 웨스팅하우스 지분 인수 관련 기대감. 공매도 관련 언급 다수.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '원전', '지분 인수']</t>
+          <t>['한국전력', '웨스팅하우스', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>278500</v>
+        <v>278250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.15%</t>
+          <t>+3.06%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="F14" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="G14" t="n">
-        <v>1838</v>
+        <v>1828</v>
       </c>
       <c r="H14" t="n">
         <v>46.79</v>
@@ -1705,7 +1705,7 @@
         <v>272000</v>
       </c>
       <c r="L14" t="n">
-        <v>278500</v>
+        <v>279000</v>
       </c>
       <c r="M14" t="n">
         <v>269000</v>
@@ -1714,7 +1714,7 @@
         <v>46.73</v>
       </c>
       <c r="O14" t="n">
-        <v>3308810046000</v>
+        <v>3434048050250</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 공매도 세력과의 공방 지속. 30만 전자 입성 및 자사주 매수 기대감.</t>
+          <t>삼성전자, 30만원 돌파 기대감 속 공매도 언급. 정치색 짙은 게시글 다수.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '자사주 매수', '30만 전자']</t>
+          <t>['삼성전자', '공매도', '30만원']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10520</v>
+        <v>10470</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.14%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.23</v>
       </c>
       <c r="E15" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H15" t="n">
         <v>0.44</v>
@@ -1806,7 +1806,7 @@
         <v>0.21</v>
       </c>
       <c r="O15" t="n">
-        <v>72942831290</v>
+        <v>78752095185</v>
       </c>
       <c r="P15" t="n">
         <v>20850</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>터빈블레이드 수주 기대감과 강한 재료 발생 가능성이 제기되나, 대주주 물량 매도 및 개미 털기 의혹이 존재합니다.</t>
+          <t>터빈블레이드 수주 기대감 및 개미 털기 논란. 기관+외계인 수급 주시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['수주', '대주주', '재료']</t>
+          <t>['터빈블레이드', '수주', '기관']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15040</v>
+        <v>14990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.66%</t>
+          <t>+2.32%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.14</v>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -1898,7 +1898,7 @@
         <v>1.58</v>
       </c>
       <c r="O16" t="n">
-        <v>45861196040</v>
+        <v>46317093150</v>
       </c>
       <c r="P16" t="n">
         <v>21400</v>
@@ -1943,92 +1943,92 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>300</v>
+        <v>12520</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.05</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="H17" t="n">
-        <v>5.34</v>
+        <v>17.11</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>299</v>
+        <v>12680</v>
       </c>
       <c r="K17" t="n">
-        <v>220</v>
+        <v>12680</v>
       </c>
       <c r="L17" t="n">
-        <v>349</v>
+        <v>13130</v>
       </c>
       <c r="M17" t="n">
-        <v>220</v>
+        <v>11550</v>
       </c>
       <c r="N17" t="n">
-        <v>5.29</v>
+        <v>18.05</v>
       </c>
       <c r="O17" t="n">
-        <v>8192145524</v>
+        <v>43176451550</v>
       </c>
       <c r="P17" t="n">
-        <v>901</v>
+        <v>14350</v>
       </c>
       <c r="Q17" t="n">
-        <v>217</v>
+        <v>465</v>
       </c>
       <c r="R17" t="n">
-        <v>727000</v>
+        <v>48000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>상장폐지 가능성 언급 속 변동성 확대. 정리매매 및 종가 하락 우려.</t>
+          <t>계단식 하락 및 하한가 가능성 언급. 투자자들의 공포 심리 확산.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['상장폐지', '정리매매', '변동성']</t>
+          <t>['하락', '하한가', '공포']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16070</v>
+        <v>15860</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-1.55%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="F18" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G18" t="n">
-        <v>396</v>
+        <v>477</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>16130</v>
       </c>
       <c r="L18" t="n">
-        <v>16140</v>
+        <v>16420</v>
       </c>
       <c r="M18" t="n">
         <v>15310</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>41184091345</v>
+        <v>60997602570</v>
       </c>
       <c r="P18" t="n">
         <v>19380</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>건설주 상승세 속 호남 메가프로젝트 및 대미 투자 1호 가스복합발전소 수주 기대감. 광주공항 재개장 이슈도 긍정적 요인.</t>
+          <t>금호건설, 호남 메가 프로젝트 및 광주공항 재개장 관련 언급. 건설주 전반 상승세.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['건설주', '대미 투자', '광주공항']</t>
+          <t>['금호건설', '메가 프로젝트', '광주공항']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12370</v>
+        <v>8500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.44%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G19" t="n">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="H19" t="n">
-        <v>17.11</v>
+        <v>1.68</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>12680</v>
+        <v>8780</v>
       </c>
       <c r="K19" t="n">
-        <v>12680</v>
+        <v>9060</v>
       </c>
       <c r="L19" t="n">
-        <v>12680</v>
+        <v>9960</v>
       </c>
       <c r="M19" t="n">
-        <v>11550</v>
+        <v>8270</v>
       </c>
       <c r="N19" t="n">
-        <v>18.05</v>
+        <v>1.72</v>
       </c>
       <c r="O19" t="n">
-        <v>29297294100</v>
+        <v>108457703190</v>
       </c>
       <c r="P19" t="n">
-        <v>14350</v>
+        <v>25050</v>
       </c>
       <c r="Q19" t="n">
-        <v>465</v>
+        <v>3705</v>
       </c>
       <c r="R19" t="n">
-        <v>48000</v>
+        <v>-59000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>계단식 하락 및 하한가 가능성 언급. 투자자들의 공포 심리 확산.</t>
+          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['하락', '하한가', '공포']</t>
+          <t>['투경', '탈모 테마', 'JAK 억제']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8430</v>
+        <v>288</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.99%</t>
+          <t>-3.68%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E20" t="n">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="F20" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H20" t="n">
-        <v>1.68</v>
+        <v>5.34</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,60 +2251,60 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>8780</v>
+        <v>299</v>
       </c>
       <c r="K20" t="n">
-        <v>9060</v>
+        <v>220</v>
       </c>
       <c r="L20" t="n">
-        <v>9960</v>
+        <v>349</v>
       </c>
       <c r="M20" t="n">
-        <v>8270</v>
+        <v>220</v>
       </c>
       <c r="N20" t="n">
-        <v>1.72</v>
+        <v>5.29</v>
       </c>
       <c r="O20" t="n">
-        <v>106990736255</v>
+        <v>8494931403</v>
       </c>
       <c r="P20" t="n">
-        <v>25050</v>
+        <v>901</v>
       </c>
       <c r="Q20" t="n">
-        <v>3705</v>
+        <v>217</v>
       </c>
       <c r="R20" t="n">
-        <v>-59000</v>
+        <v>727000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
+          <t>원풍물산, 상장폐지 가능성 및 정리매매 언급. 폭탄 돌리기 및 탈출 지능순 강조.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['투경', '탈모 테마', 'JAK 억제']</t>
+          <t>['원풍물산', '상장폐지', '정리매매']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8240</v>
+        <v>8260</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-12.90%</t>
+          <t>-12.68%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="H21" t="n">
         <v>38.84</v>
@@ -2358,7 +2358,7 @@
         <v>38.69</v>
       </c>
       <c r="O21" t="n">
-        <v>28978939025</v>
+        <v>29770948205</v>
       </c>
       <c r="P21" t="n">
         <v>19150</v>
@@ -2418,13 +2418,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F22" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G22" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H22" t="n">
         <v>0.08</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>감사의견 적정 및 상반기 보고서 적정으로 인한 거래 재개 기대감. 그러나 과거 재무 악화 및 정리매매 시작으로 인한 불확실성 상존.</t>
+          <t>카프로, 감사의견 적정 및 상반기 보고서 제출. 유통물량 감소 및 공개 매수 가능성 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['감사의견 적정', '정리매매', '재무']</t>
+          <t>['카프로', '감사의견', '유통물량']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>141941767783</v>
+        <v>142005857263</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>빛과전자, AI 데이터센터 국산화 수행기관 선정 및 광통신 상용화 기대. 10방 뉴스 언급.</t>
+          <t>AI 데이터센터 국산화 수행 기관 선정. 광통신 사업 성장 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['빛과전자', 'AI 데이터센터', '광통신']</t>
+          <t>['AI', '데이터센터', '광통신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10320</v>
+        <v>10330</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+22.57%</t>
+          <t>+22.68%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G3" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>274126572370</v>
+        <v>275987373665</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36900</v>
+        <v>36850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+20.79%</t>
+          <t>+20.62%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>622</v>
+        <v>636</v>
       </c>
       <c r="F4" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="G4" t="n">
-        <v>1147</v>
+        <v>1189</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>804827269225</v>
+        <v>813014592175</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 지분 공시 및 비교군 없는 세계 첫 기술 보유, 주포 언급 및 급등 기대.</t>
+          <t>정부 지분 공시 6.54%. 세계 최초 반지형 웨어러블 의료기기 개발.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정부 지분', '세계 최초', '주포']</t>
+          <t>['정부지분', '웨어러블', '의료기기']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141300</v>
+        <v>141400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+15.54%</t>
+          <t>+15.62%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>134</v>
       </c>
       <c r="F5" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G5" t="n">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="H5" t="n">
         <v>13.33</v>
@@ -886,7 +886,7 @@
         <v>13.22</v>
       </c>
       <c r="O5" t="n">
-        <v>199526246100</v>
+        <v>202549104050</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 260조 원전 사업 수주 구체화 및 AP1000 계약 관련 기대감. 대형 원전 사업 관련 내용 포함.</t>
+          <t>260조 미국 원전 사업 관련 구체적인 내용 언급 및 기대감. 단기 고점 및 외인 매도에 따른 하락 우려도 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '사업', '계약']</t>
+          <t>['원전', '260조', '외인']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20800</v>
+        <v>7750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+12.98%</t>
+          <t>+15.50%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="E6" t="n">
-        <v>272</v>
+        <v>88</v>
       </c>
       <c r="F6" t="n">
-        <v>172</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>1117</v>
+        <v>142</v>
       </c>
       <c r="H6" t="n">
-        <v>10.47</v>
+        <v>0.41</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18410</v>
+        <v>6710</v>
       </c>
       <c r="K6" t="n">
-        <v>18800</v>
+        <v>6710</v>
       </c>
       <c r="L6" t="n">
-        <v>21300</v>
+        <v>8090</v>
       </c>
       <c r="M6" t="n">
-        <v>18480</v>
+        <v>6200</v>
       </c>
       <c r="N6" t="n">
-        <v>10.4</v>
+        <v>0.61</v>
       </c>
       <c r="O6" t="n">
-        <v>431887965915</v>
+        <v>74710907470</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>10300</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>952</v>
       </c>
       <c r="R6" t="n">
-        <v>256000</v>
+        <v>75000</v>
       </c>
       <c r="S6" t="n">
-        <v>207000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>원전 사업 신사업 재료 발표 임박 및 에너지 인프라 건설 수요 증가 전망. 2만 원 돌파 기록.</t>
+          <t>외인 매수세에 따른 상승 기대감과 투경 해제 호재. 일부에서는 프로그램 매도 우려도 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '신사업', '에너지 인프라']</t>
+          <t>['외인', '투경']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11980</v>
+        <v>20700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.71%</t>
+          <t>+12.44%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>128</v>
+        <v>273</v>
       </c>
       <c r="F7" t="n">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="G7" t="n">
-        <v>421</v>
+        <v>1134</v>
       </c>
       <c r="H7" t="n">
-        <v>5.42</v>
+        <v>10.47</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>10920</v>
+        <v>18410</v>
       </c>
       <c r="K7" t="n">
-        <v>11300</v>
+        <v>18800</v>
       </c>
       <c r="L7" t="n">
-        <v>12700</v>
+        <v>21300</v>
       </c>
       <c r="M7" t="n">
-        <v>11050</v>
+        <v>18480</v>
       </c>
       <c r="N7" t="n">
-        <v>5.53</v>
+        <v>10.4</v>
       </c>
       <c r="O7" t="n">
-        <v>126157464270</v>
+        <v>435888436690</v>
       </c>
       <c r="P7" t="n">
-        <v>30200</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>3540</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-712000</v>
+        <v>256000</v>
       </c>
       <c r="S7" t="n">
-        <v>1000</v>
+        <v>207000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>프랑스 원자력 협정 및 미국 원전 8기 수주 기대감에 따른 주가 상승 전망. 다만, 과도한 테마 열기 가능성 경계.</t>
+          <t>원전 사업 신사업 재료 발표 임박 및 에너지 인프라 건설 수요 증가 전망. 2만 원 돌파 기록.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '협정', '기대감']</t>
+          <t>['원전', '신사업', '에너지 인프라']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3875</v>
+        <v>11890</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.24%</t>
+          <t>+8.88%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.31</v>
+        <v>-0.11</v>
       </c>
       <c r="E8" t="n">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="F8" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G8" t="n">
-        <v>267</v>
+        <v>430</v>
       </c>
       <c r="H8" t="n">
-        <v>1.56</v>
+        <v>5.42</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3580</v>
+        <v>10920</v>
       </c>
       <c r="K8" t="n">
-        <v>3600</v>
+        <v>11300</v>
       </c>
       <c r="L8" t="n">
-        <v>4335</v>
+        <v>12700</v>
       </c>
       <c r="M8" t="n">
-        <v>3450</v>
+        <v>11050</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>5.53</v>
       </c>
       <c r="O8" t="n">
-        <v>257292170977</v>
+        <v>127993162690</v>
       </c>
       <c r="P8" t="n">
-        <v>4335</v>
+        <v>30200</v>
       </c>
       <c r="Q8" t="n">
-        <v>1246</v>
+        <v>3540</v>
       </c>
       <c r="R8" t="n">
-        <v>-338000</v>
+        <v>-712000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>JW신약, 탈모 관련 사업 기대감. 10년 매집 언급 및 목표가 30만 제시.</t>
+          <t>원전 섹터 강세, 프랑스와 원자력 협정 체결. 8기 원전 70% 대규모 투자 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['JW신약', '탈모', '10년 매집']</t>
+          <t>['원전', '프랑스', '협정']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1884000</v>
+        <v>3895</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.66%</t>
+          <t>+8.80%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>798</v>
+        <v>165</v>
       </c>
       <c r="F9" t="n">
-        <v>486</v>
+        <v>94</v>
       </c>
       <c r="G9" t="n">
-        <v>2366</v>
+        <v>280</v>
       </c>
       <c r="H9" t="n">
-        <v>50.63</v>
+        <v>1.56</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1783000</v>
+        <v>3580</v>
       </c>
       <c r="K9" t="n">
-        <v>1799000</v>
+        <v>3600</v>
       </c>
       <c r="L9" t="n">
-        <v>1887000</v>
+        <v>4335</v>
       </c>
       <c r="M9" t="n">
-        <v>1777000</v>
+        <v>3450</v>
       </c>
       <c r="N9" t="n">
-        <v>50.5</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>4327610092000</v>
+        <v>259997264080</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>4335</v>
       </c>
       <c r="Q9" t="n">
-        <v>274000</v>
+        <v>1246</v>
       </c>
       <c r="R9" t="n">
-        <v>-8000</v>
+        <v>-338000</v>
       </c>
       <c r="S9" t="n">
-        <v>108000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스, 185~195만대 물량 소화 후 상승 기대. 용인 반도체 클러스터 언급.</t>
+          <t>탈모 관련 신규 사업 기대감. 10년 매집 후 반등 가능성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '반도체 클러스터', '물량 소화']</t>
+          <t>['탈모', '신규사업', '반등']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50600</v>
+        <v>1881000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.42%</t>
+          <t>+5.50%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E10" t="n">
-        <v>72</v>
+        <v>799</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>492</v>
       </c>
       <c r="G10" t="n">
-        <v>209</v>
+        <v>2548</v>
       </c>
       <c r="H10" t="n">
-        <v>38.34</v>
+        <v>50.63</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>48000</v>
+        <v>1783000</v>
       </c>
       <c r="K10" t="n">
-        <v>48550</v>
+        <v>1799000</v>
       </c>
       <c r="L10" t="n">
-        <v>51600</v>
+        <v>1888000</v>
       </c>
       <c r="M10" t="n">
-        <v>48350</v>
+        <v>1777000</v>
       </c>
       <c r="N10" t="n">
-        <v>38.24</v>
+        <v>50.5</v>
       </c>
       <c r="O10" t="n">
-        <v>121092116825</v>
+        <v>4525180966000</v>
       </c>
       <c r="P10" t="n">
-        <v>67300</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>23150</v>
+        <v>274000</v>
       </c>
       <c r="R10" t="n">
-        <v>275000</v>
+        <v>-8000</v>
       </c>
       <c r="S10" t="n">
-        <v>66000</v>
+        <v>108000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
+          <t>개인 매도세 속 185~195만 물량 소화 후 200만 돌파 기대. 40조 자사주 소각 가능성.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['건설', '원전', '재건']</t>
+          <t>['물량소화', '자사주', '200만돌파']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>92300</v>
+        <v>50600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.01%</t>
+          <t>+5.42%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>444</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
-        <v>262</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>2033</v>
+        <v>217</v>
       </c>
       <c r="H11" t="n">
-        <v>23.63</v>
+        <v>38.34</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,139 +1423,139 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>87900</v>
+        <v>48000</v>
       </c>
       <c r="K11" t="n">
-        <v>91200</v>
+        <v>48550</v>
       </c>
       <c r="L11" t="n">
-        <v>93500</v>
+        <v>51600</v>
       </c>
       <c r="M11" t="n">
-        <v>90200</v>
+        <v>48350</v>
       </c>
       <c r="N11" t="n">
-        <v>23.53</v>
+        <v>38.24</v>
       </c>
       <c r="O11" t="n">
-        <v>377347841300</v>
+        <v>122785571325</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>67300</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>23150</v>
       </c>
       <c r="R11" t="n">
-        <v>-222000</v>
+        <v>275000</v>
       </c>
       <c r="S11" t="n">
-        <v>267000</v>
+        <v>66000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 텍사스 발전 사업 참여 확정 및 원전 8기 건설 수주 기대감. SMR 분야 강자로서 웨스팅하우스 지분 인수 및 체코 원전 시공 참여 가능성 부각.</t>
+          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['SMR', '미국 발전 사업', '원전']</t>
+          <t>['건설', '원전', '재건']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14070</v>
+        <v>91900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.45%</t>
+          <t>+4.55%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>134</v>
+        <v>455</v>
       </c>
       <c r="F12" t="n">
-        <v>87</v>
+        <v>266</v>
       </c>
       <c r="G12" t="n">
-        <v>553</v>
+        <v>2041</v>
       </c>
       <c r="H12" t="n">
-        <v>1.94</v>
+        <v>23.63</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13470</v>
+        <v>87900</v>
       </c>
       <c r="K12" t="n">
-        <v>13580</v>
+        <v>91200</v>
       </c>
       <c r="L12" t="n">
-        <v>14450</v>
+        <v>93500</v>
       </c>
       <c r="M12" t="n">
-        <v>13420</v>
+        <v>90200</v>
       </c>
       <c r="N12" t="n">
-        <v>1.82</v>
+        <v>23.53</v>
       </c>
       <c r="O12" t="n">
-        <v>199515799545</v>
+        <v>384342332800</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>1252</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-161000</v>
+        <v>-222000</v>
       </c>
       <c r="S12" t="n">
-        <v>11000</v>
+        <v>267000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대한광통신, Texas 소식 및 단기 저항선 돌파 기대. 빛과전자와의 연관성 언급.</t>
+          <t>미국 텍사스 발전 사업 참여 확정 및 원전 8기 건설 수주 기대감. SMR 분야 강자로서 웨스팅하우스 지분 인수 및 체코 원전 시공 참여 가능성 부각.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대한광통신', 'Texas', '단기 저항선']</t>
+          <t>['SMR', '미국 발전 사업', '원전']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33900</v>
+        <v>14060</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.51%</t>
+          <t>+4.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="E13" t="n">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="F13" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="G13" t="n">
-        <v>343</v>
+        <v>637</v>
       </c>
       <c r="H13" t="n">
-        <v>52.7</v>
+        <v>1.94</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>32750</v>
+        <v>13470</v>
       </c>
       <c r="K13" t="n">
-        <v>33700</v>
+        <v>13580</v>
       </c>
       <c r="L13" t="n">
-        <v>34350</v>
+        <v>14450</v>
       </c>
       <c r="M13" t="n">
-        <v>33450</v>
+        <v>13420</v>
       </c>
       <c r="N13" t="n">
-        <v>21.02</v>
+        <v>1.82</v>
       </c>
       <c r="O13" t="n">
-        <v>67561681150</v>
+        <v>200678110685</v>
       </c>
       <c r="P13" t="n">
-        <v>69500</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>30400</v>
+        <v>1252</v>
       </c>
       <c r="R13" t="n">
-        <v>324000</v>
+        <v>-161000</v>
       </c>
       <c r="S13" t="n">
-        <v>194000</v>
+        <v>11000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>한국전력, 웨스팅하우스 지분 인수 관련 기대감. 공매도 관련 언급 다수.</t>
+          <t>Texas 소식 관련 단기 저항선 돌파 및 매물대 소화 과정. 14000원 돌파 시 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['한국전력', '웨스팅하우스', '공매도']</t>
+          <t>['Texas', '매물대', '14000원돌파']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>278250</v>
+        <v>33850</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.06%</t>
+          <t>+3.36%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>789</v>
+        <v>86</v>
       </c>
       <c r="F14" t="n">
-        <v>454</v>
+        <v>59</v>
       </c>
       <c r="G14" t="n">
-        <v>1828</v>
+        <v>349</v>
       </c>
       <c r="H14" t="n">
-        <v>46.79</v>
+        <v>52.7</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>270000</v>
+        <v>32750</v>
       </c>
       <c r="K14" t="n">
-        <v>272000</v>
+        <v>33700</v>
       </c>
       <c r="L14" t="n">
-        <v>279000</v>
+        <v>34350</v>
       </c>
       <c r="M14" t="n">
-        <v>269000</v>
+        <v>33450</v>
       </c>
       <c r="N14" t="n">
-        <v>46.73</v>
+        <v>21.02</v>
       </c>
       <c r="O14" t="n">
-        <v>3434048050250</v>
+        <v>68785381200</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>69500</v>
       </c>
       <c r="Q14" t="n">
-        <v>69600</v>
+        <v>30400</v>
       </c>
       <c r="R14" t="n">
-        <v>1295000</v>
+        <v>324000</v>
       </c>
       <c r="S14" t="n">
-        <v>223000</v>
+        <v>194000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼성전자, 30만원 돌파 기대감 속 공매도 언급. 정치색 짙은 게시글 다수.</t>
+          <t>한국전력, 웨스팅하우스 지분 인수 관련 기대감. 공매도 관련 언급 다수.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['삼성전자', '공매도', '30만원']</t>
+          <t>['한국전력', '웨스팅하우스', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10470</v>
+        <v>278500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+3.15%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.23</v>
+        <v>0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>108</v>
+        <v>797</v>
       </c>
       <c r="F15" t="n">
-        <v>66</v>
+        <v>462</v>
       </c>
       <c r="G15" t="n">
-        <v>120</v>
+        <v>1937</v>
       </c>
       <c r="H15" t="n">
-        <v>0.44</v>
+        <v>46.79</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>10200</v>
+        <v>270000</v>
       </c>
       <c r="K15" t="n">
-        <v>10600</v>
+        <v>272000</v>
       </c>
       <c r="L15" t="n">
-        <v>10970</v>
+        <v>279000</v>
       </c>
       <c r="M15" t="n">
-        <v>9980</v>
+        <v>269000</v>
       </c>
       <c r="N15" t="n">
-        <v>0.21</v>
+        <v>46.73</v>
       </c>
       <c r="O15" t="n">
-        <v>78752095185</v>
+        <v>3571441950250</v>
       </c>
       <c r="P15" t="n">
-        <v>20850</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>4020</v>
+        <v>69600</v>
       </c>
       <c r="R15" t="n">
-        <v>-59000</v>
+        <v>1295000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>223000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>터빈블레이드 수주 기대감 및 개미 털기 논란. 기관+외계인 수급 주시.</t>
+          <t>이재명 연임 추진 시 코스피 15000, 삼성전자 100만 예상. 공매도 발악으로 28만 돌파 시 숏커버링 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['터빈블레이드', '수주', '기관']</t>
+          <t>['이재명', '공매도', '숏커버링']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14990</v>
+        <v>10490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.32%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="G16" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="H16" t="n">
-        <v>1.72</v>
+        <v>0.44</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,47 +1883,47 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14650</v>
+        <v>10200</v>
       </c>
       <c r="K16" t="n">
-        <v>15100</v>
+        <v>10600</v>
       </c>
       <c r="L16" t="n">
-        <v>16680</v>
+        <v>10970</v>
       </c>
       <c r="M16" t="n">
-        <v>14800</v>
+        <v>9980</v>
       </c>
       <c r="N16" t="n">
-        <v>1.58</v>
+        <v>0.21</v>
       </c>
       <c r="O16" t="n">
-        <v>46317093150</v>
+        <v>79895816560</v>
       </c>
       <c r="P16" t="n">
-        <v>21400</v>
+        <v>20850</v>
       </c>
       <c r="Q16" t="n">
-        <v>12090</v>
+        <v>4020</v>
       </c>
       <c r="R16" t="n">
-        <v>-3000</v>
+        <v>-59000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
+          <t>터빈블레이드 수주 기대감으로 인한 상승 전망. 개미 털기 및 기관/외계인 매수세 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['단주 거래', '자전거래', '스카이랩스']</t>
+          <t>['터빈블레이드', '수주', '기관']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,82 +1931,82 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0155E0</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12520</v>
+        <v>14940</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.26%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="E17" t="n">
         <v>51</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G17" t="n">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="H17" t="n">
-        <v>17.11</v>
+        <v>1.72</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>12680</v>
+        <v>14650</v>
       </c>
       <c r="K17" t="n">
-        <v>12680</v>
+        <v>15100</v>
       </c>
       <c r="L17" t="n">
-        <v>13130</v>
+        <v>16680</v>
       </c>
       <c r="M17" t="n">
-        <v>11550</v>
+        <v>14800</v>
       </c>
       <c r="N17" t="n">
-        <v>18.05</v>
+        <v>1.58</v>
       </c>
       <c r="O17" t="n">
-        <v>43176451550</v>
+        <v>46526937540</v>
       </c>
       <c r="P17" t="n">
-        <v>14350</v>
+        <v>21400</v>
       </c>
       <c r="Q17" t="n">
-        <v>465</v>
+        <v>12090</v>
       </c>
       <c r="R17" t="n">
-        <v>48000</v>
+        <v>-3000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>계단식 하락 및 하한가 가능성 언급. 투자자들의 공포 심리 확산.</t>
+          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['하락', '하한가', '공포']</t>
+          <t>['단주 거래', '자전거래', '스카이랩스']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>0155E0</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15860</v>
+        <v>16110</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.55%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F18" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G18" t="n">
-        <v>477</v>
+        <v>517</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60997602570</v>
+        <v>64450211905</v>
       </c>
       <c r="P18" t="n">
         <v>19380</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>금호건설, 호남 메가 프로젝트 및 광주공항 재개장 관련 언급. 건설주 전반 상승세.</t>
+          <t>반도체 조정 속 호남 메가 프로젝트 기대감. 광주공항 재개장 뉴스.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['금호건설', '메가 프로젝트', '광주공항']</t>
+          <t>['호남', '메가프로젝트', '광주공항']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8500</v>
+        <v>12650</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.04</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="H19" t="n">
-        <v>1.68</v>
+        <v>17.11</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8780</v>
+        <v>12680</v>
       </c>
       <c r="K19" t="n">
-        <v>9060</v>
+        <v>12680</v>
       </c>
       <c r="L19" t="n">
-        <v>9960</v>
+        <v>13130</v>
       </c>
       <c r="M19" t="n">
-        <v>8270</v>
+        <v>11550</v>
       </c>
       <c r="N19" t="n">
-        <v>1.72</v>
+        <v>18.05</v>
       </c>
       <c r="O19" t="n">
-        <v>108457703190</v>
+        <v>46378290780</v>
       </c>
       <c r="P19" t="n">
-        <v>25050</v>
+        <v>14350</v>
       </c>
       <c r="Q19" t="n">
-        <v>3705</v>
+        <v>465</v>
       </c>
       <c r="R19" t="n">
-        <v>-59000</v>
+        <v>48000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
+          <t>계단식 하락 및 하한가 가능성 언급. 투자자들의 공포 심리 확산.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['투경', '탈모 테마', 'JAK 억제']</t>
+          <t>['하락', '하한가', '공포']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.68%</t>
+          <t>-3.01%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>96</v>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H20" t="n">
         <v>5.34</v>
@@ -2266,7 +2266,7 @@
         <v>5.29</v>
       </c>
       <c r="O20" t="n">
-        <v>8494931403</v>
+        <v>8617209082</v>
       </c>
       <c r="P20" t="n">
         <v>901</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>원풍물산, 상장폐지 가능성 및 정리매매 언급. 폭탄 돌리기 및 탈출 지능순 강조.</t>
+          <t>상장폐지 우려 속 거래량 급증. 회생 가능성 및 추석 매출 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원풍물산', '상장폐지', '정리매매']</t>
+          <t>['상장폐지', '거래량', '회생']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8260</v>
+        <v>8510</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-12.68%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.15</v>
+        <v>-0.04</v>
       </c>
       <c r="E21" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
-        <v>223</v>
+        <v>59</v>
       </c>
       <c r="H21" t="n">
-        <v>38.84</v>
+        <v>1.68</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>9460</v>
+        <v>8780</v>
       </c>
       <c r="K21" t="n">
-        <v>9700</v>
+        <v>9060</v>
       </c>
       <c r="L21" t="n">
-        <v>9760</v>
+        <v>9960</v>
       </c>
       <c r="M21" t="n">
-        <v>8110</v>
+        <v>8270</v>
       </c>
       <c r="N21" t="n">
-        <v>38.69</v>
+        <v>1.72</v>
       </c>
       <c r="O21" t="n">
-        <v>29770948205</v>
+        <v>109205800295</v>
       </c>
       <c r="P21" t="n">
-        <v>19150</v>
+        <v>25050</v>
       </c>
       <c r="Q21" t="n">
-        <v>3445</v>
+        <v>3705</v>
       </c>
       <c r="R21" t="n">
-        <v>-32000</v>
+        <v>-59000</v>
       </c>
       <c r="S21" t="n">
-        <v>-106000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>삼성, 포스코 관련주 상승 대비 부진한 주가 흐름과 조정에 대한 언급.</t>
+          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['포스코', '삼성', '조정']</t>
+          <t>['투경', '탈모 테마', 'JAK 억제']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,86 +2396,86 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>257</v>
+        <v>8230</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-92.98%</t>
+          <t>-13.00%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E22" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="G22" t="n">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="H22" t="n">
-        <v>0.08</v>
+        <v>38.84</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3660</v>
+        <v>9460</v>
       </c>
       <c r="K22" t="n">
-        <v>300</v>
+        <v>9700</v>
       </c>
       <c r="L22" t="n">
-        <v>340</v>
+        <v>9760</v>
       </c>
       <c r="M22" t="n">
-        <v>251</v>
+        <v>8110</v>
       </c>
       <c r="N22" t="n">
-        <v>0.08</v>
+        <v>38.69</v>
       </c>
       <c r="O22" t="n">
-        <v>897092097</v>
+        <v>30850983660</v>
       </c>
       <c r="P22" t="n">
-        <v>3660</v>
+        <v>19150</v>
       </c>
       <c r="Q22" t="n">
-        <v>251</v>
+        <v>3445</v>
       </c>
       <c r="R22" t="n">
-        <v>-2000</v>
+        <v>-32000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-106000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>카프로, 감사의견 적정 및 상반기 보고서 제출. 유통물량 감소 및 공개 매수 가능성 언급.</t>
+          <t>삼성, 포스코 관련주 상승 대비 부진한 주가 흐름과 조정에 대한 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['카프로', '감사의견', '유통물량']</t>
+          <t>['포스코', '삼성', '조정']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2483,10 +2483,102 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>033790</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>카프로</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>258</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-92.95%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>93</v>
+      </c>
+      <c r="F23" t="n">
+        <v>57</v>
+      </c>
+      <c r="G23" t="n">
+        <v>195</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>3660</v>
+      </c>
+      <c r="K23" t="n">
+        <v>300</v>
+      </c>
+      <c r="L23" t="n">
+        <v>340</v>
+      </c>
+      <c r="M23" t="n">
+        <v>251</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O23" t="n">
+        <v>943676577</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3660</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>251</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>감사의견 적정으로 재개 기대. 대주주 및 유통물량 변동성 우려.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['감사의견', '재개', '유통물량']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>006380</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F2" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G2" t="n">
-        <v>254</v>
+        <v>306</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>142005857263</v>
+        <v>142703630703</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 국산화 수행 기관 선정. 광통신 사업 성장 기대.</t>
+          <t>AI 데이터센터 정부 주최 수행기관 선정 및 광통신 상용화 뉴스 기반 10방 상한가 기대. 글로벌 고객사 확보.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', '데이터센터', '광통신']</t>
+          <t>['AI 데이터센터', '광통신', '상한가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10330</v>
+        <v>10070</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+22.68%</t>
+          <t>+19.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="F3" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="G3" t="n">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>275987373665</v>
+        <v>295074592205</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미프진 국내 독점 판권 보유 현대약품, 연내 허가 기대감. 정부 지원 및 전략적 투자 언급.</t>
+          <t>미프진 연내 허가 및 정부 도입 구체화 소식, 대화제약과의 전략적 투자 언급. 일부 외인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미프진', '현대약품', '독점 판권']</t>
+          <t>['미프진', '허가', '투자']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36850</v>
+        <v>144500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+20.62%</t>
+          <t>+18.15%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="E4" t="n">
-        <v>636</v>
+        <v>178</v>
       </c>
       <c r="F4" t="n">
-        <v>322</v>
+        <v>90</v>
       </c>
       <c r="G4" t="n">
-        <v>1189</v>
+        <v>236</v>
       </c>
       <c r="H4" t="n">
-        <v>0.23</v>
+        <v>13.33</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>30550</v>
+        <v>122300</v>
       </c>
       <c r="K4" t="n">
-        <v>31650</v>
+        <v>129400</v>
       </c>
       <c r="L4" t="n">
-        <v>39350</v>
+        <v>145800</v>
       </c>
       <c r="M4" t="n">
-        <v>31350</v>
+        <v>128100</v>
       </c>
       <c r="N4" t="n">
-        <v>0.16</v>
+        <v>13.22</v>
       </c>
       <c r="O4" t="n">
-        <v>813014592175</v>
+        <v>244867928400</v>
       </c>
       <c r="P4" t="n">
-        <v>39350</v>
+        <v>198000</v>
       </c>
       <c r="Q4" t="n">
-        <v>8200</v>
+        <v>77100</v>
       </c>
       <c r="R4" t="n">
-        <v>-49000</v>
+        <v>10000</v>
       </c>
       <c r="S4" t="n">
-        <v>-2000</v>
+        <v>88000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 지분 공시 6.54%. 세계 최초 반지형 웨어러블 의료기기 개발.</t>
+          <t>260조 규모의 원전 사업 수주 가능성이 언급되며 강한 상승세를 보임. AP1000 관련 구체적인 내용과 수익 계산이 포함된 뉴스가 투자 심리를 자극하고 있음.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정부지분', '웨어러블', '의료기기']</t>
+          <t>['원전 사업', '260조', 'AP1000']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>052690</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141400</v>
+        <v>7900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+15.62%</t>
+          <t>+17.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.11</v>
+        <v>-0.2</v>
       </c>
       <c r="E5" t="n">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="F5" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>197</v>
+        <v>423</v>
       </c>
       <c r="H5" t="n">
-        <v>13.33</v>
+        <v>0.41</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>122300</v>
+        <v>6710</v>
       </c>
       <c r="K5" t="n">
-        <v>129400</v>
+        <v>6710</v>
       </c>
       <c r="L5" t="n">
-        <v>144600</v>
+        <v>8450</v>
       </c>
       <c r="M5" t="n">
-        <v>128100</v>
+        <v>6200</v>
       </c>
       <c r="N5" t="n">
-        <v>13.22</v>
+        <v>0.61</v>
       </c>
       <c r="O5" t="n">
-        <v>202549104050</v>
+        <v>138929546330</v>
       </c>
       <c r="P5" t="n">
-        <v>198000</v>
+        <v>10300</v>
       </c>
       <c r="Q5" t="n">
-        <v>77100</v>
+        <v>952</v>
       </c>
       <c r="R5" t="n">
-        <v>-11000</v>
+        <v>31000</v>
       </c>
       <c r="S5" t="n">
-        <v>64000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>260조 미국 원전 사업 관련 구체적인 내용 언급 및 기대감. 단기 고점 및 외인 매도에 따른 하락 우려도 존재.</t>
+          <t>레미콘 총파업 관련 수혜 기대감, 독점 공급 가능성 언급. 신고가 근접 및 7연상 목표 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '260조', '외인']</t>
+          <t>['서산', '레미콘', '수혜']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7750</v>
+        <v>35700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+15.50%</t>
+          <t>+16.86%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>88</v>
+        <v>787</v>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>368</v>
       </c>
       <c r="G6" t="n">
-        <v>142</v>
+        <v>1480</v>
       </c>
       <c r="H6" t="n">
-        <v>0.41</v>
+        <v>0.23</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6710</v>
+        <v>30550</v>
       </c>
       <c r="K6" t="n">
-        <v>6710</v>
+        <v>31650</v>
       </c>
       <c r="L6" t="n">
-        <v>8090</v>
+        <v>39350</v>
       </c>
       <c r="M6" t="n">
-        <v>6200</v>
+        <v>31350</v>
       </c>
       <c r="N6" t="n">
-        <v>0.61</v>
+        <v>0.16</v>
       </c>
       <c r="O6" t="n">
-        <v>74710907470</v>
+        <v>896921830275</v>
       </c>
       <c r="P6" t="n">
-        <v>10300</v>
+        <v>39350</v>
       </c>
       <c r="Q6" t="n">
-        <v>952</v>
+        <v>8200</v>
       </c>
       <c r="R6" t="n">
-        <v>75000</v>
+        <v>-24000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외인 매수세에 따른 상승 기대감과 투경 해제 호재. 일부에서는 프로그램 매도 우려도 제기.</t>
+          <t>정부 지분 공시(6.54%) 및 세계 최초 비침습적 비교군 없는 기술 기반 10만원 목표 기대. 주포 개입 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외인', '투경']</t>
+          <t>['정부 지분', '비침습적', '주포']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20700</v>
+        <v>20800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+12.44%</t>
+          <t>+12.98%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>273</v>
+        <v>310</v>
       </c>
       <c r="F7" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="G7" t="n">
-        <v>1134</v>
+        <v>1257</v>
       </c>
       <c r="H7" t="n">
         <v>10.47</v>
@@ -1070,7 +1070,7 @@
         <v>10.4</v>
       </c>
       <c r="O7" t="n">
-        <v>435888436690</v>
+        <v>483602718490</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1079,14 +1079,14 @@
         <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>256000</v>
+        <v>325000</v>
       </c>
       <c r="S7" t="n">
-        <v>207000</v>
+        <v>555000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원전 사업 신사업 재료 발표 임박 및 에너지 인프라 건설 수요 증가 전망. 2만 원 돌파 기록.</t>
+          <t>원전 사업과 에너지 인프라 건설 신사업 발표에 따른 기대감. 2만대 돌파 및 골든크로스 형성, 대장주로서의 면모 부각.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '신사업', '에너지 인프라']</t>
+          <t>['원전', '에너지 인프라', '골든크로스']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11890</v>
+        <v>12070</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.88%</t>
+          <t>+10.53%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.11</v>
       </c>
       <c r="E8" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G8" t="n">
-        <v>430</v>
+        <v>502</v>
       </c>
       <c r="H8" t="n">
         <v>5.42</v>
@@ -1162,7 +1162,7 @@
         <v>5.53</v>
       </c>
       <c r="O8" t="n">
-        <v>127993162690</v>
+        <v>140948467085</v>
       </c>
       <c r="P8" t="n">
         <v>30200</v>
@@ -1171,23 +1171,23 @@
         <v>3540</v>
       </c>
       <c r="R8" t="n">
-        <v>-712000</v>
+        <v>-564000</v>
       </c>
       <c r="S8" t="n">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원전 섹터 강세, 프랑스와 원자력 협정 체결. 8기 원전 70% 대규모 투자 기대.</t>
+          <t>미국 원전 8기 관련 70% 계약 기대감, 프랑스와의 원자력 협정 언급. 14000원 돌파 및 이번 달, 내일 상한가 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '프랑스', '협정']</t>
+          <t>['우리기술', '원전', '대미투자']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3895</v>
+        <v>3820</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.80%</t>
+          <t>+6.70%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="F9" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="H9" t="n">
         <v>1.56</v>
@@ -1254,7 +1254,7 @@
         <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>259997264080</v>
+        <v>277429162534</v>
       </c>
       <c r="P9" t="n">
         <v>4335</v>
@@ -1263,14 +1263,14 @@
         <v>1246</v>
       </c>
       <c r="R9" t="n">
-        <v>-338000</v>
+        <v>-389000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>탈모 관련 신규 사업 기대감. 10년 매집 후 반등 가능성.</t>
+          <t>계단식 하락 및 음봉 마무리 가능성 언급, 4천원 이하 하락 시 주의 경고. 탈모 관련 사업 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['탈모', '신규사업', '반등']</t>
+          <t>['JW신약', '하락', '탈모']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1881000</v>
+        <v>34800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.50%</t>
+          <t>+6.26%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.13</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>799</v>
+        <v>111</v>
       </c>
       <c r="F10" t="n">
-        <v>492</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>2548</v>
+        <v>414</v>
       </c>
       <c r="H10" t="n">
-        <v>50.63</v>
+        <v>52.79</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1783000</v>
+        <v>32750</v>
       </c>
       <c r="K10" t="n">
-        <v>1799000</v>
+        <v>33700</v>
       </c>
       <c r="L10" t="n">
-        <v>1888000</v>
+        <v>34800</v>
       </c>
       <c r="M10" t="n">
-        <v>1777000</v>
+        <v>33450</v>
       </c>
       <c r="N10" t="n">
-        <v>50.5</v>
+        <v>21.02</v>
       </c>
       <c r="O10" t="n">
-        <v>4525180966000</v>
+        <v>98651235650</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>69500</v>
       </c>
       <c r="Q10" t="n">
-        <v>274000</v>
+        <v>30400</v>
       </c>
       <c r="R10" t="n">
-        <v>-8000</v>
+        <v>263000</v>
       </c>
       <c r="S10" t="n">
-        <v>108000</v>
+        <v>237000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>개인 매도세 속 185~195만 물량 소화 후 200만 돌파 기대. 40조 자사주 소각 가능성.</t>
+          <t>한국전력, 웨스팅하우스 지분 인수 관련 기대감. 공매도 관련 언급 다수.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['물량소화', '자사주', '200만돌파']</t>
+          <t>['한국전력', '웨스팅하우스', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50600</v>
+        <v>50500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.42%</t>
+          <t>+5.21%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F11" t="n">
         <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="H11" t="n">
         <v>38.34</v>
@@ -1438,7 +1438,7 @@
         <v>38.24</v>
       </c>
       <c r="O11" t="n">
-        <v>122785571325</v>
+        <v>137324046175</v>
       </c>
       <c r="P11" t="n">
         <v>67300</v>
@@ -1447,10 +1447,10 @@
         <v>23150</v>
       </c>
       <c r="R11" t="n">
-        <v>275000</v>
+        <v>242000</v>
       </c>
       <c r="S11" t="n">
-        <v>66000</v>
+        <v>126000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>91900</v>
+        <v>91500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.55%</t>
+          <t>+4.10%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>455</v>
+        <v>517</v>
       </c>
       <c r="F12" t="n">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="G12" t="n">
-        <v>2041</v>
+        <v>2216</v>
       </c>
       <c r="H12" t="n">
         <v>23.63</v>
@@ -1530,7 +1530,7 @@
         <v>23.53</v>
       </c>
       <c r="O12" t="n">
-        <v>384342332800</v>
+        <v>450836329600</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1539,23 +1539,23 @@
         <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-222000</v>
+        <v>-92000</v>
       </c>
       <c r="S12" t="n">
-        <v>267000</v>
+        <v>544000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 텍사스 발전 사업 참여 확정 및 원전 8기 건설 수주 기대감. SMR 분야 강자로서 웨스팅하우스 지분 인수 및 체코 원전 시공 참여 가능성 부각.</t>
+          <t>미국 텍사스 발전사업(SMR 8기 포함) 확정 및 웨스팅하우스 지분 인수 추진 소식, 체코 원전 시공 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['SMR', '미국 발전 사업', '원전']</t>
+          <t>['SMR', '원전', '텍사스']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14060</v>
+        <v>13980</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+4.38%</t>
+          <t>+3.79%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.12</v>
       </c>
       <c r="E13" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F13" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G13" t="n">
-        <v>637</v>
+        <v>672</v>
       </c>
       <c r="H13" t="n">
         <v>1.94</v>
@@ -1622,7 +1622,7 @@
         <v>1.82</v>
       </c>
       <c r="O13" t="n">
-        <v>200678110685</v>
+        <v>212917779660</v>
       </c>
       <c r="P13" t="n">
         <v>31500</v>
@@ -1631,23 +1631,23 @@
         <v>1252</v>
       </c>
       <c r="R13" t="n">
-        <v>-161000</v>
+        <v>-132000</v>
       </c>
       <c r="S13" t="n">
-        <v>11000</v>
+        <v>27000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Texas 소식 관련 단기 저항선 돌파 및 매물대 소화 과정. 14000원 돌파 시 추가 상승 기대.</t>
+          <t>Texas 관련 소식 및 14000원, 14500원, 15000원, 17510원 등 목표가 제시. 공매도 물량 소화 및 매집 구간 분석.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['Texas', '매물대', '14000원돌파']</t>
+          <t>['대한광통신', 'Texas', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33850</v>
+        <v>1850000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+3.76%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.01</v>
+        <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>86</v>
+        <v>794</v>
       </c>
       <c r="F14" t="n">
-        <v>59</v>
+        <v>487</v>
       </c>
       <c r="G14" t="n">
-        <v>349</v>
+        <v>2187</v>
       </c>
       <c r="H14" t="n">
-        <v>52.7</v>
+        <v>50.63</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>32750</v>
+        <v>1783000</v>
       </c>
       <c r="K14" t="n">
-        <v>33700</v>
+        <v>1799000</v>
       </c>
       <c r="L14" t="n">
-        <v>34350</v>
+        <v>1889000</v>
       </c>
       <c r="M14" t="n">
-        <v>33450</v>
+        <v>1777000</v>
       </c>
       <c r="N14" t="n">
-        <v>21.02</v>
+        <v>50.5</v>
       </c>
       <c r="O14" t="n">
-        <v>68785381200</v>
+        <v>5961519918000</v>
       </c>
       <c r="P14" t="n">
-        <v>69500</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>30400</v>
+        <v>274000</v>
       </c>
       <c r="R14" t="n">
-        <v>324000</v>
+        <v>23000</v>
       </c>
       <c r="S14" t="n">
-        <v>194000</v>
+        <v>221000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>한국전력, 웨스팅하우스 지분 인수 관련 기대감. 공매도 관련 언급 다수.</t>
+          <t>외국인 및 기관의 대량 매수세 관찰, 190만원 돌파 및 200만원, 220만원 목표가 제시. 추석 랠리 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['한국전력', '웨스팅하우스', '공매도']</t>
+          <t>['SK하이닉스', '외인매수', '목표가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>278500</v>
+        <v>276000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.15%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="F15" t="n">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="G15" t="n">
-        <v>1937</v>
+        <v>1789</v>
       </c>
       <c r="H15" t="n">
         <v>46.79</v>
@@ -1806,7 +1806,7 @@
         <v>46.73</v>
       </c>
       <c r="O15" t="n">
-        <v>3571441950250</v>
+        <v>4710873998750</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1815,23 +1815,23 @@
         <v>69600</v>
       </c>
       <c r="R15" t="n">
-        <v>1295000</v>
+        <v>2004000</v>
       </c>
       <c r="S15" t="n">
-        <v>223000</v>
+        <v>568000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이재명 연임 추진 시 코스피 15000, 삼성전자 100만 예상. 공매도 발악으로 28만 돌파 시 숏커버링 기대.</t>
+          <t>28만원 이상 돌파 시 숏커버 기대감 및 30만원, 35만원, 40만원, 50층 등 높은 목표가 제시. AI/AGI 시대 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['이재명', '공매도', '숏커버링']</t>
+          <t>['삼성전자', '목표가', 'AI']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10490</v>
+        <v>10260</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.23</v>
       </c>
       <c r="E16" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="F16" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G16" t="n">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="H16" t="n">
         <v>0.44</v>
@@ -1898,7 +1898,7 @@
         <v>0.21</v>
       </c>
       <c r="O16" t="n">
-        <v>79895816560</v>
+        <v>86557693645</v>
       </c>
       <c r="P16" t="n">
         <v>20850</v>
@@ -1907,23 +1907,23 @@
         <v>4020</v>
       </c>
       <c r="R16" t="n">
-        <v>-59000</v>
+        <v>-56000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>터빈블레이드 수주 기대감으로 인한 상승 전망. 개미 털기 및 기관/외계인 매수세 언급.</t>
+          <t>종목에 대한 부정적 의견과 기대감이 혼재하며, 투자자들의 잦은 매매 움직임이 나타나는 상황. 터빈 블레이드 수주 관련 기대감이 있으나, 매도세가 강하게 나타나고 있음.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['터빈블레이드', '수주', '기관']</t>
+          <t>['개미탕', '터빈블레이드', '매도세']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,175 +1943,175 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14940</v>
+        <v>15980</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.98%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>51</v>
+        <v>185</v>
       </c>
       <c r="F17" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="G17" t="n">
-        <v>51</v>
+        <v>677</v>
       </c>
       <c r="H17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>14650</v>
+        <v>16110</v>
       </c>
       <c r="K17" t="n">
-        <v>15100</v>
+        <v>16130</v>
       </c>
       <c r="L17" t="n">
-        <v>16680</v>
+        <v>16420</v>
       </c>
       <c r="M17" t="n">
-        <v>14800</v>
+        <v>15310</v>
       </c>
       <c r="N17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>46526937540</v>
+        <v>85351589965</v>
       </c>
       <c r="P17" t="n">
-        <v>21400</v>
+        <v>19380</v>
       </c>
       <c r="Q17" t="n">
-        <v>12090</v>
+        <v>3200</v>
       </c>
       <c r="R17" t="n">
-        <v>-3000</v>
+        <v>-106000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
+          <t>호남 메가 프로젝트 및 30조대 투자 언급에도 불구하고 건설주 상승 추세와 상반된 약세. 주가 상승 기대감 희미.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['단주 거래', '자전거래', '스카이랩스']</t>
+          <t>['메가 프로젝트', '가스복합발전소', '건설주']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0155E0</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16110</v>
+        <v>295</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E18" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="F18" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G18" t="n">
-        <v>517</v>
+        <v>67</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>16110</v>
+        <v>299</v>
       </c>
       <c r="K18" t="n">
-        <v>16130</v>
+        <v>220</v>
       </c>
       <c r="L18" t="n">
-        <v>16420</v>
+        <v>349</v>
       </c>
       <c r="M18" t="n">
-        <v>15310</v>
+        <v>220</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="O18" t="n">
-        <v>64450211905</v>
+        <v>9890523513</v>
       </c>
       <c r="P18" t="n">
-        <v>19380</v>
+        <v>901</v>
       </c>
       <c r="Q18" t="n">
-        <v>3200</v>
+        <v>217</v>
       </c>
       <c r="R18" t="n">
-        <v>-5000</v>
+        <v>644000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>반도체 조정 속 호남 메가 프로젝트 기대감. 광주공항 재개장 뉴스.</t>
+          <t>상장폐지 가능성 및 거래 정지 공시 우려, 하한가 및 폭탄 돌리기 언급. 투자 탈출 의견 다수.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['호남', '메가프로젝트', '광주공항']</t>
+          <t>['원풍물산', '상장폐지', '거래정지']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12650</v>
+        <v>14410</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="E19" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="H19" t="n">
-        <v>17.11</v>
+        <v>1.72</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>12680</v>
+        <v>14650</v>
       </c>
       <c r="K19" t="n">
-        <v>12680</v>
+        <v>15100</v>
       </c>
       <c r="L19" t="n">
-        <v>13130</v>
+        <v>16680</v>
       </c>
       <c r="M19" t="n">
-        <v>11550</v>
+        <v>14340</v>
       </c>
       <c r="N19" t="n">
-        <v>18.05</v>
+        <v>1.58</v>
       </c>
       <c r="O19" t="n">
-        <v>46378290780</v>
+        <v>49486307210</v>
       </c>
       <c r="P19" t="n">
-        <v>14350</v>
+        <v>21400</v>
       </c>
       <c r="Q19" t="n">
-        <v>465</v>
+        <v>12090</v>
       </c>
       <c r="R19" t="n">
-        <v>48000</v>
+        <v>-4000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>계단식 하락 및 하한가 가능성 언급. 투자자들의 공포 심리 확산.</t>
+          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['하락', '하한가', '공포']</t>
+          <t>['단주 거래', '자전거래', '스카이랩스']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,99 +2212,99 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>0155E0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>290</v>
+        <v>12320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.01%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.05</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="H20" t="n">
-        <v>5.34</v>
+        <v>17.11</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>299</v>
+        <v>12680</v>
       </c>
       <c r="K20" t="n">
-        <v>220</v>
+        <v>12680</v>
       </c>
       <c r="L20" t="n">
-        <v>349</v>
+        <v>13130</v>
       </c>
       <c r="M20" t="n">
-        <v>220</v>
+        <v>11550</v>
       </c>
       <c r="N20" t="n">
-        <v>5.29</v>
+        <v>18.05</v>
       </c>
       <c r="O20" t="n">
-        <v>8617209082</v>
+        <v>58799344940</v>
       </c>
       <c r="P20" t="n">
-        <v>901</v>
+        <v>14350</v>
       </c>
       <c r="Q20" t="n">
-        <v>217</v>
+        <v>465</v>
       </c>
       <c r="R20" t="n">
-        <v>727000</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>상장폐지 우려 속 거래량 급증. 회생 가능성 및 추석 매출 기대.</t>
+          <t>계단식 하락 및 하한가 가능성 언급. 투자자들의 공포 심리 확산.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['상장폐지', '거래량', '회생']</t>
+          <t>['하락', '하한가', '공포']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8510</v>
+        <v>8440</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-3.87%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.04</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F21" t="n">
         <v>34</v>
       </c>
       <c r="G21" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H21" t="n">
         <v>1.68</v>
@@ -2358,7 +2358,7 @@
         <v>1.72</v>
       </c>
       <c r="O21" t="n">
-        <v>109205800295</v>
+        <v>111722690085</v>
       </c>
       <c r="P21" t="n">
         <v>25050</v>
@@ -2367,7 +2367,7 @@
         <v>3705</v>
       </c>
       <c r="R21" t="n">
-        <v>-59000</v>
+        <v>-50000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8230</v>
+        <v>8170</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-13.00%</t>
+          <t>-13.64%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.15</v>
       </c>
       <c r="E22" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F22" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G22" t="n">
-        <v>230</v>
+        <v>288</v>
       </c>
       <c r="H22" t="n">
         <v>38.84</v>
@@ -2450,7 +2450,7 @@
         <v>38.69</v>
       </c>
       <c r="O22" t="n">
-        <v>30850983660</v>
+        <v>35117744340</v>
       </c>
       <c r="P22" t="n">
         <v>19150</v>
@@ -2459,10 +2459,10 @@
         <v>3445</v>
       </c>
       <c r="R22" t="n">
-        <v>-32000</v>
+        <v>-7000</v>
       </c>
       <c r="S22" t="n">
-        <v>-106000</v>
+        <v>-249000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>258</v>
+        <v>220</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-92.95%</t>
+          <t>-93.99%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="F23" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G23" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H23" t="n">
         <v>0.08</v>
@@ -2536,19 +2536,19 @@
         <v>340</v>
       </c>
       <c r="M23" t="n">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="N23" t="n">
         <v>0.08</v>
       </c>
       <c r="O23" t="n">
-        <v>943676577</v>
+        <v>1043199511</v>
       </c>
       <c r="P23" t="n">
         <v>3660</v>
       </c>
       <c r="Q23" t="n">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="R23" t="n">
         <v>-2000</v>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F2" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G2" t="n">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>142703630703</v>
+        <v>143240527063</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 정부 주최 수행기관 선정 및 광통신 상용화 뉴스 기반 10방 상한가 기대. 글로벌 고객사 확보.</t>
+          <t>빛과전자, AI 데이터센터 및 국산화 사업 선정, 글로벌 고객사 확보 언급. 광통신 상용화 및 구리 가격 상승 모멘텀으로 주가 급등 기대감. 정부 주관 사업 수혜 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '상한가']</t>
+          <t>['AI 데이터센터', '광통신', '정부 주관']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10070</v>
+        <v>10230</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+19.60%</t>
+          <t>+21.50%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>223</v>
+        <v>162</v>
       </c>
       <c r="F3" t="n">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="G3" t="n">
-        <v>220</v>
+        <v>145</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>295074592205</v>
+        <v>309829989830</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -711,23 +711,23 @@
         <v>3500</v>
       </c>
       <c r="R3" t="n">
-        <v>57000</v>
+        <v>67000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미프진 연내 허가 및 정부 도입 구체화 소식, 대화제약과의 전략적 투자 언급. 일부 외인 매도세 관찰.</t>
+          <t>미프진 관련 대화제약과의 전략적 투자 및 정부 도입 구체화 뉴스로 기대감 상승. 그러나 확인되지 않은 재료로 인한 단기 급등 후 차익 실현 가능성도 제기.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미프진', '허가', '투자']</t>
+          <t>['미프진', '전략적 투자', '정부 도입']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>144500</v>
+        <v>141000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+18.15%</t>
+          <t>+15.29%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.11</v>
       </c>
       <c r="E4" t="n">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="F4" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="G4" t="n">
-        <v>236</v>
+        <v>299</v>
       </c>
       <c r="H4" t="n">
         <v>13.33</v>
@@ -785,7 +785,7 @@
         <v>129400</v>
       </c>
       <c r="L4" t="n">
-        <v>145800</v>
+        <v>147500</v>
       </c>
       <c r="M4" t="n">
         <v>128100</v>
@@ -794,7 +794,7 @@
         <v>13.22</v>
       </c>
       <c r="O4" t="n">
-        <v>244867928400</v>
+        <v>301043362000</v>
       </c>
       <c r="P4" t="n">
         <v>198000</v>
@@ -803,14 +803,14 @@
         <v>77100</v>
       </c>
       <c r="R4" t="n">
-        <v>10000</v>
+        <v>27000</v>
       </c>
       <c r="S4" t="n">
-        <v>88000</v>
+        <v>97000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>260조 규모의 원전 사업 수주 가능성이 언급되며 강한 상승세를 보임. AP1000 관련 구체적인 내용과 수익 계산이 포함된 뉴스가 투자 심리를 자극하고 있음.</t>
+          <t>원전 섹터 내에서의 강세와 함께 260조 규모의 사업 수주 가능성에 대한 기대감. 외인 및 기관의 매수세와 관련된 구체적인 내용 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['원전 사업', '260조', 'AP1000']</t>
+          <t>['원전', '사업수주', '외인매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7900</v>
+        <v>7580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.73%</t>
+          <t>+12.97%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.2</v>
       </c>
       <c r="E5" t="n">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G5" t="n">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="H5" t="n">
         <v>0.41</v>
@@ -886,7 +886,7 @@
         <v>0.61</v>
       </c>
       <c r="O5" t="n">
-        <v>138929546330</v>
+        <v>153289146355</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -895,23 +895,23 @@
         <v>952</v>
       </c>
       <c r="R5" t="n">
-        <v>31000</v>
+        <v>44000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>레미콘 총파업 관련 수혜 기대감, 독점 공급 가능성 언급. 신고가 근접 및 7연상 목표 제시.</t>
+          <t>레미콘 총파업 관련 독점 수혜 기대감 및 외국인 매수세 유입으로 급등. 7연상 재도전 가능성 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['서산', '레미콘', '수혜']</t>
+          <t>['레미콘', '독점 수혜', '외국인 매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35700</v>
+        <v>20150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+16.86%</t>
+          <t>+9.45%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>787</v>
+        <v>281</v>
       </c>
       <c r="F6" t="n">
-        <v>368</v>
+        <v>171</v>
       </c>
       <c r="G6" t="n">
-        <v>1480</v>
+        <v>1110</v>
       </c>
       <c r="H6" t="n">
-        <v>0.23</v>
+        <v>10.47</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>30550</v>
+        <v>18410</v>
       </c>
       <c r="K6" t="n">
-        <v>31650</v>
+        <v>18800</v>
       </c>
       <c r="L6" t="n">
-        <v>39350</v>
+        <v>21300</v>
       </c>
       <c r="M6" t="n">
-        <v>31350</v>
+        <v>18480</v>
       </c>
       <c r="N6" t="n">
-        <v>0.16</v>
+        <v>10.4</v>
       </c>
       <c r="O6" t="n">
-        <v>896921830275</v>
+        <v>525258270190</v>
       </c>
       <c r="P6" t="n">
-        <v>39350</v>
+        <v>40350</v>
       </c>
       <c r="Q6" t="n">
-        <v>8200</v>
+        <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>-24000</v>
+        <v>265000</v>
       </c>
       <c r="S6" t="n">
-        <v>-2000</v>
+        <v>664000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정부 지분 공시(6.54%) 및 세계 최초 비침습적 비교군 없는 기술 기반 10만원 목표 기대. 주포 개입 언급.</t>
+          <t>원전 사업 및 에너지 인프라 건설 신사업 재료 부각으로 주가 상승. 과거 고점 돌파 및 2만 원대 안착 기대감 형성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['정부 지분', '비침습적', '주포']</t>
+          <t>['원전 사업', '신사업', '에너지 인프라']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20800</v>
+        <v>11860</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+12.98%</t>
+          <t>+8.61%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="E7" t="n">
-        <v>310</v>
+        <v>150</v>
       </c>
       <c r="F7" t="n">
-        <v>187</v>
+        <v>91</v>
       </c>
       <c r="G7" t="n">
-        <v>1257</v>
+        <v>542</v>
       </c>
       <c r="H7" t="n">
-        <v>10.47</v>
+        <v>5.42</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18410</v>
+        <v>10920</v>
       </c>
       <c r="K7" t="n">
-        <v>18800</v>
+        <v>11300</v>
       </c>
       <c r="L7" t="n">
-        <v>21300</v>
+        <v>12700</v>
       </c>
       <c r="M7" t="n">
-        <v>18480</v>
+        <v>11050</v>
       </c>
       <c r="N7" t="n">
-        <v>10.4</v>
+        <v>5.53</v>
       </c>
       <c r="O7" t="n">
-        <v>483602718490</v>
+        <v>151358428865</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>30200</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>3540</v>
       </c>
       <c r="R7" t="n">
-        <v>325000</v>
+        <v>-507000</v>
       </c>
       <c r="S7" t="n">
-        <v>555000</v>
+        <v>16000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원전 사업과 에너지 인프라 건설 신사업 발표에 따른 기대감. 2만대 돌파 및 골든크로스 형성, 대장주로서의 면모 부각.</t>
+          <t>원전 섹터 전반의 긍정적 분위기 속, 프랑스와의 원자력 협정 관련 소식에 따른 상승 기대. 공매도에 대한 언급도 포함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '에너지 인프라', '골든크로스']</t>
+          <t>['원전', '협정', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12070</v>
+        <v>3840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+10.53%</t>
+          <t>+7.26%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.11</v>
+        <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="F8" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="G8" t="n">
-        <v>502</v>
+        <v>351</v>
       </c>
       <c r="H8" t="n">
-        <v>5.42</v>
+        <v>1.56</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10920</v>
+        <v>3580</v>
       </c>
       <c r="K8" t="n">
-        <v>11300</v>
+        <v>3600</v>
       </c>
       <c r="L8" t="n">
-        <v>12700</v>
+        <v>4335</v>
       </c>
       <c r="M8" t="n">
-        <v>11050</v>
+        <v>3450</v>
       </c>
       <c r="N8" t="n">
-        <v>5.53</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>140948467085</v>
+        <v>284493743865</v>
       </c>
       <c r="P8" t="n">
-        <v>30200</v>
+        <v>4335</v>
       </c>
       <c r="Q8" t="n">
-        <v>3540</v>
+        <v>1246</v>
       </c>
       <c r="R8" t="n">
-        <v>-564000</v>
+        <v>-436000</v>
       </c>
       <c r="S8" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 원전 8기 관련 70% 계약 기대감, 프랑스와의 원자력 협정 언급. 14000원 돌파 및 이번 달, 내일 상한가 기대.</t>
+          <t>거래량 증가 속 횡보하며 계단식 하락세 지속. 4천 원 이탈 시 추가 하락 가능성 우려.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['우리기술', '원전', '대미투자']</t>
+          <t>['계단식 하락', '거래량', '횡보']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3820</v>
+        <v>32600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.70%</t>
+          <t>+6.71%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.31</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>187</v>
+        <v>794</v>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
+        <v>353</v>
       </c>
       <c r="G9" t="n">
-        <v>330</v>
+        <v>1497</v>
       </c>
       <c r="H9" t="n">
-        <v>1.56</v>
+        <v>0.23</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3580</v>
+        <v>30550</v>
       </c>
       <c r="K9" t="n">
-        <v>3600</v>
+        <v>31650</v>
       </c>
       <c r="L9" t="n">
-        <v>4335</v>
+        <v>39350</v>
       </c>
       <c r="M9" t="n">
-        <v>3450</v>
+        <v>30900</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>0.16</v>
       </c>
       <c r="O9" t="n">
-        <v>277429162534</v>
+        <v>1083278531050</v>
       </c>
       <c r="P9" t="n">
-        <v>4335</v>
+        <v>39350</v>
       </c>
       <c r="Q9" t="n">
-        <v>1246</v>
+        <v>8200</v>
       </c>
       <c r="R9" t="n">
-        <v>-389000</v>
+        <v>-51000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>계단식 하락 및 음봉 마무리 가능성 언급, 4천원 이하 하락 시 주의 경고. 탈모 관련 사업 가능성 언급.</t>
+          <t>주포의 매집 및 10만 원 돌파 기대감 형성. 상승 후 장시간 횡보하며 급등 가능성 시사.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['JW신약', '하락', '탈모']</t>
+          <t>['주포', '매집', '급등 기대']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -1303,27 +1303,27 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34800</v>
+        <v>34200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.26%</t>
+          <t>+4.43%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" t="n">
-        <v>414</v>
+        <v>498</v>
       </c>
       <c r="H10" t="n">
-        <v>52.79</v>
+        <v>52.78</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>21.02</v>
       </c>
       <c r="O10" t="n">
-        <v>98651235650</v>
+        <v>115865718300</v>
       </c>
       <c r="P10" t="n">
         <v>69500</v>
@@ -1355,23 +1355,23 @@
         <v>30400</v>
       </c>
       <c r="R10" t="n">
-        <v>263000</v>
+        <v>344000</v>
       </c>
       <c r="S10" t="n">
-        <v>237000</v>
+        <v>275000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>한국전력, 웨스팅하우스 지분 인수 관련 기대감. 공매도 관련 언급 다수.</t>
+          <t>미국 원전 사업 투자 및 웨스팅하우스 지분 인수 기대감으로 주가 상승. 공매도 물량 부담 속 10만 원 돌파 가능성 제시.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['한국전력', '웨스팅하우스', '공매도']</t>
+          <t>['미국 원전', '웨스팅하우스', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50500</v>
+        <v>49250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.21%</t>
+          <t>+2.60%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="H11" t="n">
         <v>38.34</v>
@@ -1438,7 +1438,7 @@
         <v>38.24</v>
       </c>
       <c r="O11" t="n">
-        <v>137324046175</v>
+        <v>151721462850</v>
       </c>
       <c r="P11" t="n">
         <v>67300</v>
@@ -1447,10 +1447,10 @@
         <v>23150</v>
       </c>
       <c r="R11" t="n">
-        <v>242000</v>
+        <v>229000</v>
       </c>
       <c r="S11" t="n">
-        <v>126000</v>
+        <v>153000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>91500</v>
+        <v>89600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.10%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>517</v>
+        <v>422</v>
       </c>
       <c r="F12" t="n">
-        <v>296</v>
+        <v>245</v>
       </c>
       <c r="G12" t="n">
-        <v>2216</v>
+        <v>2001</v>
       </c>
       <c r="H12" t="n">
         <v>23.63</v>
@@ -1524,13 +1524,13 @@
         <v>93500</v>
       </c>
       <c r="M12" t="n">
-        <v>90200</v>
+        <v>89500</v>
       </c>
       <c r="N12" t="n">
         <v>23.53</v>
       </c>
       <c r="O12" t="n">
-        <v>450836329600</v>
+        <v>509134381450</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1539,14 +1539,14 @@
         <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-92000</v>
+        <v>-48000</v>
       </c>
       <c r="S12" t="n">
-        <v>544000</v>
+        <v>605000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 텍사스 발전사업(SMR 8기 포함) 확정 및 웨스팅하우스 지분 인수 추진 소식, 체코 원전 시공 관련 긍정적 전망.</t>
+          <t>텍사스 발전 사업 수주 확정 및 SMR 강자 부각, 웨스팅하우스 지분 인수 가능성 등 대형 호재 지속. 10만 원 돌파 및 15만 원까지 상승 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['SMR', '원전', '텍사스']</t>
+          <t>['SMR', '텍사스 발전', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13980</v>
+        <v>13710</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.79%</t>
+          <t>+1.78%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.12</v>
       </c>
       <c r="E13" t="n">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="F13" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G13" t="n">
-        <v>672</v>
+        <v>721</v>
       </c>
       <c r="H13" t="n">
         <v>1.94</v>
@@ -1622,7 +1622,7 @@
         <v>1.82</v>
       </c>
       <c r="O13" t="n">
-        <v>212917779660</v>
+        <v>227504423075</v>
       </c>
       <c r="P13" t="n">
         <v>31500</v>
@@ -1631,23 +1631,23 @@
         <v>1252</v>
       </c>
       <c r="R13" t="n">
-        <v>-132000</v>
+        <v>-103000</v>
       </c>
       <c r="S13" t="n">
         <v>27000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Texas 관련 소식 및 14000원, 14500원, 15000원, 17510원 등 목표가 제시. 공매도 물량 소화 및 매집 구간 분석.</t>
+          <t>Texas 소식 및 광통신 관련 호재로 인한 상승 기대감. 14000원 돌파 및 15000원, 17510원 목표가 제시. 공매도 물량 부담.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대한광통신', 'Texas', '공매도']</t>
+          <t>['Texas', '광통신', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1850000</v>
+        <v>1797000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.76%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="F14" t="n">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="G14" t="n">
-        <v>2187</v>
+        <v>1348</v>
       </c>
       <c r="H14" t="n">
         <v>50.63</v>
@@ -1714,7 +1714,7 @@
         <v>50.5</v>
       </c>
       <c r="O14" t="n">
-        <v>5961519918000</v>
+        <v>7060564885500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1723,23 +1723,23 @@
         <v>274000</v>
       </c>
       <c r="R14" t="n">
-        <v>23000</v>
+        <v>57000</v>
       </c>
       <c r="S14" t="n">
-        <v>221000</v>
+        <v>202000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외국인 및 기관의 대량 매수세 관찰, 190만원 돌파 및 200만원, 220만원 목표가 제시. 추석 랠리 기대감.</t>
+          <t>미국 증시 반도체 회복에 따른 단기 반등 시도. 그러나 급락 후 재조정 가능성 및 155 부근 회귀 예상.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '외인매수', '목표가']</t>
+          <t>['반도체 회복', '단기 반등', '재조정']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>276000</v>
+        <v>270500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>793</v>
+        <v>634</v>
       </c>
       <c r="F15" t="n">
-        <v>448</v>
+        <v>386</v>
       </c>
       <c r="G15" t="n">
-        <v>1789</v>
+        <v>1290</v>
       </c>
       <c r="H15" t="n">
         <v>46.79</v>
@@ -1806,7 +1806,7 @@
         <v>46.73</v>
       </c>
       <c r="O15" t="n">
-        <v>4710873998750</v>
+        <v>5641489097500</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1815,23 +1815,23 @@
         <v>69600</v>
       </c>
       <c r="R15" t="n">
-        <v>2004000</v>
+        <v>1925000</v>
       </c>
       <c r="S15" t="n">
-        <v>568000</v>
+        <v>862000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>28만원 이상 돌파 시 숏커버 기대감 및 30만원, 35만원, 40만원, 50층 등 높은 목표가 제시. AI/AGI 시대 언급.</t>
+          <t>28만 원대 매물대 돌파 시도 및 연기금 순매수세 유입. 35만 원 및 50만 원 목표가 제시 등 장기적인 상승 전망 제시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['삼성전자', '목표가', 'AI']</t>
+          <t>['매물대 돌파', '연기금', '목표가']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10260</v>
+        <v>8700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.23</v>
+        <v>-0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="F16" t="n">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>187</v>
+        <v>90</v>
       </c>
       <c r="H16" t="n">
-        <v>0.44</v>
+        <v>1.68</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,47 +1883,47 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>10200</v>
+        <v>8780</v>
       </c>
       <c r="K16" t="n">
-        <v>10600</v>
+        <v>9060</v>
       </c>
       <c r="L16" t="n">
-        <v>10970</v>
+        <v>9960</v>
       </c>
       <c r="M16" t="n">
-        <v>9980</v>
+        <v>8270</v>
       </c>
       <c r="N16" t="n">
-        <v>0.21</v>
+        <v>1.72</v>
       </c>
       <c r="O16" t="n">
-        <v>86557693645</v>
+        <v>115262872690</v>
       </c>
       <c r="P16" t="n">
-        <v>20850</v>
+        <v>25050</v>
       </c>
       <c r="Q16" t="n">
-        <v>4020</v>
+        <v>3705</v>
       </c>
       <c r="R16" t="n">
-        <v>-56000</v>
+        <v>-51000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>종목에 대한 부정적 의견과 기대감이 혼재하며, 투자자들의 잦은 매매 움직임이 나타나는 상황. 터빈 블레이드 수주 관련 기대감이 있으나, 매도세가 강하게 나타나고 있음.</t>
+          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['개미탕', '터빈블레이드', '매도세']</t>
+          <t>['투경', '탈모 테마', 'JAK 억제']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,95 +1931,95 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15980</v>
+        <v>10050</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="F17" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="G17" t="n">
-        <v>677</v>
+        <v>209</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>16110</v>
+        <v>10200</v>
       </c>
       <c r="K17" t="n">
-        <v>16130</v>
+        <v>10600</v>
       </c>
       <c r="L17" t="n">
-        <v>16420</v>
+        <v>10970</v>
       </c>
       <c r="M17" t="n">
-        <v>15310</v>
+        <v>9950</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="O17" t="n">
-        <v>85351589965</v>
+        <v>89884086995</v>
       </c>
       <c r="P17" t="n">
-        <v>19380</v>
+        <v>20850</v>
       </c>
       <c r="Q17" t="n">
-        <v>3200</v>
+        <v>4020</v>
       </c>
       <c r="R17" t="n">
-        <v>-106000</v>
+        <v>-56000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>호남 메가 프로젝트 및 30조대 투자 언급에도 불구하고 건설주 상승 추세와 상반된 약세. 주가 상승 기대감 희미.</t>
+          <t>신용 매수 이후 주가 하락에 대한 불만과 함께 '개미 무덤', '개잡주' 등의 부정적 표현. 터빈블레이드 수주 기대감도 있으나 매도세 심화 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['메가 프로젝트', '가스복합발전소', '건설주']</t>
+          <t>['신용매수', '개잡주', '매도세']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>295</v>
+        <v>1927</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.34%</t>
+          <t>-2.18%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="E18" t="n">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="F18" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>67</v>
+        <v>261</v>
       </c>
       <c r="H18" t="n">
-        <v>5.34</v>
+        <v>0.61</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>299</v>
+        <v>1970</v>
       </c>
       <c r="K18" t="n">
-        <v>220</v>
+        <v>1931</v>
       </c>
       <c r="L18" t="n">
-        <v>349</v>
+        <v>2185</v>
       </c>
       <c r="M18" t="n">
-        <v>220</v>
+        <v>1821</v>
       </c>
       <c r="N18" t="n">
-        <v>5.29</v>
+        <v>0.48</v>
       </c>
       <c r="O18" t="n">
-        <v>9890523513</v>
+        <v>16380497316</v>
       </c>
       <c r="P18" t="n">
-        <v>901</v>
+        <v>2930</v>
       </c>
       <c r="Q18" t="n">
-        <v>217</v>
+        <v>910</v>
       </c>
       <c r="R18" t="n">
-        <v>644000</v>
+        <v>58000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>상장폐지 가능성 및 거래 정지 공시 우려, 하한가 및 폭탄 돌리기 언급. 투자 탈출 의견 다수.</t>
+          <t>부지 개발 관련 사업 협의 중이라는 뉴스 언급과 함께 주가 회복에 대한 기대감. 다만, '잡주', '개미 피빨아먹는' 등 부정적 시각도 공존.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원풍물산', '상장폐지', '거래정지']</t>
+          <t>['부지개발', '협의', '개미']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14410</v>
+        <v>15620</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="G19" t="n">
-        <v>81</v>
+        <v>398</v>
       </c>
       <c r="H19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14650</v>
+        <v>16110</v>
       </c>
       <c r="K19" t="n">
-        <v>15100</v>
+        <v>16130</v>
       </c>
       <c r="L19" t="n">
-        <v>16680</v>
+        <v>16420</v>
       </c>
       <c r="M19" t="n">
-        <v>14340</v>
+        <v>15310</v>
       </c>
       <c r="N19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>49486307210</v>
+        <v>91816231530</v>
       </c>
       <c r="P19" t="n">
-        <v>21400</v>
+        <v>19380</v>
       </c>
       <c r="Q19" t="n">
-        <v>12090</v>
+        <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>-4000</v>
+        <v>-113000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
+          <t>호남 메가 프로젝트 및 30조대 투자 언급에도 불구하고 건설주 상승 추세와 상반된 약세. 주가 상승 기대감 희미.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['단주 거래', '자전거래', '스카이랩스']</t>
+          <t>['메가 프로젝트', '가스복합발전소', '건설주']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0155E0</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12320</v>
+        <v>12170</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-4.02%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="H20" t="n">
         <v>17.11</v>
@@ -2266,7 +2266,7 @@
         <v>18.05</v>
       </c>
       <c r="O20" t="n">
-        <v>58799344940</v>
+        <v>61533970700</v>
       </c>
       <c r="P20" t="n">
         <v>14350</v>
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8440</v>
+        <v>13850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.87%</t>
+          <t>-5.46%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.04</v>
+        <v>0.14</v>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="H21" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>8780</v>
+        <v>14650</v>
       </c>
       <c r="K21" t="n">
-        <v>9060</v>
+        <v>15100</v>
       </c>
       <c r="L21" t="n">
-        <v>9960</v>
+        <v>16680</v>
       </c>
       <c r="M21" t="n">
-        <v>8270</v>
+        <v>13850</v>
       </c>
       <c r="N21" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="O21" t="n">
-        <v>111722690085</v>
+        <v>52472728955</v>
       </c>
       <c r="P21" t="n">
-        <v>25050</v>
+        <v>21400</v>
       </c>
       <c r="Q21" t="n">
-        <v>3705</v>
+        <v>12090</v>
       </c>
       <c r="R21" t="n">
-        <v>-50000</v>
+        <v>-5000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
+          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['투경', '탈모 테마', 'JAK 억제']</t>
+          <t>['단주 거래', '자전거래', '스카이랩스']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>0155E0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8170</v>
+        <v>264</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-13.64%</t>
+          <t>-11.71%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="E22" t="n">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="F22" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>288</v>
+        <v>67</v>
       </c>
       <c r="H22" t="n">
-        <v>38.84</v>
+        <v>5.34</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,47 +2435,47 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>9460</v>
+        <v>299</v>
       </c>
       <c r="K22" t="n">
-        <v>9700</v>
+        <v>220</v>
       </c>
       <c r="L22" t="n">
-        <v>9760</v>
+        <v>349</v>
       </c>
       <c r="M22" t="n">
-        <v>8110</v>
+        <v>220</v>
       </c>
       <c r="N22" t="n">
-        <v>38.69</v>
+        <v>5.29</v>
       </c>
       <c r="O22" t="n">
-        <v>35117744340</v>
+        <v>10794128442</v>
       </c>
       <c r="P22" t="n">
-        <v>19150</v>
+        <v>901</v>
       </c>
       <c r="Q22" t="n">
-        <v>3445</v>
+        <v>217</v>
       </c>
       <c r="R22" t="n">
-        <v>-7000</v>
+        <v>331000</v>
       </c>
       <c r="S22" t="n">
-        <v>-249000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>삼성, 포스코 관련주 상승 대비 부진한 주가 흐름과 조정에 대한 언급.</t>
+          <t>상장폐지 가능성 및 거래 정지 공시 우려, 하한가 및 폭탄 돌리기 언급. 투자 탈출 의견 다수.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['포스코', '삼성', '조정']</t>
+          <t>['원풍물산', '상장폐지', '거래정지']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2483,82 +2483,82 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>220</v>
+        <v>7980</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-93.99%</t>
+          <t>-15.64%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E23" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F23" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>200</v>
+        <v>329</v>
       </c>
       <c r="H23" t="n">
-        <v>0.08</v>
+        <v>38.84</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3660</v>
+        <v>9460</v>
       </c>
       <c r="K23" t="n">
-        <v>300</v>
+        <v>9700</v>
       </c>
       <c r="L23" t="n">
-        <v>340</v>
+        <v>9760</v>
       </c>
       <c r="M23" t="n">
-        <v>220</v>
+        <v>7960</v>
       </c>
       <c r="N23" t="n">
-        <v>0.08</v>
+        <v>38.69</v>
       </c>
       <c r="O23" t="n">
-        <v>1043199511</v>
+        <v>39880059690</v>
       </c>
       <c r="P23" t="n">
-        <v>3660</v>
+        <v>19150</v>
       </c>
       <c r="Q23" t="n">
-        <v>220</v>
+        <v>3445</v>
       </c>
       <c r="R23" t="n">
-        <v>-2000</v>
+        <v>3000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-283000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>감사의견 적정으로 재개 기대. 대주주 및 유통물량 변동성 우려.</t>
+          <t>삼성, 포스코 관련주 상승 대비 부진한 주가 흐름과 조정에 대한 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['감사의견', '재개', '유통물량']</t>
+          <t>['포스코', '삼성', '조정']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2579,6 +2579,98 @@
         </is>
       </c>
       <c r="Z23" t="inlineStr">
+        <is>
+          <t>033790</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>카프로</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>199</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-94.56%</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>113</v>
+      </c>
+      <c r="F24" t="n">
+        <v>64</v>
+      </c>
+      <c r="G24" t="n">
+        <v>211</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>3660</v>
+      </c>
+      <c r="K24" t="n">
+        <v>300</v>
+      </c>
+      <c r="L24" t="n">
+        <v>340</v>
+      </c>
+      <c r="M24" t="n">
+        <v>199</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1187683544</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3660</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>199</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>감사의견 적정으로 재개 기대. 대주주 및 유통물량 변동성 우려.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>['감사의견', '재개', '유통물량']</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>006380</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15250</v>
+        <v>13300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+11.31%</t>
+          <t>+12.62%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.39</v>
+        <v>0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>287</v>
+        <v>382</v>
       </c>
       <c r="H2" t="n">
-        <v>1.55</v>
+        <v>5.64</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>13700</v>
+        <v>11810</v>
       </c>
       <c r="K2" t="n">
-        <v>14260</v>
+        <v>12050</v>
       </c>
       <c r="L2" t="n">
-        <v>15300</v>
+        <v>13990</v>
       </c>
       <c r="M2" t="n">
-        <v>14210</v>
+        <v>11950</v>
       </c>
       <c r="N2" t="n">
-        <v>1.94</v>
+        <v>5.42</v>
       </c>
       <c r="O2" t="n">
-        <v>109644678625</v>
+        <v>119536095005</v>
       </c>
       <c r="P2" t="n">
-        <v>31500</v>
+        <v>30200</v>
       </c>
       <c r="Q2" t="n">
-        <v>1252</v>
+        <v>3540</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>731000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 급등 영향. 투명거래 규제 해제 후 기대감.</t>
+          <t>원전 및 로봇 섹터 주도주 전망. 미국 원전 관련 뉴스 및 소형원자로 배치 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '미국', '차트']</t>
+          <t>['원전', '로봇', '소형원자로']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32800</v>
+        <v>55200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+10.25%</t>
+          <t>+12.08%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31</v>
+        <v>14.96</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>29750</v>
+        <v>49250</v>
       </c>
       <c r="K3" t="n">
-        <v>31600</v>
+        <v>53500</v>
       </c>
       <c r="L3" t="n">
-        <v>34200</v>
+        <v>55900</v>
       </c>
       <c r="M3" t="n">
-        <v>31300</v>
+        <v>51600</v>
       </c>
       <c r="N3" t="n">
-        <v>0.23</v>
+        <v>14.93</v>
       </c>
       <c r="O3" t="n">
-        <v>103622203825</v>
+        <v>47421466300</v>
       </c>
       <c r="P3" t="n">
-        <v>39350</v>
+        <v>108900</v>
       </c>
       <c r="Q3" t="n">
-        <v>8200</v>
+        <v>18230</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-198000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>상장폐지 우려 및 주가 급락 전망. 개인 투자자 탈출 권유.</t>
+          <t>외인 매도세 속 목표가 상향 및 성장성 기대. 수소 에너지 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['상장폐지', '주가', '탈출']</t>
+          <t>['수소에너지', '목표가', '성장성']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53300</v>
+        <v>4025</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+8.22%</t>
+          <t>+10.58%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.03</v>
+        <v>2.74</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>125</v>
+        <v>228</v>
       </c>
       <c r="H4" t="n">
-        <v>14.96</v>
+        <v>3.19</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>49250</v>
+        <v>3640</v>
       </c>
       <c r="K4" t="n">
-        <v>53500</v>
+        <v>3750</v>
       </c>
       <c r="L4" t="n">
-        <v>55500</v>
+        <v>4460</v>
       </c>
       <c r="M4" t="n">
-        <v>51600</v>
+        <v>3680</v>
       </c>
       <c r="N4" t="n">
-        <v>14.93</v>
+        <v>0.45</v>
       </c>
       <c r="O4" t="n">
-        <v>28186189200</v>
+        <v>181903605956</v>
       </c>
       <c r="P4" t="n">
-        <v>108900</v>
+        <v>8100</v>
       </c>
       <c r="Q4" t="n">
-        <v>18230</v>
+        <v>592</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>282000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>블룸에너지 언급하며 매출 성장성 기대. 개인 투자자 매수세.</t>
+          <t>미국 광통신 섹터 급등에 따른 기대감. 글로벌 회사 공급 및 긍정적 재료 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['수소에너지', '매출', '개인']</t>
+          <t>['광통신', '급등', '글로벌공급']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>92800</v>
+        <v>15120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+3.69%</t>
+          <t>+10.36%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="F5" t="n">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="G5" t="n">
-        <v>1104</v>
+        <v>556</v>
       </c>
       <c r="H5" t="n">
-        <v>23.61</v>
+        <v>1.55</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>89500</v>
+        <v>13700</v>
       </c>
       <c r="K5" t="n">
-        <v>92000</v>
+        <v>14260</v>
       </c>
       <c r="L5" t="n">
-        <v>94300</v>
+        <v>15860</v>
       </c>
       <c r="M5" t="n">
-        <v>91300</v>
+        <v>14210</v>
       </c>
       <c r="N5" t="n">
-        <v>23.63</v>
+        <v>1.94</v>
       </c>
       <c r="O5" t="n">
-        <v>71408600250</v>
+        <v>238411826045</v>
       </c>
       <c r="P5" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>57000</v>
+        <v>1252</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 기술 개발 소식을 바탕으로 두산에너빌리티의 하반기 주도주 가능성 및 35만원 목표가 제시. 한-프랑스 정상회담 등 일부 근거 포함.</t>
+          <t>단기 박스권 돌파 및 우상향 추세 기대. 광통신 관련 미장 흐름 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '주가']</t>
+          <t>['광통신', '우상향', '박스권돌파']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35050</v>
+        <v>93700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+2.79%</t>
+          <t>+4.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>165</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="G6" t="n">
-        <v>116</v>
+        <v>1211</v>
       </c>
       <c r="H6" t="n">
-        <v>52.79</v>
+        <v>23.61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>34100</v>
+        <v>89500</v>
       </c>
       <c r="K6" t="n">
-        <v>34450</v>
+        <v>92000</v>
       </c>
       <c r="L6" t="n">
-        <v>35325</v>
+        <v>94400</v>
       </c>
       <c r="M6" t="n">
-        <v>34050</v>
+        <v>91300</v>
       </c>
       <c r="N6" t="n">
-        <v>21.01</v>
+        <v>23.63</v>
       </c>
       <c r="O6" t="n">
-        <v>16510441075</v>
+        <v>127622223050</v>
       </c>
       <c r="P6" t="n">
-        <v>69500</v>
+        <v>139200</v>
       </c>
       <c r="Q6" t="n">
-        <v>30400</v>
+        <v>57000</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 원전 협력 및 25조 선납매 언급. 유가 상승에 따른 기대감.</t>
+          <t>미국 원전주 급등 및 SMR 관련 기술 개발 소식을 바탕으로 두산에너빌리티의 하반기 주도주 가능성 및 35만원 목표가 제시. 한-프랑스 정상회담 등 일부 근거 포함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '선납매', '유가']</t>
+          <t>['원전', 'SMR', '주가']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20450</v>
+        <v>20700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+2.40%</t>
+          <t>+3.66%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.38</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>243</v>
+        <v>306</v>
       </c>
       <c r="H7" t="n">
         <v>10.85</v>
@@ -1061,7 +1061,7 @@
         <v>20250</v>
       </c>
       <c r="L7" t="n">
-        <v>21200</v>
+        <v>21300</v>
       </c>
       <c r="M7" t="n">
         <v>20050</v>
@@ -1070,7 +1070,7 @@
         <v>10.47</v>
       </c>
       <c r="O7" t="n">
-        <v>59774083500</v>
+        <v>106119797075</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 대형 원전 건설 참여 가능성 언급. 역대 거래량으로 장기 매물 흡수.</t>
+          <t>미국 원전 참여 기대감 속 거래량 증가. 이란 관련 이슈와 유가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '거래량', '건설']</t>
+          <t>['원전', '거래량', '이란']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12070</v>
+        <v>30700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+3.19%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-2.16</v>
+        <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>83</v>
+        <v>181</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="G8" t="n">
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11990</v>
+        <v>29750</v>
       </c>
       <c r="K8" t="n">
-        <v>12440</v>
+        <v>31600</v>
       </c>
       <c r="L8" t="n">
-        <v>12800</v>
+        <v>34200</v>
       </c>
       <c r="M8" t="n">
-        <v>12000</v>
+        <v>30500</v>
       </c>
       <c r="N8" t="n">
-        <v>2.16</v>
+        <v>0.23</v>
       </c>
       <c r="O8" t="n">
-        <v>16520125245</v>
+        <v>155325823100</v>
       </c>
       <c r="P8" t="n">
-        <v>36200</v>
+        <v>39350</v>
       </c>
       <c r="Q8" t="n">
-        <v>8920</v>
+        <v>8200</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 지정학적 리스크 언급. 주가 상승 기대.</t>
+          <t>상장 폐지 관련 우려와 함께 상승 기대감 혼재. 기술적 분석 및 거래 대금 중요성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['유가', '전쟁', '지정학']</t>
+          <t>['상장폐지', '기술적분석', '거래대금']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,97 +1200,373 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>269500</v>
+        <v>12330</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
+        <v>-2.16</v>
       </c>
       <c r="E9" t="n">
-        <v>691</v>
+        <v>96</v>
       </c>
       <c r="F9" t="n">
-        <v>392</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>2732</v>
+        <v>205</v>
       </c>
       <c r="H9" t="n">
-        <v>46.85</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>269500</v>
+        <v>11990</v>
       </c>
       <c r="K9" t="n">
-        <v>269500</v>
+        <v>12440</v>
       </c>
       <c r="L9" t="n">
-        <v>270500</v>
+        <v>12800</v>
       </c>
       <c r="M9" t="n">
-        <v>268500</v>
+        <v>11920</v>
       </c>
       <c r="N9" t="n">
-        <v>46.79</v>
+        <v>2.16</v>
       </c>
       <c r="O9" t="n">
-        <v>429755191250</v>
+        <v>23752552365</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>36200</v>
       </c>
       <c r="Q9" t="n">
-        <v>70000</v>
+        <v>8920</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 반도체주 상승 소식에 삼성전자 10% 상승 기대감 표출. 구체적인 근거 제시 부족.</t>
+          <t>국제 유가 급등 및 지정학적 리스크 부각으로 인한 주가 상승 기대감. 이란 관련 뉴스 다수.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['국제유가', '전쟁', '이란']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>024060</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>한국전력</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>34850</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>+2.20%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>0.1</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>['반도체', 'AI', '주가']</t>
-        </is>
-      </c>
-      <c r="X9" t="n">
+      <c r="E10" t="n">
+        <v>52</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" t="n">
+        <v>144</v>
+      </c>
+      <c r="H10" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>34100</v>
+      </c>
+      <c r="K10" t="n">
+        <v>34450</v>
+      </c>
+      <c r="L10" t="n">
+        <v>35325</v>
+      </c>
+      <c r="M10" t="n">
+        <v>34050</v>
+      </c>
+      <c r="N10" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="O10" t="n">
+        <v>28771066725</v>
+      </c>
+      <c r="P10" t="n">
+        <v>69500</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>30400</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-46000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>유가 상승 및 미국 원전 협력 기대감 속에서 발전 5사 통합 긍정적 전망. 공매도 세력에 대한 경계감.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['원전', '발전', '유가']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>015760</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LG디스플레이</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8960</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G11" t="n">
+        <v>192</v>
+      </c>
+      <c r="H11" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>8940</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8940</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8990</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8710</v>
+      </c>
+      <c r="N11" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7224664160</v>
+      </c>
+      <c r="P11" t="n">
+        <v>17950</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8120</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-245000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>중국산 제품 경쟁 심화 및 유증 가능성 언급. 주가 관리 능력에 대한 부정적 의견.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['중국산', '유증', '주가관리']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>269750</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E12" t="n">
+        <v>794</v>
+      </c>
+      <c r="F12" t="n">
+        <v>444</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2922</v>
+      </c>
+      <c r="H12" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>269500</v>
+      </c>
+      <c r="K12" t="n">
+        <v>269500</v>
+      </c>
+      <c r="L12" t="n">
+        <v>272000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>268500</v>
+      </c>
+      <c r="N12" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="O12" t="n">
+        <v>748886359250</v>
+      </c>
+      <c r="P12" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>70000</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-689000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>AI 및 반도체 산업 관련 뉴스 언급. 30만 전자 및 국내 정치 관련 논의.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['반도체', 'AI', '30만전자']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>102</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>005930</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13300</v>
+        <v>6570</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+12.62%</t>
+          <t>+29.84%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.22</v>
+        <v>0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>382</v>
+        <v>147</v>
       </c>
       <c r="H2" t="n">
-        <v>5.64</v>
+        <v>2.46</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>11810</v>
+        <v>5060</v>
       </c>
       <c r="K2" t="n">
-        <v>12050</v>
+        <v>5190</v>
       </c>
       <c r="L2" t="n">
-        <v>13990</v>
+        <v>6570</v>
       </c>
       <c r="M2" t="n">
-        <v>11950</v>
+        <v>5110</v>
       </c>
       <c r="N2" t="n">
-        <v>5.42</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>119536095005</v>
+        <v>32756958435</v>
       </c>
       <c r="P2" t="n">
-        <v>30200</v>
+        <v>16200</v>
       </c>
       <c r="Q2" t="n">
-        <v>3540</v>
+        <v>1206</v>
       </c>
       <c r="R2" t="n">
-        <v>731000</v>
+        <v>144000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>원전 및 로봇 섹터 주도주 전망. 미국 원전 관련 뉴스 및 소형원자로 배치 언급.</t>
+          <t>신규 상장 후 주가 상승 기대감 높음. 매집 및 대장주 역할 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['원전', '로봇', '소형원자로']</t>
+          <t>['신규상장', '매집', '대장주']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55200</v>
+        <v>57300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+12.08%</t>
+          <t>+16.35%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="H3" t="n">
         <v>14.96</v>
@@ -693,7 +693,7 @@
         <v>53500</v>
       </c>
       <c r="L3" t="n">
-        <v>55900</v>
+        <v>57600</v>
       </c>
       <c r="M3" t="n">
         <v>51600</v>
@@ -702,7 +702,7 @@
         <v>14.93</v>
       </c>
       <c r="O3" t="n">
-        <v>47421466300</v>
+        <v>63886117400</v>
       </c>
       <c r="P3" t="n">
         <v>108900</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인 매도세 속 목표가 상향 및 성장성 기대. 수소 에너지 관련 언급.</t>
+          <t>외인 매도세 속 연기금 매수 기대. 블룸에너지, 범한퓨얼셀 등 경쟁사 부각.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['수소에너지', '목표가', '성장성']</t>
+          <t>['청정에너지', '연기금', '블룸에너지']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4025</v>
+        <v>13300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.58%</t>
+          <t>+12.62%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.74</v>
+        <v>0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>228</v>
+        <v>432</v>
       </c>
       <c r="H4" t="n">
-        <v>3.19</v>
+        <v>5.64</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3640</v>
+        <v>11810</v>
       </c>
       <c r="K4" t="n">
-        <v>3750</v>
+        <v>12050</v>
       </c>
       <c r="L4" t="n">
-        <v>4460</v>
+        <v>13990</v>
       </c>
       <c r="M4" t="n">
-        <v>3680</v>
+        <v>11950</v>
       </c>
       <c r="N4" t="n">
-        <v>0.45</v>
+        <v>5.42</v>
       </c>
       <c r="O4" t="n">
-        <v>181903605956</v>
+        <v>134782365715</v>
       </c>
       <c r="P4" t="n">
-        <v>8100</v>
+        <v>30200</v>
       </c>
       <c r="Q4" t="n">
-        <v>592</v>
+        <v>3540</v>
       </c>
       <c r="R4" t="n">
-        <v>282000</v>
+        <v>731000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 급등에 따른 기대감. 글로벌 회사 공급 및 긍정적 재료 언급.</t>
+          <t>원전 로봇 하반기 주도주 전망. 미국 원전 관련 호재 및 외국 자본 유입 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신', '급등', '글로벌공급']</t>
+          <t>['원전', '로봇', '외국자본']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15120</v>
+        <v>15190</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+10.36%</t>
+          <t>+10.88%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="H5" t="n">
         <v>1.55</v>
@@ -886,7 +886,7 @@
         <v>1.94</v>
       </c>
       <c r="O5" t="n">
-        <v>238411826045</v>
+        <v>261727855620</v>
       </c>
       <c r="P5" t="n">
         <v>31500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>단기 박스권 돌파 및 우상향 추세 기대. 광통신 관련 미장 흐름 언급.</t>
+          <t>미국 광통신 관련주 급등에 따른 기대감. 외국인 대량 순매수 및 거래대금 증가.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '우상향', '박스권돌파']</t>
+          <t>['광통신', '외국인', '거래대금']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93700</v>
+        <v>4025</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+4.69%</t>
+          <t>+10.58%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>2.74</v>
       </c>
       <c r="E6" t="n">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>1211</v>
+        <v>222</v>
       </c>
       <c r="H6" t="n">
-        <v>23.61</v>
+        <v>3.19</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>89500</v>
+        <v>3640</v>
       </c>
       <c r="K6" t="n">
-        <v>92000</v>
+        <v>3750</v>
       </c>
       <c r="L6" t="n">
-        <v>94400</v>
+        <v>4460</v>
       </c>
       <c r="M6" t="n">
-        <v>91300</v>
+        <v>3680</v>
       </c>
       <c r="N6" t="n">
-        <v>23.63</v>
+        <v>0.45</v>
       </c>
       <c r="O6" t="n">
-        <v>127622223050</v>
+        <v>197111758802</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>8100</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>592</v>
       </c>
       <c r="R6" t="n">
-        <v>36000</v>
+        <v>282000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 기술 개발 소식을 바탕으로 두산에너빌리티의 하반기 주도주 가능성 및 35만원 목표가 제시. 한-프랑스 정상회담 등 일부 근거 포함.</t>
+          <t>미국 광통신 개폭등 및 글로벌 회사 대량 공급 뉴스. 투자경고 종목 지정 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '주가']</t>
+          <t>['광통신', '재료', '투자경고']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20700</v>
+        <v>8280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+3.66%</t>
+          <t>+7.81%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.38</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>306</v>
+        <v>109</v>
       </c>
       <c r="H7" t="n">
-        <v>10.85</v>
+        <v>1.81</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>19970</v>
+        <v>7680</v>
       </c>
       <c r="K7" t="n">
-        <v>20250</v>
+        <v>7780</v>
       </c>
       <c r="L7" t="n">
-        <v>21300</v>
+        <v>9000</v>
       </c>
       <c r="M7" t="n">
-        <v>20050</v>
+        <v>7750</v>
       </c>
       <c r="N7" t="n">
-        <v>10.47</v>
+        <v>0.41</v>
       </c>
       <c r="O7" t="n">
-        <v>106119797075</v>
+        <v>59420667735</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>10300</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>952</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>105000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 원전 참여 기대감 속 거래량 증가. 이란 관련 이슈와 유가 상승 가능성 언급.</t>
+          <t>시멘트 기초 작업 시작 및 추석까지 실적 기대감. 외인 대량 매수 및 5% 이상 상승.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '거래량', '이란']</t>
+          <t>['시멘트', '실적', '외인']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30700</v>
+        <v>31350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+3.19%</t>
+          <t>+5.38%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="F8" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G8" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="H8" t="n">
         <v>0.31</v>
@@ -1162,7 +1162,7 @@
         <v>0.23</v>
       </c>
       <c r="O8" t="n">
-        <v>155325823100</v>
+        <v>172625449525</v>
       </c>
       <c r="P8" t="n">
         <v>39350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>상장 폐지 관련 우려와 함께 상승 기대감 혼재. 기술적 분석 및 거래 대금 중요성 언급.</t>
+          <t>상장 폐지 가능성 언급 속 기술적 반등 기대감 공존. 시외 거래 및 기준봉 존재 근거 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['상장폐지', '기술적분석', '거래대금']</t>
+          <t>['기준봉', '시외거래', '기술적반등']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,70 +1207,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12330</v>
+        <v>93100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+4.02%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2.16</v>
+        <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="G9" t="n">
-        <v>205</v>
+        <v>1230</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>23.61</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11990</v>
+        <v>89500</v>
       </c>
       <c r="K9" t="n">
-        <v>12440</v>
+        <v>92000</v>
       </c>
       <c r="L9" t="n">
-        <v>12800</v>
+        <v>94400</v>
       </c>
       <c r="M9" t="n">
-        <v>11920</v>
+        <v>91300</v>
       </c>
       <c r="N9" t="n">
-        <v>2.16</v>
+        <v>23.63</v>
       </c>
       <c r="O9" t="n">
-        <v>23752552365</v>
+        <v>144442199350</v>
       </c>
       <c r="P9" t="n">
-        <v>36200</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>8920</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>34000</v>
+        <v>36000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 지정학적 리스크 부각으로 인한 주가 상승 기대감. 이란 관련 뉴스 다수.</t>
+          <t>미국 원전주 급등 및 SMR 관련 기술 개발 소식을 바탕으로 두산에너빌리티의 하반기 주도주 가능성 및 35만원 목표가 제시. 한-프랑스 정상회담 등 일부 근거 포함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['국제유가', '전쟁', '이란']</t>
+          <t>['원전', 'SMR', '주가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34850</v>
+        <v>20650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+2.20%</t>
+          <t>+3.41%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="E10" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>144</v>
+        <v>327</v>
       </c>
       <c r="H10" t="n">
-        <v>52.75</v>
+        <v>10.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>34100</v>
+        <v>19970</v>
       </c>
       <c r="K10" t="n">
-        <v>34450</v>
+        <v>20250</v>
       </c>
       <c r="L10" t="n">
-        <v>35325</v>
+        <v>21300</v>
       </c>
       <c r="M10" t="n">
-        <v>34050</v>
+        <v>20050</v>
       </c>
       <c r="N10" t="n">
-        <v>21.01</v>
+        <v>10.47</v>
       </c>
       <c r="O10" t="n">
-        <v>28771066725</v>
+        <v>114561315700</v>
       </c>
       <c r="P10" t="n">
-        <v>69500</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>30400</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-46000</v>
+        <v>-693000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>유가 상승 및 미국 원전 협력 기대감 속에서 발전 5사 통합 긍정적 전망. 공매도 세력에 대한 경계감.</t>
+          <t>미국 원전 참여 기대감 속 거래량 증가. 이란 관련 불확실성과 개미 털기 경고.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '발전', '유가']</t>
+          <t>['원전', '거래량', '매물']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8960</v>
+        <v>34750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.36</v>
+        <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="H11" t="n">
-        <v>27.69</v>
+        <v>52.74</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8940</v>
+        <v>34100</v>
       </c>
       <c r="K11" t="n">
-        <v>8940</v>
+        <v>34450</v>
       </c>
       <c r="L11" t="n">
-        <v>8990</v>
+        <v>35325</v>
       </c>
       <c r="M11" t="n">
-        <v>8710</v>
+        <v>34050</v>
       </c>
       <c r="N11" t="n">
-        <v>28.05</v>
+        <v>21.01</v>
       </c>
       <c r="O11" t="n">
-        <v>7224664160</v>
+        <v>33555199850</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>69500</v>
       </c>
       <c r="Q11" t="n">
-        <v>8120</v>
+        <v>30400</v>
       </c>
       <c r="R11" t="n">
-        <v>-245000</v>
+        <v>-46000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>중국산 제품 경쟁 심화 및 유증 가능성 언급. 주가 관리 능력에 대한 부정적 의견.</t>
+          <t>미국 원전 협력 기대감 및 발전 5사 통합 긍정적. Smp 급락 및 공매도 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['중국산', '유증', '주가관리']</t>
+          <t>['원전', 'SMP', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>269750</v>
+        <v>12210</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>-2.16</v>
       </c>
       <c r="E12" t="n">
-        <v>794</v>
+        <v>101</v>
       </c>
       <c r="F12" t="n">
-        <v>444</v>
+        <v>61</v>
       </c>
       <c r="G12" t="n">
-        <v>2922</v>
+        <v>216</v>
       </c>
       <c r="H12" t="n">
-        <v>46.85</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>269500</v>
+        <v>11990</v>
       </c>
       <c r="K12" t="n">
-        <v>269500</v>
+        <v>12440</v>
       </c>
       <c r="L12" t="n">
-        <v>272000</v>
+        <v>12800</v>
       </c>
       <c r="M12" t="n">
-        <v>268500</v>
+        <v>11920</v>
       </c>
       <c r="N12" t="n">
-        <v>46.79</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
-        <v>748886359250</v>
+        <v>25833368905</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>36200</v>
       </c>
       <c r="Q12" t="n">
-        <v>70000</v>
+        <v>8920</v>
       </c>
       <c r="R12" t="n">
-        <v>-689000</v>
+        <v>34000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AI 및 반도체 산업 관련 뉴스 언급. 30만 전자 및 국내 정치 관련 논의.</t>
+          <t>국제 유가 급등 및 지정학적 리스크 부각으로 인한 주가 상승 기대감. 이란 관련 뉴스 다수.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,18 +1555,294 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '30만전자']</t>
+          <t>['국제유가', '전쟁', '이란']</t>
         </is>
       </c>
       <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>024060</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1824500</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>+1.76%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E13" t="n">
+        <v>796</v>
+      </c>
+      <c r="F13" t="n">
+        <v>424</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2734</v>
+      </c>
+      <c r="H13" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1793000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1795000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1840000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1795000</v>
+      </c>
+      <c r="N13" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1321786716500</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>277000</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-27000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>JP모건의 심각한 저평가 분석 제시. 미국 증시 및 ADR 급등에 따른 200 돌파 기대감.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['반도체', '저평가', 'ADR']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LG디스플레이</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>8980</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>+0.45%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E14" t="n">
+        <v>49</v>
+      </c>
+      <c r="F14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G14" t="n">
+        <v>207</v>
+      </c>
+      <c r="H14" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>8940</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8940</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8710</v>
+      </c>
+      <c r="N14" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>8221830470</v>
+      </c>
+      <c r="P14" t="n">
+        <v>17950</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8120</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-245000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>본격적인 성장 국면 진입 기대에도 불구하고 중국산 영향 및 3분기 실적 악화 우려. 주가 관리 무능력 비판.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['디스플레이', '실적', '환율']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>270000</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E15" t="n">
+        <v>793</v>
+      </c>
+      <c r="F15" t="n">
+        <v>440</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2616</v>
+      </c>
+      <c r="H15" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>269500</v>
+      </c>
+      <c r="K15" t="n">
+        <v>269500</v>
+      </c>
+      <c r="L15" t="n">
+        <v>272000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>268500</v>
+      </c>
+      <c r="N15" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="O15" t="n">
+        <v>875386477750</v>
+      </c>
+      <c r="P15" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>70000</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-689000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>미국 반도체(인텔) 폭등에 따른 기대감. 개인의 저가 매수 유입.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['반도체', 'AI', '인텔']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
         <v>102</v>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>005930</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="H2" t="n">
         <v>2.46</v>
@@ -610,7 +610,7 @@
         <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>32756958435</v>
+        <v>33282223365</v>
       </c>
       <c r="P2" t="n">
         <v>16200</v>
@@ -619,14 +619,14 @@
         <v>1206</v>
       </c>
       <c r="R2" t="n">
-        <v>144000</v>
+        <v>84000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장 후 주가 상승 기대감 높음. 매집 및 대장주 역할 가능성 언급.</t>
+          <t>주주들의 기다림 끝에 상승세 예상, 단기 고점 및 상장 기대감 존재. 매집 정황 포착.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규상장', '매집', '대장주']</t>
+          <t>['상장', '단기 고점', '매집']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57300</v>
+        <v>57500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+16.35%</t>
+          <t>+16.75%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="H3" t="n">
         <v>14.96</v>
@@ -693,7 +693,7 @@
         <v>53500</v>
       </c>
       <c r="L3" t="n">
-        <v>57600</v>
+        <v>58200</v>
       </c>
       <c r="M3" t="n">
         <v>51600</v>
@@ -702,7 +702,7 @@
         <v>14.93</v>
       </c>
       <c r="O3" t="n">
-        <v>63886117400</v>
+        <v>79329483800</v>
       </c>
       <c r="P3" t="n">
         <v>108900</v>
@@ -711,14 +711,14 @@
         <v>18230</v>
       </c>
       <c r="R3" t="n">
-        <v>-198000</v>
+        <v>-232000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인 매도세 속 연기금 매수 기대. 블룸에너지, 범한퓨얼셀 등 경쟁사 부각.</t>
+          <t>두산퓨얼셀의 성장성 및 목표가 상향 기대감. 블룸에너지, 범한퓨얼셀 언급 및 연기금/기관 매수 관련 내용 포함.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['청정에너지', '연기금', '블룸에너지']</t>
+          <t>['두산퓨얼셀', '청정에너지', '블룸에너지']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13300</v>
+        <v>13700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+12.62%</t>
+          <t>+16.00%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>432</v>
+        <v>463</v>
       </c>
       <c r="H4" t="n">
         <v>5.64</v>
@@ -794,7 +794,7 @@
         <v>5.42</v>
       </c>
       <c r="O4" t="n">
-        <v>134782365715</v>
+        <v>154908415725</v>
       </c>
       <c r="P4" t="n">
         <v>30200</v>
@@ -803,23 +803,23 @@
         <v>3540</v>
       </c>
       <c r="R4" t="n">
-        <v>731000</v>
+        <v>553000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>원전 로봇 하반기 주도주 전망. 미국 원전 관련 호재 및 외국 자본 유입 기대.</t>
+          <t>우리기술의 원전 관련주 대장주 부상 및 급등 전망. 사우디, 미국 원전 관련 뉴스 및 정부 정책 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['원전', '로봇', '외국자본']</t>
+          <t>['우리기술', '원전', '대장주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15190</v>
+        <v>14920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+10.88%</t>
+          <t>+8.91%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.39</v>
       </c>
       <c r="E5" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F5" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G5" t="n">
-        <v>570</v>
+        <v>611</v>
       </c>
       <c r="H5" t="n">
         <v>1.55</v>
@@ -886,7 +886,7 @@
         <v>1.94</v>
       </c>
       <c r="O5" t="n">
-        <v>261727855620</v>
+        <v>275492112085</v>
       </c>
       <c r="P5" t="n">
         <v>31500</v>
@@ -895,23 +895,23 @@
         <v>1252</v>
       </c>
       <c r="R5" t="n">
-        <v>500000</v>
+        <v>559000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 급등에 따른 기대감. 외국인 대량 순매수 및 거래대금 증가.</t>
+          <t>대한광통신의 단기 박스권 돌파 및 우상향 추세 전망. 거래대금 상위, 외국인 순매수, 공매도 감소 등 긍정적 지표 포함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '외국인', '거래대금']</t>
+          <t>['대한광통신', '광통신', '우상향']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4025</v>
+        <v>3890</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+10.58%</t>
+          <t>+6.87%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2.74</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G6" t="n">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="H6" t="n">
         <v>3.19</v>
@@ -978,7 +978,7 @@
         <v>0.45</v>
       </c>
       <c r="O6" t="n">
-        <v>197111758802</v>
+        <v>210247609163</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -987,23 +987,23 @@
         <v>592</v>
       </c>
       <c r="R6" t="n">
-        <v>282000</v>
+        <v>-15000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 광통신 개폭등 및 글로벌 회사 대량 공급 뉴스. 투자경고 종목 지정 우려.</t>
+          <t>미국 광통신주 급등에 따른 빛과전자 상한가 기대감. 글로벌 회사 대량 공급 뉴스 및 골드만삭스 자료 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '재료', '투자경고']</t>
+          <t>['빛과전자', '광통신', '글로벌']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8280</v>
+        <v>8170</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+7.81%</t>
+          <t>+6.38%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1.4</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="H7" t="n">
         <v>1.81</v>
@@ -1070,7 +1070,7 @@
         <v>0.41</v>
       </c>
       <c r="O7" t="n">
-        <v>59420667735</v>
+        <v>64469157170</v>
       </c>
       <c r="P7" t="n">
         <v>10300</v>
@@ -1079,23 +1079,23 @@
         <v>952</v>
       </c>
       <c r="R7" t="n">
-        <v>105000</v>
+        <v>-73000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>시멘트 기초 작업 시작 및 추석까지 실적 기대감. 외인 대량 매수 및 5% 이상 상승.</t>
+          <t>서산의 시멘트 업종 및 건설 관련 기대감. 대장주로서의 움직임 및 외인 대량 매수 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['시멘트', '실적', '외인']</t>
+          <t>['서산', '시멘트', '건설']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31350</v>
+        <v>2040</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.38%</t>
+          <t>+6.14%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>280</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31</v>
+        <v>0.51</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>29750</v>
+        <v>1922</v>
       </c>
       <c r="K8" t="n">
-        <v>31600</v>
+        <v>1920</v>
       </c>
       <c r="L8" t="n">
-        <v>34200</v>
+        <v>2090</v>
       </c>
       <c r="M8" t="n">
-        <v>30500</v>
+        <v>1862</v>
       </c>
       <c r="N8" t="n">
-        <v>0.23</v>
+        <v>0.61</v>
       </c>
       <c r="O8" t="n">
-        <v>172625449525</v>
+        <v>3692179070</v>
       </c>
       <c r="P8" t="n">
-        <v>39350</v>
+        <v>2930</v>
       </c>
       <c r="Q8" t="n">
-        <v>8200</v>
+        <v>910</v>
       </c>
       <c r="R8" t="n">
-        <v>1000</v>
+        <v>29000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>상장 폐지 가능성 언급 속 기술적 반등 기대감 공존. 시외 거래 및 기준봉 존재 근거 언급.</t>
+          <t>대주주 매도 공시 핑계 하락 후, 광주 개발 및 나대지 가치 상승 등 대규모 재료 공시 기대. 2차 파동 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['기준봉', '시외거래', '기술적반등']</t>
+          <t>['대주주 매도', '재료 공시', '나대지 가치']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93100</v>
+        <v>31000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.02%</t>
+          <t>+4.20%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>176</v>
+        <v>234</v>
       </c>
       <c r="F9" t="n">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="G9" t="n">
-        <v>1230</v>
+        <v>296</v>
       </c>
       <c r="H9" t="n">
-        <v>23.61</v>
+        <v>0.31</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>89500</v>
+        <v>29750</v>
       </c>
       <c r="K9" t="n">
-        <v>92000</v>
+        <v>31600</v>
       </c>
       <c r="L9" t="n">
-        <v>94400</v>
+        <v>34200</v>
       </c>
       <c r="M9" t="n">
-        <v>91300</v>
+        <v>30500</v>
       </c>
       <c r="N9" t="n">
-        <v>23.63</v>
+        <v>0.23</v>
       </c>
       <c r="O9" t="n">
-        <v>144442199350</v>
+        <v>179095113300</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>39350</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>8200</v>
       </c>
       <c r="R9" t="n">
-        <v>36000</v>
+        <v>3000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 기술 개발 소식을 바탕으로 두산에너빌리티의 하반기 주도주 가능성 및 35만원 목표가 제시. 한-프랑스 정상회담 등 일부 근거 포함.</t>
+          <t>상장 폐지 우려와 함께 시외 상승 및 기술적 반등 기대감이 혼재하나, 하락 시작 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '주가']</t>
+          <t>['상폐', '기준봉', '기술적 반등']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20650</v>
+        <v>92700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+3.41%</t>
+          <t>+3.58%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.38</v>
+        <v>-0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>137</v>
       </c>
       <c r="G10" t="n">
-        <v>327</v>
+        <v>1291</v>
       </c>
       <c r="H10" t="n">
-        <v>10.85</v>
+        <v>23.61</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>19970</v>
+        <v>89500</v>
       </c>
       <c r="K10" t="n">
-        <v>20250</v>
+        <v>92000</v>
       </c>
       <c r="L10" t="n">
-        <v>21300</v>
+        <v>94400</v>
       </c>
       <c r="M10" t="n">
-        <v>20050</v>
+        <v>91300</v>
       </c>
       <c r="N10" t="n">
-        <v>10.47</v>
+        <v>23.63</v>
       </c>
       <c r="O10" t="n">
-        <v>114561315700</v>
+        <v>154874798300</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>-693000</v>
+        <v>113000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 원전 참여 기대감 속 거래량 증가. 이란 관련 불확실성과 개미 털기 경고.</t>
+          <t>미국 원전주 급등 및 SMR 관련 기술 개발 소식을 바탕으로 두산에너빌리티의 하반기 주도주 가능성 및 35만원 목표가 제시. 한-프랑스 정상회담 등 일부 근거 포함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '거래량', '매물']</t>
+          <t>['원전', 'SMR', '주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34750</v>
+        <v>1846000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.91%</t>
+          <t>+2.96%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>794</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>430</v>
       </c>
       <c r="G11" t="n">
-        <v>158</v>
+        <v>2496</v>
       </c>
       <c r="H11" t="n">
-        <v>52.74</v>
+        <v>50.66</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>34100</v>
+        <v>1793000</v>
       </c>
       <c r="K11" t="n">
-        <v>34450</v>
+        <v>1795000</v>
       </c>
       <c r="L11" t="n">
-        <v>35325</v>
+        <v>1849000</v>
       </c>
       <c r="M11" t="n">
-        <v>34050</v>
+        <v>1795000</v>
       </c>
       <c r="N11" t="n">
-        <v>21.01</v>
+        <v>50.63</v>
       </c>
       <c r="O11" t="n">
-        <v>33555199850</v>
+        <v>1575741199000</v>
       </c>
       <c r="P11" t="n">
-        <v>69500</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>30400</v>
+        <v>277000</v>
       </c>
       <c r="R11" t="n">
-        <v>-46000</v>
+        <v>3000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 원전 협력 기대감 및 발전 5사 통합 긍정적. Smp 급락 및 공매도 우려.</t>
+          <t>SK하이닉스의 200돌파 기대감 및 미국채 금리 하락 영향. 반도체 업종 내에서 삼성전자 대비 우위 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', 'SMP', '공매도']</t>
+          <t>['SK하이닉스', '반도체', '미국채']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12210</v>
+        <v>20500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-2.16</v>
+        <v>0.38</v>
       </c>
       <c r="E12" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="F12" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>216</v>
+        <v>368</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>10.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>11990</v>
+        <v>19970</v>
       </c>
       <c r="K12" t="n">
-        <v>12440</v>
+        <v>20250</v>
       </c>
       <c r="L12" t="n">
-        <v>12800</v>
+        <v>21300</v>
       </c>
       <c r="M12" t="n">
-        <v>11920</v>
+        <v>20050</v>
       </c>
       <c r="N12" t="n">
-        <v>2.16</v>
+        <v>10.47</v>
       </c>
       <c r="O12" t="n">
-        <v>25833368905</v>
+        <v>119696056550</v>
       </c>
       <c r="P12" t="n">
-        <v>36200</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>8920</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>34000</v>
+        <v>-974000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-23000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 지정학적 리스크 부각으로 인한 주가 상승 기대감. 이란 관련 뉴스 다수.</t>
+          <t>미국 원전 관련주 상승에 따른 기대감 및 대우건설 언급. 이란 항복, 유가 상승 등의 외부 요인도 거론됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국제유가', '전쟁', '이란']</t>
+          <t>['원전', '대우건설', '미국']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1824500</v>
+        <v>34600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>796</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
-        <v>424</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>2734</v>
+        <v>165</v>
       </c>
       <c r="H13" t="n">
-        <v>50.66</v>
+        <v>52.73</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1793000</v>
+        <v>34100</v>
       </c>
       <c r="K13" t="n">
-        <v>1795000</v>
+        <v>34450</v>
       </c>
       <c r="L13" t="n">
-        <v>1840000</v>
+        <v>35325</v>
       </c>
       <c r="M13" t="n">
-        <v>1795000</v>
+        <v>34050</v>
       </c>
       <c r="N13" t="n">
-        <v>50.63</v>
+        <v>21.01</v>
       </c>
       <c r="O13" t="n">
-        <v>1321786716500</v>
+        <v>36722512425</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>69500</v>
       </c>
       <c r="Q13" t="n">
-        <v>277000</v>
+        <v>30400</v>
       </c>
       <c r="R13" t="n">
-        <v>-27000</v>
+        <v>7000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>JP모건의 심각한 저평가 분석 제시. 미국 증시 및 ADR 급등에 따른 200 돌파 기대감.</t>
+          <t>한국전력의 주가 상승 기대감 및 미국 원전 협력 가능성 언급. 발전 5사 통합 및 선납매 관련 내용도 포함.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', '저평가', 'ADR']</t>
+          <t>['한국전력', '원전', 'Smp']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,86 +1660,86 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8980</v>
+        <v>12100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.36</v>
+        <v>-2.16</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="F14" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="G14" t="n">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="H14" t="n">
-        <v>27.69</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8940</v>
+        <v>11990</v>
       </c>
       <c r="K14" t="n">
-        <v>8940</v>
+        <v>12440</v>
       </c>
       <c r="L14" t="n">
-        <v>9000</v>
+        <v>12800</v>
       </c>
       <c r="M14" t="n">
-        <v>8710</v>
+        <v>11920</v>
       </c>
       <c r="N14" t="n">
-        <v>28.05</v>
+        <v>2.16</v>
       </c>
       <c r="O14" t="n">
-        <v>8221830470</v>
+        <v>26987687415</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>36200</v>
       </c>
       <c r="Q14" t="n">
-        <v>8120</v>
+        <v>8920</v>
       </c>
       <c r="R14" t="n">
-        <v>-245000</v>
+        <v>37000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>본격적인 성장 국면 진입 기대에도 불구하고 중국산 영향 및 3분기 실적 악화 우려. 주가 관리 무능력 비판.</t>
+          <t>국제 유가 급등에 따른 기대감 고조, 100달러 돌파 및 지정학적 리스크 언급. 외인 매도세 주의.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['디스플레이', '실적', '환율']</t>
+          <t>['국제 유가', '지정학적 리스크', '외인 매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>270000</v>
+        <v>271500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="F15" t="n">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="G15" t="n">
-        <v>2616</v>
+        <v>2552</v>
       </c>
       <c r="H15" t="n">
         <v>46.85</v>
@@ -1806,7 +1806,7 @@
         <v>46.79</v>
       </c>
       <c r="O15" t="n">
-        <v>875386477750</v>
+        <v>980221751000</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1815,10 +1815,10 @@
         <v>70000</v>
       </c>
       <c r="R15" t="n">
-        <v>-689000</v>
+        <v>-467000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1845,6 +1845,190 @@
       <c r="Z15" t="inlineStr">
         <is>
           <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LG디스플레이</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>8980</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>+0.45%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E16" t="n">
+        <v>53</v>
+      </c>
+      <c r="F16" t="n">
+        <v>34</v>
+      </c>
+      <c r="G16" t="n">
+        <v>255</v>
+      </c>
+      <c r="H16" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>8940</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8940</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9030</v>
+      </c>
+      <c r="M16" t="n">
+        <v>8710</v>
+      </c>
+      <c r="N16" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="O16" t="n">
+        <v>9027832295</v>
+      </c>
+      <c r="P16" t="n">
+        <v>17950</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>8120</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-209000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>9000</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>LG디스플레이의 성장성 및 목표가 하향에 대한 부정적 전망. 중국산 경쟁 심화 및 외인 매도 관련 내용 포함.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['LG디스플레이', '중국산', '매각']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>현대약품</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10470</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>+0.29%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E17" t="n">
+        <v>42</v>
+      </c>
+      <c r="F17" t="n">
+        <v>37</v>
+      </c>
+      <c r="G17" t="n">
+        <v>112</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>10440</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10180</v>
+      </c>
+      <c r="L17" t="n">
+        <v>11340</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10100</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O17" t="n">
+        <v>101996324330</v>
+      </c>
+      <c r="P17" t="n">
+        <v>15960</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3500</v>
+      </c>
+      <c r="R17" t="n">
+        <v>34000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>미국 바이오 종목 상승에 대한 기대감 속 현대약품 언급. 다만, 미증시 제약바이오 폭락 및 종목 내 감정적 표현이 다수.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['미프진', '제약바이오', '신고가']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>004310</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6570</v>
+        <v>7420</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+29.84%</t>
+          <t>+29.95%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.01</v>
+        <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>165</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G2" t="n">
-        <v>161</v>
+        <v>796</v>
       </c>
       <c r="H2" t="n">
-        <v>2.46</v>
+        <v>0.77</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5060</v>
+        <v>5710</v>
       </c>
       <c r="K2" t="n">
-        <v>5190</v>
+        <v>5620</v>
       </c>
       <c r="L2" t="n">
-        <v>6570</v>
+        <v>7420</v>
       </c>
       <c r="M2" t="n">
-        <v>5110</v>
+        <v>5580</v>
       </c>
       <c r="N2" t="n">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>33282223365</v>
+        <v>29105139135</v>
       </c>
       <c r="P2" t="n">
-        <v>16200</v>
+        <v>21500</v>
       </c>
       <c r="Q2" t="n">
-        <v>1206</v>
+        <v>2300</v>
       </c>
       <c r="R2" t="n">
-        <v>84000</v>
+        <v>-15000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>주주들의 기다림 끝에 상승세 예상, 단기 고점 및 상장 기대감 존재. 매집 정황 포착.</t>
+          <t>미 FDA 2A상 승인 및 폐암·난소암 관련 뉴스 기반, 글로벌 시장 도장깨기 기대감 고조. 외인 비중 하락에도 불구하고 긍정적 전망. 10연상 예약 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['상장', '단기 고점', '매집']</t>
+          <t>['FDA 2A상', '글로벌 시장', '암세포 사멸']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,99 +648,99 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57500</v>
+        <v>6570</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+16.75%</t>
+          <t>+29.84%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="H3" t="n">
-        <v>14.96</v>
+        <v>2.46</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>49250</v>
+        <v>5060</v>
       </c>
       <c r="K3" t="n">
-        <v>53500</v>
+        <v>5190</v>
       </c>
       <c r="L3" t="n">
-        <v>58200</v>
+        <v>6570</v>
       </c>
       <c r="M3" t="n">
-        <v>51600</v>
+        <v>5110</v>
       </c>
       <c r="N3" t="n">
-        <v>14.93</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>79329483800</v>
+        <v>36821088165</v>
       </c>
       <c r="P3" t="n">
-        <v>108900</v>
+        <v>16200</v>
       </c>
       <c r="Q3" t="n">
-        <v>18230</v>
+        <v>1206</v>
       </c>
       <c r="R3" t="n">
-        <v>-232000</v>
+        <v>84000</v>
       </c>
       <c r="S3" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>두산퓨얼셀의 성장성 및 목표가 상향 기대감. 블룸에너지, 범한퓨얼셀 언급 및 연기금/기관 매수 관련 내용 포함.</t>
+          <t>주주들의 기다림 끝에 상승세 예상, 단기 고점 및 상장 기대감 존재. 매집 정황 포착.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['두산퓨얼셀', '청정에너지', '블룸에너지']</t>
+          <t>['상장', '단기 고점', '매집']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13700</v>
+        <v>13980</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+16.00%</t>
+          <t>+18.37%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>463</v>
+        <v>805</v>
       </c>
       <c r="H4" t="n">
         <v>5.64</v>
@@ -785,7 +785,7 @@
         <v>12050</v>
       </c>
       <c r="L4" t="n">
-        <v>13990</v>
+        <v>14200</v>
       </c>
       <c r="M4" t="n">
         <v>11950</v>
@@ -794,7 +794,7 @@
         <v>5.42</v>
       </c>
       <c r="O4" t="n">
-        <v>154908415725</v>
+        <v>275769823370</v>
       </c>
       <c r="P4" t="n">
         <v>30200</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>우리기술의 원전 관련주 대장주 부상 및 급등 전망. 사우디, 미국 원전 관련 뉴스 및 정부 정책 언급.</t>
+          <t>원전 로봇 및 소형원자로 사업 관련 기대감. 체코, 미국, 사우디 등 해외 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['우리기술', '원전', '대장주']</t>
+          <t>['원전', '로봇', '해외수주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>현대바이오</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14920</v>
+        <v>7280</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+8.91%</t>
+          <t>+16.29%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.39</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="F5" t="n">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
-        <v>611</v>
+        <v>431</v>
       </c>
       <c r="H5" t="n">
-        <v>1.55</v>
+        <v>7.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13700</v>
+        <v>6260</v>
       </c>
       <c r="K5" t="n">
-        <v>14260</v>
+        <v>6200</v>
       </c>
       <c r="L5" t="n">
-        <v>15860</v>
+        <v>7730</v>
       </c>
       <c r="M5" t="n">
-        <v>14210</v>
+        <v>6140</v>
       </c>
       <c r="N5" t="n">
-        <v>1.94</v>
+        <v>7.35</v>
       </c>
       <c r="O5" t="n">
-        <v>275492112085</v>
+        <v>42228810730</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>21500</v>
       </c>
       <c r="Q5" t="n">
-        <v>1252</v>
+        <v>4565</v>
       </c>
       <c r="R5" t="n">
-        <v>559000</v>
+        <v>9000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대한광통신의 단기 박스권 돌파 및 우상향 추세 전망. 거래대금 상위, 외국인 순매수, 공매도 감소 등 긍정적 지표 포함.</t>
+          <t>신약 개발(페니트리움바이오) 관련 희망 회로와 주가 부진에 대한 답답함 토로. 실험 결과 발표 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['대한광통신', '광통신', '우상향']</t>
+          <t>['신약개발', '희망회로', '실험결과']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>048410</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3890</v>
+        <v>7320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+6.87%</t>
+          <t>+13.84%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.74</v>
+        <v>0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
+        <v>171</v>
       </c>
       <c r="F6" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="G6" t="n">
-        <v>250</v>
+        <v>171</v>
       </c>
       <c r="H6" t="n">
-        <v>3.19</v>
+        <v>16.71</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3640</v>
+        <v>6430</v>
       </c>
       <c r="K6" t="n">
-        <v>3750</v>
+        <v>6400</v>
       </c>
       <c r="L6" t="n">
-        <v>4460</v>
+        <v>7470</v>
       </c>
       <c r="M6" t="n">
-        <v>3680</v>
+        <v>6250</v>
       </c>
       <c r="N6" t="n">
-        <v>0.45</v>
+        <v>16.4</v>
       </c>
       <c r="O6" t="n">
-        <v>210247609163</v>
+        <v>67652376605</v>
       </c>
       <c r="P6" t="n">
-        <v>8100</v>
+        <v>13000</v>
       </c>
       <c r="Q6" t="n">
-        <v>592</v>
+        <v>6030</v>
       </c>
       <c r="R6" t="n">
-        <v>-15000</v>
+        <v>-91000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 빛과전자 상한가 기대감. 글로벌 회사 대량 공급 뉴스 및 골드만삭스 자료 언급.</t>
+          <t>주주환원 정책 및 공매도 관련 언급, 반도체 사업 부문에 대한 저평가 주장. 외인 매도세 속 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['빛과전자', '광통신', '글로벌']</t>
+          <t>['주주환원', '공매도', '반도체']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8170</v>
+        <v>55200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.38%</t>
+          <t>+12.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.4</v>
+        <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="G7" t="n">
-        <v>134</v>
+        <v>363</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81</v>
+        <v>14.96</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7680</v>
+        <v>49250</v>
       </c>
       <c r="K7" t="n">
-        <v>7780</v>
+        <v>53500</v>
       </c>
       <c r="L7" t="n">
-        <v>9000</v>
+        <v>59000</v>
       </c>
       <c r="M7" t="n">
-        <v>7750</v>
+        <v>51600</v>
       </c>
       <c r="N7" t="n">
-        <v>0.41</v>
+        <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>64469157170</v>
+        <v>133186977500</v>
       </c>
       <c r="P7" t="n">
-        <v>10300</v>
+        <v>108900</v>
       </c>
       <c r="Q7" t="n">
-        <v>952</v>
+        <v>18230</v>
       </c>
       <c r="R7" t="n">
-        <v>-73000</v>
+        <v>-232000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>서산의 시멘트 업종 및 건설 관련 기대감. 대장주로서의 움직임 및 외인 대량 매수 언급.</t>
+          <t>기관/외인 수급 변화 및 목표가 관련 논의. 수소 연료 전지 사업 성장성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['서산', '시멘트', '건설']</t>
+          <t>['기관', '외인', '수소연료전지']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2040</v>
+        <v>8370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+6.14%</t>
+          <t>+8.98%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.1</v>
+        <v>1.4</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>221</v>
       </c>
       <c r="H8" t="n">
-        <v>0.51</v>
+        <v>1.81</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1922</v>
+        <v>7680</v>
       </c>
       <c r="K8" t="n">
-        <v>1920</v>
+        <v>7780</v>
       </c>
       <c r="L8" t="n">
-        <v>2090</v>
+        <v>9000</v>
       </c>
       <c r="M8" t="n">
-        <v>1862</v>
+        <v>7750</v>
       </c>
       <c r="N8" t="n">
-        <v>0.61</v>
+        <v>0.41</v>
       </c>
       <c r="O8" t="n">
-        <v>3692179070</v>
+        <v>93016766555</v>
       </c>
       <c r="P8" t="n">
-        <v>2930</v>
+        <v>10300</v>
       </c>
       <c r="Q8" t="n">
-        <v>910</v>
+        <v>952</v>
       </c>
       <c r="R8" t="n">
-        <v>29000</v>
+        <v>-73000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대주주 매도 공시 핑계 하락 후, 광주 개발 및 나대지 가치 상승 등 대규모 재료 공시 기대. 2차 파동 전망.</t>
+          <t>서산의 시멘트 업종 및 건설 관련 기대감. 대장주로서의 움직임 및 외인 대량 매수 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['대주주 매도', '재료 공시', '나대지 가치']</t>
+          <t>['서산', '시멘트', '건설']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31000</v>
+        <v>14720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.20%</t>
+          <t>+7.45%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.08</v>
+        <v>-0.39</v>
       </c>
       <c r="E9" t="n">
-        <v>234</v>
+        <v>179</v>
       </c>
       <c r="F9" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="G9" t="n">
-        <v>296</v>
+        <v>930</v>
       </c>
       <c r="H9" t="n">
-        <v>0.31</v>
+        <v>1.55</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>29750</v>
+        <v>13700</v>
       </c>
       <c r="K9" t="n">
-        <v>31600</v>
+        <v>14260</v>
       </c>
       <c r="L9" t="n">
-        <v>34200</v>
+        <v>15860</v>
       </c>
       <c r="M9" t="n">
-        <v>30500</v>
+        <v>14210</v>
       </c>
       <c r="N9" t="n">
-        <v>0.23</v>
+        <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>179095113300</v>
+        <v>359062276575</v>
       </c>
       <c r="P9" t="n">
-        <v>39350</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>8200</v>
+        <v>1252</v>
       </c>
       <c r="R9" t="n">
-        <v>3000</v>
+        <v>559000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>상장 폐지 우려와 함께 시외 상승 및 기술적 반등 기대감이 혼재하나, 하락 시작 가능성 언급.</t>
+          <t>단기 박스권 돌파 및 상승 추세 기대. 미국 광통신 종목 동반 상승 언급. 공매도 물량 소화.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['상폐', '기준봉', '기술적 반등']</t>
+          <t>['광통신', '상승추세', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,182 +1292,182 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92700</v>
+        <v>2055</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+3.58%</t>
+          <t>+6.92%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>1291</v>
+        <v>154</v>
       </c>
       <c r="H10" t="n">
-        <v>23.61</v>
+        <v>0.51</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>89500</v>
+        <v>1922</v>
       </c>
       <c r="K10" t="n">
-        <v>92000</v>
+        <v>1920</v>
       </c>
       <c r="L10" t="n">
-        <v>94400</v>
+        <v>2165</v>
       </c>
       <c r="M10" t="n">
-        <v>91300</v>
+        <v>1862</v>
       </c>
       <c r="N10" t="n">
-        <v>23.63</v>
+        <v>0.61</v>
       </c>
       <c r="O10" t="n">
-        <v>154874798300</v>
+        <v>12317890385</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>2930</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>910</v>
       </c>
       <c r="R10" t="n">
-        <v>113000</v>
+        <v>29000</v>
       </c>
       <c r="S10" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 기술 개발 소식을 바탕으로 두산에너빌리티의 하반기 주도주 가능성 및 35만원 목표가 제시. 한-프랑스 정상회담 등 일부 근거 포함.</t>
+          <t>대주주 매도 공시 핑계 하락 후, 광주 개발 및 나대지 가치 상승 등 대규모 재료 공시 기대. 2차 파동 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '주가']</t>
+          <t>['대주주 매도', '재료 공시', '나대지 가치']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1846000</v>
+        <v>3850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.96%</t>
+          <t>+5.77%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.03</v>
+        <v>2.74</v>
       </c>
       <c r="E11" t="n">
-        <v>794</v>
+        <v>143</v>
       </c>
       <c r="F11" t="n">
-        <v>430</v>
+        <v>97</v>
       </c>
       <c r="G11" t="n">
-        <v>2496</v>
+        <v>362</v>
       </c>
       <c r="H11" t="n">
-        <v>50.66</v>
+        <v>3.19</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1793000</v>
+        <v>3640</v>
       </c>
       <c r="K11" t="n">
-        <v>1795000</v>
+        <v>3750</v>
       </c>
       <c r="L11" t="n">
-        <v>1849000</v>
+        <v>4460</v>
       </c>
       <c r="M11" t="n">
-        <v>1795000</v>
+        <v>3680</v>
       </c>
       <c r="N11" t="n">
-        <v>50.63</v>
+        <v>0.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1575741199000</v>
+        <v>241763663096</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>8100</v>
       </c>
       <c r="Q11" t="n">
-        <v>277000</v>
+        <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>3000</v>
+        <v>-15000</v>
       </c>
       <c r="S11" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>SK하이닉스의 200돌파 기대감 및 미국채 금리 하락 영향. 반도체 업종 내에서 삼성전자 대비 우위 언급.</t>
+          <t>광통신 관련 미국 시장 급등 소식 언급. 투자경고 종목 지정 및 단기 급등 가능성 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '반도체', '미국채']</t>
+          <t>['광통신', '투자경고', '미국 시장']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20500</v>
+        <v>1855000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+3.46%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.38</v>
+        <v>0.03</v>
       </c>
       <c r="E12" t="n">
-        <v>88</v>
+        <v>795</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>441</v>
       </c>
       <c r="G12" t="n">
-        <v>368</v>
+        <v>2180</v>
       </c>
       <c r="H12" t="n">
-        <v>10.85</v>
+        <v>50.66</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>19970</v>
+        <v>1793000</v>
       </c>
       <c r="K12" t="n">
-        <v>20250</v>
+        <v>1795000</v>
       </c>
       <c r="L12" t="n">
-        <v>21300</v>
+        <v>1864000</v>
       </c>
       <c r="M12" t="n">
-        <v>20050</v>
+        <v>1795000</v>
       </c>
       <c r="N12" t="n">
-        <v>10.47</v>
+        <v>50.63</v>
       </c>
       <c r="O12" t="n">
-        <v>119696056550</v>
+        <v>2643279558000</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>277000</v>
       </c>
       <c r="R12" t="n">
-        <v>-974000</v>
+        <v>11000</v>
       </c>
       <c r="S12" t="n">
-        <v>-23000</v>
+        <v>-3000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 원전 관련주 상승에 따른 기대감 및 대우건설 언급. 이란 항복, 유가 상승 등의 외부 요인도 거론됨.</t>
+          <t>미국채 금리 하락과 함께 차트 분석 기반 190 돌파 및 200 이상 상승 기대감 형성. UBS 매집 및 시체 감소 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '대우건설', '미국']</t>
+          <t>['미국채 금리', '차트 분석', 'HBM']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34600</v>
+        <v>92500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>+3.35%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>168</v>
       </c>
       <c r="G13" t="n">
-        <v>165</v>
+        <v>1420</v>
       </c>
       <c r="H13" t="n">
-        <v>52.73</v>
+        <v>23.61</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>34100</v>
+        <v>89500</v>
       </c>
       <c r="K13" t="n">
-        <v>34450</v>
+        <v>92000</v>
       </c>
       <c r="L13" t="n">
-        <v>35325</v>
+        <v>94400</v>
       </c>
       <c r="M13" t="n">
-        <v>34050</v>
+        <v>91300</v>
       </c>
       <c r="N13" t="n">
-        <v>21.01</v>
+        <v>23.63</v>
       </c>
       <c r="O13" t="n">
-        <v>36722512425</v>
+        <v>209388378000</v>
       </c>
       <c r="P13" t="n">
-        <v>69500</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>30400</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>7000</v>
+        <v>113000</v>
       </c>
       <c r="S13" t="n">
         <v>15000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>한국전력의 주가 상승 기대감 및 미국 원전 협력 가능성 언급. 발전 5사 통합 및 선납매 관련 내용도 포함.</t>
+          <t>미국 원전 사업 참여 및 SMR 기술 관련 기대감. 프랑스와의 원자력 협력 뉴스 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['한국전력', '원전', 'Smp']</t>
+          <t>['원전', 'SMR', '프랑스 협력']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12100</v>
+        <v>30350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-2.16</v>
+        <v>0.08</v>
       </c>
       <c r="E14" t="n">
-        <v>104</v>
+        <v>336</v>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="G14" t="n">
-        <v>233</v>
+        <v>390</v>
       </c>
       <c r="H14" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>29750</v>
+      </c>
+      <c r="K14" t="n">
+        <v>31600</v>
+      </c>
+      <c r="L14" t="n">
+        <v>34200</v>
+      </c>
+      <c r="M14" t="n">
+        <v>29750</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O14" t="n">
+        <v>231112094175</v>
+      </c>
+      <c r="P14" t="n">
+        <v>39350</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8200</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>11990</v>
-      </c>
-      <c r="K14" t="n">
-        <v>12440</v>
-      </c>
-      <c r="L14" t="n">
-        <v>12800</v>
-      </c>
-      <c r="M14" t="n">
-        <v>11920</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="O14" t="n">
-        <v>26987687415</v>
-      </c>
-      <c r="P14" t="n">
-        <v>36200</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>8920</v>
-      </c>
-      <c r="R14" t="n">
-        <v>37000</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-3000</v>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>국제 유가 급등에 따른 기대감 고조, 100달러 돌파 및 지정학적 리스크 언급. 외인 매도세 주의.</t>
+          <t>상장 후 주가 하락에 대한 우려와 기술적 반등 기대감 혼재. 상폐 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['국제 유가', '지정학적 리스크', '외인 매도']</t>
+          <t>['상장', '기술적반등', '상폐']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>271500</v>
+        <v>273500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>790</v>
       </c>
       <c r="F15" t="n">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="G15" t="n">
-        <v>2552</v>
+        <v>1726</v>
       </c>
       <c r="H15" t="n">
         <v>46.85</v>
@@ -1797,7 +1797,7 @@
         <v>269500</v>
       </c>
       <c r="L15" t="n">
-        <v>272000</v>
+        <v>274000</v>
       </c>
       <c r="M15" t="n">
         <v>268500</v>
@@ -1806,7 +1806,7 @@
         <v>46.79</v>
       </c>
       <c r="O15" t="n">
-        <v>980221751000</v>
+        <v>1701016930000</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1815,14 +1815,14 @@
         <v>70000</v>
       </c>
       <c r="R15" t="n">
-        <v>-467000</v>
+        <v>-486000</v>
       </c>
       <c r="S15" t="n">
         <v>12000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 반도체(인텔) 폭등에 따른 기대감. 개인의 저가 매수 유입.</t>
+          <t>반도체 업황 및 경쟁사(하이닉스) 비교 언급. 정치적 발언 및 개인적인 매매 전략 공유.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '인텔']</t>
+          <t>['반도체', '하이닉스', '매매 전략']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8980</v>
+        <v>9050</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.36</v>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="F16" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G16" t="n">
-        <v>255</v>
+        <v>319</v>
       </c>
       <c r="H16" t="n">
         <v>27.69</v>
@@ -1889,7 +1889,7 @@
         <v>8940</v>
       </c>
       <c r="L16" t="n">
-        <v>9030</v>
+        <v>9060</v>
       </c>
       <c r="M16" t="n">
         <v>8710</v>
@@ -1898,7 +1898,7 @@
         <v>28.05</v>
       </c>
       <c r="O16" t="n">
-        <v>9027832295</v>
+        <v>15086996990</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1907,7 +1907,7 @@
         <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>-209000</v>
+        <v>-243000</v>
       </c>
       <c r="S16" t="n">
         <v>9000</v>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10470</v>
+        <v>34500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+1.17%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G17" t="n">
-        <v>112</v>
+        <v>187</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9399999999999999</v>
+        <v>52.68</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,58 +1975,334 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10440</v>
+        <v>34100</v>
       </c>
       <c r="K17" t="n">
-        <v>10180</v>
+        <v>34450</v>
       </c>
       <c r="L17" t="n">
-        <v>11340</v>
+        <v>35325</v>
       </c>
       <c r="M17" t="n">
-        <v>10100</v>
+        <v>34050</v>
       </c>
       <c r="N17" t="n">
-        <v>0.62</v>
+        <v>21.01</v>
       </c>
       <c r="O17" t="n">
-        <v>101996324330</v>
+        <v>51319193800</v>
       </c>
       <c r="P17" t="n">
-        <v>15960</v>
+        <v>69500</v>
       </c>
       <c r="Q17" t="n">
-        <v>3500</v>
+        <v>30400</v>
       </c>
       <c r="R17" t="n">
-        <v>34000</v>
+        <v>-26000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 바이오 종목 상승에 대한 기대감 속 현대약품 언급. 다만, 미증시 제약바이오 폭락 및 종목 내 감정적 표현이 다수.</t>
+          <t>한국전력의 주가 상승 기대감 및 미국 원전 협력 가능성 언급. 발전 5사 통합 및 선납매 관련 내용도 포함.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>['한국전력', '원전', 'Smp']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>015760</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>흥구석유</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12100</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>+0.92%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>130</v>
+      </c>
+      <c r="F18" t="n">
+        <v>79</v>
+      </c>
+      <c r="G18" t="n">
+        <v>268</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>11990</v>
+      </c>
+      <c r="K18" t="n">
+        <v>12440</v>
+      </c>
+      <c r="L18" t="n">
+        <v>12800</v>
+      </c>
+      <c r="M18" t="n">
+        <v>11920</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O18" t="n">
+        <v>31382019440</v>
+      </c>
+      <c r="P18" t="n">
+        <v>36200</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8920</v>
+      </c>
+      <c r="R18" t="n">
+        <v>37000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>국제유가 급등에 따른 수혜 기대감 및 중동 지역 지정학적 리스크 부각. 단기 트레이딩 관점에서의 접근.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['국제유가', '지정학적 리스크', '단기 트레이딩']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>024060</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>19790</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-0.90%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E19" t="n">
+        <v>148</v>
+      </c>
+      <c r="F19" t="n">
+        <v>82</v>
+      </c>
+      <c r="G19" t="n">
+        <v>553</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>19970</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20250</v>
+      </c>
+      <c r="L19" t="n">
+        <v>21300</v>
+      </c>
+      <c r="M19" t="n">
+        <v>19630</v>
+      </c>
+      <c r="N19" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="O19" t="n">
+        <v>186693858625</v>
+      </c>
+      <c r="P19" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-976000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-23000</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>미국 원전 사업 참여 기대감 속 공시 내용 확인. 통정거래 및 단기매매 비판.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['원전', '공시', '통정거래']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>현대약품</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>10210</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-2.20%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E20" t="n">
+        <v>71</v>
+      </c>
+      <c r="F20" t="n">
+        <v>58</v>
+      </c>
+      <c r="G20" t="n">
+        <v>163</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>10440</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10180</v>
+      </c>
+      <c r="L20" t="n">
+        <v>11340</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10100</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O20" t="n">
+        <v>121468759935</v>
+      </c>
+      <c r="P20" t="n">
+        <v>15960</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3500</v>
+      </c>
+      <c r="R20" t="n">
+        <v>34000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>미국 바이오 종목 상승에 대한 기대감 속 현대약품 언급. 다만, 미증시 제약바이오 폭락 및 종목 내 감정적 표현이 다수.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>['미프진', '제약바이오', '신고가']</t>
         </is>
       </c>
-      <c r="X17" t="n">
+      <c r="X20" t="n">
         <v>7</v>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>004310</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F2" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G2" t="n">
-        <v>796</v>
+        <v>852</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29105139135</v>
+        <v>29209397555</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -619,7 +619,7 @@
         <v>2300</v>
       </c>
       <c r="R2" t="n">
-        <v>-15000</v>
+        <v>164000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -673,10 +673,10 @@
         <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
@@ -702,7 +702,7 @@
         <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>36821088165</v>
+        <v>36894580185</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -711,7 +711,7 @@
         <v>1206</v>
       </c>
       <c r="R3" t="n">
-        <v>84000</v>
+        <v>29000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13980</v>
+        <v>14310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+18.37%</t>
+          <t>+21.17%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G4" t="n">
-        <v>805</v>
+        <v>845</v>
       </c>
       <c r="H4" t="n">
         <v>5.64</v>
@@ -785,7 +785,7 @@
         <v>12050</v>
       </c>
       <c r="L4" t="n">
-        <v>14200</v>
+        <v>14370</v>
       </c>
       <c r="M4" t="n">
         <v>11950</v>
@@ -794,7 +794,7 @@
         <v>5.42</v>
       </c>
       <c r="O4" t="n">
-        <v>275769823370</v>
+        <v>306684044415</v>
       </c>
       <c r="P4" t="n">
         <v>30200</v>
@@ -803,10 +803,10 @@
         <v>3540</v>
       </c>
       <c r="R4" t="n">
-        <v>553000</v>
+        <v>515000</v>
       </c>
       <c r="S4" t="n">
-        <v>6000</v>
+        <v>18000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7280</v>
+        <v>7150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.29%</t>
+          <t>+14.22%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>431</v>
+        <v>519</v>
       </c>
       <c r="H5" t="n">
         <v>7.4</v>
@@ -886,7 +886,7 @@
         <v>7.35</v>
       </c>
       <c r="O5" t="n">
-        <v>42228810730</v>
+        <v>45982359535</v>
       </c>
       <c r="P5" t="n">
         <v>21500</v>
@@ -895,23 +895,23 @@
         <v>4565</v>
       </c>
       <c r="R5" t="n">
-        <v>9000</v>
+        <v>-376000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>신약 개발(페니트리움바이오) 관련 희망 회로와 주가 부진에 대한 답답함 토로. 실험 결과 발표 기대.</t>
+          <t>오가노이드 및 뎅기열 관련 신규 임상 결과 발표에 따른 긍정적 전망. 항암제 개발 기대감 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['신약개발', '희망회로', '실험결과']</t>
+          <t>['오가노이드', '뎅기열', '항암제']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7320</v>
+        <v>54800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+13.84%</t>
+          <t>+11.27%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.31</v>
+        <v>0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="F6" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G6" t="n">
-        <v>171</v>
+        <v>381</v>
       </c>
       <c r="H6" t="n">
-        <v>16.71</v>
+        <v>14.96</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6430</v>
+        <v>49250</v>
       </c>
       <c r="K6" t="n">
-        <v>6400</v>
+        <v>53500</v>
       </c>
       <c r="L6" t="n">
-        <v>7470</v>
+        <v>59000</v>
       </c>
       <c r="M6" t="n">
-        <v>6250</v>
+        <v>51600</v>
       </c>
       <c r="N6" t="n">
-        <v>16.4</v>
+        <v>14.93</v>
       </c>
       <c r="O6" t="n">
-        <v>67652376605</v>
+        <v>135754430350</v>
       </c>
       <c r="P6" t="n">
-        <v>13000</v>
+        <v>108900</v>
       </c>
       <c r="Q6" t="n">
-        <v>6030</v>
+        <v>18230</v>
       </c>
       <c r="R6" t="n">
-        <v>-91000</v>
+        <v>-225000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주주환원 정책 및 공매도 관련 언급, 반도체 사업 부문에 대한 저평가 주장. 외인 매도세 속 주가 상승 기대.</t>
+          <t>수소 에너지 관련 기업의 성장성 및 목표가 상향 기대. 기관 매수세 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주주환원', '공매도', '반도체']</t>
+          <t>['수소에너지', '성장성', '기관']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55200</v>
+        <v>7070</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+12.08%</t>
+          <t>+9.95%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.03</v>
+        <v>0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>118</v>
+        <v>186</v>
       </c>
       <c r="F7" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="G7" t="n">
-        <v>363</v>
+        <v>199</v>
       </c>
       <c r="H7" t="n">
-        <v>14.96</v>
+        <v>16.71</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>49250</v>
+        <v>6430</v>
       </c>
       <c r="K7" t="n">
-        <v>53500</v>
+        <v>6400</v>
       </c>
       <c r="L7" t="n">
-        <v>59000</v>
+        <v>7470</v>
       </c>
       <c r="M7" t="n">
-        <v>51600</v>
+        <v>6250</v>
       </c>
       <c r="N7" t="n">
-        <v>14.93</v>
+        <v>16.4</v>
       </c>
       <c r="O7" t="n">
-        <v>133186977500</v>
+        <v>73255064640</v>
       </c>
       <c r="P7" t="n">
-        <v>108900</v>
+        <v>13000</v>
       </c>
       <c r="Q7" t="n">
-        <v>18230</v>
+        <v>6030</v>
       </c>
       <c r="R7" t="n">
-        <v>-232000</v>
+        <v>-554000</v>
       </c>
       <c r="S7" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>기관/외인 수급 변화 및 목표가 관련 논의. 수소 연료 전지 사업 성장성 언급.</t>
+          <t>6천억~1조 규모 주주환원 및 배당 관련 긍정적 전망. 공매도 세력에 대한 기대감 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기관', '외인', '수소연료전지']</t>
+          <t>['주주환원', '배당', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8370</v>
+        <v>8330</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.98%</t>
+          <t>+8.46%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>1.4</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H8" t="n">
         <v>1.81</v>
@@ -1162,7 +1162,7 @@
         <v>0.41</v>
       </c>
       <c r="O8" t="n">
-        <v>93016766555</v>
+        <v>94375689195</v>
       </c>
       <c r="P8" t="n">
         <v>10300</v>
@@ -1171,7 +1171,7 @@
         <v>952</v>
       </c>
       <c r="R8" t="n">
-        <v>-73000</v>
+        <v>-206000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14720</v>
+        <v>14830</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.45%</t>
+          <t>+8.25%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.39</v>
       </c>
       <c r="E9" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F9" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G9" t="n">
-        <v>930</v>
+        <v>949</v>
       </c>
       <c r="H9" t="n">
         <v>1.55</v>
@@ -1254,7 +1254,7 @@
         <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>359062276575</v>
+        <v>364548002510</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1263,23 +1263,23 @@
         <v>1252</v>
       </c>
       <c r="R9" t="n">
-        <v>559000</v>
+        <v>820000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>단기 박스권 돌파 및 상승 추세 기대. 미국 광통신 종목 동반 상승 언급. 공매도 물량 소화.</t>
+          <t>단기 박스권 돌파 및 우상향 추세 전망. 공매도 물량 청산 기대감 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '상승추세', '공매도']</t>
+          <t>['상한가', '우상향', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2055</v>
+        <v>2065</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.92%</t>
+          <t>+7.44%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="H10" t="n">
         <v>0.51</v>
@@ -1346,7 +1346,7 @@
         <v>0.61</v>
       </c>
       <c r="O10" t="n">
-        <v>12317890385</v>
+        <v>12841113661</v>
       </c>
       <c r="P10" t="n">
         <v>2930</v>
@@ -1355,7 +1355,7 @@
         <v>910</v>
       </c>
       <c r="R10" t="n">
-        <v>29000</v>
+        <v>70000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3850</v>
+        <v>3890</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.77%</t>
+          <t>+6.87%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2.74</v>
       </c>
       <c r="E11" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="F11" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G11" t="n">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="H11" t="n">
         <v>3.19</v>
@@ -1438,7 +1438,7 @@
         <v>0.45</v>
       </c>
       <c r="O11" t="n">
-        <v>241763663096</v>
+        <v>245383209824</v>
       </c>
       <c r="P11" t="n">
         <v>8100</v>
@@ -1447,7 +1447,7 @@
         <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>-15000</v>
+        <v>-348000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1855000</v>
+        <v>92900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.46%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>795</v>
+        <v>242</v>
       </c>
       <c r="F12" t="n">
-        <v>441</v>
+        <v>168</v>
       </c>
       <c r="G12" t="n">
-        <v>2180</v>
+        <v>1435</v>
       </c>
       <c r="H12" t="n">
-        <v>50.66</v>
+        <v>23.61</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1793000</v>
+        <v>89500</v>
       </c>
       <c r="K12" t="n">
-        <v>1795000</v>
+        <v>92000</v>
       </c>
       <c r="L12" t="n">
-        <v>1864000</v>
+        <v>94400</v>
       </c>
       <c r="M12" t="n">
-        <v>1795000</v>
+        <v>91300</v>
       </c>
       <c r="N12" t="n">
-        <v>50.63</v>
+        <v>23.63</v>
       </c>
       <c r="O12" t="n">
-        <v>2643279558000</v>
+        <v>215319549150</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>277000</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>11000</v>
+        <v>104000</v>
       </c>
       <c r="S12" t="n">
-        <v>-3000</v>
+        <v>26000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국채 금리 하락과 함께 차트 분석 기반 190 돌파 및 200 이상 상승 기대감 형성. UBS 매집 및 시체 감소 언급.</t>
+          <t>미국 원전 사업 참여 및 SMR 기술 관련 기대감. 프랑스와의 원자력 협력 뉴스 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미국채 금리', '차트 분석', 'HBM']</t>
+          <t>['원전', 'SMR', '프랑스 협력']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>92500</v>
+        <v>1859000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>+3.68%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>236</v>
+        <v>795</v>
       </c>
       <c r="F13" t="n">
-        <v>168</v>
+        <v>445</v>
       </c>
       <c r="G13" t="n">
-        <v>1420</v>
+        <v>2194</v>
       </c>
       <c r="H13" t="n">
-        <v>23.61</v>
+        <v>50.66</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>89500</v>
+        <v>1793000</v>
       </c>
       <c r="K13" t="n">
-        <v>92000</v>
+        <v>1795000</v>
       </c>
       <c r="L13" t="n">
-        <v>94400</v>
+        <v>1864000</v>
       </c>
       <c r="M13" t="n">
-        <v>91300</v>
+        <v>1795000</v>
       </c>
       <c r="N13" t="n">
-        <v>23.63</v>
+        <v>50.63</v>
       </c>
       <c r="O13" t="n">
-        <v>209388378000</v>
+        <v>2750704625000</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>277000</v>
       </c>
       <c r="R13" t="n">
-        <v>113000</v>
+        <v>53000</v>
       </c>
       <c r="S13" t="n">
-        <v>15000</v>
+        <v>37000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 원전 사업 참여 및 SMR 기술 관련 기대감. 프랑스와의 원자력 협력 뉴스 기반 상승 전망.</t>
+          <t>SK하이닉스 주가 190~200만원대 회복 및 추가 상승 전망. 자사주 매입 및 기관 매집 관련 긍정적 신호 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '프랑스 협력']</t>
+          <t>['반도체', 'HBM', '자사주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30350</v>
+        <v>30250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>+1.68%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.08</v>
       </c>
       <c r="E14" t="n">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="F14" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G14" t="n">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="H14" t="n">
         <v>0.31</v>
@@ -1714,7 +1714,7 @@
         <v>0.23</v>
       </c>
       <c r="O14" t="n">
-        <v>231112094175</v>
+        <v>233706993925</v>
       </c>
       <c r="P14" t="n">
         <v>39350</v>
@@ -1723,7 +1723,7 @@
         <v>8200</v>
       </c>
       <c r="R14" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>273500</v>
+        <v>273750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+1.58%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>790</v>
       </c>
       <c r="F15" t="n">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="G15" t="n">
-        <v>1726</v>
+        <v>1697</v>
       </c>
       <c r="H15" t="n">
         <v>46.85</v>
@@ -1797,7 +1797,7 @@
         <v>269500</v>
       </c>
       <c r="L15" t="n">
-        <v>274000</v>
+        <v>274500</v>
       </c>
       <c r="M15" t="n">
         <v>268500</v>
@@ -1806,7 +1806,7 @@
         <v>46.79</v>
       </c>
       <c r="O15" t="n">
-        <v>1701016930000</v>
+        <v>1848418750000</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1815,14 +1815,14 @@
         <v>70000</v>
       </c>
       <c r="R15" t="n">
-        <v>-486000</v>
+        <v>-301000</v>
       </c>
       <c r="S15" t="n">
-        <v>12000</v>
+        <v>176000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>반도체 업황 및 경쟁사(하이닉스) 비교 언급. 정치적 발언 및 개인적인 매매 전략 공유.</t>
+          <t>삼성전자 주가 관련 혼조세, 하이닉스와의 비교 언급. 정치적 이슈 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['반도체', '하이닉스', '매매 전략']</t>
+          <t>['반도체', '주가', '하이닉스']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9050</v>
+        <v>9060</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>+1.34%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.36</v>
       </c>
       <c r="E16" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="H16" t="n">
         <v>27.69</v>
@@ -1889,7 +1889,7 @@
         <v>8940</v>
       </c>
       <c r="L16" t="n">
-        <v>9060</v>
+        <v>9070</v>
       </c>
       <c r="M16" t="n">
         <v>8710</v>
@@ -1898,7 +1898,7 @@
         <v>28.05</v>
       </c>
       <c r="O16" t="n">
-        <v>15086996990</v>
+        <v>16039677820</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1907,10 +1907,10 @@
         <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>-243000</v>
+        <v>-289000</v>
       </c>
       <c r="S16" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1947,27 +1947,27 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34500</v>
+        <v>34550</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G17" t="n">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="H17" t="n">
-        <v>52.68</v>
+        <v>52.67</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>21.01</v>
       </c>
       <c r="O17" t="n">
-        <v>51319193800</v>
+        <v>52833652650</v>
       </c>
       <c r="P17" t="n">
         <v>69500</v>
@@ -1999,10 +1999,10 @@
         <v>30400</v>
       </c>
       <c r="R17" t="n">
-        <v>-26000</v>
+        <v>-78000</v>
       </c>
       <c r="S17" t="n">
-        <v>15000</v>
+        <v>61000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12100</v>
+        <v>12030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-2.16</v>
       </c>
       <c r="E18" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F18" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>2.16</v>
       </c>
       <c r="O18" t="n">
-        <v>31382019440</v>
+        <v>32362285865</v>
       </c>
       <c r="P18" t="n">
         <v>36200</v>
@@ -2091,10 +2091,10 @@
         <v>8920</v>
       </c>
       <c r="R18" t="n">
-        <v>37000</v>
+        <v>43000</v>
       </c>
       <c r="S18" t="n">
-        <v>-3000</v>
+        <v>-6000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19790</v>
+        <v>20000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.90%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.38</v>
       </c>
       <c r="E19" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F19" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G19" t="n">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="H19" t="n">
         <v>10.85</v>
@@ -2174,7 +2174,7 @@
         <v>10.47</v>
       </c>
       <c r="O19" t="n">
-        <v>186693858625</v>
+        <v>192675664420</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2183,10 +2183,10 @@
         <v>3320</v>
       </c>
       <c r="R19" t="n">
-        <v>-976000</v>
+        <v>-844000</v>
       </c>
       <c r="S19" t="n">
-        <v>-23000</v>
+        <v>45000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10210</v>
+        <v>10160</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.20%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.32</v>
       </c>
       <c r="E20" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F20" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G20" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H20" t="n">
         <v>0.9399999999999999</v>
@@ -2266,7 +2266,7 @@
         <v>0.62</v>
       </c>
       <c r="O20" t="n">
-        <v>121468759935</v>
+        <v>123389341610</v>
       </c>
       <c r="P20" t="n">
         <v>15960</v>
@@ -2275,7 +2275,7 @@
         <v>3500</v>
       </c>
       <c r="R20" t="n">
-        <v>34000</v>
+        <v>-43000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="F2" t="n">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="G2" t="n">
-        <v>852</v>
+        <v>1114</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29209397555</v>
+        <v>29510627295</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미 FDA 2A상 승인 및 폐암·난소암 관련 뉴스 기반, 글로벌 시장 도장깨기 기대감 고조. 외인 비중 하락에도 불구하고 긍정적 전망. 10연상 예약 언급.</t>
+          <t>미 FDA 2A상 승인 및 다락손라십 대비 우수한 임상 결과. 20,800원 전고점 돌파 및 5~10연상 기대감. 폐암, 난소암 등 다양한 암종에 대한 효능 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA 2A상', '글로벌 시장', '암세포 사멸']</t>
+          <t>['FDA', '임상결과', '암치료']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>195</v>
+        <v>265</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
@@ -702,7 +702,7 @@
         <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>36894580185</v>
+        <v>37546974615</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14310</v>
+        <v>12440</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.17%</t>
+          <t>+24.03%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.22</v>
+        <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="F4" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>845</v>
+        <v>201</v>
       </c>
       <c r="H4" t="n">
-        <v>5.64</v>
+        <v>0.36</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11810</v>
+        <v>10030</v>
       </c>
       <c r="K4" t="n">
-        <v>12050</v>
+        <v>10270</v>
       </c>
       <c r="L4" t="n">
-        <v>14370</v>
+        <v>12790</v>
       </c>
       <c r="M4" t="n">
-        <v>11950</v>
+        <v>10040</v>
       </c>
       <c r="N4" t="n">
-        <v>5.42</v>
+        <v>0.44</v>
       </c>
       <c r="O4" t="n">
-        <v>306684044415</v>
+        <v>132341196320</v>
       </c>
       <c r="P4" t="n">
-        <v>30200</v>
+        <v>20850</v>
       </c>
       <c r="Q4" t="n">
-        <v>3540</v>
+        <v>4020</v>
       </c>
       <c r="R4" t="n">
-        <v>515000</v>
+        <v>25000</v>
       </c>
       <c r="S4" t="n">
-        <v>18000</v>
+        <v>19000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>원전 로봇 및 소형원자로 사업 관련 기대감. 체코, 미국, 사우디 등 해외 수주 가능성 언급.</t>
+          <t>미국 증시 SMR 및 원전 관련주 폭등 영향. 12,000원 돌파 시 추가 상승 전망. 2연상 이상 기대감 및 글로벌 원전 터빈 시장 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['원전', '로봇', '해외수주']</t>
+          <t>['원전', 'SMR', '가스터빈']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>현대바이오</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7150</v>
+        <v>13800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+14.22%</t>
+          <t>+16.85%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="G5" t="n">
-        <v>519</v>
+        <v>1113</v>
       </c>
       <c r="H5" t="n">
-        <v>7.4</v>
+        <v>5.64</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6260</v>
+        <v>11810</v>
       </c>
       <c r="K5" t="n">
-        <v>6200</v>
+        <v>12050</v>
       </c>
       <c r="L5" t="n">
-        <v>7730</v>
+        <v>14550</v>
       </c>
       <c r="M5" t="n">
-        <v>6140</v>
+        <v>11950</v>
       </c>
       <c r="N5" t="n">
-        <v>7.35</v>
+        <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>45982359535</v>
+        <v>413027345160</v>
       </c>
       <c r="P5" t="n">
-        <v>21500</v>
+        <v>30200</v>
       </c>
       <c r="Q5" t="n">
-        <v>4565</v>
+        <v>3540</v>
       </c>
       <c r="R5" t="n">
-        <v>-376000</v>
+        <v>515000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>오가노이드 및 뎅기열 관련 신규 임상 결과 발표에 따른 긍정적 전망. 항암제 개발 기대감 언급.</t>
+          <t>체코, 미국 등 원전 관련 국가와의 협력 강화 및 하반기 주도주로서의 원전 로봇 부각. 사우디 수주 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['오가노이드', '뎅기열', '항암제']</t>
+          <t>['원전', '로봇', '수주']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>048410</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>현대바이오</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54800</v>
+        <v>7210</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+11.27%</t>
+          <t>+15.18%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="F6" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G6" t="n">
-        <v>381</v>
+        <v>761</v>
       </c>
       <c r="H6" t="n">
-        <v>14.96</v>
+        <v>7.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>49250</v>
+        <v>6260</v>
       </c>
       <c r="K6" t="n">
-        <v>53500</v>
+        <v>6200</v>
       </c>
       <c r="L6" t="n">
-        <v>59000</v>
+        <v>7730</v>
       </c>
       <c r="M6" t="n">
-        <v>51600</v>
+        <v>6140</v>
       </c>
       <c r="N6" t="n">
-        <v>14.93</v>
+        <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>135754430350</v>
+        <v>59776763780</v>
       </c>
       <c r="P6" t="n">
-        <v>108900</v>
+        <v>21500</v>
       </c>
       <c r="Q6" t="n">
-        <v>18230</v>
+        <v>4565</v>
       </c>
       <c r="R6" t="n">
-        <v>-225000</v>
+        <v>-376000</v>
       </c>
       <c r="S6" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>수소 에너지 관련 기업의 성장성 및 목표가 상향 기대. 기관 매수세 유입 가능성 언급.</t>
+          <t>췌장암 치료제 '다락손라십' 및 뎅기열 치료제 개발 관련 긍정적 임상 결과 발표. 공매도와의 승부 예상.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['수소에너지', '성장성', '기관']</t>
+          <t>['췌장암', '뎅기열', '임상결과']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>048410</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7070</v>
+        <v>54200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.95%</t>
+          <t>+10.05%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.31</v>
+        <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="F7" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G7" t="n">
-        <v>199</v>
+        <v>434</v>
       </c>
       <c r="H7" t="n">
-        <v>16.71</v>
+        <v>14.96</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6430</v>
+        <v>49250</v>
       </c>
       <c r="K7" t="n">
-        <v>6400</v>
+        <v>53500</v>
       </c>
       <c r="L7" t="n">
-        <v>7470</v>
+        <v>59000</v>
       </c>
       <c r="M7" t="n">
-        <v>6250</v>
+        <v>51600</v>
       </c>
       <c r="N7" t="n">
-        <v>16.4</v>
+        <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>73255064640</v>
+        <v>146540580950</v>
       </c>
       <c r="P7" t="n">
-        <v>13000</v>
+        <v>108900</v>
       </c>
       <c r="Q7" t="n">
-        <v>6030</v>
+        <v>18230</v>
       </c>
       <c r="R7" t="n">
-        <v>-554000</v>
+        <v>-225000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>6천억~1조 규모 주주환원 및 배당 관련 긍정적 전망. 공매도 세력에 대한 기대감 언급.</t>
+          <t>2분기 영업이익 적자 전환에도 불구하고 목표가 상향 조정 의견 존재. 외인 매도세 지속.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주주환원', '배당', '공매도']</t>
+          <t>['영업이익', '목표가', '외인매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8330</v>
+        <v>14830</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.46%</t>
+          <t>+8.25%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.4</v>
+        <v>-0.39</v>
       </c>
       <c r="E8" t="n">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="G8" t="n">
-        <v>224</v>
+        <v>1122</v>
       </c>
       <c r="H8" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7680</v>
+        <v>13700</v>
       </c>
       <c r="K8" t="n">
-        <v>7780</v>
+        <v>14260</v>
       </c>
       <c r="L8" t="n">
-        <v>9000</v>
+        <v>15860</v>
       </c>
       <c r="M8" t="n">
-        <v>7750</v>
+        <v>14210</v>
       </c>
       <c r="N8" t="n">
-        <v>0.41</v>
+        <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>94375689195</v>
+        <v>393707434040</v>
       </c>
       <c r="P8" t="n">
-        <v>10300</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>952</v>
+        <v>1252</v>
       </c>
       <c r="R8" t="n">
-        <v>-206000</v>
+        <v>820000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>서산의 시멘트 업종 및 건설 관련 기대감. 대장주로서의 움직임 및 외인 대량 매수 언급.</t>
+          <t>빛과전자 수급 흡수 및 단기 박스권 돌파로 인한 상승세. 2만 원 돌파 및 우상향 추세 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['서산', '시멘트', '건설']</t>
+          <t>['빛과전자', '박스권 돌파', '우상향']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14830</v>
+        <v>8130</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.25%</t>
+          <t>+5.86%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.39</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
-        <v>183</v>
+        <v>93</v>
       </c>
       <c r="F9" t="n">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
-        <v>949</v>
+        <v>268</v>
       </c>
       <c r="H9" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13700</v>
+        <v>7680</v>
       </c>
       <c r="K9" t="n">
-        <v>14260</v>
+        <v>7780</v>
       </c>
       <c r="L9" t="n">
-        <v>15860</v>
+        <v>9000</v>
       </c>
       <c r="M9" t="n">
-        <v>14210</v>
+        <v>7750</v>
       </c>
       <c r="N9" t="n">
-        <v>1.94</v>
+        <v>0.41</v>
       </c>
       <c r="O9" t="n">
-        <v>364548002510</v>
+        <v>105728927760</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>10300</v>
       </c>
       <c r="Q9" t="n">
-        <v>1252</v>
+        <v>952</v>
       </c>
       <c r="R9" t="n">
-        <v>820000</v>
+        <v>-206000</v>
       </c>
       <c r="S9" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>단기 박스권 돌파 및 우상향 추세 전망. 공매도 물량 청산 기대감 언급.</t>
+          <t>레미콘 파업 시작으로 인한 대장주로서의 상승 모멘텀 확보. 강동구 건설 호재와 함께 상한가 기록 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['상한가', '우상향', '공매도']</t>
+          <t>['레미콘', '대장주', '상한가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2065</v>
+        <v>3850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+7.44%</t>
+          <t>+5.77%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1</v>
+        <v>2.74</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="G10" t="n">
-        <v>166</v>
+        <v>416</v>
       </c>
       <c r="H10" t="n">
-        <v>0.51</v>
+        <v>3.19</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1922</v>
+        <v>3640</v>
       </c>
       <c r="K10" t="n">
-        <v>1920</v>
+        <v>3750</v>
       </c>
       <c r="L10" t="n">
-        <v>2165</v>
+        <v>4460</v>
       </c>
       <c r="M10" t="n">
-        <v>1862</v>
+        <v>3680</v>
       </c>
       <c r="N10" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="O10" t="n">
-        <v>12841113661</v>
+        <v>256416681658</v>
       </c>
       <c r="P10" t="n">
-        <v>2930</v>
+        <v>8100</v>
       </c>
       <c r="Q10" t="n">
-        <v>910</v>
+        <v>592</v>
       </c>
       <c r="R10" t="n">
-        <v>70000</v>
+        <v>-348000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대주주 매도 공시 핑계 하락 후, 광주 개발 및 나대지 가치 상승 등 대규모 재료 공시 기대. 2차 파동 전망.</t>
+          <t>미국 광통신 섹터 급등과 연관. 재료의 우수성을 근거로 6천원 이상 목표가 제시. 투자경고 종목 지정 가능성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['대주주 매도', '재료 공시', '나대지 가치']</t>
+          <t>['광통신', '재료', '투자경고']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,82 +1379,82 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3890</v>
+        <v>6730</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+6.87%</t>
+          <t>+4.67%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.74</v>
+        <v>0.31</v>
       </c>
       <c r="E11" t="n">
-        <v>152</v>
+        <v>284</v>
       </c>
       <c r="F11" t="n">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="G11" t="n">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H11" t="n">
-        <v>3.19</v>
+        <v>16.71</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3640</v>
+        <v>6430</v>
       </c>
       <c r="K11" t="n">
-        <v>3750</v>
+        <v>6400</v>
       </c>
       <c r="L11" t="n">
-        <v>4460</v>
+        <v>7470</v>
       </c>
       <c r="M11" t="n">
-        <v>3680</v>
+        <v>6250</v>
       </c>
       <c r="N11" t="n">
-        <v>0.45</v>
+        <v>16.4</v>
       </c>
       <c r="O11" t="n">
-        <v>245383209824</v>
+        <v>91075124055</v>
       </c>
       <c r="P11" t="n">
-        <v>8100</v>
+        <v>13000</v>
       </c>
       <c r="Q11" t="n">
-        <v>592</v>
+        <v>6030</v>
       </c>
       <c r="R11" t="n">
-        <v>-348000</v>
+        <v>-554000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>광통신 관련 미국 시장 급등 소식 언급. 투자경고 종목 지정 및 단기 급등 가능성 제기.</t>
+          <t>사명 변경 후 주가 하락 및 공매도 관련 우려. 배당 지급 예정에도 불구하고 주가 부진 지속. 일부 투자자는 단기 급등 전망 제시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '투자경고', '미국 시장']</t>
+          <t>['공매도', '배당', '주주환원']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>92900</v>
+        <v>1859000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>+3.68%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E12" t="n">
-        <v>242</v>
+        <v>798</v>
       </c>
       <c r="F12" t="n">
-        <v>168</v>
+        <v>442</v>
       </c>
       <c r="G12" t="n">
-        <v>1435</v>
+        <v>2240</v>
       </c>
       <c r="H12" t="n">
-        <v>23.61</v>
+        <v>50.66</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>89500</v>
+        <v>1793000</v>
       </c>
       <c r="K12" t="n">
-        <v>92000</v>
+        <v>1795000</v>
       </c>
       <c r="L12" t="n">
-        <v>94400</v>
+        <v>1883000</v>
       </c>
       <c r="M12" t="n">
-        <v>91300</v>
+        <v>1795000</v>
       </c>
       <c r="N12" t="n">
-        <v>23.63</v>
+        <v>50.63</v>
       </c>
       <c r="O12" t="n">
-        <v>215319549150</v>
+        <v>3779674340500</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>277000</v>
       </c>
       <c r="R12" t="n">
-        <v>104000</v>
+        <v>53000</v>
       </c>
       <c r="S12" t="n">
-        <v>26000</v>
+        <v>37000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 원전 사업 참여 및 SMR 기술 관련 기대감. 프랑스와의 원자력 협력 뉴스 기반 상승 전망.</t>
+          <t>외국인 및 기관 매수세 유입. 190, 200만원 목표가 제시 및 긍정적 수급 전망. 리밸런싱 완료 및 매물대 소화 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '프랑스 협력']</t>
+          <t>['외인매수', '목표가', '수급']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1859000</v>
+        <v>1988</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.68%</t>
+          <t>+3.43%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>795</v>
+        <v>101</v>
       </c>
       <c r="F13" t="n">
-        <v>445</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>2194</v>
+        <v>230</v>
       </c>
       <c r="H13" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1793000</v>
+        <v>1922</v>
       </c>
       <c r="K13" t="n">
-        <v>1795000</v>
+        <v>1920</v>
       </c>
       <c r="L13" t="n">
-        <v>1864000</v>
+        <v>2165</v>
       </c>
       <c r="M13" t="n">
-        <v>1795000</v>
+        <v>1862</v>
       </c>
       <c r="N13" t="n">
-        <v>50.63</v>
+        <v>0.61</v>
       </c>
       <c r="O13" t="n">
-        <v>2750704625000</v>
+        <v>15708183766</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q13" t="n">
-        <v>277000</v>
+        <v>910</v>
       </c>
       <c r="R13" t="n">
-        <v>53000</v>
+        <v>70000</v>
       </c>
       <c r="S13" t="n">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가 190~200만원대 회복 및 추가 상승 전망. 자사주 매입 및 기관 매집 관련 긍정적 신호 언급.</t>
+          <t>호남반도체 클러스터 대장주로서의 기대감과 텐버거 가능성 언급. 대주주 매도 공시를 핑계로 한 하락 가능성도 있으나, 주포 세력의 시세 조작 및 물량 넘기기 수법에 대한 경계와 함께 반등을 기대하는 분위기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', 'HBM', '자사주']</t>
+          <t>['반도체 클러스터', '텐버거', '주포']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30250</v>
+        <v>92100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+1.68%</t>
+          <t>+2.91%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>348</v>
+        <v>289</v>
       </c>
       <c r="F14" t="n">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="G14" t="n">
-        <v>397</v>
+        <v>1539</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31</v>
+        <v>23.61</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>29750</v>
+        <v>89500</v>
       </c>
       <c r="K14" t="n">
-        <v>31600</v>
+        <v>92000</v>
       </c>
       <c r="L14" t="n">
-        <v>34200</v>
+        <v>94400</v>
       </c>
       <c r="M14" t="n">
-        <v>29750</v>
+        <v>91300</v>
       </c>
       <c r="N14" t="n">
-        <v>0.23</v>
+        <v>23.63</v>
       </c>
       <c r="O14" t="n">
-        <v>233706993925</v>
+        <v>244690318550</v>
       </c>
       <c r="P14" t="n">
-        <v>39350</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>8200</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>104000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>상장 후 주가 하락에 대한 우려와 기술적 반등 기대감 혼재. 상폐 가능성 언급.</t>
+          <t>미국 원전 사업 참여 및 SMR 기술 관련 기대감. 프랑스와의 원자력 협력 뉴스 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['상장', '기술적반등', '상폐']</t>
+          <t>['원전', 'SMR', '프랑스 협력']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>273750</v>
+        <v>12270</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+1.58%</t>
+          <t>+2.34%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.06</v>
+        <v>-2.16</v>
       </c>
       <c r="E15" t="n">
-        <v>790</v>
+        <v>149</v>
       </c>
       <c r="F15" t="n">
-        <v>459</v>
+        <v>91</v>
       </c>
       <c r="G15" t="n">
-        <v>1697</v>
+        <v>286</v>
       </c>
       <c r="H15" t="n">
-        <v>46.85</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>269500</v>
+        <v>11990</v>
       </c>
       <c r="K15" t="n">
-        <v>269500</v>
+        <v>12440</v>
       </c>
       <c r="L15" t="n">
-        <v>274500</v>
+        <v>12800</v>
       </c>
       <c r="M15" t="n">
-        <v>268500</v>
+        <v>11920</v>
       </c>
       <c r="N15" t="n">
-        <v>46.79</v>
+        <v>2.16</v>
       </c>
       <c r="O15" t="n">
-        <v>1848418750000</v>
+        <v>37276944785</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>36200</v>
       </c>
       <c r="Q15" t="n">
-        <v>70000</v>
+        <v>8920</v>
       </c>
       <c r="R15" t="n">
-        <v>-301000</v>
+        <v>43000</v>
       </c>
       <c r="S15" t="n">
-        <v>176000</v>
+        <v>-6000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성전자 주가 관련 혼조세, 하이닉스와의 비교 언급. 정치적 이슈 언급.</t>
+          <t>국제유가 급등세 지속 및 100달러 돌파 임박. 이란 유조선 공격 등 지정학적 리스크 부각. 단기 트레이딩 관점 유지.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['반도체', '주가', '하이닉스']</t>
+          <t>['국제유가', '지정학적리스크', '단기트레이딩']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9060</v>
+        <v>271750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+1.34%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.36</v>
+        <v>0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>787</v>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>463</v>
       </c>
       <c r="G16" t="n">
-        <v>327</v>
+        <v>1511</v>
       </c>
       <c r="H16" t="n">
-        <v>27.69</v>
+        <v>46.85</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="K16" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="L16" t="n">
-        <v>9070</v>
+        <v>275000</v>
       </c>
       <c r="M16" t="n">
-        <v>8710</v>
+        <v>268500</v>
       </c>
       <c r="N16" t="n">
-        <v>28.05</v>
+        <v>46.79</v>
       </c>
       <c r="O16" t="n">
-        <v>16039677820</v>
+        <v>2459061203000</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>8120</v>
+        <v>70000</v>
       </c>
       <c r="R16" t="n">
-        <v>-289000</v>
+        <v>-301000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>176000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>LG디스플레이의 성장성 및 목표가 하향에 대한 부정적 전망. 중국산 경쟁 심화 및 외인 매도 관련 내용 포함.</t>
+          <t>SK하이닉스 대비 상승률 저조에 대한 지적. 반도체 섹터 내 경쟁 및 투자 의견. 28만원 박스권 및 100만원 목표가 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['LG디스플레이', '중국산', '매각']</t>
+          <t>['반도체', 'SK하이닉스', '목표가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34550</v>
+        <v>8980</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.1</v>
+        <v>-0.36</v>
       </c>
       <c r="E17" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="G17" t="n">
-        <v>203</v>
+        <v>380</v>
       </c>
       <c r="H17" t="n">
-        <v>52.67</v>
+        <v>27.69</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,130 +1975,130 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>34100</v>
+        <v>8940</v>
       </c>
       <c r="K17" t="n">
-        <v>34450</v>
+        <v>8940</v>
       </c>
       <c r="L17" t="n">
-        <v>35325</v>
+        <v>9070</v>
       </c>
       <c r="M17" t="n">
-        <v>34050</v>
+        <v>8710</v>
       </c>
       <c r="N17" t="n">
-        <v>21.01</v>
+        <v>28.05</v>
       </c>
       <c r="O17" t="n">
-        <v>52833652650</v>
+        <v>20694091970</v>
       </c>
       <c r="P17" t="n">
-        <v>69500</v>
+        <v>17950</v>
       </c>
       <c r="Q17" t="n">
-        <v>30400</v>
+        <v>8120</v>
       </c>
       <c r="R17" t="n">
-        <v>-78000</v>
+        <v>-289000</v>
       </c>
       <c r="S17" t="n">
-        <v>61000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>한국전력의 주가 상승 기대감 및 미국 원전 협력 가능성 언급. 발전 5사 통합 및 선납매 관련 내용도 포함.</t>
+          <t>중국산 제품 경쟁 심화 및 주가 관리 무능력으로 인한 성장성 부재. 개인 투자자만 매수.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['한국전력', '원전', 'Smp']</t>
+          <t>['중국산', '주가관리', '성장성']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12030</v>
+        <v>20050</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-2.16</v>
+        <v>0.38</v>
       </c>
       <c r="E18" t="n">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="F18" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="G18" t="n">
-        <v>273</v>
+        <v>651</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>10.85</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>11990</v>
+        <v>19970</v>
       </c>
       <c r="K18" t="n">
-        <v>12440</v>
+        <v>20250</v>
       </c>
       <c r="L18" t="n">
-        <v>12800</v>
+        <v>21300</v>
       </c>
       <c r="M18" t="n">
-        <v>11920</v>
+        <v>19630</v>
       </c>
       <c r="N18" t="n">
-        <v>2.16</v>
+        <v>10.47</v>
       </c>
       <c r="O18" t="n">
-        <v>32362285865</v>
+        <v>224200159390</v>
       </c>
       <c r="P18" t="n">
-        <v>36200</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>8920</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>43000</v>
+        <v>-844000</v>
       </c>
       <c r="S18" t="n">
-        <v>-6000</v>
+        <v>45000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>국제유가 급등에 따른 수혜 기대감 및 중동 지역 지정학적 리스크 부각. 단기 트레이딩 관점에서의 접근.</t>
+          <t>나스닥 원전 관련주 급등 영향. 계약 체결 공시 확인. 3~4만원 목표가 제시 및 공매도 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적 리스크', '단기 트레이딩']</t>
+          <t>['원전', '계약체결', '공시']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,18 +2120,18 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20000</v>
+        <v>34150</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.38</v>
+        <v>0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>161</v>
+        <v>102</v>
       </c>
       <c r="F19" t="n">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="G19" t="n">
-        <v>568</v>
+        <v>230</v>
       </c>
       <c r="H19" t="n">
-        <v>10.85</v>
+        <v>52.61</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>19970</v>
+        <v>34100</v>
       </c>
       <c r="K19" t="n">
-        <v>20250</v>
+        <v>34450</v>
       </c>
       <c r="L19" t="n">
-        <v>21300</v>
+        <v>35325</v>
       </c>
       <c r="M19" t="n">
-        <v>19630</v>
+        <v>34050</v>
       </c>
       <c r="N19" t="n">
-        <v>10.47</v>
+        <v>21.01</v>
       </c>
       <c r="O19" t="n">
-        <v>192675664420</v>
+        <v>62256698025</v>
       </c>
       <c r="P19" t="n">
-        <v>40350</v>
+        <v>69500</v>
       </c>
       <c r="Q19" t="n">
-        <v>3320</v>
+        <v>30400</v>
       </c>
       <c r="R19" t="n">
-        <v>-844000</v>
+        <v>-78000</v>
       </c>
       <c r="S19" t="n">
-        <v>45000</v>
+        <v>61000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 원전 사업 참여 기대감 속 공시 내용 확인. 통정거래 및 단기매매 비판.</t>
+          <t>미국 원전 섹터 급등과 연계. 한국전력의 원전주 전환 및 25조 선납매 관련 내용. 45,000원 1차 목표가 및 우상향 전망.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '공시', '통정거래']</t>
+          <t>['원전', '선납매', '우상향']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,97 +2212,189 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10160</v>
+        <v>29000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.32</v>
+        <v>0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>78</v>
+        <v>424</v>
       </c>
       <c r="F20" t="n">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="G20" t="n">
-        <v>177</v>
+        <v>502</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.31</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>10440</v>
+        <v>29750</v>
       </c>
       <c r="K20" t="n">
-        <v>10180</v>
+        <v>31600</v>
       </c>
       <c r="L20" t="n">
-        <v>11340</v>
+        <v>34200</v>
       </c>
       <c r="M20" t="n">
-        <v>10100</v>
+        <v>28950</v>
       </c>
       <c r="N20" t="n">
-        <v>0.62</v>
+        <v>0.23</v>
       </c>
       <c r="O20" t="n">
-        <v>123389341610</v>
+        <v>260176220850</v>
       </c>
       <c r="P20" t="n">
-        <v>15960</v>
+        <v>39350</v>
       </c>
       <c r="Q20" t="n">
-        <v>3500</v>
+        <v>8200</v>
       </c>
       <c r="R20" t="n">
-        <v>-43000</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 바이오 종목 상승에 대한 기대감 속 현대약품 언급. 다만, 미증시 제약바이오 폭락 및 종목 내 감정적 표현이 다수.</t>
+          <t>상장 직후 하한가 우려 및 단기 급등 후 하락 가능성 제기. 혈압 측정 반지 관련 재료 언급. 기술적 분석 기반의 조정 구간 예측.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['상폐', '혈압측정', '기술적분석']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>현대약품</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10140</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-2.87%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E21" t="n">
+        <v>90</v>
+      </c>
+      <c r="F21" t="n">
+        <v>63</v>
+      </c>
+      <c r="G21" t="n">
+        <v>204</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>10440</v>
+      </c>
+      <c r="K21" t="n">
+        <v>10180</v>
+      </c>
+      <c r="L21" t="n">
+        <v>11340</v>
+      </c>
+      <c r="M21" t="n">
+        <v>10030</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O21" t="n">
+        <v>129869540460</v>
+      </c>
+      <c r="P21" t="n">
+        <v>15960</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3500</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-43000</v>
+      </c>
+      <c r="S21" t="n">
         <v>0</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>['미프진', '제약바이오', '신고가']</t>
-        </is>
-      </c>
-      <c r="X20" t="n">
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>미국 증시 제약/바이오 섹터와는 다른 흐름. 탈모 관련주로서 신고가 기대감 존재. 단기적 움직임에 대한 의견 분분.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['탈모주', '신고가', '제약바이오']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
         <v>7</v>
       </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>추적</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>004310</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="F2" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G2" t="n">
-        <v>1114</v>
+        <v>1306</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29510627295</v>
+        <v>29616866855</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미 FDA 2A상 승인 및 다락손라십 대비 우수한 임상 결과. 20,800원 전고점 돌파 및 5~10연상 기대감. 폐암, 난소암 등 다양한 암종에 대한 효능 언급.</t>
+          <t>미 FDA 2A상 승인 및 다락손라십 대비 우수한 약효에 대한 기대감. 글로벌 시장 진출 및 10연상까지 가능한 획기적인 신약 개발에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA', '임상결과', '암치료']</t>
+          <t>['FDA 2A상', '암세포 사멸', '다락손라십']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
@@ -702,7 +702,7 @@
         <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>37546974615</v>
+        <v>37705364175</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12440</v>
+        <v>12340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+24.03%</t>
+          <t>+23.03%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G4" t="n">
-        <v>201</v>
+        <v>279</v>
       </c>
       <c r="H4" t="n">
         <v>0.36</v>
@@ -794,7 +794,7 @@
         <v>0.44</v>
       </c>
       <c r="O4" t="n">
-        <v>132341196320</v>
+        <v>177479462045</v>
       </c>
       <c r="P4" t="n">
         <v>20850</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 증시 SMR 및 원전 관련주 폭등 영향. 12,000원 돌파 시 추가 상승 전망. 2연상 이상 기대감 및 글로벌 원전 터빈 시장 언급.</t>
+          <t>미국 SMR 및 가스터빈 발전소 관련 뉴스, 품절주·주포 움직임 주목.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '가스터빈']</t>
+          <t>['SMR', '가스터빈', '품절주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13800</v>
+        <v>13770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.85%</t>
+          <t>+16.60%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F5" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G5" t="n">
-        <v>1113</v>
+        <v>1184</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>413027345160</v>
+        <v>439506685865</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>체코, 미국 등 원전 관련 국가와의 협력 강화 및 하반기 주도주로서의 원전 로봇 부각. 사우디 수주 기대감.</t>
+          <t>체코·미국 원전 사업 및 사우디 등 해외 수주 기대감. 정부 정책 수혜.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '로봇', '수주']</t>
+          <t>['원전', '수주', '해외']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="F6" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G6" t="n">
-        <v>761</v>
+        <v>944</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>59776763780</v>
+        <v>66453785590</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>췌장암 치료제 '다락손라십' 및 뎅기열 치료제 개발 관련 긍정적 임상 결과 발표. 공매도와의 승부 예상.</t>
+          <t>뎅기열 및 췌장암 치료제 관련 임상 결과 발표 기대감과 페니트리움바이오와의 시너지에 대한 긍정적 전망. 공매도 세력에 대한 경계도 있으나, 긍정적 데이터 공개 시 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['췌장암', '뎅기열', '임상결과']</t>
+          <t>['뎅기열', '췌장암 치료제', '페니트리움바이오']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54200</v>
+        <v>54100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+10.05%</t>
+          <t>+9.85%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F7" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G7" t="n">
-        <v>434</v>
+        <v>477</v>
       </c>
       <c r="H7" t="n">
         <v>14.96</v>
@@ -1070,7 +1070,7 @@
         <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>146540580950</v>
+        <v>152740090550</v>
       </c>
       <c r="P7" t="n">
         <v>108900</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2분기 영업이익 적자 전환에도 불구하고 목표가 상향 조정 의견 존재. 외인 매도세 지속.</t>
+          <t>2분기 영업이익 적자 기록 및 목표가 상향 조정 기대감 혼재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '목표가', '외인매도']</t>
+          <t>['영업이익', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14830</v>
+        <v>14850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.25%</t>
+          <t>+8.39%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.39</v>
       </c>
       <c r="E8" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="F8" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G8" t="n">
-        <v>1122</v>
+        <v>1204</v>
       </c>
       <c r="H8" t="n">
         <v>1.55</v>
@@ -1162,7 +1162,7 @@
         <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>393707434040</v>
+        <v>407205990290</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>빛과전자 수급 흡수 및 단기 박스권 돌파로 인한 상승세. 2만 원 돌파 및 우상향 추세 전망.</t>
+          <t>빛과전자와의 시너지 기대감 속 거래대금 1위 기록. 단기 박스권 돌파.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['빛과전자', '박스권 돌파', '우상향']</t>
+          <t>['광통신', '거래대금', '박스권 돌파']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8130</v>
+        <v>3815</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>+4.81%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>2.74</v>
       </c>
       <c r="E9" t="n">
-        <v>93</v>
+        <v>200</v>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="G9" t="n">
-        <v>268</v>
+        <v>460</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81</v>
+        <v>3.19</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7680</v>
+        <v>3640</v>
       </c>
       <c r="K9" t="n">
-        <v>7780</v>
+        <v>3750</v>
       </c>
       <c r="L9" t="n">
-        <v>9000</v>
+        <v>4460</v>
       </c>
       <c r="M9" t="n">
-        <v>7750</v>
+        <v>3680</v>
       </c>
       <c r="N9" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="O9" t="n">
-        <v>105728927760</v>
+        <v>265588595766</v>
       </c>
       <c r="P9" t="n">
-        <v>10300</v>
+        <v>8100</v>
       </c>
       <c r="Q9" t="n">
-        <v>952</v>
+        <v>592</v>
       </c>
       <c r="R9" t="n">
-        <v>-206000</v>
+        <v>-348000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>레미콘 파업 시작으로 인한 대장주로서의 상승 모멘텀 확보. 강동구 건설 호재와 함께 상한가 기록 기대.</t>
+          <t>미국 광통신 시장 급등에 따른 기대감, 글로벌 회사 공급 뉴스.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['레미콘', '대장주', '상한가']</t>
+          <t>['광통신', '글로벌 공급']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3850</v>
+        <v>8030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.77%</t>
+          <t>+4.56%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.74</v>
+        <v>1.4</v>
       </c>
       <c r="E10" t="n">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="F10" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="G10" t="n">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="H10" t="n">
-        <v>3.19</v>
+        <v>1.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3640</v>
+        <v>7680</v>
       </c>
       <c r="K10" t="n">
-        <v>3750</v>
+        <v>7780</v>
       </c>
       <c r="L10" t="n">
-        <v>4460</v>
+        <v>9000</v>
       </c>
       <c r="M10" t="n">
-        <v>3680</v>
+        <v>7750</v>
       </c>
       <c r="N10" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="O10" t="n">
-        <v>256416681658</v>
+        <v>110178001370</v>
       </c>
       <c r="P10" t="n">
-        <v>8100</v>
+        <v>10300</v>
       </c>
       <c r="Q10" t="n">
-        <v>592</v>
+        <v>952</v>
       </c>
       <c r="R10" t="n">
-        <v>-348000</v>
+        <v>-206000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 급등과 연관. 재료의 우수성을 근거로 6천원 이상 목표가 제시. 투자경고 종목 지정 가능성 언급.</t>
+          <t>레미콘 파업 및 긍정적인 시장 흐름에 따른 상한가 기대감. 하지만 구체적인 근거는 부족.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '재료', '투자경고']</t>
+          <t>['레미콘 파업', '상한가 기대', '지지선']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6730</v>
+        <v>6720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.67%</t>
+          <t>+4.51%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.31</v>
       </c>
       <c r="E11" t="n">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="F11" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="G11" t="n">
-        <v>368</v>
+        <v>451</v>
       </c>
       <c r="H11" t="n">
         <v>16.71</v>
@@ -1438,7 +1438,7 @@
         <v>16.4</v>
       </c>
       <c r="O11" t="n">
-        <v>91075124055</v>
+        <v>94723395380</v>
       </c>
       <c r="P11" t="n">
         <v>13000</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>사명 변경 후 주가 하락 및 공매도 관련 우려. 배당 지급 예정에도 불구하고 주가 부진 지속. 일부 투자자는 단기 급등 전망 제시.</t>
+          <t>배당금 지급에도 불구하고 주가 부진, 공매도 관련 언급과 함께 투자자들의 불확실성 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '배당', '주주환원']</t>
+          <t>['배당', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1859000</v>
+        <v>2005</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.68%</t>
+          <t>+4.32%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>798</v>
+        <v>108</v>
       </c>
       <c r="F12" t="n">
-        <v>442</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>2240</v>
+        <v>246</v>
       </c>
       <c r="H12" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1793000</v>
+        <v>1922</v>
       </c>
       <c r="K12" t="n">
-        <v>1795000</v>
+        <v>1920</v>
       </c>
       <c r="L12" t="n">
-        <v>1883000</v>
+        <v>2165</v>
       </c>
       <c r="M12" t="n">
-        <v>1795000</v>
+        <v>1862</v>
       </c>
       <c r="N12" t="n">
-        <v>50.63</v>
+        <v>0.61</v>
       </c>
       <c r="O12" t="n">
-        <v>3779674340500</v>
+        <v>16308568259</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q12" t="n">
-        <v>277000</v>
+        <v>910</v>
       </c>
       <c r="R12" t="n">
-        <v>53000</v>
+        <v>70000</v>
       </c>
       <c r="S12" t="n">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수세 유입. 190, 200만원 목표가 제시 및 긍정적 수급 전망. 리밸런싱 완료 및 매물대 소화 언급.</t>
+          <t>호남반도체 클러스터 대장으로서의 역할 부각 및 텐버거 기대감. 대주주 매도 공시 등 부정적 요인도 있으나, 물량 소화 후 상승 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['외인매수', '목표가', '수급']</t>
+          <t>['호남반도체', '텐버거', '대주주 매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1988</v>
+        <v>30750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.43%</t>
+          <t>+3.36%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E13" t="n">
-        <v>101</v>
+        <v>594</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>227</v>
       </c>
       <c r="G13" t="n">
-        <v>230</v>
+        <v>789</v>
       </c>
       <c r="H13" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1922</v>
+        <v>29750</v>
       </c>
       <c r="K13" t="n">
-        <v>1920</v>
+        <v>31600</v>
       </c>
       <c r="L13" t="n">
-        <v>2165</v>
+        <v>34200</v>
       </c>
       <c r="M13" t="n">
-        <v>1862</v>
+        <v>28300</v>
       </c>
       <c r="N13" t="n">
-        <v>0.61</v>
+        <v>0.23</v>
       </c>
       <c r="O13" t="n">
-        <v>15708183766</v>
+        <v>408742722825</v>
       </c>
       <c r="P13" t="n">
-        <v>2930</v>
+        <v>39350</v>
       </c>
       <c r="Q13" t="n">
-        <v>910</v>
+        <v>8200</v>
       </c>
       <c r="R13" t="n">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>호남반도체 클러스터 대장주로서의 기대감과 텐버거 가능성 언급. 대주주 매도 공시를 핑계로 한 하락 가능성도 있으나, 주포 세력의 시세 조작 및 물량 넘기기 수법에 대한 경계와 함께 반등을 기대하는 분위기.</t>
+          <t>세계 최초 혈압 반지에 대한 유럽 진출 뉴스 및 ESC 관련 속보로 인한 긍정적 전망. 다만, 상장폐지 우려 및 단기 급등에 대한 경계감도 혼재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '텐버거', '주포']</t>
+          <t>['혈압 반지', '유럽 진출', 'ESC']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>92100</v>
+        <v>1847000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+2.91%</t>
+          <t>+3.01%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>289</v>
+        <v>798</v>
       </c>
       <c r="F14" t="n">
-        <v>188</v>
+        <v>459</v>
       </c>
       <c r="G14" t="n">
-        <v>1539</v>
+        <v>2146</v>
       </c>
       <c r="H14" t="n">
-        <v>23.61</v>
+        <v>50.66</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>89500</v>
+        <v>1793000</v>
       </c>
       <c r="K14" t="n">
-        <v>92000</v>
+        <v>1795000</v>
       </c>
       <c r="L14" t="n">
-        <v>94400</v>
+        <v>1883000</v>
       </c>
       <c r="M14" t="n">
-        <v>91300</v>
+        <v>1795000</v>
       </c>
       <c r="N14" t="n">
-        <v>23.63</v>
+        <v>50.63</v>
       </c>
       <c r="O14" t="n">
-        <v>244690318550</v>
+        <v>4351450306000</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>277000</v>
       </c>
       <c r="R14" t="n">
-        <v>104000</v>
+        <v>53000</v>
       </c>
       <c r="S14" t="n">
-        <v>26000</v>
+        <v>37000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 원전 사업 참여 및 SMR 기술 관련 기대감. 프랑스와의 원자력 협력 뉴스 기반 상승 전망.</t>
+          <t>외국인 및 기관 매수세 유입에 따른 상승 추세 기대감. 자사주 매입.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '프랑스 협력']</t>
+          <t>['외국인', '기관', '자사주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12270</v>
+        <v>91900</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.34%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-2.16</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>149</v>
+        <v>309</v>
       </c>
       <c r="F15" t="n">
-        <v>91</v>
+        <v>197</v>
       </c>
       <c r="G15" t="n">
-        <v>286</v>
+        <v>1615</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>23.61</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>11990</v>
+        <v>89500</v>
       </c>
       <c r="K15" t="n">
-        <v>12440</v>
+        <v>92000</v>
       </c>
       <c r="L15" t="n">
-        <v>12800</v>
+        <v>94400</v>
       </c>
       <c r="M15" t="n">
-        <v>11920</v>
+        <v>91300</v>
       </c>
       <c r="N15" t="n">
-        <v>2.16</v>
+        <v>23.63</v>
       </c>
       <c r="O15" t="n">
-        <v>37276944785</v>
+        <v>266093131300</v>
       </c>
       <c r="P15" t="n">
-        <v>36200</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>8920</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>43000</v>
+        <v>104000</v>
       </c>
       <c r="S15" t="n">
-        <v>-6000</v>
+        <v>26000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>국제유가 급등세 지속 및 100달러 돌파 임박. 이란 유조선 공격 등 지정학적 리스크 부각. 단기 트레이딩 관점 유지.</t>
+          <t>미국 원전 사업 참여 및 SMR 기술 관련 기대감. 프랑스와의 원자력 협력 뉴스 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적리스크', '단기트레이딩']</t>
+          <t>['원전', 'SMR', '프랑스 협력']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>271750</v>
+        <v>12250</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.06</v>
+        <v>-2.16</v>
       </c>
       <c r="E16" t="n">
-        <v>787</v>
+        <v>164</v>
       </c>
       <c r="F16" t="n">
-        <v>463</v>
+        <v>95</v>
       </c>
       <c r="G16" t="n">
-        <v>1511</v>
+        <v>315</v>
       </c>
       <c r="H16" t="n">
-        <v>46.85</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>269500</v>
+        <v>11990</v>
       </c>
       <c r="K16" t="n">
-        <v>269500</v>
+        <v>12440</v>
       </c>
       <c r="L16" t="n">
-        <v>275000</v>
+        <v>12800</v>
       </c>
       <c r="M16" t="n">
-        <v>268500</v>
+        <v>11920</v>
       </c>
       <c r="N16" t="n">
-        <v>46.79</v>
+        <v>2.16</v>
       </c>
       <c r="O16" t="n">
-        <v>2459061203000</v>
+        <v>40878536410</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>36200</v>
       </c>
       <c r="Q16" t="n">
-        <v>70000</v>
+        <v>8920</v>
       </c>
       <c r="R16" t="n">
-        <v>-301000</v>
+        <v>43000</v>
       </c>
       <c r="S16" t="n">
-        <v>176000</v>
+        <v>-6000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>SK하이닉스 대비 상승률 저조에 대한 지적. 반도체 섹터 내 경쟁 및 투자 의견. 28만원 박스권 및 100만원 목표가 언급.</t>
+          <t>국제유가 급등에 따른 기대감 고조. 지정학적 리스크 부각되며 유가 추가 상승 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['반도체', 'SK하이닉스', '목표가']</t>
+          <t>['국제유가', '지정학적 리스크']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8980</v>
+        <v>8990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.36</v>
       </c>
       <c r="E17" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F17" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G17" t="n">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="H17" t="n">
         <v>27.69</v>
@@ -1990,7 +1990,7 @@
         <v>28.05</v>
       </c>
       <c r="O17" t="n">
-        <v>20694091970</v>
+        <v>25159938545</v>
       </c>
       <c r="P17" t="n">
         <v>17950</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>중국산 제품 경쟁 심화 및 주가 관리 무능력으로 인한 성장성 부재. 개인 투자자만 매수.</t>
+          <t>AI 문명 관련 기대감에도 불구하고 중국산 경쟁 심화 및 실적 부진으로 인한 주가 하락세 지속. 유상증자 및 시가총액 하락에 대한 부정적 전망 우세.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['중국산', '주가관리', '성장성']</t>
+          <t>['AI', '중국산', '유상증자']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20050</v>
+        <v>269750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.38</v>
+        <v>0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>188</v>
+        <v>793</v>
       </c>
       <c r="F18" t="n">
-        <v>108</v>
+        <v>471</v>
       </c>
       <c r="G18" t="n">
-        <v>651</v>
+        <v>1532</v>
       </c>
       <c r="H18" t="n">
-        <v>10.85</v>
+        <v>46.85</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19970</v>
+        <v>269500</v>
       </c>
       <c r="K18" t="n">
-        <v>20250</v>
+        <v>269500</v>
       </c>
       <c r="L18" t="n">
-        <v>21300</v>
+        <v>275000</v>
       </c>
       <c r="M18" t="n">
-        <v>19630</v>
+        <v>268500</v>
       </c>
       <c r="N18" t="n">
-        <v>10.47</v>
+        <v>46.79</v>
       </c>
       <c r="O18" t="n">
-        <v>224200159390</v>
+        <v>2844409840000</v>
       </c>
       <c r="P18" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q18" t="n">
-        <v>3320</v>
+        <v>70000</v>
       </c>
       <c r="R18" t="n">
-        <v>-844000</v>
+        <v>-301000</v>
       </c>
       <c r="S18" t="n">
-        <v>45000</v>
+        <v>176000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>나스닥 원전 관련주 급등 영향. 계약 체결 공시 확인. 3~4만원 목표가 제시 및 공매도 세력에 대한 언급.</t>
+          <t>SK하이닉스 등 경쟁사 대비 부진한 흐름에 대한 아쉬움 표출.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', '계약체결', '공시']</t>
+          <t>['반도체', '경쟁사']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34150</v>
+        <v>19850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="E19" t="n">
-        <v>102</v>
+        <v>205</v>
       </c>
       <c r="F19" t="n">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="G19" t="n">
-        <v>230</v>
+        <v>698</v>
       </c>
       <c r="H19" t="n">
-        <v>52.61</v>
+        <v>10.85</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>34100</v>
+        <v>19970</v>
       </c>
       <c r="K19" t="n">
-        <v>34450</v>
+        <v>20250</v>
       </c>
       <c r="L19" t="n">
-        <v>35325</v>
+        <v>21300</v>
       </c>
       <c r="M19" t="n">
-        <v>34050</v>
+        <v>19630</v>
       </c>
       <c r="N19" t="n">
-        <v>21.01</v>
+        <v>10.47</v>
       </c>
       <c r="O19" t="n">
-        <v>62256698025</v>
+        <v>236289758345</v>
       </c>
       <c r="P19" t="n">
-        <v>69500</v>
+        <v>40350</v>
       </c>
       <c r="Q19" t="n">
-        <v>30400</v>
+        <v>3320</v>
       </c>
       <c r="R19" t="n">
-        <v>-78000</v>
+        <v>-844000</v>
       </c>
       <c r="S19" t="n">
-        <v>61000</v>
+        <v>45000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 원전 섹터 급등과 연계. 한국전력의 원전주 전환 및 25조 선납매 관련 내용. 45,000원 1차 목표가 및 우상향 전망.</t>
+          <t>미국 원전 사업 참여 기대감 속 계약 체결 공시 확인.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '선납매', '우상향']</t>
+          <t>['원전', '계약 체결']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29000</v>
+        <v>33850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>424</v>
+        <v>110</v>
       </c>
       <c r="F20" t="n">
-        <v>167</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>502</v>
+        <v>260</v>
       </c>
       <c r="H20" t="n">
-        <v>0.31</v>
+        <v>52.59</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>29750</v>
+        <v>34100</v>
       </c>
       <c r="K20" t="n">
-        <v>31600</v>
+        <v>34450</v>
       </c>
       <c r="L20" t="n">
-        <v>34200</v>
+        <v>35325</v>
       </c>
       <c r="M20" t="n">
-        <v>28950</v>
+        <v>33800</v>
       </c>
       <c r="N20" t="n">
-        <v>0.23</v>
+        <v>21.01</v>
       </c>
       <c r="O20" t="n">
-        <v>260176220850</v>
+        <v>67924412150</v>
       </c>
       <c r="P20" t="n">
-        <v>39350</v>
+        <v>69500</v>
       </c>
       <c r="Q20" t="n">
-        <v>8200</v>
+        <v>30400</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>-78000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>61000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>상장 직후 하한가 우려 및 단기 급등 후 하락 가능성 제기. 혈압 측정 반지 관련 재료 언급. 기술적 분석 기반의 조정 구간 예측.</t>
+          <t>미국 원전 협력 강화 및 차세대 원전 사업 관련 긍정적 전망. 전기료 인상 및 발전 5사 통합 논의도 주가에 영향을 미칠 가능성. 다만, 공매도 및 정부 기업의 한계성에 대한 우려도 존재.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['상폐', '혈압측정', '기술적분석']</t>
+          <t>['원전 협력', '전기료 인상', '발전 5사 통합']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10140</v>
+        <v>10230</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.32</v>
       </c>
       <c r="E21" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F21" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G21" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H21" t="n">
         <v>0.9399999999999999</v>
@@ -2352,13 +2352,13 @@
         <v>11340</v>
       </c>
       <c r="M21" t="n">
-        <v>10030</v>
+        <v>9980</v>
       </c>
       <c r="N21" t="n">
         <v>0.62</v>
       </c>
       <c r="O21" t="n">
-        <v>129869540460</v>
+        <v>141662149515</v>
       </c>
       <c r="P21" t="n">
         <v>15960</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 증시 제약/바이오 섹터와는 다른 흐름. 탈모 관련주로서 신고가 기대감 존재. 단기적 움직임에 대한 의견 분분.</t>
+          <t>미국 제약바이오 시장 혼조세 속 탈모주 관련 기대감.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['탈모주', '신고가', '제약바이오']</t>
+          <t>['탈모주', '신고가']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2397,6 +2397,98 @@
       <c r="Z21" t="inlineStr">
         <is>
           <t>004310</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>JW신약</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3765</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-3.21%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E22" t="n">
+        <v>90</v>
+      </c>
+      <c r="F22" t="n">
+        <v>49</v>
+      </c>
+      <c r="G22" t="n">
+        <v>178</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>3890</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3890</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4115</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3700</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O22" t="n">
+        <v>63311995606</v>
+      </c>
+      <c r="P22" t="n">
+        <v>4335</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1246</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-505000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>탈모 관련 기대감과 조정·하락 우려 공존. 재료 부족 논란.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['탈모', '조정', '재료']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>067290</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G2" t="n">
-        <v>1306</v>
+        <v>1346</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29616866855</v>
+        <v>29638325495</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -676,7 +676,7 @@
         <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
@@ -702,7 +702,7 @@
         <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>37705364175</v>
+        <v>37761774195</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -711,7 +711,7 @@
         <v>1206</v>
       </c>
       <c r="R3" t="n">
-        <v>29000</v>
+        <v>34000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12340</v>
+        <v>2640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+23.03%</t>
+          <t>+22.22%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.08</v>
+        <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>279</v>
+        <v>147</v>
       </c>
       <c r="H4" t="n">
-        <v>0.36</v>
+        <v>5.26</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>10030</v>
+        <v>2160</v>
       </c>
       <c r="K4" t="n">
-        <v>10270</v>
+        <v>2200</v>
       </c>
       <c r="L4" t="n">
-        <v>12790</v>
+        <v>2670</v>
       </c>
       <c r="M4" t="n">
-        <v>10040</v>
+        <v>2200</v>
       </c>
       <c r="N4" t="n">
-        <v>0.44</v>
+        <v>5.49</v>
       </c>
       <c r="O4" t="n">
-        <v>177479462045</v>
+        <v>27353186547</v>
       </c>
       <c r="P4" t="n">
-        <v>20850</v>
+        <v>2670</v>
       </c>
       <c r="Q4" t="n">
-        <v>4020</v>
+        <v>1418</v>
       </c>
       <c r="R4" t="n">
-        <v>25000</v>
+        <v>-166000</v>
       </c>
       <c r="S4" t="n">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 SMR 및 가스터빈 발전소 관련 뉴스, 품절주·주포 움직임 주목.</t>
+          <t>경영권 분쟁 및 신규 대주주 관련 긍정적 전망. 단기 급등 기대감 및 기타법인 매수세 유입 관찰. 과열 우려 및 매도량 급증 주의.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['SMR', '가스터빈', '품절주']</t>
+          <t>['경영권분쟁', '기타법인', '단기과열']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13770</v>
+        <v>12210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.60%</t>
+          <t>+21.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.22</v>
+        <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="F5" t="n">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="G5" t="n">
-        <v>1184</v>
+        <v>312</v>
       </c>
       <c r="H5" t="n">
-        <v>5.64</v>
+        <v>0.36</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11810</v>
+        <v>10030</v>
       </c>
       <c r="K5" t="n">
-        <v>12050</v>
+        <v>10270</v>
       </c>
       <c r="L5" t="n">
-        <v>14550</v>
+        <v>12790</v>
       </c>
       <c r="M5" t="n">
-        <v>11950</v>
+        <v>10040</v>
       </c>
       <c r="N5" t="n">
-        <v>5.42</v>
+        <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>439506685865</v>
+        <v>184430443710</v>
       </c>
       <c r="P5" t="n">
-        <v>30200</v>
+        <v>20850</v>
       </c>
       <c r="Q5" t="n">
-        <v>3540</v>
+        <v>4020</v>
       </c>
       <c r="R5" t="n">
-        <v>515000</v>
+        <v>4000</v>
       </c>
       <c r="S5" t="n">
-        <v>18000</v>
+        <v>19000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>체코·미국 원전 사업 및 사우디 등 해외 수주 기대감. 정부 정책 수혜.</t>
+          <t>가스터빈 및 원전 관련 사업 부각. 국내 1위 업체로 미국 시장 진출 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '수주', '해외']</t>
+          <t>['가스터빈', '원전', '미국 시장']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>현대바이오</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7210</v>
+        <v>13870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+15.18%</t>
+          <t>+17.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="E6" t="n">
-        <v>181</v>
+        <v>248</v>
       </c>
       <c r="F6" t="n">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="G6" t="n">
-        <v>944</v>
+        <v>1252</v>
       </c>
       <c r="H6" t="n">
-        <v>7.4</v>
+        <v>5.64</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6260</v>
+        <v>11810</v>
       </c>
       <c r="K6" t="n">
-        <v>6200</v>
+        <v>12050</v>
       </c>
       <c r="L6" t="n">
-        <v>7730</v>
+        <v>14550</v>
       </c>
       <c r="M6" t="n">
-        <v>6140</v>
+        <v>11950</v>
       </c>
       <c r="N6" t="n">
-        <v>7.35</v>
+        <v>5.42</v>
       </c>
       <c r="O6" t="n">
-        <v>66453785590</v>
+        <v>446002878090</v>
       </c>
       <c r="P6" t="n">
-        <v>21500</v>
+        <v>30200</v>
       </c>
       <c r="Q6" t="n">
-        <v>4565</v>
+        <v>3540</v>
       </c>
       <c r="R6" t="n">
-        <v>-376000</v>
+        <v>294000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>73000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뎅기열 및 췌장암 치료제 관련 임상 결과 발표 기대감과 페니트리움바이오와의 시너지에 대한 긍정적 전망. 공매도 세력에 대한 경계도 있으나, 긍정적 데이터 공개 시 주가 상승 기대.</t>
+          <t>하반기 주도주로서 원전 및 로봇 섹터 전망. 미국 및 사우디 등 해외 수주 기대감 반영. 13750원 및 22300원 등 단기 목표가 제시. 정부 정책 및 외국인 자본 유입 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['뎅기열', '췌장암 치료제', '페니트리움바이오']</t>
+          <t>['원전', '로봇', '해외수주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>048410</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>현대바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54100</v>
+        <v>7150</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>+14.22%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="F7" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G7" t="n">
-        <v>477</v>
+        <v>1035</v>
       </c>
       <c r="H7" t="n">
-        <v>14.96</v>
+        <v>7.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>49250</v>
+        <v>6260</v>
       </c>
       <c r="K7" t="n">
-        <v>53500</v>
+        <v>6200</v>
       </c>
       <c r="L7" t="n">
-        <v>59000</v>
+        <v>7730</v>
       </c>
       <c r="M7" t="n">
-        <v>51600</v>
+        <v>6140</v>
       </c>
       <c r="N7" t="n">
-        <v>14.93</v>
+        <v>7.35</v>
       </c>
       <c r="O7" t="n">
-        <v>152740090550</v>
+        <v>67325430180</v>
       </c>
       <c r="P7" t="n">
-        <v>108900</v>
+        <v>21500</v>
       </c>
       <c r="Q7" t="n">
-        <v>18230</v>
+        <v>4565</v>
       </c>
       <c r="R7" t="n">
-        <v>-225000</v>
+        <v>-509000</v>
       </c>
       <c r="S7" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2분기 영업이익 적자 기록 및 목표가 상향 조정 기대감 혼재.</t>
+          <t>췌장암 치료제 관련 임상 결과 발표 기대. 공매도와의 경쟁 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '목표가']</t>
+          <t>['췌장암 치료제', '임상 결과', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>048410</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14850</v>
+        <v>54200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.39%</t>
+          <t>+10.05%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.39</v>
+        <v>0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>233</v>
+        <v>144</v>
       </c>
       <c r="F8" t="n">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="G8" t="n">
-        <v>1204</v>
+        <v>494</v>
       </c>
       <c r="H8" t="n">
-        <v>1.55</v>
+        <v>14.96</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13700</v>
+        <v>49250</v>
       </c>
       <c r="K8" t="n">
-        <v>14260</v>
+        <v>53500</v>
       </c>
       <c r="L8" t="n">
-        <v>15860</v>
+        <v>59000</v>
       </c>
       <c r="M8" t="n">
-        <v>14210</v>
+        <v>51600</v>
       </c>
       <c r="N8" t="n">
-        <v>1.94</v>
+        <v>14.93</v>
       </c>
       <c r="O8" t="n">
-        <v>407205990290</v>
+        <v>154490394300</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>108900</v>
       </c>
       <c r="Q8" t="n">
-        <v>1252</v>
+        <v>18230</v>
       </c>
       <c r="R8" t="n">
-        <v>820000</v>
+        <v>-220000</v>
       </c>
       <c r="S8" t="n">
-        <v>20000</v>
+        <v>135000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>빛과전자와의 시너지 기대감 속 거래대금 1위 기록. 단기 박스권 돌파.</t>
+          <t>두산퓨얼셀 수주 관련 긍정적 언급 및 목표가 상향 주장. 2분기 영업이익 적자에도 불구하고 향후 매출 성장성 기대. 기관 연기금 유입 및 공매도 세력 관련 논쟁.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '거래대금', '박스권 돌파']</t>
+          <t>['수주', '목표가', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3815</v>
+        <v>14830</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.81%</t>
+          <t>+8.25%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.74</v>
+        <v>-0.39</v>
       </c>
       <c r="E9" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="F9" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="G9" t="n">
-        <v>460</v>
+        <v>1252</v>
       </c>
       <c r="H9" t="n">
-        <v>3.19</v>
+        <v>1.55</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3640</v>
+        <v>13700</v>
       </c>
       <c r="K9" t="n">
-        <v>3750</v>
+        <v>14260</v>
       </c>
       <c r="L9" t="n">
-        <v>4460</v>
+        <v>15860</v>
       </c>
       <c r="M9" t="n">
-        <v>3680</v>
+        <v>14210</v>
       </c>
       <c r="N9" t="n">
-        <v>0.45</v>
+        <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>265588595766</v>
+        <v>411682688180</v>
       </c>
       <c r="P9" t="n">
-        <v>8100</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>592</v>
+        <v>1252</v>
       </c>
       <c r="R9" t="n">
-        <v>-348000</v>
+        <v>488000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 광통신 시장 급등에 따른 기대감, 글로벌 회사 공급 뉴스.</t>
+          <t>단기 박스권 돌파 및 상승 추세 전망. 차트 분석 기반 가격 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '글로벌 공급']</t>
+          <t>['차트 분석', '상승 추세', '단기 박스권']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8030</v>
+        <v>6780</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.56%</t>
+          <t>+5.44%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.4</v>
+        <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>104</v>
+        <v>327</v>
       </c>
       <c r="F10" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="G10" t="n">
-        <v>300</v>
+        <v>462</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81</v>
+        <v>16.71</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7680</v>
+        <v>6430</v>
       </c>
       <c r="K10" t="n">
-        <v>7780</v>
+        <v>6400</v>
       </c>
       <c r="L10" t="n">
-        <v>9000</v>
+        <v>7470</v>
       </c>
       <c r="M10" t="n">
-        <v>7750</v>
+        <v>6250</v>
       </c>
       <c r="N10" t="n">
-        <v>0.41</v>
+        <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>110178001370</v>
+        <v>95982087090</v>
       </c>
       <c r="P10" t="n">
-        <v>10300</v>
+        <v>13000</v>
       </c>
       <c r="Q10" t="n">
-        <v>952</v>
+        <v>6030</v>
       </c>
       <c r="R10" t="n">
-        <v>-206000</v>
+        <v>-684000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>레미콘 파업 및 긍정적인 시장 흐름에 따른 상한가 기대감. 하지만 구체적인 근거는 부족.</t>
+          <t>배당 관련 언급 있으나 주가 하락 우려 및 공매도 관련 부정적 전망 혼재. 외인 순매수 전환 기대감도 일부 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['레미콘 파업', '상한가 기대', '지지선']</t>
+          <t>['배당', '공매도', '외인']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6720</v>
+        <v>3795</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.51%</t>
+          <t>+4.26%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.31</v>
+        <v>2.74</v>
       </c>
       <c r="E11" t="n">
-        <v>317</v>
+        <v>209</v>
       </c>
       <c r="F11" t="n">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="G11" t="n">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="H11" t="n">
-        <v>16.71</v>
+        <v>3.19</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6430</v>
+        <v>3640</v>
       </c>
       <c r="K11" t="n">
-        <v>6400</v>
+        <v>3750</v>
       </c>
       <c r="L11" t="n">
-        <v>7470</v>
+        <v>4460</v>
       </c>
       <c r="M11" t="n">
-        <v>6250</v>
+        <v>3680</v>
       </c>
       <c r="N11" t="n">
-        <v>16.4</v>
+        <v>0.45</v>
       </c>
       <c r="O11" t="n">
-        <v>94723395380</v>
+        <v>267541700273</v>
       </c>
       <c r="P11" t="n">
-        <v>13000</v>
+        <v>8100</v>
       </c>
       <c r="Q11" t="n">
-        <v>6030</v>
+        <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>-554000</v>
+        <v>-816000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>배당금 지급에도 불구하고 주가 부진, 공매도 관련 언급과 함께 투자자들의 불확실성 혼재.</t>
+          <t>미국 광통신 섹터 급등 및 관련 수혜 기대. 재료 우수성 및 거래량 풍부함 언급. 6천원 이상 목표가 설정 및 국책사업 선정 가능성 제기. 투기과열 지정 우려도 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['배당', '공매도']</t>
+          <t>['광통신', '재료', '국책사업']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2005</v>
+        <v>30900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>+3.87%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>108</v>
+        <v>615</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>231</v>
       </c>
       <c r="G12" t="n">
-        <v>246</v>
+        <v>821</v>
       </c>
       <c r="H12" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1922</v>
+        <v>29750</v>
       </c>
       <c r="K12" t="n">
-        <v>1920</v>
+        <v>31600</v>
       </c>
       <c r="L12" t="n">
-        <v>2165</v>
+        <v>34200</v>
       </c>
       <c r="M12" t="n">
-        <v>1862</v>
+        <v>28300</v>
       </c>
       <c r="N12" t="n">
-        <v>0.61</v>
+        <v>0.23</v>
       </c>
       <c r="O12" t="n">
-        <v>16308568259</v>
+        <v>438695175550</v>
       </c>
       <c r="P12" t="n">
-        <v>2930</v>
+        <v>39350</v>
       </c>
       <c r="Q12" t="n">
-        <v>910</v>
+        <v>8200</v>
       </c>
       <c r="R12" t="n">
-        <v>70000</v>
+        <v>-1000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>호남반도체 클러스터 대장으로서의 역할 부각 및 텐버거 기대감. 대주주 매도 공시 등 부정적 요인도 있으나, 물량 소화 후 상승 전망.</t>
+          <t>혈압계 관련 기술 유럽 진출 뉴스. 상장 초기 급등 후 조정 국면.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['호남반도체', '텐버거', '대주주 매도']</t>
+          <t>['혈압계', '유럽 진출', '기술']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30750</v>
+        <v>1995</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>594</v>
+        <v>106</v>
       </c>
       <c r="F13" t="n">
-        <v>227</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>789</v>
+        <v>251</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31</v>
+        <v>0.51</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>29750</v>
+        <v>1922</v>
       </c>
       <c r="K13" t="n">
-        <v>31600</v>
+        <v>1920</v>
       </c>
       <c r="L13" t="n">
-        <v>34200</v>
+        <v>2165</v>
       </c>
       <c r="M13" t="n">
-        <v>28300</v>
+        <v>1862</v>
       </c>
       <c r="N13" t="n">
-        <v>0.23</v>
+        <v>0.61</v>
       </c>
       <c r="O13" t="n">
-        <v>408742722825</v>
+        <v>16439677578</v>
       </c>
       <c r="P13" t="n">
-        <v>39350</v>
+        <v>2930</v>
       </c>
       <c r="Q13" t="n">
-        <v>8200</v>
+        <v>910</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>106000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>세계 최초 혈압 반지에 대한 유럽 진출 뉴스 및 ESC 관련 속보로 인한 긍정적 전망. 다만, 상장폐지 우려 및 단기 급등에 대한 경계감도 혼재.</t>
+          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['혈압 반지', '유럽 진출', 'ESC']</t>
+          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1847000</v>
+        <v>7950</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.01%</t>
+          <t>+3.52%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.03</v>
+        <v>1.4</v>
       </c>
       <c r="E14" t="n">
-        <v>798</v>
+        <v>105</v>
       </c>
       <c r="F14" t="n">
-        <v>459</v>
+        <v>71</v>
       </c>
       <c r="G14" t="n">
-        <v>2146</v>
+        <v>311</v>
       </c>
       <c r="H14" t="n">
-        <v>50.66</v>
+        <v>1.81</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1793000</v>
+        <v>7680</v>
       </c>
       <c r="K14" t="n">
-        <v>1795000</v>
+        <v>7780</v>
       </c>
       <c r="L14" t="n">
-        <v>1883000</v>
+        <v>9000</v>
       </c>
       <c r="M14" t="n">
-        <v>1795000</v>
+        <v>7750</v>
       </c>
       <c r="N14" t="n">
-        <v>50.63</v>
+        <v>0.41</v>
       </c>
       <c r="O14" t="n">
-        <v>4351450306000</v>
+        <v>111498719895</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>10300</v>
       </c>
       <c r="Q14" t="n">
-        <v>277000</v>
+        <v>952</v>
       </c>
       <c r="R14" t="n">
-        <v>53000</v>
+        <v>-210000</v>
       </c>
       <c r="S14" t="n">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수세 유입에 따른 상승 추세 기대감. 자사주 매입.</t>
+          <t>레미콘 파업 및 긍정적인 시장 흐름에 따른 상한가 기대감. 하지만 구체적인 근거는 부족.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외국인', '기관', '자사주']</t>
+          <t>['레미콘 파업', '상한가 기대', '지지선']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>91900</v>
+        <v>1852000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+3.29%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>309</v>
+        <v>795</v>
       </c>
       <c r="F15" t="n">
-        <v>197</v>
+        <v>458</v>
       </c>
       <c r="G15" t="n">
-        <v>1615</v>
+        <v>1978</v>
       </c>
       <c r="H15" t="n">
-        <v>23.61</v>
+        <v>50.66</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>89500</v>
+        <v>1793000</v>
       </c>
       <c r="K15" t="n">
-        <v>92000</v>
+        <v>1795000</v>
       </c>
       <c r="L15" t="n">
-        <v>94400</v>
+        <v>1883000</v>
       </c>
       <c r="M15" t="n">
-        <v>91300</v>
+        <v>1795000</v>
       </c>
       <c r="N15" t="n">
-        <v>23.63</v>
+        <v>50.63</v>
       </c>
       <c r="O15" t="n">
-        <v>266093131300</v>
+        <v>4628215964000</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>277000</v>
       </c>
       <c r="R15" t="n">
-        <v>104000</v>
+        <v>157000</v>
       </c>
       <c r="S15" t="n">
-        <v>26000</v>
+        <v>153000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 원전 사업 참여 및 SMR 기술 관련 기대감. 프랑스와의 원자력 협력 뉴스 기반 상승 전망.</t>
+          <t>외국인 4일째 매수 중이며 수급 긍정적. 리밸런싱 완료 후 상승 추세 기대. 190 이상 돌파 및 두 자릿수 상승 가능성 언급. 단기 물량 이탈 확인.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '프랑스 협력']</t>
+          <t>['외국인', '수급', '상승추세']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12250</v>
+        <v>92000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-2.16</v>
+        <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>164</v>
+        <v>311</v>
       </c>
       <c r="F16" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>315</v>
+        <v>1582</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>23.61</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>11990</v>
+        <v>89500</v>
       </c>
       <c r="K16" t="n">
-        <v>12440</v>
+        <v>92000</v>
       </c>
       <c r="L16" t="n">
-        <v>12800</v>
+        <v>94400</v>
       </c>
       <c r="M16" t="n">
-        <v>11920</v>
+        <v>91300</v>
       </c>
       <c r="N16" t="n">
-        <v>2.16</v>
+        <v>23.63</v>
       </c>
       <c r="O16" t="n">
-        <v>40878536410</v>
+        <v>273691831950</v>
       </c>
       <c r="P16" t="n">
-        <v>36200</v>
+        <v>139200</v>
       </c>
       <c r="Q16" t="n">
-        <v>8920</v>
+        <v>57000</v>
       </c>
       <c r="R16" t="n">
-        <v>43000</v>
+        <v>103000</v>
       </c>
       <c r="S16" t="n">
-        <v>-6000</v>
+        <v>66000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>국제유가 급등에 따른 기대감 고조. 지정학적 리스크 부각되며 유가 추가 상승 및 주가 상승 전망.</t>
+          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적 리스크']</t>
+          <t>['원전', 'SMR', '한-프랑스']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,86 +1936,86 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8990</v>
+        <v>12210</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.36</v>
+        <v>-2.16</v>
       </c>
       <c r="E17" t="n">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="G17" t="n">
-        <v>422</v>
+        <v>313</v>
       </c>
       <c r="H17" t="n">
-        <v>27.69</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8940</v>
+        <v>11990</v>
       </c>
       <c r="K17" t="n">
-        <v>8940</v>
+        <v>12440</v>
       </c>
       <c r="L17" t="n">
-        <v>9070</v>
+        <v>12800</v>
       </c>
       <c r="M17" t="n">
-        <v>8710</v>
+        <v>11920</v>
       </c>
       <c r="N17" t="n">
-        <v>28.05</v>
+        <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>25159938545</v>
+        <v>42373946165</v>
       </c>
       <c r="P17" t="n">
-        <v>17950</v>
+        <v>36200</v>
       </c>
       <c r="Q17" t="n">
-        <v>8120</v>
+        <v>8920</v>
       </c>
       <c r="R17" t="n">
-        <v>-289000</v>
+        <v>27000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>AI 문명 관련 기대감에도 불구하고 중국산 경쟁 심화 및 실적 부진으로 인한 주가 하락세 지속. 유상증자 및 시가총액 하락에 대한 부정적 전망 우세.</t>
+          <t>국제유가 급등에 따른 기대감 고조. 지정학적 리스크 부각되며 유가 추가 상승 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AI', '중국산', '유상증자']</t>
+          <t>['국제유가', '지정학적 리스크']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>269750</v>
+        <v>8970</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="E18" t="n">
-        <v>793</v>
+        <v>105</v>
       </c>
       <c r="F18" t="n">
-        <v>471</v>
+        <v>64</v>
       </c>
       <c r="G18" t="n">
-        <v>1532</v>
+        <v>444</v>
       </c>
       <c r="H18" t="n">
-        <v>46.85</v>
+        <v>27.69</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="K18" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="L18" t="n">
-        <v>275000</v>
+        <v>9070</v>
       </c>
       <c r="M18" t="n">
-        <v>268500</v>
+        <v>8710</v>
       </c>
       <c r="N18" t="n">
-        <v>46.79</v>
+        <v>28.05</v>
       </c>
       <c r="O18" t="n">
-        <v>2844409840000</v>
+        <v>26673444165</v>
       </c>
       <c r="P18" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q18" t="n">
-        <v>70000</v>
+        <v>8120</v>
       </c>
       <c r="R18" t="n">
-        <v>-301000</v>
+        <v>-481000</v>
       </c>
       <c r="S18" t="n">
-        <v>176000</v>
+        <v>5000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>SK하이닉스 등 경쟁사 대비 부진한 흐름에 대한 아쉬움 표출.</t>
+          <t>중국산 제품 경쟁력 및 부정적 전망. 주주 불만 및 기업의 낮은 주가 관리 능력 지적. AI 관련 언급은 있으나 구체적 호재는 부재.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['반도체', '경쟁사']</t>
+          <t>['중국산', '주가관리', 'AI']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19850</v>
+        <v>270000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.38</v>
+        <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>205</v>
+        <v>792</v>
       </c>
       <c r="F19" t="n">
-        <v>113</v>
+        <v>473</v>
       </c>
       <c r="G19" t="n">
-        <v>698</v>
+        <v>1553</v>
       </c>
       <c r="H19" t="n">
-        <v>10.85</v>
+        <v>46.85</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>19970</v>
+        <v>269500</v>
       </c>
       <c r="K19" t="n">
-        <v>20250</v>
+        <v>269500</v>
       </c>
       <c r="L19" t="n">
-        <v>21300</v>
+        <v>275000</v>
       </c>
       <c r="M19" t="n">
-        <v>19630</v>
+        <v>268500</v>
       </c>
       <c r="N19" t="n">
-        <v>10.47</v>
+        <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>236289758345</v>
+        <v>3027345347500</v>
       </c>
       <c r="P19" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q19" t="n">
-        <v>3320</v>
+        <v>70000</v>
       </c>
       <c r="R19" t="n">
-        <v>-844000</v>
+        <v>-1252000</v>
       </c>
       <c r="S19" t="n">
-        <v>45000</v>
+        <v>720000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 원전 사업 참여 기대감 속 계약 체결 공시 확인.</t>
+          <t>SK하이닉스와의 주가 상승률 비교 및 상대적 부진에 대한 지적. 외국인 선물 매도 전환 등 부정적 신호 감지. 자사주 매입 요구 및 목표가 상향 의견도 일부.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '계약 체결']</t>
+          <t>['반도체', '외국인', '목표가']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33850</v>
+        <v>33800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F20" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G20" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H20" t="n">
         <v>52.59</v>
@@ -2260,13 +2260,13 @@
         <v>35325</v>
       </c>
       <c r="M20" t="n">
-        <v>33800</v>
+        <v>33750</v>
       </c>
       <c r="N20" t="n">
         <v>21.01</v>
       </c>
       <c r="O20" t="n">
-        <v>67924412150</v>
+        <v>70947402525</v>
       </c>
       <c r="P20" t="n">
         <v>69500</v>
@@ -2275,14 +2275,14 @@
         <v>30400</v>
       </c>
       <c r="R20" t="n">
-        <v>-78000</v>
+        <v>-69000</v>
       </c>
       <c r="S20" t="n">
-        <v>61000</v>
+        <v>68000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 원전 협력 강화 및 차세대 원전 사업 관련 긍정적 전망. 전기료 인상 및 발전 5사 통합 논의도 주가에 영향을 미칠 가능성. 다만, 공매도 및 정부 기업의 한계성에 대한 우려도 존재.</t>
+          <t>미국 원전 협력 및 한국-프랑스 차세대 원전 사업 기대. 발전 5사 통합 및 선납매 이슈.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전 협력', '전기료 인상', '발전 5사 통합']</t>
+          <t>['원전', '미국 협력', '발전 5사']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10230</v>
+        <v>19790</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>-0.90%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="E21" t="n">
-        <v>98</v>
+        <v>209</v>
       </c>
       <c r="F21" t="n">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="G21" t="n">
-        <v>200</v>
+        <v>699</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9399999999999999</v>
+        <v>10.85</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>10440</v>
+        <v>19970</v>
       </c>
       <c r="K21" t="n">
-        <v>10180</v>
+        <v>20250</v>
       </c>
       <c r="L21" t="n">
-        <v>11340</v>
+        <v>21300</v>
       </c>
       <c r="M21" t="n">
-        <v>9980</v>
+        <v>19630</v>
       </c>
       <c r="N21" t="n">
-        <v>0.62</v>
+        <v>10.47</v>
       </c>
       <c r="O21" t="n">
-        <v>141662149515</v>
+        <v>242991349215</v>
       </c>
       <c r="P21" t="n">
-        <v>15960</v>
+        <v>40350</v>
       </c>
       <c r="Q21" t="n">
-        <v>3500</v>
+        <v>3320</v>
       </c>
       <c r="R21" t="n">
-        <v>-43000</v>
+        <v>-1134000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-151000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 제약바이오 시장 혼조세 속 탈모주 관련 기대감.</t>
+          <t>미국 원전 사업 참여 기대감 속 계약 체결 공시 확인.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['탈모주', '신고가']</t>
+          <t>['원전', '계약 체결']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,97 +2396,189 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3765</v>
+        <v>10120</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.21%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.52</v>
+        <v>0.32</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F22" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="G22" t="n">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="H22" t="n">
-        <v>2.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3890</v>
+        <v>10440</v>
       </c>
       <c r="K22" t="n">
-        <v>3890</v>
+        <v>10180</v>
       </c>
       <c r="L22" t="n">
-        <v>4115</v>
+        <v>11340</v>
       </c>
       <c r="M22" t="n">
-        <v>3700</v>
+        <v>9980</v>
       </c>
       <c r="N22" t="n">
-        <v>1.56</v>
+        <v>0.62</v>
       </c>
       <c r="O22" t="n">
-        <v>63311995606</v>
+        <v>143263719045</v>
       </c>
       <c r="P22" t="n">
-        <v>4335</v>
+        <v>15960</v>
       </c>
       <c r="Q22" t="n">
-        <v>1246</v>
+        <v>3500</v>
       </c>
       <c r="R22" t="n">
-        <v>-505000</v>
+        <v>-11000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>탈모 관련 기대감과 조정·하락 우려 공존. 재료 부족 논란.</t>
+          <t>미국 제약 바이오 시장 동향 언급 및 주포 관련 부정적 의견 존재. 탈모 관련 테마 기대감 및 신고가 돌파 의지 표출.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['탈모주', '신고가', '주포']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>004310</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JW신약</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3735</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-3.98%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E23" t="n">
+        <v>94</v>
+      </c>
+      <c r="F23" t="n">
+        <v>50</v>
+      </c>
+      <c r="G23" t="n">
+        <v>181</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>3890</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3890</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4115</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3700</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O23" t="n">
+        <v>64364158194</v>
+      </c>
+      <c r="P23" t="n">
+        <v>4335</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1246</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-519000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>탈모 관련 제약주 수급 변화 가능성 언급. 일부 하락 및 보합세 전망.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
         <v>0.1</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>['탈모', '조정', '재료']</t>
-        </is>
-      </c>
-      <c r="X22" t="n">
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['탈모 치료제', '제약주', '수급']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
         <v>8</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>067290</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G2" t="n">
-        <v>1346</v>
+        <v>1377</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29638325495</v>
+        <v>29644016635</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -670,13 +670,13 @@
         <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G3" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
@@ -702,7 +702,7 @@
         <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>37761774195</v>
+        <v>37785222525</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2640</v>
+        <v>2645</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+22.22%</t>
+          <t>+22.45%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="H4" t="n">
         <v>5.26</v>
@@ -785,7 +785,7 @@
         <v>2200</v>
       </c>
       <c r="L4" t="n">
-        <v>2670</v>
+        <v>2700</v>
       </c>
       <c r="M4" t="n">
         <v>2200</v>
@@ -794,10 +794,10 @@
         <v>5.49</v>
       </c>
       <c r="O4" t="n">
-        <v>27353186547</v>
+        <v>29777779299</v>
       </c>
       <c r="P4" t="n">
-        <v>2670</v>
+        <v>2700</v>
       </c>
       <c r="Q4" t="n">
         <v>1418</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>경영권 분쟁 및 신규 대주주 관련 긍정적 전망. 단기 급등 기대감 및 기타법인 매수세 유입 관찰. 과열 우려 및 매도량 급증 주의.</t>
+          <t>경영권 분쟁 및 지분 싸움 가능성, 엔비디아 관련 루머 및 단기 과열 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['경영권분쟁', '기타법인', '단기과열']</t>
+          <t>['지분싸움', '엔비디아', '경영권']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12210</v>
+        <v>12160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+21.73%</t>
+          <t>+21.24%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F5" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G5" t="n">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="H5" t="n">
         <v>0.36</v>
@@ -886,7 +886,7 @@
         <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>184430443710</v>
+        <v>186908591250</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>가스터빈 및 원전 관련 사업 부각. 국내 1위 업체로 미국 시장 진출 기대.</t>
+          <t>SMR 및 가스터빈 관련 사업 부각, 미국 발전소 투자 확대 뉴스 기반 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['가스터빈', '원전', '미국 시장']</t>
+          <t>['SMR', '가스터빈', '미국투자']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13870</v>
+        <v>13940</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+17.44%</t>
+          <t>+18.04%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.22</v>
       </c>
       <c r="E6" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F6" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G6" t="n">
-        <v>1252</v>
+        <v>1276</v>
       </c>
       <c r="H6" t="n">
         <v>5.64</v>
@@ -978,7 +978,7 @@
         <v>5.42</v>
       </c>
       <c r="O6" t="n">
-        <v>446002878090</v>
+        <v>452028611710</v>
       </c>
       <c r="P6" t="n">
         <v>30200</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7150</v>
+        <v>7140</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+14.22%</t>
+          <t>+14.06%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F7" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G7" t="n">
-        <v>1035</v>
+        <v>1069</v>
       </c>
       <c r="H7" t="n">
         <v>7.4</v>
@@ -1070,7 +1070,7 @@
         <v>7.35</v>
       </c>
       <c r="O7" t="n">
-        <v>67325430180</v>
+        <v>67567685965</v>
       </c>
       <c r="P7" t="n">
         <v>21500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>췌장암 치료제 관련 임상 결과 발표 기대. 공매도와의 경쟁 및 주가 상승 전망.</t>
+          <t>뎅기열 중간 발표 기대감과 페니트리움바이오 관련 임상 데이터 발표 예정. 공매도와의 경쟁 속 거래량 증가 추세.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['췌장암 치료제', '임상 결과', '공매도']</t>
+          <t>['뎅기열', '페니트리움', '임상 데이터']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54200</v>
+        <v>54100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+10.05%</t>
+          <t>+9.85%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F8" t="n">
         <v>113</v>
       </c>
       <c r="G8" t="n">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="H8" t="n">
         <v>14.96</v>
@@ -1162,7 +1162,7 @@
         <v>14.93</v>
       </c>
       <c r="O8" t="n">
-        <v>154490394300</v>
+        <v>155416736150</v>
       </c>
       <c r="P8" t="n">
         <v>108900</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>두산퓨얼셀 수주 관련 긍정적 언급 및 목표가 상향 주장. 2분기 영업이익 적자에도 불구하고 향후 매출 성장성 기대. 기관 연기금 유입 및 공매도 세력 관련 논쟁.</t>
+          <t>수주 관련 언급 및 2분기 실적 부진, 목표가 상향 전망 및 기관 연기금 매수 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주', '목표가', '공매도']</t>
+          <t>['수주', '실적', '목표가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14830</v>
+        <v>14880</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.25%</t>
+          <t>+8.61%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.39</v>
       </c>
       <c r="E9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F9" t="n">
         <v>146</v>
       </c>
       <c r="G9" t="n">
-        <v>1252</v>
+        <v>1276</v>
       </c>
       <c r="H9" t="n">
         <v>1.55</v>
@@ -1254,7 +1254,7 @@
         <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>411682688180</v>
+        <v>413754855825</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6780</v>
+        <v>6790</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.44%</t>
+          <t>+5.60%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>327</v>
+        <v>158</v>
       </c>
       <c r="F10" t="n">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="G10" t="n">
-        <v>462</v>
+        <v>286</v>
       </c>
       <c r="H10" t="n">
         <v>16.71</v>
@@ -1346,7 +1346,7 @@
         <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>95982087090</v>
+        <v>96405403020</v>
       </c>
       <c r="P10" t="n">
         <v>13000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>배당 관련 언급 있으나 주가 하락 우려 및 공매도 관련 부정적 전망 혼재. 외인 순매수 전환 기대감도 일부 존재.</t>
+          <t>배당 관련 언급은 있으나 주가 부양에 대한 구체적인 근거 부족, 외인 유입 여부 불확실.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['배당', '공매도', '외인']</t>
+          <t>['배당', '외인']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3795</v>
+        <v>31050</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.26%</t>
+          <t>+4.37%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.74</v>
+        <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>209</v>
+        <v>625</v>
       </c>
       <c r="F11" t="n">
-        <v>121</v>
+        <v>232</v>
       </c>
       <c r="G11" t="n">
-        <v>471</v>
+        <v>846</v>
       </c>
       <c r="H11" t="n">
-        <v>3.19</v>
+        <v>0.31</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3640</v>
+        <v>29750</v>
       </c>
       <c r="K11" t="n">
-        <v>3750</v>
+        <v>31600</v>
       </c>
       <c r="L11" t="n">
-        <v>4460</v>
+        <v>34200</v>
       </c>
       <c r="M11" t="n">
-        <v>3680</v>
+        <v>28300</v>
       </c>
       <c r="N11" t="n">
-        <v>0.45</v>
+        <v>0.23</v>
       </c>
       <c r="O11" t="n">
-        <v>267541700273</v>
+        <v>446292048850</v>
       </c>
       <c r="P11" t="n">
-        <v>8100</v>
+        <v>39350</v>
       </c>
       <c r="Q11" t="n">
-        <v>592</v>
+        <v>8200</v>
       </c>
       <c r="R11" t="n">
-        <v>-816000</v>
+        <v>-1000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 급등 및 관련 수혜 기대. 재료 우수성 및 거래량 풍부함 언급. 6천원 이상 목표가 설정 및 국책사업 선정 가능성 제기. 투기과열 지정 우려도 존재.</t>
+          <t>혈압계 관련 기술 유럽 진출 뉴스. 상장 초기 급등 후 조정 국면.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '재료', '국책사업']</t>
+          <t>['혈압계', '유럽 진출', '기술']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30900</v>
+        <v>8010</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.87%</t>
+          <t>+4.30%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.08</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
-        <v>615</v>
+        <v>107</v>
       </c>
       <c r="F12" t="n">
-        <v>231</v>
+        <v>71</v>
       </c>
       <c r="G12" t="n">
-        <v>821</v>
+        <v>315</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31</v>
+        <v>1.81</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>29750</v>
+        <v>7680</v>
       </c>
       <c r="K12" t="n">
-        <v>31600</v>
+        <v>7780</v>
       </c>
       <c r="L12" t="n">
-        <v>34200</v>
+        <v>9000</v>
       </c>
       <c r="M12" t="n">
-        <v>28300</v>
+        <v>7750</v>
       </c>
       <c r="N12" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="O12" t="n">
-        <v>438695175550</v>
+        <v>111870587010</v>
       </c>
       <c r="P12" t="n">
-        <v>39350</v>
+        <v>10300</v>
       </c>
       <c r="Q12" t="n">
-        <v>8200</v>
+        <v>952</v>
       </c>
       <c r="R12" t="n">
-        <v>-1000</v>
+        <v>-210000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>혈압계 관련 기술 유럽 진출 뉴스. 상장 초기 급등 후 조정 국면.</t>
+          <t>레미콘 파업 관련 기대감 및 강한 지지선 언급, 당일 상승 추세.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['혈압계', '유럽 진출', '기술']</t>
+          <t>['레미콘', '파업', '지지선']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1995</v>
+        <v>3792</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>+4.18%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>2.74</v>
       </c>
       <c r="E13" t="n">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="G13" t="n">
-        <v>251</v>
+        <v>480</v>
       </c>
       <c r="H13" t="n">
-        <v>0.51</v>
+        <v>3.19</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1922</v>
+        <v>3640</v>
       </c>
       <c r="K13" t="n">
-        <v>1920</v>
+        <v>3750</v>
       </c>
       <c r="L13" t="n">
-        <v>2165</v>
+        <v>4460</v>
       </c>
       <c r="M13" t="n">
-        <v>1862</v>
+        <v>3680</v>
       </c>
       <c r="N13" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="O13" t="n">
-        <v>16439677578</v>
+        <v>268457392846</v>
       </c>
       <c r="P13" t="n">
-        <v>2930</v>
+        <v>8100</v>
       </c>
       <c r="Q13" t="n">
-        <v>910</v>
+        <v>592</v>
       </c>
       <c r="R13" t="n">
-        <v>106000</v>
+        <v>-816000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
+          <t>미국 광통신 섹터 급등 및 관련 수혜 기대. 재료 우수성 및 거래량 풍부함 언급. 6천원 이상 목표가 설정 및 국책사업 선정 가능성 제기. 투기과열 지정 우려도 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
+          <t>['광통신', '재료', '국책사업']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7950</v>
+        <v>1863000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.52%</t>
+          <t>+3.90%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.4</v>
+        <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>105</v>
+        <v>798</v>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>456</v>
       </c>
       <c r="G14" t="n">
-        <v>311</v>
+        <v>1873</v>
       </c>
       <c r="H14" t="n">
-        <v>1.81</v>
+        <v>50.66</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7680</v>
+        <v>1793000</v>
       </c>
       <c r="K14" t="n">
-        <v>7780</v>
+        <v>1795000</v>
       </c>
       <c r="L14" t="n">
-        <v>9000</v>
+        <v>1883000</v>
       </c>
       <c r="M14" t="n">
-        <v>7750</v>
+        <v>1795000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.41</v>
+        <v>50.63</v>
       </c>
       <c r="O14" t="n">
-        <v>111498719895</v>
+        <v>4757133693000</v>
       </c>
       <c r="P14" t="n">
-        <v>10300</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>952</v>
+        <v>277000</v>
       </c>
       <c r="R14" t="n">
-        <v>-210000</v>
+        <v>157000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>153000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>레미콘 파업 및 긍정적인 시장 흐름에 따른 상한가 기대감. 하지만 구체적인 근거는 부족.</t>
+          <t>외인 4일째 매수 중, 호가창 가벼워짐 및 상승 추세 기대감, 전일 대비 분위기 변화.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['레미콘 파업', '상한가 기대', '지지선']</t>
+          <t>['외인매수', '상승추세']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1852000</v>
+        <v>1995</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.29%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>795</v>
+        <v>109</v>
       </c>
       <c r="F15" t="n">
-        <v>458</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>1978</v>
+        <v>254</v>
       </c>
       <c r="H15" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1793000</v>
+        <v>1922</v>
       </c>
       <c r="K15" t="n">
-        <v>1795000</v>
+        <v>1920</v>
       </c>
       <c r="L15" t="n">
-        <v>1883000</v>
+        <v>2165</v>
       </c>
       <c r="M15" t="n">
-        <v>1795000</v>
+        <v>1862</v>
       </c>
       <c r="N15" t="n">
-        <v>50.63</v>
+        <v>0.61</v>
       </c>
       <c r="O15" t="n">
-        <v>4628215964000</v>
+        <v>16506600266</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q15" t="n">
-        <v>277000</v>
+        <v>910</v>
       </c>
       <c r="R15" t="n">
-        <v>157000</v>
+        <v>106000</v>
       </c>
       <c r="S15" t="n">
-        <v>153000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>외국인 4일째 매수 중이며 수급 긍정적. 리밸런싱 완료 후 상승 추세 기대. 190 이상 돌파 및 두 자릿수 상승 가능성 언급. 단기 물량 이탈 확인.</t>
+          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['외국인', '수급', '상승추세']</t>
+          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
@@ -1866,13 +1866,13 @@
         <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="F16" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G16" t="n">
-        <v>1582</v>
+        <v>1605</v>
       </c>
       <c r="H16" t="n">
         <v>23.61</v>
@@ -1898,7 +1898,7 @@
         <v>23.63</v>
       </c>
       <c r="O16" t="n">
-        <v>273691831950</v>
+        <v>276414420150</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12210</v>
+        <v>12070</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-2.16</v>
       </c>
       <c r="E17" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F17" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G17" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>42373946165</v>
+        <v>43330055710</v>
       </c>
       <c r="P17" t="n">
         <v>36200</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8970</v>
+        <v>8990</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.36</v>
       </c>
       <c r="E18" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F18" t="n">
         <v>64</v>
       </c>
       <c r="G18" t="n">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="H18" t="n">
         <v>27.69</v>
@@ -2082,7 +2082,7 @@
         <v>28.05</v>
       </c>
       <c r="O18" t="n">
-        <v>26673444165</v>
+        <v>27340992090</v>
       </c>
       <c r="P18" t="n">
         <v>17950</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>270000</v>
+        <v>270750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>792</v>
+        <v>654</v>
       </c>
       <c r="F19" t="n">
-        <v>473</v>
+        <v>409</v>
       </c>
       <c r="G19" t="n">
-        <v>1553</v>
+        <v>1229</v>
       </c>
       <c r="H19" t="n">
         <v>46.85</v>
@@ -2174,7 +2174,7 @@
         <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>3027345347500</v>
+        <v>3101435211000</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>SK하이닉스와의 주가 상승률 비교 및 상대적 부진에 대한 지적. 외국인 선물 매도 전환 등 부정적 신호 감지. 자사주 매입 요구 및 목표가 상향 의견도 일부.</t>
+          <t>SK하이닉스 대비 부진한 주가 흐름, 자사주 매입 및 주가 부양 기대감 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반도체', '외국인', '목표가']</t>
+          <t>['SK하이닉스', '자사주매입']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33800</v>
+        <v>19850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="E20" t="n">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="F20" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="G20" t="n">
-        <v>263</v>
+        <v>437</v>
       </c>
       <c r="H20" t="n">
-        <v>52.59</v>
+        <v>10.85</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,38 +2251,38 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>34100</v>
+        <v>19970</v>
       </c>
       <c r="K20" t="n">
-        <v>34450</v>
+        <v>20250</v>
       </c>
       <c r="L20" t="n">
-        <v>35325</v>
+        <v>21300</v>
       </c>
       <c r="M20" t="n">
-        <v>33750</v>
+        <v>19630</v>
       </c>
       <c r="N20" t="n">
-        <v>21.01</v>
+        <v>10.47</v>
       </c>
       <c r="O20" t="n">
-        <v>70947402525</v>
+        <v>245308735610</v>
       </c>
       <c r="P20" t="n">
-        <v>69500</v>
+        <v>40350</v>
       </c>
       <c r="Q20" t="n">
-        <v>30400</v>
+        <v>3320</v>
       </c>
       <c r="R20" t="n">
-        <v>-69000</v>
+        <v>-1134000</v>
       </c>
       <c r="S20" t="n">
-        <v>68000</v>
+        <v>-151000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 원전 협력 및 한국-프랑스 차세대 원전 사업 기대. 발전 5사 통합 및 선납매 이슈.</t>
+          <t>계약 체결 공시 확인, 공매도 관련 언급 있으나 차트상 긍정적 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '미국 협력', '발전 5사']</t>
+          <t>['공시', '계약체결', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19790</v>
+        <v>33850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.90%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.38</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>209</v>
+        <v>119</v>
       </c>
       <c r="F21" t="n">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="G21" t="n">
-        <v>699</v>
+        <v>271</v>
       </c>
       <c r="H21" t="n">
-        <v>10.85</v>
+        <v>52.59</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>19970</v>
+        <v>34100</v>
       </c>
       <c r="K21" t="n">
-        <v>20250</v>
+        <v>34450</v>
       </c>
       <c r="L21" t="n">
-        <v>21300</v>
+        <v>35325</v>
       </c>
       <c r="M21" t="n">
-        <v>19630</v>
+        <v>33750</v>
       </c>
       <c r="N21" t="n">
-        <v>10.47</v>
+        <v>21.01</v>
       </c>
       <c r="O21" t="n">
-        <v>242991349215</v>
+        <v>72345336125</v>
       </c>
       <c r="P21" t="n">
-        <v>40350</v>
+        <v>69500</v>
       </c>
       <c r="Q21" t="n">
-        <v>3320</v>
+        <v>30400</v>
       </c>
       <c r="R21" t="n">
-        <v>-1134000</v>
+        <v>-69000</v>
       </c>
       <c r="S21" t="n">
-        <v>-151000</v>
+        <v>68000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 원전 사업 참여 기대감 속 계약 체결 공시 확인.</t>
+          <t>미국 원전 협력 기대감과 25조 선납매 언급. SMP 급락 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '계약 체결']</t>
+          <t>['원전', '선납매', 'SMP']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10120</v>
+        <v>10140</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-2.87%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.32</v>
       </c>
       <c r="E22" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F22" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G22" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H22" t="n">
         <v>0.9399999999999999</v>
@@ -2450,7 +2450,7 @@
         <v>0.62</v>
       </c>
       <c r="O22" t="n">
-        <v>143263719045</v>
+        <v>144027634705</v>
       </c>
       <c r="P22" t="n">
         <v>15960</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 제약 바이오 시장 동향 언급 및 주포 관련 부정적 의견 존재. 탈모 관련 테마 기대감 및 신고가 돌파 의지 표출.</t>
+          <t>미증시 제약바이오와는 다른 움직임, 탈모주 관련 기대감 있으나 구체적인 재료 및 공시 부재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['탈모주', '신고가', '주포']</t>
+          <t>['탈모주', '재료']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3735</v>
+        <v>3755</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.98%</t>
+          <t>-3.47%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.52</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F23" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G23" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H23" t="n">
         <v>2.08</v>
@@ -2542,7 +2542,7 @@
         <v>1.56</v>
       </c>
       <c r="O23" t="n">
-        <v>64364158194</v>
+        <v>64634348454</v>
       </c>
       <c r="P23" t="n">
         <v>4335</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>탈모 관련 제약주 수급 변화 가능성 언급. 일부 하락 및 보합세 전망.</t>
+          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '제약주', '수급']</t>
+          <t>['탈모주', '하락']</t>
         </is>
       </c>
       <c r="X23" t="n">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G2" t="n">
-        <v>1377</v>
+        <v>1440</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29644016635</v>
+        <v>29692625055</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미 FDA 2A상 승인 및 다락손라십 대비 우수한 약효에 대한 기대감. 글로벌 시장 진출 및 10연상까지 가능한 획기적인 신약 개발에 대한 긍정적 전망.</t>
+          <t>미 FDA 2A상 승인 및 병용 요법 연구 결과 발표 등 긍정적인 뉴스가 다수 확인됨. 특히 다락손라십 대비 우수하다는 비교 결과와 암세포 사멸 효과에 대한 기대감이 높으며, 이를 바탕으로 주가 상승 및 상한가 가능성이 언급됨.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA 2A상', '암세포 사멸', '다락손라십']</t>
+          <t>['FDA', '암치료제', '연구 결과']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6570</v>
+        <v>13030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+29.84%</t>
+          <t>+29.91%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>174</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="G3" t="n">
-        <v>291</v>
+        <v>334</v>
       </c>
       <c r="H3" t="n">
-        <v>2.46</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,139 +687,139 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5060</v>
+        <v>10030</v>
       </c>
       <c r="K3" t="n">
-        <v>5190</v>
+        <v>10270</v>
       </c>
       <c r="L3" t="n">
-        <v>6570</v>
+        <v>13030</v>
       </c>
       <c r="M3" t="n">
-        <v>5110</v>
+        <v>10040</v>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>37785222525</v>
+        <v>231191124165</v>
       </c>
       <c r="P3" t="n">
-        <v>16200</v>
+        <v>20850</v>
       </c>
       <c r="Q3" t="n">
-        <v>1206</v>
+        <v>4020</v>
       </c>
       <c r="R3" t="n">
-        <v>34000</v>
+        <v>4000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>주주들의 기다림 끝에 상승세 예상, 단기 고점 및 상장 기대감 존재. 매집 정황 포착.</t>
+          <t>미국 SMR 관련주 폭등에 따른 기대감 속 거래량 부족 및 주포 자금력 의문. 12000원 돌파 시 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['상장', '단기 고점', '매집']</t>
+          <t>['SMR', '주포', '가스터빈']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2645</v>
+        <v>6570</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+22.45%</t>
+          <t>+29.84%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.23</v>
+        <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>181</v>
+        <v>294</v>
       </c>
       <c r="H4" t="n">
-        <v>5.26</v>
+        <v>2.46</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2160</v>
+        <v>5060</v>
       </c>
       <c r="K4" t="n">
-        <v>2200</v>
+        <v>5190</v>
       </c>
       <c r="L4" t="n">
-        <v>2700</v>
+        <v>6570</v>
       </c>
       <c r="M4" t="n">
-        <v>2200</v>
+        <v>5110</v>
       </c>
       <c r="N4" t="n">
-        <v>5.49</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>29777779299</v>
+        <v>37821456075</v>
       </c>
       <c r="P4" t="n">
-        <v>2700</v>
+        <v>16200</v>
       </c>
       <c r="Q4" t="n">
-        <v>1418</v>
+        <v>1206</v>
       </c>
       <c r="R4" t="n">
-        <v>-166000</v>
+        <v>34000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>경영권 분쟁 및 지분 싸움 가능성, 엔비디아 관련 루머 및 단기 과열 언급.</t>
+          <t>주주들의 기다림 끝에 상승세 예상, 단기 고점 및 상장 기대감 존재. 매집 정황 포착.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['지분싸움', '엔비디아', '경영권']</t>
+          <t>['상장', '단기 고점', '매집']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12160</v>
+        <v>13950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+21.24%</t>
+          <t>+18.12%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.08</v>
+        <v>0.22</v>
       </c>
       <c r="E5" t="n">
+        <v>261</v>
+      </c>
+      <c r="F5" t="n">
         <v>153</v>
       </c>
-      <c r="F5" t="n">
-        <v>86</v>
-      </c>
       <c r="G5" t="n">
-        <v>326</v>
+        <v>1341</v>
       </c>
       <c r="H5" t="n">
-        <v>0.36</v>
+        <v>5.64</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>10030</v>
+        <v>11810</v>
       </c>
       <c r="K5" t="n">
-        <v>10270</v>
+        <v>12050</v>
       </c>
       <c r="L5" t="n">
-        <v>12790</v>
+        <v>14550</v>
       </c>
       <c r="M5" t="n">
-        <v>10040</v>
+        <v>11950</v>
       </c>
       <c r="N5" t="n">
-        <v>0.44</v>
+        <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>186908591250</v>
+        <v>461562890735</v>
       </c>
       <c r="P5" t="n">
-        <v>20850</v>
+        <v>30200</v>
       </c>
       <c r="Q5" t="n">
-        <v>4020</v>
+        <v>3540</v>
       </c>
       <c r="R5" t="n">
-        <v>4000</v>
+        <v>294000</v>
       </c>
       <c r="S5" t="n">
-        <v>19000</v>
+        <v>73000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SMR 및 가스터빈 관련 사업 부각, 미국 발전소 투자 확대 뉴스 기반 상승 기대.</t>
+          <t>하반기 주도주로서 원전 및 로봇 섹터 전망. 미국 및 사우디 등 해외 수주 기대감 반영. 13750원 및 22300원 등 단기 목표가 제시. 정부 정책 및 외국인 자본 유입 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['SMR', '가스터빈', '미국투자']</t>
+          <t>['원전', '로봇', '해외수주']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,99 +924,99 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13940</v>
+        <v>2525</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+18.04%</t>
+          <t>+16.90%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="E6" t="n">
-        <v>251</v>
+        <v>103</v>
       </c>
       <c r="F6" t="n">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>1276</v>
+        <v>201</v>
       </c>
       <c r="H6" t="n">
-        <v>5.64</v>
+        <v>5.26</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>11810</v>
+        <v>2160</v>
       </c>
       <c r="K6" t="n">
-        <v>12050</v>
+        <v>2200</v>
       </c>
       <c r="L6" t="n">
-        <v>14550</v>
+        <v>2705</v>
       </c>
       <c r="M6" t="n">
-        <v>11950</v>
+        <v>2200</v>
       </c>
       <c r="N6" t="n">
-        <v>5.42</v>
+        <v>5.49</v>
       </c>
       <c r="O6" t="n">
-        <v>452028611710</v>
+        <v>33277793878</v>
       </c>
       <c r="P6" t="n">
-        <v>30200</v>
+        <v>2705</v>
       </c>
       <c r="Q6" t="n">
-        <v>3540</v>
+        <v>1418</v>
       </c>
       <c r="R6" t="n">
-        <v>294000</v>
+        <v>-166000</v>
       </c>
       <c r="S6" t="n">
-        <v>73000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>하반기 주도주로서 원전 및 로봇 섹터 전망. 미국 및 사우디 등 해외 수주 기대감 반영. 13750원 및 22300원 등 단기 목표가 제시. 정부 정책 및 외국인 자본 유입 언급.</t>
+          <t>경영권 분쟁 및 지분 싸움 가능성, 엔비디아 관련 루머 및 단기 과열 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '로봇', '해외수주']</t>
+          <t>['지분싸움', '엔비디아', '경영권']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7140</v>
+        <v>7210</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+14.06%</t>
+          <t>+15.18%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F7" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G7" t="n">
-        <v>1069</v>
+        <v>1127</v>
       </c>
       <c r="H7" t="n">
         <v>7.4</v>
@@ -1070,7 +1070,7 @@
         <v>7.35</v>
       </c>
       <c r="O7" t="n">
-        <v>67567685965</v>
+        <v>68323496895</v>
       </c>
       <c r="P7" t="n">
         <v>21500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>뎅기열 중간 발표 기대감과 페니트리움바이오 관련 임상 데이터 발표 예정. 공매도와의 경쟁 속 거래량 증가 추세.</t>
+          <t>페니트리움바이오 관련 긍정적 데이터 발표 기대감. 공매도 세력과의 주가 방어 및 거래량 증가.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['뎅기열', '페니트리움', '임상 데이터']</t>
+          <t>['페니트리움바이오', '공매도', '항암치료제']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F8" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G8" t="n">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="H8" t="n">
         <v>14.96</v>
@@ -1162,7 +1162,7 @@
         <v>14.93</v>
       </c>
       <c r="O8" t="n">
-        <v>155416736150</v>
+        <v>157198226750</v>
       </c>
       <c r="P8" t="n">
         <v>108900</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>수주 관련 언급 및 2분기 실적 부진, 목표가 상향 전망 및 기관 연기금 매수 기대.</t>
+          <t>2분기 영업이익 적자에도 불구하고 높은 목표가 제시. 외인 매도세 속 기관 매수 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주', '실적', '목표가']</t>
+          <t>['영업이익', '목표가', '기관매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14880</v>
+        <v>14800</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.61%</t>
+          <t>+8.03%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.39</v>
       </c>
       <c r="E9" t="n">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="F9" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G9" t="n">
-        <v>1276</v>
+        <v>1327</v>
       </c>
       <c r="H9" t="n">
         <v>1.55</v>
@@ -1254,7 +1254,7 @@
         <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>413754855825</v>
+        <v>416488535615</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6790</v>
+        <v>6750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.60%</t>
+          <t>+4.98%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>158</v>
+        <v>345</v>
       </c>
       <c r="F10" t="n">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="G10" t="n">
-        <v>286</v>
+        <v>512</v>
       </c>
       <c r="H10" t="n">
         <v>16.71</v>
@@ -1346,7 +1346,7 @@
         <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>96405403020</v>
+        <v>97249601370</v>
       </c>
       <c r="P10" t="n">
         <v>13000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>배당 관련 언급은 있으나 주가 부양에 대한 구체적인 근거 부족, 외인 유입 여부 불확실.</t>
+          <t>주가 폭락 가능성과 600억 배당의 상반된 평가. 공매도 세력과의 주가 방어 시도.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['배당', '외인']</t>
+          <t>['배당', '공매도', '주주환원']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31050</v>
+        <v>7980</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.37%</t>
+          <t>+3.91%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.08</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="n">
-        <v>625</v>
+        <v>112</v>
       </c>
       <c r="F11" t="n">
-        <v>232</v>
+        <v>72</v>
       </c>
       <c r="G11" t="n">
-        <v>846</v>
+        <v>323</v>
       </c>
       <c r="H11" t="n">
-        <v>0.31</v>
+        <v>1.81</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>29750</v>
+        <v>7680</v>
       </c>
       <c r="K11" t="n">
-        <v>31600</v>
+        <v>7780</v>
       </c>
       <c r="L11" t="n">
-        <v>34200</v>
+        <v>9000</v>
       </c>
       <c r="M11" t="n">
-        <v>28300</v>
+        <v>7750</v>
       </c>
       <c r="N11" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="O11" t="n">
-        <v>446292048850</v>
+        <v>112939264480</v>
       </c>
       <c r="P11" t="n">
-        <v>39350</v>
+        <v>10300</v>
       </c>
       <c r="Q11" t="n">
-        <v>8200</v>
+        <v>952</v>
       </c>
       <c r="R11" t="n">
-        <v>-1000</v>
+        <v>-210000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>혈압계 관련 기술 유럽 진출 뉴스. 상장 초기 급등 후 조정 국면.</t>
+          <t>레미콘 파업 관련 기대감 및 강한 지지선 언급, 당일 상승 추세.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['혈압계', '유럽 진출', '기술']</t>
+          <t>['레미콘', '파업', '지지선']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8010</v>
+        <v>3775</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.30%</t>
+          <t>+3.71%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.4</v>
+        <v>2.74</v>
       </c>
       <c r="E12" t="n">
-        <v>107</v>
+        <v>213</v>
       </c>
       <c r="F12" t="n">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="G12" t="n">
-        <v>315</v>
+        <v>486</v>
       </c>
       <c r="H12" t="n">
-        <v>1.81</v>
+        <v>3.19</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7680</v>
+        <v>3640</v>
       </c>
       <c r="K12" t="n">
-        <v>7780</v>
+        <v>3750</v>
       </c>
       <c r="L12" t="n">
-        <v>9000</v>
+        <v>4460</v>
       </c>
       <c r="M12" t="n">
-        <v>7750</v>
+        <v>3680</v>
       </c>
       <c r="N12" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="O12" t="n">
-        <v>111870587010</v>
+        <v>269615574874</v>
       </c>
       <c r="P12" t="n">
-        <v>10300</v>
+        <v>8100</v>
       </c>
       <c r="Q12" t="n">
-        <v>952</v>
+        <v>592</v>
       </c>
       <c r="R12" t="n">
-        <v>-210000</v>
+        <v>-816000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>레미콘 파업 관련 기대감 및 강한 지지선 언급, 당일 상승 추세.</t>
+          <t>미국 광통신 산업 급등에 따른 기대감. 투기 과열 종목 지정 우려 및 6G 기반 성장성.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['레미콘', '파업', '지지선']</t>
+          <t>['광통신', '6G', '투기과열']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3792</v>
+        <v>1859000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+4.18%</t>
+          <t>+3.68%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.74</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>213</v>
+        <v>795</v>
       </c>
       <c r="F13" t="n">
-        <v>122</v>
+        <v>452</v>
       </c>
       <c r="G13" t="n">
-        <v>480</v>
+        <v>1755</v>
       </c>
       <c r="H13" t="n">
-        <v>3.19</v>
+        <v>50.66</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3640</v>
+        <v>1793000</v>
       </c>
       <c r="K13" t="n">
-        <v>3750</v>
+        <v>1795000</v>
       </c>
       <c r="L13" t="n">
-        <v>4460</v>
+        <v>1883000</v>
       </c>
       <c r="M13" t="n">
-        <v>3680</v>
+        <v>1795000</v>
       </c>
       <c r="N13" t="n">
-        <v>0.45</v>
+        <v>50.63</v>
       </c>
       <c r="O13" t="n">
-        <v>268457392846</v>
+        <v>4974924459500</v>
       </c>
       <c r="P13" t="n">
-        <v>8100</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>592</v>
+        <v>277000</v>
       </c>
       <c r="R13" t="n">
-        <v>-816000</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 급등 및 관련 수혜 기대. 재료 우수성 및 거래량 풍부함 언급. 6천원 이상 목표가 설정 및 국책사업 선정 가능성 제기. 투기과열 지정 우려도 존재.</t>
+          <t>외국인 및 기관 매수세 유입 속 200만원 돌파 기대감. 단기 차익 매물 소화 후 상승 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', '재료', '국책사업']</t>
+          <t>['외국인매수', '기관매수', '200만원돌파']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,130 +1660,130 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1863000</v>
+        <v>1991</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.90%</t>
+          <t>+3.59%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>798</v>
+        <v>112</v>
       </c>
       <c r="F14" t="n">
-        <v>456</v>
+        <v>46</v>
       </c>
       <c r="G14" t="n">
-        <v>1873</v>
+        <v>263</v>
       </c>
       <c r="H14" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1793000</v>
+        <v>1922</v>
       </c>
       <c r="K14" t="n">
-        <v>1795000</v>
+        <v>1920</v>
       </c>
       <c r="L14" t="n">
-        <v>1883000</v>
+        <v>2165</v>
       </c>
       <c r="M14" t="n">
-        <v>1795000</v>
+        <v>1862</v>
       </c>
       <c r="N14" t="n">
-        <v>50.63</v>
+        <v>0.61</v>
       </c>
       <c r="O14" t="n">
-        <v>4757133693000</v>
+        <v>16656079360</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q14" t="n">
-        <v>277000</v>
+        <v>910</v>
       </c>
       <c r="R14" t="n">
-        <v>157000</v>
+        <v>106000</v>
       </c>
       <c r="S14" t="n">
-        <v>153000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외인 4일째 매수 중, 호가창 가벼워짐 및 상승 추세 기대감, 전일 대비 분위기 변화.</t>
+          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외인매수', '상승추세']</t>
+          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1995</v>
+        <v>30700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>+3.19%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E15" t="n">
-        <v>109</v>
+        <v>645</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>237</v>
       </c>
       <c r="G15" t="n">
-        <v>254</v>
+        <v>894</v>
       </c>
       <c r="H15" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1922</v>
+        <v>29750</v>
       </c>
       <c r="K15" t="n">
-        <v>1920</v>
+        <v>31600</v>
       </c>
       <c r="L15" t="n">
-        <v>2165</v>
+        <v>34200</v>
       </c>
       <c r="M15" t="n">
-        <v>1862</v>
+        <v>28300</v>
       </c>
       <c r="N15" t="n">
-        <v>0.61</v>
+        <v>0.23</v>
       </c>
       <c r="O15" t="n">
-        <v>16506600266</v>
+        <v>466747258850</v>
       </c>
       <c r="P15" t="n">
-        <v>2930</v>
+        <v>39350</v>
       </c>
       <c r="Q15" t="n">
-        <v>910</v>
+        <v>8200</v>
       </c>
       <c r="R15" t="n">
-        <v>106000</v>
+        <v>-1000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
+          <t>혈압계 반지 관련 유럽 진출 뉴스에 따른 기대감. 상장폐지 우려와 함께 2차 파동 시작 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
+          <t>['혈압계', '유럽진출', '2차파동']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -1866,13 +1866,13 @@
         <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F16" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G16" t="n">
-        <v>1605</v>
+        <v>1636</v>
       </c>
       <c r="H16" t="n">
         <v>23.61</v>
@@ -1898,7 +1898,7 @@
         <v>23.63</v>
       </c>
       <c r="O16" t="n">
-        <v>276414420150</v>
+        <v>283027184000</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12070</v>
+        <v>12130</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+1.17%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-2.16</v>
       </c>
       <c r="E17" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F17" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G17" t="n">
-        <v>315</v>
+        <v>382</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>43330055710</v>
+        <v>43941251465</v>
       </c>
       <c r="P17" t="n">
         <v>36200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>국제유가 급등에 따른 기대감 고조. 지정학적 리스크 부각되며 유가 추가 상승 및 주가 상승 전망.</t>
+          <t>국제 유가 급등에도 불구하고 주가는 큰 변동이 없는 상황. 지정학적 리스크(후티, 사우디, 이란 유조선 공격 등)와 유가 상승 뉴스가 지속적으로 언급되나, 실제 주가 움직임은 이를 반영하지 못하고 있음. 향후 유가 100달러 돌파 여부가 관건.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적 리스크']</t>
+          <t>['국제유가', '지정학적 리스크', '주가']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8990</v>
+        <v>270250</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.36</v>
+        <v>0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>109</v>
+        <v>786</v>
       </c>
       <c r="F18" t="n">
-        <v>64</v>
+        <v>480</v>
       </c>
       <c r="G18" t="n">
-        <v>456</v>
+        <v>1526</v>
       </c>
       <c r="H18" t="n">
-        <v>27.69</v>
+        <v>46.85</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="K18" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="L18" t="n">
-        <v>9070</v>
+        <v>275000</v>
       </c>
       <c r="M18" t="n">
-        <v>8710</v>
+        <v>268500</v>
       </c>
       <c r="N18" t="n">
-        <v>28.05</v>
+        <v>46.79</v>
       </c>
       <c r="O18" t="n">
-        <v>27340992090</v>
+        <v>3219942808500</v>
       </c>
       <c r="P18" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q18" t="n">
-        <v>8120</v>
+        <v>70000</v>
       </c>
       <c r="R18" t="n">
-        <v>-481000</v>
+        <v>-1252000</v>
       </c>
       <c r="S18" t="n">
-        <v>5000</v>
+        <v>720000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>중국산 제품 경쟁력 및 부정적 전망. 주주 불만 및 기업의 낮은 주가 관리 능력 지적. AI 관련 언급은 있으나 구체적 호재는 부재.</t>
+          <t>SK하이닉스와의 주가 격차 확대에 대한 실망감. 자사주 매입 및 공매도 관련 비판.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['중국산', '주가관리', 'AI']</t>
+          <t>['SK하이닉스', '자사주매입', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>270750</v>
+        <v>8960</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="E19" t="n">
-        <v>654</v>
+        <v>112</v>
       </c>
       <c r="F19" t="n">
-        <v>409</v>
+        <v>66</v>
       </c>
       <c r="G19" t="n">
-        <v>1229</v>
+        <v>467</v>
       </c>
       <c r="H19" t="n">
-        <v>46.85</v>
+        <v>27.69</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,91 +2159,91 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="K19" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="L19" t="n">
-        <v>275000</v>
+        <v>9070</v>
       </c>
       <c r="M19" t="n">
-        <v>268500</v>
+        <v>8710</v>
       </c>
       <c r="N19" t="n">
-        <v>46.79</v>
+        <v>28.05</v>
       </c>
       <c r="O19" t="n">
-        <v>3101435211000</v>
+        <v>28389680550</v>
       </c>
       <c r="P19" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q19" t="n">
-        <v>70000</v>
+        <v>8120</v>
       </c>
       <c r="R19" t="n">
-        <v>-1252000</v>
+        <v>-481000</v>
       </c>
       <c r="S19" t="n">
-        <v>720000</v>
+        <v>5000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>SK하이닉스 대비 부진한 주가 흐름, 자사주 매입 및 주가 부양 기대감 언급.</t>
+          <t>중국산 제품 경쟁력 및 부정적 전망. 주주 불만 및 기업의 낮은 주가 관리 능력 지적. AI 관련 언급은 있으나 구체적 호재는 부재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '자사주매입']</t>
+          <t>['중국산', '주가관리', 'AI']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19850</v>
+        <v>33600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.38</v>
+        <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="F20" t="n">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="G20" t="n">
-        <v>437</v>
+        <v>276</v>
       </c>
       <c r="H20" t="n">
-        <v>10.85</v>
+        <v>52.58</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>19970</v>
+        <v>34100</v>
       </c>
       <c r="K20" t="n">
-        <v>20250</v>
+        <v>34450</v>
       </c>
       <c r="L20" t="n">
-        <v>21300</v>
+        <v>35325</v>
       </c>
       <c r="M20" t="n">
-        <v>19630</v>
+        <v>33550</v>
       </c>
       <c r="N20" t="n">
-        <v>10.47</v>
+        <v>21.01</v>
       </c>
       <c r="O20" t="n">
-        <v>245308735610</v>
+        <v>75764847575</v>
       </c>
       <c r="P20" t="n">
-        <v>40350</v>
+        <v>69500</v>
       </c>
       <c r="Q20" t="n">
-        <v>3320</v>
+        <v>30400</v>
       </c>
       <c r="R20" t="n">
-        <v>-1134000</v>
+        <v>-69000</v>
       </c>
       <c r="S20" t="n">
-        <v>-151000</v>
+        <v>68000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>계약 체결 공시 확인, 공매도 관련 언급 있으나 차트상 긍정적 전망.</t>
+          <t>미국 원전 협력 및 발전 5사 통합 가능성에 대한 기대감. SMP 급락 및 정부 정책 변화에 따른 주가 변동성.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['공시', '계약체결', '공매도']</t>
+          <t>['원전협력', '발전5사통합', 'SMP']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>33850</v>
+        <v>19650</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-1.60%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="E21" t="n">
-        <v>119</v>
+        <v>219</v>
       </c>
       <c r="F21" t="n">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="G21" t="n">
-        <v>271</v>
+        <v>737</v>
       </c>
       <c r="H21" t="n">
-        <v>52.59</v>
+        <v>10.85</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>34100</v>
+        <v>19970</v>
       </c>
       <c r="K21" t="n">
-        <v>34450</v>
+        <v>20250</v>
       </c>
       <c r="L21" t="n">
-        <v>35325</v>
+        <v>21300</v>
       </c>
       <c r="M21" t="n">
-        <v>33750</v>
+        <v>19630</v>
       </c>
       <c r="N21" t="n">
-        <v>21.01</v>
+        <v>10.47</v>
       </c>
       <c r="O21" t="n">
-        <v>72345336125</v>
+        <v>251895259610</v>
       </c>
       <c r="P21" t="n">
-        <v>69500</v>
+        <v>40350</v>
       </c>
       <c r="Q21" t="n">
-        <v>30400</v>
+        <v>3320</v>
       </c>
       <c r="R21" t="n">
-        <v>-69000</v>
+        <v>-1134000</v>
       </c>
       <c r="S21" t="n">
-        <v>68000</v>
+        <v>-151000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 원전 협력 기대감과 25조 선납매 언급. SMP 급락 및 공매도 관련 언급.</t>
+          <t>원전 사업 참여 기대감 속 공시 확인 후 주가 하락. 차트상 긍정적 흐름.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '선납매', 'SMP']</t>
+          <t>['원전', '공시', '차트']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2418,13 +2418,13 @@
         <v>0.32</v>
       </c>
       <c r="E22" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F22" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G22" t="n">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="H22" t="n">
         <v>0.9399999999999999</v>
@@ -2450,7 +2450,7 @@
         <v>0.62</v>
       </c>
       <c r="O22" t="n">
-        <v>144027634705</v>
+        <v>145026298515</v>
       </c>
       <c r="P22" t="n">
         <v>15960</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3755</v>
+        <v>3740</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.47%</t>
+          <t>-3.86%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.52</v>
       </c>
       <c r="E23" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F23" t="n">
         <v>51</v>
       </c>
       <c r="G23" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H23" t="n">
         <v>2.08</v>
@@ -2542,7 +2542,7 @@
         <v>1.56</v>
       </c>
       <c r="O23" t="n">
-        <v>64634348454</v>
+        <v>65194789772</v>
       </c>
       <c r="P23" t="n">
         <v>4335</v>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F2" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G2" t="n">
-        <v>1440</v>
+        <v>1502</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29692625055</v>
+        <v>29712696155</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미 FDA 2A상 승인 및 병용 요법 연구 결과 발표 등 긍정적인 뉴스가 다수 확인됨. 특히 다락손라십 대비 우수하다는 비교 결과와 암세포 사멸 효과에 대한 기대감이 높으며, 이를 바탕으로 주가 상승 및 상한가 가능성이 언급됨.</t>
+          <t>FDA 2A상 승인 및 암세포 사멸 관련 획기적 약물 뉴스.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA', '암치료제', '연구 결과']</t>
+          <t>['FDA 2A상', '암세포 사멸', '다락손라십']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="F3" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G3" t="n">
-        <v>334</v>
+        <v>386</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>231191124165</v>
+        <v>232621844225</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -711,23 +711,23 @@
         <v>4020</v>
       </c>
       <c r="R3" t="n">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="S3" t="n">
         <v>19000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 SMR 관련주 폭등에 따른 기대감 속 거래량 부족 및 주포 자금력 의문. 12000원 돌파 시 추가 상승 전망.</t>
+          <t>미국 SMR 및 가스터빈 관련주 폭등 수혜 기대. 80% 품절주 및 정부 대미 투자 1호 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['SMR', '주포', '가스터빈']</t>
+          <t>['SMR', '가스터빈', '품절주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37821456075</v>
+        <v>37855311285</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13950</v>
+        <v>13700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+18.12%</t>
+          <t>+16.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="F5" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G5" t="n">
-        <v>1341</v>
+        <v>1426</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>461562890735</v>
+        <v>468995254055</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -895,10 +895,10 @@
         <v>3540</v>
       </c>
       <c r="R5" t="n">
-        <v>294000</v>
+        <v>392000</v>
       </c>
       <c r="S5" t="n">
-        <v>73000</v>
+        <v>82000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -931,79 +931,79 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>현대바이오</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2525</v>
+        <v>7160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+16.90%</t>
+          <t>+14.38%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.23</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="G6" t="n">
-        <v>201</v>
+        <v>1184</v>
       </c>
       <c r="H6" t="n">
-        <v>5.26</v>
+        <v>7.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2160</v>
+        <v>6260</v>
       </c>
       <c r="K6" t="n">
-        <v>2200</v>
+        <v>6200</v>
       </c>
       <c r="L6" t="n">
-        <v>2705</v>
+        <v>7730</v>
       </c>
       <c r="M6" t="n">
-        <v>2200</v>
+        <v>6140</v>
       </c>
       <c r="N6" t="n">
-        <v>5.49</v>
+        <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>33277793878</v>
+        <v>68989792020</v>
       </c>
       <c r="P6" t="n">
-        <v>2705</v>
+        <v>21500</v>
       </c>
       <c r="Q6" t="n">
-        <v>1418</v>
+        <v>4565</v>
       </c>
       <c r="R6" t="n">
-        <v>-166000</v>
+        <v>-471000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>경영권 분쟁 및 지분 싸움 가능성, 엔비디아 관련 루머 및 단기 과열 언급.</t>
+          <t>뎅기열 중간 발표 및 오가노이드 실험 결과에 대한 기대감. 다락손라십 췌장암 치료제 및 페니트리움 항암 치료제 개발 진행.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['지분싸움', '엔비디아', '경영권']</t>
+          <t>['뎅기열', '오가노이드', '항암 치료제']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,91 +1011,91 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>048410</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>현대바이오</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7210</v>
+        <v>2430</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+15.18%</t>
+          <t>+12.50%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>-0.23</v>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="F7" t="n">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>1127</v>
+        <v>240</v>
       </c>
       <c r="H7" t="n">
-        <v>7.4</v>
+        <v>5.26</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6260</v>
+        <v>2160</v>
       </c>
       <c r="K7" t="n">
-        <v>6200</v>
+        <v>2200</v>
       </c>
       <c r="L7" t="n">
-        <v>7730</v>
+        <v>2705</v>
       </c>
       <c r="M7" t="n">
-        <v>6140</v>
+        <v>2200</v>
       </c>
       <c r="N7" t="n">
-        <v>7.35</v>
+        <v>5.49</v>
       </c>
       <c r="O7" t="n">
-        <v>68323496895</v>
+        <v>36615516621</v>
       </c>
       <c r="P7" t="n">
-        <v>21500</v>
+        <v>2705</v>
       </c>
       <c r="Q7" t="n">
-        <v>4565</v>
+        <v>1418</v>
       </c>
       <c r="R7" t="n">
-        <v>-509000</v>
+        <v>22000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>페니트리움바이오 관련 긍정적 데이터 발표 기대감. 공매도 세력과의 주가 방어 및 거래량 증가.</t>
+          <t>경영권 분쟁 및 지분 싸움 가능성, 엔비디아 관련 루머 및 단기 과열 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['페니트리움바이오', '공매도', '항암치료제']</t>
+          <t>['지분싸움', '엔비디아', '경영권']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>048410</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54100</v>
+        <v>53300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>+8.22%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F8" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G8" t="n">
-        <v>543</v>
+        <v>579</v>
       </c>
       <c r="H8" t="n">
         <v>14.96</v>
@@ -1162,7 +1162,7 @@
         <v>14.93</v>
       </c>
       <c r="O8" t="n">
-        <v>157198226750</v>
+        <v>160999870450</v>
       </c>
       <c r="P8" t="n">
         <v>108900</v>
@@ -1171,23 +1171,23 @@
         <v>18230</v>
       </c>
       <c r="R8" t="n">
-        <v>-220000</v>
+        <v>-215000</v>
       </c>
       <c r="S8" t="n">
-        <v>135000</v>
+        <v>154000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2분기 영업이익 적자에도 불구하고 높은 목표가 제시. 외인 매도세 속 기관 매수 기대.</t>
+          <t>수주 확정 및 2분기 영업이익 악화에도 불구하고 향후 매출 성장성 및 목표 주가 상향 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['영업이익', '목표가', '기관매수']</t>
+          <t>['수주 확정', '매출 성장성', '목표 주가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14800</v>
+        <v>14730</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.03%</t>
+          <t>+7.52%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.39</v>
       </c>
       <c r="E9" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F9" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G9" t="n">
-        <v>1327</v>
+        <v>1368</v>
       </c>
       <c r="H9" t="n">
         <v>1.55</v>
@@ -1254,7 +1254,7 @@
         <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>416488535615</v>
+        <v>422097736005</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1263,23 +1263,23 @@
         <v>1252</v>
       </c>
       <c r="R9" t="n">
-        <v>488000</v>
+        <v>590000</v>
       </c>
       <c r="S9" t="n">
         <v>20000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>단기 박스권 돌파 및 상승 추세 전망. 차트 분석 기반 가격 상승 기대.</t>
+          <t>단기 박스권 돌파 및 2만 원 목표, 긍정적 차트 분석.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['차트 분석', '상승 추세', '단기 박스권']</t>
+          <t>['박스권 돌파', '차트 분석', '우상향']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6750</v>
+        <v>31550</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.98%</t>
+          <t>+6.05%</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>655</v>
+      </c>
+      <c r="F10" t="n">
+        <v>241</v>
+      </c>
+      <c r="G10" t="n">
+        <v>914</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.31</v>
       </c>
-      <c r="E10" t="n">
-        <v>345</v>
-      </c>
-      <c r="F10" t="n">
-        <v>159</v>
-      </c>
-      <c r="G10" t="n">
-        <v>512</v>
-      </c>
-      <c r="H10" t="n">
-        <v>16.71</v>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6430</v>
+        <v>29750</v>
       </c>
       <c r="K10" t="n">
-        <v>6400</v>
+        <v>31600</v>
       </c>
       <c r="L10" t="n">
-        <v>7470</v>
+        <v>34200</v>
       </c>
       <c r="M10" t="n">
-        <v>6250</v>
+        <v>28300</v>
       </c>
       <c r="N10" t="n">
-        <v>16.4</v>
+        <v>0.23</v>
       </c>
       <c r="O10" t="n">
-        <v>97249601370</v>
+        <v>481347456925</v>
       </c>
       <c r="P10" t="n">
-        <v>13000</v>
+        <v>39350</v>
       </c>
       <c r="Q10" t="n">
-        <v>6030</v>
+        <v>8200</v>
       </c>
       <c r="R10" t="n">
-        <v>-684000</v>
+        <v>-1000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>주가 폭락 가능성과 600억 배당의 상반된 평가. 공매도 세력과의 주가 방어 시도.</t>
+          <t>혈압 반지에 대한 유럽 진출 뉴스 및 2차 파동 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['배당', '공매도', '주주환원']</t>
+          <t>['혈압 반지', '유럽 진출', '2차 파동']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,99 +1384,99 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7980</v>
+        <v>6780</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.91%</t>
+          <t>+5.44%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>0.31</v>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>344</v>
       </c>
       <c r="F11" t="n">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="G11" t="n">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="H11" t="n">
-        <v>1.81</v>
+        <v>16.71</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7680</v>
+        <v>6430</v>
       </c>
       <c r="K11" t="n">
-        <v>7780</v>
+        <v>6400</v>
       </c>
       <c r="L11" t="n">
-        <v>9000</v>
+        <v>7470</v>
       </c>
       <c r="M11" t="n">
-        <v>7750</v>
+        <v>6250</v>
       </c>
       <c r="N11" t="n">
-        <v>0.41</v>
+        <v>16.4</v>
       </c>
       <c r="O11" t="n">
-        <v>112939264480</v>
+        <v>98026458320</v>
       </c>
       <c r="P11" t="n">
-        <v>10300</v>
+        <v>13000</v>
       </c>
       <c r="Q11" t="n">
-        <v>952</v>
+        <v>6030</v>
       </c>
       <c r="R11" t="n">
-        <v>-210000</v>
+        <v>-679000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>레미콘 파업 관련 기대감 및 강한 지지선 언급, 당일 상승 추세.</t>
+          <t>주가 하락 예상 및 공매도 관련 언급. 배당금 지급에도 불구하고 주가 하락 가능성에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['레미콘', '파업', '지지선']</t>
+          <t>['주가 하락', '공매도', '배당금']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3775</v>
+        <v>3790</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.71%</t>
+          <t>+4.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2.74</v>
       </c>
       <c r="E12" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="F12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G12" t="n">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H12" t="n">
         <v>3.19</v>
@@ -1530,7 +1530,7 @@
         <v>0.45</v>
       </c>
       <c r="O12" t="n">
-        <v>269615574874</v>
+        <v>271692994567</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1539,7 +1539,7 @@
         <v>592</v>
       </c>
       <c r="R12" t="n">
-        <v>-816000</v>
+        <v>-731000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1575,215 +1575,215 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1859000</v>
+        <v>1980</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.68%</t>
+          <t>+3.02%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>795</v>
+        <v>115</v>
       </c>
       <c r="F13" t="n">
-        <v>452</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>1755</v>
+        <v>269</v>
       </c>
       <c r="H13" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1793000</v>
+        <v>1922</v>
       </c>
       <c r="K13" t="n">
-        <v>1795000</v>
+        <v>1920</v>
       </c>
       <c r="L13" t="n">
-        <v>1883000</v>
+        <v>2165</v>
       </c>
       <c r="M13" t="n">
-        <v>1795000</v>
+        <v>1862</v>
       </c>
       <c r="N13" t="n">
-        <v>50.63</v>
+        <v>0.61</v>
       </c>
       <c r="O13" t="n">
-        <v>4974924459500</v>
+        <v>16932829192</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q13" t="n">
-        <v>277000</v>
+        <v>910</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수세 유입 속 200만원 돌파 기대감. 단기 차익 매물 소화 후 상승 전망.</t>
+          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외국인매수', '기관매수', '200만원돌파']</t>
+          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1991</v>
+        <v>1842000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.59%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>112</v>
+        <v>793</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>439</v>
       </c>
       <c r="G14" t="n">
-        <v>263</v>
+        <v>1680</v>
       </c>
       <c r="H14" t="n">
-        <v>0.51</v>
+        <v>50.66</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1922</v>
+        <v>1793000</v>
       </c>
       <c r="K14" t="n">
-        <v>1920</v>
+        <v>1795000</v>
       </c>
       <c r="L14" t="n">
-        <v>2165</v>
+        <v>1883000</v>
       </c>
       <c r="M14" t="n">
-        <v>1862</v>
+        <v>1795000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.61</v>
+        <v>50.63</v>
       </c>
       <c r="O14" t="n">
-        <v>16656079360</v>
+        <v>5283333654500</v>
       </c>
       <c r="P14" t="n">
-        <v>2930</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>910</v>
+        <v>277000</v>
       </c>
       <c r="R14" t="n">
-        <v>106000</v>
+        <v>180000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
+          <t>외인 매수세 유입 및 프로그램 매수세 확인. 호가창 가벼움과 250 목표 주가 달성 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
+          <t>['외인 매수', '프로그램 매수', '목표 주가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30700</v>
+        <v>7880</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.19%</t>
+          <t>+2.60%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.08</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
-        <v>645</v>
+        <v>123</v>
       </c>
       <c r="F15" t="n">
-        <v>237</v>
+        <v>77</v>
       </c>
       <c r="G15" t="n">
-        <v>894</v>
+        <v>340</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31</v>
+        <v>1.81</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>29750</v>
+        <v>7680</v>
       </c>
       <c r="K15" t="n">
-        <v>31600</v>
+        <v>7780</v>
       </c>
       <c r="L15" t="n">
-        <v>34200</v>
+        <v>9000</v>
       </c>
       <c r="M15" t="n">
-        <v>28300</v>
+        <v>7750</v>
       </c>
       <c r="N15" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="O15" t="n">
-        <v>466747258850</v>
+        <v>114868266545</v>
       </c>
       <c r="P15" t="n">
-        <v>39350</v>
+        <v>10300</v>
       </c>
       <c r="Q15" t="n">
-        <v>8200</v>
+        <v>952</v>
       </c>
       <c r="R15" t="n">
-        <v>-1000</v>
+        <v>-211000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>혈압계 반지 관련 유럽 진출 뉴스에 따른 기대감. 상장폐지 우려와 함께 2차 파동 시작 전망.</t>
+          <t>강력한 지지선 확인 및 상승 추세 기대. 레미콘 파업 이슈와 연계된 긍정적 주가 움직임 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['혈압계', '유럽진출', '2차파동']</t>
+          <t>['지지선', '상승 추세', '레미콘 파업']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>92000</v>
+        <v>12220</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.79%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.02</v>
+        <v>-2.16</v>
       </c>
       <c r="E16" t="n">
-        <v>325</v>
+        <v>181</v>
       </c>
       <c r="F16" t="n">
-        <v>212</v>
+        <v>103</v>
       </c>
       <c r="G16" t="n">
-        <v>1636</v>
+        <v>409</v>
       </c>
       <c r="H16" t="n">
-        <v>23.61</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>89500</v>
+        <v>11990</v>
       </c>
       <c r="K16" t="n">
-        <v>92000</v>
+        <v>12440</v>
       </c>
       <c r="L16" t="n">
-        <v>94400</v>
+        <v>12800</v>
       </c>
       <c r="M16" t="n">
-        <v>91300</v>
+        <v>11920</v>
       </c>
       <c r="N16" t="n">
-        <v>23.63</v>
+        <v>2.16</v>
       </c>
       <c r="O16" t="n">
-        <v>283027184000</v>
+        <v>45249632925</v>
       </c>
       <c r="P16" t="n">
-        <v>139200</v>
+        <v>36200</v>
       </c>
       <c r="Q16" t="n">
-        <v>57000</v>
+        <v>8920</v>
       </c>
       <c r="R16" t="n">
-        <v>103000</v>
+        <v>22000</v>
       </c>
       <c r="S16" t="n">
-        <v>66000</v>
+        <v>-6000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
+          <t>국제 유가 급등에도 불구하고 주가 변동성 없음. 이란 유조선 공격 관련 지정학적 리스크 및 브렌트유 100달러 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '한-프랑스']</t>
+          <t>['국제 유가', '지정학적 리스크', '브렌트유']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12130</v>
+        <v>91100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>+1.79%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-2.16</v>
+        <v>-0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>174</v>
+        <v>333</v>
       </c>
       <c r="F17" t="n">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="G17" t="n">
-        <v>382</v>
+        <v>1671</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>23.61</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>11990</v>
+        <v>89500</v>
       </c>
       <c r="K17" t="n">
-        <v>12440</v>
+        <v>92000</v>
       </c>
       <c r="L17" t="n">
-        <v>12800</v>
+        <v>94400</v>
       </c>
       <c r="M17" t="n">
-        <v>11920</v>
+        <v>91100</v>
       </c>
       <c r="N17" t="n">
-        <v>2.16</v>
+        <v>23.63</v>
       </c>
       <c r="O17" t="n">
-        <v>43941251465</v>
+        <v>297112392200</v>
       </c>
       <c r="P17" t="n">
-        <v>36200</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>8920</v>
+        <v>57000</v>
       </c>
       <c r="R17" t="n">
-        <v>27000</v>
+        <v>123000</v>
       </c>
       <c r="S17" t="n">
-        <v>-6000</v>
+        <v>96000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>국제 유가 급등에도 불구하고 주가는 큰 변동이 없는 상황. 지정학적 리스크(후티, 사우디, 이란 유조선 공격 등)와 유가 상승 뉴스가 지속적으로 언급되나, 실제 주가 움직임은 이를 반영하지 못하고 있음. 향후 유가 100달러 돌파 여부가 관건.</t>
+          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적 리스크', '주가']</t>
+          <t>['원전', 'SMR', '한-프랑스']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>270250</v>
+        <v>8950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="E18" t="n">
-        <v>786</v>
+        <v>119</v>
       </c>
       <c r="F18" t="n">
-        <v>480</v>
+        <v>67</v>
       </c>
       <c r="G18" t="n">
-        <v>1526</v>
+        <v>487</v>
       </c>
       <c r="H18" t="n">
-        <v>46.85</v>
+        <v>27.69</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,91 +2067,91 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="K18" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="L18" t="n">
-        <v>275000</v>
+        <v>9070</v>
       </c>
       <c r="M18" t="n">
-        <v>268500</v>
+        <v>8710</v>
       </c>
       <c r="N18" t="n">
-        <v>46.79</v>
+        <v>28.05</v>
       </c>
       <c r="O18" t="n">
-        <v>3219942808500</v>
+        <v>29801862235</v>
       </c>
       <c r="P18" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q18" t="n">
-        <v>70000</v>
+        <v>8120</v>
       </c>
       <c r="R18" t="n">
-        <v>-1252000</v>
+        <v>-309000</v>
       </c>
       <c r="S18" t="n">
-        <v>720000</v>
+        <v>7000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>SK하이닉스와의 주가 격차 확대에 대한 실망감. 자사주 매입 및 공매도 관련 비판.</t>
+          <t>중국산 제품 경쟁력 및 부정적 전망. 주주 불만 및 기업의 낮은 주가 관리 능력 지적. AI 관련 언급은 있으나 구체적 호재는 부재.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '자사주매입', '공매도']</t>
+          <t>['중국산', '주가관리', 'AI']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8960</v>
+        <v>267750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.36</v>
+        <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>789</v>
       </c>
       <c r="F19" t="n">
-        <v>66</v>
+        <v>481</v>
       </c>
       <c r="G19" t="n">
-        <v>467</v>
+        <v>1578</v>
       </c>
       <c r="H19" t="n">
-        <v>27.69</v>
+        <v>46.85</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,60 +2159,60 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="K19" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="L19" t="n">
-        <v>9070</v>
+        <v>275000</v>
       </c>
       <c r="M19" t="n">
-        <v>8710</v>
+        <v>267500</v>
       </c>
       <c r="N19" t="n">
-        <v>28.05</v>
+        <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>28389680550</v>
+        <v>3476334513750</v>
       </c>
       <c r="P19" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q19" t="n">
-        <v>8120</v>
+        <v>70000</v>
       </c>
       <c r="R19" t="n">
-        <v>-481000</v>
+        <v>-1876000</v>
       </c>
       <c r="S19" t="n">
-        <v>5000</v>
+        <v>784000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>중국산 제품 경쟁력 및 부정적 전망. 주주 불만 및 기업의 낮은 주가 관리 능력 지적. AI 관련 언급은 있으나 구체적 호재는 부재.</t>
+          <t>하이닉스와의 주가 격차 및 경쟁력 약화에 대한 부정적 평가. 노조 관련 이슈 및 자사주 매입 필요성 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['중국산', '주가관리', 'AI']</t>
+          <t>['주가 격차', '경쟁력', '자사주 매입']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2223,27 +2223,27 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33600</v>
+        <v>33550</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F20" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G20" t="n">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="H20" t="n">
-        <v>52.58</v>
+        <v>52.57</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>21.01</v>
       </c>
       <c r="O20" t="n">
-        <v>75764847575</v>
+        <v>79019619150</v>
       </c>
       <c r="P20" t="n">
         <v>69500</v>
@@ -2275,23 +2275,23 @@
         <v>30400</v>
       </c>
       <c r="R20" t="n">
-        <v>-69000</v>
+        <v>-80000</v>
       </c>
       <c r="S20" t="n">
-        <v>68000</v>
+        <v>58000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 원전 협력 및 발전 5사 통합 가능성에 대한 기대감. SMP 급락 및 정부 정책 변화에 따른 주가 변동성.</t>
+          <t>미국 원전 협력 및 한전기술 움직임 관련 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전협력', '발전5사통합', 'SMP']</t>
+          <t>['원전', 'Smp', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19650</v>
+        <v>19430</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.60%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.38</v>
       </c>
       <c r="E21" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="F21" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G21" t="n">
         <v>737</v>
@@ -2352,13 +2352,13 @@
         <v>21300</v>
       </c>
       <c r="M21" t="n">
-        <v>19630</v>
+        <v>19390</v>
       </c>
       <c r="N21" t="n">
         <v>10.47</v>
       </c>
       <c r="O21" t="n">
-        <v>251895259610</v>
+        <v>265922653500</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2367,14 +2367,14 @@
         <v>3320</v>
       </c>
       <c r="R21" t="n">
-        <v>-1134000</v>
+        <v>-1107000</v>
       </c>
       <c r="S21" t="n">
-        <v>-151000</v>
+        <v>-209000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전 사업 참여 기대감 속 공시 확인 후 주가 하락. 차트상 긍정적 흐름.</t>
+          <t>미국 원전 사업 참여 기대감. 계약 체결 공시 확인 및 차트 분석 기반 긍정적 전망.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '공시', '차트']</t>
+          <t>['원전 사업', '계약 체결', '차트 분석']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10140</v>
+        <v>10120</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.32</v>
       </c>
       <c r="E22" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F22" t="n">
         <v>71</v>
       </c>
       <c r="G22" t="n">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="H22" t="n">
         <v>0.9399999999999999</v>
@@ -2450,7 +2450,7 @@
         <v>0.62</v>
       </c>
       <c r="O22" t="n">
-        <v>145026298515</v>
+        <v>145997429785</v>
       </c>
       <c r="P22" t="n">
         <v>15960</v>
@@ -2459,7 +2459,7 @@
         <v>3500</v>
       </c>
       <c r="R22" t="n">
-        <v>-11000</v>
+        <v>-50000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3740</v>
+        <v>3720</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.86%</t>
+          <t>-4.37%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.52</v>
       </c>
       <c r="E23" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="H23" t="n">
         <v>2.08</v>
@@ -2542,7 +2542,7 @@
         <v>1.56</v>
       </c>
       <c r="O23" t="n">
-        <v>65194789772</v>
+        <v>66063714110</v>
       </c>
       <c r="P23" t="n">
         <v>4335</v>
@@ -2551,7 +2551,7 @@
         <v>1246</v>
       </c>
       <c r="R23" t="n">
-        <v>-519000</v>
+        <v>-599000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F2" t="n">
         <v>132</v>
       </c>
       <c r="G2" t="n">
-        <v>1502</v>
+        <v>1544</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29712696155</v>
+        <v>29716539715</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>FDA 2A상 승인 및 암세포 사멸 관련 획기적 약물 뉴스.</t>
+          <t>미 FDA 2A상 승인 및 병용요법 관련 후속 연구 결과 공개 기대감. 외인 매수세 유입 및 거래량 증가.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA 2A상', '암세포 사멸', '다락손라십']</t>
+          <t>['FDA 2A상', '병용요법', '암치료제']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F3" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G3" t="n">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>232621844225</v>
+        <v>232859628695</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 SMR 및 가스터빈 관련주 폭등 수혜 기대. 80% 품절주 및 정부 대미 투자 1호 관련 긍정적 전망.</t>
+          <t>미국 SMR 및 원전 관련 수혜 기대감, 품절주 및 높은 변동성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['SMR', '가스터빈', '품절주']</t>
+          <t>['SMR', '원전', '품절주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37855311285</v>
+        <v>37915610745</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13700</v>
+        <v>13730</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.00%</t>
+          <t>+16.26%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F5" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G5" t="n">
-        <v>1426</v>
+        <v>1436</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>468995254055</v>
+        <v>473665586735</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7160</v>
+        <v>7180</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.38%</t>
+          <t>+14.70%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F6" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G6" t="n">
-        <v>1184</v>
+        <v>1211</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>68989792020</v>
+        <v>69202433730</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2430</v>
+        <v>53600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+12.50%</t>
+          <t>+8.83%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.23</v>
+        <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>121</v>
       </c>
       <c r="G7" t="n">
-        <v>240</v>
+        <v>595</v>
       </c>
       <c r="H7" t="n">
-        <v>5.26</v>
+        <v>14.96</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,143 +1055,143 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2160</v>
+        <v>49250</v>
       </c>
       <c r="K7" t="n">
-        <v>2200</v>
+        <v>53500</v>
       </c>
       <c r="L7" t="n">
-        <v>2705</v>
+        <v>59000</v>
       </c>
       <c r="M7" t="n">
-        <v>2200</v>
+        <v>51600</v>
       </c>
       <c r="N7" t="n">
-        <v>5.49</v>
+        <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>36615516621</v>
+        <v>162020745400</v>
       </c>
       <c r="P7" t="n">
-        <v>2705</v>
+        <v>108900</v>
       </c>
       <c r="Q7" t="n">
-        <v>1418</v>
+        <v>18230</v>
       </c>
       <c r="R7" t="n">
-        <v>22000</v>
+        <v>-215000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>경영권 분쟁 및 지분 싸움 가능성, 엔비디아 관련 루머 및 단기 과열 언급.</t>
+          <t>수주 기대감 속 목표가 상향 전망, 일부 부정적 실적 발표에도 기대감 유지.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['지분싸움', '엔비디아', '경영권']</t>
+          <t>['수주', '목표가', '매출성장성']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53300</v>
+        <v>14760</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.22%</t>
+          <t>+7.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.03</v>
+        <v>-0.39</v>
       </c>
       <c r="E8" t="n">
-        <v>155</v>
+        <v>249</v>
       </c>
       <c r="F8" t="n">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G8" t="n">
-        <v>579</v>
+        <v>1396</v>
       </c>
       <c r="H8" t="n">
-        <v>14.96</v>
+        <v>1.55</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>49250</v>
+        <v>13700</v>
       </c>
       <c r="K8" t="n">
-        <v>53500</v>
+        <v>14260</v>
       </c>
       <c r="L8" t="n">
-        <v>59000</v>
+        <v>15860</v>
       </c>
       <c r="M8" t="n">
-        <v>51600</v>
+        <v>14210</v>
       </c>
       <c r="N8" t="n">
-        <v>14.93</v>
+        <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>160999870450</v>
+        <v>424072532190</v>
       </c>
       <c r="P8" t="n">
-        <v>108900</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>18230</v>
+        <v>1252</v>
       </c>
       <c r="R8" t="n">
-        <v>-215000</v>
+        <v>590000</v>
       </c>
       <c r="S8" t="n">
-        <v>154000</v>
+        <v>20000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>수주 확정 및 2분기 영업이익 악화에도 불구하고 향후 매출 성장성 및 목표 주가 상향 전망.</t>
+          <t>단기 박스권 돌파 및 불기둥 형성, 2만 목표 상향 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주 확정', '매출 성장성', '목표 주가']</t>
+          <t>['불기둥', '박스권돌파', '우상향']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14730</v>
+        <v>2300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.52%</t>
+          <t>+6.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.39</v>
+        <v>-0.23</v>
       </c>
       <c r="E9" t="n">
-        <v>244</v>
+        <v>127</v>
       </c>
       <c r="F9" t="n">
-        <v>150</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
-        <v>1368</v>
+        <v>278</v>
       </c>
       <c r="H9" t="n">
-        <v>1.55</v>
+        <v>5.26</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13700</v>
+        <v>2160</v>
       </c>
       <c r="K9" t="n">
-        <v>14260</v>
+        <v>2200</v>
       </c>
       <c r="L9" t="n">
-        <v>15860</v>
+        <v>2705</v>
       </c>
       <c r="M9" t="n">
-        <v>14210</v>
+        <v>2200</v>
       </c>
       <c r="N9" t="n">
-        <v>1.94</v>
+        <v>5.49</v>
       </c>
       <c r="O9" t="n">
-        <v>422097736005</v>
+        <v>39330742400</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>2705</v>
       </c>
       <c r="Q9" t="n">
-        <v>1252</v>
+        <v>1418</v>
       </c>
       <c r="R9" t="n">
-        <v>590000</v>
+        <v>22000</v>
       </c>
       <c r="S9" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>단기 박스권 돌파 및 2만 원 목표, 긍정적 차트 분석.</t>
+          <t>기타법인 매수세 유입 속 지분 싸움 및 단기 과열 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['박스권 돌파', '차트 분석', '우상향']</t>
+          <t>['PBR', '지분싸움', '기타법인']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31550</v>
+        <v>6820</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.05%</t>
+          <t>+6.07%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.08</v>
+        <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>655</v>
+        <v>345</v>
       </c>
       <c r="F10" t="n">
-        <v>241</v>
+        <v>155</v>
       </c>
       <c r="G10" t="n">
-        <v>914</v>
+        <v>538</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31</v>
+        <v>16.71</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>29750</v>
+        <v>6430</v>
       </c>
       <c r="K10" t="n">
-        <v>31600</v>
+        <v>6400</v>
       </c>
       <c r="L10" t="n">
-        <v>34200</v>
+        <v>7470</v>
       </c>
       <c r="M10" t="n">
-        <v>28300</v>
+        <v>6250</v>
       </c>
       <c r="N10" t="n">
-        <v>0.23</v>
+        <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>481347456925</v>
+        <v>98818522280</v>
       </c>
       <c r="P10" t="n">
-        <v>39350</v>
+        <v>13000</v>
       </c>
       <c r="Q10" t="n">
-        <v>8200</v>
+        <v>6030</v>
       </c>
       <c r="R10" t="n">
-        <v>-1000</v>
+        <v>-679000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>혈압 반지에 대한 유럽 진출 뉴스 및 2차 파동 전망.</t>
+          <t>주가 하락 예상 및 공매도 관련 언급. 배당금 지급에도 불구하고 주가 하락 가능성에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['혈압 반지', '유럽 진출', '2차 파동']</t>
+          <t>['주가 하락', '공매도', '배당금']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6780</v>
+        <v>31000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.44%</t>
+          <t>+4.20%</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>673</v>
+      </c>
+      <c r="F11" t="n">
+        <v>248</v>
+      </c>
+      <c r="G11" t="n">
+        <v>952</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.31</v>
       </c>
-      <c r="E11" t="n">
-        <v>344</v>
-      </c>
-      <c r="F11" t="n">
-        <v>156</v>
-      </c>
-      <c r="G11" t="n">
-        <v>538</v>
-      </c>
-      <c r="H11" t="n">
-        <v>16.71</v>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6430</v>
+        <v>29750</v>
       </c>
       <c r="K11" t="n">
-        <v>6400</v>
+        <v>31600</v>
       </c>
       <c r="L11" t="n">
-        <v>7470</v>
+        <v>34200</v>
       </c>
       <c r="M11" t="n">
-        <v>6250</v>
+        <v>28300</v>
       </c>
       <c r="N11" t="n">
-        <v>16.4</v>
+        <v>0.23</v>
       </c>
       <c r="O11" t="n">
-        <v>98026458320</v>
+        <v>492789306325</v>
       </c>
       <c r="P11" t="n">
-        <v>13000</v>
+        <v>39350</v>
       </c>
       <c r="Q11" t="n">
-        <v>6030</v>
+        <v>8200</v>
       </c>
       <c r="R11" t="n">
-        <v>-679000</v>
+        <v>-1000</v>
       </c>
       <c r="S11" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 하락 예상 및 공매도 관련 언급. 배당금 지급에도 불구하고 주가 하락 가능성에 대한 우려 제기.</t>
+          <t>혈압 반지 관련 유럽 진출 뉴스 및 2차 파동 시작 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '배당금']</t>
+          <t>['혈압반지', '유럽진출', '2차파동']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3790</v>
+        <v>3780</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.12%</t>
+          <t>+3.85%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2.74</v>
       </c>
       <c r="E12" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F12" t="n">
         <v>124</v>
       </c>
       <c r="G12" t="n">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="H12" t="n">
         <v>3.19</v>
@@ -1530,7 +1530,7 @@
         <v>0.45</v>
       </c>
       <c r="O12" t="n">
-        <v>271692994567</v>
+        <v>272260110861</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1575,267 +1575,267 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1980</v>
+        <v>1849000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.02%</t>
+          <t>+3.12%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>115</v>
+        <v>791</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>433</v>
       </c>
       <c r="G13" t="n">
-        <v>269</v>
+        <v>1692</v>
       </c>
       <c r="H13" t="n">
-        <v>0.51</v>
+        <v>50.66</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1922</v>
+        <v>1793000</v>
       </c>
       <c r="K13" t="n">
-        <v>1920</v>
+        <v>1795000</v>
       </c>
       <c r="L13" t="n">
-        <v>2165</v>
+        <v>1883000</v>
       </c>
       <c r="M13" t="n">
-        <v>1862</v>
+        <v>1795000</v>
       </c>
       <c r="N13" t="n">
-        <v>0.61</v>
+        <v>50.63</v>
       </c>
       <c r="O13" t="n">
-        <v>16932829192</v>
+        <v>5441594671000</v>
       </c>
       <c r="P13" t="n">
-        <v>2930</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>910</v>
+        <v>277000</v>
       </c>
       <c r="R13" t="n">
-        <v>154000</v>
+        <v>180000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
+          <t>외인 매수세 지속 및 상승 추세 전환 신호 포착, 190 돌파 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
+          <t>['외인매수', '상승추세', '자사주매입']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1842000</v>
+        <v>1974</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+2.73%</t>
+          <t>+2.71%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>793</v>
+        <v>118</v>
       </c>
       <c r="F14" t="n">
-        <v>439</v>
+        <v>47</v>
       </c>
       <c r="G14" t="n">
-        <v>1680</v>
+        <v>275</v>
       </c>
       <c r="H14" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1793000</v>
+        <v>1922</v>
       </c>
       <c r="K14" t="n">
-        <v>1795000</v>
+        <v>1920</v>
       </c>
       <c r="L14" t="n">
-        <v>1883000</v>
+        <v>2165</v>
       </c>
       <c r="M14" t="n">
-        <v>1795000</v>
+        <v>1862</v>
       </c>
       <c r="N14" t="n">
-        <v>50.63</v>
+        <v>0.61</v>
       </c>
       <c r="O14" t="n">
-        <v>5283333654500</v>
+        <v>17055578141</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q14" t="n">
-        <v>277000</v>
+        <v>910</v>
       </c>
       <c r="R14" t="n">
-        <v>180000</v>
+        <v>154000</v>
       </c>
       <c r="S14" t="n">
-        <v>151000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외인 매수세 유입 및 프로그램 매수세 확인. 호가창 가벼움과 250 목표 주가 달성 기대감.</t>
+          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외인 매수', '프로그램 매수', '목표 주가']</t>
+          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7880</v>
+        <v>91300</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.60%</t>
+          <t>+2.01%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.4</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>123</v>
+        <v>343</v>
       </c>
       <c r="F15" t="n">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="G15" t="n">
-        <v>340</v>
+        <v>1690</v>
       </c>
       <c r="H15" t="n">
-        <v>1.81</v>
+        <v>23.61</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7680</v>
+        <v>89500</v>
       </c>
       <c r="K15" t="n">
-        <v>7780</v>
+        <v>92000</v>
       </c>
       <c r="L15" t="n">
-        <v>9000</v>
+        <v>94400</v>
       </c>
       <c r="M15" t="n">
-        <v>7750</v>
+        <v>91100</v>
       </c>
       <c r="N15" t="n">
-        <v>0.41</v>
+        <v>23.63</v>
       </c>
       <c r="O15" t="n">
-        <v>114868266545</v>
+        <v>305586070500</v>
       </c>
       <c r="P15" t="n">
-        <v>10300</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>952</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-211000</v>
+        <v>123000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>강력한 지지선 확인 및 상승 추세 기대. 레미콘 파업 이슈와 연계된 긍정적 주가 움직임 전망.</t>
+          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['지지선', '상승 추세', '레미콘 파업']</t>
+          <t>['원전', 'SMR', '한-프랑스']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12220</v>
+        <v>7830</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-2.16</v>
+        <v>1.4</v>
       </c>
       <c r="E16" t="n">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="F16" t="n">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="G16" t="n">
-        <v>409</v>
+        <v>353</v>
       </c>
       <c r="H16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>7680</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7780</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>7750</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="O16" t="n">
+        <v>116026744840</v>
+      </c>
+      <c r="P16" t="n">
+        <v>10300</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>952</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-211000</v>
+      </c>
+      <c r="S16" t="n">
         <v>0</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>11990</v>
-      </c>
-      <c r="K16" t="n">
-        <v>12440</v>
-      </c>
-      <c r="L16" t="n">
-        <v>12800</v>
-      </c>
-      <c r="M16" t="n">
-        <v>11920</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="O16" t="n">
-        <v>45249632925</v>
-      </c>
-      <c r="P16" t="n">
-        <v>36200</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>8920</v>
-      </c>
-      <c r="R16" t="n">
-        <v>22000</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-6000</v>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>국제 유가 급등에도 불구하고 주가 변동성 없음. 이란 유조선 공격 관련 지정학적 리스크 및 브렌트유 100달러 돌파 가능성 언급.</t>
+          <t>레미콘 파업 및 강한 지지선 구간, 상한가 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['국제 유가', '지정학적 리스크', '브렌트유']</t>
+          <t>['레미콘', '지지선', '상한가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>91100</v>
+        <v>12140</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.02</v>
+        <v>-2.16</v>
       </c>
       <c r="E17" t="n">
-        <v>333</v>
+        <v>182</v>
       </c>
       <c r="F17" t="n">
-        <v>216</v>
+        <v>103</v>
       </c>
       <c r="G17" t="n">
-        <v>1671</v>
+        <v>410</v>
       </c>
       <c r="H17" t="n">
-        <v>23.61</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>89500</v>
+        <v>11990</v>
       </c>
       <c r="K17" t="n">
-        <v>92000</v>
+        <v>12440</v>
       </c>
       <c r="L17" t="n">
-        <v>94400</v>
+        <v>12800</v>
       </c>
       <c r="M17" t="n">
-        <v>91100</v>
+        <v>11920</v>
       </c>
       <c r="N17" t="n">
-        <v>23.63</v>
+        <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>297112392200</v>
+        <v>45702533465</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>36200</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>8920</v>
       </c>
       <c r="R17" t="n">
-        <v>123000</v>
+        <v>22000</v>
       </c>
       <c r="S17" t="n">
-        <v>96000</v>
+        <v>-6000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
+          <t>국제 유가 급등에도 불구하고 주가 변동성 없음. 이란 유조선 공격 관련 지정학적 리스크 및 브렌트유 100달러 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '한-프랑스']</t>
+          <t>['국제 유가', '지정학적 리스크', '브렌트유']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8950</v>
+        <v>8960</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.36</v>
       </c>
       <c r="E18" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F18" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G18" t="n">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="H18" t="n">
         <v>27.69</v>
@@ -2082,7 +2082,7 @@
         <v>28.05</v>
       </c>
       <c r="O18" t="n">
-        <v>29801862235</v>
+        <v>31181080545</v>
       </c>
       <c r="P18" t="n">
         <v>17950</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>중국산 제품 경쟁력 및 부정적 전망. 주주 불만 및 기업의 낮은 주가 관리 능력 지적. AI 관련 언급은 있으나 구체적 호재는 부재.</t>
+          <t>AI 관련 기대감 있으나, 개인 투자자 매수 집중 및 기업 성장성 의문 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['중국산', '주가관리', 'AI']</t>
+          <t>['AI', '개인투자자', '성장성']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>267750</v>
+        <v>268750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F19" t="n">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="G19" t="n">
-        <v>1578</v>
+        <v>1682</v>
       </c>
       <c r="H19" t="n">
         <v>46.85</v>
@@ -2174,7 +2174,7 @@
         <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>3476334513750</v>
+        <v>3611520617000</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>하이닉스와의 주가 격차 및 경쟁력 약화에 대한 부정적 평가. 노조 관련 이슈 및 자사주 매입 필요성 언급.</t>
+          <t>노조 이슈 및 하이닉스와의 주가 비교 속 부정적 전망.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주가 격차', '경쟁력', '자사주 매입']</t>
+          <t>['노조', '하이닉스', '주가']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33550</v>
+        <v>33600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F20" t="n">
         <v>64</v>
       </c>
       <c r="G20" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H20" t="n">
         <v>52.57</v>
@@ -2266,7 +2266,7 @@
         <v>21.01</v>
       </c>
       <c r="O20" t="n">
-        <v>79019619150</v>
+        <v>80963310875</v>
       </c>
       <c r="P20" t="n">
         <v>69500</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19430</v>
+        <v>19410</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>-2.80%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.38</v>
       </c>
       <c r="E21" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="F21" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G21" t="n">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="H21" t="n">
         <v>10.85</v>
@@ -2352,13 +2352,13 @@
         <v>21300</v>
       </c>
       <c r="M21" t="n">
-        <v>19390</v>
+        <v>19350</v>
       </c>
       <c r="N21" t="n">
         <v>10.47</v>
       </c>
       <c r="O21" t="n">
-        <v>265922653500</v>
+        <v>271933828105</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 원전 사업 참여 기대감. 계약 체결 공시 확인 및 차트 분석 기반 긍정적 전망.</t>
+          <t>원전 관련 호재 속 계약 체결 공시 확인, 일부 투자자 기대감.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전 사업', '계약 체결', '차트 분석']</t>
+          <t>['원전', '공시', '계약체결']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10120</v>
+        <v>10090</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.32</v>
       </c>
       <c r="E22" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F22" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G22" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H22" t="n">
         <v>0.9399999999999999</v>
@@ -2450,7 +2450,7 @@
         <v>0.62</v>
       </c>
       <c r="O22" t="n">
-        <v>145997429785</v>
+        <v>146494818395</v>
       </c>
       <c r="P22" t="n">
         <v>15960</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3720</v>
+        <v>3740</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.37%</t>
+          <t>-3.86%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.52</v>
       </c>
       <c r="E23" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F23" t="n">
         <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H23" t="n">
         <v>2.08</v>
@@ -2542,7 +2542,7 @@
         <v>1.56</v>
       </c>
       <c r="O23" t="n">
-        <v>66063714110</v>
+        <v>66503090377</v>
       </c>
       <c r="P23" t="n">
         <v>4335</v>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G2" t="n">
-        <v>1544</v>
+        <v>1564</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29716539715</v>
+        <v>29737412175</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미 FDA 2A상 승인 및 병용요법 관련 후속 연구 결과 공개 기대감. 외인 매수세 유입 및 거래량 증가.</t>
+          <t>미 FDA 2A상 승인 및 다락손라십 대비 우수한 효능 확인. 5연상 기대감 고조.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA 2A상', '병용요법', '암치료제']</t>
+          <t>['FDA', '암치료제', '효능']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G3" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>232859628695</v>
+        <v>233014216615</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 SMR 및 원전 관련 수혜 기대감, 품절주 및 높은 변동성.</t>
+          <t>미국 증시 SMR 관련주 동반 급등 및 품절주 특징 부각. 신규 재료 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['SMR', '원전', '품절주']</t>
+          <t>['SMR', '품절주', '재료']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37915610745</v>
+        <v>37934650605</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13730</v>
+        <v>13930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.26%</t>
+          <t>+17.95%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="F5" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G5" t="n">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>473665586735</v>
+        <v>477472931945</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7180</v>
+        <v>7190</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.70%</t>
+          <t>+14.86%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F6" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G6" t="n">
-        <v>1211</v>
+        <v>1260</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>69202433730</v>
+        <v>69494672970</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뎅기열 중간 발표 및 오가노이드 실험 결과에 대한 기대감. 다락손라십 췌장암 치료제 및 페니트리움 항암 치료제 개발 진행.</t>
+          <t>뎅기열 치료제 및 췌장암 치료제 관련 데이터 발표 기대. 공매도와의 경쟁 심화.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['뎅기열', '오가노이드', '항암 치료제']</t>
+          <t>['뎅기열', '췌장암', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53600</v>
+        <v>53800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.83%</t>
+          <t>+9.24%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F7" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G7" t="n">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="H7" t="n">
         <v>14.96</v>
@@ -1070,7 +1070,7 @@
         <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>162020745400</v>
+        <v>163034458000</v>
       </c>
       <c r="P7" t="n">
         <v>108900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>수주 기대감 속 목표가 상향 전망, 일부 부정적 실적 발표에도 기대감 유지.</t>
+          <t>대규모 수주 및 2분기 영업이익 흑자 전환 기대감. 목표가 상향 논의 활발.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '목표가', '매출성장성']</t>
+          <t>['수주', '영업이익', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14760</v>
+        <v>14870</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.74%</t>
+          <t>+8.54%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.39</v>
       </c>
       <c r="E8" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F8" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G8" t="n">
-        <v>1396</v>
+        <v>1423</v>
       </c>
       <c r="H8" t="n">
         <v>1.55</v>
@@ -1162,7 +1162,7 @@
         <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>424072532190</v>
+        <v>427323960390</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2300</v>
+        <v>6820</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.48%</t>
+          <t>+6.07%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.23</v>
+        <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>127</v>
+        <v>347</v>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>155</v>
       </c>
       <c r="G9" t="n">
-        <v>278</v>
+        <v>545</v>
       </c>
       <c r="H9" t="n">
-        <v>5.26</v>
+        <v>16.71</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2160</v>
+        <v>6430</v>
       </c>
       <c r="K9" t="n">
-        <v>2200</v>
+        <v>6400</v>
       </c>
       <c r="L9" t="n">
-        <v>2705</v>
+        <v>7470</v>
       </c>
       <c r="M9" t="n">
-        <v>2200</v>
+        <v>6250</v>
       </c>
       <c r="N9" t="n">
-        <v>5.49</v>
+        <v>16.4</v>
       </c>
       <c r="O9" t="n">
-        <v>39330742400</v>
+        <v>99305201865</v>
       </c>
       <c r="P9" t="n">
-        <v>2705</v>
+        <v>13000</v>
       </c>
       <c r="Q9" t="n">
-        <v>1418</v>
+        <v>6030</v>
       </c>
       <c r="R9" t="n">
-        <v>22000</v>
+        <v>-679000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>기타법인 매수세 유입 속 지분 싸움 및 단기 과열 기대감.</t>
+          <t>주가 하락 예상 및 공매도 관련 언급. 배당금 지급에도 불구하고 주가 하락 가능성에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['PBR', '지분싸움', '기타법인']</t>
+          <t>['주가 하락', '공매도', '배당금']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6820</v>
+        <v>31250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.07%</t>
+          <t>+5.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>694</v>
+      </c>
+      <c r="F10" t="n">
+        <v>251</v>
+      </c>
+      <c r="G10" t="n">
+        <v>993</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.31</v>
       </c>
-      <c r="E10" t="n">
-        <v>345</v>
-      </c>
-      <c r="F10" t="n">
-        <v>155</v>
-      </c>
-      <c r="G10" t="n">
-        <v>538</v>
-      </c>
-      <c r="H10" t="n">
-        <v>16.71</v>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6430</v>
+        <v>29750</v>
       </c>
       <c r="K10" t="n">
-        <v>6400</v>
+        <v>31600</v>
       </c>
       <c r="L10" t="n">
-        <v>7470</v>
+        <v>34200</v>
       </c>
       <c r="M10" t="n">
-        <v>6250</v>
+        <v>28300</v>
       </c>
       <c r="N10" t="n">
-        <v>16.4</v>
+        <v>0.23</v>
       </c>
       <c r="O10" t="n">
-        <v>98818522280</v>
+        <v>508127145875</v>
       </c>
       <c r="P10" t="n">
-        <v>13000</v>
+        <v>39350</v>
       </c>
       <c r="Q10" t="n">
-        <v>6030</v>
+        <v>8200</v>
       </c>
       <c r="R10" t="n">
-        <v>-679000</v>
+        <v>-1000</v>
       </c>
       <c r="S10" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>주가 하락 예상 및 공매도 관련 언급. 배당금 지급에도 불구하고 주가 하락 가능성에 대한 우려 제기.</t>
+          <t>세계 최초 혈압 반지의 유럽 진출 뉴스 확인. 최저점 매수 논의 및 2차 파동 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '배당금']</t>
+          <t>['혈압반지', '유럽진출', '최저점']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31000</v>
+        <v>2245</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.20%</t>
+          <t>+3.94%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.08</v>
+        <v>-0.23</v>
       </c>
       <c r="E11" t="n">
-        <v>673</v>
+        <v>147</v>
       </c>
       <c r="F11" t="n">
-        <v>248</v>
+        <v>72</v>
       </c>
       <c r="G11" t="n">
-        <v>952</v>
+        <v>314</v>
       </c>
       <c r="H11" t="n">
-        <v>0.31</v>
+        <v>5.26</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>29750</v>
+        <v>2160</v>
       </c>
       <c r="K11" t="n">
-        <v>31600</v>
+        <v>2200</v>
       </c>
       <c r="L11" t="n">
-        <v>34200</v>
+        <v>2705</v>
       </c>
       <c r="M11" t="n">
-        <v>28300</v>
+        <v>2200</v>
       </c>
       <c r="N11" t="n">
-        <v>0.23</v>
+        <v>5.49</v>
       </c>
       <c r="O11" t="n">
-        <v>492789306325</v>
+        <v>41787657462</v>
       </c>
       <c r="P11" t="n">
-        <v>39350</v>
+        <v>2705</v>
       </c>
       <c r="Q11" t="n">
-        <v>8200</v>
+        <v>1418</v>
       </c>
       <c r="R11" t="n">
-        <v>-1000</v>
+        <v>22000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>혈압 반지 관련 유럽 진출 뉴스 및 2차 파동 시작 기대감.</t>
+          <t>기타 법인 장내 매수세 유입 및 지분 싸움 기대감. 단기 과열 우려도 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['혈압반지', '유럽진출', '2차파동']</t>
+          <t>['PBR', '지분싸움', '기타법인']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -1498,13 +1498,13 @@
         <v>2.74</v>
       </c>
       <c r="E12" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="F12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G12" t="n">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="H12" t="n">
         <v>3.19</v>
@@ -1530,7 +1530,7 @@
         <v>0.45</v>
       </c>
       <c r="O12" t="n">
-        <v>272260110861</v>
+        <v>273083000735</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1575,184 +1575,184 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1849000</v>
+        <v>1986</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.12%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>791</v>
+        <v>118</v>
       </c>
       <c r="F13" t="n">
-        <v>433</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>1692</v>
+        <v>277</v>
       </c>
       <c r="H13" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1793000</v>
+        <v>1922</v>
       </c>
       <c r="K13" t="n">
-        <v>1795000</v>
+        <v>1920</v>
       </c>
       <c r="L13" t="n">
-        <v>1883000</v>
+        <v>2165</v>
       </c>
       <c r="M13" t="n">
-        <v>1795000</v>
+        <v>1862</v>
       </c>
       <c r="N13" t="n">
-        <v>50.63</v>
+        <v>0.61</v>
       </c>
       <c r="O13" t="n">
-        <v>5441594671000</v>
+        <v>17132888371</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q13" t="n">
-        <v>277000</v>
+        <v>910</v>
       </c>
       <c r="R13" t="n">
-        <v>180000</v>
+        <v>154000</v>
       </c>
       <c r="S13" t="n">
-        <v>151000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외인 매수세 지속 및 상승 추세 전환 신호 포착, 190 돌파 기대감.</t>
+          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외인매수', '상승추세', '자사주매입']</t>
+          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1974</v>
+        <v>1851000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>118</v>
+        <v>792</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>438</v>
       </c>
       <c r="G14" t="n">
-        <v>275</v>
+        <v>1711</v>
       </c>
       <c r="H14" t="n">
-        <v>0.51</v>
+        <v>50.66</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1922</v>
+        <v>1793000</v>
       </c>
       <c r="K14" t="n">
-        <v>1920</v>
+        <v>1795000</v>
       </c>
       <c r="L14" t="n">
-        <v>2165</v>
+        <v>1883000</v>
       </c>
       <c r="M14" t="n">
-        <v>1862</v>
+        <v>1795000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.61</v>
+        <v>50.63</v>
       </c>
       <c r="O14" t="n">
-        <v>17055578141</v>
+        <v>5555893967500</v>
       </c>
       <c r="P14" t="n">
-        <v>2930</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>910</v>
+        <v>277000</v>
       </c>
       <c r="R14" t="n">
-        <v>154000</v>
+        <v>180000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
+          <t>외국인 및 기관의 지속적인 매수세 유입 확인. 상승 추세 전환 신호 및 악성 매물 소화 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
+          <t>['외인매수', '상승추세', '악성매물']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>91300</v>
+        <v>91600</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.01%</t>
+          <t>+2.35%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="F15" t="n">
         <v>221</v>
       </c>
       <c r="G15" t="n">
-        <v>1690</v>
+        <v>1711</v>
       </c>
       <c r="H15" t="n">
         <v>23.61</v>
@@ -1806,7 +1806,7 @@
         <v>23.63</v>
       </c>
       <c r="O15" t="n">
-        <v>305586070500</v>
+        <v>309774192850</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7830</v>
+        <v>7730</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1.4</v>
       </c>
       <c r="E16" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F16" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G16" t="n">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="H16" t="n">
         <v>1.81</v>
@@ -1892,13 +1892,13 @@
         <v>9000</v>
       </c>
       <c r="M16" t="n">
-        <v>7750</v>
+        <v>7690</v>
       </c>
       <c r="N16" t="n">
         <v>0.41</v>
       </c>
       <c r="O16" t="n">
-        <v>116026744840</v>
+        <v>117384898455</v>
       </c>
       <c r="P16" t="n">
         <v>10300</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>레미콘 파업 및 강한 지지선 구간, 상한가 기대감.</t>
+          <t>레미콘 파업 시작 및 대장주로서의 강세 기대. 하지만 전반적인 상승 동력은 약함.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['레미콘', '지지선', '상한가']</t>
+          <t>['레미콘', '대장주', '파업']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12140</v>
+        <v>12050</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.25%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-2.16</v>
       </c>
       <c r="E17" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F17" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G17" t="n">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>45702533465</v>
+        <v>46532096305</v>
       </c>
       <c r="P17" t="n">
         <v>36200</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8960</v>
+        <v>8945</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.36</v>
       </c>
       <c r="E18" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F18" t="n">
         <v>68</v>
       </c>
       <c r="G18" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="H18" t="n">
         <v>27.69</v>
@@ -2082,7 +2082,7 @@
         <v>28.05</v>
       </c>
       <c r="O18" t="n">
-        <v>31181080545</v>
+        <v>31730490160</v>
       </c>
       <c r="P18" t="n">
         <v>17950</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2142,13 +2142,13 @@
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="F19" t="n">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="G19" t="n">
-        <v>1682</v>
+        <v>1770</v>
       </c>
       <c r="H19" t="n">
         <v>46.85</v>
@@ -2174,7 +2174,7 @@
         <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>3611520617000</v>
+        <v>3672169233250</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>노조 이슈 및 하이닉스와의 주가 비교 속 부정적 전망.</t>
+          <t>하이닉스와의 주가 비교 열세 및 경영진에 대한 부정적 의견 대두.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['노조', '하이닉스', '주가']</t>
+          <t>['하이닉스', '주가', '경영진']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33600</v>
+        <v>33625</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F20" t="n">
         <v>64</v>
       </c>
       <c r="G20" t="n">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="H20" t="n">
         <v>52.57</v>
@@ -2266,7 +2266,7 @@
         <v>21.01</v>
       </c>
       <c r="O20" t="n">
-        <v>80963310875</v>
+        <v>82740620325</v>
       </c>
       <c r="P20" t="n">
         <v>69500</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 원전 협력 및 한전기술 움직임 관련 언급.</t>
+          <t>한국-프랑스 차세대 원전 협력 뉴스 및 25조 선납매 논의. 공매도 세력의 움직임 주시.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', 'Smp', '공매도']</t>
+          <t>['원전', '선납매', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19410</v>
+        <v>19420</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.80%</t>
+          <t>-2.75%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.38</v>
       </c>
       <c r="E21" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F21" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G21" t="n">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="H21" t="n">
         <v>10.85</v>
@@ -2358,7 +2358,7 @@
         <v>10.47</v>
       </c>
       <c r="O21" t="n">
-        <v>271933828105</v>
+        <v>276765273045</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2403,70 +2403,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10090</v>
+        <v>3750</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>-3.60%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.32</v>
+        <v>0.52</v>
       </c>
       <c r="E22" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F22" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
-        <v>229</v>
+        <v>196</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.08</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10440</v>
+        <v>3890</v>
       </c>
       <c r="K22" t="n">
-        <v>10180</v>
+        <v>3890</v>
       </c>
       <c r="L22" t="n">
-        <v>11340</v>
+        <v>4115</v>
       </c>
       <c r="M22" t="n">
-        <v>9980</v>
+        <v>3700</v>
       </c>
       <c r="N22" t="n">
-        <v>0.62</v>
+        <v>1.56</v>
       </c>
       <c r="O22" t="n">
-        <v>146494818395</v>
+        <v>66740430704</v>
       </c>
       <c r="P22" t="n">
-        <v>15960</v>
+        <v>4335</v>
       </c>
       <c r="Q22" t="n">
-        <v>3500</v>
+        <v>1246</v>
       </c>
       <c r="R22" t="n">
-        <v>-50000</v>
+        <v>-599000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미증시 제약바이오와는 다른 움직임, 탈모주 관련 기대감 있으나 구체적인 재료 및 공시 부재.</t>
+          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['탈모주', '재료']</t>
+          <t>['탈모주', '하락']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,77 +2488,77 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3740</v>
+        <v>10040</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.86%</t>
+          <t>-3.83%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.52</v>
+        <v>0.32</v>
       </c>
       <c r="E23" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G23" t="n">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="H23" t="n">
-        <v>2.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3890</v>
+        <v>10440</v>
       </c>
       <c r="K23" t="n">
-        <v>3890</v>
+        <v>10180</v>
       </c>
       <c r="L23" t="n">
-        <v>4115</v>
+        <v>11340</v>
       </c>
       <c r="M23" t="n">
-        <v>3700</v>
+        <v>9980</v>
       </c>
       <c r="N23" t="n">
-        <v>1.56</v>
+        <v>0.62</v>
       </c>
       <c r="O23" t="n">
-        <v>66503090377</v>
+        <v>146950594215</v>
       </c>
       <c r="P23" t="n">
-        <v>4335</v>
+        <v>15960</v>
       </c>
       <c r="Q23" t="n">
-        <v>1246</v>
+        <v>3500</v>
       </c>
       <c r="R23" t="n">
-        <v>-599000</v>
+        <v>-50000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
+          <t>미증시 제약바이오와는 다른 움직임, 탈모주 관련 기대감 있으나 구체적인 재료 및 공시 부재.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['탈모주', '하락']</t>
+          <t>['탈모주', '재료']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>004310</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G2" t="n">
-        <v>1564</v>
+        <v>1599</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29737412175</v>
+        <v>29742101615</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미 FDA 2A상 승인 및 다락손라십 대비 우수한 효능 확인. 5연상 기대감 고조.</t>
+          <t>미 FDA 2A상 승인, 병용요법 연구 결과 공개, 암치료제 획기적 효능 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA', '암치료제', '효능']</t>
+          <t>['FDA', '암치료제']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3" t="n">
         <v>105</v>
       </c>
       <c r="G3" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>233014216615</v>
+        <v>233176179515</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 증시 SMR 관련주 동반 급등 및 품절주 특징 부각. 신규 재료 기대감.</t>
+          <t>미국 증시 SMR 관련주 폭등, 가스터빈 대장, 물량 이슈.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['SMR', '품절주', '재료']</t>
+          <t>['SMR', '가스터빈']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37934650605</v>
+        <v>37946312355</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13930</v>
+        <v>13880</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.95%</t>
+          <t>+17.53%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F5" t="n">
         <v>163</v>
       </c>
       <c r="G5" t="n">
-        <v>1442</v>
+        <v>1456</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>477472931945</v>
+        <v>482707675585</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7190</v>
+        <v>7270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.86%</t>
+          <t>+16.13%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F6" t="n">
         <v>112</v>
       </c>
       <c r="G6" t="n">
-        <v>1260</v>
+        <v>1274</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>69494672970</v>
+        <v>70094505380</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53800</v>
+        <v>53700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.24%</t>
+          <t>+9.04%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F7" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G7" t="n">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H7" t="n">
         <v>14.96</v>
@@ -1070,7 +1070,7 @@
         <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>163034458000</v>
+        <v>163987257000</v>
       </c>
       <c r="P7" t="n">
         <v>108900</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14870</v>
+        <v>14910</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.54%</t>
+          <t>+8.83%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.39</v>
       </c>
       <c r="E8" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F8" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G8" t="n">
-        <v>1423</v>
+        <v>1444</v>
       </c>
       <c r="H8" t="n">
         <v>1.55</v>
@@ -1162,7 +1162,7 @@
         <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>427323960390</v>
+        <v>432641911245</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6820</v>
+        <v>6810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.07%</t>
+          <t>+5.91%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F9" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G9" t="n">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="H9" t="n">
         <v>16.71</v>
@@ -1254,7 +1254,7 @@
         <v>16.4</v>
       </c>
       <c r="O9" t="n">
-        <v>99305201865</v>
+        <v>99652661920</v>
       </c>
       <c r="P9" t="n">
         <v>13000</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31250</v>
+        <v>3805</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.04%</t>
+          <t>+4.53%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.08</v>
+        <v>2.74</v>
       </c>
       <c r="E10" t="n">
-        <v>694</v>
+        <v>230</v>
       </c>
       <c r="F10" t="n">
-        <v>251</v>
+        <v>128</v>
       </c>
       <c r="G10" t="n">
-        <v>993</v>
+        <v>523</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31</v>
+        <v>3.19</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>29750</v>
+        <v>3640</v>
       </c>
       <c r="K10" t="n">
-        <v>31600</v>
+        <v>3750</v>
       </c>
       <c r="L10" t="n">
-        <v>34200</v>
+        <v>4460</v>
       </c>
       <c r="M10" t="n">
-        <v>28300</v>
+        <v>3680</v>
       </c>
       <c r="N10" t="n">
-        <v>0.23</v>
+        <v>0.45</v>
       </c>
       <c r="O10" t="n">
-        <v>508127145875</v>
+        <v>273965701912</v>
       </c>
       <c r="P10" t="n">
-        <v>39350</v>
+        <v>8100</v>
       </c>
       <c r="Q10" t="n">
-        <v>8200</v>
+        <v>592</v>
       </c>
       <c r="R10" t="n">
-        <v>-1000</v>
+        <v>-731000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>세계 최초 혈압 반지의 유럽 진출 뉴스 확인. 최저점 매수 논의 및 2차 파동 기대.</t>
+          <t>미국 광통신 폭등 관련, 6G 기반, 국책사업 선정 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['혈압반지', '유럽진출', '최저점']</t>
+          <t>['광통신', '6G']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,130 +1384,130 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2245</v>
+        <v>1998</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.94%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.23</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="F11" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="H11" t="n">
-        <v>5.26</v>
+        <v>0.51</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2160</v>
+        <v>1922</v>
       </c>
       <c r="K11" t="n">
-        <v>2200</v>
+        <v>1920</v>
       </c>
       <c r="L11" t="n">
-        <v>2705</v>
+        <v>2165</v>
       </c>
       <c r="M11" t="n">
-        <v>2200</v>
+        <v>1862</v>
       </c>
       <c r="N11" t="n">
-        <v>5.49</v>
+        <v>0.61</v>
       </c>
       <c r="O11" t="n">
-        <v>41787657462</v>
+        <v>17347678072</v>
       </c>
       <c r="P11" t="n">
-        <v>2705</v>
+        <v>2930</v>
       </c>
       <c r="Q11" t="n">
-        <v>1418</v>
+        <v>910</v>
       </c>
       <c r="R11" t="n">
-        <v>22000</v>
+        <v>154000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기타 법인 장내 매수세 유입 및 지분 싸움 기대감. 단기 과열 우려도 존재.</t>
+          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['PBR', '지분싸움', '기타법인']</t>
+          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3780</v>
+        <v>30850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.85%</t>
+          <t>+3.70%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.74</v>
+        <v>0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>229</v>
+        <v>705</v>
       </c>
       <c r="F12" t="n">
-        <v>127</v>
+        <v>250</v>
       </c>
       <c r="G12" t="n">
-        <v>514</v>
+        <v>1012</v>
       </c>
       <c r="H12" t="n">
-        <v>3.19</v>
+        <v>0.31</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3640</v>
+        <v>29750</v>
       </c>
       <c r="K12" t="n">
-        <v>3750</v>
+        <v>31600</v>
       </c>
       <c r="L12" t="n">
-        <v>4460</v>
+        <v>34200</v>
       </c>
       <c r="M12" t="n">
-        <v>3680</v>
+        <v>28300</v>
       </c>
       <c r="N12" t="n">
-        <v>0.45</v>
+        <v>0.23</v>
       </c>
       <c r="O12" t="n">
-        <v>273083000735</v>
+        <v>516227295575</v>
       </c>
       <c r="P12" t="n">
-        <v>8100</v>
+        <v>39350</v>
       </c>
       <c r="Q12" t="n">
-        <v>592</v>
+        <v>8200</v>
       </c>
       <c r="R12" t="n">
-        <v>-731000</v>
+        <v>-1000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 광통신 산업 급등에 따른 기대감. 투기 과열 종목 지정 우려 및 6G 기반 성장성.</t>
+          <t>세계 최초 혈압 반지, 유럽 진출 뉴스, 1차 파동 조정 후 2차 파동 시작 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '6G', '투기과열']</t>
+          <t>['혈압 반지', '유럽 진출']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,130 +1568,130 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1986</v>
+        <v>1852000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.33%</t>
+          <t>+3.29%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>118</v>
+        <v>791</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>445</v>
       </c>
       <c r="G13" t="n">
-        <v>277</v>
+        <v>1692</v>
       </c>
       <c r="H13" t="n">
-        <v>0.51</v>
+        <v>50.66</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1922</v>
+        <v>1793000</v>
       </c>
       <c r="K13" t="n">
-        <v>1920</v>
+        <v>1795000</v>
       </c>
       <c r="L13" t="n">
-        <v>2165</v>
+        <v>1883000</v>
       </c>
       <c r="M13" t="n">
-        <v>1862</v>
+        <v>1795000</v>
       </c>
       <c r="N13" t="n">
-        <v>0.61</v>
+        <v>50.63</v>
       </c>
       <c r="O13" t="n">
-        <v>17132888371</v>
+        <v>5678214655000</v>
       </c>
       <c r="P13" t="n">
-        <v>2930</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>910</v>
+        <v>277000</v>
       </c>
       <c r="R13" t="n">
-        <v>154000</v>
+        <v>180000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
+          <t>상승 추세 전환 신호, 외인/기관 매수세 유입, 악성매물 소화.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
+          <t>['상승 추세', '외인 매수', '악성매물']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1851000</v>
+        <v>91800</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.23%</t>
+          <t>+2.57%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>792</v>
+        <v>353</v>
       </c>
       <c r="F14" t="n">
-        <v>438</v>
+        <v>224</v>
       </c>
       <c r="G14" t="n">
-        <v>1711</v>
+        <v>1727</v>
       </c>
       <c r="H14" t="n">
-        <v>50.66</v>
+        <v>23.61</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1793000</v>
+        <v>89500</v>
       </c>
       <c r="K14" t="n">
-        <v>1795000</v>
+        <v>92000</v>
       </c>
       <c r="L14" t="n">
-        <v>1883000</v>
+        <v>94400</v>
       </c>
       <c r="M14" t="n">
-        <v>1795000</v>
+        <v>91100</v>
       </c>
       <c r="N14" t="n">
-        <v>50.63</v>
+        <v>23.63</v>
       </c>
       <c r="O14" t="n">
-        <v>5555893967500</v>
+        <v>314743516850</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>277000</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>180000</v>
+        <v>123000</v>
       </c>
       <c r="S14" t="n">
-        <v>151000</v>
+        <v>96000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외국인 및 기관의 지속적인 매수세 유입 확인. 상승 추세 전환 신호 및 악성 매물 소화 기대.</t>
+          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외인매수', '상승추세', '악성매물']</t>
+          <t>['원전', 'SMR', '한-프랑스']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>91600</v>
+        <v>7860</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.35%</t>
+          <t>+2.34%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.02</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
-        <v>348</v>
+        <v>143</v>
       </c>
       <c r="F15" t="n">
-        <v>221</v>
+        <v>85</v>
       </c>
       <c r="G15" t="n">
-        <v>1711</v>
+        <v>381</v>
       </c>
       <c r="H15" t="n">
-        <v>23.61</v>
+        <v>1.81</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>89500</v>
+        <v>7680</v>
       </c>
       <c r="K15" t="n">
-        <v>92000</v>
+        <v>7780</v>
       </c>
       <c r="L15" t="n">
-        <v>94400</v>
+        <v>9000</v>
       </c>
       <c r="M15" t="n">
-        <v>91100</v>
+        <v>7690</v>
       </c>
       <c r="N15" t="n">
-        <v>23.63</v>
+        <v>0.41</v>
       </c>
       <c r="O15" t="n">
-        <v>309774192850</v>
+        <v>118313720035</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>10300</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>952</v>
       </c>
       <c r="R15" t="n">
-        <v>123000</v>
+        <v>-211000</v>
       </c>
       <c r="S15" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
+          <t>레미콘 파업 시작 및 대장주로서의 강세 기대. 하지만 전반적인 상승 동력은 약함.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '한-프랑스']</t>
+          <t>['레미콘', '대장주', '파업']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7730</v>
+        <v>2180</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>+0.93%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.4</v>
+        <v>-0.23</v>
       </c>
       <c r="E16" t="n">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="F16" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G16" t="n">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="H16" t="n">
-        <v>1.81</v>
+        <v>5.26</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7680</v>
+        <v>2160</v>
       </c>
       <c r="K16" t="n">
-        <v>7780</v>
+        <v>2200</v>
       </c>
       <c r="L16" t="n">
-        <v>9000</v>
+        <v>2705</v>
       </c>
       <c r="M16" t="n">
-        <v>7690</v>
+        <v>2180</v>
       </c>
       <c r="N16" t="n">
-        <v>0.41</v>
+        <v>5.49</v>
       </c>
       <c r="O16" t="n">
-        <v>117384898455</v>
+        <v>43156761833</v>
       </c>
       <c r="P16" t="n">
-        <v>10300</v>
+        <v>2705</v>
       </c>
       <c r="Q16" t="n">
-        <v>952</v>
+        <v>1418</v>
       </c>
       <c r="R16" t="n">
-        <v>-211000</v>
+        <v>22000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>레미콘 파업 시작 및 대장주로서의 강세 기대. 하지만 전반적인 상승 동력은 약함.</t>
+          <t>지분 싸움 및 기타법인 장내매수, 단기 목표가 설정.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['레미콘', '대장주', '파업']</t>
+          <t>['지분 싸움', '장내매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12050</v>
+        <v>12070</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-2.16</v>
       </c>
       <c r="E17" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F17" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G17" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>46532096305</v>
+        <v>47867563250</v>
       </c>
       <c r="P17" t="n">
         <v>36200</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8945</v>
+        <v>8980</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.36</v>
       </c>
       <c r="E18" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F18" t="n">
         <v>68</v>
       </c>
       <c r="G18" t="n">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="H18" t="n">
         <v>27.69</v>
@@ -2082,7 +2082,7 @@
         <v>28.05</v>
       </c>
       <c r="O18" t="n">
-        <v>31730490160</v>
+        <v>32684986350</v>
       </c>
       <c r="P18" t="n">
         <v>17950</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>AI 관련 기대감 있으나, 개인 투자자 매수 집중 및 기업 성장성 의문 제기.</t>
+          <t>매도, 중국산 영향, 개인 매수 집중 등 부정적 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['AI', '개인투자자', '성장성']</t>
+          <t>['매도', '중국산']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>268750</v>
+        <v>269500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="F19" t="n">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="G19" t="n">
-        <v>1770</v>
+        <v>1712</v>
       </c>
       <c r="H19" t="n">
         <v>46.85</v>
@@ -2174,7 +2174,7 @@
         <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>3672169233250</v>
+        <v>3766183064250</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>하이닉스와의 주가 비교 열세 및 경영진에 대한 부정적 의견 대두.</t>
+          <t>노조, 이재용 해임, 하이닉스와의 비교 등 부정적 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['하이닉스', '주가', '경영진']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33625</v>
+        <v>33700</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.39%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,13 +2237,13 @@
         <v>132</v>
       </c>
       <c r="F20" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G20" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H20" t="n">
-        <v>52.57</v>
+        <v>52.56</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>21.01</v>
       </c>
       <c r="O20" t="n">
-        <v>82740620325</v>
+        <v>84099487100</v>
       </c>
       <c r="P20" t="n">
         <v>69500</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>한국-프랑스 차세대 원전 협력 뉴스 및 25조 선납매 논의. 공매도 세력의 움직임 주시.</t>
+          <t>미국 원전 협력, 공매도 이슈, SMP 급락 우려.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '선납매', '공매도']</t>
+          <t>['원전', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19420</v>
+        <v>19540</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>-2.15%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.38</v>
       </c>
       <c r="E21" t="n">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F21" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G21" t="n">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="H21" t="n">
         <v>10.85</v>
@@ -2358,7 +2358,7 @@
         <v>10.47</v>
       </c>
       <c r="O21" t="n">
-        <v>276765273045</v>
+        <v>280620347755</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2418,13 +2418,13 @@
         <v>0.52</v>
       </c>
       <c r="E22" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F22" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G22" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H22" t="n">
         <v>2.08</v>
@@ -2450,7 +2450,7 @@
         <v>1.56</v>
       </c>
       <c r="O22" t="n">
-        <v>66740430704</v>
+        <v>66962221584</v>
       </c>
       <c r="P22" t="n">
         <v>4335</v>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10040</v>
+        <v>10060</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.83%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2516,7 +2516,7 @@
         <v>72</v>
       </c>
       <c r="G23" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H23" t="n">
         <v>0.9399999999999999</v>
@@ -2542,7 +2542,7 @@
         <v>0.62</v>
       </c>
       <c r="O23" t="n">
-        <v>146950594215</v>
+        <v>147390691635</v>
       </c>
       <c r="P23" t="n">
         <v>15960</v>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F2" t="n">
         <v>133</v>
       </c>
       <c r="G2" t="n">
-        <v>1599</v>
+        <v>1630</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29742101615</v>
+        <v>29749128355</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미 FDA 2A상 승인, 병용요법 연구 결과 공개, 암치료제 획기적 효능 기대.</t>
+          <t>미 FDA 2A상 승인 및 병용요법 관련 연구 결과 공개 예고. 외인 매수세 유입으로 인한 기대감 형성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA', '암치료제']</t>
+          <t>['FDA 2A상', '병용요법', '연구 결과']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F3" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G3" t="n">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>233176179515</v>
+        <v>233282725825</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 증시 SMR 관련주 폭등, 가스터빈 대장, 물량 이슈.</t>
+          <t>미국 증시 SMR 관련주 폭등에 따른 기대감, 품절주 특성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['SMR', '가스터빈']</t>
+          <t>['SMR', '품절주', '가스터빈']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37946312355</v>
+        <v>37954314615</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13880</v>
+        <v>13960</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.53%</t>
+          <t>+18.20%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1456</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>482707675585</v>
+        <v>487315522485</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7270</v>
+        <v>7200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+16.13%</t>
+          <t>+15.02%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F6" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G6" t="n">
-        <v>1274</v>
+        <v>1301</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>70094505380</v>
+        <v>70629618770</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뎅기열 치료제 및 췌장암 치료제 관련 데이터 발표 기대. 공매도와의 경쟁 심화.</t>
+          <t>뎅기열, 췌장암 치료제 등 신약 개발 기대감 및 공매도와의 경쟁.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['뎅기열', '췌장암', '공매도']</t>
+          <t>['신약 개발', '공매도', '임상 결과']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53700</v>
+        <v>14950</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.04%</t>
+          <t>+9.12%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.03</v>
+        <v>-0.39</v>
       </c>
       <c r="E7" t="n">
-        <v>169</v>
+        <v>273</v>
       </c>
       <c r="F7" t="n">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="G7" t="n">
-        <v>611</v>
+        <v>1484</v>
       </c>
       <c r="H7" t="n">
-        <v>14.96</v>
+        <v>1.55</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>49250</v>
+        <v>13700</v>
       </c>
       <c r="K7" t="n">
-        <v>53500</v>
+        <v>14260</v>
       </c>
       <c r="L7" t="n">
-        <v>59000</v>
+        <v>15860</v>
       </c>
       <c r="M7" t="n">
-        <v>51600</v>
+        <v>14210</v>
       </c>
       <c r="N7" t="n">
-        <v>14.93</v>
+        <v>1.94</v>
       </c>
       <c r="O7" t="n">
-        <v>163987257000</v>
+        <v>437313985410</v>
       </c>
       <c r="P7" t="n">
-        <v>108900</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>18230</v>
+        <v>1252</v>
       </c>
       <c r="R7" t="n">
-        <v>-215000</v>
+        <v>590000</v>
       </c>
       <c r="S7" t="n">
-        <v>154000</v>
+        <v>20000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대규모 수주 및 2분기 영업이익 흑자 전환 기대감. 목표가 상향 논의 활발.</t>
+          <t>단기 박스권 돌파 및 불기둥 형성, 2만 목표 상향 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '영업이익', '목표가']</t>
+          <t>['불기둥', '박스권돌파', '우상향']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14910</v>
+        <v>53500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.83%</t>
+          <t>+8.63%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.39</v>
+        <v>0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>261</v>
+        <v>171</v>
       </c>
       <c r="F8" t="n">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="G8" t="n">
-        <v>1444</v>
+        <v>623</v>
       </c>
       <c r="H8" t="n">
-        <v>1.55</v>
+        <v>14.96</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13700</v>
+        <v>49250</v>
       </c>
       <c r="K8" t="n">
-        <v>14260</v>
+        <v>53500</v>
       </c>
       <c r="L8" t="n">
-        <v>15860</v>
+        <v>59000</v>
       </c>
       <c r="M8" t="n">
-        <v>14210</v>
+        <v>51600</v>
       </c>
       <c r="N8" t="n">
-        <v>1.94</v>
+        <v>14.93</v>
       </c>
       <c r="O8" t="n">
-        <v>432641911245</v>
+        <v>165288875800</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>108900</v>
       </c>
       <c r="Q8" t="n">
-        <v>1252</v>
+        <v>18230</v>
       </c>
       <c r="R8" t="n">
-        <v>590000</v>
+        <v>-215000</v>
       </c>
       <c r="S8" t="n">
-        <v>20000</v>
+        <v>154000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>단기 박스권 돌파 및 불기둥 형성, 2만 목표 상향 기대감.</t>
+          <t>대규모 수주 및 2분기 영업이익 흑자 전환 기대감. 목표가 상향 논의 활발.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['불기둥', '박스권돌파', '우상향']</t>
+          <t>['수주', '영업이익', '목표가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6810</v>
+        <v>6840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.91%</t>
+          <t>+6.38%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F9" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G9" t="n">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="H9" t="n">
         <v>16.71</v>
@@ -1254,7 +1254,7 @@
         <v>16.4</v>
       </c>
       <c r="O9" t="n">
-        <v>99652661920</v>
+        <v>100353110875</v>
       </c>
       <c r="P9" t="n">
         <v>13000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주가 하락 예상 및 공매도 관련 언급. 배당금 지급에도 불구하고 주가 하락 가능성에 대한 우려 제기.</t>
+          <t>배당 관련 논의와 함께 주가 상승 및 하락에 대한 기대감 공존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '배당금']</t>
+          <t>['배당', '주가 상승', '공매']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3805</v>
+        <v>2035</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>+5.88%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.74</v>
+        <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="F10" t="n">
-        <v>128</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>523</v>
+        <v>285</v>
       </c>
       <c r="H10" t="n">
-        <v>3.19</v>
+        <v>0.51</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3640</v>
+        <v>1922</v>
       </c>
       <c r="K10" t="n">
-        <v>3750</v>
+        <v>1920</v>
       </c>
       <c r="L10" t="n">
-        <v>4460</v>
+        <v>2165</v>
       </c>
       <c r="M10" t="n">
-        <v>3680</v>
+        <v>1862</v>
       </c>
       <c r="N10" t="n">
-        <v>0.45</v>
+        <v>0.61</v>
       </c>
       <c r="O10" t="n">
-        <v>273965701912</v>
+        <v>17571997184</v>
       </c>
       <c r="P10" t="n">
-        <v>8100</v>
+        <v>2930</v>
       </c>
       <c r="Q10" t="n">
-        <v>592</v>
+        <v>910</v>
       </c>
       <c r="R10" t="n">
-        <v>-731000</v>
+        <v>154000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 광통신 폭등 관련, 6G 기반, 국책사업 선정 기대.</t>
+          <t>반도체 클러스터 관련 논의 및 주포 동향 주시, 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '6G']</t>
+          <t>['반도체 클러스터', '주포', '텐버거']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1998</v>
+        <v>3800</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+4.40%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.1</v>
+        <v>2.74</v>
       </c>
       <c r="E11" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.51</v>
+        <v>3.19</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1922</v>
+        <v>3640</v>
       </c>
       <c r="K11" t="n">
-        <v>1920</v>
+        <v>3750</v>
       </c>
       <c r="L11" t="n">
-        <v>2165</v>
+        <v>4460</v>
       </c>
       <c r="M11" t="n">
-        <v>1862</v>
+        <v>3680</v>
       </c>
       <c r="N11" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="O11" t="n">
-        <v>17347678072</v>
+        <v>274896197449</v>
       </c>
       <c r="P11" t="n">
-        <v>2930</v>
+        <v>8100</v>
       </c>
       <c r="Q11" t="n">
-        <v>910</v>
+        <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>154000</v>
+        <v>-731000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
+          <t>미국 광통신 폭등 관련, 6G 기반, 국책사업 선정 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
+          <t>['광통신', '6G']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30850</v>
+        <v>1859000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.70%</t>
+          <t>+3.68%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="E12" t="n">
-        <v>705</v>
+        <v>791</v>
       </c>
       <c r="F12" t="n">
-        <v>250</v>
+        <v>438</v>
       </c>
       <c r="G12" t="n">
-        <v>1012</v>
+        <v>1846</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31</v>
+        <v>50.66</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>29750</v>
+        <v>1793000</v>
       </c>
       <c r="K12" t="n">
-        <v>31600</v>
+        <v>1795000</v>
       </c>
       <c r="L12" t="n">
-        <v>34200</v>
+        <v>1883000</v>
       </c>
       <c r="M12" t="n">
-        <v>28300</v>
+        <v>1795000</v>
       </c>
       <c r="N12" t="n">
-        <v>0.23</v>
+        <v>50.63</v>
       </c>
       <c r="O12" t="n">
-        <v>516227295575</v>
+        <v>5776700759500</v>
       </c>
       <c r="P12" t="n">
-        <v>39350</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>8200</v>
+        <v>277000</v>
       </c>
       <c r="R12" t="n">
-        <v>-1000</v>
+        <v>180000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>세계 최초 혈압 반지, 유럽 진출 뉴스, 1차 파동 조정 후 2차 파동 시작 기대.</t>
+          <t>외인 매수세 유입 및 상승 추세 전환 신호 포착, 긍정적 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['혈압 반지', '유럽 진출']</t>
+          <t>['외인 매수', '상승 추세', '호재']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1852000</v>
+        <v>30750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.29%</t>
+          <t>+3.36%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="E13" t="n">
-        <v>791</v>
+        <v>714</v>
       </c>
       <c r="F13" t="n">
-        <v>445</v>
+        <v>252</v>
       </c>
       <c r="G13" t="n">
-        <v>1692</v>
+        <v>1032</v>
       </c>
       <c r="H13" t="n">
-        <v>50.66</v>
+        <v>0.31</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1793000</v>
+        <v>29750</v>
       </c>
       <c r="K13" t="n">
-        <v>1795000</v>
+        <v>31600</v>
       </c>
       <c r="L13" t="n">
-        <v>1883000</v>
+        <v>34200</v>
       </c>
       <c r="M13" t="n">
-        <v>1795000</v>
+        <v>28300</v>
       </c>
       <c r="N13" t="n">
-        <v>50.63</v>
+        <v>0.23</v>
       </c>
       <c r="O13" t="n">
-        <v>5678214655000</v>
+        <v>522764760150</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>39350</v>
       </c>
       <c r="Q13" t="n">
-        <v>277000</v>
+        <v>8200</v>
       </c>
       <c r="R13" t="n">
-        <v>180000</v>
+        <v>-1000</v>
       </c>
       <c r="S13" t="n">
-        <v>151000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>상승 추세 전환 신호, 외인/기관 매수세 유입, 악성매물 소화.</t>
+          <t>혈압계 관련 뉴스 및 유럽 진출 소식, 주가 반등 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['상승 추세', '외인 매수', '악성매물']</t>
+          <t>['혈압계', '유럽 진출', '최저점']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F14" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G14" t="n">
-        <v>1727</v>
+        <v>1739</v>
       </c>
       <c r="H14" t="n">
         <v>23.61</v>
@@ -1714,7 +1714,7 @@
         <v>23.63</v>
       </c>
       <c r="O14" t="n">
-        <v>314743516850</v>
+        <v>319193723450</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1774,13 +1774,13 @@
         <v>1.4</v>
       </c>
       <c r="E15" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F15" t="n">
         <v>85</v>
       </c>
       <c r="G15" t="n">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="H15" t="n">
         <v>1.81</v>
@@ -1806,7 +1806,7 @@
         <v>0.41</v>
       </c>
       <c r="O15" t="n">
-        <v>118313720035</v>
+        <v>119236391540</v>
       </c>
       <c r="P15" t="n">
         <v>10300</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2180</v>
+        <v>2185</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.23</v>
       </c>
       <c r="E16" t="n">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="F16" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G16" t="n">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="H16" t="n">
         <v>5.26</v>
@@ -1892,13 +1892,13 @@
         <v>2705</v>
       </c>
       <c r="M16" t="n">
-        <v>2180</v>
+        <v>2130</v>
       </c>
       <c r="N16" t="n">
         <v>5.49</v>
       </c>
       <c r="O16" t="n">
-        <v>43156761833</v>
+        <v>44640050294</v>
       </c>
       <c r="P16" t="n">
         <v>2705</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>지분 싸움 및 기타법인 장내매수, 단기 목표가 설정.</t>
+          <t>지분 싸움 및 신규 대주주 관련 논의, 단기 목표가 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['지분 싸움', '장내매수']</t>
+          <t>['지분 싸움', '신규 대주주', '단기 목표가']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12070</v>
+        <v>12050</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>105</v>
       </c>
       <c r="G17" t="n">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>47867563250</v>
+        <v>48540091605</v>
       </c>
       <c r="P17" t="n">
         <v>36200</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>국제 유가 급등에도 불구하고 주가 변동성 없음. 이란 유조선 공격 관련 지정학적 리스크 및 브렌트유 100달러 돌파 가능성 언급.</t>
+          <t>국제 유가 급등 및 지정학적 이슈에도 주가 부진, 투자자들의 불만.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['국제 유가', '지정학적 리스크', '브렌트유']</t>
+          <t>['국제 유가', '지정학적 이슈', '주가 부진']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8980</v>
+        <v>270500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.36</v>
+        <v>0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>120</v>
+        <v>763</v>
       </c>
       <c r="F18" t="n">
-        <v>68</v>
+        <v>476</v>
       </c>
       <c r="G18" t="n">
-        <v>510</v>
+        <v>1711</v>
       </c>
       <c r="H18" t="n">
-        <v>27.69</v>
+        <v>46.85</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="K18" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="L18" t="n">
-        <v>9070</v>
+        <v>275000</v>
       </c>
       <c r="M18" t="n">
-        <v>8710</v>
+        <v>267500</v>
       </c>
       <c r="N18" t="n">
-        <v>28.05</v>
+        <v>46.79</v>
       </c>
       <c r="O18" t="n">
-        <v>32684986350</v>
+        <v>3879752757000</v>
       </c>
       <c r="P18" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q18" t="n">
-        <v>8120</v>
+        <v>70000</v>
       </c>
       <c r="R18" t="n">
-        <v>-309000</v>
+        <v>-1876000</v>
       </c>
       <c r="S18" t="n">
-        <v>7000</v>
+        <v>784000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>매도, 중국산 영향, 개인 매수 집중 등 부정적 전망.</t>
+          <t>노조, 경영진 관련 부정적 언급 및 주가 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['매도', '중국산']</t>
+          <t>['노조', '경영진', '주가 부진']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>269500</v>
+        <v>8970</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="E19" t="n">
-        <v>787</v>
+        <v>120</v>
       </c>
       <c r="F19" t="n">
-        <v>491</v>
+        <v>68</v>
       </c>
       <c r="G19" t="n">
-        <v>1712</v>
+        <v>516</v>
       </c>
       <c r="H19" t="n">
-        <v>46.85</v>
+        <v>27.69</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="K19" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="L19" t="n">
-        <v>275000</v>
+        <v>9070</v>
       </c>
       <c r="M19" t="n">
-        <v>267500</v>
+        <v>8710</v>
       </c>
       <c r="N19" t="n">
-        <v>46.79</v>
+        <v>28.05</v>
       </c>
       <c r="O19" t="n">
-        <v>3766183064250</v>
+        <v>33176217140</v>
       </c>
       <c r="P19" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q19" t="n">
-        <v>70000</v>
+        <v>8120</v>
       </c>
       <c r="R19" t="n">
-        <v>-1876000</v>
+        <v>-309000</v>
       </c>
       <c r="S19" t="n">
-        <v>784000</v>
+        <v>7000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>노조, 이재용 해임, 하이닉스와의 비교 등 부정적 언급.</t>
+          <t>기업 실적 및 성장성에 대한 부정적 전망, 투자 비판.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['실적', '성장성', '투자 비판']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
         <v>65</v>
       </c>
       <c r="G20" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H20" t="n">
         <v>52.56</v>
@@ -2266,7 +2266,7 @@
         <v>21.01</v>
       </c>
       <c r="O20" t="n">
-        <v>84099487100</v>
+        <v>85214685575</v>
       </c>
       <c r="P20" t="n">
         <v>69500</v>
@@ -2311,184 +2311,184 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19540</v>
+        <v>3800</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-2.31%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.38</v>
+        <v>0.52</v>
       </c>
       <c r="E21" t="n">
-        <v>245</v>
+        <v>104</v>
       </c>
       <c r="F21" t="n">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="G21" t="n">
-        <v>758</v>
+        <v>197</v>
       </c>
       <c r="H21" t="n">
-        <v>10.85</v>
+        <v>2.08</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>19970</v>
+        <v>3890</v>
       </c>
       <c r="K21" t="n">
-        <v>20250</v>
+        <v>3890</v>
       </c>
       <c r="L21" t="n">
-        <v>21300</v>
+        <v>4115</v>
       </c>
       <c r="M21" t="n">
-        <v>19350</v>
+        <v>3700</v>
       </c>
       <c r="N21" t="n">
-        <v>10.47</v>
+        <v>1.56</v>
       </c>
       <c r="O21" t="n">
-        <v>280620347755</v>
+        <v>67606736408</v>
       </c>
       <c r="P21" t="n">
-        <v>40350</v>
+        <v>4335</v>
       </c>
       <c r="Q21" t="n">
-        <v>3320</v>
+        <v>1246</v>
       </c>
       <c r="R21" t="n">
-        <v>-1107000</v>
+        <v>-599000</v>
       </c>
       <c r="S21" t="n">
-        <v>-209000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전 관련 호재 속 계약 체결 공시 확인, 일부 투자자 기대감.</t>
+          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '공시', '계약체결']</t>
+          <t>['탈모주', '하락']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3750</v>
+        <v>19480</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.60%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.52</v>
+        <v>0.38</v>
       </c>
       <c r="E22" t="n">
-        <v>103</v>
+        <v>249</v>
       </c>
       <c r="F22" t="n">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="G22" t="n">
-        <v>197</v>
+        <v>766</v>
       </c>
       <c r="H22" t="n">
-        <v>2.08</v>
+        <v>10.85</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3890</v>
+        <v>19970</v>
       </c>
       <c r="K22" t="n">
-        <v>3890</v>
+        <v>20250</v>
       </c>
       <c r="L22" t="n">
-        <v>4115</v>
+        <v>21300</v>
       </c>
       <c r="M22" t="n">
-        <v>3700</v>
+        <v>19350</v>
       </c>
       <c r="N22" t="n">
-        <v>1.56</v>
+        <v>10.47</v>
       </c>
       <c r="O22" t="n">
-        <v>66962221584</v>
+        <v>284975878165</v>
       </c>
       <c r="P22" t="n">
-        <v>4335</v>
+        <v>40350</v>
       </c>
       <c r="Q22" t="n">
-        <v>1246</v>
+        <v>3320</v>
       </c>
       <c r="R22" t="n">
-        <v>-599000</v>
+        <v>-1107000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-209000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
+          <t>원전 관련 호재 속 계약 체결 공시 확인, 일부 투자자 기대감.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['탈모주', '하락']</t>
+          <t>['원전', '공시', '계약체결']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10060</v>
+        <v>10130</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.64%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.32</v>
       </c>
       <c r="E23" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F23" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G23" t="n">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="H23" t="n">
         <v>0.9399999999999999</v>
@@ -2542,7 +2542,7 @@
         <v>0.62</v>
       </c>
       <c r="O23" t="n">
-        <v>147390691635</v>
+        <v>148040577390</v>
       </c>
       <c r="P23" t="n">
         <v>15960</v>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G2" t="n">
-        <v>1630</v>
+        <v>1668</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29749128355</v>
+        <v>29766186935</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미 FDA 2A상 승인 및 병용요법 관련 연구 결과 공개 예고. 외인 매수세 유입으로 인한 기대감 형성.</t>
+          <t>미 FDA 2A상 승인 기대감 및 병용요법 연구 결과 공개 예정. 외국인 매수세 유입.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA 2A상', '병용요법', '연구 결과']</t>
+          <t>['FDA 2A상', '병용요법', '외국인 매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F3" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3" t="n">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>233282725825</v>
+        <v>233391187545</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -768,7 +768,7 @@
         <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37954314615</v>
+        <v>37957849275</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13960</v>
+        <v>14160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+18.20%</t>
+          <t>+19.90%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1532</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>487315522485</v>
+        <v>504360904950</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>하반기 주도주로서 원전 및 로봇 섹터 전망. 미국 및 사우디 등 해외 수주 기대감 반영. 13750원 및 22300원 등 단기 목표가 제시. 정부 정책 및 외국인 자본 유입 언급.</t>
+          <t>미국 원전주 강세 및 체코, 사우디 관련 이슈 언급. 하반기 주도주, 단기 급등 전망 제시하며 긍정적 논조 강화.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '로봇', '해외수주']</t>
+          <t>['원전', '체코', '사우디']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7200</v>
+        <v>7180</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+15.02%</t>
+          <t>+14.70%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F6" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G6" t="n">
-        <v>1301</v>
+        <v>1315</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>70629618770</v>
+        <v>71136651975</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14950</v>
+        <v>14900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.12%</t>
+          <t>+8.76%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.39</v>
       </c>
       <c r="E7" t="n">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F7" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G7" t="n">
-        <v>1484</v>
+        <v>1540</v>
       </c>
       <c r="H7" t="n">
         <v>1.55</v>
@@ -1070,7 +1070,7 @@
         <v>1.94</v>
       </c>
       <c r="O7" t="n">
-        <v>437313985410</v>
+        <v>442093417145</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1130,13 +1130,13 @@
         <v>0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F8" t="n">
         <v>128</v>
       </c>
       <c r="G8" t="n">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="H8" t="n">
         <v>14.96</v>
@@ -1162,7 +1162,7 @@
         <v>14.93</v>
       </c>
       <c r="O8" t="n">
-        <v>165288875800</v>
+        <v>166382026200</v>
       </c>
       <c r="P8" t="n">
         <v>108900</v>
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6840</v>
+        <v>2045</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.38%</t>
+          <t>+6.40%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.31</v>
+        <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>355</v>
+        <v>126</v>
       </c>
       <c r="F9" t="n">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>558</v>
+        <v>310</v>
       </c>
       <c r="H9" t="n">
-        <v>16.71</v>
+        <v>0.51</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6430</v>
+        <v>1922</v>
       </c>
       <c r="K9" t="n">
-        <v>6400</v>
+        <v>1920</v>
       </c>
       <c r="L9" t="n">
-        <v>7470</v>
+        <v>2165</v>
       </c>
       <c r="M9" t="n">
-        <v>6250</v>
+        <v>1862</v>
       </c>
       <c r="N9" t="n">
-        <v>16.4</v>
+        <v>0.61</v>
       </c>
       <c r="O9" t="n">
-        <v>100353110875</v>
+        <v>17990772384</v>
       </c>
       <c r="P9" t="n">
-        <v>13000</v>
+        <v>2930</v>
       </c>
       <c r="Q9" t="n">
-        <v>6030</v>
+        <v>910</v>
       </c>
       <c r="R9" t="n">
-        <v>-679000</v>
+        <v>154000</v>
       </c>
       <c r="S9" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>배당 관련 논의와 함께 주가 상승 및 하락에 대한 기대감 공존.</t>
+          <t>호남 반도체 클러스터 대장이라는 분석과 함께 텐버거 기대감 제시. 대주주 매도 공시, 물량 넘기기 등 부정적 언급도 공존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['배당', '주가 상승', '공매']</t>
+          <t>['반도체', '텐버거', '대주주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2035</v>
+        <v>6840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.88%</t>
+          <t>+6.38%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1</v>
+        <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>120</v>
+        <v>359</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="G10" t="n">
-        <v>285</v>
+        <v>569</v>
       </c>
       <c r="H10" t="n">
-        <v>0.51</v>
+        <v>16.71</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1922</v>
+        <v>6430</v>
       </c>
       <c r="K10" t="n">
-        <v>1920</v>
+        <v>6400</v>
       </c>
       <c r="L10" t="n">
-        <v>2165</v>
+        <v>7470</v>
       </c>
       <c r="M10" t="n">
-        <v>1862</v>
+        <v>6250</v>
       </c>
       <c r="N10" t="n">
-        <v>0.61</v>
+        <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>17571997184</v>
+        <v>100921006795</v>
       </c>
       <c r="P10" t="n">
-        <v>2930</v>
+        <v>13000</v>
       </c>
       <c r="Q10" t="n">
-        <v>910</v>
+        <v>6030</v>
       </c>
       <c r="R10" t="n">
-        <v>154000</v>
+        <v>-679000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 클러스터 관련 논의 및 주포 동향 주시, 주가 상승 전망.</t>
+          <t>배당금 관련 긍정적 언급과 함께 일부 하락 예측 존재. 거래량 증가 및 손바뀜 추정으로 상승 기대감 나타남.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '주포', '텐버거']</t>
+          <t>['배당금', '거래량', '손바뀜']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,169 +1384,169 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3800</v>
+        <v>2260</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.40%</t>
+          <t>+4.63%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.74</v>
+        <v>-0.23</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="H11" t="n">
-        <v>3.19</v>
+        <v>5.26</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3640</v>
+        <v>2160</v>
       </c>
       <c r="K11" t="n">
-        <v>3750</v>
+        <v>2200</v>
       </c>
       <c r="L11" t="n">
-        <v>4460</v>
+        <v>2705</v>
       </c>
       <c r="M11" t="n">
-        <v>3680</v>
+        <v>2130</v>
       </c>
       <c r="N11" t="n">
-        <v>0.45</v>
+        <v>5.49</v>
       </c>
       <c r="O11" t="n">
-        <v>274896197449</v>
+        <v>46160448335</v>
       </c>
       <c r="P11" t="n">
-        <v>8100</v>
+        <v>2705</v>
       </c>
       <c r="Q11" t="n">
-        <v>592</v>
+        <v>1418</v>
       </c>
       <c r="R11" t="n">
-        <v>-731000</v>
+        <v>22000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신 폭등 관련, 6G 기반, 국책사업 선정 기대.</t>
+          <t>기타법인 장내매수 및 새로운 대주주에 대한 기대감 존재. 일부는 하한가 및 음봉을 예측하며 부정적인 전망도 제시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '6G']</t>
+          <t>['기타법인', '대주주', '음봉']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1859000</v>
+        <v>3805</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.68%</t>
+          <t>+4.53%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.03</v>
+        <v>2.74</v>
       </c>
       <c r="E12" t="n">
-        <v>791</v>
+        <v>237</v>
       </c>
       <c r="F12" t="n">
-        <v>438</v>
+        <v>128</v>
       </c>
       <c r="G12" t="n">
-        <v>1846</v>
+        <v>554</v>
       </c>
       <c r="H12" t="n">
-        <v>50.66</v>
+        <v>3.19</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1793000</v>
+        <v>3640</v>
       </c>
       <c r="K12" t="n">
-        <v>1795000</v>
+        <v>3750</v>
       </c>
       <c r="L12" t="n">
-        <v>1883000</v>
+        <v>4460</v>
       </c>
       <c r="M12" t="n">
-        <v>1795000</v>
+        <v>3680</v>
       </c>
       <c r="N12" t="n">
-        <v>50.63</v>
+        <v>0.45</v>
       </c>
       <c r="O12" t="n">
-        <v>5776700759500</v>
+        <v>276093833628</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>8100</v>
       </c>
       <c r="Q12" t="n">
-        <v>277000</v>
+        <v>592</v>
       </c>
       <c r="R12" t="n">
-        <v>180000</v>
+        <v>-731000</v>
       </c>
       <c r="S12" t="n">
-        <v>151000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>외인 매수세 유입 및 상승 추세 전환 신호 포착, 긍정적 전망.</t>
+          <t>미국 광통신 섹터 강세 및 글로벌 회사 대량 공급 뉴스 기반으로 긍정적 전망 제시. 투경 우려와 함께 1만 전자, 6천원 목표가 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['외인 매수', '상승 추세', '호재']</t>
+          <t>['광통신', '글로벌 공급', '투경']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30750</v>
+        <v>1857000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+3.57%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>714</v>
+        <v>792</v>
       </c>
       <c r="F13" t="n">
-        <v>252</v>
+        <v>427</v>
       </c>
       <c r="G13" t="n">
-        <v>1032</v>
+        <v>1992</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31</v>
+        <v>50.66</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>29750</v>
+        <v>1793000</v>
       </c>
       <c r="K13" t="n">
-        <v>31600</v>
+        <v>1795000</v>
       </c>
       <c r="L13" t="n">
-        <v>34200</v>
+        <v>1883000</v>
       </c>
       <c r="M13" t="n">
-        <v>28300</v>
+        <v>1795000</v>
       </c>
       <c r="N13" t="n">
-        <v>0.23</v>
+        <v>50.63</v>
       </c>
       <c r="O13" t="n">
-        <v>522764760150</v>
+        <v>5874294887500</v>
       </c>
       <c r="P13" t="n">
-        <v>39350</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>8200</v>
+        <v>277000</v>
       </c>
       <c r="R13" t="n">
-        <v>-1000</v>
+        <v>180000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>혈압계 관련 뉴스 및 유럽 진출 소식, 주가 반등 기대감.</t>
+          <t>상승 추세 전환 신호 및 외인/기관의 긍정적 수급 포착. 악성 매물 소화 및 우상향 표준이라는 분석 제시. 일부 2시 이후 하락 예측 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['혈압계', '유럽 진출', '최저점']</t>
+          <t>['상승 추세', '수급', '악성매물']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>91800</v>
+        <v>7900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+2.57%</t>
+          <t>+2.86%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>1.4</v>
       </c>
       <c r="E14" t="n">
-        <v>355</v>
+        <v>143</v>
       </c>
       <c r="F14" t="n">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="G14" t="n">
-        <v>1739</v>
+        <v>363</v>
       </c>
       <c r="H14" t="n">
-        <v>23.61</v>
+        <v>1.81</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>89500</v>
+        <v>7680</v>
       </c>
       <c r="K14" t="n">
-        <v>92000</v>
+        <v>7780</v>
       </c>
       <c r="L14" t="n">
-        <v>94400</v>
+        <v>9000</v>
       </c>
       <c r="M14" t="n">
-        <v>91100</v>
+        <v>7690</v>
       </c>
       <c r="N14" t="n">
-        <v>23.63</v>
+        <v>0.41</v>
       </c>
       <c r="O14" t="n">
-        <v>319193723450</v>
+        <v>120266040840</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>10300</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>952</v>
       </c>
       <c r="R14" t="n">
-        <v>123000</v>
+        <v>-211000</v>
       </c>
       <c r="S14" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
+          <t>강력한 지지선 및 신고가 돌파 기대감 존재. 일부는 하락 및 숏커버링 가능성을 언급하며 관망세.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '한-프랑스']</t>
+          <t>['지지선', '돌파', '숏커버링']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7860</v>
+        <v>30550</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.34%</t>
+          <t>+2.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.4</v>
+        <v>0.08</v>
       </c>
       <c r="E15" t="n">
-        <v>147</v>
+        <v>725</v>
       </c>
       <c r="F15" t="n">
-        <v>85</v>
+        <v>253</v>
       </c>
       <c r="G15" t="n">
-        <v>390</v>
+        <v>1046</v>
       </c>
       <c r="H15" t="n">
-        <v>1.81</v>
+        <v>0.31</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7680</v>
+        <v>29750</v>
       </c>
       <c r="K15" t="n">
-        <v>7780</v>
+        <v>31600</v>
       </c>
       <c r="L15" t="n">
-        <v>9000</v>
+        <v>34200</v>
       </c>
       <c r="M15" t="n">
-        <v>7690</v>
+        <v>28300</v>
       </c>
       <c r="N15" t="n">
-        <v>0.41</v>
+        <v>0.23</v>
       </c>
       <c r="O15" t="n">
-        <v>119236391540</v>
+        <v>529460328575</v>
       </c>
       <c r="P15" t="n">
-        <v>10300</v>
+        <v>39350</v>
       </c>
       <c r="Q15" t="n">
-        <v>952</v>
+        <v>8200</v>
       </c>
       <c r="R15" t="n">
-        <v>-211000</v>
+        <v>-1000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>레미콘 파업 시작 및 대장주로서의 강세 기대. 하지만 전반적인 상승 동력은 약함.</t>
+          <t>혈압계 관련 뉴스 및 유럽 진출 소식, 주가 반등 기대감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['레미콘', '대장주', '파업']</t>
+          <t>['혈압계', '유럽 진출', '최저점']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2185</v>
+        <v>91700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>+2.46%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.23</v>
+        <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>358</v>
       </c>
       <c r="F16" t="n">
-        <v>84</v>
+        <v>227</v>
       </c>
       <c r="G16" t="n">
-        <v>375</v>
+        <v>1754</v>
       </c>
       <c r="H16" t="n">
-        <v>5.26</v>
+        <v>23.61</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>2160</v>
+        <v>89500</v>
       </c>
       <c r="K16" t="n">
-        <v>2200</v>
+        <v>92000</v>
       </c>
       <c r="L16" t="n">
-        <v>2705</v>
+        <v>94400</v>
       </c>
       <c r="M16" t="n">
-        <v>2130</v>
+        <v>91100</v>
       </c>
       <c r="N16" t="n">
-        <v>5.49</v>
+        <v>23.63</v>
       </c>
       <c r="O16" t="n">
-        <v>44640050294</v>
+        <v>325255660850</v>
       </c>
       <c r="P16" t="n">
-        <v>2705</v>
+        <v>139200</v>
       </c>
       <c r="Q16" t="n">
-        <v>1418</v>
+        <v>57000</v>
       </c>
       <c r="R16" t="n">
-        <v>22000</v>
+        <v>123000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>지분 싸움 및 신규 대주주 관련 논의, 단기 목표가 언급.</t>
+          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['지분 싸움', '신규 대주주', '단기 목표가']</t>
+          <t>['원전', 'SMR', '한-프랑스']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12050</v>
+        <v>12120</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>191</v>
       </c>
       <c r="F17" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G17" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>48540091605</v>
+        <v>49177428615</v>
       </c>
       <c r="P17" t="n">
         <v>36200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 지정학적 이슈에도 주가 부진, 투자자들의 불만.</t>
+          <t>국제 유가 급등 및 이란 관련 이슈로 인한 상승 기대감 있으나, 주가는 반응이 없고 오히려 하락했다는 분석 제시.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['국제 유가', '지정학적 이슈', '주가 부진']</t>
+          <t>['국제유가', '이란', '주가 반응']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>270500</v>
+        <v>8970</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="E18" t="n">
-        <v>763</v>
+        <v>121</v>
       </c>
       <c r="F18" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="G18" t="n">
-        <v>1711</v>
+        <v>524</v>
       </c>
       <c r="H18" t="n">
-        <v>46.85</v>
+        <v>27.69</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="K18" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="L18" t="n">
-        <v>275000</v>
+        <v>9070</v>
       </c>
       <c r="M18" t="n">
-        <v>267500</v>
+        <v>8710</v>
       </c>
       <c r="N18" t="n">
-        <v>46.79</v>
+        <v>28.05</v>
       </c>
       <c r="O18" t="n">
-        <v>3879752757000</v>
+        <v>34206964330</v>
       </c>
       <c r="P18" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q18" t="n">
-        <v>70000</v>
+        <v>8120</v>
       </c>
       <c r="R18" t="n">
-        <v>-1876000</v>
+        <v>-309000</v>
       </c>
       <c r="S18" t="n">
-        <v>784000</v>
+        <v>7000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>노조, 경영진 관련 부정적 언급 및 주가 부진에 대한 불만.</t>
+          <t>기업 실적 및 성장성에 대한 부정적 전망, 투자 비판.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['노조', '경영진', '주가 부진']</t>
+          <t>['실적', '성장성', '투자 비판']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8970</v>
+        <v>270000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.36</v>
+        <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>120</v>
+        <v>787</v>
       </c>
       <c r="F19" t="n">
-        <v>68</v>
+        <v>489</v>
       </c>
       <c r="G19" t="n">
-        <v>516</v>
+        <v>1758</v>
       </c>
       <c r="H19" t="n">
-        <v>27.69</v>
+        <v>46.85</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="K19" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="L19" t="n">
-        <v>9070</v>
+        <v>275000</v>
       </c>
       <c r="M19" t="n">
-        <v>8710</v>
+        <v>267500</v>
       </c>
       <c r="N19" t="n">
-        <v>28.05</v>
+        <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>33176217140</v>
+        <v>3951124796250</v>
       </c>
       <c r="P19" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q19" t="n">
-        <v>8120</v>
+        <v>70000</v>
       </c>
       <c r="R19" t="n">
-        <v>-309000</v>
+        <v>-1876000</v>
       </c>
       <c r="S19" t="n">
-        <v>7000</v>
+        <v>784000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>기업 실적 및 성장성에 대한 부정적 전망, 투자 비판.</t>
+          <t>노조, 이재용 관련 이슈 및 외인 매도세에 대한 부정적 언급과 함께 영업이익 전세계 1위라는 팩트 제시. 주가 하락 및 희망 없는 전망 다수.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['실적', '성장성', '투자 비판']</t>
+          <t>['노조', '외인 매도', '영업이익']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,222 +2212,222 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33700</v>
+        <v>3870</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1</v>
+        <v>0.52</v>
       </c>
       <c r="E20" t="n">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F20" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>322</v>
+        <v>201</v>
       </c>
       <c r="H20" t="n">
-        <v>52.56</v>
+        <v>2.08</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>34100</v>
+        <v>3890</v>
       </c>
       <c r="K20" t="n">
-        <v>34450</v>
+        <v>3890</v>
       </c>
       <c r="L20" t="n">
-        <v>35325</v>
+        <v>4115</v>
       </c>
       <c r="M20" t="n">
-        <v>33550</v>
+        <v>3700</v>
       </c>
       <c r="N20" t="n">
-        <v>21.01</v>
+        <v>1.56</v>
       </c>
       <c r="O20" t="n">
-        <v>85214685575</v>
+        <v>70042091952</v>
       </c>
       <c r="P20" t="n">
-        <v>69500</v>
+        <v>4335</v>
       </c>
       <c r="Q20" t="n">
-        <v>30400</v>
+        <v>1246</v>
       </c>
       <c r="R20" t="n">
-        <v>-80000</v>
+        <v>-599000</v>
       </c>
       <c r="S20" t="n">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 원전 협력, 공매도 이슈, SMP 급락 우려.</t>
+          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '공매도']</t>
+          <t>['탈모주', '하락']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3800</v>
+        <v>33750</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.52</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="F21" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G21" t="n">
-        <v>197</v>
+        <v>324</v>
       </c>
       <c r="H21" t="n">
-        <v>2.08</v>
+        <v>52.55</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>3890</v>
+        <v>34100</v>
       </c>
       <c r="K21" t="n">
-        <v>3890</v>
+        <v>34450</v>
       </c>
       <c r="L21" t="n">
-        <v>4115</v>
+        <v>35325</v>
       </c>
       <c r="M21" t="n">
-        <v>3700</v>
+        <v>33550</v>
       </c>
       <c r="N21" t="n">
-        <v>1.56</v>
+        <v>21.01</v>
       </c>
       <c r="O21" t="n">
-        <v>67606736408</v>
+        <v>86575259200</v>
       </c>
       <c r="P21" t="n">
-        <v>4335</v>
+        <v>69500</v>
       </c>
       <c r="Q21" t="n">
-        <v>1246</v>
+        <v>30400</v>
       </c>
       <c r="R21" t="n">
-        <v>-599000</v>
+        <v>-80000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
+          <t>미국 원전 협력 및 발전 5사 통합, 25조 선납매 관련 긍정적 이슈 언급. 공매도 세력 및 20년째 주주 피해 상황으로 부정적 전망도 제시.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['탈모주', '하락']</t>
+          <t>['원전', '발전 5사 통합', '공매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19480</v>
+        <v>10200</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>-2.30%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="E22" t="n">
-        <v>249</v>
+        <v>107</v>
       </c>
       <c r="F22" t="n">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="G22" t="n">
-        <v>766</v>
+        <v>257</v>
       </c>
       <c r="H22" t="n">
-        <v>10.85</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,91 +2435,91 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>19970</v>
+        <v>10440</v>
       </c>
       <c r="K22" t="n">
-        <v>20250</v>
+        <v>10180</v>
       </c>
       <c r="L22" t="n">
-        <v>21300</v>
+        <v>11340</v>
       </c>
       <c r="M22" t="n">
-        <v>19350</v>
+        <v>9980</v>
       </c>
       <c r="N22" t="n">
-        <v>10.47</v>
+        <v>0.62</v>
       </c>
       <c r="O22" t="n">
-        <v>284975878165</v>
+        <v>149740010280</v>
       </c>
       <c r="P22" t="n">
-        <v>40350</v>
+        <v>15960</v>
       </c>
       <c r="Q22" t="n">
-        <v>3320</v>
+        <v>3500</v>
       </c>
       <c r="R22" t="n">
-        <v>-1107000</v>
+        <v>-50000</v>
       </c>
       <c r="S22" t="n">
-        <v>-209000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>원전 관련 호재 속 계약 체결 공시 확인, 일부 투자자 기대감.</t>
+          <t>미증시 제약바이오와는 다른 움직임, 탈모주 관련 기대감 있으나 구체적인 재료 및 공시 부재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['원전', '공시', '계약체결']</t>
+          <t>['탈모주', '재료']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10130</v>
+        <v>19450</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.97%</t>
+          <t>-2.60%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="E23" t="n">
-        <v>104</v>
+        <v>254</v>
       </c>
       <c r="F23" t="n">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="G23" t="n">
-        <v>249</v>
+        <v>777</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9399999999999999</v>
+        <v>10.85</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,60 +2527,60 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>10440</v>
+        <v>19970</v>
       </c>
       <c r="K23" t="n">
-        <v>10180</v>
+        <v>20250</v>
       </c>
       <c r="L23" t="n">
-        <v>11340</v>
+        <v>21300</v>
       </c>
       <c r="M23" t="n">
-        <v>9980</v>
+        <v>19350</v>
       </c>
       <c r="N23" t="n">
-        <v>0.62</v>
+        <v>10.47</v>
       </c>
       <c r="O23" t="n">
-        <v>148040577390</v>
+        <v>289449585835</v>
       </c>
       <c r="P23" t="n">
-        <v>15960</v>
+        <v>40350</v>
       </c>
       <c r="Q23" t="n">
-        <v>3500</v>
+        <v>3320</v>
       </c>
       <c r="R23" t="n">
-        <v>-50000</v>
+        <v>-1107000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-209000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>미증시 제약바이오와는 다른 움직임, 탈모주 관련 기대감 있으나 구체적인 재료 및 공시 부재.</t>
+          <t>원전 관련 호재 속 계약 체결 공시 확인, 일부 투자자 기대감.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['탈모주', '재료']</t>
+          <t>['원전', '공시', '계약체결']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>047040</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G2" t="n">
-        <v>1668</v>
+        <v>1683</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29766186935</v>
+        <v>29784514335</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F3" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G3" t="n">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>233391187545</v>
+        <v>233465315215</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -762,13 +762,13 @@
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
         <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37957849275</v>
+        <v>37978952115</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14160</v>
+        <v>14290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+19.90%</t>
+          <t>+21.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="F5" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="G5" t="n">
-        <v>1532</v>
+        <v>1575</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>504360904950</v>
+        <v>522857428495</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7180</v>
+        <v>7150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.70%</t>
+          <t>+14.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F6" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G6" t="n">
-        <v>1315</v>
+        <v>1339</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>71136651975</v>
+        <v>71771967855</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14900</v>
+        <v>53900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.76%</t>
+          <t>+9.44%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.39</v>
+        <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>279</v>
+        <v>175</v>
       </c>
       <c r="F7" t="n">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="G7" t="n">
-        <v>1540</v>
+        <v>660</v>
       </c>
       <c r="H7" t="n">
-        <v>1.55</v>
+        <v>14.96</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13700</v>
+        <v>49250</v>
       </c>
       <c r="K7" t="n">
-        <v>14260</v>
+        <v>53500</v>
       </c>
       <c r="L7" t="n">
-        <v>15860</v>
+        <v>59000</v>
       </c>
       <c r="M7" t="n">
-        <v>14210</v>
+        <v>51600</v>
       </c>
       <c r="N7" t="n">
-        <v>1.94</v>
+        <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>442093417145</v>
+        <v>167660719050</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>108900</v>
       </c>
       <c r="Q7" t="n">
-        <v>1252</v>
+        <v>18230</v>
       </c>
       <c r="R7" t="n">
-        <v>590000</v>
+        <v>-215000</v>
       </c>
       <c r="S7" t="n">
-        <v>20000</v>
+        <v>154000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기 박스권 돌파 및 불기둥 형성, 2만 목표 상향 기대감.</t>
+          <t>대규모 수주 및 2분기 영업이익 흑자 전환 기대감. 목표가 상향 논의 활발.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['불기둥', '박스권돌파', '우상향']</t>
+          <t>['수주', '영업이익', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53500</v>
+        <v>14960</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.63%</t>
+          <t>+9.20%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.03</v>
+        <v>-0.39</v>
       </c>
       <c r="E8" t="n">
-        <v>173</v>
+        <v>282</v>
       </c>
       <c r="F8" t="n">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="G8" t="n">
-        <v>627</v>
+        <v>1565</v>
       </c>
       <c r="H8" t="n">
-        <v>14.96</v>
+        <v>1.55</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>49250</v>
+        <v>13700</v>
       </c>
       <c r="K8" t="n">
-        <v>53500</v>
+        <v>14260</v>
       </c>
       <c r="L8" t="n">
-        <v>59000</v>
+        <v>15860</v>
       </c>
       <c r="M8" t="n">
-        <v>51600</v>
+        <v>14210</v>
       </c>
       <c r="N8" t="n">
-        <v>14.93</v>
+        <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>166382026200</v>
+        <v>447240616025</v>
       </c>
       <c r="P8" t="n">
-        <v>108900</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>18230</v>
+        <v>1252</v>
       </c>
       <c r="R8" t="n">
-        <v>-215000</v>
+        <v>590000</v>
       </c>
       <c r="S8" t="n">
-        <v>154000</v>
+        <v>20000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대규모 수주 및 2분기 영업이익 흑자 전환 기대감. 목표가 상향 논의 활발.</t>
+          <t>빛과전자 수급 흡수 및 개인 매도세 속 상승 기대. 단기 박스권 돌파 및 우상향 추세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주', '영업이익', '목표가']</t>
+          <t>['수급', '단기 박스권', '우상향']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2045</v>
+        <v>2090</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.40%</t>
+          <t>+8.74%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>126</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="H9" t="n">
         <v>0.51</v>
@@ -1254,7 +1254,7 @@
         <v>0.61</v>
       </c>
       <c r="O9" t="n">
-        <v>17990772384</v>
+        <v>18309827760</v>
       </c>
       <c r="P9" t="n">
         <v>2930</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>호남 반도체 클러스터 대장이라는 분석과 함께 텐버거 기대감 제시. 대주주 매도 공시, 물량 넘기기 등 부정적 언급도 공존.</t>
+          <t>반도체 클러스터 대장주 언급 및 텐버거 찌라시. 대주주 매도 공시 및 물량 넘기기 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '텐버거', '대주주']</t>
+          <t>['반도체 클러스터', '텐버거', '대주주 매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6840</v>
+        <v>6850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.38%</t>
+          <t>+6.53%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>359</v>
+        <v>299</v>
       </c>
       <c r="F10" t="n">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G10" t="n">
-        <v>569</v>
+        <v>528</v>
       </c>
       <c r="H10" t="n">
         <v>16.71</v>
@@ -1346,7 +1346,7 @@
         <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>100921006795</v>
+        <v>102089843410</v>
       </c>
       <c r="P10" t="n">
         <v>13000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>배당금 관련 긍정적 언급과 함께 일부 하락 예측 존재. 거래량 증가 및 손바뀜 추정으로 상승 기대감 나타남.</t>
+          <t>배당금 대비 낮은 주가 및 시총 관련 논의. 거래량 증가와 함께 일부 상승 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['배당금', '거래량', '손바뀜']</t>
+          <t>['배당금', '시가총액', '거래량']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,70 +1391,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2260</v>
+        <v>8340</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.63%</t>
+          <t>+5.97%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.23</v>
+        <v>0.46</v>
       </c>
       <c r="E11" t="n">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>347</v>
+        <v>175</v>
       </c>
       <c r="H11" t="n">
-        <v>5.26</v>
+        <v>39.3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2160</v>
+        <v>7870</v>
       </c>
       <c r="K11" t="n">
-        <v>2200</v>
+        <v>7950</v>
       </c>
       <c r="L11" t="n">
-        <v>2705</v>
+        <v>8350</v>
       </c>
       <c r="M11" t="n">
-        <v>2130</v>
+        <v>7480</v>
       </c>
       <c r="N11" t="n">
-        <v>5.49</v>
+        <v>38.84</v>
       </c>
       <c r="O11" t="n">
-        <v>46160448335</v>
+        <v>42363747010</v>
       </c>
       <c r="P11" t="n">
-        <v>2705</v>
+        <v>19150</v>
       </c>
       <c r="Q11" t="n">
-        <v>1418</v>
+        <v>3445</v>
       </c>
       <c r="R11" t="n">
-        <v>22000</v>
+        <v>-169000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-393000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기타법인 장내매수 및 새로운 대주주에 대한 기대감 존재. 일부는 하한가 및 음봉을 예측하며 부정적인 전망도 제시.</t>
+          <t>물량 터는 중이라는 의견과 함께 급락. 상패 직전 우려 및 유증 재료 소멸.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['기타법인', '대주주', '음봉']</t>
+          <t>['물량 터는 중', '급락', '유증 재료 소멸']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3805</v>
+        <v>2260</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>+4.63%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.74</v>
+        <v>-0.23</v>
       </c>
       <c r="E12" t="n">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="F12" t="n">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="G12" t="n">
-        <v>554</v>
+        <v>397</v>
       </c>
       <c r="H12" t="n">
-        <v>3.19</v>
+        <v>5.26</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3640</v>
+        <v>2160</v>
       </c>
       <c r="K12" t="n">
-        <v>3750</v>
+        <v>2200</v>
       </c>
       <c r="L12" t="n">
-        <v>4460</v>
+        <v>2705</v>
       </c>
       <c r="M12" t="n">
-        <v>3680</v>
+        <v>2130</v>
       </c>
       <c r="N12" t="n">
-        <v>0.45</v>
+        <v>5.49</v>
       </c>
       <c r="O12" t="n">
-        <v>276093833628</v>
+        <v>47851656010</v>
       </c>
       <c r="P12" t="n">
-        <v>8100</v>
+        <v>2705</v>
       </c>
       <c r="Q12" t="n">
-        <v>592</v>
+        <v>1418</v>
       </c>
       <c r="R12" t="n">
-        <v>-731000</v>
+        <v>22000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세 및 글로벌 회사 대량 공급 뉴스 기반으로 긍정적 전망 제시. 투경 우려와 함께 1만 전자, 6천원 목표가 언급.</t>
+          <t>지분 싸움 및 기타법인 장내매수 포착. 단기 과열 우려 속 변동성 확대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '글로벌 공급', '투경']</t>
+          <t>['지분 싸움', '장내매수', '단기 과열']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1857000</v>
+        <v>3805</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.57%</t>
+          <t>+4.53%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>2.74</v>
       </c>
       <c r="E13" t="n">
-        <v>792</v>
+        <v>245</v>
       </c>
       <c r="F13" t="n">
-        <v>427</v>
+        <v>131</v>
       </c>
       <c r="G13" t="n">
-        <v>1992</v>
+        <v>562</v>
       </c>
       <c r="H13" t="n">
-        <v>50.66</v>
+        <v>3.19</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1793000</v>
+        <v>3640</v>
       </c>
       <c r="K13" t="n">
-        <v>1795000</v>
+        <v>3750</v>
       </c>
       <c r="L13" t="n">
-        <v>1883000</v>
+        <v>4460</v>
       </c>
       <c r="M13" t="n">
-        <v>1795000</v>
+        <v>3680</v>
       </c>
       <c r="N13" t="n">
-        <v>50.63</v>
+        <v>0.45</v>
       </c>
       <c r="O13" t="n">
-        <v>5874294887500</v>
+        <v>277930731752</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>8100</v>
       </c>
       <c r="Q13" t="n">
-        <v>277000</v>
+        <v>592</v>
       </c>
       <c r="R13" t="n">
-        <v>180000</v>
+        <v>-731000</v>
       </c>
       <c r="S13" t="n">
-        <v>151000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>상승 추세 전환 신호 및 외인/기관의 긍정적 수급 포착. 악성 매물 소화 및 우상향 표준이라는 분석 제시. 일부 2시 이후 하락 예측 존재.</t>
+          <t>미국 광통신 섹터 급등에 따른 기대감. 글로벌 회사 대량 공급 뉴스 및 6G 기반 재료.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['상승 추세', '수급', '악성매물']</t>
+          <t>['광통신', '글로벌 공급', '6G']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7900</v>
+        <v>1858000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+2.86%</t>
+          <t>+3.63%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.4</v>
+        <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>143</v>
+        <v>793</v>
       </c>
       <c r="F14" t="n">
-        <v>86</v>
+        <v>423</v>
       </c>
       <c r="G14" t="n">
-        <v>363</v>
+        <v>2124</v>
       </c>
       <c r="H14" t="n">
-        <v>1.81</v>
+        <v>50.66</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7680</v>
+        <v>1793000</v>
       </c>
       <c r="K14" t="n">
-        <v>7780</v>
+        <v>1795000</v>
       </c>
       <c r="L14" t="n">
-        <v>9000</v>
+        <v>1883000</v>
       </c>
       <c r="M14" t="n">
-        <v>7690</v>
+        <v>1795000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.41</v>
+        <v>50.63</v>
       </c>
       <c r="O14" t="n">
-        <v>120266040840</v>
+        <v>5976730313500</v>
       </c>
       <c r="P14" t="n">
-        <v>10300</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>952</v>
+        <v>277000</v>
       </c>
       <c r="R14" t="n">
-        <v>-211000</v>
+        <v>180000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>강력한 지지선 및 신고가 돌파 기대감 존재. 일부는 하락 및 숏커버링 가능성을 언급하며 관망세.</t>
+          <t>개인 매도세 속 기관/외인 매수 유입. 상승 추세 전환 신호 및 악성 매물 소화.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['지지선', '돌파', '숏커버링']</t>
+          <t>['기관 매수', '외인 매수', '상승 추세']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30550</v>
+        <v>91700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.69%</t>
+          <t>+2.46%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>725</v>
+        <v>363</v>
       </c>
       <c r="F15" t="n">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="G15" t="n">
-        <v>1046</v>
+        <v>1762</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31</v>
+        <v>23.61</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>29750</v>
+        <v>89500</v>
       </c>
       <c r="K15" t="n">
-        <v>31600</v>
+        <v>92000</v>
       </c>
       <c r="L15" t="n">
-        <v>34200</v>
+        <v>94400</v>
       </c>
       <c r="M15" t="n">
-        <v>28300</v>
+        <v>91100</v>
       </c>
       <c r="N15" t="n">
-        <v>0.23</v>
+        <v>23.63</v>
       </c>
       <c r="O15" t="n">
-        <v>529460328575</v>
+        <v>331624140600</v>
       </c>
       <c r="P15" t="n">
-        <v>39350</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>8200</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-1000</v>
+        <v>123000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>혈압계 관련 뉴스 및 유럽 진출 소식, 주가 반등 기대감.</t>
+          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['혈압계', '유럽 진출', '최저점']</t>
+          <t>['원전', 'SMR', '한-프랑스']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>91700</v>
+        <v>7820</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.46%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.02</v>
+        <v>1.4</v>
       </c>
       <c r="E16" t="n">
-        <v>358</v>
+        <v>145</v>
       </c>
       <c r="F16" t="n">
-        <v>227</v>
+        <v>86</v>
       </c>
       <c r="G16" t="n">
-        <v>1754</v>
+        <v>369</v>
       </c>
       <c r="H16" t="n">
-        <v>23.61</v>
+        <v>1.81</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>89500</v>
+        <v>7680</v>
       </c>
       <c r="K16" t="n">
-        <v>92000</v>
+        <v>7780</v>
       </c>
       <c r="L16" t="n">
-        <v>94400</v>
+        <v>9000</v>
       </c>
       <c r="M16" t="n">
-        <v>91100</v>
+        <v>7690</v>
       </c>
       <c r="N16" t="n">
-        <v>23.63</v>
+        <v>0.41</v>
       </c>
       <c r="O16" t="n">
-        <v>325255660850</v>
+        <v>121183731840</v>
       </c>
       <c r="P16" t="n">
-        <v>139200</v>
+        <v>10300</v>
       </c>
       <c r="Q16" t="n">
-        <v>57000</v>
+        <v>952</v>
       </c>
       <c r="R16" t="n">
-        <v>123000</v>
+        <v>-211000</v>
       </c>
       <c r="S16" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
+          <t>강력 지지선 확인 및 상승 중. 레미콘 파업 이슈와 함께 상한가 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '한-프랑스']</t>
+          <t>['지지선', '레미콘 파업', '상한가 기대']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12120</v>
+        <v>30200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+1.51%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-2.16</v>
+        <v>0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>191</v>
+        <v>749</v>
       </c>
       <c r="F17" t="n">
-        <v>103</v>
+        <v>254</v>
       </c>
       <c r="G17" t="n">
-        <v>435</v>
+        <v>1065</v>
       </c>
       <c r="H17" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>29750</v>
+      </c>
+      <c r="K17" t="n">
+        <v>31600</v>
+      </c>
+      <c r="L17" t="n">
+        <v>34200</v>
+      </c>
+      <c r="M17" t="n">
+        <v>28300</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O17" t="n">
+        <v>542388000350</v>
+      </c>
+      <c r="P17" t="n">
+        <v>39350</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>8200</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="S17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>11990</v>
-      </c>
-      <c r="K17" t="n">
-        <v>12440</v>
-      </c>
-      <c r="L17" t="n">
-        <v>12800</v>
-      </c>
-      <c r="M17" t="n">
-        <v>11920</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="O17" t="n">
-        <v>49177428615</v>
-      </c>
-      <c r="P17" t="n">
-        <v>36200</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>8920</v>
-      </c>
-      <c r="R17" t="n">
-        <v>22000</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-6000</v>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 이란 관련 이슈로 인한 상승 기대감 있으나, 주가는 반응이 없고 오히려 하락했다는 분석 제시.</t>
+          <t>혈압계 관련 뉴스 및 유럽 진출 소식, 주가 반등 기대감.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['국제유가', '이란', '주가 반응']</t>
+          <t>['혈압계', '유럽 진출', '최저점']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,86 +2028,86 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8970</v>
+        <v>12090</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.36</v>
+        <v>-2.16</v>
       </c>
       <c r="E18" t="n">
-        <v>121</v>
+        <v>192</v>
       </c>
       <c r="F18" t="n">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="G18" t="n">
-        <v>524</v>
+        <v>439</v>
       </c>
       <c r="H18" t="n">
-        <v>27.69</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8940</v>
+        <v>11990</v>
       </c>
       <c r="K18" t="n">
-        <v>8940</v>
+        <v>12440</v>
       </c>
       <c r="L18" t="n">
-        <v>9070</v>
+        <v>12800</v>
       </c>
       <c r="M18" t="n">
-        <v>8710</v>
+        <v>11920</v>
       </c>
       <c r="N18" t="n">
-        <v>28.05</v>
+        <v>2.16</v>
       </c>
       <c r="O18" t="n">
-        <v>34206964330</v>
+        <v>49930616835</v>
       </c>
       <c r="P18" t="n">
-        <v>17950</v>
+        <v>36200</v>
       </c>
       <c r="Q18" t="n">
-        <v>8120</v>
+        <v>8920</v>
       </c>
       <c r="R18" t="n">
-        <v>-309000</v>
+        <v>22000</v>
       </c>
       <c r="S18" t="n">
-        <v>7000</v>
+        <v>-6000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>기업 실적 및 성장성에 대한 부정적 전망, 투자 비판.</t>
+          <t>국제유가 급등에도 불구하고 흥구석유 주가 움직임은 미미하며, 투자자들은 전쟁 관련 뉴스에 주목하고 있으나 명확한 근거는 부족한 상황이다.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적', '성장성', '투자 비판']</t>
+          <t>['국제유가', '흥구석유', '전쟁']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>270000</v>
+        <v>270250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="F19" t="n">
         <v>489</v>
       </c>
       <c r="G19" t="n">
-        <v>1758</v>
+        <v>1821</v>
       </c>
       <c r="H19" t="n">
         <v>46.85</v>
@@ -2174,7 +2174,7 @@
         <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>3951124796250</v>
+        <v>4018635669250</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>노조, 이재용 관련 이슈 및 외인 매도세에 대한 부정적 언급과 함께 영업이익 전세계 1위라는 팩트 제시. 주가 하락 및 희망 없는 전망 다수.</t>
+          <t>노조 이슈 및 경영진 관련 부정적 언급 다수. 하이닉스와의 비교 속 주가 부진 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['노조', '외인 매도', '영업이익']</t>
+          <t>['노조', '경영진', '주가 부진']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,215 +2219,215 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3870</v>
+        <v>8950</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.52</v>
+        <v>-0.36</v>
       </c>
       <c r="E20" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="G20" t="n">
-        <v>201</v>
+        <v>522</v>
       </c>
       <c r="H20" t="n">
-        <v>2.08</v>
+        <v>27.69</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>3890</v>
+        <v>8940</v>
       </c>
       <c r="K20" t="n">
-        <v>3890</v>
+        <v>8940</v>
       </c>
       <c r="L20" t="n">
-        <v>4115</v>
+        <v>9070</v>
       </c>
       <c r="M20" t="n">
-        <v>3700</v>
+        <v>8710</v>
       </c>
       <c r="N20" t="n">
-        <v>1.56</v>
+        <v>28.05</v>
       </c>
       <c r="O20" t="n">
-        <v>70042091952</v>
+        <v>35220676930</v>
       </c>
       <c r="P20" t="n">
-        <v>4335</v>
+        <v>17950</v>
       </c>
       <c r="Q20" t="n">
-        <v>1246</v>
+        <v>8120</v>
       </c>
       <c r="R20" t="n">
-        <v>-599000</v>
+        <v>-309000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
+          <t>기업 실적 및 성장성에 대한 부정적 전망, 투자 비판.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['탈모주', '하락']</t>
+          <t>['실적', '성장성', '투자 비판']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>33750</v>
+        <v>3865</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1</v>
+        <v>0.52</v>
       </c>
       <c r="E21" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="F21" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="G21" t="n">
-        <v>324</v>
+        <v>209</v>
       </c>
       <c r="H21" t="n">
-        <v>52.55</v>
+        <v>2.08</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>34100</v>
+        <v>3890</v>
       </c>
       <c r="K21" t="n">
-        <v>34450</v>
+        <v>3890</v>
       </c>
       <c r="L21" t="n">
-        <v>35325</v>
+        <v>4115</v>
       </c>
       <c r="M21" t="n">
-        <v>33550</v>
+        <v>3700</v>
       </c>
       <c r="N21" t="n">
-        <v>21.01</v>
+        <v>1.56</v>
       </c>
       <c r="O21" t="n">
-        <v>86575259200</v>
+        <v>71702919453</v>
       </c>
       <c r="P21" t="n">
-        <v>69500</v>
+        <v>4335</v>
       </c>
       <c r="Q21" t="n">
-        <v>30400</v>
+        <v>1246</v>
       </c>
       <c r="R21" t="n">
-        <v>-80000</v>
+        <v>-599000</v>
       </c>
       <c r="S21" t="n">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 원전 협력 및 발전 5사 통합, 25조 선납매 관련 긍정적 이슈 언급. 공매도 세력 및 20년째 주주 피해 상황으로 부정적 전망도 제시.</t>
+          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '발전 5사 통합', '공매도']</t>
+          <t>['탈모주', '하락']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10200</v>
+        <v>33750</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.30%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="F22" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G22" t="n">
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9399999999999999</v>
+        <v>52.56</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,91 +2435,91 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10440</v>
+        <v>34100</v>
       </c>
       <c r="K22" t="n">
-        <v>10180</v>
+        <v>34450</v>
       </c>
       <c r="L22" t="n">
-        <v>11340</v>
+        <v>35325</v>
       </c>
       <c r="M22" t="n">
-        <v>9980</v>
+        <v>33550</v>
       </c>
       <c r="N22" t="n">
-        <v>0.62</v>
+        <v>21.01</v>
       </c>
       <c r="O22" t="n">
-        <v>149740010280</v>
+        <v>87628386400</v>
       </c>
       <c r="P22" t="n">
-        <v>15960</v>
+        <v>69500</v>
       </c>
       <c r="Q22" t="n">
-        <v>3500</v>
+        <v>30400</v>
       </c>
       <c r="R22" t="n">
-        <v>-50000</v>
+        <v>-80000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미증시 제약바이오와는 다른 움직임, 탈모주 관련 기대감 있으나 구체적인 재료 및 공시 부재.</t>
+          <t>미국 원전 협력 및 한전 발전 5사 통합 긍정적 뉴스. 25조 선납매 및 SMP 급락 우려.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['탈모주', '재료']</t>
+          <t>['원전 협력', '발전 5사 통합', 'SMP']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19450</v>
+        <v>10270</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.60%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="E23" t="n">
-        <v>254</v>
+        <v>109</v>
       </c>
       <c r="F23" t="n">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="G23" t="n">
-        <v>777</v>
+        <v>260</v>
       </c>
       <c r="H23" t="n">
-        <v>10.85</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,58 +2527,150 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>19970</v>
+        <v>10440</v>
       </c>
       <c r="K23" t="n">
-        <v>20250</v>
+        <v>10180</v>
       </c>
       <c r="L23" t="n">
-        <v>21300</v>
+        <v>11340</v>
       </c>
       <c r="M23" t="n">
-        <v>19350</v>
+        <v>9980</v>
       </c>
       <c r="N23" t="n">
-        <v>10.47</v>
+        <v>0.62</v>
       </c>
       <c r="O23" t="n">
-        <v>289449585835</v>
+        <v>152241849525</v>
       </c>
       <c r="P23" t="n">
-        <v>40350</v>
+        <v>15960</v>
       </c>
       <c r="Q23" t="n">
-        <v>3320</v>
+        <v>3500</v>
       </c>
       <c r="R23" t="n">
-        <v>-1107000</v>
+        <v>-50000</v>
       </c>
       <c r="S23" t="n">
-        <v>-209000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>원전 관련 호재 속 계약 체결 공시 확인, 일부 투자자 기대감.</t>
+          <t>미증시 제약바이오와는 다른 움직임, 탈모주 관련 기대감 있으나 구체적인 재료 및 공시 부재.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['탈모주', '재료']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>004310</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>19440</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-2.65%</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E24" t="n">
+        <v>261</v>
+      </c>
+      <c r="F24" t="n">
+        <v>131</v>
+      </c>
+      <c r="G24" t="n">
+        <v>792</v>
+      </c>
+      <c r="H24" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>19970</v>
+      </c>
+      <c r="K24" t="n">
+        <v>20250</v>
+      </c>
+      <c r="L24" t="n">
+        <v>21300</v>
+      </c>
+      <c r="M24" t="n">
+        <v>19350</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="O24" t="n">
+        <v>294861460090</v>
+      </c>
+      <c r="P24" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-1107000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-209000</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>원전 관련 호재 속 계약 체결 공시 확인, 일부 투자자 기대감.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
         <v>0.3</v>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>['원전', '공시', '계약체결']</t>
         </is>
       </c>
-      <c r="X23" t="n">
+      <c r="X24" t="n">
         <v>12</v>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>047040</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F2" t="n">
         <v>135</v>
       </c>
       <c r="G2" t="n">
-        <v>1683</v>
+        <v>1713</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29784514335</v>
+        <v>29788795675</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G3" t="n">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>233465315215</v>
+        <v>233498007485</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 증시 SMR 관련주 폭등에 따른 기대감, 품절주 특성 언급.</t>
+          <t>SMR 관련주 폭등 및 삼미금속 목표가 상승 전망. 정부 대미 투자 및 가스터빈 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['SMR', '품절주', '가스터빈']</t>
+          <t>['SMR', '삼미금속', '가스터빈']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
         <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37978952115</v>
+        <v>37984628595</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14290</v>
+        <v>14320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+21.00%</t>
+          <t>+21.25%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F5" t="n">
         <v>176</v>
       </c>
       <c r="G5" t="n">
-        <v>1575</v>
+        <v>1620</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>522857428495</v>
+        <v>530428985295</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 원전주 강세 및 체코, 사우디 관련 이슈 언급. 하반기 주도주, 단기 급등 전망 제시하며 긍정적 논조 강화.</t>
+          <t>원전 및 로봇 관련주 상승 전망. 단기 목표가 제시 및 외국 자본 유입 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '체코', '사우디']</t>
+          <t>['원전', '로봇', '목표가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7150</v>
+        <v>7130</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.22%</t>
+          <t>+13.90%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F6" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G6" t="n">
-        <v>1339</v>
+        <v>1360</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>71771967855</v>
+        <v>72172966185</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -1038,13 +1038,13 @@
         <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F7" t="n">
         <v>128</v>
       </c>
       <c r="G7" t="n">
-        <v>660</v>
+        <v>676</v>
       </c>
       <c r="H7" t="n">
         <v>14.96</v>
@@ -1070,7 +1070,7 @@
         <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>167660719050</v>
+        <v>168662127150</v>
       </c>
       <c r="P7" t="n">
         <v>108900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대규모 수주 및 2분기 영업이익 흑자 전환 기대감. 목표가 상향 논의 활발.</t>
+          <t>두산퓨얼셀, 2분기 실적 부진에도 불구하고 목표가 상향 및 수주 기대감으로 인한 단기 상승세.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '영업이익', '목표가']</t>
+          <t>['수주', '목표가', '실적']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>-0.39</v>
       </c>
       <c r="E8" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F8" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G8" t="n">
-        <v>1565</v>
+        <v>1604</v>
       </c>
       <c r="H8" t="n">
         <v>1.55</v>
@@ -1162,7 +1162,7 @@
         <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>447240616025</v>
+        <v>449834620185</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2090</v>
+        <v>2085</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.74%</t>
+          <t>+8.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="H9" t="n">
         <v>0.51</v>
@@ -1254,7 +1254,7 @@
         <v>0.61</v>
       </c>
       <c r="O9" t="n">
-        <v>18309827760</v>
+        <v>18426089445</v>
       </c>
       <c r="P9" t="n">
         <v>2930</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>반도체 클러스터 대장주 언급 및 텐버거 찌라시. 대주주 매도 공시 및 물량 넘기기 우려.</t>
+          <t>강동씨앤엘, 반도체 클러스터 대장주 부각 속 대주주 매도 공시로 인한 단기 변동성 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '텐버거', '대주주 매도']</t>
+          <t>['반도체', '대주주매도', '전망']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6850</v>
+        <v>6860</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.53%</t>
+          <t>+6.69%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>136</v>
       </c>
       <c r="G10" t="n">
-        <v>528</v>
+        <v>509</v>
       </c>
       <c r="H10" t="n">
         <v>16.71</v>
@@ -1346,7 +1346,7 @@
         <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>102089843410</v>
+        <v>102686244950</v>
       </c>
       <c r="P10" t="n">
         <v>13000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>배당금 대비 낮은 주가 및 시총 관련 논의. 거래량 증가와 함께 일부 상승 기대감.</t>
+          <t>배당 및 주가 부진에 대한 언급. 투자자들의 실망감 표출.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['배당금', '시가총액', '거래량']</t>
+          <t>['배당', '주가', '실망감']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8340</v>
+        <v>8350</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.97%</t>
+          <t>+6.10%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.46</v>
       </c>
       <c r="E11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H11" t="n">
         <v>39.3</v>
@@ -1438,7 +1438,7 @@
         <v>38.84</v>
       </c>
       <c r="O11" t="n">
-        <v>42363747010</v>
+        <v>42724951310</v>
       </c>
       <c r="P11" t="n">
         <v>19150</v>
@@ -1483,83 +1483,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2260</v>
+        <v>3810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.63%</t>
+          <t>+4.67%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.23</v>
+        <v>2.74</v>
       </c>
       <c r="E12" t="n">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="F12" t="n">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="G12" t="n">
-        <v>397</v>
+        <v>573</v>
       </c>
       <c r="H12" t="n">
-        <v>5.26</v>
+        <v>3.19</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2160</v>
+        <v>3640</v>
       </c>
       <c r="K12" t="n">
-        <v>2200</v>
+        <v>3750</v>
       </c>
       <c r="L12" t="n">
-        <v>2705</v>
+        <v>4460</v>
       </c>
       <c r="M12" t="n">
-        <v>2130</v>
+        <v>3680</v>
       </c>
       <c r="N12" t="n">
-        <v>5.49</v>
+        <v>0.45</v>
       </c>
       <c r="O12" t="n">
-        <v>47851656010</v>
+        <v>278852496482</v>
       </c>
       <c r="P12" t="n">
-        <v>2705</v>
+        <v>8100</v>
       </c>
       <c r="Q12" t="n">
-        <v>1418</v>
+        <v>592</v>
       </c>
       <c r="R12" t="n">
-        <v>22000</v>
+        <v>-731000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>지분 싸움 및 기타법인 장내매수 포착. 단기 과열 우려 속 변동성 확대.</t>
+          <t>광통신 관련주 급등 및 빛과전자 강세 전망. 6G 기반 기술 및 글로벌 공급 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['지분 싸움', '장내매수', '단기 과열']</t>
+          <t>['광통신', '빛과전자', '6G']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3805</v>
+        <v>2260</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>+4.63%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.74</v>
+        <v>-0.23</v>
       </c>
       <c r="E13" t="n">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="F13" t="n">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="G13" t="n">
-        <v>562</v>
+        <v>422</v>
       </c>
       <c r="H13" t="n">
-        <v>3.19</v>
+        <v>5.26</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3640</v>
+        <v>2160</v>
       </c>
       <c r="K13" t="n">
-        <v>3750</v>
+        <v>2200</v>
       </c>
       <c r="L13" t="n">
-        <v>4460</v>
+        <v>2705</v>
       </c>
       <c r="M13" t="n">
-        <v>3680</v>
+        <v>2130</v>
       </c>
       <c r="N13" t="n">
-        <v>0.45</v>
+        <v>5.49</v>
       </c>
       <c r="O13" t="n">
-        <v>277930731752</v>
+        <v>48057169110</v>
       </c>
       <c r="P13" t="n">
-        <v>8100</v>
+        <v>2705</v>
       </c>
       <c r="Q13" t="n">
-        <v>592</v>
+        <v>1418</v>
       </c>
       <c r="R13" t="n">
-        <v>-731000</v>
+        <v>22000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 급등에 따른 기대감. 글로벌 회사 대량 공급 뉴스 및 6G 기반 재료.</t>
+          <t>지분 싸움과 기타 법인 장내 매수 관련 언급. 일부 투자자는 하락 예측.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', '글로벌 공급', '6G']</t>
+          <t>['지분 싸움', '장내매수', '투자']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1858000</v>
+        <v>1856000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.63%</t>
+          <t>+3.51%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F14" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G14" t="n">
-        <v>2124</v>
+        <v>2145</v>
       </c>
       <c r="H14" t="n">
         <v>50.66</v>
@@ -1714,7 +1714,7 @@
         <v>50.63</v>
       </c>
       <c r="O14" t="n">
-        <v>5976730313500</v>
+        <v>6512518537500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>개인 매도세 속 기관/외인 매수 유입. 상승 추세 전환 신호 및 악성 매물 소화.</t>
+          <t>SK하이닉스 상승 추세 전환 신호 및 목표가 상승 전망. 수급 및 악성매물 소화 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['기관 매수', '외인 매수', '상승 추세']</t>
+          <t>['SK하이닉스', '상승 추세', '수급']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F15" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G15" t="n">
-        <v>1762</v>
+        <v>1775</v>
       </c>
       <c r="H15" t="n">
         <v>23.61</v>
@@ -1806,7 +1806,7 @@
         <v>23.63</v>
       </c>
       <c r="O15" t="n">
-        <v>331624140600</v>
+        <v>343506810000</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7820</v>
+        <v>7830</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1.4</v>
       </c>
       <c r="E16" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F16" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G16" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H16" t="n">
         <v>1.81</v>
@@ -1898,7 +1898,7 @@
         <v>0.41</v>
       </c>
       <c r="O16" t="n">
-        <v>121183731840</v>
+        <v>121380006450</v>
       </c>
       <c r="P16" t="n">
         <v>10300</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30200</v>
+        <v>30300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.51%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>749</v>
+        <v>762</v>
       </c>
       <c r="F17" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G17" t="n">
-        <v>1065</v>
+        <v>1091</v>
       </c>
       <c r="H17" t="n">
         <v>0.31</v>
@@ -1990,7 +1990,7 @@
         <v>0.23</v>
       </c>
       <c r="O17" t="n">
-        <v>542388000350</v>
+        <v>544717252250</v>
       </c>
       <c r="P17" t="n">
         <v>39350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>혈압계 관련 뉴스 및 유럽 진출 소식, 주가 반등 기대감.</t>
+          <t>혈압 반기 관련 기술 및 유럽 진출 뉴스. 주가 최저점 및 반등 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['혈압계', '유럽 진출', '최저점']</t>
+          <t>['혈압 반지', '스카이랩스', '유럽 진출']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>-2.16</v>
       </c>
       <c r="E18" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F18" t="n">
         <v>104</v>
       </c>
       <c r="G18" t="n">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>2.16</v>
       </c>
       <c r="O18" t="n">
-        <v>49930616835</v>
+        <v>50268749955</v>
       </c>
       <c r="P18" t="n">
         <v>36200</v>
@@ -2127,31 +2127,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>270250</v>
+        <v>8950</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="E19" t="n">
-        <v>785</v>
+        <v>123</v>
       </c>
       <c r="F19" t="n">
-        <v>489</v>
+        <v>67</v>
       </c>
       <c r="G19" t="n">
-        <v>1821</v>
+        <v>523</v>
       </c>
       <c r="H19" t="n">
-        <v>46.85</v>
+        <v>27.69</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="K19" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="L19" t="n">
-        <v>275000</v>
+        <v>9070</v>
       </c>
       <c r="M19" t="n">
-        <v>267500</v>
+        <v>8710</v>
       </c>
       <c r="N19" t="n">
-        <v>46.79</v>
+        <v>28.05</v>
       </c>
       <c r="O19" t="n">
-        <v>4018635669250</v>
+        <v>37459877430</v>
       </c>
       <c r="P19" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q19" t="n">
-        <v>70000</v>
+        <v>8120</v>
       </c>
       <c r="R19" t="n">
-        <v>-1876000</v>
+        <v>-309000</v>
       </c>
       <c r="S19" t="n">
-        <v>784000</v>
+        <v>7000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>노조 이슈 및 경영진 관련 부정적 언급 다수. 하이닉스와의 비교 속 주가 부진 우려.</t>
+          <t>LG디스플레이 주가 부진 및 매도 의견. AI 및 중국산 영향 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['노조', '경영진', '주가 부진']</t>
+          <t>['LG디스플레이', '주가', '매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8950</v>
+        <v>269500</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.36</v>
+        <v>0.06</v>
       </c>
       <c r="E20" t="n">
-        <v>121</v>
+        <v>785</v>
       </c>
       <c r="F20" t="n">
-        <v>68</v>
+        <v>475</v>
       </c>
       <c r="G20" t="n">
-        <v>522</v>
+        <v>1997</v>
       </c>
       <c r="H20" t="n">
-        <v>27.69</v>
+        <v>46.85</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,38 +2251,38 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="K20" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="L20" t="n">
-        <v>9070</v>
+        <v>275000</v>
       </c>
       <c r="M20" t="n">
-        <v>8710</v>
+        <v>267500</v>
       </c>
       <c r="N20" t="n">
-        <v>28.05</v>
+        <v>46.79</v>
       </c>
       <c r="O20" t="n">
-        <v>35220676930</v>
+        <v>4357725689750</v>
       </c>
       <c r="P20" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q20" t="n">
-        <v>8120</v>
+        <v>70000</v>
       </c>
       <c r="R20" t="n">
-        <v>-309000</v>
+        <v>-1876000</v>
       </c>
       <c r="S20" t="n">
-        <v>7000</v>
+        <v>784000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>기업 실적 및 성장성에 대한 부정적 전망, 투자 비판.</t>
+          <t>삼성전자 주가 부진에 대한 부정적 의견 및 하이닉스와의 비교. 노조 및 경영진 관련 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['실적', '성장성', '투자 비판']</t>
+          <t>['삼성전자', '하이닉스', '주가']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2326,13 +2326,13 @@
         <v>0.52</v>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F21" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="H21" t="n">
         <v>2.08</v>
@@ -2358,7 +2358,7 @@
         <v>1.56</v>
       </c>
       <c r="O21" t="n">
-        <v>71702919453</v>
+        <v>72177549183</v>
       </c>
       <c r="P21" t="n">
         <v>4335</v>
@@ -2418,7 +2418,7 @@
         <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F22" t="n">
         <v>67</v>
@@ -2427,7 +2427,7 @@
         <v>330</v>
       </c>
       <c r="H22" t="n">
-        <v>52.56</v>
+        <v>52.55</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>21.01</v>
       </c>
       <c r="O22" t="n">
-        <v>87628386400</v>
+        <v>89776303900</v>
       </c>
       <c r="P22" t="n">
         <v>69500</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10270</v>
+        <v>10300</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.32</v>
       </c>
       <c r="E23" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F23" t="n">
         <v>71</v>
       </c>
       <c r="G23" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H23" t="n">
         <v>0.9399999999999999</v>
@@ -2542,7 +2542,7 @@
         <v>0.62</v>
       </c>
       <c r="O23" t="n">
-        <v>152241849525</v>
+        <v>153244503025</v>
       </c>
       <c r="P23" t="n">
         <v>15960</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19440</v>
+        <v>19450</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>-2.60%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.38</v>
       </c>
       <c r="E24" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F24" t="n">
         <v>131</v>
       </c>
       <c r="G24" t="n">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="H24" t="n">
         <v>10.85</v>
@@ -2634,7 +2634,7 @@
         <v>10.47</v>
       </c>
       <c r="O24" t="n">
-        <v>294861460090</v>
+        <v>296687153790</v>
       </c>
       <c r="P24" t="n">
         <v>40350</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>원전 관련 호재 속 계약 체결 공시 확인, 일부 투자자 기대감.</t>
+          <t>원전 관련주 상승 및 대우건설 적정가 논의. 계약 체결 공시 언급.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['원전', '공시', '계약체결']</t>
+          <t>['원전', '계약', '적정가']</t>
         </is>
       </c>
       <c r="X24" t="n">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F2" t="n">
         <v>135</v>
       </c>
       <c r="G2" t="n">
-        <v>1713</v>
+        <v>1746</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29788795675</v>
+        <v>29788869875</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미 FDA 2A상 승인 기대감 및 병용요법 연구 결과 공개 예정. 외국인 매수세 유입.</t>
+          <t>페니트리움바이오, 미국 FDA 2A상 승인 및 뎅기열 치료제 글로벌 임상 결과 발표 기대감 고조. 다락손라십 대비 우수한 효능 및 병용 확장 전략에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA 2A상', '병용요법', '외국인 매수']</t>
+          <t>['FDA', '뎅기열', '병용 확장']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F3" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G3" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>233498007485</v>
+        <v>233499141095</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -768,7 +768,7 @@
         <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -854,13 +854,13 @@
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F5" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G5" t="n">
-        <v>1620</v>
+        <v>1652</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>530428985295</v>
+        <v>530851410975</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>원전 및 로봇 관련주 상승 전망. 단기 목표가 제시 및 외국 자본 유입 언급.</t>
+          <t>우리기술, 체코 원전 수주 기대감 및 하반기 주도주 전망. 정부 정책 및 외국 자본 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '로봇', '목표가']</t>
+          <t>['원전', '수주', '정책']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F6" t="n">
         <v>123</v>
       </c>
       <c r="G6" t="n">
-        <v>1360</v>
+        <v>1399</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>72172966185</v>
+        <v>72186149555</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뎅기열, 췌장암 치료제 등 신약 개발 기대감 및 공매도와의 경쟁.</t>
+          <t>현대바이오, 공매도 세력과의 경쟁 속 뎅기열 및 췌장암 치료제 관련 실험 결과 발표 기대감 고조. 페니트리움바이오의 최대 주주로서 전립선 치료제 데이터 발표에 대한 전망도 긍정적.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['신약 개발', '공매도', '임상 결과']</t>
+          <t>['뎅기열', '췌장암', '전립선']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1044,7 +1044,7 @@
         <v>128</v>
       </c>
       <c r="G7" t="n">
-        <v>676</v>
+        <v>698</v>
       </c>
       <c r="H7" t="n">
         <v>14.96</v>
@@ -1070,7 +1070,7 @@
         <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>168662127150</v>
+        <v>168678782250</v>
       </c>
       <c r="P7" t="n">
         <v>108900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>두산퓨얼셀, 2분기 실적 부진에도 불구하고 목표가 상향 및 수주 기대감으로 인한 단기 상승세.</t>
+          <t>두산퓨얼셀, 수주 건 확인 및 2분기 영업이익 부진에도 불구하고 향후 매출 성장성 및 목표가 상향 조정에 대한 기대감 형성. 기관 및 외인 매수세 유입 가능성 논의.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '목표가', '실적']</t>
+          <t>['수주', '영업이익', '매출 성장성']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1136,7 +1136,7 @@
         <v>170</v>
       </c>
       <c r="G8" t="n">
-        <v>1604</v>
+        <v>1635</v>
       </c>
       <c r="H8" t="n">
         <v>1.55</v>
@@ -1162,7 +1162,7 @@
         <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>449834620185</v>
+        <v>450052497625</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>빛과전자 수급 흡수 및 개인 매도세 속 상승 기대. 단기 박스권 돌파 및 우상향 추세.</t>
+          <t>대한광통신, 빛과전자와의 수급 연계 및 차트상 우상향 추세 분석. 외인, 기관, 투신 매수세 유입 및 박스권 돌파.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수급', '단기 박스권', '우상향']</t>
+          <t>['수급', '차트', '매수세']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="H9" t="n">
         <v>0.51</v>
@@ -1254,7 +1254,7 @@
         <v>0.61</v>
       </c>
       <c r="O9" t="n">
-        <v>18426089445</v>
+        <v>18440617725</v>
       </c>
       <c r="P9" t="n">
         <v>2930</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>강동씨앤엘, 반도체 클러스터 대장주 부각 속 대주주 매도 공시로 인한 단기 변동성 우려.</t>
+          <t>강동씨앤엘, 시멘트 공급 경쟁력 언급 및 반도체 사업 전환 가능성에 대한 기대감 형성. 대주주 매도 공시 이후 주가 변동성 및 향후 전망에 대한 논의.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '대주주매도', '전망']</t>
+          <t>['시멘트', '반도체', '대주주 매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>299</v>
+        <v>158</v>
       </c>
       <c r="F10" t="n">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="G10" t="n">
-        <v>509</v>
+        <v>315</v>
       </c>
       <c r="H10" t="n">
         <v>16.71</v>
@@ -1346,7 +1346,7 @@
         <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>102686244950</v>
+        <v>102689366250</v>
       </c>
       <c r="P10" t="n">
         <v>13000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>배당 및 주가 부진에 대한 언급. 투자자들의 실망감 표출.</t>
+          <t>한화머시너리앤서비스홀딩스, 배당 관련 논의 및 주가 하락에 대한 실망감 표현. 거래량 증가 및 손바뀜 가능성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['배당', '주가', '실망감']</t>
+          <t>['배당', '거래량', '주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1412,7 +1412,7 @@
         <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="H11" t="n">
         <v>39.3</v>
@@ -1438,7 +1438,7 @@
         <v>38.84</v>
       </c>
       <c r="O11" t="n">
-        <v>42724951310</v>
+        <v>42739037760</v>
       </c>
       <c r="P11" t="n">
         <v>19150</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>물량 터는 중이라는 의견과 함께 급락. 상패 직전 우려 및 유증 재료 소멸.</t>
+          <t>피노, 급격한 하락세 속 상폐 가능성 및 거래량 증가에 대한 우려 제기. 유상증자 재료 소멸 후 하방 압력 지속 및 투자자들의 부정적 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['물량 터는 중', '급락', '유증 재료 소멸']</t>
+          <t>['상폐', '거래량', '유상증자']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1501,10 +1501,10 @@
         <v>248</v>
       </c>
       <c r="F12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G12" t="n">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="H12" t="n">
         <v>3.19</v>
@@ -1530,7 +1530,7 @@
         <v>0.45</v>
       </c>
       <c r="O12" t="n">
-        <v>278852496482</v>
+        <v>278916980732</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>광통신 관련주 급등 및 빛과전자 강세 전망. 6G 기반 기술 및 글로벌 공급 언급.</t>
+          <t>빛과전자, 미국 광통신주 급등에 따른 기대감. 글로벌 회사 대량 공급 뉴스 및 6G 기반 기술 관련 긍정적 전망. 투기과열종목 지정 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '빛과전자', '6G']</t>
+          <t>['광통신', '6G', '뉴스']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,13 +1590,13 @@
         <v>-0.23</v>
       </c>
       <c r="E13" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="F13" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G13" t="n">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="H13" t="n">
         <v>5.26</v>
@@ -1622,7 +1622,7 @@
         <v>5.49</v>
       </c>
       <c r="O13" t="n">
-        <v>48057169110</v>
+        <v>48077305710</v>
       </c>
       <c r="P13" t="n">
         <v>2705</v>
@@ -1682,13 +1682,13 @@
         <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F14" t="n">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="G14" t="n">
-        <v>2145</v>
+        <v>2165</v>
       </c>
       <c r="H14" t="n">
         <v>50.66</v>
@@ -1714,7 +1714,7 @@
         <v>50.63</v>
       </c>
       <c r="O14" t="n">
-        <v>6512518537500</v>
+        <v>6513090185500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>SK하이닉스 상승 추세 전환 신호 및 목표가 상승 전망. 수급 및 악성매물 소화 언급.</t>
+          <t>SK하이닉스, 상승 추세 전환 신호 포착 및 60일선 돌파 기대감. 기관 및 외국인 매수세 유입 확인. 악성 매물 소화.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '상승 추세', '수급']</t>
+          <t>['상승추세', '기관', '외국인']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F15" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="G15" t="n">
-        <v>1775</v>
+        <v>1811</v>
       </c>
       <c r="H15" t="n">
         <v>23.61</v>
@@ -1806,7 +1806,7 @@
         <v>23.63</v>
       </c>
       <c r="O15" t="n">
-        <v>343506810000</v>
+        <v>343511670100</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1866,13 +1866,13 @@
         <v>1.4</v>
       </c>
       <c r="E16" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F16" t="n">
         <v>89</v>
       </c>
       <c r="G16" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="H16" t="n">
         <v>1.81</v>
@@ -1898,7 +1898,7 @@
         <v>0.41</v>
       </c>
       <c r="O16" t="n">
-        <v>121380006450</v>
+        <v>121407795120</v>
       </c>
       <c r="P16" t="n">
         <v>10300</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>강력 지지선 확인 및 상승 중. 레미콘 파업 이슈와 함께 상한가 기대감.</t>
+          <t>서산, 레미콘 파업 시작에 따른 기대감. 8200선 지지 및 주가 상승 흐름 분석. 개미 꼬시기 및 물갈이 정황.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['지지선', '레미콘 파업', '상한가 기대']</t>
+          <t>['레미콘', '파업', '주가']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="F17" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G17" t="n">
-        <v>1091</v>
+        <v>1106</v>
       </c>
       <c r="H17" t="n">
         <v>0.31</v>
@@ -1990,7 +1990,7 @@
         <v>0.23</v>
       </c>
       <c r="O17" t="n">
-        <v>544717252250</v>
+        <v>545161722950</v>
       </c>
       <c r="P17" t="n">
         <v>39350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>혈압 반기 관련 기술 및 유럽 진출 뉴스. 주가 최저점 및 반등 기대.</t>
+          <t>스카이랩스, 혈압 반지의 유럽 진출 뉴스 언급. 주가 급락 및 상장폐지 가능성에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['혈압 반지', '스카이랩스', '유럽 진출']</t>
+          <t>['혈압반지', '유럽진출', '주가']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>-2.16</v>
       </c>
       <c r="E18" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F18" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G18" t="n">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>2.16</v>
       </c>
       <c r="O18" t="n">
-        <v>50268749955</v>
+        <v>50281601625</v>
       </c>
       <c r="P18" t="n">
         <v>36200</v>
@@ -2142,10 +2142,10 @@
         <v>-0.36</v>
       </c>
       <c r="E19" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F19" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G19" t="n">
         <v>523</v>
@@ -2174,7 +2174,7 @@
         <v>28.05</v>
       </c>
       <c r="O19" t="n">
-        <v>37459877430</v>
+        <v>37473293480</v>
       </c>
       <c r="P19" t="n">
         <v>17950</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>LG디스플레이 주가 부진 및 매도 의견. AI 및 중국산 영향 언급.</t>
+          <t>LG디스플레이, 주가 부진 및 중국산 경쟁력 약화에 대한 부정적 전망. AI 및 차세대 기술 관련 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['LG디스플레이', '주가', '매도']</t>
+          <t>['주가', '중국산', 'AI']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>0.06</v>
       </c>
       <c r="E20" t="n">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F20" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G20" t="n">
-        <v>1997</v>
+        <v>2015</v>
       </c>
       <c r="H20" t="n">
         <v>46.85</v>
@@ -2266,7 +2266,7 @@
         <v>46.79</v>
       </c>
       <c r="O20" t="n">
-        <v>4357725689750</v>
+        <v>4357847234250</v>
       </c>
       <c r="P20" t="n">
         <v>374500</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>삼성전자 주가 부진에 대한 부정적 의견 및 하이닉스와의 비교. 노조 및 경영진 관련 언급.</t>
+          <t>삼성전자, 영업이익 1위에도 불구하고 하이닉스 대비 낮은 주가 상승률에 대한 불만 제기. 노조, 이재용 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['삼성전자', '하이닉스', '주가']</t>
+          <t>['영업이익', '노조', '주가']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,13 +2326,13 @@
         <v>0.52</v>
       </c>
       <c r="E21" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F21" t="n">
         <v>57</v>
       </c>
       <c r="G21" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="H21" t="n">
         <v>2.08</v>
@@ -2358,7 +2358,7 @@
         <v>1.56</v>
       </c>
       <c r="O21" t="n">
-        <v>72177549183</v>
+        <v>72217826348</v>
       </c>
       <c r="P21" t="n">
         <v>4335</v>
@@ -2418,13 +2418,13 @@
         <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F22" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G22" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="H22" t="n">
         <v>52.55</v>
@@ -2450,7 +2450,7 @@
         <v>21.01</v>
       </c>
       <c r="O22" t="n">
-        <v>89776303900</v>
+        <v>89776877650</v>
       </c>
       <c r="P22" t="n">
         <v>69500</v>
@@ -2510,13 +2510,13 @@
         <v>0.32</v>
       </c>
       <c r="E23" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F23" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G23" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H23" t="n">
         <v>0.9399999999999999</v>
@@ -2542,7 +2542,7 @@
         <v>0.62</v>
       </c>
       <c r="O23" t="n">
-        <v>153244503025</v>
+        <v>153308352725</v>
       </c>
       <c r="P23" t="n">
         <v>15960</v>
@@ -2602,13 +2602,13 @@
         <v>0.38</v>
       </c>
       <c r="E24" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F24" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G24" t="n">
-        <v>779</v>
+        <v>811</v>
       </c>
       <c r="H24" t="n">
         <v>10.85</v>
@@ -2634,7 +2634,7 @@
         <v>10.47</v>
       </c>
       <c r="O24" t="n">
-        <v>296687153790</v>
+        <v>296793564740</v>
       </c>
       <c r="P24" t="n">
         <v>40350</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>원전 관련주 상승 및 대우건설 적정가 논의. 계약 체결 공시 언급.</t>
+          <t>대우건설, 미국 원전 참여 기대감 속 계약 체결 공시 발표. 공매도 세력 및 단기 투자에 대한 언급.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['원전', '계약', '적정가']</t>
+          <t>['원전', '공시', '계약체결']</t>
         </is>
       </c>
       <c r="X24" t="n">

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8400</v>
+        <v>8810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+47.11%</t>
+          <t>+18.73%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G2" t="n">
-        <v>385</v>
+        <v>504</v>
       </c>
       <c r="H2" t="n">
         <v>1.17</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5710</v>
+        <v>7420</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="N2" t="n">
         <v>0.77</v>
       </c>
       <c r="O2" t="n">
-        <v>4849000000</v>
+        <v>25413713280</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>세계 폐암학회 발표 및 항암제 내성 극복 연구 결과 기반 기대감. 오가노이드 실험 성공 및 임상 2상 전초전 연구 언급.</t>
+          <t>항암제 내성 극복 및 오가노이드 실험 성공 관련 긍정적 뉴스. FDA 임상 2상 성공 기대감으로 급등세. 4연상 이상 목표.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['폐암학회', '항암제 내성', '오가노이드']</t>
+          <t>['항암제', '오가노이드', 'FDA']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,60 +655,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>159800</v>
+        <v>13910</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+15.80%</t>
+          <t>+15.05%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4</v>
+        <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>322</v>
+        <v>131</v>
       </c>
       <c r="H3" t="n">
-        <v>15.65</v>
+        <v>0.03</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>138000</v>
+        <v>12090</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12730</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>13910</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>12720</v>
       </c>
       <c r="N3" t="n">
-        <v>15.25</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>20781000000</v>
+        <v>39697337350</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>36200</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>8920</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>유가 폭등 및 정제마진 고공행진에 따른 긍정적 전망. JP모건 대량매수 패턴 언급.</t>
+          <t>이란 사태 고조로 인한 국제 유가 급등 및 흥구석유 주가 상승 기대감. 일시적인 유가 변동성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유가 폭등', '정제마진', 'JP모건']</t>
+          <t>['국제유가', '이란', '급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,67 +740,67 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14770</v>
+        <v>157700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+7.81%</t>
+          <t>+2.74%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.34</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="G4" t="n">
-        <v>246</v>
+        <v>334</v>
       </c>
       <c r="H4" t="n">
-        <v>2.89</v>
+        <v>15.65</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>13700</v>
+        <v>153500</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>155500</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>160800</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>154500</v>
       </c>
       <c r="N4" t="n">
-        <v>1.55</v>
+        <v>15.25</v>
       </c>
       <c r="O4" t="n">
-        <v>6035000000</v>
+        <v>57532692700</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>160800</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>87700</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 강세 및 AI 관련주로의 편입 기대감. 거래량 증가 및 상환가 가능성 언급.</t>
+          <t>유가 폭등 및 정제 마진 호조에 따른 긍정적 전망. JP모건 대량 매수 패턴 언급. 단기적 시세 영향.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '거래량']</t>
+          <t>['유가', '정제마진', 'JP모건']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1876000</v>
+        <v>1864000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+4.63%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="F5" t="n">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G5" t="n">
-        <v>2653</v>
+        <v>2168</v>
       </c>
       <c r="H5" t="n">
         <v>50.67</v>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1793000</v>
+        <v>1856000</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1879000</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1890000</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1858000</v>
       </c>
       <c r="N5" t="n">
         <v>50.66</v>
       </c>
       <c r="O5" t="n">
-        <v>170352000000</v>
+        <v>579305119500</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>293000</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SK하이닉스 ADR 신고가 돌파 및 가치 재평가 시작 전망. 연말 300만 돌파 및 250만 목표 제시.</t>
+          <t>SK하이닉스 ADR 및 미국 반도체 관련주 동반 상승에 따른 기대감. AI 관련 긍정적 전망과 자사주 매수 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['ADR', '가치 재평가', '신고가']</t>
+          <t>['ADR', '반도체', 'AI']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>89600</v>
+        <v>268000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>795</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>471</v>
       </c>
       <c r="G6" t="n">
-        <v>507</v>
+        <v>2535</v>
       </c>
       <c r="H6" t="n">
-        <v>23.65</v>
+        <v>46.81</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,28 +963,28 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>89500</v>
+        <v>269500</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>269000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>270500</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>267500</v>
       </c>
       <c r="N6" t="n">
-        <v>23.61</v>
+        <v>46.85</v>
       </c>
       <c r="O6" t="n">
-        <v>6725000000</v>
+        <v>281135630000</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>71600</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -994,20 +994,20 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>원전 관련 사업 호재 및 미국 원전 건설 수주 기대감. 웨스턴하우스 지분 인수 가능성 언급.</t>
+          <t>이재용·홍라희 지분 관련 언급 및 하이닉스 ADR 상승에 따른 기대감. 실질적인 주가 상승 근거는 부족.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '웨스턴하우스', '미국 건설']</t>
+          <t>['지분', '기대감', 'ADR']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>269000</v>
+        <v>89100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>770</v>
+        <v>91</v>
       </c>
       <c r="F7" t="n">
-        <v>466</v>
+        <v>66</v>
       </c>
       <c r="G7" t="n">
-        <v>2699</v>
+        <v>512</v>
       </c>
       <c r="H7" t="n">
-        <v>46.81</v>
+        <v>23.65</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,28 +1055,28 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>269500</v>
+        <v>91700</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>90700</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>89000</v>
       </c>
       <c r="N7" t="n">
-        <v>46.85</v>
+        <v>23.61</v>
       </c>
       <c r="O7" t="n">
-        <v>104779000000</v>
+        <v>23696976450</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1086,20 +1086,20 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>홍라희 여사 물량 소화 및 이재용 지분 취득 관련 언급. 하이닉스 ADR 급등에 따른 기대감 형성.</t>
+          <t>미국 원전 건설 수주 확정 및 웨스턴하우스 지분 인수 관련 호재. '팀코리아' 관련 긍정적 전망 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['홍라희', '이재용', '하이닉스 ADR']</t>
+          <t>['원전', '수주', '웨스턴하우스']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,191 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>18770</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-3.50%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="E8" t="n">
+        <v>41</v>
+      </c>
+      <c r="F8" t="n">
+        <v>27</v>
+      </c>
+      <c r="G8" t="n">
+        <v>136</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>19450</v>
+      </c>
+      <c r="K8" t="n">
+        <v>18900</v>
+      </c>
+      <c r="L8" t="n">
+        <v>19190</v>
+      </c>
+      <c r="M8" t="n">
+        <v>18670</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="O8" t="n">
+        <v>15402967435</v>
+      </c>
+      <c r="P8" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>원전 관련 건설 수주 기대감과 함께 주가 급락 우려 및 매도 의견 대립. 부정적 전망 다수.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['원전', '건설주', '급락']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14370</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-3.94%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G9" t="n">
+        <v>259</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>14960</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15040</v>
+      </c>
+      <c r="L9" t="n">
+        <v>15040</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14320</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O9" t="n">
+        <v>26089608820</v>
+      </c>
+      <c r="P9" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1263</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>미국 광통신 및 AI 관련주 강세에 따른 대한광통신 주가 상승 기대감. 거래량 증가 및 120일선 돌파 가능성.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['광통신', 'AI', '거래량']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>010170</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8810</v>
+        <v>5030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+18.73%</t>
+          <t>+151.50%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G2" t="n">
-        <v>504</v>
+        <v>46</v>
       </c>
       <c r="H2" t="n">
-        <v>1.17</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7420</v>
+        <v>2000</v>
       </c>
       <c r="K2" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="L2" t="n">
-        <v>9100</v>
+        <v>5660</v>
       </c>
       <c r="M2" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="N2" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>25413713280</v>
+        <v>284467308563</v>
       </c>
       <c r="P2" t="n">
-        <v>21500</v>
+        <v>5660</v>
       </c>
       <c r="Q2" t="n">
-        <v>2300</v>
+        <v>4000</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-134000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>항암제 내성 극복 및 오가노이드 실험 성공 관련 긍정적 뉴스. FDA 임상 2상 성공 기대감으로 급등세. 4연상 이상 목표.</t>
+          <t>스팩주 특성상 단기 수익 기대. 신재생 에너지 합병 관련 언급 있으며, 2천원 종가 예상 및 타이밍 중요성 강조.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['항암제', '오가노이드', 'FDA']</t>
+          <t>['스팩주', '신재생 에너지', '단기 수익']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>0197V0</t>
         </is>
       </c>
     </row>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13910</v>
+        <v>14910</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+15.05%</t>
+          <t>+23.33%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>196</v>
       </c>
       <c r="H3" t="n">
         <v>0.03</v>
@@ -693,7 +693,7 @@
         <v>12730</v>
       </c>
       <c r="L3" t="n">
-        <v>13910</v>
+        <v>14910</v>
       </c>
       <c r="M3" t="n">
         <v>12720</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>39697337350</v>
+        <v>106797590820</v>
       </c>
       <c r="P3" t="n">
         <v>36200</v>
@@ -711,14 +711,14 @@
         <v>8920</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>245000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>이란 사태 고조로 인한 국제 유가 급등 및 흥구석유 주가 상승 기대감. 일시적인 유가 변동성 언급.</t>
+          <t>중동 긴장 고조 및 유가 급등에 따른 주가 상승 기대. 트럼프 발언 및 유가 전망 관련 분석.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['국제유가', '이란', '급등']</t>
+          <t>['유가 급등', '중동 긴장', '트럼프']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>157700</v>
+        <v>8470</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+2.74%</t>
+          <t>+14.15%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="F4" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
-        <v>334</v>
+        <v>626</v>
       </c>
       <c r="H4" t="n">
-        <v>15.65</v>
+        <v>1.17</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>153500</v>
+        <v>7420</v>
       </c>
       <c r="K4" t="n">
-        <v>155500</v>
+        <v>8000</v>
       </c>
       <c r="L4" t="n">
-        <v>160800</v>
+        <v>9100</v>
       </c>
       <c r="M4" t="n">
-        <v>154500</v>
+        <v>8000</v>
       </c>
       <c r="N4" t="n">
-        <v>15.25</v>
+        <v>0.77</v>
       </c>
       <c r="O4" t="n">
-        <v>57532692700</v>
+        <v>38687484830</v>
       </c>
       <c r="P4" t="n">
-        <v>160800</v>
+        <v>21500</v>
       </c>
       <c r="Q4" t="n">
-        <v>87700</v>
+        <v>2300</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>108000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>유가 폭등 및 정제 마진 호조에 따른 긍정적 전망. JP모건 대량 매수 패턴 언급. 단기적 시세 영향.</t>
+          <t>세계 폐암학회 참여 및 키투르다 관련 임상 결과 발표. 항암제 내성 극복 기대감으로 인한 주가 급등 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유가', '정제마진', 'JP모건']</t>
+          <t>['폐암학회', '키투르다', '항암제 내성']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1864000</v>
+        <v>161700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+5.34%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>794</v>
+        <v>186</v>
       </c>
       <c r="F5" t="n">
-        <v>469</v>
+        <v>96</v>
       </c>
       <c r="G5" t="n">
-        <v>2168</v>
+        <v>475</v>
       </c>
       <c r="H5" t="n">
-        <v>50.67</v>
+        <v>15.65</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1856000</v>
+        <v>153500</v>
       </c>
       <c r="K5" t="n">
-        <v>1879000</v>
+        <v>155500</v>
       </c>
       <c r="L5" t="n">
-        <v>1890000</v>
+        <v>164700</v>
       </c>
       <c r="M5" t="n">
-        <v>1858000</v>
+        <v>154500</v>
       </c>
       <c r="N5" t="n">
-        <v>50.66</v>
+        <v>15.25</v>
       </c>
       <c r="O5" t="n">
-        <v>579305119500</v>
+        <v>149308564200</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>164700</v>
       </c>
       <c r="Q5" t="n">
-        <v>293000</v>
+        <v>87700</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SK하이닉스 ADR 및 미국 반도체 관련주 동반 상승에 따른 기대감. AI 관련 긍정적 전망과 자사주 매수 가능성 언급.</t>
+          <t>유가 폭등 및 정제마진 개선에 따른 긍정적 전망. 외인 대량 매수 이후 패턴 분석 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['ADR', '반도체', 'AI']</t>
+          <t>['유가', '정제마진', '외인 매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>268000</v>
+        <v>2125</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.04</v>
+        <v>0.34</v>
       </c>
       <c r="E6" t="n">
-        <v>795</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>471</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>2535</v>
+        <v>87</v>
       </c>
       <c r="H6" t="n">
-        <v>46.81</v>
+        <v>0.85</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>269500</v>
+        <v>2085</v>
       </c>
       <c r="K6" t="n">
-        <v>269000</v>
+        <v>2255</v>
       </c>
       <c r="L6" t="n">
-        <v>270500</v>
+        <v>2395</v>
       </c>
       <c r="M6" t="n">
-        <v>267500</v>
+        <v>2085</v>
       </c>
       <c r="N6" t="n">
-        <v>46.85</v>
+        <v>0.51</v>
       </c>
       <c r="O6" t="n">
-        <v>281135630000</v>
+        <v>12340697343</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>2930</v>
       </c>
       <c r="Q6" t="n">
-        <v>71600</v>
+        <v>910</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>이재용·홍라희 지분 관련 언급 및 하이닉스 ADR 상승에 따른 기대감. 실질적인 주가 상승 근거는 부족.</t>
+          <t>거래량 증가 및 주가 상승에 대한 기대감. 경영진 긍정 평가 및 매물 소화 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['지분', '기대감', 'ADR']</t>
+          <t>['거래량', '주가 상승', '경영진']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>89100</v>
+        <v>1849000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>91</v>
+        <v>794</v>
       </c>
       <c r="F7" t="n">
-        <v>66</v>
+        <v>468</v>
       </c>
       <c r="G7" t="n">
-        <v>512</v>
+        <v>1657</v>
       </c>
       <c r="H7" t="n">
-        <v>23.65</v>
+        <v>50.67</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>91700</v>
+        <v>1856000</v>
       </c>
       <c r="K7" t="n">
-        <v>90000</v>
+        <v>1879000</v>
       </c>
       <c r="L7" t="n">
-        <v>90700</v>
+        <v>1890000</v>
       </c>
       <c r="M7" t="n">
-        <v>89000</v>
+        <v>1848000</v>
       </c>
       <c r="N7" t="n">
-        <v>23.61</v>
+        <v>50.66</v>
       </c>
       <c r="O7" t="n">
-        <v>23696976450</v>
+        <v>1075477771000</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>293000</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 원전 건설 수주 확정 및 웨스턴하우스 지분 인수 관련 호재. '팀코리아' 관련 긍정적 전망 및 주가 상승 기대.</t>
+          <t>ADR 상승에 따른 본장 급등 기대감. 매물 부족 및 저점 매수 찬스 언급. 200 돌파 가능성 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '수주', '웨스턴하우스']</t>
+          <t>['ADR', '급등 기대', '저점 매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18770</v>
+        <v>267000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.50%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>41</v>
+        <v>792</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>464</v>
       </c>
       <c r="G8" t="n">
-        <v>136</v>
+        <v>2052</v>
       </c>
       <c r="H8" t="n">
-        <v>10.64</v>
+        <v>46.81</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>19450</v>
+        <v>269500</v>
       </c>
       <c r="K8" t="n">
-        <v>18900</v>
+        <v>269000</v>
       </c>
       <c r="L8" t="n">
-        <v>19190</v>
+        <v>270500</v>
       </c>
       <c r="M8" t="n">
-        <v>18670</v>
+        <v>266500</v>
       </c>
       <c r="N8" t="n">
-        <v>10.85</v>
+        <v>46.85</v>
       </c>
       <c r="O8" t="n">
-        <v>15402967435</v>
+        <v>532159491250</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>71600</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>68000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원전 관련 건설 수주 기대감과 함께 주가 급락 우려 및 매도 의견 대립. 부정적 전망 다수.</t>
+          <t>하이닉스 대비 삼성전자 주가 부진에 대한 언급 다수. 일부 투자자는 외국인 매도세 및 자사주 매입 관련 리스크 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '건설주', '급락']</t>
+          <t>['하이닉스', '외국인 매도', '자사주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,99 +1200,559 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14370</v>
+        <v>19020</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.94%</t>
+          <t>-2.21%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.34</v>
+        <v>-0.21</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>259</v>
+        <v>166</v>
       </c>
       <c r="H9" t="n">
-        <v>2.89</v>
+        <v>10.64</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14960</v>
+        <v>19450</v>
       </c>
       <c r="K9" t="n">
-        <v>15040</v>
+        <v>18900</v>
       </c>
       <c r="L9" t="n">
-        <v>15040</v>
+        <v>19220</v>
       </c>
       <c r="M9" t="n">
-        <v>14320</v>
+        <v>18670</v>
       </c>
       <c r="N9" t="n">
-        <v>1.55</v>
+        <v>10.85</v>
       </c>
       <c r="O9" t="n">
-        <v>26089608820</v>
+        <v>29561633500</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>1263</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 광통신 및 AI 관련주 강세에 따른 대한광통신 주가 상승 기대감. 거래량 증가 및 120일선 돌파 가능성.</t>
+          <t>원전 관련 기대감 및 중동 정세 언급. 일부 투자자는 주가 하락 이유 분석 및 반등 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '거래량']</t>
+          <t>['원전', '중동', '주가 분석']</t>
         </is>
       </c>
       <c r="X9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>89500</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-2.40%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E10" t="n">
+        <v>117</v>
+      </c>
+      <c r="F10" t="n">
+        <v>83</v>
+      </c>
+      <c r="G10" t="n">
+        <v>606</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>91700</v>
+      </c>
+      <c r="K10" t="n">
+        <v>90000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>90700</v>
+      </c>
+      <c r="M10" t="n">
+        <v>88400</v>
+      </c>
+      <c r="N10" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="O10" t="n">
+        <v>47170860100</v>
+      </c>
+      <c r="P10" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>원전 관련주로서 최고 호재가 부각되며 10만원 터치 기대감이 형성됨. 웨스팅하우스 지분 인수 가능성 및 '팀 코리아'의 미국 원전 건설 참여 소식이 긍정적 요인으로 작용하나, 외인 트릭 및 공매도에 대한 경계심도 존재함.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['원전', '웨스팅하우스', '팀 코리아']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
         <v>12</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>14520</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-2.94%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E11" t="n">
+        <v>80</v>
+      </c>
+      <c r="F11" t="n">
+        <v>52</v>
+      </c>
+      <c r="G11" t="n">
+        <v>291</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>14960</v>
+      </c>
+      <c r="K11" t="n">
+        <v>15040</v>
+      </c>
+      <c r="L11" t="n">
+        <v>15040</v>
+      </c>
+      <c r="M11" t="n">
+        <v>14190</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O11" t="n">
+        <v>45206750260</v>
+      </c>
+      <c r="P11" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1263</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-191000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>미국 광통신 관련주로 부각되며 16000원 돌파 기대감이 형성되었으나, 외인 인기 순위 1위 등에도 불구하고 상승 추세는 불확실함. 시외 상승 후 급락 가능성도 제기됨.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['광통신', 'AI 관련주', '시간외']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>우리기술</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>13740</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-4.05%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E12" t="n">
+        <v>58</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43</v>
+      </c>
+      <c r="G12" t="n">
+        <v>183</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>14320</v>
+      </c>
+      <c r="K12" t="n">
+        <v>13800</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13900</v>
+      </c>
+      <c r="M12" t="n">
+        <v>13260</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="O12" t="n">
+        <v>45246109425</v>
+      </c>
+      <c r="P12" t="n">
+        <v>30200</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3540</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-82000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>공매도 금지 지정 관련 언급. 일부 투자자는 주가 하락 예상 및 단타 매매 전략 제시. 그래핀 개발 관련 내용도 포함.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['공매도 금지', '주가 하락', '그래핀']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>032820</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>한화머시너리앤서비스홀딩스</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>6510</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-5.10%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="E13" t="n">
+        <v>42</v>
+      </c>
+      <c r="F13" t="n">
+        <v>32</v>
+      </c>
+      <c r="G13" t="n">
+        <v>98</v>
+      </c>
+      <c r="H13" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>6860</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6800</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6820</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6490</v>
+      </c>
+      <c r="N13" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4586562845</v>
+      </c>
+      <c r="P13" t="n">
+        <v>13000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6030</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>외국인 매도세 및 주가 하락에 대한 우려. 로봇 및 반도체 관련 기대감에도 불구하고 주가 흐름 부진.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['외국인 매도', '로봇', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0220W0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>삼미금속</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>12350</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-5.22%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="E14" t="n">
+        <v>43</v>
+      </c>
+      <c r="F14" t="n">
+        <v>32</v>
+      </c>
+      <c r="G14" t="n">
+        <v>38</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>13030</v>
+      </c>
+      <c r="K14" t="n">
+        <v>13160</v>
+      </c>
+      <c r="L14" t="n">
+        <v>13240</v>
+      </c>
+      <c r="M14" t="n">
+        <v>12150</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O14" t="n">
+        <v>35283481460</v>
+      </c>
+      <c r="P14" t="n">
+        <v>20850</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4020</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>3500억 달러 규모의 대미 투자 관련 호재가 언급되었으나, 주가는 5% 이상 하락하며 투자자들의 불안감이 커지고 있음. 일부 투자자는 매도 후 다른 종목으로 이동함.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['대미 투자', '원전', '악재']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>012210</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5030</v>
+        <v>4800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+151.50%</t>
+          <t>+140.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F2" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G2" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>284467308563</v>
+        <v>313709843048</v>
       </c>
       <c r="P2" t="n">
         <v>5660</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>스팩주 특성상 단기 수익 기대. 신재생 에너지 합병 관련 언급 있으며, 2천원 종가 예상 및 타이밍 중요성 강조.</t>
+          <t>합병 대상 업종(신재생에너지)에 대한 언급과 스팩주의 일반적인 주가 패턴에 대한 의견 교환. 단기 수익 실현 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '신재생 에너지', '단기 수익']</t>
+          <t>['스팩주', '합병', '수익']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14910</v>
+        <v>14990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+23.33%</t>
+          <t>+23.99%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="H3" t="n">
         <v>0.03</v>
@@ -693,7 +693,7 @@
         <v>12730</v>
       </c>
       <c r="L3" t="n">
-        <v>14910</v>
+        <v>15100</v>
       </c>
       <c r="M3" t="n">
         <v>12720</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>106797590820</v>
+        <v>133418021815</v>
       </c>
       <c r="P3" t="n">
         <v>36200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>중동 긴장 고조 및 유가 급등에 따른 주가 상승 기대. 트럼프 발언 및 유가 전망 관련 분석.</t>
+          <t>이란발 지정학적 리스크로 인한 유가 급등에 따른 기대감 표현. 단기 매매 및 유가 변동성 주의 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유가 급등', '중동 긴장', '트럼프']</t>
+          <t>['유가', '이란', '지정학적']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8470</v>
+        <v>8350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+14.15%</t>
+          <t>+12.53%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G4" t="n">
-        <v>626</v>
+        <v>675</v>
       </c>
       <c r="H4" t="n">
         <v>1.17</v>
@@ -794,7 +794,7 @@
         <v>0.77</v>
       </c>
       <c r="O4" t="n">
-        <v>38687484830</v>
+        <v>41975027490</v>
       </c>
       <c r="P4" t="n">
         <v>21500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>세계 폐암학회 참여 및 키투르다 관련 임상 결과 발표. 항암제 내성 극복 기대감으로 인한 주가 급등 전망.</t>
+          <t>항암제 내성 극복 및 임상 성공에 대한 강한 기대감 표현. 글로벌 제약사 참여 및 오가노이드 기술 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['폐암학회', '키투르다', '항암제 내성']</t>
+          <t>['항암제', '임상', '오가노이드']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>161700</v>
+        <v>158400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+5.34%</t>
+          <t>+3.19%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="F5" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H5" t="n">
         <v>15.65</v>
@@ -886,7 +886,7 @@
         <v>15.25</v>
       </c>
       <c r="O5" t="n">
-        <v>149308564200</v>
+        <v>181131186300</v>
       </c>
       <c r="P5" t="n">
         <v>164700</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>유가 폭등 및 정제마진 개선에 따른 긍정적 전망. 외인 대량 매수 이후 패턴 분석 및 주가 상승 기대.</t>
+          <t>고유가 상황 속 긍정적 전망, 정제마진 및 유가 상승에 따른 수익 기대. JP모건 매수 패턴 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가', '정제마진', '외인 매수']</t>
+          <t>['유가', '정제마진', 'JP모건']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2125</v>
+        <v>2105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.34</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H6" t="n">
         <v>0.85</v>
@@ -972,13 +972,13 @@
         <v>2395</v>
       </c>
       <c r="M6" t="n">
-        <v>2085</v>
+        <v>2075</v>
       </c>
       <c r="N6" t="n">
         <v>0.51</v>
       </c>
       <c r="O6" t="n">
-        <v>12340697343</v>
+        <v>13079081685</v>
       </c>
       <c r="P6" t="n">
         <v>2930</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>거래량 증가 및 주가 상승에 대한 기대감. 경영진 긍정 평가 및 매물 소화 관련 언급.</t>
+          <t>거래량 급증 및 경영진에 대한 긍정적 언급과 함께, 투자자들의 불안감 및 저항선에 대한 논의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['거래량', '주가 상승', '경영진']</t>
+          <t>['거래량', '경영진', '저항선']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1849000</v>
+        <v>1832000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="F7" t="n">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="G7" t="n">
-        <v>1657</v>
+        <v>1403</v>
       </c>
       <c r="H7" t="n">
         <v>50.67</v>
@@ -1064,13 +1064,13 @@
         <v>1890000</v>
       </c>
       <c r="M7" t="n">
-        <v>1848000</v>
+        <v>1832000</v>
       </c>
       <c r="N7" t="n">
         <v>50.66</v>
       </c>
       <c r="O7" t="n">
-        <v>1075477771000</v>
+        <v>1311335510500</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>ADR 상승에 따른 본장 급등 기대감. 매물 부족 및 저점 매수 찬스 언급. 200 돌파 가능성 제기.</t>
+          <t>ADR 신고가 및 프리장 흐름을 기반으로 한 강한 상승 기대감 표현. 리밸런싱 물량 부담 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['ADR', '급등 기대', '저점 매수']</t>
+          <t>['ADR', '프리장', '상승']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>267000</v>
+        <v>265500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F8" t="n">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="G8" t="n">
-        <v>2052</v>
+        <v>1790</v>
       </c>
       <c r="H8" t="n">
         <v>46.81</v>
@@ -1156,13 +1156,13 @@
         <v>270500</v>
       </c>
       <c r="M8" t="n">
-        <v>266500</v>
+        <v>265500</v>
       </c>
       <c r="N8" t="n">
         <v>46.85</v>
       </c>
       <c r="O8" t="n">
-        <v>532159491250</v>
+        <v>622498905500</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>하이닉스 대비 삼성전자 주가 부진에 대한 언급 다수. 일부 투자자는 외국인 매도세 및 자사주 매입 관련 리스크 제기.</t>
+          <t>하이닉스와의 비교 속 부진한 주가 흐름, 자사주 매입 리스크 언급. 정치 관련 언급 다수.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['하이닉스', '외국인 매도', '자사주']</t>
+          <t>['자사주', '하이닉스', '주가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19020</v>
+        <v>18860</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-3.03%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.21</v>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H9" t="n">
         <v>10.64</v>
@@ -1254,7 +1254,7 @@
         <v>10.85</v>
       </c>
       <c r="O9" t="n">
-        <v>29561633500</v>
+        <v>32811826595</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>89500</v>
+        <v>88700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.40%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="F10" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G10" t="n">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="H10" t="n">
         <v>23.65</v>
@@ -1346,7 +1346,7 @@
         <v>23.61</v>
       </c>
       <c r="O10" t="n">
-        <v>47170860100</v>
+        <v>54312506650</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14520</v>
+        <v>14410</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.94%</t>
+          <t>-3.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1.34</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="H11" t="n">
         <v>2.89</v>
@@ -1438,7 +1438,7 @@
         <v>1.55</v>
       </c>
       <c r="O11" t="n">
-        <v>45206750260</v>
+        <v>51488297895</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주로 부각되며 16000원 돌파 기대감이 형성되었으나, 외인 인기 순위 1위 등에도 불구하고 상승 추세는 불확실함. 시외 상승 후 급락 가능성도 제기됨.</t>
+          <t>미국 광통신 관련주로 언급되며, 16,000원 돌파 기대감과 함께 외인 인기가 높은 것으로 나타남. 다만, 일부 부정적 의견과 함께 급락 가능성도 제기됨.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', 'AI 관련주', '시간외']</t>
+          <t>['광통신', 'AI', '시간외']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13740</v>
+        <v>14920</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>-4.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="G12" t="n">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="H12" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14320</v>
+        <v>15640</v>
       </c>
       <c r="K12" t="n">
-        <v>13800</v>
+        <v>15600</v>
       </c>
       <c r="L12" t="n">
-        <v>13900</v>
+        <v>15600</v>
       </c>
       <c r="M12" t="n">
-        <v>13260</v>
+        <v>14845</v>
       </c>
       <c r="N12" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>45246109425</v>
+        <v>10847373930</v>
       </c>
       <c r="P12" t="n">
-        <v>30200</v>
+        <v>19380</v>
       </c>
       <c r="Q12" t="n">
-        <v>3540</v>
+        <v>3200</v>
       </c>
       <c r="R12" t="n">
-        <v>-82000</v>
+        <v>-9000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>공매도 금지 지정 관련 언급. 일부 투자자는 주가 하락 예상 및 단타 매매 전략 제시. 그래핀 개발 관련 내용도 포함.</t>
+          <t>주가 하락세 지속 및 재료 약화에 대한 실망감 표현. 반도체 인재 양성 등 지역 개발 이슈 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도 금지', '주가 하락', '그래핀']</t>
+          <t>['주가', '재료', '반도체']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6510</v>
+        <v>13500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-5.10%</t>
+          <t>-5.73%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.03</v>
+        <v>0.45</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>98</v>
+        <v>202</v>
       </c>
       <c r="H13" t="n">
-        <v>15.68</v>
+        <v>6.09</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6860</v>
+        <v>14320</v>
       </c>
       <c r="K13" t="n">
-        <v>6800</v>
+        <v>13800</v>
       </c>
       <c r="L13" t="n">
-        <v>6820</v>
+        <v>13900</v>
       </c>
       <c r="M13" t="n">
-        <v>6490</v>
+        <v>13260</v>
       </c>
       <c r="N13" t="n">
-        <v>16.71</v>
+        <v>5.64</v>
       </c>
       <c r="O13" t="n">
-        <v>4586562845</v>
+        <v>50989762540</v>
       </c>
       <c r="P13" t="n">
-        <v>13000</v>
+        <v>30200</v>
       </c>
       <c r="Q13" t="n">
-        <v>6030</v>
+        <v>3540</v>
       </c>
       <c r="R13" t="n">
-        <v>-20000</v>
+        <v>-82000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외국인 매도세 및 주가 하락에 대한 우려. 로봇 및 반도체 관련 기대감에도 불구하고 주가 흐름 부진.</t>
+          <t>공매도 금지 조치에도 불구하고 하락세를 예상하며 단기 매도 의견 제시. 그래핀 개발 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외국인 매도', '로봇', '주가 하락']</t>
+          <t>['공매도', '하락', '그래핀']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12350</v>
+        <v>12260</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-5.22%</t>
+          <t>-5.91%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.22</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H14" t="n">
         <v>0.14</v>
@@ -1714,7 +1714,7 @@
         <v>0.36</v>
       </c>
       <c r="O14" t="n">
-        <v>35283481460</v>
+        <v>37674448945</v>
       </c>
       <c r="P14" t="n">
         <v>20850</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>3500억 달러 규모의 대미 투자 관련 호재가 언급되었으나, 주가는 5% 이상 하락하며 투자자들의 불안감이 커지고 있음. 일부 투자자는 매도 후 다른 종목으로 이동함.</t>
+          <t>창사 이래 최대 호재 및 3500억 달러 규모 대미 투자 관련 언급이 있으나, 원전 하락세와 더불어 5% 이상 하락하며 투자자들의 혼란과 부정적인 심리가 나타남.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대미 투자', '원전', '악재']</t>
+          <t>['대미 투자', '원전', '호재']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1753,6 +1753,98 @@
       <c r="Z14" t="inlineStr">
         <is>
           <t>012210</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>한화머시너리앤서비스홀딩스</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6430</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-6.27%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="E15" t="n">
+        <v>51</v>
+      </c>
+      <c r="F15" t="n">
+        <v>36</v>
+      </c>
+      <c r="G15" t="n">
+        <v>131</v>
+      </c>
+      <c r="H15" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>6860</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6800</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6820</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6400</v>
+      </c>
+      <c r="N15" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5839987155</v>
+      </c>
+      <c r="P15" t="n">
+        <v>13000</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6030</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>외국인 매도세와 주가 장난질에 대한 부정적 인식, 잡주 취급. 로봇/반도체 관련 언급.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['외국인', '주가', '로봇']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>0220W0</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4800</v>
+        <v>4990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+140.00%</t>
+          <t>+149.50%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>313709843048</v>
+        <v>377384884908</v>
       </c>
       <c r="P2" t="n">
         <v>5660</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>합병 대상 업종(신재생에너지)에 대한 언급과 스팩주의 일반적인 주가 패턴에 대한 의견 교환. 단기 수익 실현 언급.</t>
+          <t>엔에이치스팩34호, 합병 대상 업종 신재생에너지 관련 기대감 있으나 스팩주 특성상 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '합병', '수익']</t>
+          <t>['스팩주', '신재생에너지', '하락']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14990</v>
+        <v>14980</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+23.99%</t>
+          <t>+23.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="G3" t="n">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="H3" t="n">
         <v>0.03</v>
@@ -693,7 +693,7 @@
         <v>12730</v>
       </c>
       <c r="L3" t="n">
-        <v>15100</v>
+        <v>15120</v>
       </c>
       <c r="M3" t="n">
         <v>12720</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>133418021815</v>
+        <v>150781273085</v>
       </c>
       <c r="P3" t="n">
         <v>36200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>이란발 지정학적 리스크로 인한 유가 급등에 따른 기대감 표현. 단기 매매 및 유가 변동성 주의 언급.</t>
+          <t>흥구석유, 중동 긴장 고조로 인한 유가 급등세 속 상승 기대감. 단기 차익 실현 매물 가능성도 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유가', '이란', '지정학적']</t>
+          <t>['유가급등', '중동', '차익실현']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8350</v>
+        <v>3580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+12.53%</t>
+          <t>+15.30%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>675</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7420</v>
+        <v>3105</v>
       </c>
       <c r="K4" t="n">
-        <v>8000</v>
+        <v>3170</v>
       </c>
       <c r="L4" t="n">
-        <v>9100</v>
+        <v>3775</v>
       </c>
       <c r="M4" t="n">
-        <v>8000</v>
+        <v>3165</v>
       </c>
       <c r="N4" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>41975027490</v>
+        <v>14153552503</v>
       </c>
       <c r="P4" t="n">
-        <v>21500</v>
+        <v>20800</v>
       </c>
       <c r="Q4" t="n">
-        <v>2300</v>
+        <v>1700</v>
       </c>
       <c r="R4" t="n">
-        <v>108000</v>
+        <v>24000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>항암제 내성 극복 및 임상 성공에 대한 강한 기대감 표현. 글로벌 제약사 참여 및 오가노이드 기술 언급.</t>
+          <t>20% 이상 상승하며 외인 수급 긍정적 신호, 단기 과열 및 주가 조작 의혹 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['항암제', '임상', '오가노이드']</t>
+          <t>['수급', '단기과열', '주가조작']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>950250</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>158400</v>
+        <v>7930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+3.19%</t>
+          <t>+6.87%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>201</v>
+        <v>145</v>
       </c>
       <c r="F5" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
-        <v>493</v>
+        <v>743</v>
       </c>
       <c r="H5" t="n">
-        <v>15.65</v>
+        <v>1.17</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>153500</v>
+        <v>7420</v>
       </c>
       <c r="K5" t="n">
-        <v>155500</v>
+        <v>8000</v>
       </c>
       <c r="L5" t="n">
-        <v>164700</v>
+        <v>9100</v>
       </c>
       <c r="M5" t="n">
-        <v>154500</v>
+        <v>7930</v>
       </c>
       <c r="N5" t="n">
-        <v>15.25</v>
+        <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>181131186300</v>
+        <v>45351366880</v>
       </c>
       <c r="P5" t="n">
-        <v>164700</v>
+        <v>21500</v>
       </c>
       <c r="Q5" t="n">
-        <v>87700</v>
+        <v>2300</v>
       </c>
       <c r="R5" t="n">
-        <v>56000</v>
+        <v>108000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>고유가 상황 속 긍정적 전망, 정제마진 및 유가 상승에 따른 수익 기대. JP모건 매수 패턴 언급.</t>
+          <t>페니트리움바이오, 세계 최초 항암제 내성 극복 기술 개발 성공 및 글로벌 제약사 참여 기대감. 5연상 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가', '정제마진', 'JP모건']</t>
+          <t>['항암제내성', '오가노이드', '5연상']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2105</v>
+        <v>4005</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+5.12%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.34</v>
+        <v>-1.62</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H6" t="n">
-        <v>0.85</v>
+        <v>1.57</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2085</v>
+        <v>3810</v>
       </c>
       <c r="K6" t="n">
-        <v>2255</v>
+        <v>3870</v>
       </c>
       <c r="L6" t="n">
-        <v>2395</v>
+        <v>4250</v>
       </c>
       <c r="M6" t="n">
-        <v>2075</v>
+        <v>3660</v>
       </c>
       <c r="N6" t="n">
-        <v>0.51</v>
+        <v>3.19</v>
       </c>
       <c r="O6" t="n">
-        <v>13079081685</v>
+        <v>87185636585</v>
       </c>
       <c r="P6" t="n">
-        <v>2930</v>
+        <v>8100</v>
       </c>
       <c r="Q6" t="n">
-        <v>910</v>
+        <v>592</v>
       </c>
       <c r="R6" t="n">
-        <v>63000</v>
+        <v>365000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>거래량 급증 및 경영진에 대한 긍정적 언급과 함께, 투자자들의 불안감 및 저항선에 대한 논의.</t>
+          <t>빛과전자, AI 데이터센터·6G 광통신 기술 개발 발표로 인한 기대감. 투경 회피 및 상승 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['거래량', '경영진', '저항선']</t>
+          <t>['AI', '6G', '광통신']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1832000</v>
+        <v>158100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>+3.00%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>780</v>
+        <v>225</v>
       </c>
       <c r="F7" t="n">
-        <v>457</v>
+        <v>115</v>
       </c>
       <c r="G7" t="n">
-        <v>1403</v>
+        <v>575</v>
       </c>
       <c r="H7" t="n">
-        <v>50.67</v>
+        <v>15.65</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1856000</v>
+        <v>153500</v>
       </c>
       <c r="K7" t="n">
-        <v>1879000</v>
+        <v>155500</v>
       </c>
       <c r="L7" t="n">
-        <v>1890000</v>
+        <v>164700</v>
       </c>
       <c r="M7" t="n">
-        <v>1832000</v>
+        <v>154500</v>
       </c>
       <c r="N7" t="n">
-        <v>50.66</v>
+        <v>15.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1311335510500</v>
+        <v>196907001300</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>164700</v>
       </c>
       <c r="Q7" t="n">
-        <v>293000</v>
+        <v>87700</v>
       </c>
       <c r="R7" t="n">
-        <v>-48000</v>
+        <v>56000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>ADR 신고가 및 프리장 흐름을 기반으로 한 강한 상승 기대감 표현. 리밸런싱 물량 부담 언급.</t>
+          <t>SK이노베이션, 유가 폭등 및 정제마진 고공행진으로 인한 실적 개선 기대감. 단기 상승 후 조정 가능성도 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['ADR', '프리장', '상승']</t>
+          <t>['유가폭등', '정제마진', '실적개선']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>265500</v>
+        <v>2120</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>+1.68%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.04</v>
+        <v>0.34</v>
       </c>
       <c r="E8" t="n">
-        <v>791</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>471</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>1790</v>
+        <v>104</v>
       </c>
       <c r="H8" t="n">
-        <v>46.81</v>
+        <v>0.85</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>269500</v>
+        <v>2085</v>
       </c>
       <c r="K8" t="n">
-        <v>269000</v>
+        <v>2255</v>
       </c>
       <c r="L8" t="n">
-        <v>270500</v>
+        <v>2395</v>
       </c>
       <c r="M8" t="n">
-        <v>265500</v>
+        <v>2075</v>
       </c>
       <c r="N8" t="n">
-        <v>46.85</v>
+        <v>0.51</v>
       </c>
       <c r="O8" t="n">
-        <v>622498905500</v>
+        <v>13535012145</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>2930</v>
       </c>
       <c r="Q8" t="n">
-        <v>71600</v>
+        <v>910</v>
       </c>
       <c r="R8" t="n">
-        <v>68000</v>
+        <v>63000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>하이닉스와의 비교 속 부진한 주가 흐름, 자사주 매입 리스크 언급. 정치 관련 언급 다수.</t>
+          <t>강동씨앤엘, 단기 급등 후 차익 실현 매물 출회 및 저항선 언급. 일부 부정적 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주', '하이닉스', '주가']</t>
+          <t>['차익실현', '저항선', '부정적']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18860</v>
+        <v>1836000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>-1.08%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.21</v>
+        <v>0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>785</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>458</v>
       </c>
       <c r="G9" t="n">
-        <v>172</v>
+        <v>1384</v>
       </c>
       <c r="H9" t="n">
-        <v>10.64</v>
+        <v>50.67</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>19450</v>
+        <v>1856000</v>
       </c>
       <c r="K9" t="n">
-        <v>18900</v>
+        <v>1879000</v>
       </c>
       <c r="L9" t="n">
-        <v>19220</v>
+        <v>1890000</v>
       </c>
       <c r="M9" t="n">
-        <v>18670</v>
+        <v>1829000</v>
       </c>
       <c r="N9" t="n">
-        <v>10.85</v>
+        <v>50.66</v>
       </c>
       <c r="O9" t="n">
-        <v>32811826595</v>
+        <v>1496230542000</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>293000</v>
       </c>
       <c r="R9" t="n">
-        <v>87000</v>
+        <v>-48000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 및 중동 정세 언급. 일부 투자자는 주가 하락 이유 분석 및 반등 기대.</t>
+          <t>SK하이닉스, ADR 상승에 따른 본장 급등 기대감 있으나 대규모 매도 물량 출회 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '중동', '주가 분석']</t>
+          <t>['ADR', '급등', '매도물량']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88700</v>
+        <v>265750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.27%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>129</v>
+        <v>784</v>
       </c>
       <c r="F10" t="n">
-        <v>90</v>
+        <v>467</v>
       </c>
       <c r="G10" t="n">
-        <v>622</v>
+        <v>1560</v>
       </c>
       <c r="H10" t="n">
-        <v>23.65</v>
+        <v>46.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>91700</v>
+        <v>269500</v>
       </c>
       <c r="K10" t="n">
-        <v>90000</v>
+        <v>269000</v>
       </c>
       <c r="L10" t="n">
-        <v>90700</v>
+        <v>270500</v>
       </c>
       <c r="M10" t="n">
-        <v>88400</v>
+        <v>265000</v>
       </c>
       <c r="N10" t="n">
-        <v>23.61</v>
+        <v>46.85</v>
       </c>
       <c r="O10" t="n">
-        <v>54312506650</v>
+        <v>737857933500</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>71600</v>
       </c>
       <c r="R10" t="n">
-        <v>-1000</v>
+        <v>68000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>원전 관련주로서 최고 호재가 부각되며 10만원 터치 기대감이 형성됨. 웨스팅하우스 지분 인수 가능성 및 '팀 코리아'의 미국 원전 건설 참여 소식이 긍정적 요인으로 작용하나, 외인 트릭 및 공매도에 대한 경계심도 존재함.</t>
+          <t>삼성전자, 자사주 매입 리스크와 주주환원 요구 제기. 일부 투자자 매도 의견.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '웨스팅하우스', '팀 코리아']</t>
+          <t>['자사주매입', '주주환원', '매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14410</v>
+        <v>18960</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.68%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.34</v>
+        <v>-0.21</v>
       </c>
       <c r="E11" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>298</v>
+        <v>192</v>
       </c>
       <c r="H11" t="n">
-        <v>2.89</v>
+        <v>10.64</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14960</v>
+        <v>19450</v>
       </c>
       <c r="K11" t="n">
-        <v>15040</v>
+        <v>18900</v>
       </c>
       <c r="L11" t="n">
-        <v>15040</v>
+        <v>19220</v>
       </c>
       <c r="M11" t="n">
-        <v>14190</v>
+        <v>18670</v>
       </c>
       <c r="N11" t="n">
-        <v>1.55</v>
+        <v>10.85</v>
       </c>
       <c r="O11" t="n">
-        <v>51488297895</v>
+        <v>36005098945</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>1263</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-191000</v>
+        <v>87000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주로 언급되며, 16,000원 돌파 기대감과 함께 외인 인기가 높은 것으로 나타남. 다만, 일부 부정적 의견과 함께 급락 가능성도 제기됨.</t>
+          <t>대우건설, 미국 투자 및 원전 관련 긍정적 기대감 속 급등 가능성 언급. 일부는 하락 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '시간외']</t>
+          <t>['미국투자', '원전', '급등']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14920</v>
+        <v>89000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.60%</t>
+          <t>-2.94%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>41</v>
+        <v>136</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="G12" t="n">
-        <v>143</v>
+        <v>601</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>15640</v>
+        <v>91700</v>
       </c>
       <c r="K12" t="n">
-        <v>15600</v>
+        <v>90000</v>
       </c>
       <c r="L12" t="n">
-        <v>15600</v>
+        <v>90700</v>
       </c>
       <c r="M12" t="n">
-        <v>14845</v>
+        <v>88400</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>23.61</v>
       </c>
       <c r="O12" t="n">
-        <v>10847373930</v>
+        <v>62734295950</v>
       </c>
       <c r="P12" t="n">
-        <v>19380</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>3200</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-9000</v>
+        <v>-1000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주가 하락세 지속 및 재료 약화에 대한 실망감 표현. 반도체 인재 양성 등 지역 개발 이슈 언급.</t>
+          <t>원전 사업 수주 기대감 및 웨스팅하우스 인수전 참여 가능성, 10만원 터치 및 전약후강 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가', '재료', '반도체']</t>
+          <t>['원전', '수주', '인수전']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13500</v>
+        <v>14440</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-5.73%</t>
+          <t>-3.48%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.45</v>
+        <v>1.34</v>
       </c>
       <c r="E13" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>202</v>
+        <v>300</v>
       </c>
       <c r="H13" t="n">
-        <v>6.09</v>
+        <v>2.89</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14320</v>
+        <v>14960</v>
       </c>
       <c r="K13" t="n">
-        <v>13800</v>
+        <v>15040</v>
       </c>
       <c r="L13" t="n">
-        <v>13900</v>
+        <v>15040</v>
       </c>
       <c r="M13" t="n">
-        <v>13260</v>
+        <v>14190</v>
       </c>
       <c r="N13" t="n">
-        <v>5.64</v>
+        <v>1.55</v>
       </c>
       <c r="O13" t="n">
-        <v>50989762540</v>
+        <v>55550569390</v>
       </c>
       <c r="P13" t="n">
-        <v>30200</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3540</v>
+        <v>1263</v>
       </c>
       <c r="R13" t="n">
-        <v>-82000</v>
+        <v>-191000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 금지 조치에도 불구하고 하락세를 예상하며 단기 매도 의견 제시. 그래핀 개발 관련 언급.</t>
+          <t>미국 광통신 시장 강세 및 AI 관련주 부각, 외인 매수세 유입 및 16000원 돌파 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '하락', '그래핀']</t>
+          <t>['광통신', 'AI', '외인매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12260</v>
+        <v>28950</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-5.91%</t>
+          <t>-4.46%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.22</v>
+        <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="H14" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13030</v>
+        <v>30300</v>
       </c>
       <c r="K14" t="n">
-        <v>13160</v>
+        <v>30800</v>
       </c>
       <c r="L14" t="n">
-        <v>13240</v>
+        <v>31500</v>
       </c>
       <c r="M14" t="n">
-        <v>12150</v>
+        <v>28150</v>
       </c>
       <c r="N14" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="O14" t="n">
-        <v>37674448945</v>
+        <v>59243029750</v>
       </c>
       <c r="P14" t="n">
-        <v>20850</v>
+        <v>39350</v>
       </c>
       <c r="Q14" t="n">
-        <v>4020</v>
+        <v>8200</v>
       </c>
       <c r="R14" t="n">
-        <v>-6000</v>
+        <v>25000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>창사 이래 최대 호재 및 3500억 달러 규모 대미 투자 관련 언급이 있으나, 원전 하락세와 더불어 5% 이상 하락하며 투자자들의 혼란과 부정적인 심리가 나타남.</t>
+          <t>하락 추세 지속, 3만원 지지선 이탈 및 폭포수 같은 급락 우려, 매수세 실종.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대미 투자', '원전', '호재']</t>
+          <t>['하락', '지지선', '매수세']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6430</v>
+        <v>14910</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-6.27%</t>
+          <t>-4.67%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="H15" t="n">
-        <v>15.68</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,58 +1791,334 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6860</v>
+        <v>15640</v>
       </c>
       <c r="K15" t="n">
-        <v>6800</v>
+        <v>15600</v>
       </c>
       <c r="L15" t="n">
-        <v>6820</v>
+        <v>15600</v>
       </c>
       <c r="M15" t="n">
-        <v>6400</v>
+        <v>14770</v>
       </c>
       <c r="N15" t="n">
-        <v>16.71</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5839987155</v>
+        <v>12870840320</v>
       </c>
       <c r="P15" t="n">
-        <v>13000</v>
+        <v>19380</v>
       </c>
       <c r="Q15" t="n">
-        <v>6030</v>
+        <v>3200</v>
       </c>
       <c r="R15" t="n">
-        <v>-20000</v>
+        <v>-9000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>외국인 매도세와 주가 장난질에 대한 부정적 인식, 잡주 취급. 로봇/반도체 관련 언급.</t>
+          <t>금호건설, 일부 호재 언급 있으나 전반적으로 부정적 전망과 투매 의견 지배적.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['호재', '부정적전망', '투매']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>002990</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>우리기술</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>13650</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-4.68%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E16" t="n">
+        <v>62</v>
+      </c>
+      <c r="F16" t="n">
+        <v>46</v>
+      </c>
+      <c r="G16" t="n">
+        <v>222</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>14320</v>
+      </c>
+      <c r="K16" t="n">
+        <v>13800</v>
+      </c>
+      <c r="L16" t="n">
+        <v>13900</v>
+      </c>
+      <c r="M16" t="n">
+        <v>13260</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="O16" t="n">
+        <v>53633826020</v>
+      </c>
+      <c r="P16" t="n">
+        <v>30200</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3540</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-82000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>그래핀 개발 호재에도 불구하고 하락세 전망, 공매도 금지 영향 언급.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
         <v>0.1</v>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['그래핀', '공매도', '하락']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>032820</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>삼미금속</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>12260</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-5.91%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="E17" t="n">
+        <v>52</v>
+      </c>
+      <c r="F17" t="n">
+        <v>37</v>
+      </c>
+      <c r="G17" t="n">
+        <v>43</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>13030</v>
+      </c>
+      <c r="K17" t="n">
+        <v>13160</v>
+      </c>
+      <c r="L17" t="n">
+        <v>13240</v>
+      </c>
+      <c r="M17" t="n">
+        <v>12150</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O17" t="n">
+        <v>40183932945</v>
+      </c>
+      <c r="P17" t="n">
+        <v>20850</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4020</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>대규모 대미 투자 호재에도 불구하고 하락세, 개인 투자자들의 차익 실현 및 주포 움직임 주시.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['대미투자', '하락', '주포']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>012210</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>한화머시너리앤서비스홀딩스</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6450</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-5.98%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="E18" t="n">
+        <v>57</v>
+      </c>
+      <c r="F18" t="n">
+        <v>39</v>
+      </c>
+      <c r="G18" t="n">
+        <v>140</v>
+      </c>
+      <c r="H18" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>6860</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6800</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6820</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6400</v>
+      </c>
+      <c r="N18" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="O18" t="n">
+        <v>6228637870</v>
+      </c>
+      <c r="P18" t="n">
+        <v>13000</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6030</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>외국인 매도세와 주가 장난질에 대한 부정적 인식, 잡주 취급. 로봇/반도체 관련 언급.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>['외국인', '주가', '로봇']</t>
         </is>
       </c>
-      <c r="X15" t="n">
+      <c r="X18" t="n">
         <v>11</v>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>0220W0</t>
         </is>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4990</v>
+        <v>5520</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+149.50%</t>
+          <t>+176.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>377384884908</v>
+        <v>428143236204</v>
       </c>
       <c r="P2" t="n">
         <v>5660</v>
@@ -619,23 +619,23 @@
         <v>4000</v>
       </c>
       <c r="R2" t="n">
-        <v>-134000</v>
+        <v>-152000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-2278000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호, 합병 대상 업종 신재생에너지 관련 기대감 있으나 스팩주 특성상 하락 가능성 언급.</t>
+          <t>엔에이치스팩34호, 합병 대상 업종(신재생에너지) 및 스팩주 특성 언급. 단기 변동성 속 종가 예측.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '신재생에너지', '하락']</t>
+          <t>['스팩주', '합병', '신재생에너지']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>샘표식품</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14980</v>
+        <v>28550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+23.90%</t>
+          <t>+23.06%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>145</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>229</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03</v>
+        <v>7.54</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12090</v>
+        <v>23200</v>
       </c>
       <c r="K3" t="n">
-        <v>12730</v>
+        <v>26900</v>
       </c>
       <c r="L3" t="n">
-        <v>15120</v>
+        <v>30150</v>
       </c>
       <c r="M3" t="n">
-        <v>12720</v>
+        <v>24500</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="O3" t="n">
-        <v>150781273085</v>
+        <v>26586377725</v>
       </c>
       <c r="P3" t="n">
-        <v>36200</v>
+        <v>34750</v>
       </c>
       <c r="Q3" t="n">
-        <v>8920</v>
+        <v>20450</v>
       </c>
       <c r="R3" t="n">
-        <v>245000</v>
+        <v>-37000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>흥구석유, 중동 긴장 고조로 인한 유가 급등세 속 상승 기대감. 단기 차익 실현 매물 가능성도 언급.</t>
+          <t>샘표식품, 샘표의 자사주 소각 이슈와 연계된 기대감 부각. 30% 자사주 소각 뉴스 및 3연상 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유가급등', '중동', '차익실현']</t>
+          <t>['자사주소각', '이벤트', '식품']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>248170</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>테라뷰</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3580</v>
+        <v>14710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+15.30%</t>
+          <t>+21.67%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>163</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3105</v>
+        <v>12090</v>
       </c>
       <c r="K4" t="n">
-        <v>3170</v>
+        <v>12730</v>
       </c>
       <c r="L4" t="n">
-        <v>3775</v>
+        <v>15120</v>
       </c>
       <c r="M4" t="n">
-        <v>3165</v>
+        <v>12720</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>14153552503</v>
+        <v>160313043585</v>
       </c>
       <c r="P4" t="n">
-        <v>20800</v>
+        <v>36200</v>
       </c>
       <c r="Q4" t="n">
-        <v>1700</v>
+        <v>8920</v>
       </c>
       <c r="R4" t="n">
-        <v>24000</v>
+        <v>39000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20% 이상 상승하며 외인 수급 긍정적 신호, 단기 과열 및 주가 조작 의혹 언급.</t>
+          <t>흥구석유, 유가 급등 요인(이란 사태, 트럼프 발언) 분석 및 급등 가능성 언급. 유가와 반도체 연관성 부인.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['수급', '단기과열', '주가조작']</t>
+          <t>['유가', '이란', '트럼프']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>950250</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7930</v>
+        <v>3615</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+6.87%</t>
+          <t>+16.43%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>145</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>743</v>
+        <v>18</v>
       </c>
       <c r="H5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7420</v>
+        <v>3105</v>
       </c>
       <c r="K5" t="n">
-        <v>8000</v>
+        <v>3170</v>
       </c>
       <c r="L5" t="n">
-        <v>9100</v>
+        <v>3775</v>
       </c>
       <c r="M5" t="n">
-        <v>7930</v>
+        <v>3165</v>
       </c>
       <c r="N5" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>45351366880</v>
+        <v>15181370606</v>
       </c>
       <c r="P5" t="n">
-        <v>21500</v>
+        <v>20800</v>
       </c>
       <c r="Q5" t="n">
-        <v>2300</v>
+        <v>1700</v>
       </c>
       <c r="R5" t="n">
-        <v>108000</v>
+        <v>16000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>페니트리움바이오, 세계 최초 항암제 내성 극복 기술 개발 성공 및 글로벌 제약사 참여 기대감. 5연상 전망.</t>
+          <t>큰 폭의 상승 후 단기 과열 진입, 전고점 돌파 기대감과 함께 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['항암제내성', '오가노이드', '5연상']</t>
+          <t>['단기 과열', '전고점 돌파', '주가 조작']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>950250</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4005</v>
+        <v>8170</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+5.12%</t>
+          <t>+10.11%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.62</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G6" t="n">
-        <v>106</v>
+        <v>767</v>
       </c>
       <c r="H6" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3810</v>
+        <v>7420</v>
       </c>
       <c r="K6" t="n">
-        <v>3870</v>
+        <v>8000</v>
       </c>
       <c r="L6" t="n">
-        <v>4250</v>
+        <v>9100</v>
       </c>
       <c r="M6" t="n">
-        <v>3660</v>
+        <v>7930</v>
       </c>
       <c r="N6" t="n">
-        <v>3.19</v>
+        <v>0.77</v>
       </c>
       <c r="O6" t="n">
-        <v>87185636585</v>
+        <v>48211805075</v>
       </c>
       <c r="P6" t="n">
-        <v>8100</v>
+        <v>21500</v>
       </c>
       <c r="Q6" t="n">
-        <v>592</v>
+        <v>2300</v>
       </c>
       <c r="R6" t="n">
-        <v>365000</v>
+        <v>100000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>빛과전자, AI 데이터센터·6G 광통신 기술 개발 발표로 인한 기대감. 투경 회피 및 상승 전망.</t>
+          <t>페니트리움바이오, 세계 최초 항암제 내성 극복 기술 개발 성공 및 글로벌 제약사 참여 기대감. 5연상 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI', '6G', '광통신']</t>
+          <t>['항암제내성', '오가노이드', '5연상']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>158100</v>
+        <v>3965</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+3.00%</t>
+          <t>+4.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>-1.62</v>
       </c>
       <c r="E7" t="n">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>575</v>
+        <v>120</v>
       </c>
       <c r="H7" t="n">
-        <v>15.65</v>
+        <v>1.57</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>153500</v>
+        <v>3810</v>
       </c>
       <c r="K7" t="n">
-        <v>155500</v>
+        <v>3870</v>
       </c>
       <c r="L7" t="n">
-        <v>164700</v>
+        <v>4250</v>
       </c>
       <c r="M7" t="n">
-        <v>154500</v>
+        <v>3660</v>
       </c>
       <c r="N7" t="n">
-        <v>15.25</v>
+        <v>3.19</v>
       </c>
       <c r="O7" t="n">
-        <v>196907001300</v>
+        <v>96089823733</v>
       </c>
       <c r="P7" t="n">
-        <v>164700</v>
+        <v>8100</v>
       </c>
       <c r="Q7" t="n">
-        <v>87700</v>
+        <v>592</v>
       </c>
       <c r="R7" t="n">
-        <v>56000</v>
+        <v>20000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>SK이노베이션, 유가 폭등 및 정제마진 고공행진으로 인한 실적 개선 기대감. 단기 상승 후 조정 가능성도 제기.</t>
+          <t>빛과전자, AI 데이터센터·6G 광통신 관련 뉴스 및 투기과열예방구간 회피 소식. 6G 기대감으로 인한 상승 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유가폭등', '정제마진', '실적개선']</t>
+          <t>['AI', '6G', '광통신']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2120</v>
+        <v>156200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+1.68%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>245</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="G8" t="n">
-        <v>104</v>
+        <v>611</v>
       </c>
       <c r="H8" t="n">
-        <v>0.85</v>
+        <v>15.65</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2085</v>
+        <v>153500</v>
       </c>
       <c r="K8" t="n">
-        <v>2255</v>
+        <v>155500</v>
       </c>
       <c r="L8" t="n">
-        <v>2395</v>
+        <v>164700</v>
       </c>
       <c r="M8" t="n">
-        <v>2075</v>
+        <v>154500</v>
       </c>
       <c r="N8" t="n">
-        <v>0.51</v>
+        <v>15.25</v>
       </c>
       <c r="O8" t="n">
-        <v>13535012145</v>
+        <v>213739865700</v>
       </c>
       <c r="P8" t="n">
-        <v>2930</v>
+        <v>164700</v>
       </c>
       <c r="Q8" t="n">
-        <v>910</v>
+        <v>87700</v>
       </c>
       <c r="R8" t="n">
-        <v>63000</v>
+        <v>112000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>강동씨앤엘, 단기 급등 후 차익 실현 매물 출회 및 저항선 언급. 일부 부정적 전망.</t>
+          <t>SK이노베이션, 유가 폭등 및 정제마진 고공행진으로 인한 실적 개선 기대감. 단기 상승 후 조정 가능성도 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['차익실현', '저항선', '부정적']</t>
+          <t>['유가폭등', '정제마진', '실적개선']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1836000</v>
+        <v>2115</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.08%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.01</v>
+        <v>0.34</v>
       </c>
       <c r="E9" t="n">
-        <v>785</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
-        <v>458</v>
+        <v>39</v>
       </c>
       <c r="G9" t="n">
-        <v>1384</v>
+        <v>115</v>
       </c>
       <c r="H9" t="n">
-        <v>50.67</v>
+        <v>0.85</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1856000</v>
+        <v>2085</v>
       </c>
       <c r="K9" t="n">
-        <v>1879000</v>
+        <v>2255</v>
       </c>
       <c r="L9" t="n">
-        <v>1890000</v>
+        <v>2395</v>
       </c>
       <c r="M9" t="n">
-        <v>1829000</v>
+        <v>2075</v>
       </c>
       <c r="N9" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="O9" t="n">
-        <v>1496230542000</v>
+        <v>13968491537</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q9" t="n">
-        <v>293000</v>
+        <v>910</v>
       </c>
       <c r="R9" t="n">
-        <v>-48000</v>
+        <v>-4000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스, ADR 상승에 따른 본장 급등 기대감 있으나 대규모 매도 물량 출회 가능성 언급.</t>
+          <t>강동씨앤엘, 시간외 단일가 거래량 및 외국인/기관 매수세 언급. 2000원 지지선 이탈 가능성 및 저항 구간 제시.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['ADR', '급등', '매도물량']</t>
+          <t>['거래량', '저항', '매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>265750</v>
+        <v>1829000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.39%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="F10" t="n">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="G10" t="n">
-        <v>1560</v>
+        <v>1264</v>
       </c>
       <c r="H10" t="n">
-        <v>46.81</v>
+        <v>50.67</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>269500</v>
+        <v>1856000</v>
       </c>
       <c r="K10" t="n">
-        <v>269000</v>
+        <v>1879000</v>
       </c>
       <c r="L10" t="n">
-        <v>270500</v>
+        <v>1890000</v>
       </c>
       <c r="M10" t="n">
-        <v>265000</v>
+        <v>1825000</v>
       </c>
       <c r="N10" t="n">
-        <v>46.85</v>
+        <v>50.66</v>
       </c>
       <c r="O10" t="n">
-        <v>737857933500</v>
+        <v>1676519058000</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>71600</v>
+        <v>293000</v>
       </c>
       <c r="R10" t="n">
-        <v>68000</v>
+        <v>-64000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-67000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>삼성전자, 자사주 매입 리스크와 주주환원 요구 제기. 일부 투자자 매도 의견.</t>
+          <t>SK하이닉스, 리밸런싱 물량 및 매도 폭탄 우려로 인한 하락세 전망. ADR 지표와 상반된 움직임 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['자사주매입', '주주환원', '매도']</t>
+          <t>['리밸런싱', 'ADR', '매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18960</v>
+        <v>265250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="E11" t="n">
-        <v>55</v>
+        <v>789</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>470</v>
       </c>
       <c r="G11" t="n">
-        <v>192</v>
+        <v>1469</v>
       </c>
       <c r="H11" t="n">
-        <v>10.64</v>
+        <v>46.81</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>19450</v>
+        <v>269500</v>
       </c>
       <c r="K11" t="n">
-        <v>18900</v>
+        <v>269000</v>
       </c>
       <c r="L11" t="n">
-        <v>19220</v>
+        <v>270500</v>
       </c>
       <c r="M11" t="n">
-        <v>18670</v>
+        <v>264500</v>
       </c>
       <c r="N11" t="n">
-        <v>10.85</v>
+        <v>46.85</v>
       </c>
       <c r="O11" t="n">
-        <v>36005098945</v>
+        <v>874314122000</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>71600</v>
       </c>
       <c r="R11" t="n">
-        <v>87000</v>
+        <v>236000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-272000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대우건설, 미국 투자 및 원전 관련 긍정적 기대감 속 급등 가능성 언급. 일부는 하락 전망.</t>
+          <t>삼성전자, 하이닉스 대비 상대적 약세 및 자사주 매입 리스크 언급. 주가 부진에 대한 부정적 전망 제시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['미국투자', '원전', '급등']</t>
+          <t>['자사주매입', '반도체', '주주환원']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>89000</v>
+        <v>19000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.94%</t>
+          <t>-2.31%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.04</v>
+        <v>-0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="F12" t="n">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>601</v>
+        <v>197</v>
       </c>
       <c r="H12" t="n">
-        <v>23.65</v>
+        <v>10.64</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>91700</v>
+        <v>19450</v>
       </c>
       <c r="K12" t="n">
-        <v>90000</v>
+        <v>18900</v>
       </c>
       <c r="L12" t="n">
-        <v>90700</v>
+        <v>19220</v>
       </c>
       <c r="M12" t="n">
-        <v>88400</v>
+        <v>18670</v>
       </c>
       <c r="N12" t="n">
-        <v>23.61</v>
+        <v>10.85</v>
       </c>
       <c r="O12" t="n">
-        <v>62734295950</v>
+        <v>38244989205</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-1000</v>
+        <v>58000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-29000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>원전 사업 수주 기대감 및 웨스팅하우스 인수전 참여 가능성, 10만원 터치 및 전약후강 전망.</t>
+          <t>대우건설, 미국 투자 및 원전 관련 긍정적 기대감 속 급등 가능성 언급. 일부는 하락 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '수주', '인수전']</t>
+          <t>['미국투자', '원전', '급등']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14440</v>
+        <v>14470</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.48%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1.34</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="H13" t="n">
         <v>2.89</v>
@@ -1622,7 +1622,7 @@
         <v>1.55</v>
       </c>
       <c r="O13" t="n">
-        <v>55550569390</v>
+        <v>58046710935</v>
       </c>
       <c r="P13" t="n">
         <v>31500</v>
@@ -1631,23 +1631,23 @@
         <v>1263</v>
       </c>
       <c r="R13" t="n">
-        <v>-191000</v>
+        <v>-282000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 광통신 시장 강세 및 AI 관련주 부각, 외인 매수세 유입 및 16000원 돌파 기대.</t>
+          <t>미국 광통신 테마 강세 속 상승 추세, 외인 순위 상승 및 거래량 증가로 16000원 돌파 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '외인매수']</t>
+          <t>['광통신 테마', '외인 순위', '거래량 증가']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,83 +1667,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28950</v>
+        <v>88500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.46%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="G14" t="n">
-        <v>122</v>
+        <v>618</v>
       </c>
       <c r="H14" t="n">
-        <v>0.33</v>
+        <v>23.65</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>30300</v>
+        <v>91700</v>
       </c>
       <c r="K14" t="n">
-        <v>30800</v>
+        <v>90000</v>
       </c>
       <c r="L14" t="n">
-        <v>31500</v>
+        <v>90700</v>
       </c>
       <c r="M14" t="n">
-        <v>28150</v>
+        <v>88400</v>
       </c>
       <c r="N14" t="n">
-        <v>0.31</v>
+        <v>23.61</v>
       </c>
       <c r="O14" t="n">
-        <v>59243029750</v>
+        <v>69570240900</v>
       </c>
       <c r="P14" t="n">
-        <v>39350</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>8200</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>25000</v>
+        <v>-73000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-24000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>하락 추세 지속, 3만원 지지선 이탈 및 폭포수 같은 급락 우려, 매수세 실종.</t>
+          <t>두산에너빌리티, 미국 원전 건설 '팀코리아' 참여 및 웨스턴하우스 지분 인수 건 등 역사적 호재 발생. 공매도 세력의 움직임과 관계없이 상승 추세 지속 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['하락', '지지선', '매수세']</t>
+          <t>['원전 건설', '웨스팅하우스', '호재']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14910</v>
+        <v>13800</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.67%</t>
+          <t>-3.63%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="E15" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>156</v>
+        <v>234</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>15640</v>
+        <v>14320</v>
       </c>
       <c r="K15" t="n">
-        <v>15600</v>
+        <v>13800</v>
       </c>
       <c r="L15" t="n">
-        <v>15600</v>
+        <v>13900</v>
       </c>
       <c r="M15" t="n">
-        <v>14770</v>
+        <v>13260</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="O15" t="n">
-        <v>12870840320</v>
+        <v>58719476755</v>
       </c>
       <c r="P15" t="n">
-        <v>19380</v>
+        <v>30200</v>
       </c>
       <c r="Q15" t="n">
-        <v>3200</v>
+        <v>3540</v>
       </c>
       <c r="R15" t="n">
-        <v>-9000</v>
+        <v>-70000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>금호건설, 일부 호재 언급 있으나 전반적으로 부정적 전망과 투매 의견 지배적.</t>
+          <t>공매도 금지에도 불구하고 하락 예상, 주포의 움직임에 따른 단기 매매 관점.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['호재', '부정적전망', '투매']</t>
+          <t>['공매도 금지', '주포', '단기 매매']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,18 +1844,18 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13650</v>
+        <v>12420</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1863,19 +1863,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.45</v>
+        <v>-0.22</v>
       </c>
       <c r="E16" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G16" t="n">
-        <v>222</v>
+        <v>47</v>
       </c>
       <c r="H16" t="n">
-        <v>6.09</v>
+        <v>0.14</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14320</v>
+        <v>13030</v>
       </c>
       <c r="K16" t="n">
-        <v>13800</v>
+        <v>13160</v>
       </c>
       <c r="L16" t="n">
-        <v>13900</v>
+        <v>13240</v>
       </c>
       <c r="M16" t="n">
-        <v>13260</v>
+        <v>12150</v>
       </c>
       <c r="N16" t="n">
-        <v>5.64</v>
+        <v>0.36</v>
       </c>
       <c r="O16" t="n">
-        <v>53633826020</v>
+        <v>43722966995</v>
       </c>
       <c r="P16" t="n">
-        <v>30200</v>
+        <v>20850</v>
       </c>
       <c r="Q16" t="n">
-        <v>3540</v>
+        <v>4020</v>
       </c>
       <c r="R16" t="n">
-        <v>-82000</v>
+        <v>231000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>그래핀 개발 호재에도 불구하고 하락세 전망, 공매도 금지 영향 언급.</t>
+          <t>창사 이래 최대 호재와 대규모 대미 투자 발표, 단기 하락에도 불구하고 추가 매수 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['그래핀', '공매도', '하락']</t>
+          <t>['최대 호재', '대미 투자', '추가 매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12260</v>
+        <v>28750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.91%</t>
+          <t>-5.12%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.22</v>
+        <v>0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="G17" t="n">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="H17" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13030</v>
+        <v>30300</v>
       </c>
       <c r="K17" t="n">
-        <v>13160</v>
+        <v>30800</v>
       </c>
       <c r="L17" t="n">
-        <v>13240</v>
+        <v>31500</v>
       </c>
       <c r="M17" t="n">
-        <v>12150</v>
+        <v>28150</v>
       </c>
       <c r="N17" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="O17" t="n">
-        <v>40183932945</v>
+        <v>62602115200</v>
       </c>
       <c r="P17" t="n">
-        <v>20850</v>
+        <v>39350</v>
       </c>
       <c r="Q17" t="n">
-        <v>4020</v>
+        <v>8200</v>
       </c>
       <c r="R17" t="n">
-        <v>-6000</v>
+        <v>-1000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대규모 대미 투자 호재에도 불구하고 하락세, 개인 투자자들의 차익 실현 및 주포 움직임 주시.</t>
+          <t>급격한 하락 추세 속에서 반등 시도했으나 매수세 실종, 프로그램 매매에 의존한 단기 흐름에 대한 비관론.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대미투자', '하락', '주포']</t>
+          <t>['급격한 하락', '매수세 실종', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6450</v>
+        <v>14810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.98%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="H18" t="n">
-        <v>15.68</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,60 +2067,336 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6860</v>
+        <v>15640</v>
       </c>
       <c r="K18" t="n">
-        <v>6800</v>
+        <v>15600</v>
       </c>
       <c r="L18" t="n">
-        <v>6820</v>
+        <v>15600</v>
       </c>
       <c r="M18" t="n">
-        <v>6400</v>
+        <v>14770</v>
       </c>
       <c r="N18" t="n">
-        <v>16.71</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>6228637870</v>
+        <v>13906651730</v>
       </c>
       <c r="P18" t="n">
-        <v>13000</v>
+        <v>19380</v>
       </c>
       <c r="Q18" t="n">
-        <v>6030</v>
+        <v>3200</v>
       </c>
       <c r="R18" t="n">
-        <v>-20000</v>
+        <v>-14000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>외국인 매도세와 주가 장난질에 대한 부정적 인식, 잡주 취급. 로봇/반도체 관련 언급.</t>
+          <t>금호건설, 호남 반도체 설계 용역 발주 소식과 함께 건설 흑자 및 주가 회복 기대감 언급. 계단식 하락 후 반등 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['반도체', '건설', '설계용역']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>002990</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>한화머시너리앤서비스홀딩스</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6460</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-5.83%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="E19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F19" t="n">
+        <v>40</v>
+      </c>
+      <c r="G19" t="n">
+        <v>153</v>
+      </c>
+      <c r="H19" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>6860</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6800</v>
+      </c>
+      <c r="L19" t="n">
+        <v>6820</v>
+      </c>
+      <c r="M19" t="n">
+        <v>6400</v>
+      </c>
+      <c r="N19" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="O19" t="n">
+        <v>6546717605</v>
+      </c>
+      <c r="P19" t="n">
+        <v>13000</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6030</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-131000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>한화머시너리앤서비스홀딩스, 외국인 매도세와 함께 주가 부진 지속. 분사 및 로봇/반도체 사업 관련 투자 언급.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
         <v>0.1</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>['외국인', '주가', '로봇']</t>
-        </is>
-      </c>
-      <c r="X18" t="n">
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['분사', '로봇', '반도체']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
         <v>11</v>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>0220W0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>써니전자</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-7.08%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E20" t="n">
+        <v>48</v>
+      </c>
+      <c r="F20" t="n">
+        <v>33</v>
+      </c>
+      <c r="G20" t="n">
+        <v>94</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>2260</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2250</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2290</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2095</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3586981194</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2705</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1418</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-47000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>써니전자, 새로운 대주주 부각 및 M&amp;A 기대감으로 인한 단기 급등 가능성 언급. 1만원 목표가 제시.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['M&amp;A', '대주주', '지분경쟁']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>004770</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>원풍물산</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>137</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-44.76%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E21" t="n">
+        <v>43</v>
+      </c>
+      <c r="F21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G21" t="n">
+        <v>37</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>248</v>
+      </c>
+      <c r="K21" t="n">
+        <v>172</v>
+      </c>
+      <c r="L21" t="n">
+        <v>172</v>
+      </c>
+      <c r="M21" t="n">
+        <v>137</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="O21" t="n">
+        <v>409582898</v>
+      </c>
+      <c r="P21" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>137</v>
+      </c>
+      <c r="R21" t="n">
+        <v>29000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>정매 종목으로 분류, 거래량 부진 및 급락 가능성 언급, 상폐 우려 및 외국인 매매 패턴에 대한 부정적 시각.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['정매 종목', '거래량 부진', '상폐 우려']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>008290</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated.xlsx
+++ b/data/trending_integrated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5520</v>
+        <v>5250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+176.00%</t>
+          <t>+162.50%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G2" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -601,7 +601,7 @@
         <v>4000</v>
       </c>
       <c r="L2" t="n">
-        <v>5660</v>
+        <v>5700</v>
       </c>
       <c r="M2" t="n">
         <v>4000</v>
@@ -610,10 +610,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>428143236204</v>
+        <v>484080562239</v>
       </c>
       <c r="P2" t="n">
-        <v>5660</v>
+        <v>5700</v>
       </c>
       <c r="Q2" t="n">
         <v>4000</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호, 합병 대상 업종(신재생에너지) 및 스팩주 특성 언급. 단기 변동성 속 종가 예측.</t>
+          <t>스팩주 특성상 변동성 언급. 합병 대상 업종 및 개미 꼬심 경계, 단타 및 도박성 매매 언급. 종가 예상치 제시.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '합병', '신재생에너지']</t>
+          <t>['스팩주', '합병', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,70 +655,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>샘표식품</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28550</v>
+        <v>15240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+23.06%</t>
+          <t>+26.05%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>189</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>137</v>
       </c>
       <c r="G3" t="n">
-        <v>24</v>
+        <v>254</v>
       </c>
       <c r="H3" t="n">
-        <v>7.54</v>
+        <v>0.03</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>23200</v>
+        <v>12090</v>
       </c>
       <c r="K3" t="n">
-        <v>26900</v>
+        <v>12730</v>
       </c>
       <c r="L3" t="n">
-        <v>30150</v>
+        <v>15250</v>
       </c>
       <c r="M3" t="n">
-        <v>24500</v>
+        <v>12720</v>
       </c>
       <c r="N3" t="n">
-        <v>7.58</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>26586377725</v>
+        <v>176288639405</v>
       </c>
       <c r="P3" t="n">
-        <v>34750</v>
+        <v>36200</v>
       </c>
       <c r="Q3" t="n">
-        <v>20450</v>
+        <v>8920</v>
       </c>
       <c r="R3" t="n">
-        <v>-37000</v>
+        <v>39000</v>
       </c>
       <c r="S3" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>샘표식품, 샘표의 자사주 소각 이슈와 연계된 기대감 부각. 30% 자사주 소각 뉴스 및 3연상 가능성 언급.</t>
+          <t>트럼프의 유가 상승 용인 및 호르무즈 해협 긴장 고조로 인한 유가 급등 전망. 단기 반등 초입 구간.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주소각', '이벤트', '식품']</t>
+          <t>['유가', '브렌트유', 'WTI']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,77 +740,77 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>248170</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>샘표식품</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14710</v>
+        <v>28800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.67%</t>
+          <t>+24.14%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>231</v>
+        <v>35</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03</v>
+        <v>7.54</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>12090</v>
+        <v>23200</v>
       </c>
       <c r="K4" t="n">
-        <v>12730</v>
+        <v>26900</v>
       </c>
       <c r="L4" t="n">
-        <v>15120</v>
+        <v>30150</v>
       </c>
       <c r="M4" t="n">
-        <v>12720</v>
+        <v>24500</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="O4" t="n">
-        <v>160313043585</v>
+        <v>28473028000</v>
       </c>
       <c r="P4" t="n">
-        <v>36200</v>
+        <v>34750</v>
       </c>
       <c r="Q4" t="n">
-        <v>8920</v>
+        <v>20450</v>
       </c>
       <c r="R4" t="n">
-        <v>39000</v>
+        <v>-37000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>흥구석유, 유가 급등 요인(이란 사태, 트럼프 발언) 분석 및 급등 가능성 언급. 유가와 반도체 연관성 부인.</t>
+          <t>샘표식품 30% 자사주 소각 관련 뉴스 기반 상승. 샘표와의 관계 및 유동주식 수, 신한외인프매 관련 논의.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유가', '이란', '트럼프']</t>
+          <t>['자사주 소각', '샘표', '유동주식']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>248170</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3615</v>
+        <v>3645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.43%</t>
+          <t>+17.39%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>15181370606</v>
+        <v>16355378315</v>
       </c>
       <c r="P5" t="n">
         <v>20800</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>큰 폭의 상승 후 단기 과열 진입, 전고점 돌파 기대감과 함께 주가 조작 의혹 제기.</t>
+          <t>단기 과열 지정 속 윗꼬리 보합 마감. 전고점 돌파 시 6천원 목표.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['단기 과열', '전고점 돌파', '주가 조작']</t>
+          <t>['단기과열', '전고점', '테라뷰']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8170</v>
+        <v>1990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+10.11%</t>
+          <t>+13.07%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>767</v>
+        <v>29</v>
       </c>
       <c r="H6" t="n">
-        <v>1.17</v>
+        <v>2.12</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7420</v>
+        <v>1760</v>
       </c>
       <c r="K6" t="n">
-        <v>8000</v>
+        <v>1782</v>
       </c>
       <c r="L6" t="n">
-        <v>9100</v>
+        <v>2020</v>
       </c>
       <c r="M6" t="n">
-        <v>7930</v>
+        <v>1772</v>
       </c>
       <c r="N6" t="n">
-        <v>0.77</v>
+        <v>2.07</v>
       </c>
       <c r="O6" t="n">
-        <v>48211805075</v>
+        <v>63200810901</v>
       </c>
       <c r="P6" t="n">
-        <v>21500</v>
+        <v>4795</v>
       </c>
       <c r="Q6" t="n">
-        <v>2300</v>
+        <v>1524</v>
       </c>
       <c r="R6" t="n">
-        <v>100000</v>
+        <v>283000</v>
       </c>
       <c r="S6" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>페니트리움바이오, 세계 최초 항암제 내성 극복 기술 개발 성공 및 글로벌 제약사 참여 기대감. 5연상 전망.</t>
+          <t>외인 매수세 유입에도 불구하고 하락하며, 거래량 증가와 함께 일부 상승하는 모습. 신규 상장사 언급 및 석유 관련 테마 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['항암제내성', '오가노이드', '5연상']</t>
+          <t>['해운', '거래량', '외인']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3965</v>
+        <v>8230</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+4.07%</t>
+          <t>+10.92%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.62</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>171</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="G7" t="n">
-        <v>120</v>
+        <v>831</v>
       </c>
       <c r="H7" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3810</v>
+        <v>7420</v>
       </c>
       <c r="K7" t="n">
-        <v>3870</v>
+        <v>8000</v>
       </c>
       <c r="L7" t="n">
-        <v>4250</v>
+        <v>9100</v>
       </c>
       <c r="M7" t="n">
-        <v>3660</v>
+        <v>7930</v>
       </c>
       <c r="N7" t="n">
-        <v>3.19</v>
+        <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>96089823733</v>
+        <v>49939447000</v>
       </c>
       <c r="P7" t="n">
-        <v>8100</v>
+        <v>21500</v>
       </c>
       <c r="Q7" t="n">
-        <v>592</v>
+        <v>2300</v>
       </c>
       <c r="R7" t="n">
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>빛과전자, AI 데이터센터·6G 광통신 관련 뉴스 및 투기과열예방구간 회피 소식. 6G 기대감으로 인한 상승 전망.</t>
+          <t>세계 폐암학회 참여 및 항암제 내성 극복, FDA 2상 승인 기대감. 4연상 이상 목표.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '6G', '광통신']</t>
+          <t>['폐암학회', '항암제', 'FDA']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>156200</v>
+        <v>3950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+3.67%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>-1.62</v>
       </c>
       <c r="E8" t="n">
-        <v>245</v>
+        <v>53</v>
       </c>
       <c r="F8" t="n">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>611</v>
+        <v>122</v>
       </c>
       <c r="H8" t="n">
-        <v>15.65</v>
+        <v>1.57</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>153500</v>
+        <v>3810</v>
       </c>
       <c r="K8" t="n">
-        <v>155500</v>
+        <v>3870</v>
       </c>
       <c r="L8" t="n">
-        <v>164700</v>
+        <v>4250</v>
       </c>
       <c r="M8" t="n">
-        <v>154500</v>
+        <v>3660</v>
       </c>
       <c r="N8" t="n">
-        <v>15.25</v>
+        <v>3.19</v>
       </c>
       <c r="O8" t="n">
-        <v>213739865700</v>
+        <v>101050388174</v>
       </c>
       <c r="P8" t="n">
-        <v>164700</v>
+        <v>8100</v>
       </c>
       <c r="Q8" t="n">
-        <v>87700</v>
+        <v>592</v>
       </c>
       <c r="R8" t="n">
-        <v>112000</v>
+        <v>20000</v>
       </c>
       <c r="S8" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SK이노베이션, 유가 폭등 및 정제마진 고공행진으로 인한 실적 개선 기대감. 단기 상승 후 조정 가능성도 제기.</t>
+          <t>AI 데이터센터·6G 광통신 사업 기대감 및 투기과열예고 회피. 15% 상승 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['유가폭등', '정제마진', '실적개선']</t>
+          <t>['AI', '6G', '광통신']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2115</v>
+        <v>154000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>270</v>
       </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="G9" t="n">
-        <v>115</v>
+        <v>642</v>
       </c>
       <c r="H9" t="n">
-        <v>0.85</v>
+        <v>15.65</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2085</v>
+        <v>153500</v>
       </c>
       <c r="K9" t="n">
-        <v>2255</v>
+        <v>155500</v>
       </c>
       <c r="L9" t="n">
-        <v>2395</v>
+        <v>164700</v>
       </c>
       <c r="M9" t="n">
-        <v>2075</v>
+        <v>152500</v>
       </c>
       <c r="N9" t="n">
-        <v>0.51</v>
+        <v>15.25</v>
       </c>
       <c r="O9" t="n">
-        <v>13968491537</v>
+        <v>243767702200</v>
       </c>
       <c r="P9" t="n">
-        <v>2930</v>
+        <v>164700</v>
       </c>
       <c r="Q9" t="n">
-        <v>910</v>
+        <v>87700</v>
       </c>
       <c r="R9" t="n">
-        <v>-4000</v>
+        <v>112000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>강동씨앤엘, 시간외 단일가 거래량 및 외국인/기관 매수세 언급. 2000원 지지선 이탈 가능성 및 저항 구간 제시.</t>
+          <t>유가 상승에 따른 SK이노베이션 주가 상승 기대감. 정제마진 호조 및 환율 하락 영향 언급, 전고점 돌파 및 보유자 홀딩 의견.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['거래량', '저항', '매수']</t>
+          <t>['유가', '정제마진', '전고점']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1829000</v>
+        <v>2065</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.01</v>
+        <v>0.34</v>
       </c>
       <c r="E10" t="n">
-        <v>796</v>
+        <v>77</v>
       </c>
       <c r="F10" t="n">
-        <v>463</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>1264</v>
+        <v>118</v>
       </c>
       <c r="H10" t="n">
-        <v>50.67</v>
+        <v>0.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1856000</v>
+        <v>2085</v>
       </c>
       <c r="K10" t="n">
-        <v>1879000</v>
+        <v>2255</v>
       </c>
       <c r="L10" t="n">
-        <v>1890000</v>
+        <v>2395</v>
       </c>
       <c r="M10" t="n">
-        <v>1825000</v>
+        <v>2050</v>
       </c>
       <c r="N10" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="O10" t="n">
-        <v>1676519058000</v>
+        <v>14447934237</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q10" t="n">
-        <v>293000</v>
+        <v>910</v>
       </c>
       <c r="R10" t="n">
-        <v>-64000</v>
+        <v>-4000</v>
       </c>
       <c r="S10" t="n">
-        <v>-67000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SK하이닉스, 리밸런싱 물량 및 매도 폭탄 우려로 인한 하락세 전망. ADR 지표와 상반된 움직임 언급.</t>
+          <t>새만금 소식 관련 불확실성 및 2000원 이탈 가능성. 매물대 저항.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['리밸런싱', 'ADR', '매도']</t>
+          <t>['새만금', '강동씨앤엘', '매물대']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>265250</v>
+        <v>1820000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="F11" t="n">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="G11" t="n">
-        <v>1469</v>
+        <v>1304</v>
       </c>
       <c r="H11" t="n">
-        <v>46.81</v>
+        <v>50.67</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>269500</v>
+        <v>1856000</v>
       </c>
       <c r="K11" t="n">
-        <v>269000</v>
+        <v>1879000</v>
       </c>
       <c r="L11" t="n">
-        <v>270500</v>
+        <v>1890000</v>
       </c>
       <c r="M11" t="n">
-        <v>264500</v>
+        <v>1820000</v>
       </c>
       <c r="N11" t="n">
-        <v>46.85</v>
+        <v>50.66</v>
       </c>
       <c r="O11" t="n">
-        <v>874314122000</v>
+        <v>1837173027000</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>71600</v>
+        <v>293000</v>
       </c>
       <c r="R11" t="n">
-        <v>236000</v>
+        <v>-64000</v>
       </c>
       <c r="S11" t="n">
-        <v>-272000</v>
+        <v>-67000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>삼성전자, 하이닉스 대비 상대적 약세 및 자사주 매입 리스크 언급. 주가 부진에 대한 부정적 전망 제시.</t>
+          <t>SK하이닉스 주가 변동성 속 공매도 및 매도 압력 언급. 자사주 매입 및 소각, ADR 상승세, 옵션 만기 영향 분석.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['자사주매입', '반도체', '주주환원']</t>
+          <t>['SK하이닉스', '공매도', '자사주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19000</v>
+        <v>264000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>56</v>
+        <v>790</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>465</v>
       </c>
       <c r="G12" t="n">
-        <v>197</v>
+        <v>1396</v>
       </c>
       <c r="H12" t="n">
-        <v>10.64</v>
+        <v>46.81</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>19450</v>
+        <v>269500</v>
       </c>
       <c r="K12" t="n">
-        <v>18900</v>
+        <v>269000</v>
       </c>
       <c r="L12" t="n">
-        <v>19220</v>
+        <v>270500</v>
       </c>
       <c r="M12" t="n">
-        <v>18670</v>
+        <v>263500</v>
       </c>
       <c r="N12" t="n">
-        <v>10.85</v>
+        <v>46.85</v>
       </c>
       <c r="O12" t="n">
-        <v>38244989205</v>
+        <v>1009563716750</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>71600</v>
       </c>
       <c r="R12" t="n">
-        <v>58000</v>
+        <v>236000</v>
       </c>
       <c r="S12" t="n">
-        <v>-29000</v>
+        <v>-272000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대우건설, 미국 투자 및 원전 관련 긍정적 기대감 속 급등 가능성 언급. 일부는 하락 전망.</t>
+          <t>반도체 섹터 부진 속 삼성전자 주가 하락. 자사주 매입 및 주주 환원 요구, 하이닉스와의 비교 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미국투자', '원전', '급등']</t>
+          <t>['반도체', '주주환원', '자사주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14470</v>
+        <v>18750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-3.60%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.34</v>
+        <v>-0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F13" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>316</v>
+        <v>196</v>
       </c>
       <c r="H13" t="n">
-        <v>2.89</v>
+        <v>10.64</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14960</v>
+        <v>19450</v>
       </c>
       <c r="K13" t="n">
-        <v>15040</v>
+        <v>18900</v>
       </c>
       <c r="L13" t="n">
-        <v>15040</v>
+        <v>19220</v>
       </c>
       <c r="M13" t="n">
-        <v>14190</v>
+        <v>18670</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>10.85</v>
       </c>
       <c r="O13" t="n">
-        <v>58046710935</v>
+        <v>44192297955</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>1263</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-282000</v>
+        <v>58000</v>
       </c>
       <c r="S13" t="n">
-        <v>-7000</v>
+        <v>-29000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 광통신 테마 강세 속 상승 추세, 외인 순위 상승 및 거래량 증가로 16000원 돌파 기대.</t>
+          <t>대우건설 주가 상승 기대와 함께 조정 언급. 미국 투자 및 원전 관련 테마 언급, 자사주 소각 요구.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신 테마', '외인 순위', '거래량 증가']</t>
+          <t>['건설', '미국 투자', '자사주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>88500</v>
+        <v>14420</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>-3.61%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.04</v>
+        <v>1.34</v>
       </c>
       <c r="E14" t="n">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="F14" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="G14" t="n">
-        <v>618</v>
+        <v>319</v>
       </c>
       <c r="H14" t="n">
-        <v>23.65</v>
+        <v>2.89</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>91700</v>
+        <v>14960</v>
       </c>
       <c r="K14" t="n">
-        <v>90000</v>
+        <v>15040</v>
       </c>
       <c r="L14" t="n">
-        <v>90700</v>
+        <v>15040</v>
       </c>
       <c r="M14" t="n">
-        <v>88400</v>
+        <v>14190</v>
       </c>
       <c r="N14" t="n">
-        <v>23.61</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>69570240900</v>
+        <v>60377302525</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>1263</v>
       </c>
       <c r="R14" t="n">
-        <v>-73000</v>
+        <v>-282000</v>
       </c>
       <c r="S14" t="n">
-        <v>-24000</v>
+        <v>-7000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 미국 원전 건설 '팀코리아' 참여 및 웨스턴하우스 지분 인수 건 등 역사적 호재 발생. 공매도 세력의 움직임과 관계없이 상승 추세 지속 전망.</t>
+          <t>미국 광통신 관련주 강세 및 AI 관련주 부각. 16000원 돌파 및 상한가 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전 건설', '웨스팅하우스', '호재']</t>
+          <t>['광통신', 'AI', '대한광통신']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13800</v>
+        <v>88200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.63%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.45</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="G15" t="n">
-        <v>234</v>
+        <v>623</v>
       </c>
       <c r="H15" t="n">
-        <v>6.09</v>
+        <v>23.65</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14320</v>
+        <v>91700</v>
       </c>
       <c r="K15" t="n">
-        <v>13800</v>
+        <v>90000</v>
       </c>
       <c r="L15" t="n">
-        <v>13900</v>
+        <v>90700</v>
       </c>
       <c r="M15" t="n">
-        <v>13260</v>
+        <v>87900</v>
       </c>
       <c r="N15" t="n">
-        <v>5.64</v>
+        <v>23.61</v>
       </c>
       <c r="O15" t="n">
-        <v>58719476755</v>
+        <v>85523580550</v>
       </c>
       <c r="P15" t="n">
-        <v>30200</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>3540</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-70000</v>
+        <v>-73000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-24000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>공매도 금지에도 불구하고 하락 예상, 주포의 움직임에 따른 단기 매매 관점.</t>
+          <t>미국 신규 원전 8기 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성. 역사상 최대 호재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도 금지', '주포', '단기 매매']</t>
+          <t>['원전', '팀코리아', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12420</v>
+        <v>12440</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.68%</t>
+          <t>-4.53%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.22</v>
       </c>
       <c r="E16" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G16" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H16" t="n">
         <v>0.14</v>
@@ -1898,7 +1898,7 @@
         <v>0.36</v>
       </c>
       <c r="O16" t="n">
-        <v>43722966995</v>
+        <v>46606545280</v>
       </c>
       <c r="P16" t="n">
         <v>20850</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>창사 이래 최대 호재와 대규모 대미 투자 발표, 단기 하락에도 불구하고 추가 매수 및 추가 상승 전망.</t>
+          <t>3500억 달러 규모 대미 투자 호재와 원전 관련 불확실성 혼재. 20% 만족 후 일부 매도.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['최대 호재', '대미 투자', '추가 매수']</t>
+          <t>['대미투자', '호재', '삼미금속']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28750</v>
+        <v>13655</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.12%</t>
+          <t>-4.64%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.02</v>
+        <v>0.45</v>
       </c>
       <c r="E17" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>139</v>
+        <v>242</v>
       </c>
       <c r="H17" t="n">
-        <v>0.33</v>
+        <v>6.09</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>30300</v>
+        <v>14320</v>
       </c>
       <c r="K17" t="n">
-        <v>30800</v>
+        <v>13800</v>
       </c>
       <c r="L17" t="n">
-        <v>31500</v>
+        <v>13900</v>
       </c>
       <c r="M17" t="n">
-        <v>28150</v>
+        <v>13260</v>
       </c>
       <c r="N17" t="n">
-        <v>0.31</v>
+        <v>5.64</v>
       </c>
       <c r="O17" t="n">
-        <v>62602115200</v>
+        <v>61508785755</v>
       </c>
       <c r="P17" t="n">
-        <v>39350</v>
+        <v>30200</v>
       </c>
       <c r="Q17" t="n">
-        <v>8200</v>
+        <v>3540</v>
       </c>
       <c r="R17" t="n">
-        <v>-1000</v>
+        <v>-70000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>급격한 하락 추세 속에서 반등 시도했으나 매수세 실종, 프로그램 매매에 의존한 단기 흐름에 대한 비관론.</t>
+          <t>공매도 금지 지정 속 하락 전망. 9시 20분까지 주포의 말아올림 시도.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['급격한 하락', '매수세 실종', '프로그램 매매']</t>
+          <t>['공매도', '우리기술', '주포']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14810</v>
+        <v>3650</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
-        <v>185</v>
+        <v>83</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>15640</v>
+        <v>3865</v>
       </c>
       <c r="K18" t="n">
-        <v>15600</v>
+        <v>3845</v>
       </c>
       <c r="L18" t="n">
-        <v>15600</v>
+        <v>4075</v>
       </c>
       <c r="M18" t="n">
-        <v>14770</v>
+        <v>3650</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O18" t="n">
-        <v>13906651730</v>
+        <v>38391092992</v>
       </c>
       <c r="P18" t="n">
-        <v>19380</v>
+        <v>4335</v>
       </c>
       <c r="Q18" t="n">
-        <v>3200</v>
+        <v>1246</v>
       </c>
       <c r="R18" t="n">
-        <v>-14000</v>
+        <v>-73000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>금호건설, 호남 반도체 설계 용역 발주 소식과 함께 건설 흑자 및 주가 회복 기대감 언급. 계단식 하락 후 반등 전망.</t>
+          <t>주간 조정 가능성 및 3500원대 하락 전망. 탈모 관련 신규 사업 기대감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['반도체', '건설', '설계용역']</t>
+          <t>['탈모', 'JW신약', '조정']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6460</v>
+        <v>14740</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.83%</t>
+          <t>-5.75%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F19" t="n">
         <v>40</v>
       </c>
       <c r="G19" t="n">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="H19" t="n">
-        <v>15.68</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6860</v>
+        <v>15640</v>
       </c>
       <c r="K19" t="n">
-        <v>6800</v>
+        <v>15600</v>
       </c>
       <c r="L19" t="n">
-        <v>6820</v>
+        <v>15600</v>
       </c>
       <c r="M19" t="n">
-        <v>6400</v>
+        <v>14740</v>
       </c>
       <c r="N19" t="n">
-        <v>16.71</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6546717605</v>
+        <v>15077685360</v>
       </c>
       <c r="P19" t="n">
-        <v>13000</v>
+        <v>19380</v>
       </c>
       <c r="Q19" t="n">
-        <v>6030</v>
+        <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>-131000</v>
+        <v>-14000</v>
       </c>
       <c r="S19" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스, 외국인 매도세와 함께 주가 부진 지속. 분사 및 로봇/반도체 사업 관련 투자 언급.</t>
+          <t>건설 및 반도체 관련 사업 언급. 호남 반도체 설계 용역 발주 및 2030년 반도체 인재 양성 언급, 주가 하락 및 횡보 구간.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['분사', '로봇', '반도체']</t>
+          <t>['건설', '반도체', '용역']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2100</v>
+        <v>6460</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-7.08%</t>
+          <t>-5.83%</t>
         </is>
       </c>
       <c r="D20" t="n">
- 